--- a/data/ARIS.MI.xlsx
+++ b/data/ARIS.MI.xlsx
@@ -28348,7 +28348,7 @@
         <v>158454</v>
       </c>
       <c r="C1217" t="n">
-        <v>3.62199997901917</v>
+        <v>3.62599992752075</v>
       </c>
       <c r="D1217" t="n">
         <v>3.57999992370605</v>
@@ -28360,6 +28360,29 @@
         <v>3.62599992752075</v>
       </c>
       <c r="G1217" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1218" t="n">
+        <v>404539</v>
+      </c>
+      <c r="C1218" t="n">
+        <v>3.62599992752075</v>
+      </c>
+      <c r="D1218" t="n">
+        <v>3.48000001907349</v>
+      </c>
+      <c r="E1218" t="n">
+        <v>3.62599992752075</v>
+      </c>
+      <c r="F1218" t="n">
+        <v>3.53600001335144</v>
+      </c>
+      <c r="G1218" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ARIS.MI.xlsx
+++ b/data/ARIS.MI.xlsx
@@ -28386,6 +28386,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1219">
+      <c r="A1219" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1219" t="n">
+        <v>216945</v>
+      </c>
+      <c r="C1219" t="n">
+        <v>3.5699999332428</v>
+      </c>
+      <c r="D1219" t="n">
+        <v>3.47199988365173</v>
+      </c>
+      <c r="E1219" t="n">
+        <v>3.54999995231628</v>
+      </c>
+      <c r="F1219" t="n">
+        <v>3.55999994277954</v>
+      </c>
+      <c r="G1219" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ARIS.MI.xlsx
+++ b/data/ARIS.MI.xlsx
@@ -28409,6 +28409,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1220">
+      <c r="A1220" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1220" t="n">
+        <v>345437</v>
+      </c>
+      <c r="C1220" t="n">
+        <v>3.65799999237061</v>
+      </c>
+      <c r="D1220" t="n">
+        <v>3.46000003814697</v>
+      </c>
+      <c r="E1220" t="n">
+        <v>3.46000003814697</v>
+      </c>
+      <c r="F1220" t="n">
+        <v>3.62599992752075</v>
+      </c>
+      <c r="G1220" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ARIS.MI.xlsx
+++ b/data/ARIS.MI.xlsx
@@ -28432,6 +28432,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1221">
+      <c r="A1221" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1221" t="n">
+        <v>231942</v>
+      </c>
+      <c r="C1221" t="n">
+        <v>3.72000002861023</v>
+      </c>
+      <c r="D1221" t="n">
+        <v>3.66599988937378</v>
+      </c>
+      <c r="E1221" t="n">
+        <v>3.66799998283386</v>
+      </c>
+      <c r="F1221" t="n">
+        <v>3.69199991226196</v>
+      </c>
+      <c r="G1221" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ARIS.MI.xlsx
+++ b/data/ARIS.MI.xlsx
@@ -28273,22 +28273,22 @@
     </row>
     <row r="1214">
       <c r="A1214" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1214" t="n">
-        <v>118965</v>
+        <v>152126</v>
       </c>
       <c r="C1214" t="n">
-        <v>3.79999995231628</v>
+        <v>3.84400010108948</v>
       </c>
       <c r="D1214" t="n">
-        <v>3.71000003814697</v>
+        <v>3.75</v>
       </c>
       <c r="E1214" t="n">
-        <v>3.79999995231628</v>
+        <v>3.76999998092651</v>
       </c>
       <c r="F1214" t="n">
-        <v>3.75200009346008</v>
+        <v>3.77800011634827</v>
       </c>
       <c r="G1214" t="s">
         <v>7</v>
@@ -28296,22 +28296,22 @@
     </row>
     <row r="1215">
       <c r="A1215" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1215" t="n">
-        <v>423458</v>
+        <v>118965</v>
       </c>
       <c r="C1215" t="n">
-        <v>3.76999998092651</v>
+        <v>3.79999995231628</v>
       </c>
       <c r="D1215" t="n">
-        <v>3.58400011062622</v>
+        <v>3.71000003814697</v>
       </c>
       <c r="E1215" t="n">
-        <v>3.70000004768372</v>
+        <v>3.79999995231628</v>
       </c>
       <c r="F1215" t="n">
-        <v>3.62800002098083</v>
+        <v>3.75200009346008</v>
       </c>
       <c r="G1215" t="s">
         <v>7</v>
@@ -28319,22 +28319,22 @@
     </row>
     <row r="1216">
       <c r="A1216" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1216" t="n">
-        <v>136916</v>
+        <v>423458</v>
       </c>
       <c r="C1216" t="n">
-        <v>3.67000007629395</v>
+        <v>3.76999998092651</v>
       </c>
       <c r="D1216" t="n">
         <v>3.58400011062622</v>
       </c>
       <c r="E1216" t="n">
-        <v>3.67000007629395</v>
+        <v>3.70000004768372</v>
       </c>
       <c r="F1216" t="n">
-        <v>3.59999990463257</v>
+        <v>3.62800002098083</v>
       </c>
       <c r="G1216" t="s">
         <v>7</v>
@@ -28342,22 +28342,22 @@
     </row>
     <row r="1217">
       <c r="A1217" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1217" t="n">
-        <v>158454</v>
+        <v>136916</v>
       </c>
       <c r="C1217" t="n">
-        <v>3.62599992752075</v>
+        <v>3.67000007629395</v>
       </c>
       <c r="D1217" t="n">
-        <v>3.57999992370605</v>
+        <v>3.58400011062622</v>
       </c>
       <c r="E1217" t="n">
-        <v>3.60800004005432</v>
+        <v>3.67000007629395</v>
       </c>
       <c r="F1217" t="n">
-        <v>3.62599992752075</v>
+        <v>3.59999990463257</v>
       </c>
       <c r="G1217" t="s">
         <v>7</v>
@@ -28365,22 +28365,22 @@
     </row>
     <row r="1218">
       <c r="A1218" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1218" t="n">
-        <v>404539</v>
+        <v>158454</v>
       </c>
       <c r="C1218" t="n">
         <v>3.62599992752075</v>
       </c>
       <c r="D1218" t="n">
-        <v>3.48000001907349</v>
+        <v>3.57999992370605</v>
       </c>
       <c r="E1218" t="n">
+        <v>3.60800004005432</v>
+      </c>
+      <c r="F1218" t="n">
         <v>3.62599992752075</v>
-      </c>
-      <c r="F1218" t="n">
-        <v>3.53600001335144</v>
       </c>
       <c r="G1218" t="s">
         <v>7</v>
@@ -28388,22 +28388,22 @@
     </row>
     <row r="1219">
       <c r="A1219" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1219" t="n">
-        <v>216945</v>
+        <v>404539</v>
       </c>
       <c r="C1219" t="n">
-        <v>3.5699999332428</v>
+        <v>3.62599992752075</v>
       </c>
       <c r="D1219" t="n">
-        <v>3.47199988365173</v>
+        <v>3.48000001907349</v>
       </c>
       <c r="E1219" t="n">
-        <v>3.54999995231628</v>
+        <v>3.62599992752075</v>
       </c>
       <c r="F1219" t="n">
-        <v>3.55999994277954</v>
+        <v>3.53600001335144</v>
       </c>
       <c r="G1219" t="s">
         <v>7</v>
@@ -28411,22 +28411,22 @@
     </row>
     <row r="1220">
       <c r="A1220" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1220" t="n">
-        <v>345437</v>
+        <v>216945</v>
       </c>
       <c r="C1220" t="n">
-        <v>3.65799999237061</v>
+        <v>3.5699999332428</v>
       </c>
       <c r="D1220" t="n">
-        <v>3.46000003814697</v>
+        <v>3.47199988365173</v>
       </c>
       <c r="E1220" t="n">
-        <v>3.46000003814697</v>
+        <v>3.54999995231628</v>
       </c>
       <c r="F1220" t="n">
-        <v>3.62599992752075</v>
+        <v>3.55999994277954</v>
       </c>
       <c r="G1220" t="s">
         <v>7</v>
@@ -28434,24 +28434,47 @@
     </row>
     <row r="1221">
       <c r="A1221" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1221" t="n">
-        <v>231942</v>
+        <v>345437</v>
       </c>
       <c r="C1221" t="n">
-        <v>3.72000002861023</v>
+        <v>3.65799999237061</v>
       </c>
       <c r="D1221" t="n">
-        <v>3.66599988937378</v>
+        <v>3.46000003814697</v>
       </c>
       <c r="E1221" t="n">
-        <v>3.66799998283386</v>
+        <v>3.46000003814697</v>
       </c>
       <c r="F1221" t="n">
-        <v>3.69199991226196</v>
+        <v>3.62599992752075</v>
       </c>
       <c r="G1221" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1222" t="n">
+        <v>330700</v>
+      </c>
+      <c r="C1222" t="n">
+        <v>3.68199992179871</v>
+      </c>
+      <c r="D1222" t="n">
+        <v>3.59400010108948</v>
+      </c>
+      <c r="E1222" t="n">
+        <v>3.60999989509583</v>
+      </c>
+      <c r="F1222" t="n">
+        <v>3.61800003051758</v>
+      </c>
+      <c r="G1222" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ARIS.MI.xlsx
+++ b/data/ARIS.MI.xlsx
@@ -473,7 +473,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G4" t="n">
-        <v>9.1745138168335</v>
+        <v>9.17451477050781</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G5" t="n">
-        <v>9.25538539886475</v>
+        <v>9.25538635253906</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G11" t="n">
-        <v>9.23741340637207</v>
+        <v>9.23741436004639</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G20" t="n">
-        <v>9.12958431243896</v>
+        <v>9.12958335876465</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G21" t="n">
-        <v>9.07567119598389</v>
+        <v>9.07567024230957</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G23" t="n">
-        <v>9.07567119598389</v>
+        <v>9.07567024230957</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G24" t="n">
-        <v>9.12958431243896</v>
+        <v>9.12958335876465</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G26" t="n">
-        <v>9.12958431243896</v>
+        <v>9.12958335876465</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G29" t="n">
-        <v>9.74061870574951</v>
+        <v>9.74061965942383</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G32" t="n">
-        <v>9.1745138168335</v>
+        <v>9.17451477050781</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G33" t="n">
-        <v>9.63279056549072</v>
+        <v>9.63279151916504</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G34" t="n">
-        <v>10.0191793441772</v>
+        <v>10.0191783905029</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G42" t="n">
-        <v>9.10262775421143</v>
+        <v>9.10262680053711</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G43" t="n">
-        <v>9.1745138168335</v>
+        <v>9.17451477050781</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G45" t="n">
-        <v>9.04871368408203</v>
+        <v>9.04871273040771</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G52" t="n">
-        <v>9.12958431243896</v>
+        <v>9.12958335876465</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G57" t="n">
-        <v>9.10262775421143</v>
+        <v>9.10262680053711</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G60" t="n">
-        <v>8.95885372161865</v>
+        <v>8.95885467529297</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>8.75</v>
       </c>
       <c r="G64" t="n">
-        <v>7.86258554458618</v>
+        <v>7.86258506774902</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G67" t="n">
-        <v>7.70982599258423</v>
+        <v>7.70982646942139</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G68" t="n">
-        <v>8.03331470489502</v>
+        <v>8.03331565856934</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G69" t="n">
-        <v>7.95244359970093</v>
+        <v>7.95244407653809</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>8.78499984741211</v>
       </c>
       <c r="G75" t="n">
-        <v>7.89403390884399</v>
+        <v>7.89403486251831</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G78" t="n">
-        <v>9.23741340637207</v>
+        <v>9.23741436004639</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G79" t="n">
-        <v>9.08465576171875</v>
+        <v>9.08465480804443</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>9.71500015258789</v>
       </c>
       <c r="G81" t="n">
-        <v>8.72971630096436</v>
+        <v>8.72971725463867</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G82" t="n">
-        <v>9.07567119598389</v>
+        <v>9.07567024230957</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G83" t="n">
-        <v>8.74319458007812</v>
+        <v>8.74319362640381</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G85" t="n">
-        <v>8.6443510055542</v>
+        <v>8.64435005187988</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G87" t="n">
-        <v>8.67130851745605</v>
+        <v>8.67130661010742</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G88" t="n">
-        <v>8.80609607696533</v>
+        <v>8.80609512329102</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G94" t="n">
-        <v>8.18607425689697</v>
+        <v>8.18607330322266</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G96" t="n">
-        <v>8.24897575378418</v>
+        <v>8.24897480010986</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G98" t="n">
-        <v>8.62637901306152</v>
+        <v>8.62637805938721</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G100" t="n">
-        <v>8.80609607696533</v>
+        <v>8.80609512329102</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>9.75</v>
       </c>
       <c r="G101" t="n">
-        <v>8.76116752624512</v>
+        <v>8.7611665725708</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G102" t="n">
-        <v>8.59043502807617</v>
+        <v>8.59043598175049</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>9.71500015258789</v>
       </c>
       <c r="G106" t="n">
-        <v>8.72971630096436</v>
+        <v>8.72971725463867</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G107" t="n">
-        <v>8.67130851745605</v>
+        <v>8.67130661010742</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G110" t="n">
-        <v>7.89852857589722</v>
+        <v>7.89852905273438</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G112" t="n">
-        <v>8.10520267486572</v>
+        <v>8.10520172119141</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G113" t="n">
-        <v>7.99737215042114</v>
+        <v>7.9973726272583</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G115" t="n">
-        <v>7.80867052078247</v>
+        <v>7.80867004394531</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G117" t="n">
-        <v>8.32086086273193</v>
+        <v>8.32086181640625</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G119" t="n">
-        <v>8.62637901306152</v>
+        <v>8.62637805938721</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>8.80609607696533</v>
+        <v>8.80609512329102</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G121" t="n">
-        <v>8.74319458007812</v>
+        <v>8.74319362640381</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G123" t="n">
-        <v>8.96334648132324</v>
+        <v>8.96334743499756</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G127" t="n">
-        <v>9.25042915344238</v>
+        <v>9.25042819976807</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G129" t="n">
-        <v>9.51472759246826</v>
+        <v>9.51472663879395</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G130" t="n">
-        <v>9.35068225860596</v>
+        <v>9.35068035125732</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G131" t="n">
-        <v>9.20486164093018</v>
+        <v>9.20486068725586</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G132" t="n">
-        <v>9.24131679534912</v>
+        <v>9.2413158416748</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G134" t="n">
-        <v>9.24131679534912</v>
+        <v>9.2413158416748</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>10.25</v>
       </c>
       <c r="G135" t="n">
-        <v>9.34156703948975</v>
+        <v>9.34156608581543</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G138" t="n">
-        <v>8.70360565185547</v>
+        <v>8.70360660552979</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G144" t="n">
-        <v>7.6464147567749</v>
+        <v>7.64641427993774</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G146" t="n">
-        <v>7.34566164016724</v>
+        <v>7.34566211700439</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>7.375</v>
       </c>
       <c r="G148" t="n">
-        <v>6.72137117385864</v>
+        <v>6.7213716506958</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G149" t="n">
-        <v>6.8717474937439</v>
+        <v>6.87174797058105</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G151" t="n">
-        <v>7.0266809463501</v>
+        <v>7.02668142318726</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G155" t="n">
-        <v>6.7441554069519</v>
+        <v>6.74415588378906</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G156" t="n">
-        <v>6.68035984039307</v>
+        <v>6.68035936355591</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G157" t="n">
-        <v>6.78061008453369</v>
+        <v>6.78061056137085</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G159" t="n">
-        <v>6.6530179977417</v>
+        <v>6.65301847457886</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G160" t="n">
-        <v>6.68035984039307</v>
+        <v>6.68035936355591</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>7.31500005722046</v>
       </c>
       <c r="G163" t="n">
-        <v>6.66668939590454</v>
+        <v>6.66668891906738</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G164" t="n">
-        <v>6.88086128234863</v>
+        <v>6.88086175918579</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G165" t="n">
-        <v>6.9947829246521</v>
+        <v>6.99478340148926</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G168" t="n">
-        <v>6.9947829246521</v>
+        <v>6.99478340148926</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G170" t="n">
-        <v>6.7441554069519</v>
+        <v>6.74415588378906</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G171" t="n">
-        <v>6.9947829246521</v>
+        <v>6.99478340148926</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>8.20499992370605</v>
       </c>
       <c r="G176" t="n">
-        <v>7.4778094291687</v>
+        <v>7.47780990600586</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G177" t="n">
-        <v>7.46413898468018</v>
+        <v>7.46413946151733</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>8.1850004196167</v>
       </c>
       <c r="G178" t="n">
-        <v>7.45958375930786</v>
+        <v>7.4595832824707</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G180" t="n">
-        <v>7.24996662139893</v>
+        <v>7.24996709823608</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>8</v>
       </c>
       <c r="G181" t="n">
-        <v>7.29097890853882</v>
+        <v>7.29097938537598</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>8</v>
       </c>
       <c r="G182" t="n">
-        <v>7.29097890853882</v>
+        <v>7.29097938537598</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>8</v>
       </c>
       <c r="G184" t="n">
-        <v>7.29097890853882</v>
+        <v>7.29097938537598</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G185" t="n">
-        <v>7.05402183532715</v>
+        <v>7.05402231216431</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>8</v>
       </c>
       <c r="G186" t="n">
-        <v>7.29097890853882</v>
+        <v>7.29097938537598</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G187" t="n">
-        <v>7.30009269714355</v>
+        <v>7.30009317398071</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G188" t="n">
-        <v>7.10870456695557</v>
+        <v>7.10870504379272</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G190" t="n">
-        <v>7.11781787872314</v>
+        <v>7.1178183555603</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G196" t="n">
-        <v>6.85351991653442</v>
+        <v>6.85352039337158</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G199" t="n">
-        <v>6.42517518997192</v>
+        <v>6.42517566680908</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G201" t="n">
-        <v>6.6302342414856</v>
+        <v>6.63023376464844</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>7.75</v>
       </c>
       <c r="G203" t="n">
-        <v>7.06313562393188</v>
+        <v>7.06313610076904</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G204" t="n">
-        <v>6.830735206604</v>
+        <v>6.83073568344116</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>8.46500015258789</v>
       </c>
       <c r="G207" t="n">
-        <v>7.71476697921753</v>
+        <v>7.71476745605469</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>8.40499973297119</v>
       </c>
       <c r="G210" t="n">
-        <v>7.66008472442627</v>
+        <v>7.66008520126343</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G211" t="n">
-        <v>7.70565319061279</v>
+        <v>7.70565366744995</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G212" t="n">
-        <v>7.75577926635742</v>
+        <v>7.75577974319458</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>8.48499965667725</v>
       </c>
       <c r="G215" t="n">
-        <v>7.73299407958984</v>
+        <v>7.732994556427</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G217" t="n">
-        <v>7.93805408477783</v>
+        <v>7.93805360794067</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G218" t="n">
-        <v>8.02007579803467</v>
+        <v>8.02007675170898</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>9.13500022888184</v>
       </c>
       <c r="G219" t="n">
-        <v>8.32538604736328</v>
+        <v>8.3253870010376</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>8.86499977111816</v>
       </c>
       <c r="G223" t="n">
-        <v>8.07931518554688</v>
+        <v>8.07931613922119</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>8.79500007629395</v>
       </c>
       <c r="G224" t="n">
-        <v>8.0155200958252</v>
+        <v>8.01552104949951</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>8.60499954223633</v>
       </c>
       <c r="G229" t="n">
-        <v>7.84235858917236</v>
+        <v>7.84235906600952</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G230" t="n">
-        <v>7.59173154830933</v>
+        <v>7.59173202514648</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>7.48236703872681</v>
+        <v>7.48236751556396</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G233" t="n">
-        <v>7.60084629058838</v>
+        <v>7.60084581375122</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G234" t="n">
-        <v>7.85602951049805</v>
+        <v>7.85602998733521</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G235" t="n">
-        <v>7.81957530975342</v>
+        <v>7.81957483291626</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>8.59500026702881</v>
       </c>
       <c r="G236" t="n">
-        <v>7.83324575424194</v>
+        <v>7.83324670791626</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>8.50500011444092</v>
       </c>
       <c r="G239" t="n">
-        <v>7.75122213363647</v>
+        <v>7.75122261047363</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>8.3149995803833</v>
       </c>
       <c r="G244" t="n">
-        <v>7.57806062698364</v>
+        <v>7.5780611038208</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>8.49499988555908</v>
       </c>
       <c r="G246" t="n">
-        <v>7.74210739135742</v>
+        <v>7.74210786819458</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>8.44499969482422</v>
       </c>
       <c r="G250" t="n">
-        <v>7.6965389251709</v>
+        <v>7.69653940200806</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G251" t="n">
-        <v>7.76489305496216</v>
+        <v>7.76489353179932</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G255" t="n">
-        <v>8.06564617156982</v>
+        <v>8.06564712524414</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G258" t="n">
-        <v>8.34817028045654</v>
+        <v>8.34817123413086</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>9.50500011444092</v>
       </c>
       <c r="G261" t="n">
-        <v>8.66259384155273</v>
+        <v>8.66259479522705</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G262" t="n">
-        <v>8.61246776580811</v>
+        <v>8.61246871948242</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>9.23499965667725</v>
       </c>
       <c r="G265" t="n">
-        <v>8.41652297973633</v>
+        <v>8.41652393341064</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G266" t="n">
-        <v>8.4438648223877</v>
+        <v>8.44386577606201</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G267" t="n">
-        <v>8.61246776580811</v>
+        <v>8.61246871948242</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G270" t="n">
-        <v>8.61246776580811</v>
+        <v>8.61246871948242</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G272" t="n">
-        <v>8.46665000915527</v>
+        <v>8.46664905548096</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G273" t="n">
-        <v>8.40285491943359</v>
+        <v>8.40285396575928</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G274" t="n">
-        <v>8.28437423706055</v>
+        <v>8.28437519073486</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G275" t="n">
-        <v>8.46665000915527</v>
+        <v>8.46664905548096</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G276" t="n">
-        <v>8.45753479003906</v>
+        <v>8.45753574371338</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>9.66499996185303</v>
       </c>
       <c r="G278" t="n">
-        <v>8.8084135055542</v>
+        <v>8.80841445922852</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>9.25500011444092</v>
       </c>
       <c r="G279" t="n">
-        <v>8.43475151062012</v>
+        <v>8.43475246429443</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>9.40499973297119</v>
       </c>
       <c r="G280" t="n">
-        <v>8.57145595550537</v>
+        <v>8.57145690917969</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>9.98499965667725</v>
       </c>
       <c r="G283" t="n">
-        <v>9.10005283355713</v>
+        <v>9.10005378723145</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G286" t="n">
-        <v>9.17751979827881</v>
+        <v>9.17751884460449</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G289" t="n">
-        <v>8.84031200408936</v>
+        <v>8.84031295776367</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G290" t="n">
-        <v>8.70360565185547</v>
+        <v>8.70360660552979</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>9.375</v>
       </c>
       <c r="G293" t="n">
-        <v>8.54411602020264</v>
+        <v>8.54411697387695</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G295" t="n">
-        <v>8.60335445404053</v>
+        <v>8.60335540771484</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G296" t="n">
-        <v>8.63069629669189</v>
+        <v>8.63069725036621</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G297" t="n">
-        <v>8.82208442687988</v>
+        <v>8.8220853805542</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G302" t="n">
-        <v>8.59424114227295</v>
+        <v>8.59424209594727</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>9.61499977111816</v>
       </c>
       <c r="G304" t="n">
-        <v>8.76284503936768</v>
+        <v>8.76284599304199</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>9.66499996185303</v>
       </c>
       <c r="G307" t="n">
-        <v>8.8084135055542</v>
+        <v>8.80841445922852</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>9.61499977111816</v>
       </c>
       <c r="G308" t="n">
-        <v>8.76284503936768</v>
+        <v>8.76284599304199</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G309" t="n">
-        <v>8.59424114227295</v>
+        <v>8.59424209594727</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>9.5649995803833</v>
       </c>
       <c r="G315" t="n">
-        <v>8.71727561950684</v>
+        <v>8.71727657318115</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G317" t="n">
-        <v>8.4438648223877</v>
+        <v>8.44386577606201</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G319" t="n">
-        <v>8.10210037231445</v>
+        <v>8.10210132598877</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G321" t="n">
-        <v>8.26159000396729</v>
+        <v>8.2615909576416</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>9.23499965667725</v>
       </c>
       <c r="G322" t="n">
-        <v>8.41652297973633</v>
+        <v>8.41652393341064</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G326" t="n">
-        <v>8.59424114227295</v>
+        <v>8.59424209594727</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>9.64500045776367</v>
       </c>
       <c r="G327" t="n">
-        <v>8.79018688201904</v>
+        <v>8.79018783569336</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>9.71500015258789</v>
       </c>
       <c r="G328" t="n">
-        <v>8.85398292541504</v>
+        <v>8.85398387908936</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G329" t="n">
-        <v>8.9405632019043</v>
+        <v>8.94056415557861</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>9.58500003814697</v>
       </c>
       <c r="G331" t="n">
-        <v>8.73550319671631</v>
+        <v>8.73550415039062</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G332" t="n">
-        <v>8.49398994445801</v>
+        <v>8.49399089813232</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G333" t="n">
-        <v>8.60335445404053</v>
+        <v>8.60335540771484</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G335" t="n">
-        <v>8.48487663269043</v>
+        <v>8.48487758636475</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G336" t="n">
-        <v>8.60335445404053</v>
+        <v>8.60335540771484</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G337" t="n">
-        <v>8.70360565185547</v>
+        <v>8.70360660552979</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G346" t="n">
-        <v>9.25042915344238</v>
+        <v>9.25042819976807</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G348" t="n">
-        <v>9.1319522857666</v>
+        <v>9.13195133209229</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G353" t="n">
-        <v>8.96790313720703</v>
+        <v>8.96790409088135</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G357" t="n">
-        <v>9.16840553283691</v>
+        <v>9.16840648651123</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G358" t="n">
-        <v>9.46916007995605</v>
+        <v>9.46915912628174</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>10.3699998855591</v>
       </c>
       <c r="G362" t="n">
-        <v>9.45093059539795</v>
+        <v>9.45093154907227</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G363" t="n">
-        <v>9.70611572265625</v>
+        <v>9.70611476898193</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G364" t="n">
-        <v>9.42359066009521</v>
+        <v>9.4235897064209</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G365" t="n">
-        <v>9.33245182037354</v>
+        <v>9.33245277404785</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>9.83500003814697</v>
       </c>
       <c r="G366" t="n">
-        <v>8.96334743499756</v>
+        <v>8.96334838867188</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>9.40499973297119</v>
       </c>
       <c r="G370" t="n">
-        <v>8.57145595550537</v>
+        <v>8.57145690917969</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>9.47500038146973</v>
       </c>
       <c r="G371" t="n">
-        <v>8.63525295257568</v>
+        <v>8.63525390625</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G374" t="n">
-        <v>9.10461044311523</v>
+        <v>9.10460948944092</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G378" t="n">
-        <v>9.09549522399902</v>
+        <v>9.09549617767334</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>10.25</v>
       </c>
       <c r="G385" t="n">
-        <v>9.46485710144043</v>
+        <v>9.46485614776611</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G386" t="n">
-        <v>9.43715476989746</v>
+        <v>9.43715572357178</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G387" t="n">
-        <v>9.54796314239502</v>
+        <v>9.5479621887207</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G389" t="n">
-        <v>9.64030265808105</v>
+        <v>9.64030170440674</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G390" t="n">
-        <v>9.78804683685303</v>
+        <v>9.78804779052734</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G392" t="n">
-        <v>9.64030265808105</v>
+        <v>9.64030170440674</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G394" t="n">
-        <v>9.84345054626465</v>
+        <v>9.84345149993896</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G397" t="n">
-        <v>9.56643009185791</v>
+        <v>9.56643104553223</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G405" t="n">
-        <v>8.58762550354004</v>
+        <v>8.58762645721436</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>9.55500030517578</v>
       </c>
       <c r="G407" t="n">
-        <v>8.82309341430664</v>
+        <v>8.82309246063232</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G409" t="n">
-        <v>8.71690082550049</v>
+        <v>8.7169017791748</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G410" t="n">
-        <v>8.64302921295166</v>
+        <v>8.64303016662598</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G413" t="n">
-        <v>8.42141342163086</v>
+        <v>8.42141437530518</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G414" t="n">
-        <v>8.50452041625977</v>
+        <v>8.50451946258545</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>9.21500015258789</v>
       </c>
       <c r="G415" t="n">
-        <v>8.50913619995117</v>
+        <v>8.50913715362549</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G416" t="n">
-        <v>8.67073154449463</v>
+        <v>8.67073249816895</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G419" t="n">
-        <v>8.57839202880859</v>
+        <v>8.57839298248291</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G423" t="n">
-        <v>8.0382022857666</v>
+        <v>8.03820323944092</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G424" t="n">
-        <v>8.0520544052124</v>
+        <v>8.05205345153809</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>8.54500007629395</v>
       </c>
       <c r="G425" t="n">
-        <v>7.89045906066895</v>
+        <v>7.89045858383179</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G426" t="n">
-        <v>7.92277717590332</v>
+        <v>7.92277669906616</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G427" t="n">
-        <v>7.82120323181152</v>
+        <v>7.82120370864868</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G428" t="n">
-        <v>7.82120323181152</v>
+        <v>7.82120370864868</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>8.46500015258789</v>
       </c>
       <c r="G429" t="n">
-        <v>7.81658697128296</v>
+        <v>7.8165864944458</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G430" t="n">
-        <v>7.8766074180603</v>
+        <v>7.87660694122314</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G431" t="n">
-        <v>7.81196975708008</v>
+        <v>7.81196928024292</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G434" t="n">
-        <v>7.2579288482666</v>
+        <v>7.25792932510376</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G437" t="n">
-        <v>7.16558885574341</v>
+        <v>7.16558933258057</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G439" t="n">
-        <v>7.12403631210327</v>
+        <v>7.12403583526611</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G440" t="n">
-        <v>6.90703725814819</v>
+        <v>6.90703678131104</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G441" t="n">
-        <v>6.90241956710815</v>
+        <v>6.90242004394531</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>7.02500009536743</v>
       </c>
       <c r="G445" t="n">
-        <v>6.48688983917236</v>
+        <v>6.48688936233521</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G449" t="n">
-        <v>6.90241956710815</v>
+        <v>6.90242004394531</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G451" t="n">
-        <v>6.71312284469604</v>
+        <v>6.71312236785889</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G452" t="n">
-        <v>6.55614423751831</v>
+        <v>6.55614471435547</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G453" t="n">
-        <v>6.88856840133667</v>
+        <v>6.88856887817383</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>7.40500020980835</v>
       </c>
       <c r="G454" t="n">
-        <v>6.83778190612793</v>
+        <v>6.83778142929077</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>7.09499979019165</v>
       </c>
       <c r="G458" t="n">
-        <v>6.55152750015259</v>
+        <v>6.55152702331543</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G459" t="n">
-        <v>6.55614423751831</v>
+        <v>6.55614471435547</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G461" t="n">
-        <v>6.37146472930908</v>
+        <v>6.37146425247192</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G462" t="n">
-        <v>6.37146472930908</v>
+        <v>6.37146425247192</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G466" t="n">
-        <v>5.80818939208984</v>
+        <v>5.808189868927</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>5.84499979019165</v>
       </c>
       <c r="G469" t="n">
-        <v>5.39727687835693</v>
+        <v>5.39727640151978</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>6.16499996185303</v>
       </c>
       <c r="G472" t="n">
-        <v>5.69276475906372</v>
+        <v>5.69276523590088</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G473" t="n">
-        <v>5.59580755233765</v>
+        <v>5.5958080291748</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>5.82499980926514</v>
       </c>
       <c r="G475" t="n">
-        <v>5.37880849838257</v>
+        <v>5.37880897521973</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G479" t="n">
-        <v>5.70661544799805</v>
+        <v>5.70661592483521</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>5.86499977111816</v>
       </c>
       <c r="G481" t="n">
-        <v>5.41574430465698</v>
+        <v>5.41574478149414</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G482" t="n">
-        <v>5.18951177597046</v>
+        <v>5.1895112991333</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G483" t="n">
-        <v>5.18951177597046</v>
+        <v>5.1895112991333</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G485" t="n">
-        <v>5.17566108703613</v>
+        <v>5.17566013336182</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>5.45499992370605</v>
       </c>
       <c r="G489" t="n">
-        <v>5.03715085983276</v>
+        <v>5.03715038299561</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G494" t="n">
-        <v>4.88478946685791</v>
+        <v>4.88478899002075</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G495" t="n">
-        <v>4.88940668106079</v>
+        <v>4.88940620422363</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G496" t="n">
-        <v>5.13410711288452</v>
+        <v>5.13410758972168</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G505" t="n">
-        <v>5.39266014099121</v>
+        <v>5.39265966415405</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G510" t="n">
-        <v>5.21259641647339</v>
+        <v>5.21259689331055</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>5.65500020980835</v>
       </c>
       <c r="G511" t="n">
-        <v>5.22183036804199</v>
+        <v>5.22183084487915</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>5.65500020980835</v>
       </c>
       <c r="G512" t="n">
-        <v>5.22183036804199</v>
+        <v>5.22183084487915</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G513" t="n">
-        <v>5.21259641647339</v>
+        <v>5.21259689331055</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G515" t="n">
-        <v>5.11563968658447</v>
+        <v>5.11563920974731</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G519" t="n">
-        <v>5.25414991378784</v>
+        <v>5.25414943695068</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>5.65500020980835</v>
       </c>
       <c r="G521" t="n">
-        <v>5.22183036804199</v>
+        <v>5.22183084487915</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>6.03499984741211</v>
       </c>
       <c r="G527" t="n">
-        <v>5.57272291183472</v>
+        <v>5.57272243499756</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>6.30499982833862</v>
       </c>
       <c r="G532" t="n">
-        <v>5.82204103469849</v>
+        <v>5.82204055786133</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>6.40500020980835</v>
       </c>
       <c r="G533" t="n">
-        <v>5.91438150405884</v>
+        <v>5.91438102722168</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>6.33500003814697</v>
       </c>
       <c r="G534" t="n">
-        <v>5.84974336624146</v>
+        <v>5.8497428894043</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>6.2649998664856</v>
       </c>
       <c r="G535" t="n">
-        <v>5.78510475158691</v>
+        <v>5.78510522842407</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>6.38500022888184</v>
       </c>
       <c r="G539" t="n">
-        <v>5.89591312408447</v>
+        <v>5.89591360092163</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G544" t="n">
-        <v>5.86359405517578</v>
+        <v>5.86359357833862</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G549" t="n">
-        <v>5.56810569763184</v>
+        <v>5.56810617446899</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G551" t="n">
-        <v>5.70661544799805</v>
+        <v>5.70661592483521</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G552" t="n">
-        <v>5.70661544799805</v>
+        <v>5.70661592483521</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>6.22499990463257</v>
       </c>
       <c r="G553" t="n">
-        <v>5.74816942214966</v>
+        <v>5.7481689453125</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>6.29500007629395</v>
       </c>
       <c r="G554" t="n">
-        <v>5.81280708312988</v>
+        <v>5.81280755996704</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>6.06500005722046</v>
       </c>
       <c r="G556" t="n">
-        <v>5.60042524337769</v>
+        <v>5.60042476654053</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>6.0149998664856</v>
       </c>
       <c r="G558" t="n">
-        <v>5.55425453186035</v>
+        <v>5.55425500869751</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G559" t="n">
-        <v>5.56810569763184</v>
+        <v>5.56810617446899</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G560" t="n">
-        <v>5.36495733261108</v>
+        <v>5.36495780944824</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G562" t="n">
-        <v>5.36495733261108</v>
+        <v>5.36495780944824</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G568" t="n">
-        <v>5.32802200317383</v>
+        <v>5.32802152633667</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G571" t="n">
-        <v>5.17566108703613</v>
+        <v>5.17566013336182</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G572" t="n">
-        <v>5.24029922485352</v>
+        <v>5.24029874801636</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G573" t="n">
-        <v>5.32802200317383</v>
+        <v>5.32802152633667</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G575" t="n">
-        <v>5.13410711288452</v>
+        <v>5.13410758972168</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>5.45499992370605</v>
       </c>
       <c r="G581" t="n">
-        <v>5.03715085983276</v>
+        <v>5.03715038299561</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G586" t="n">
-        <v>5.56810569763184</v>
+        <v>5.56810617446899</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G587" t="n">
-        <v>5.57733964920044</v>
+        <v>5.57733917236328</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G588" t="n">
-        <v>5.59580755233765</v>
+        <v>5.5958080291748</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>6.06500005722046</v>
       </c>
       <c r="G589" t="n">
-        <v>5.60042524337769</v>
+        <v>5.60042476654053</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>5.53499984741211</v>
       </c>
       <c r="G591" t="n">
-        <v>5.11102247238159</v>
+        <v>5.11102199554443</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G593" t="n">
-        <v>5.39266014099121</v>
+        <v>5.39265966415405</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G594" t="n">
-        <v>5.05100154876709</v>
+        <v>5.05100107192993</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>4.92172527313232</v>
+        <v>4.92172574996948</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G601" t="n">
-        <v>4.77398157119751</v>
+        <v>4.77398109436035</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G603" t="n">
-        <v>4.89864063262939</v>
+        <v>4.89864015579224</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>4.82200002670288</v>
       </c>
       <c r="G608" t="n">
-        <v>4.45263814926147</v>
+        <v>4.45263767242432</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>4.70800018310547</v>
       </c>
       <c r="G609" t="n">
-        <v>4.34737014770508</v>
+        <v>4.34737062454224</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>4.66400003433228</v>
       </c>
       <c r="G610" t="n">
-        <v>4.30674076080322</v>
+        <v>4.30674028396606</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G612" t="n">
-        <v>4.35845041275024</v>
+        <v>4.3584508895874</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G613" t="n">
-        <v>4.37691926956177</v>
+        <v>4.37691879272461</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G615" t="n">
-        <v>4.37691926956177</v>
+        <v>4.37691879272461</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>4.96600008010864</v>
       </c>
       <c r="G617" t="n">
-        <v>4.58560752868652</v>
+        <v>4.58560800552368</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>5</v>
       </c>
       <c r="G618" t="n">
-        <v>4.61700344085693</v>
+        <v>4.61700296401978</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G619" t="n">
-        <v>4.46741199493408</v>
+        <v>4.46741247177124</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G623" t="n">
-        <v>4.79706621170044</v>
+        <v>4.7970666885376</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>4.97800016403198</v>
       </c>
       <c r="G627" t="n">
-        <v>4.59668874740601</v>
+        <v>4.59668827056885</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>5.0149998664856</v>
       </c>
       <c r="G630" t="n">
-        <v>4.63085412979126</v>
+        <v>4.6308536529541</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>4.94199991226196</v>
       </c>
       <c r="G631" t="n">
-        <v>4.56344604492188</v>
+        <v>4.56344556808472</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -32181,7 +32181,7 @@
         <v>508131</v>
       </c>
       <c r="C1224" t="n">
-        <v>3.76200008392334</v>
+        <v>3.79399991035461</v>
       </c>
       <c r="D1224" t="n">
         <v>3.61800003051758</v>
@@ -32196,6 +32196,32 @@
         <v>3.79399991035461</v>
       </c>
       <c r="H1224" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1225" t="n">
+        <v>1492907</v>
+      </c>
+      <c r="C1225" t="n">
+        <v>3.95000004768372</v>
+      </c>
+      <c r="D1225" t="n">
+        <v>3.76399993896484</v>
+      </c>
+      <c r="E1225" t="n">
+        <v>3.79399991035461</v>
+      </c>
+      <c r="F1225" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="G1225" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="H1225" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ARIS.MI.xlsx
+++ b/data/ARIS.MI.xlsx
@@ -473,7 +473,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G4" t="n">
-        <v>9.17451477050781</v>
+        <v>9.1745138168335</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G6" t="n">
-        <v>9.20147037506104</v>
+        <v>9.20147132873535</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G7" t="n">
-        <v>9.20147037506104</v>
+        <v>9.20147132873535</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G8" t="n">
-        <v>9.20147037506104</v>
+        <v>9.20147132873535</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G9" t="n">
-        <v>9.21944332122803</v>
+        <v>9.21944236755371</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G10" t="n">
-        <v>9.20147037506104</v>
+        <v>9.20147132873535</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G11" t="n">
-        <v>9.23741436004639</v>
+        <v>9.23741340637207</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G12" t="n">
-        <v>9.20147037506104</v>
+        <v>9.20147132873535</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G13" t="n">
-        <v>9.20147037506104</v>
+        <v>9.20147132873535</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G14" t="n">
-        <v>9.20147037506104</v>
+        <v>9.20147132873535</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G15" t="n">
-        <v>9.21944332122803</v>
+        <v>9.21944236755371</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G16" t="n">
-        <v>8.92291069030762</v>
+        <v>8.92291164398193</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G20" t="n">
-        <v>9.12958335876465</v>
+        <v>9.12958431243896</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G22" t="n">
-        <v>8.85102462768555</v>
+        <v>8.85102367401123</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G24" t="n">
-        <v>9.12958335876465</v>
+        <v>9.12958431243896</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G25" t="n">
-        <v>9.11161422729492</v>
+        <v>9.11161327362061</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G26" t="n">
-        <v>9.12958335876465</v>
+        <v>9.12958431243896</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G27" t="n">
-        <v>9.50698947906494</v>
+        <v>9.50698757171631</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G32" t="n">
-        <v>9.17451477050781</v>
+        <v>9.1745138168335</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G33" t="n">
-        <v>9.63279151916504</v>
+        <v>9.63279056549072</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G34" t="n">
-        <v>10.0191783905029</v>
+        <v>10.0191793441772</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>10.9899997711182</v>
       </c>
       <c r="G35" t="n">
-        <v>9.87540626525879</v>
+        <v>9.87540721893311</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G38" t="n">
-        <v>9.72264862060547</v>
+        <v>9.72264766693115</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G40" t="n">
-        <v>9.67772006988525</v>
+        <v>9.67771911621094</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G43" t="n">
-        <v>9.17451477050781</v>
+        <v>9.1745138168335</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G45" t="n">
-        <v>9.04871273040771</v>
+        <v>9.0487117767334</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G46" t="n">
-        <v>9.20147037506104</v>
+        <v>9.20147132873535</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>10.4899997711182</v>
       </c>
       <c r="G48" t="n">
-        <v>9.42611598968506</v>
+        <v>9.42611694335938</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G50" t="n">
-        <v>9.11161422729492</v>
+        <v>9.11161327362061</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G51" t="n">
-        <v>9.16552734375</v>
+        <v>9.16552829742432</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G52" t="n">
-        <v>9.12958335876465</v>
+        <v>9.12958431243896</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G54" t="n">
-        <v>9.16552734375</v>
+        <v>9.16552829742432</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>9.20499992370605</v>
       </c>
       <c r="G66" t="n">
-        <v>8.27144050598145</v>
+        <v>8.27143955230713</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G69" t="n">
-        <v>7.95244407653809</v>
+        <v>7.95244312286377</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G72" t="n">
-        <v>7.42228078842163</v>
+        <v>7.42228031158447</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G73" t="n">
-        <v>7.79069948196411</v>
+        <v>7.79069900512695</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>8.3149995803833</v>
       </c>
       <c r="G74" t="n">
-        <v>7.47170209884644</v>
+        <v>7.47170162200928</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>8.78499984741211</v>
       </c>
       <c r="G75" t="n">
-        <v>7.89403486251831</v>
+        <v>7.89403533935547</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G76" t="n">
-        <v>8.66232204437256</v>
+        <v>8.66232299804688</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>9.51500034332275</v>
       </c>
       <c r="G77" t="n">
-        <v>8.55000019073486</v>
+        <v>8.54999923706055</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G78" t="n">
-        <v>9.23741436004639</v>
+        <v>9.23741340637207</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G79" t="n">
-        <v>9.08465480804443</v>
+        <v>9.08465576171875</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>9.71500015258789</v>
       </c>
       <c r="G81" t="n">
-        <v>8.72971725463867</v>
+        <v>8.72971630096436</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G83" t="n">
-        <v>8.74319362640381</v>
+        <v>8.74319458007812</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>9.48499965667725</v>
       </c>
       <c r="G84" t="n">
-        <v>8.52304267883301</v>
+        <v>8.52304172515869</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G85" t="n">
-        <v>8.64435005187988</v>
+        <v>8.64435195922852</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G86" t="n">
-        <v>8.55898571014404</v>
+        <v>8.55898475646973</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G87" t="n">
-        <v>8.67130661010742</v>
+        <v>8.67130756378174</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G88" t="n">
-        <v>8.80609512329102</v>
+        <v>8.80609607696533</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G90" t="n">
-        <v>8.55898571014404</v>
+        <v>8.55898475646973</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G94" t="n">
-        <v>8.18607330322266</v>
+        <v>8.18607425689697</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G98" t="n">
-        <v>8.62637805938721</v>
+        <v>8.62637996673584</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G100" t="n">
-        <v>8.80609512329102</v>
+        <v>8.80609607696533</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>9.75</v>
       </c>
       <c r="G101" t="n">
-        <v>8.7611665725708</v>
+        <v>8.76116561889648</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G105" t="n">
-        <v>8.55898571014404</v>
+        <v>8.55898475646973</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>9.71500015258789</v>
       </c>
       <c r="G106" t="n">
-        <v>8.72971725463867</v>
+        <v>8.72971630096436</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G107" t="n">
-        <v>8.67130661010742</v>
+        <v>8.67130756378174</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G110" t="n">
-        <v>7.89852905273438</v>
+        <v>7.89852857589722</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G112" t="n">
-        <v>8.10520172119141</v>
+        <v>8.10520267486572</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G113" t="n">
-        <v>7.9973726272583</v>
+        <v>7.99737215042114</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>8.6850004196167</v>
       </c>
       <c r="G114" t="n">
-        <v>7.80417728424072</v>
+        <v>7.80417823791504</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G115" t="n">
-        <v>7.80867004394531</v>
+        <v>7.80867147445679</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>9.02499961853027</v>
       </c>
       <c r="G116" t="n">
-        <v>8.109694480896</v>
+        <v>8.10969352722168</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G118" t="n">
-        <v>8.54550743103027</v>
+        <v>8.54550647735596</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G119" t="n">
-        <v>8.62637805938721</v>
+        <v>8.62637996673584</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>8.80609512329102</v>
+        <v>8.80609607696533</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G121" t="n">
-        <v>8.74319362640381</v>
+        <v>8.74319458007812</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>9.94499969482422</v>
       </c>
       <c r="G122" t="n">
-        <v>8.93638896942139</v>
+        <v>8.9363899230957</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G123" t="n">
-        <v>8.96334743499756</v>
+        <v>8.96334838867188</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>9.78499984741211</v>
       </c>
       <c r="G124" t="n">
-        <v>8.91777896881104</v>
+        <v>8.91777801513672</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>9.82499980926514</v>
       </c>
       <c r="G125" t="n">
-        <v>8.95423316955566</v>
+        <v>8.95423221588135</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G126" t="n">
-        <v>8.93144989013672</v>
+        <v>8.9314489364624</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G127" t="n">
-        <v>9.25042819976807</v>
+        <v>9.2504301071167</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>9.478271484375</v>
+        <v>9.47827243804932</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G130" t="n">
-        <v>9.35068035125732</v>
+        <v>9.35068130493164</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G138" t="n">
-        <v>8.70360660552979</v>
+        <v>8.70360565185547</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G139" t="n">
-        <v>8.52133274078369</v>
+        <v>8.52133178710938</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G140" t="n">
-        <v>7.95628118515015</v>
+        <v>7.95628070831299</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G142" t="n">
-        <v>7.61907243728638</v>
+        <v>7.61907291412354</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G144" t="n">
-        <v>7.64641427993774</v>
+        <v>7.6464147567749</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G145" t="n">
-        <v>7.47325372695923</v>
+        <v>7.47325325012207</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G146" t="n">
-        <v>7.34566211700439</v>
+        <v>7.34566164016724</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>7.50500011444092</v>
       </c>
       <c r="G147" t="n">
-        <v>6.8398494720459</v>
+        <v>6.83984994888306</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>7.375</v>
       </c>
       <c r="G148" t="n">
-        <v>6.7213716506958</v>
+        <v>6.72137117385864</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G149" t="n">
-        <v>6.87174797058105</v>
+        <v>6.87174701690674</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>7.82499980926514</v>
       </c>
       <c r="G150" t="n">
-        <v>7.13148880004883</v>
+        <v>7.13148927688599</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G151" t="n">
-        <v>7.02668142318726</v>
+        <v>7.0266809463501</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>7.81500005722046</v>
       </c>
       <c r="G152" t="n">
-        <v>7.12237501144409</v>
+        <v>7.12237548828125</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>7.625</v>
       </c>
       <c r="G154" t="n">
-        <v>6.94921445846558</v>
+        <v>6.94921350479126</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G155" t="n">
-        <v>6.74415588378906</v>
+        <v>6.7441554069519</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G157" t="n">
-        <v>6.78061056137085</v>
+        <v>6.78061008453369</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G158" t="n">
-        <v>6.92642974853516</v>
+        <v>6.92643022537231</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G161" t="n">
-        <v>6.64846134185791</v>
+        <v>6.64846181869507</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>7.31500005722046</v>
       </c>
       <c r="G163" t="n">
-        <v>6.66668891906738</v>
+        <v>6.66668844223022</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G165" t="n">
-        <v>6.99478340148926</v>
+        <v>6.9947829246521</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G168" t="n">
-        <v>6.99478340148926</v>
+        <v>6.9947829246521</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>7.72499990463257</v>
       </c>
       <c r="G169" t="n">
-        <v>7.04035139083862</v>
+        <v>7.04035186767578</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G170" t="n">
-        <v>6.74415588378906</v>
+        <v>6.7441554069519</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G171" t="n">
-        <v>6.99478340148926</v>
+        <v>6.9947829246521</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G174" t="n">
-        <v>7.47325372695923</v>
+        <v>7.47325325012207</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G175" t="n">
-        <v>7.61907243728638</v>
+        <v>7.61907291412354</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>8</v>
       </c>
       <c r="G181" t="n">
-        <v>7.29097938537598</v>
+        <v>7.29097890853882</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>8</v>
       </c>
       <c r="G182" t="n">
-        <v>7.29097938537598</v>
+        <v>7.29097890853882</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>8</v>
       </c>
       <c r="G184" t="n">
-        <v>7.29097938537598</v>
+        <v>7.29097890853882</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G185" t="n">
-        <v>7.05402231216431</v>
+        <v>7.05402183532715</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>8</v>
       </c>
       <c r="G186" t="n">
-        <v>7.29097938537598</v>
+        <v>7.29097890853882</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G188" t="n">
-        <v>7.10870504379272</v>
+        <v>7.10870456695557</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>7.625</v>
       </c>
       <c r="G194" t="n">
-        <v>6.94921445846558</v>
+        <v>6.94921350479126</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G197" t="n">
-        <v>6.92642974853516</v>
+        <v>6.92643022537231</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G198" t="n">
-        <v>6.56188058853149</v>
+        <v>6.56188106536865</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>7.52500009536743</v>
       </c>
       <c r="G202" t="n">
-        <v>6.85807704925537</v>
+        <v>6.85807657241821</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>7.75</v>
       </c>
       <c r="G203" t="n">
-        <v>7.06313610076904</v>
+        <v>7.06313562393188</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>7.33500003814697</v>
       </c>
       <c r="G205" t="n">
-        <v>6.6849160194397</v>
+        <v>6.68491649627686</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G206" t="n">
-        <v>6.69858646392822</v>
+        <v>6.69858694076538</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>8.46500015258789</v>
       </c>
       <c r="G207" t="n">
-        <v>7.71476745605469</v>
+        <v>7.71476650238037</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G208" t="n">
-        <v>7.55527687072754</v>
+        <v>7.5552773475647</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>8.33500003814697</v>
       </c>
       <c r="G209" t="n">
-        <v>7.59628868103027</v>
+        <v>7.59628915786743</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>8.40499973297119</v>
       </c>
       <c r="G210" t="n">
-        <v>7.66008520126343</v>
+        <v>7.66008472442627</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G211" t="n">
-        <v>7.70565366744995</v>
+        <v>7.70565271377563</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G212" t="n">
-        <v>7.75577974319458</v>
+        <v>7.75577878952026</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G217" t="n">
-        <v>7.93805360794067</v>
+        <v>7.93805313110352</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>9.13500022888184</v>
       </c>
       <c r="G219" t="n">
-        <v>8.3253870010376</v>
+        <v>8.32538795471191</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>8.86499977111816</v>
       </c>
       <c r="G223" t="n">
-        <v>8.07931613922119</v>
+        <v>8.07931518554688</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>8.79500007629395</v>
       </c>
       <c r="G224" t="n">
-        <v>8.01552104949951</v>
+        <v>8.0155200958252</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G228" t="n">
-        <v>7.71932458877563</v>
+        <v>7.71932363510132</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>8.60499954223633</v>
       </c>
       <c r="G229" t="n">
-        <v>7.84235906600952</v>
+        <v>7.84235954284668</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>7.48236751556396</v>
+        <v>7.48236703872681</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G232" t="n">
-        <v>7.5416054725647</v>
+        <v>7.54160642623901</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G234" t="n">
-        <v>7.85602998733521</v>
+        <v>7.85603046417236</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>8.59500026702881</v>
       </c>
       <c r="G236" t="n">
-        <v>7.83324670791626</v>
+        <v>7.83324575424194</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>8.63500022888184</v>
       </c>
       <c r="G237" t="n">
-        <v>7.86970090866089</v>
+        <v>7.86970043182373</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>8.50500011444092</v>
       </c>
       <c r="G239" t="n">
-        <v>7.75122261047363</v>
+        <v>7.75122213363647</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G240" t="n">
-        <v>7.61907243728638</v>
+        <v>7.61907291412354</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G242" t="n">
-        <v>7.20895528793335</v>
+        <v>7.20895576477051</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>8.15499973297119</v>
       </c>
       <c r="G245" t="n">
-        <v>7.43224143981934</v>
+        <v>7.43224096298218</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>8.49499988555908</v>
       </c>
       <c r="G246" t="n">
-        <v>7.74210786819458</v>
+        <v>7.74210834503174</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G251" t="n">
-        <v>7.76489353179932</v>
+        <v>7.76489305496216</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G252" t="n">
-        <v>7.87425756454468</v>
+        <v>7.87425661087036</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>8.64500045776367</v>
       </c>
       <c r="G254" t="n">
-        <v>7.87881565093994</v>
+        <v>7.87881374359131</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G255" t="n">
-        <v>8.06564712524414</v>
+        <v>8.06564521789551</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>9.08500003814697</v>
       </c>
       <c r="G256" t="n">
-        <v>8.27981853485107</v>
+        <v>8.27981758117676</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G257" t="n">
-        <v>8.3800687789917</v>
+        <v>8.38006782531738</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G258" t="n">
-        <v>8.34817123413086</v>
+        <v>8.34817028045654</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G262" t="n">
-        <v>8.61246871948242</v>
+        <v>8.61246967315674</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G266" t="n">
-        <v>8.44386577606201</v>
+        <v>8.44386386871338</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G267" t="n">
-        <v>8.61246871948242</v>
+        <v>8.61246967315674</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G268" t="n">
-        <v>8.42108154296875</v>
+        <v>8.42108058929443</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G270" t="n">
-        <v>8.61246871948242</v>
+        <v>8.61246967315674</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G272" t="n">
-        <v>8.46664905548096</v>
+        <v>8.46665000915527</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G275" t="n">
-        <v>8.46664905548096</v>
+        <v>8.46665000915527</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G276" t="n">
-        <v>8.45753574371338</v>
+        <v>8.45753383636475</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G277" t="n">
-        <v>8.52133274078369</v>
+        <v>8.52133178710938</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>9.25500011444092</v>
       </c>
       <c r="G279" t="n">
-        <v>8.43475246429443</v>
+        <v>8.4347505569458</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>9.625</v>
       </c>
       <c r="G282" t="n">
-        <v>8.77195930480957</v>
+        <v>8.77195835113525</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>9.98499965667725</v>
       </c>
       <c r="G283" t="n">
-        <v>9.10005378723145</v>
+        <v>9.10005187988281</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G286" t="n">
-        <v>9.17751884460449</v>
+        <v>9.17751979827881</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G289" t="n">
-        <v>8.84031295776367</v>
+        <v>8.84031200408936</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G290" t="n">
-        <v>8.70360660552979</v>
+        <v>8.70360565185547</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>9.375</v>
       </c>
       <c r="G293" t="n">
-        <v>8.54411697387695</v>
+        <v>8.54411506652832</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G295" t="n">
-        <v>8.60335540771484</v>
+        <v>8.60335445404053</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G296" t="n">
-        <v>8.63069725036621</v>
+        <v>8.63069629669189</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G297" t="n">
-        <v>8.8220853805542</v>
+        <v>8.82208442687988</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G298" t="n">
-        <v>9.04992771148682</v>
+        <v>9.04992866516113</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>9.875</v>
       </c>
       <c r="G299" t="n">
-        <v>8.9998025894165</v>
+        <v>8.99980163574219</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>9.625</v>
       </c>
       <c r="G301" t="n">
-        <v>8.77195930480957</v>
+        <v>8.77195835113525</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G303" t="n">
-        <v>8.67626476287842</v>
+        <v>8.67626571655273</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>9.61499977111816</v>
       </c>
       <c r="G304" t="n">
-        <v>8.76284599304199</v>
+        <v>8.76284503936768</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>9.61499977111816</v>
       </c>
       <c r="G308" t="n">
-        <v>8.76284599304199</v>
+        <v>8.76284503936768</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G314" t="n">
-        <v>8.93144989013672</v>
+        <v>8.9314489364624</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>9.5649995803833</v>
       </c>
       <c r="G315" t="n">
-        <v>8.71727657318115</v>
+        <v>8.71727561950684</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G317" t="n">
-        <v>8.44386577606201</v>
+        <v>8.44386386871338</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G319" t="n">
-        <v>8.10210132598877</v>
+        <v>8.10210037231445</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>9.01500034332275</v>
       </c>
       <c r="G320" t="n">
-        <v>8.21602249145508</v>
+        <v>8.21602153778076</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G321" t="n">
-        <v>8.2615909576416</v>
+        <v>8.26158905029297</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G324" t="n">
-        <v>8.23880577087402</v>
+        <v>8.23880672454834</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>9.6850004196167</v>
       </c>
       <c r="G325" t="n">
-        <v>8.82664203643799</v>
+        <v>8.82664108276367</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>9.64500045776367</v>
       </c>
       <c r="G327" t="n">
-        <v>8.79018783569336</v>
+        <v>8.79018688201904</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>9.71500015258789</v>
       </c>
       <c r="G328" t="n">
-        <v>8.85398387908936</v>
+        <v>8.85398292541504</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G329" t="n">
-        <v>8.94056415557861</v>
+        <v>8.94056224822998</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G333" t="n">
-        <v>8.60335540771484</v>
+        <v>8.60335445404053</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G334" t="n">
-        <v>8.37551212310791</v>
+        <v>8.37551116943359</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G336" t="n">
-        <v>8.60335540771484</v>
+        <v>8.60335445404053</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G337" t="n">
-        <v>8.70360660552979</v>
+        <v>8.70360565185547</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>9.59500026702881</v>
       </c>
       <c r="G338" t="n">
-        <v>8.74461841583252</v>
+        <v>8.7446174621582</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>9.36499977111816</v>
       </c>
       <c r="G339" t="n">
-        <v>8.53500175476074</v>
+        <v>8.53500080108643</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G341" t="n">
-        <v>8.42108154296875</v>
+        <v>8.42108058929443</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G343" t="n">
-        <v>8.53955936431885</v>
+        <v>8.53955841064453</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G346" t="n">
-        <v>9.25042819976807</v>
+        <v>9.2504301071167</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G347" t="n">
-        <v>9.478271484375</v>
+        <v>9.47827243804932</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G348" t="n">
-        <v>9.13195133209229</v>
+        <v>9.1319522857666</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>9.8149995803833</v>
       </c>
       <c r="G351" t="n">
-        <v>8.94511985778809</v>
+        <v>8.94511890411377</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G354" t="n">
-        <v>9.02258682250977</v>
+        <v>9.02258586883545</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G356" t="n">
-        <v>9.02258682250977</v>
+        <v>9.02258586883545</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G361" t="n">
-        <v>9.478271484375</v>
+        <v>9.47827243804932</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G363" t="n">
-        <v>9.70611476898193</v>
+        <v>9.70611667633057</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G369" t="n">
-        <v>8.66715240478516</v>
+        <v>8.66715145111084</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>9.65499973297119</v>
       </c>
       <c r="G373" t="n">
-        <v>8.7992992401123</v>
+        <v>8.79930019378662</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G375" t="n">
-        <v>9.07726860046387</v>
+        <v>9.07726955413818</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G378" t="n">
-        <v>9.09549617767334</v>
+        <v>9.09549522399902</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G379" t="n">
-        <v>9.30787754058838</v>
+        <v>9.3078784942627</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>9.41868591308594</v>
+        <v>9.41868686676025</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G384" t="n">
-        <v>9.41868591308594</v>
+        <v>9.41868686676025</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G387" t="n">
-        <v>9.5479621887207</v>
+        <v>9.54796314239502</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G390" t="n">
-        <v>9.78804779052734</v>
+        <v>9.78804683685303</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G394" t="n">
-        <v>9.84345149993896</v>
+        <v>9.84345054626465</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G397" t="n">
-        <v>9.56643104553223</v>
+        <v>9.56643009185791</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G401" t="n">
-        <v>9.04932689666748</v>
+        <v>9.04932594299316</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G403" t="n">
-        <v>8.79539012908936</v>
+        <v>8.79539108276367</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G405" t="n">
-        <v>8.58762645721436</v>
+        <v>8.58762550354004</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>9.55500030517578</v>
       </c>
       <c r="G407" t="n">
-        <v>8.82309246063232</v>
+        <v>8.82309341430664</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G408" t="n">
-        <v>8.93851852416992</v>
+        <v>8.93851757049561</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G409" t="n">
-        <v>8.7169017791748</v>
+        <v>8.71690082550049</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G410" t="n">
-        <v>8.64303016662598</v>
+        <v>8.64302921295166</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G411" t="n">
-        <v>8.82771110534668</v>
+        <v>8.82771015167236</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G413" t="n">
-        <v>8.42141437530518</v>
+        <v>8.42141342163086</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G421" t="n">
-        <v>8.28290367126465</v>
+        <v>8.28290462493896</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G424" t="n">
-        <v>8.05205345153809</v>
+        <v>8.0520544052124</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G426" t="n">
-        <v>7.92277669906616</v>
+        <v>7.92277717590332</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G430" t="n">
-        <v>7.87660694122314</v>
+        <v>7.87660789489746</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G431" t="n">
-        <v>7.81196928024292</v>
+        <v>7.81196975708008</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G436" t="n">
-        <v>7.10095071792603</v>
+        <v>7.10095119476318</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7.72499990463257</v>
       </c>
       <c r="G438" t="n">
-        <v>7.13327026367188</v>
+        <v>7.13326978683472</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G439" t="n">
-        <v>7.12403583526611</v>
+        <v>7.12403631210327</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G441" t="n">
-        <v>6.90242004394531</v>
+        <v>6.90241956710815</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G443" t="n">
-        <v>6.61616563796997</v>
+        <v>6.61616516113281</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G447" t="n">
-        <v>6.33452892303467</v>
+        <v>6.33452844619751</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>7.13500022888184</v>
       </c>
       <c r="G448" t="n">
-        <v>6.58846378326416</v>
+        <v>6.588463306427</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G449" t="n">
-        <v>6.90242004394531</v>
+        <v>6.90241956710815</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>7.40500020980835</v>
       </c>
       <c r="G454" t="n">
-        <v>6.83778142929077</v>
+        <v>6.83778190612793</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G455" t="n">
-        <v>6.76390981674194</v>
+        <v>6.76390933990479</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G456" t="n">
-        <v>6.76390981674194</v>
+        <v>6.76390933990479</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>7.25</v>
       </c>
       <c r="G457" t="n">
-        <v>6.69465446472168</v>
+        <v>6.69465494155884</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>7.09499979019165</v>
       </c>
       <c r="G458" t="n">
-        <v>6.55152702331543</v>
+        <v>6.55152750015259</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G465" t="n">
-        <v>6.18678426742554</v>
+        <v>6.18678379058838</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>5.84499979019165</v>
       </c>
       <c r="G469" t="n">
-        <v>5.39727640151978</v>
+        <v>5.39727687835693</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>5.875</v>
       </c>
       <c r="G471" t="n">
-        <v>5.42497873306274</v>
+        <v>5.4249792098999</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>5.9850001335144</v>
       </c>
       <c r="G480" t="n">
-        <v>5.5265531539917</v>
+        <v>5.52655267715454</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>5.86499977111816</v>
       </c>
       <c r="G481" t="n">
-        <v>5.41574478149414</v>
+        <v>5.41574430465698</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G485" t="n">
-        <v>5.17566013336182</v>
+        <v>5.17566061019897</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G487" t="n">
-        <v>5.06023550033569</v>
+        <v>5.06023597717285</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>5.45499992370605</v>
       </c>
       <c r="G489" t="n">
-        <v>5.03715038299561</v>
+        <v>5.03714990615845</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G490" t="n">
-        <v>4.80168294906616</v>
+        <v>4.80168342590332</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G491" t="n">
-        <v>4.95404434204102</v>
+        <v>4.95404386520386</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G494" t="n">
-        <v>4.88478899002075</v>
+        <v>4.88478946685791</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G495" t="n">
-        <v>4.88940620422363</v>
+        <v>4.88940668106079</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>5.77500009536743</v>
       </c>
       <c r="G497" t="n">
-        <v>5.33263874053955</v>
+        <v>5.33263826370239</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>5.61499977111816</v>
       </c>
       <c r="G498" t="n">
-        <v>5.18489456176758</v>
+        <v>5.18489408493042</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>5.69500017166138</v>
       </c>
       <c r="G500" t="n">
-        <v>5.25876665115356</v>
+        <v>5.25876712799072</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G510" t="n">
-        <v>5.21259689331055</v>
+        <v>5.21259641647339</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G513" t="n">
-        <v>5.21259689331055</v>
+        <v>5.21259641647339</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>5.72499990463257</v>
       </c>
       <c r="G517" t="n">
-        <v>5.28646850585938</v>
+        <v>5.28646898269653</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>6.03499984741211</v>
       </c>
       <c r="G527" t="n">
-        <v>5.57272243499756</v>
+        <v>5.57272291183472</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>6.2649998664856</v>
       </c>
       <c r="G535" t="n">
-        <v>5.78510522842407</v>
+        <v>5.78510475158691</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G541" t="n">
-        <v>6.05750799179077</v>
+        <v>6.05750846862793</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G544" t="n">
-        <v>5.86359357833862</v>
+        <v>5.86359405517578</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G550" t="n">
-        <v>5.62812662124634</v>
+        <v>5.6281270980835</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>6.22499990463257</v>
       </c>
       <c r="G553" t="n">
-        <v>5.7481689453125</v>
+        <v>5.74816942214966</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>6.29500007629395</v>
       </c>
       <c r="G554" t="n">
-        <v>5.81280755996704</v>
+        <v>5.81280708312988</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>6.06500005722046</v>
       </c>
       <c r="G556" t="n">
-        <v>5.60042476654053</v>
+        <v>5.60042524337769</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>6.0149998664856</v>
       </c>
       <c r="G558" t="n">
-        <v>5.55425500869751</v>
+        <v>5.55425453186035</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G561" t="n">
-        <v>5.36957454681396</v>
+        <v>5.36957502365112</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G571" t="n">
-        <v>5.17566013336182</v>
+        <v>5.17566061019897</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G572" t="n">
-        <v>5.24029874801636</v>
+        <v>5.2402982711792</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>5.70499992370605</v>
       </c>
       <c r="G576" t="n">
-        <v>5.26800060272217</v>
+        <v>5.26800012588501</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G577" t="n">
-        <v>5.06023550033569</v>
+        <v>5.06023597717285</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>5.45499992370605</v>
       </c>
       <c r="G581" t="n">
-        <v>5.03715038299561</v>
+        <v>5.03714990615845</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G587" t="n">
-        <v>5.57733917236328</v>
+        <v>5.57733964920044</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>6.06500005722046</v>
       </c>
       <c r="G589" t="n">
-        <v>5.60042476654053</v>
+        <v>5.60042524337769</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>5.72499990463257</v>
       </c>
       <c r="G590" t="n">
-        <v>5.28646850585938</v>
+        <v>5.28646898269653</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>5.53499984741211</v>
       </c>
       <c r="G591" t="n">
-        <v>5.11102199554443</v>
+        <v>5.11102247238159</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>4.92172574996948</v>
+        <v>4.92172527313232</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G599" t="n">
-        <v>4.70010948181152</v>
+        <v>4.70010900497437</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G600" t="n">
-        <v>4.81091785430908</v>
+        <v>4.81091737747192</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G601" t="n">
-        <v>4.77398109436035</v>
+        <v>4.77398157119751</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G605" t="n">
-        <v>4.66317367553711</v>
+        <v>4.66317319869995</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>4.52466344833374</v>
+        <v>4.52466297149658</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G607" t="n">
-        <v>4.52466344833374</v>
+        <v>4.52466297149658</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>4.82200002670288</v>
       </c>
       <c r="G608" t="n">
-        <v>4.45263767242432</v>
+        <v>4.45263814926147</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>4.70800018310547</v>
       </c>
       <c r="G609" t="n">
-        <v>4.34737062454224</v>
+        <v>4.34737014770508</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>4.66400003433228</v>
       </c>
       <c r="G610" t="n">
-        <v>4.30674028396606</v>
+        <v>4.30674076080322</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G612" t="n">
-        <v>4.3584508895874</v>
+        <v>4.35845041275024</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>4.74399995803833</v>
       </c>
       <c r="G614" t="n">
-        <v>4.38061285018921</v>
+        <v>4.38061237335205</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>4.71799993515015</v>
       </c>
       <c r="G616" t="n">
-        <v>4.35660409927368</v>
+        <v>4.35660362243652</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>4.96600008010864</v>
       </c>
       <c r="G617" t="n">
-        <v>4.58560800552368</v>
+        <v>4.58560752868652</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G619" t="n">
-        <v>4.46741247177124</v>
+        <v>4.46741199493408</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G620" t="n">
-        <v>4.50619506835938</v>
+        <v>4.50619554519653</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G621" t="n">
-        <v>4.56898593902588</v>
+        <v>4.56898641586304</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G622" t="n">
-        <v>4.70934295654297</v>
+        <v>4.70934343338013</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G624" t="n">
-        <v>4.62623739242554</v>
+        <v>4.6262378692627</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>4.97800016403198</v>
       </c>
       <c r="G627" t="n">
-        <v>4.59668827056885</v>
+        <v>4.59668874740601</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G628" t="n">
-        <v>4.70010948181152</v>
+        <v>4.70010900497437</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G629" t="n">
-        <v>4.60776901245117</v>
+        <v>4.60776853561401</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>5.0149998664856</v>
       </c>
       <c r="G630" t="n">
-        <v>4.6308536529541</v>
+        <v>4.63085412979126</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>4.94199991226196</v>
       </c>
       <c r="G631" t="n">
-        <v>4.56344556808472</v>
+        <v>4.56344604492188</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G633" t="n">
-        <v>4.63421249389648</v>
+        <v>4.63421201705933</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G639" t="n">
-        <v>4.47546625137329</v>
+        <v>4.47546672821045</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>4.81199979782104</v>
       </c>
       <c r="G640" t="n">
-        <v>4.60169744491577</v>
+        <v>4.60169792175293</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G645" t="n">
-        <v>4.45634078979492</v>
+        <v>4.45634031295776</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>4.62400007247925</v>
       </c>
       <c r="G647" t="n">
-        <v>4.42191410064697</v>
+        <v>4.42191457748413</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G650" t="n">
-        <v>4.17136478424072</v>
+        <v>4.17136430740356</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G653" t="n">
-        <v>4.20770406723022</v>
+        <v>4.20770359039307</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G659" t="n">
-        <v>3.93037796020508</v>
+        <v>3.9303777217865</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G669" t="n">
-        <v>3.65496468544006</v>
+        <v>3.65496444702148</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G672" t="n">
-        <v>3.81370949745178</v>
+        <v>3.81370973587036</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G673" t="n">
-        <v>3.81370949745178</v>
+        <v>3.81370973587036</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>4.17600011825562</v>
       </c>
       <c r="G674" t="n">
-        <v>3.99349355697632</v>
+        <v>3.99349331855774</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G690" t="n">
-        <v>3.45605492591858</v>
+        <v>3.4560546875</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G703" t="n">
-        <v>3.96862959861755</v>
+        <v>3.96862983703613</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>4.1560001373291</v>
       </c>
       <c r="G704" t="n">
-        <v>3.97436785697937</v>
+        <v>3.97436738014221</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>4.27600002288818</v>
       </c>
       <c r="G706" t="n">
-        <v>4.0891227722168</v>
+        <v>4.08912324905396</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>4.13600015640259</v>
       </c>
       <c r="G707" t="n">
-        <v>3.95524168014526</v>
+        <v>3.95524144172668</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G709" t="n">
-        <v>3.98966813087463</v>
+        <v>3.98966789245605</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G712" t="n">
-        <v>3.67026519775391</v>
+        <v>3.67026543617249</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G717" t="n">
-        <v>3.81370949745178</v>
+        <v>3.81370973587036</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G718" t="n">
-        <v>3.82327270507812</v>
+        <v>3.82327246665955</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G719" t="n">
-        <v>3.91507697105408</v>
+        <v>3.91507720947266</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G722" t="n">
-        <v>3.98584294319153</v>
+        <v>3.98584318161011</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>4.42600011825562</v>
       </c>
       <c r="G724" t="n">
-        <v>4.23256778717041</v>
+        <v>4.23256731033325</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>4.51200008392334</v>
       </c>
       <c r="G725" t="n">
-        <v>4.31480884552002</v>
+        <v>4.31480932235718</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G727" t="n">
-        <v>4.15032625198364</v>
+        <v>4.15032577514648</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>4.25</v>
       </c>
       <c r="G729" t="n">
-        <v>4.06425905227661</v>
+        <v>4.06425952911377</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>4.2039999961853</v>
       </c>
       <c r="G732" t="n">
-        <v>4.0202693939209</v>
+        <v>4.02026987075806</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>4.11399984359741</v>
       </c>
       <c r="G737" t="n">
-        <v>3.93420267105103</v>
+        <v>3.9342029094696</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G740" t="n">
-        <v>3.96862959861755</v>
+        <v>3.96862983703613</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G741" t="n">
-        <v>3.91507697105408</v>
+        <v>3.91507720947266</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>3.90799999237061</v>
       </c>
       <c r="G748" t="n">
-        <v>3.73720574378967</v>
+        <v>3.73720598220825</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G750" t="n">
-        <v>3.70086669921875</v>
+        <v>3.70086646080017</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>3.93799996376038</v>
       </c>
       <c r="G751" t="n">
-        <v>3.76589488983154</v>
+        <v>3.76589465141296</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G755" t="n">
-        <v>3.73911881446838</v>
+        <v>3.7391185760498</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G759" t="n">
-        <v>3.57846093177795</v>
+        <v>3.57846069335938</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G760" t="n">
-        <v>3.62245059013367</v>
+        <v>3.62245035171509</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G762" t="n">
-        <v>3.56315994262695</v>
+        <v>3.56316018104553</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G763" t="n">
-        <v>3.54785919189453</v>
+        <v>3.54785943031311</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>3.64800000190735</v>
       </c>
       <c r="G766" t="n">
-        <v>3.48856902122498</v>
+        <v>3.4885687828064</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>3.64400005340576</v>
       </c>
       <c r="G771" t="n">
-        <v>3.48474359512329</v>
+        <v>3.48474383354187</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>3.63199996948242</v>
       </c>
       <c r="G772" t="n">
-        <v>3.47326827049255</v>
+        <v>3.47326803207397</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>3.95799994468689</v>
       </c>
       <c r="G776" t="n">
-        <v>3.78502082824707</v>
+        <v>3.78502058982849</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G777" t="n">
-        <v>3.76971983909607</v>
+        <v>3.76972007751465</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G779" t="n">
-        <v>3.70086669921875</v>
+        <v>3.70086646080017</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G780" t="n">
-        <v>3.59758687019348</v>
+        <v>3.5975866317749</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G783" t="n">
-        <v>3.44075393676758</v>
+        <v>3.44075417518616</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>3.41599988937378</v>
       </c>
       <c r="G784" t="n">
-        <v>3.26670813560486</v>
+        <v>3.26670789718628</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>3.41599988937378</v>
       </c>
       <c r="G785" t="n">
-        <v>3.26670813560486</v>
+        <v>3.26670789718628</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>3.46799993515015</v>
       </c>
       <c r="G786" t="n">
-        <v>3.31643533706665</v>
+        <v>3.31643557548523</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G787" t="n">
-        <v>3.29157161712646</v>
+        <v>3.29157185554504</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G795" t="n">
-        <v>3.20741772651672</v>
+        <v>3.2074179649353</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>3.47399997711182</v>
       </c>
       <c r="G808" t="n">
-        <v>3.32217335700989</v>
+        <v>3.32217311859131</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G814" t="n">
-        <v>3.22654366493225</v>
+        <v>3.22654390335083</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G820" t="n">
-        <v>3.55168461799622</v>
+        <v>3.55168437957764</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G821" t="n">
-        <v>3.5076949596405</v>
+        <v>3.50769472122192</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G823" t="n">
-        <v>3.53638362884521</v>
+        <v>3.53638386726379</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G826" t="n">
-        <v>3.58228588104248</v>
+        <v>3.58228611946106</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G827" t="n">
-        <v>3.5765483379364</v>
+        <v>3.57654809951782</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>3.84400010108948</v>
       </c>
       <c r="G828" t="n">
-        <v>3.67600321769714</v>
+        <v>3.67600297927856</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>4.22599983215332</v>
       </c>
       <c r="G833" t="n">
-        <v>4.04130792617798</v>
+        <v>4.04130840301514</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>4.68599987030029</v>
       </c>
       <c r="G841" t="n">
-        <v>4.48120450973511</v>
+        <v>4.48120403289795</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G843" t="n">
-        <v>4.54432010650635</v>
+        <v>4.54431962966919</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G846" t="n">
-        <v>4.35688591003418</v>
+        <v>4.35688638687134</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G847" t="n">
-        <v>4.26316928863525</v>
+        <v>4.2631688117981</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G849" t="n">
-        <v>4.17136478424072</v>
+        <v>4.17136430740356</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G851" t="n">
-        <v>3.93037796020508</v>
+        <v>3.9303777217865</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G854" t="n">
-        <v>3.77928280830383</v>
+        <v>3.77928304672241</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>3.51200008392334</v>
       </c>
       <c r="G858" t="n">
-        <v>3.35851263999939</v>
+        <v>3.35851287841797</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>3.56800007820129</v>
       </c>
       <c r="G859" t="n">
-        <v>3.41206526756287</v>
+        <v>3.41206550598145</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G863" t="n">
-        <v>3.47900581359863</v>
+        <v>3.47900605201721</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G868" t="n">
-        <v>3.77928280830383</v>
+        <v>3.77928304672241</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>4.12400007247925</v>
       </c>
       <c r="G872" t="n">
-        <v>3.94376587867737</v>
+        <v>3.94376611709595</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G879" t="n">
-        <v>4.47546625137329</v>
+        <v>4.47546672821045</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>4.38800001144409</v>
       </c>
       <c r="G883" t="n">
-        <v>4.19622850418091</v>
+        <v>4.19622802734375</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G886" t="n">
-        <v>4.20196580886841</v>
+        <v>4.20196628570557</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G892" t="n">
-        <v>4.57109689712524</v>
+        <v>4.57109642028809</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>4.74599981307983</v>
       </c>
       <c r="G894" t="n">
-        <v>4.53858184814453</v>
+        <v>4.53858232498169</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G895" t="n">
-        <v>4.68585205078125</v>
+        <v>4.68585157394409</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -32222,6 +32222,32 @@
         <v>3.9300000667572</v>
       </c>
       <c r="H1225" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1226" t="n">
+        <v>978763</v>
+      </c>
+      <c r="C1226" t="n">
+        <v>4.01200008392334</v>
+      </c>
+      <c r="D1226" t="n">
+        <v>3.84400010108948</v>
+      </c>
+      <c r="E1226" t="n">
+        <v>3.96000003814697</v>
+      </c>
+      <c r="F1226" t="n">
+        <v>3.98600006103516</v>
+      </c>
+      <c r="G1226" t="n">
+        <v>3.98600006103516</v>
+      </c>
+      <c r="H1226" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ARIS.MI.xlsx
+++ b/data/ARIS.MI.xlsx
@@ -421,7 +421,7 @@
         <v>10.25</v>
       </c>
       <c r="G2" t="n">
-        <v>9.21045684814453</v>
+        <v>9.21045780181885</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G5" t="n">
-        <v>9.25538635253906</v>
+        <v>9.25538539886475</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G6" t="n">
-        <v>9.20147132873535</v>
+        <v>9.20147037506104</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G7" t="n">
-        <v>9.20147132873535</v>
+        <v>9.20147037506104</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G8" t="n">
-        <v>9.20147132873535</v>
+        <v>9.20147037506104</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G9" t="n">
-        <v>9.21944236755371</v>
+        <v>9.21944332122803</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G10" t="n">
-        <v>9.20147132873535</v>
+        <v>9.20147037506104</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G11" t="n">
-        <v>9.23741340637207</v>
+        <v>9.2374153137207</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G12" t="n">
-        <v>9.20147132873535</v>
+        <v>9.20147037506104</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G13" t="n">
-        <v>9.20147132873535</v>
+        <v>9.20147037506104</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G14" t="n">
-        <v>9.20147132873535</v>
+        <v>9.20147037506104</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G15" t="n">
-        <v>9.21944236755371</v>
+        <v>9.21944332122803</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G16" t="n">
-        <v>8.92291164398193</v>
+        <v>8.92291069030762</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G17" t="n">
-        <v>8.83305358886719</v>
+        <v>8.83305263519287</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G19" t="n">
-        <v>8.71623802185059</v>
+        <v>8.71623706817627</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G20" t="n">
-        <v>9.12958431243896</v>
+        <v>9.12958526611328</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G21" t="n">
-        <v>9.07567024230957</v>
+        <v>9.07567119598389</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G22" t="n">
-        <v>8.85102367401123</v>
+        <v>8.85102462768555</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G23" t="n">
-        <v>9.07567024230957</v>
+        <v>9.07567119598389</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G24" t="n">
-        <v>9.12958431243896</v>
+        <v>9.12958526611328</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G25" t="n">
-        <v>9.11161327362061</v>
+        <v>9.11161422729492</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G26" t="n">
-        <v>9.12958431243896</v>
+        <v>9.12958526611328</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G27" t="n">
-        <v>9.50698757171631</v>
+        <v>9.50698852539062</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G29" t="n">
-        <v>9.74061965942383</v>
+        <v>9.74062061309814</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G30" t="n">
-        <v>10.1180238723755</v>
+        <v>10.1180248260498</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G34" t="n">
-        <v>10.0191793441772</v>
+        <v>10.0191802978516</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>10.9899997711182</v>
       </c>
       <c r="G35" t="n">
-        <v>9.87540721893311</v>
+        <v>9.87540626525879</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G36" t="n">
-        <v>10.1988954544067</v>
+        <v>10.1988964080811</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G37" t="n">
-        <v>10.1180238723755</v>
+        <v>10.1180248260498</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G38" t="n">
-        <v>9.72264766693115</v>
+        <v>9.72264671325684</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>10.25</v>
       </c>
       <c r="G41" t="n">
-        <v>9.21045684814453</v>
+        <v>9.21045780181885</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G42" t="n">
-        <v>9.10262680053711</v>
+        <v>9.10262775421143</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G46" t="n">
-        <v>9.20147132873535</v>
+        <v>9.20147037506104</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>10.4899997711182</v>
       </c>
       <c r="G48" t="n">
-        <v>9.42611694335938</v>
+        <v>9.42611503601074</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G50" t="n">
-        <v>9.11161327362061</v>
+        <v>9.11161422729492</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G52" t="n">
-        <v>9.12958431243896</v>
+        <v>9.12958526611328</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G55" t="n">
-        <v>8.994797706604</v>
+        <v>8.99479675292969</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G57" t="n">
-        <v>9.10262680053711</v>
+        <v>9.10262775421143</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G58" t="n">
-        <v>8.994797706604</v>
+        <v>8.99479675292969</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G59" t="n">
-        <v>9.19248485565186</v>
+        <v>9.19248390197754</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G61" t="n">
-        <v>8.71623802185059</v>
+        <v>8.71623706817627</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>9.41499996185303</v>
       </c>
       <c r="G62" t="n">
-        <v>8.46014213562012</v>
+        <v>8.4601411819458</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>9.1850004196167</v>
       </c>
       <c r="G63" t="n">
-        <v>8.25346851348877</v>
+        <v>8.25346755981445</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>8.75</v>
       </c>
       <c r="G64" t="n">
-        <v>7.86258506774902</v>
+        <v>7.86258459091187</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>9.1850004196167</v>
       </c>
       <c r="G65" t="n">
-        <v>8.25346851348877</v>
+        <v>8.25346755981445</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G67" t="n">
-        <v>7.70982646942139</v>
+        <v>7.70982599258423</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G68" t="n">
-        <v>8.03331565856934</v>
+        <v>8.03331470489502</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G69" t="n">
-        <v>7.95244312286377</v>
+        <v>7.95244359970093</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>7.875</v>
       </c>
       <c r="G70" t="n">
-        <v>7.07632684707642</v>
+        <v>7.07632637023926</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>8</v>
       </c>
       <c r="G71" t="n">
-        <v>7.18864917755127</v>
+        <v>7.18864870071411</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G72" t="n">
-        <v>7.42228031158447</v>
+        <v>7.42228078842163</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>8.3149995803833</v>
       </c>
       <c r="G74" t="n">
-        <v>7.47170162200928</v>
+        <v>7.47170209884644</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G76" t="n">
-        <v>8.66232299804688</v>
+        <v>8.66232204437256</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>9.51500034332275</v>
       </c>
       <c r="G77" t="n">
-        <v>8.54999923706055</v>
+        <v>8.55000019073486</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G78" t="n">
-        <v>9.23741340637207</v>
+        <v>9.2374153137207</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G79" t="n">
-        <v>9.08465576171875</v>
+        <v>9.08465480804443</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G80" t="n">
-        <v>9.19248485565186</v>
+        <v>9.19248390197754</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G82" t="n">
-        <v>9.07567024230957</v>
+        <v>9.07567119598389</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G85" t="n">
-        <v>8.64435195922852</v>
+        <v>8.6443510055542</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G86" t="n">
-        <v>8.55898475646973</v>
+        <v>8.55898571014404</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G89" t="n">
-        <v>8.50057792663574</v>
+        <v>8.50057697296143</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G90" t="n">
-        <v>8.55898475646973</v>
+        <v>8.55898571014404</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G91" t="n">
-        <v>8.51854801177979</v>
+        <v>8.5185489654541</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G92" t="n">
-        <v>8.71623802185059</v>
+        <v>8.71623706817627</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G93" t="n">
-        <v>8.50057792663574</v>
+        <v>8.50057697296143</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G94" t="n">
-        <v>8.18607425689697</v>
+        <v>8.18607330322266</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G96" t="n">
-        <v>8.24897480010986</v>
+        <v>8.24897575378418</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G103" t="n">
-        <v>8.71623802185059</v>
+        <v>8.71623706817627</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G105" t="n">
-        <v>8.55898475646973</v>
+        <v>8.55898571014404</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>9.53499984741211</v>
       </c>
       <c r="G108" t="n">
-        <v>8.56797122955322</v>
+        <v>8.56797218322754</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>9.25500011444092</v>
       </c>
       <c r="G111" t="n">
-        <v>8.31636905670166</v>
+        <v>8.31636810302734</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>8.6850004196167</v>
       </c>
       <c r="G114" t="n">
-        <v>7.80417823791504</v>
+        <v>7.80417776107788</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G115" t="n">
-        <v>7.80867147445679</v>
+        <v>7.80866956710815</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G117" t="n">
-        <v>8.32086181640625</v>
+        <v>8.32086277008057</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G118" t="n">
-        <v>8.54550647735596</v>
+        <v>8.54550743103027</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>9.82499980926514</v>
       </c>
       <c r="G125" t="n">
-        <v>8.95423221588135</v>
+        <v>8.95423412322998</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G126" t="n">
-        <v>8.9314489364624</v>
+        <v>8.93144989013672</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>9.47827243804932</v>
+        <v>9.478271484375</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G130" t="n">
-        <v>9.35068130493164</v>
+        <v>9.35068035125732</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G131" t="n">
-        <v>9.20486068725586</v>
+        <v>9.20486164093018</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>9.84500026702881</v>
       </c>
       <c r="G137" t="n">
-        <v>8.97246170043945</v>
+        <v>8.97246074676514</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G139" t="n">
-        <v>8.52133178710938</v>
+        <v>8.52133274078369</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G140" t="n">
-        <v>7.95628070831299</v>
+        <v>7.95628118515015</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G141" t="n">
-        <v>7.83780288696289</v>
+        <v>7.83780241012573</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G143" t="n">
-        <v>7.73755168914795</v>
+        <v>7.73755121231079</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G149" t="n">
-        <v>6.87174701690674</v>
+        <v>6.8717474937439</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>7.82499980926514</v>
       </c>
       <c r="G150" t="n">
-        <v>7.13148927688599</v>
+        <v>7.13148880004883</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>7.625</v>
       </c>
       <c r="G154" t="n">
-        <v>6.94921350479126</v>
+        <v>6.94921445846558</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G157" t="n">
-        <v>6.78061008453369</v>
+        <v>6.78061056137085</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G158" t="n">
-        <v>6.92643022537231</v>
+        <v>6.92642974853516</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>7.31500005722046</v>
       </c>
       <c r="G163" t="n">
-        <v>6.66668844223022</v>
+        <v>6.66668891906738</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G164" t="n">
-        <v>6.88086175918579</v>
+        <v>6.88086128234863</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G165" t="n">
-        <v>6.9947829246521</v>
+        <v>6.99478244781494</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G168" t="n">
-        <v>6.9947829246521</v>
+        <v>6.99478244781494</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G171" t="n">
-        <v>6.9947829246521</v>
+        <v>6.99478244781494</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G172" t="n">
-        <v>7.26819467544556</v>
+        <v>7.26819515228271</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G173" t="n">
-        <v>7.38211631774902</v>
+        <v>7.38211679458618</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G177" t="n">
-        <v>7.46413946151733</v>
+        <v>7.46413898468018</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G180" t="n">
-        <v>7.24996709823608</v>
+        <v>7.24996662139893</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G183" t="n">
-        <v>7.37300252914429</v>
+        <v>7.37300205230713</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>7.625</v>
       </c>
       <c r="G194" t="n">
-        <v>6.94921350479126</v>
+        <v>6.94921445846558</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G196" t="n">
-        <v>6.85352039337158</v>
+        <v>6.85351991653442</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G197" t="n">
-        <v>6.92643022537231</v>
+        <v>6.92642974853516</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G198" t="n">
-        <v>6.56188106536865</v>
+        <v>6.56188058853149</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G199" t="n">
-        <v>6.42517566680908</v>
+        <v>6.42517518997192</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>8.46500015258789</v>
       </c>
       <c r="G207" t="n">
-        <v>7.71476650238037</v>
+        <v>7.71476697921753</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>8.40499973297119</v>
       </c>
       <c r="G210" t="n">
-        <v>7.66008472442627</v>
+        <v>7.66008520126343</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G211" t="n">
-        <v>7.70565271377563</v>
+        <v>7.70565319061279</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G213" t="n">
-        <v>7.82868909835815</v>
+        <v>7.828688621521</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G214" t="n">
-        <v>7.82868909835815</v>
+        <v>7.828688621521</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>8.48499965667725</v>
       </c>
       <c r="G215" t="n">
-        <v>7.732994556427</v>
+        <v>7.73299407958984</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G217" t="n">
-        <v>7.93805313110352</v>
+        <v>7.93805265426636</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G218" t="n">
-        <v>8.02007675170898</v>
+        <v>8.0200777053833</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>9.13500022888184</v>
       </c>
       <c r="G219" t="n">
-        <v>8.32538795471191</v>
+        <v>8.3253870010376</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>8.84500026702881</v>
       </c>
       <c r="G222" t="n">
-        <v>8.06108856201172</v>
+        <v>8.06108951568604</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G226" t="n">
-        <v>7.65552759170532</v>
+        <v>7.65552711486816</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G228" t="n">
-        <v>7.71932363510132</v>
+        <v>7.71932411193848</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>8.60499954223633</v>
       </c>
       <c r="G229" t="n">
-        <v>7.84235954284668</v>
+        <v>7.84235906600952</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G232" t="n">
-        <v>7.54160642623901</v>
+        <v>7.54160594940186</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G235" t="n">
-        <v>7.81957483291626</v>
+        <v>7.8195743560791</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>8.59500026702881</v>
       </c>
       <c r="G236" t="n">
-        <v>7.83324575424194</v>
+        <v>7.83324527740479</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>8.63500022888184</v>
       </c>
       <c r="G237" t="n">
-        <v>7.86970043182373</v>
+        <v>7.86970138549805</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G242" t="n">
-        <v>7.20895576477051</v>
+        <v>7.20895528793335</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>8.15499973297119</v>
       </c>
       <c r="G245" t="n">
-        <v>7.43224096298218</v>
+        <v>7.43224143981934</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>8.5649995803833</v>
       </c>
       <c r="G247" t="n">
-        <v>7.80590391159058</v>
+        <v>7.80590295791626</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G248" t="n">
-        <v>7.73755168914795</v>
+        <v>7.73755121231079</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G249" t="n">
-        <v>7.82868909835815</v>
+        <v>7.828688621521</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G252" t="n">
-        <v>7.87425661087036</v>
+        <v>7.87425708770752</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>8.64500045776367</v>
       </c>
       <c r="G254" t="n">
-        <v>7.87881374359131</v>
+        <v>7.87881517410278</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>9.08500003814697</v>
       </c>
       <c r="G256" t="n">
-        <v>8.27981758117676</v>
+        <v>8.27981853485107</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G257" t="n">
-        <v>8.38006782531738</v>
+        <v>8.3800687789917</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G259" t="n">
-        <v>8.43930816650391</v>
+        <v>8.43930912017822</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>9.50500011444092</v>
       </c>
       <c r="G261" t="n">
-        <v>8.66259479522705</v>
+        <v>8.66259574890137</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G262" t="n">
-        <v>8.61246967315674</v>
+        <v>8.61246871948242</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>9.5</v>
       </c>
       <c r="G263" t="n">
-        <v>8.65803718566895</v>
+        <v>8.65803813934326</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G264" t="n">
-        <v>8.5669002532959</v>
+        <v>8.56689929962158</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G266" t="n">
-        <v>8.44386386871338</v>
+        <v>8.44386577606201</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G267" t="n">
-        <v>8.61246967315674</v>
+        <v>8.61246871948242</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>9.5</v>
       </c>
       <c r="G269" t="n">
-        <v>8.65803718566895</v>
+        <v>8.65803813934326</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G270" t="n">
-        <v>8.61246967315674</v>
+        <v>8.61246871948242</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G273" t="n">
-        <v>8.40285396575928</v>
+        <v>8.40285301208496</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G277" t="n">
-        <v>8.52133178710938</v>
+        <v>8.52133274078369</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>9.66499996185303</v>
       </c>
       <c r="G278" t="n">
-        <v>8.80841445922852</v>
+        <v>8.8084135055542</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>9.25500011444092</v>
       </c>
       <c r="G279" t="n">
-        <v>8.4347505569458</v>
+        <v>8.43475151062012</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>9.98499965667725</v>
       </c>
       <c r="G283" t="n">
-        <v>9.10005187988281</v>
+        <v>9.10005283355713</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G289" t="n">
-        <v>8.84031200408936</v>
+        <v>8.84031105041504</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G292" t="n">
-        <v>8.5669002532959</v>
+        <v>8.56689929962158</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>9.5</v>
       </c>
       <c r="G294" t="n">
-        <v>8.65803718566895</v>
+        <v>8.65803813934326</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G298" t="n">
-        <v>9.04992866516113</v>
+        <v>9.04992771148682</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G300" t="n">
-        <v>8.99524593353271</v>
+        <v>8.9952449798584</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G303" t="n">
-        <v>8.67626571655273</v>
+        <v>8.67626476287842</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>9.51500034332275</v>
       </c>
       <c r="G305" t="n">
-        <v>8.67170810699463</v>
+        <v>8.67170906066895</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>9.66499996185303</v>
       </c>
       <c r="G307" t="n">
-        <v>8.80841445922852</v>
+        <v>8.8084135055542</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>9.30500030517578</v>
       </c>
       <c r="G311" t="n">
-        <v>8.48032093048096</v>
+        <v>8.48031997680664</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>9.84500026702881</v>
       </c>
       <c r="G312" t="n">
-        <v>8.97246170043945</v>
+        <v>8.97246074676514</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>9.86499977111816</v>
       </c>
       <c r="G313" t="n">
-        <v>8.99068832397461</v>
+        <v>8.99068737030029</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G314" t="n">
-        <v>8.9314489364624</v>
+        <v>8.93144989013672</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>9.5649995803833</v>
       </c>
       <c r="G315" t="n">
-        <v>8.71727561950684</v>
+        <v>8.71727657318115</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G317" t="n">
-        <v>8.44386386871338</v>
+        <v>8.44386577606201</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>9.01500034332275</v>
       </c>
       <c r="G320" t="n">
-        <v>8.21602153778076</v>
+        <v>8.21602249145508</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>9.125</v>
       </c>
       <c r="G323" t="n">
-        <v>8.3162727355957</v>
+        <v>8.31627178192139</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G324" t="n">
-        <v>8.23880672454834</v>
+        <v>8.23880577087402</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G329" t="n">
-        <v>8.94056224822998</v>
+        <v>8.9405632019043</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>9.84500026702881</v>
       </c>
       <c r="G330" t="n">
-        <v>8.97246170043945</v>
+        <v>8.97246074676514</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G334" t="n">
-        <v>8.37551116943359</v>
+        <v>8.37551212310791</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G335" t="n">
-        <v>8.48487758636475</v>
+        <v>8.48487663269043</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>9.59500026702881</v>
       </c>
       <c r="G338" t="n">
-        <v>8.7446174621582</v>
+        <v>8.74461841583252</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G342" t="n">
-        <v>8.43930816650391</v>
+        <v>8.43930912017822</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G347" t="n">
-        <v>9.47827243804932</v>
+        <v>9.478271484375</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G348" t="n">
-        <v>9.1319522857666</v>
+        <v>9.13195133209229</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G349" t="n">
-        <v>9.18663311004639</v>
+        <v>9.18663215637207</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>9.8149995803833</v>
       </c>
       <c r="G351" t="n">
-        <v>8.94511890411377</v>
+        <v>8.94511985778809</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G353" t="n">
-        <v>8.96790409088135</v>
+        <v>8.96790313720703</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>9.88500022888184</v>
       </c>
       <c r="G355" t="n">
-        <v>9.00891590118408</v>
+        <v>9.0089168548584</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G358" t="n">
-        <v>9.46915912628174</v>
+        <v>9.46916007995605</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G359" t="n">
-        <v>9.66965961456299</v>
+        <v>9.6696605682373</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G361" t="n">
-        <v>9.47827243804932</v>
+        <v>9.478271484375</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G363" t="n">
-        <v>9.70611667633057</v>
+        <v>9.70611476898193</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G368" t="n">
-        <v>8.97701835632324</v>
+        <v>8.97701740264893</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>9.5</v>
       </c>
       <c r="G372" t="n">
-        <v>8.65803718566895</v>
+        <v>8.65803813934326</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G374" t="n">
-        <v>9.10460948944092</v>
+        <v>9.10461044311523</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G375" t="n">
-        <v>9.07726955413818</v>
+        <v>9.07726860046387</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>10.0299997329712</v>
       </c>
       <c r="G377" t="n">
-        <v>9.14106464385986</v>
+        <v>9.14106369018555</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G378" t="n">
-        <v>9.09549522399902</v>
+        <v>9.09549617767334</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G379" t="n">
-        <v>9.3078784942627</v>
+        <v>9.30787754058838</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>9.41868686676025</v>
+        <v>9.41868591308594</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G384" t="n">
-        <v>9.41868686676025</v>
+        <v>9.41868591308594</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G387" t="n">
-        <v>9.54796314239502</v>
+        <v>9.5479621887207</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G390" t="n">
-        <v>9.78804683685303</v>
+        <v>9.78804779052734</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G394" t="n">
-        <v>9.84345054626465</v>
+        <v>9.84345149993896</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G397" t="n">
-        <v>9.56643009185791</v>
+        <v>9.56643104553223</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G401" t="n">
-        <v>9.04932594299316</v>
+        <v>9.04932689666748</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G403" t="n">
-        <v>8.79539108276367</v>
+        <v>8.79539012908936</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G405" t="n">
-        <v>8.58762550354004</v>
+        <v>8.58762645721436</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>9.55500030517578</v>
       </c>
       <c r="G407" t="n">
-        <v>8.82309341430664</v>
+        <v>8.82309246063232</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G408" t="n">
-        <v>8.93851757049561</v>
+        <v>8.93851852416992</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G409" t="n">
-        <v>8.71690082550049</v>
+        <v>8.7169017791748</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G410" t="n">
-        <v>8.64302921295166</v>
+        <v>8.64303016662598</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G411" t="n">
-        <v>8.82771015167236</v>
+        <v>8.82771110534668</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G413" t="n">
-        <v>8.42141342163086</v>
+        <v>8.42141437530518</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G421" t="n">
-        <v>8.28290462493896</v>
+        <v>8.28290367126465</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G424" t="n">
-        <v>8.0520544052124</v>
+        <v>8.05205345153809</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G426" t="n">
-        <v>7.92277717590332</v>
+        <v>7.92277669906616</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G430" t="n">
-        <v>7.87660789489746</v>
+        <v>7.87660694122314</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G431" t="n">
-        <v>7.81196975708008</v>
+        <v>7.81196928024292</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G436" t="n">
-        <v>7.10095119476318</v>
+        <v>7.10095071792603</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7.72499990463257</v>
       </c>
       <c r="G438" t="n">
-        <v>7.13326978683472</v>
+        <v>7.13327026367188</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G439" t="n">
-        <v>7.12403631210327</v>
+        <v>7.12403583526611</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G441" t="n">
-        <v>6.90241956710815</v>
+        <v>6.90242004394531</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G443" t="n">
-        <v>6.61616516113281</v>
+        <v>6.61616563796997</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G447" t="n">
-        <v>6.33452844619751</v>
+        <v>6.33452892303467</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>7.13500022888184</v>
       </c>
       <c r="G448" t="n">
-        <v>6.588463306427</v>
+        <v>6.58846378326416</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G449" t="n">
-        <v>6.90241956710815</v>
+        <v>6.90242004394531</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>7.40500020980835</v>
       </c>
       <c r="G454" t="n">
-        <v>6.83778190612793</v>
+        <v>6.83778142929077</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G455" t="n">
-        <v>6.76390933990479</v>
+        <v>6.76390981674194</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G456" t="n">
-        <v>6.76390933990479</v>
+        <v>6.76390981674194</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>7.25</v>
       </c>
       <c r="G457" t="n">
-        <v>6.69465494155884</v>
+        <v>6.69465446472168</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>7.09499979019165</v>
       </c>
       <c r="G458" t="n">
-        <v>6.55152750015259</v>
+        <v>6.55152702331543</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G465" t="n">
-        <v>6.18678379058838</v>
+        <v>6.18678426742554</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>5.84499979019165</v>
       </c>
       <c r="G469" t="n">
-        <v>5.39727687835693</v>
+        <v>5.39727640151978</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>5.875</v>
       </c>
       <c r="G471" t="n">
-        <v>5.4249792098999</v>
+        <v>5.42497873306274</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>5.9850001335144</v>
       </c>
       <c r="G480" t="n">
-        <v>5.52655267715454</v>
+        <v>5.5265531539917</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>5.86499977111816</v>
       </c>
       <c r="G481" t="n">
-        <v>5.41574430465698</v>
+        <v>5.41574478149414</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G485" t="n">
-        <v>5.17566061019897</v>
+        <v>5.17566013336182</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G487" t="n">
-        <v>5.06023597717285</v>
+        <v>5.06023550033569</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>5.45499992370605</v>
       </c>
       <c r="G489" t="n">
-        <v>5.03714990615845</v>
+        <v>5.03715038299561</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G490" t="n">
-        <v>4.80168342590332</v>
+        <v>4.80168294906616</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G491" t="n">
-        <v>4.95404386520386</v>
+        <v>4.95404434204102</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G494" t="n">
-        <v>4.88478946685791</v>
+        <v>4.88478899002075</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G495" t="n">
-        <v>4.88940668106079</v>
+        <v>4.88940620422363</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>5.77500009536743</v>
       </c>
       <c r="G497" t="n">
-        <v>5.33263826370239</v>
+        <v>5.33263874053955</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>5.61499977111816</v>
       </c>
       <c r="G498" t="n">
-        <v>5.18489408493042</v>
+        <v>5.18489456176758</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>5.69500017166138</v>
       </c>
       <c r="G500" t="n">
-        <v>5.25876712799072</v>
+        <v>5.25876665115356</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G510" t="n">
-        <v>5.21259641647339</v>
+        <v>5.21259689331055</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G513" t="n">
-        <v>5.21259641647339</v>
+        <v>5.21259689331055</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>5.72499990463257</v>
       </c>
       <c r="G517" t="n">
-        <v>5.28646898269653</v>
+        <v>5.28646850585938</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>6.03499984741211</v>
       </c>
       <c r="G527" t="n">
-        <v>5.57272291183472</v>
+        <v>5.57272243499756</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>6.2649998664856</v>
       </c>
       <c r="G535" t="n">
-        <v>5.78510475158691</v>
+        <v>5.78510522842407</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G541" t="n">
-        <v>6.05750846862793</v>
+        <v>6.05750799179077</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G544" t="n">
-        <v>5.86359405517578</v>
+        <v>5.86359357833862</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G550" t="n">
-        <v>5.6281270980835</v>
+        <v>5.62812662124634</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>6.22499990463257</v>
       </c>
       <c r="G553" t="n">
-        <v>5.74816942214966</v>
+        <v>5.7481689453125</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>6.29500007629395</v>
       </c>
       <c r="G554" t="n">
-        <v>5.81280708312988</v>
+        <v>5.81280755996704</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>6.06500005722046</v>
       </c>
       <c r="G556" t="n">
-        <v>5.60042524337769</v>
+        <v>5.60042476654053</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>6.0149998664856</v>
       </c>
       <c r="G558" t="n">
-        <v>5.55425453186035</v>
+        <v>5.55425500869751</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G561" t="n">
-        <v>5.36957502365112</v>
+        <v>5.36957454681396</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G571" t="n">
-        <v>5.17566061019897</v>
+        <v>5.17566013336182</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G572" t="n">
-        <v>5.2402982711792</v>
+        <v>5.24029874801636</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>5.70499992370605</v>
       </c>
       <c r="G576" t="n">
-        <v>5.26800012588501</v>
+        <v>5.26800060272217</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G577" t="n">
-        <v>5.06023597717285</v>
+        <v>5.06023550033569</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>5.45499992370605</v>
       </c>
       <c r="G581" t="n">
-        <v>5.03714990615845</v>
+        <v>5.03715038299561</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G587" t="n">
-        <v>5.57733964920044</v>
+        <v>5.57733917236328</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>6.06500005722046</v>
       </c>
       <c r="G589" t="n">
-        <v>5.60042524337769</v>
+        <v>5.60042476654053</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>5.72499990463257</v>
       </c>
       <c r="G590" t="n">
-        <v>5.28646898269653</v>
+        <v>5.28646850585938</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>5.53499984741211</v>
       </c>
       <c r="G591" t="n">
-        <v>5.11102247238159</v>
+        <v>5.11102199554443</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>4.92172527313232</v>
+        <v>4.92172574996948</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G599" t="n">
-        <v>4.70010900497437</v>
+        <v>4.70010948181152</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G600" t="n">
-        <v>4.81091737747192</v>
+        <v>4.81091785430908</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G601" t="n">
-        <v>4.77398157119751</v>
+        <v>4.77398109436035</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G605" t="n">
-        <v>4.66317319869995</v>
+        <v>4.66317367553711</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>4.52466297149658</v>
+        <v>4.52466344833374</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G607" t="n">
-        <v>4.52466297149658</v>
+        <v>4.52466344833374</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>4.82200002670288</v>
       </c>
       <c r="G608" t="n">
-        <v>4.45263814926147</v>
+        <v>4.45263767242432</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>4.70800018310547</v>
       </c>
       <c r="G609" t="n">
-        <v>4.34737014770508</v>
+        <v>4.34737062454224</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>4.66400003433228</v>
       </c>
       <c r="G610" t="n">
-        <v>4.30674076080322</v>
+        <v>4.30674028396606</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G612" t="n">
-        <v>4.35845041275024</v>
+        <v>4.3584508895874</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>4.74399995803833</v>
       </c>
       <c r="G614" t="n">
-        <v>4.38061237335205</v>
+        <v>4.38061285018921</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>4.71799993515015</v>
       </c>
       <c r="G616" t="n">
-        <v>4.35660362243652</v>
+        <v>4.35660409927368</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>4.96600008010864</v>
       </c>
       <c r="G617" t="n">
-        <v>4.58560752868652</v>
+        <v>4.58560800552368</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G619" t="n">
-        <v>4.46741199493408</v>
+        <v>4.46741247177124</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G620" t="n">
-        <v>4.50619554519653</v>
+        <v>4.50619506835938</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G621" t="n">
-        <v>4.56898641586304</v>
+        <v>4.56898593902588</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G622" t="n">
-        <v>4.70934343338013</v>
+        <v>4.70934295654297</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G624" t="n">
-        <v>4.6262378692627</v>
+        <v>4.62623739242554</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>4.97800016403198</v>
       </c>
       <c r="G627" t="n">
-        <v>4.59668874740601</v>
+        <v>4.59668827056885</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G628" t="n">
-        <v>4.70010900497437</v>
+        <v>4.70010948181152</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G629" t="n">
-        <v>4.60776853561401</v>
+        <v>4.60776901245117</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>5.0149998664856</v>
       </c>
       <c r="G630" t="n">
-        <v>4.63085412979126</v>
+        <v>4.6308536529541</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>4.94199991226196</v>
       </c>
       <c r="G631" t="n">
-        <v>4.56344604492188</v>
+        <v>4.56344556808472</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G633" t="n">
-        <v>4.63421201705933</v>
+        <v>4.63421249389648</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G639" t="n">
-        <v>4.47546672821045</v>
+        <v>4.47546625137329</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>4.81199979782104</v>
       </c>
       <c r="G640" t="n">
-        <v>4.60169792175293</v>
+        <v>4.60169744491577</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G645" t="n">
-        <v>4.45634031295776</v>
+        <v>4.45634078979492</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>4.62400007247925</v>
       </c>
       <c r="G647" t="n">
-        <v>4.42191457748413</v>
+        <v>4.42191410064697</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G650" t="n">
-        <v>4.17136430740356</v>
+        <v>4.17136478424072</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G653" t="n">
-        <v>4.20770359039307</v>
+        <v>4.20770406723022</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G659" t="n">
-        <v>3.9303777217865</v>
+        <v>3.93037796020508</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G669" t="n">
-        <v>3.65496444702148</v>
+        <v>3.65496468544006</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G672" t="n">
-        <v>3.81370973587036</v>
+        <v>3.81370949745178</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G673" t="n">
-        <v>3.81370973587036</v>
+        <v>3.81370949745178</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>4.17600011825562</v>
       </c>
       <c r="G674" t="n">
-        <v>3.99349331855774</v>
+        <v>3.99349355697632</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G690" t="n">
-        <v>3.4560546875</v>
+        <v>3.45605492591858</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G703" t="n">
-        <v>3.96862983703613</v>
+        <v>3.96862959861755</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>4.1560001373291</v>
       </c>
       <c r="G704" t="n">
-        <v>3.97436738014221</v>
+        <v>3.97436785697937</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>4.27600002288818</v>
       </c>
       <c r="G706" t="n">
-        <v>4.08912324905396</v>
+        <v>4.0891227722168</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>4.13600015640259</v>
       </c>
       <c r="G707" t="n">
-        <v>3.95524144172668</v>
+        <v>3.95524168014526</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G709" t="n">
-        <v>3.98966789245605</v>
+        <v>3.98966813087463</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G712" t="n">
-        <v>3.67026543617249</v>
+        <v>3.67026519775391</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G717" t="n">
-        <v>3.81370973587036</v>
+        <v>3.81370949745178</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G718" t="n">
-        <v>3.82327246665955</v>
+        <v>3.82327270507812</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G719" t="n">
-        <v>3.91507720947266</v>
+        <v>3.91507697105408</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G722" t="n">
-        <v>3.98584318161011</v>
+        <v>3.98584294319153</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>4.42600011825562</v>
       </c>
       <c r="G724" t="n">
-        <v>4.23256731033325</v>
+        <v>4.23256778717041</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>4.51200008392334</v>
       </c>
       <c r="G725" t="n">
-        <v>4.31480932235718</v>
+        <v>4.31480884552002</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G727" t="n">
-        <v>4.15032577514648</v>
+        <v>4.15032625198364</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>4.25</v>
       </c>
       <c r="G729" t="n">
-        <v>4.06425952911377</v>
+        <v>4.06425905227661</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>4.2039999961853</v>
       </c>
       <c r="G732" t="n">
-        <v>4.02026987075806</v>
+        <v>4.0202693939209</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>4.11399984359741</v>
       </c>
       <c r="G737" t="n">
-        <v>3.9342029094696</v>
+        <v>3.93420267105103</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G740" t="n">
-        <v>3.96862983703613</v>
+        <v>3.96862959861755</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G741" t="n">
-        <v>3.91507720947266</v>
+        <v>3.91507697105408</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>3.90799999237061</v>
       </c>
       <c r="G748" t="n">
-        <v>3.73720598220825</v>
+        <v>3.73720574378967</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G750" t="n">
-        <v>3.70086646080017</v>
+        <v>3.70086669921875</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>3.93799996376038</v>
       </c>
       <c r="G751" t="n">
-        <v>3.76589465141296</v>
+        <v>3.76589488983154</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G755" t="n">
-        <v>3.7391185760498</v>
+        <v>3.73911881446838</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G759" t="n">
-        <v>3.57846069335938</v>
+        <v>3.57846093177795</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G760" t="n">
-        <v>3.62245035171509</v>
+        <v>3.62245059013367</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G762" t="n">
-        <v>3.56316018104553</v>
+        <v>3.56315994262695</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G763" t="n">
-        <v>3.54785943031311</v>
+        <v>3.54785919189453</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>3.64800000190735</v>
       </c>
       <c r="G766" t="n">
-        <v>3.4885687828064</v>
+        <v>3.48856902122498</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>3.64400005340576</v>
       </c>
       <c r="G771" t="n">
-        <v>3.48474383354187</v>
+        <v>3.48474359512329</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>3.63199996948242</v>
       </c>
       <c r="G772" t="n">
-        <v>3.47326803207397</v>
+        <v>3.47326827049255</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>3.95799994468689</v>
       </c>
       <c r="G776" t="n">
-        <v>3.78502058982849</v>
+        <v>3.78502082824707</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G777" t="n">
-        <v>3.76972007751465</v>
+        <v>3.76971983909607</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G779" t="n">
-        <v>3.70086646080017</v>
+        <v>3.70086669921875</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G780" t="n">
-        <v>3.5975866317749</v>
+        <v>3.59758687019348</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G783" t="n">
-        <v>3.44075417518616</v>
+        <v>3.44075393676758</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>3.41599988937378</v>
       </c>
       <c r="G784" t="n">
-        <v>3.26670789718628</v>
+        <v>3.26670813560486</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>3.41599988937378</v>
       </c>
       <c r="G785" t="n">
-        <v>3.26670789718628</v>
+        <v>3.26670813560486</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>3.46799993515015</v>
       </c>
       <c r="G786" t="n">
-        <v>3.31643557548523</v>
+        <v>3.31643533706665</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G787" t="n">
-        <v>3.29157185554504</v>
+        <v>3.29157161712646</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G795" t="n">
-        <v>3.2074179649353</v>
+        <v>3.20741772651672</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>3.47399997711182</v>
       </c>
       <c r="G808" t="n">
-        <v>3.32217311859131</v>
+        <v>3.32217335700989</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G814" t="n">
-        <v>3.22654390335083</v>
+        <v>3.22654366493225</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G820" t="n">
-        <v>3.55168437957764</v>
+        <v>3.55168461799622</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G821" t="n">
-        <v>3.50769472122192</v>
+        <v>3.5076949596405</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G823" t="n">
-        <v>3.53638386726379</v>
+        <v>3.53638362884521</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G826" t="n">
-        <v>3.58228611946106</v>
+        <v>3.58228588104248</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G827" t="n">
-        <v>3.57654809951782</v>
+        <v>3.5765483379364</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>3.84400010108948</v>
       </c>
       <c r="G828" t="n">
-        <v>3.67600297927856</v>
+        <v>3.67600321769714</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>4.22599983215332</v>
       </c>
       <c r="G833" t="n">
-        <v>4.04130840301514</v>
+        <v>4.04130792617798</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>4.68599987030029</v>
       </c>
       <c r="G841" t="n">
-        <v>4.48120403289795</v>
+        <v>4.48120450973511</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G843" t="n">
-        <v>4.54431962966919</v>
+        <v>4.54432010650635</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G846" t="n">
-        <v>4.35688638687134</v>
+        <v>4.35688591003418</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G847" t="n">
-        <v>4.2631688117981</v>
+        <v>4.26316928863525</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G849" t="n">
-        <v>4.17136430740356</v>
+        <v>4.17136478424072</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G851" t="n">
-        <v>3.9303777217865</v>
+        <v>3.93037796020508</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G854" t="n">
-        <v>3.77928304672241</v>
+        <v>3.77928280830383</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>3.51200008392334</v>
       </c>
       <c r="G858" t="n">
-        <v>3.35851287841797</v>
+        <v>3.35851263999939</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>3.56800007820129</v>
       </c>
       <c r="G859" t="n">
-        <v>3.41206550598145</v>
+        <v>3.41206526756287</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G863" t="n">
-        <v>3.47900605201721</v>
+        <v>3.47900581359863</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G868" t="n">
-        <v>3.77928304672241</v>
+        <v>3.77928280830383</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>4.12400007247925</v>
       </c>
       <c r="G872" t="n">
-        <v>3.94376611709595</v>
+        <v>3.94376587867737</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G879" t="n">
-        <v>4.47546672821045</v>
+        <v>4.47546625137329</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>4.38800001144409</v>
       </c>
       <c r="G883" t="n">
-        <v>4.19622802734375</v>
+        <v>4.19622850418091</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G886" t="n">
-        <v>4.20196628570557</v>
+        <v>4.20196580886841</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G892" t="n">
-        <v>4.57109642028809</v>
+        <v>4.57109689712524</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>4.74599981307983</v>
       </c>
       <c r="G894" t="n">
-        <v>4.53858232498169</v>
+        <v>4.53858184814453</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G895" t="n">
-        <v>4.68585157394409</v>
+        <v>4.68585205078125</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -32248,6 +32248,32 @@
         <v>3.98600006103516</v>
       </c>
       <c r="H1226" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1227" t="n">
+        <v>350488</v>
+      </c>
+      <c r="C1227" t="n">
+        <v>3.99799990653992</v>
+      </c>
+      <c r="D1227" t="n">
+        <v>3.91400003433228</v>
+      </c>
+      <c r="E1227" t="n">
+        <v>3.94199991226196</v>
+      </c>
+      <c r="F1227" t="n">
+        <v>3.91400003433228</v>
+      </c>
+      <c r="G1227" t="n">
+        <v>3.91400003433228</v>
+      </c>
+      <c r="H1227" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ARIS.MI.xlsx
+++ b/data/ARIS.MI.xlsx
@@ -421,7 +421,7 @@
         <v>10.25</v>
       </c>
       <c r="G2" t="n">
-        <v>9.21045780181885</v>
+        <v>9.21045684814453</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G5" t="n">
-        <v>9.25538539886475</v>
+        <v>9.25538635253906</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G11" t="n">
-        <v>9.2374153137207</v>
+        <v>9.23741340637207</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G16" t="n">
-        <v>8.92291069030762</v>
+        <v>8.92291164398193</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G18" t="n">
-        <v>8.6353645324707</v>
+        <v>8.63536548614502</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G20" t="n">
-        <v>9.12958526611328</v>
+        <v>9.12958431243896</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G21" t="n">
-        <v>9.07567119598389</v>
+        <v>9.07567024230957</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G23" t="n">
-        <v>9.07567119598389</v>
+        <v>9.07567024230957</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G24" t="n">
-        <v>9.12958526611328</v>
+        <v>9.12958431243896</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G25" t="n">
-        <v>9.11161422729492</v>
+        <v>9.11161327362061</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G26" t="n">
-        <v>9.12958526611328</v>
+        <v>9.12958431243896</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G28" t="n">
-        <v>9.65076160430908</v>
+        <v>9.65076065063477</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G29" t="n">
-        <v>9.74062061309814</v>
+        <v>9.74061965942383</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G30" t="n">
-        <v>10.1180248260498</v>
+        <v>10.1180238723755</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G34" t="n">
-        <v>10.0191802978516</v>
+        <v>10.0191793441772</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>10.9899997711182</v>
       </c>
       <c r="G35" t="n">
-        <v>9.87540626525879</v>
+        <v>9.87540721893311</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G37" t="n">
-        <v>10.1180248260498</v>
+        <v>10.1180238723755</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G38" t="n">
-        <v>9.72264671325684</v>
+        <v>9.72264766693115</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G39" t="n">
-        <v>9.62380409240723</v>
+        <v>9.62380504608154</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G40" t="n">
-        <v>9.67771911621094</v>
+        <v>9.67772006988525</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>10.25</v>
       </c>
       <c r="G41" t="n">
-        <v>9.21045780181885</v>
+        <v>9.21045684814453</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G42" t="n">
-        <v>9.10262775421143</v>
+        <v>9.10262680053711</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>10.4899997711182</v>
       </c>
       <c r="G48" t="n">
-        <v>9.42611503601074</v>
+        <v>9.42611694335938</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G50" t="n">
-        <v>9.11161422729492</v>
+        <v>9.11161327362061</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G52" t="n">
-        <v>9.12958526611328</v>
+        <v>9.12958431243896</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G55" t="n">
-        <v>8.99479675292969</v>
+        <v>8.994797706604</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G56" t="n">
-        <v>8.72522354125977</v>
+        <v>8.72522258758545</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G57" t="n">
-        <v>9.10262775421143</v>
+        <v>9.10262680053711</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G58" t="n">
-        <v>8.99479675292969</v>
+        <v>8.994797706604</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G59" t="n">
-        <v>9.19248390197754</v>
+        <v>9.19248485565186</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>8.75</v>
       </c>
       <c r="G64" t="n">
-        <v>7.86258459091187</v>
+        <v>7.86258602142334</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G67" t="n">
-        <v>7.70982599258423</v>
+        <v>7.70982646942139</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G68" t="n">
-        <v>8.03331470489502</v>
+        <v>8.03331565856934</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G69" t="n">
-        <v>7.95244359970093</v>
+        <v>7.95244312286377</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>8</v>
       </c>
       <c r="G71" t="n">
-        <v>7.18864870071411</v>
+        <v>7.18864917755127</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G72" t="n">
-        <v>7.42228078842163</v>
+        <v>7.42228031158447</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G78" t="n">
-        <v>9.2374153137207</v>
+        <v>9.23741340637207</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G79" t="n">
-        <v>9.08465480804443</v>
+        <v>9.08465576171875</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G80" t="n">
-        <v>9.19248390197754</v>
+        <v>9.19248485565186</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>9.71500015258789</v>
       </c>
       <c r="G81" t="n">
-        <v>8.72971630096436</v>
+        <v>8.72971439361572</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G82" t="n">
-        <v>9.07567119598389</v>
+        <v>9.07567024230957</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G83" t="n">
-        <v>8.74319458007812</v>
+        <v>8.74319553375244</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G86" t="n">
-        <v>8.55898571014404</v>
+        <v>8.55898475646973</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G88" t="n">
-        <v>8.80609607696533</v>
+        <v>8.80609512329102</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G89" t="n">
-        <v>8.50057697296143</v>
+        <v>8.50057792663574</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G90" t="n">
-        <v>8.55898571014404</v>
+        <v>8.55898475646973</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G91" t="n">
-        <v>8.5185489654541</v>
+        <v>8.51854801177979</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G93" t="n">
-        <v>8.50057697296143</v>
+        <v>8.50057792663574</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G94" t="n">
-        <v>8.18607330322266</v>
+        <v>8.18607425689697</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.25</v>
       </c>
       <c r="G95" t="n">
-        <v>8.31187534332275</v>
+        <v>8.31187629699707</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G96" t="n">
-        <v>8.24897575378418</v>
+        <v>8.24897384643555</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>9.25</v>
       </c>
       <c r="G97" t="n">
-        <v>8.31187534332275</v>
+        <v>8.31187629699707</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G100" t="n">
-        <v>8.80609607696533</v>
+        <v>8.80609512329102</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>9.75</v>
       </c>
       <c r="G101" t="n">
-        <v>8.76116561889648</v>
+        <v>8.7611665725708</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G105" t="n">
-        <v>8.55898571014404</v>
+        <v>8.55898475646973</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>9.71500015258789</v>
       </c>
       <c r="G106" t="n">
-        <v>8.72971630096436</v>
+        <v>8.72971439361572</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>9.53499984741211</v>
       </c>
       <c r="G108" t="n">
-        <v>8.56797218322754</v>
+        <v>8.56797027587891</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>9.25500011444092</v>
       </c>
       <c r="G111" t="n">
-        <v>8.31636810302734</v>
+        <v>8.31636905670166</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G113" t="n">
-        <v>7.99737215042114</v>
+        <v>7.99737310409546</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>8.6850004196167</v>
       </c>
       <c r="G114" t="n">
-        <v>7.80417776107788</v>
+        <v>7.80417728424072</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G115" t="n">
-        <v>7.80866956710815</v>
+        <v>7.80867052078247</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G117" t="n">
-        <v>8.32086277008057</v>
+        <v>8.32086086273193</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>8.80609607696533</v>
+        <v>8.80609512329102</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G121" t="n">
-        <v>8.74319458007812</v>
+        <v>8.74319553375244</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>9.94499969482422</v>
       </c>
       <c r="G122" t="n">
-        <v>8.9363899230957</v>
+        <v>8.93638896942139</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G123" t="n">
-        <v>8.96334838867188</v>
+        <v>8.96334743499756</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>9.82499980926514</v>
       </c>
       <c r="G125" t="n">
-        <v>8.95423412322998</v>
+        <v>8.95423221588135</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G126" t="n">
-        <v>8.93144989013672</v>
+        <v>8.9314489364624</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>9.478271484375</v>
+        <v>9.47827243804932</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G129" t="n">
-        <v>9.51472663879395</v>
+        <v>9.51472759246826</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G130" t="n">
-        <v>9.35068035125732</v>
+        <v>9.35068130493164</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>10.25</v>
       </c>
       <c r="G135" t="n">
-        <v>9.34156608581543</v>
+        <v>9.34156703948975</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G139" t="n">
-        <v>8.52133274078369</v>
+        <v>8.52133178710938</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G140" t="n">
-        <v>7.95628118515015</v>
+        <v>7.95628070831299</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G141" t="n">
-        <v>7.83780241012573</v>
+        <v>7.83780288696289</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G144" t="n">
-        <v>7.6464147567749</v>
+        <v>7.64641427993774</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G145" t="n">
-        <v>7.47325325012207</v>
+        <v>7.47325277328491</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G156" t="n">
-        <v>6.68035936355591</v>
+        <v>6.68035888671875</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G157" t="n">
-        <v>6.78061056137085</v>
+        <v>6.78061008453369</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G158" t="n">
-        <v>6.92642974853516</v>
+        <v>6.92643022537231</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G160" t="n">
-        <v>6.68035936355591</v>
+        <v>6.68035888671875</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G164" t="n">
-        <v>6.88086128234863</v>
+        <v>6.88086175918579</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G165" t="n">
-        <v>6.99478244781494</v>
+        <v>6.9947829246521</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G166" t="n">
-        <v>6.96288442611694</v>
+        <v>6.9628849029541</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G167" t="n">
-        <v>6.96288442611694</v>
+        <v>6.9628849029541</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G168" t="n">
-        <v>6.99478244781494</v>
+        <v>6.9947829246521</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>7.72499990463257</v>
       </c>
       <c r="G169" t="n">
-        <v>7.04035186767578</v>
+        <v>7.04035139083862</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G171" t="n">
-        <v>6.99478244781494</v>
+        <v>6.9947829246521</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G172" t="n">
-        <v>7.26819515228271</v>
+        <v>7.2681941986084</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G173" t="n">
-        <v>7.38211679458618</v>
+        <v>7.38211631774902</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G174" t="n">
-        <v>7.47325325012207</v>
+        <v>7.47325277328491</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G177" t="n">
-        <v>7.46413898468018</v>
+        <v>7.46413946151733</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>8.1850004196167</v>
       </c>
       <c r="G178" t="n">
-        <v>7.4595832824707</v>
+        <v>7.45958280563354</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G179" t="n">
-        <v>7.33199071884155</v>
+        <v>7.33199024200439</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G183" t="n">
-        <v>7.37300205230713</v>
+        <v>7.37300252914429</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G185" t="n">
-        <v>7.05402183532715</v>
+        <v>7.05402231216431</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G187" t="n">
-        <v>7.30009317398071</v>
+        <v>7.30009269714355</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G189" t="n">
-        <v>7.2135124206543</v>
+        <v>7.21351194381714</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G191" t="n">
-        <v>6.96288442611694</v>
+        <v>6.9628849029541</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G197" t="n">
-        <v>6.92642974853516</v>
+        <v>6.92643022537231</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G198" t="n">
-        <v>6.56188058853149</v>
+        <v>6.56188106536865</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>7.0149998664856</v>
       </c>
       <c r="G200" t="n">
-        <v>6.39327716827393</v>
+        <v>6.39327764511108</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G201" t="n">
-        <v>6.63023376464844</v>
+        <v>6.6302342414856</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>7.52500009536743</v>
       </c>
       <c r="G202" t="n">
-        <v>6.85807657241821</v>
+        <v>6.85807704925537</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G208" t="n">
-        <v>7.5552773475647</v>
+        <v>7.55527687072754</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G211" t="n">
-        <v>7.70565319061279</v>
+        <v>7.70565271377563</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G213" t="n">
-        <v>7.828688621521</v>
+        <v>7.82868909835815</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G214" t="n">
-        <v>7.828688621521</v>
+        <v>7.82868909835815</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>8.48499965667725</v>
       </c>
       <c r="G215" t="n">
-        <v>7.73299407958984</v>
+        <v>7.73299503326416</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>8.65499973297119</v>
       </c>
       <c r="G216" t="n">
-        <v>7.88792753219604</v>
+        <v>7.88792657852173</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G217" t="n">
-        <v>7.93805265426636</v>
+        <v>7.93805408477783</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G218" t="n">
-        <v>8.0200777053833</v>
+        <v>8.02007579803467</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>9.03499984741211</v>
       </c>
       <c r="G220" t="n">
-        <v>8.23425006866455</v>
+        <v>8.23424911499023</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G221" t="n">
-        <v>8.1932373046875</v>
+        <v>8.19323635101318</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>8.84500026702881</v>
       </c>
       <c r="G222" t="n">
-        <v>8.06108951568604</v>
+        <v>8.0610876083374</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>8.86499977111816</v>
       </c>
       <c r="G223" t="n">
-        <v>8.07931518554688</v>
+        <v>8.07931613922119</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G226" t="n">
-        <v>7.65552711486816</v>
+        <v>7.65552806854248</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G228" t="n">
-        <v>7.71932411193848</v>
+        <v>7.71932363510132</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>8.60499954223633</v>
       </c>
       <c r="G229" t="n">
-        <v>7.84235906600952</v>
+        <v>7.84235954284668</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G234" t="n">
-        <v>7.85603046417236</v>
+        <v>7.85602951049805</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G235" t="n">
-        <v>7.8195743560791</v>
+        <v>7.81957483291626</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>8.59500026702881</v>
       </c>
       <c r="G236" t="n">
-        <v>7.83324527740479</v>
+        <v>7.83324575424194</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>8.63500022888184</v>
       </c>
       <c r="G237" t="n">
-        <v>7.86970138549805</v>
+        <v>7.86970043182373</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G242" t="n">
-        <v>7.20895528793335</v>
+        <v>7.20895576477051</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>8.29500007629395</v>
       </c>
       <c r="G243" t="n">
-        <v>7.55983352661133</v>
+        <v>7.55983400344849</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>8.15499973297119</v>
       </c>
       <c r="G245" t="n">
-        <v>7.43224143981934</v>
+        <v>7.43224191665649</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>8.49499988555908</v>
       </c>
       <c r="G246" t="n">
-        <v>7.74210834503174</v>
+        <v>7.74210786819458</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>8.5649995803833</v>
       </c>
       <c r="G247" t="n">
-        <v>7.80590295791626</v>
+        <v>7.80590486526489</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G249" t="n">
-        <v>7.828688621521</v>
+        <v>7.82868909835815</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>8.44499969482422</v>
       </c>
       <c r="G250" t="n">
-        <v>7.69653940200806</v>
+        <v>7.69653987884521</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G252" t="n">
-        <v>7.87425708770752</v>
+        <v>7.87425756454468</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>8.64500045776367</v>
       </c>
       <c r="G254" t="n">
-        <v>7.87881517410278</v>
+        <v>7.87881374359131</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G257" t="n">
-        <v>8.3800687789917</v>
+        <v>8.38006782531738</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G259" t="n">
-        <v>8.43930912017822</v>
+        <v>8.43930816650391</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>9.50500011444092</v>
       </c>
       <c r="G261" t="n">
-        <v>8.66259574890137</v>
+        <v>8.66259479522705</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>9.5</v>
       </c>
       <c r="G263" t="n">
-        <v>8.65803813934326</v>
+        <v>8.65803718566895</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G264" t="n">
-        <v>8.56689929962158</v>
+        <v>8.56690120697021</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G266" t="n">
-        <v>8.44386577606201</v>
+        <v>8.4438648223877</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>9.5</v>
       </c>
       <c r="G269" t="n">
-        <v>8.65803813934326</v>
+        <v>8.65803718566895</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G271" t="n">
-        <v>8.47576332092285</v>
+        <v>8.47576236724854</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G272" t="n">
-        <v>8.46665000915527</v>
+        <v>8.46664905548096</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G274" t="n">
-        <v>8.28437519073486</v>
+        <v>8.28437614440918</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G275" t="n">
-        <v>8.46665000915527</v>
+        <v>8.46664905548096</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G276" t="n">
-        <v>8.45753383636475</v>
+        <v>8.45753479003906</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G277" t="n">
-        <v>8.52133274078369</v>
+        <v>8.52133178710938</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>9.66499996185303</v>
       </c>
       <c r="G278" t="n">
-        <v>8.8084135055542</v>
+        <v>8.80841445922852</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>9.40499973297119</v>
       </c>
       <c r="G280" t="n">
-        <v>8.57145690917969</v>
+        <v>8.57145595550537</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>9.625</v>
       </c>
       <c r="G282" t="n">
-        <v>8.77195835113525</v>
+        <v>8.77195930480957</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>9.98499965667725</v>
       </c>
       <c r="G283" t="n">
-        <v>9.10005283355713</v>
+        <v>9.10005187988281</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G284" t="n">
-        <v>9.15929222106934</v>
+        <v>9.15929126739502</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G287" t="n">
-        <v>9.15929222106934</v>
+        <v>9.15929126739502</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G288" t="n">
-        <v>8.90410804748535</v>
+        <v>8.90410900115967</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G289" t="n">
-        <v>8.84031105041504</v>
+        <v>8.84031200408936</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G292" t="n">
-        <v>8.56689929962158</v>
+        <v>8.56690120697021</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>9.5</v>
       </c>
       <c r="G294" t="n">
-        <v>8.65803813934326</v>
+        <v>8.65803718566895</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G295" t="n">
-        <v>8.60335445404053</v>
+        <v>8.60335540771484</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G298" t="n">
-        <v>9.04992771148682</v>
+        <v>9.04992866516113</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>9.625</v>
       </c>
       <c r="G301" t="n">
-        <v>8.77195835113525</v>
+        <v>8.77195930480957</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>9.51500034332275</v>
       </c>
       <c r="G305" t="n">
-        <v>8.67170906066895</v>
+        <v>8.67170810699463</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>9.66499996185303</v>
       </c>
       <c r="G307" t="n">
-        <v>8.8084135055542</v>
+        <v>8.80841445922852</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G310" t="n">
-        <v>8.71272087097168</v>
+        <v>8.71271991729736</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G314" t="n">
-        <v>8.93144989013672</v>
+        <v>8.9314489364624</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G317" t="n">
-        <v>8.44386577606201</v>
+        <v>8.4438648223877</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G318" t="n">
-        <v>8.32994365692139</v>
+        <v>8.32994270324707</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>9.01500034332275</v>
       </c>
       <c r="G320" t="n">
-        <v>8.21602249145508</v>
+        <v>8.21602153778076</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G321" t="n">
-        <v>8.26158905029297</v>
+        <v>8.26159000396729</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>9.125</v>
       </c>
       <c r="G323" t="n">
-        <v>8.31627178192139</v>
+        <v>8.3162727355957</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G324" t="n">
-        <v>8.23880577087402</v>
+        <v>8.23880672454834</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>9.71500015258789</v>
       </c>
       <c r="G328" t="n">
-        <v>8.85398292541504</v>
+        <v>8.85398197174072</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>9.58500003814697</v>
       </c>
       <c r="G331" t="n">
-        <v>8.73550415039062</v>
+        <v>8.73550510406494</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G332" t="n">
-        <v>8.49399089813232</v>
+        <v>8.49398994445801</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G333" t="n">
-        <v>8.60335445404053</v>
+        <v>8.60335540771484</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G334" t="n">
-        <v>8.37551212310791</v>
+        <v>8.37551116943359</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G335" t="n">
-        <v>8.48487663269043</v>
+        <v>8.48487758636475</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G336" t="n">
-        <v>8.60335445404053</v>
+        <v>8.60335540771484</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>9.59500026702881</v>
       </c>
       <c r="G338" t="n">
-        <v>8.74461841583252</v>
+        <v>8.7446174621582</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>9.36499977111816</v>
       </c>
       <c r="G339" t="n">
-        <v>8.53500080108643</v>
+        <v>8.53500175476074</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G340" t="n">
-        <v>8.64892387390137</v>
+        <v>8.64892292022705</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G342" t="n">
-        <v>8.43930912017822</v>
+        <v>8.43930816650391</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G347" t="n">
-        <v>9.478271484375</v>
+        <v>9.47827243804932</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G349" t="n">
-        <v>9.18663215637207</v>
+        <v>9.1866340637207</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>9.94499969482422</v>
       </c>
       <c r="G350" t="n">
-        <v>9.0635986328125</v>
+        <v>9.06359767913818</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G352" t="n">
-        <v>8.86765289306641</v>
+        <v>8.86765384674072</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G353" t="n">
-        <v>8.96790313720703</v>
+        <v>8.96790409088135</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G354" t="n">
-        <v>9.02258586883545</v>
+        <v>9.02258682250977</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>9.88500022888184</v>
       </c>
       <c r="G355" t="n">
-        <v>9.0089168548584</v>
+        <v>9.00891590118408</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G356" t="n">
-        <v>9.02258586883545</v>
+        <v>9.02258682250977</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G357" t="n">
-        <v>9.16840648651123</v>
+        <v>9.16840553283691</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G358" t="n">
-        <v>9.46916007995605</v>
+        <v>9.46915912628174</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G361" t="n">
-        <v>9.478271484375</v>
+        <v>9.47827243804932</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G363" t="n">
-        <v>9.70611476898193</v>
+        <v>9.70611572265625</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>9.83500003814697</v>
       </c>
       <c r="G366" t="n">
-        <v>8.96334838867188</v>
+        <v>8.96334743499756</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G368" t="n">
-        <v>8.97701740264893</v>
+        <v>8.97701835632324</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>9.40499973297119</v>
       </c>
       <c r="G370" t="n">
-        <v>8.57145690917969</v>
+        <v>8.57145595550537</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>9.5</v>
       </c>
       <c r="G372" t="n">
-        <v>8.65803813934326</v>
+        <v>8.65803718566895</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>9.65499973297119</v>
       </c>
       <c r="G373" t="n">
-        <v>8.79930019378662</v>
+        <v>8.7992992401123</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G374" t="n">
-        <v>9.10461044311523</v>
+        <v>9.10460948944092</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G375" t="n">
-        <v>9.07726860046387</v>
+        <v>9.07726955413818</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>9.94499969482422</v>
       </c>
       <c r="G376" t="n">
-        <v>9.0635986328125</v>
+        <v>9.06359767913818</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G379" t="n">
-        <v>9.30787754058838</v>
+        <v>9.3078784942627</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G383" t="n">
-        <v>9.61260032653809</v>
+        <v>9.6126012802124</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>10.25</v>
       </c>
       <c r="G385" t="n">
-        <v>9.46485614776611</v>
+        <v>9.46485710144043</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G386" t="n">
-        <v>9.43715572357178</v>
+        <v>9.43715476989746</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G387" t="n">
-        <v>9.5479621887207</v>
+        <v>9.54796314239502</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G388" t="n">
-        <v>9.63106918334961</v>
+        <v>9.63106822967529</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G389" t="n">
-        <v>9.64030170440674</v>
+        <v>9.64030265808105</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G390" t="n">
-        <v>9.78804779052734</v>
+        <v>9.78804683685303</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G392" t="n">
-        <v>9.64030170440674</v>
+        <v>9.64030265808105</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>10.5</v>
       </c>
       <c r="G393" t="n">
-        <v>9.69570636749268</v>
+        <v>9.69570732116699</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G394" t="n">
-        <v>9.84345149993896</v>
+        <v>9.84345054626465</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G397" t="n">
-        <v>9.56643104553223</v>
+        <v>9.56642913818359</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G398" t="n">
-        <v>9.4279203414917</v>
+        <v>9.42792129516602</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G400" t="n">
-        <v>9.18783664703369</v>
+        <v>9.18783569335938</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G401" t="n">
-        <v>9.04932689666748</v>
+        <v>9.04932594299316</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G403" t="n">
-        <v>8.79539012908936</v>
+        <v>8.79539108276367</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G405" t="n">
-        <v>8.58762645721436</v>
+        <v>8.58762550354004</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>9.55500030517578</v>
       </c>
       <c r="G407" t="n">
-        <v>8.82309246063232</v>
+        <v>8.82309341430664</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G410" t="n">
-        <v>8.64303016662598</v>
+        <v>8.64302921295166</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G411" t="n">
-        <v>8.82771110534668</v>
+        <v>8.82771015167236</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G413" t="n">
-        <v>8.42141437530518</v>
+        <v>8.42141342163086</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G414" t="n">
-        <v>8.50451946258545</v>
+        <v>8.50452041625977</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>9.21500015258789</v>
       </c>
       <c r="G415" t="n">
-        <v>8.50913715362549</v>
+        <v>8.5091381072998</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>9.57499980926514</v>
       </c>
       <c r="G418" t="n">
-        <v>8.84156131744385</v>
+        <v>8.84156036376953</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G419" t="n">
-        <v>8.57839298248291</v>
+        <v>8.57839202880859</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G423" t="n">
-        <v>8.03820323944092</v>
+        <v>8.0382022857666</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G426" t="n">
-        <v>7.92277669906616</v>
+        <v>7.92277717590332</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G427" t="n">
-        <v>7.82120370864868</v>
+        <v>7.82120275497437</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G428" t="n">
-        <v>7.82120370864868</v>
+        <v>7.82120275497437</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>8.46500015258789</v>
       </c>
       <c r="G429" t="n">
-        <v>7.8165864944458</v>
+        <v>7.81658744812012</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G431" t="n">
-        <v>7.81196928024292</v>
+        <v>7.81196975708008</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>8.42500019073486</v>
       </c>
       <c r="G432" t="n">
-        <v>7.77965021133423</v>
+        <v>7.77965116500854</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G434" t="n">
-        <v>7.25792932510376</v>
+        <v>7.2579288482666</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G435" t="n">
-        <v>7.06401491165161</v>
+        <v>7.06401538848877</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G436" t="n">
-        <v>7.10095071792603</v>
+        <v>7.10095119476318</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G437" t="n">
-        <v>7.16558933258057</v>
+        <v>7.16558885574341</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7.72499990463257</v>
       </c>
       <c r="G438" t="n">
-        <v>7.13327026367188</v>
+        <v>7.13326930999756</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G441" t="n">
-        <v>6.90242004394531</v>
+        <v>6.90241956710815</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G443" t="n">
-        <v>6.61616563796997</v>
+        <v>6.61616516113281</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G444" t="n">
-        <v>6.61154890060425</v>
+        <v>6.61154842376709</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>7.02500009536743</v>
       </c>
       <c r="G445" t="n">
-        <v>6.48688936233521</v>
+        <v>6.48688983917236</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G447" t="n">
-        <v>6.33452892303467</v>
+        <v>6.33452844619751</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>7.13500022888184</v>
       </c>
       <c r="G448" t="n">
-        <v>6.58846378326416</v>
+        <v>6.588463306427</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G449" t="n">
-        <v>6.90242004394531</v>
+        <v>6.90241956710815</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>7.40500020980835</v>
       </c>
       <c r="G454" t="n">
-        <v>6.83778142929077</v>
+        <v>6.83778190612793</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G455" t="n">
-        <v>6.76390981674194</v>
+        <v>6.76390933990479</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G456" t="n">
-        <v>6.76390981674194</v>
+        <v>6.76390933990479</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>7.09499979019165</v>
       </c>
       <c r="G458" t="n">
-        <v>6.55152702331543</v>
+        <v>6.55152750015259</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G461" t="n">
-        <v>6.37146425247192</v>
+        <v>6.37146472930908</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G462" t="n">
-        <v>6.37146425247192</v>
+        <v>6.37146472930908</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>6.69500017166138</v>
       </c>
       <c r="G464" t="n">
-        <v>6.18216753005981</v>
+        <v>6.18216800689697</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G465" t="n">
-        <v>6.18678426742554</v>
+        <v>6.18678379058838</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G466" t="n">
-        <v>5.808189868927</v>
+        <v>5.80819034576416</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>5.82499980926514</v>
       </c>
       <c r="G475" t="n">
-        <v>5.37880897521973</v>
+        <v>5.37880849838257</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G479" t="n">
-        <v>5.70661592483521</v>
+        <v>5.70661544799805</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>5.9850001335144</v>
       </c>
       <c r="G480" t="n">
-        <v>5.5265531539917</v>
+        <v>5.52655267715454</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G485" t="n">
-        <v>5.17566013336182</v>
+        <v>5.17566108703613</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>5.75</v>
       </c>
       <c r="G486" t="n">
-        <v>5.30955362319946</v>
+        <v>5.30955410003662</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G487" t="n">
-        <v>5.06023550033569</v>
+        <v>5.06023597717285</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G490" t="n">
-        <v>4.80168294906616</v>
+        <v>4.80168342590332</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G494" t="n">
-        <v>4.88478899002075</v>
+        <v>4.88478946685791</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G495" t="n">
-        <v>4.88940620422363</v>
+        <v>4.88940668106079</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>5.69500017166138</v>
       </c>
       <c r="G500" t="n">
-        <v>5.25876665115356</v>
+        <v>5.25876712799072</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G508" t="n">
-        <v>5.41112804412842</v>
+        <v>5.41112756729126</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G509" t="n">
-        <v>5.24491548538208</v>
+        <v>5.24491500854492</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G510" t="n">
-        <v>5.21259689331055</v>
+        <v>5.21259641647339</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G513" t="n">
-        <v>5.21259689331055</v>
+        <v>5.21259641647339</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G515" t="n">
-        <v>5.11563920974731</v>
+        <v>5.11563968658447</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G518" t="n">
-        <v>5.24491548538208</v>
+        <v>5.24491500854492</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>5.5</v>
       </c>
       <c r="G524" t="n">
-        <v>5.0787034034729</v>
+        <v>5.07870388031006</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>6.03499984741211</v>
       </c>
       <c r="G527" t="n">
-        <v>5.57272243499756</v>
+        <v>5.57272291183472</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>6.40500020980835</v>
       </c>
       <c r="G533" t="n">
-        <v>5.91438102722168</v>
+        <v>5.91438150405884</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>6.2649998664856</v>
       </c>
       <c r="G535" t="n">
-        <v>5.78510522842407</v>
+        <v>5.78510475158691</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>6.38500022888184</v>
       </c>
       <c r="G539" t="n">
-        <v>5.89591360092163</v>
+        <v>5.89591312408447</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G540" t="n">
-        <v>6.03904008865356</v>
+        <v>6.03904056549072</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G541" t="n">
-        <v>6.05750799179077</v>
+        <v>6.05750846862793</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>6.57499980926514</v>
       </c>
       <c r="G542" t="n">
-        <v>6.07135915756226</v>
+        <v>6.0713586807251</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G544" t="n">
-        <v>5.86359357833862</v>
+        <v>5.86359405517578</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G551" t="n">
-        <v>5.70661592483521</v>
+        <v>5.70661544799805</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G552" t="n">
-        <v>5.70661592483521</v>
+        <v>5.70661544799805</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>6.29500007629395</v>
       </c>
       <c r="G554" t="n">
-        <v>5.81280755996704</v>
+        <v>5.81280660629272</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>6.0149998664856</v>
       </c>
       <c r="G558" t="n">
-        <v>5.55425500869751</v>
+        <v>5.55425453186035</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G564" t="n">
-        <v>5.41112804412842</v>
+        <v>5.41112756729126</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G571" t="n">
-        <v>5.17566013336182</v>
+        <v>5.17566108703613</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G577" t="n">
-        <v>5.06023550033569</v>
+        <v>5.06023597717285</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G579" t="n">
-        <v>5.07408666610718</v>
+        <v>5.07408618927002</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G582" t="n">
-        <v>5.3003191947937</v>
+        <v>5.30031967163086</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G584" t="n">
-        <v>5.37419176101685</v>
+        <v>5.374192237854</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G585" t="n">
-        <v>5.47576570510864</v>
+        <v>5.47576522827148</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G587" t="n">
-        <v>5.57733917236328</v>
+        <v>5.5773401260376</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>5.53499984741211</v>
       </c>
       <c r="G591" t="n">
-        <v>5.11102199554443</v>
+        <v>5.11102247238159</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G594" t="n">
-        <v>5.05100107192993</v>
+        <v>5.05100154876709</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>4.92172574996948</v>
+        <v>4.92172527313232</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G598" t="n">
-        <v>4.80630016326904</v>
+        <v>4.8063006401062</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G599" t="n">
-        <v>4.70010948181152</v>
+        <v>4.70010900497437</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G600" t="n">
-        <v>4.81091785430908</v>
+        <v>4.81091737747192</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G601" t="n">
-        <v>4.77398109436035</v>
+        <v>4.77398157119751</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>5.22499990463257</v>
       </c>
       <c r="G602" t="n">
-        <v>4.82476854324341</v>
+        <v>4.82476806640625</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G603" t="n">
-        <v>4.89864015579224</v>
+        <v>4.89863967895508</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>4.80630016326904</v>
+        <v>4.8063006401062</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G605" t="n">
-        <v>4.66317367553711</v>
+        <v>4.66317319869995</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>4.52466344833374</v>
+        <v>4.52466297149658</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G607" t="n">
-        <v>4.52466344833374</v>
+        <v>4.52466297149658</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>4.82200002670288</v>
       </c>
       <c r="G608" t="n">
-        <v>4.45263767242432</v>
+        <v>4.45263814926147</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>4.70800018310547</v>
       </c>
       <c r="G609" t="n">
-        <v>4.34737062454224</v>
+        <v>4.34737014770508</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>4.66400003433228</v>
       </c>
       <c r="G610" t="n">
-        <v>4.30674028396606</v>
+        <v>4.30674076080322</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>4.74399995803833</v>
       </c>
       <c r="G614" t="n">
-        <v>4.38061285018921</v>
+        <v>4.38061237335205</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>4.96600008010864</v>
       </c>
       <c r="G617" t="n">
-        <v>4.58560800552368</v>
+        <v>4.58560752868652</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>5</v>
       </c>
       <c r="G618" t="n">
-        <v>4.61700296401978</v>
+        <v>4.61700344085693</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G619" t="n">
-        <v>4.46741247177124</v>
+        <v>4.46741199493408</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G621" t="n">
-        <v>4.56898593902588</v>
+        <v>4.56898641586304</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>5.06500005722046</v>
       </c>
       <c r="G625" t="n">
-        <v>4.67702436447144</v>
+        <v>4.67702388763428</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>4.97800016403198</v>
       </c>
       <c r="G627" t="n">
-        <v>4.59668827056885</v>
+        <v>4.59668874740601</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G628" t="n">
-        <v>4.70010948181152</v>
+        <v>4.70010900497437</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>5.0149998664856</v>
       </c>
       <c r="G630" t="n">
-        <v>4.6308536529541</v>
+        <v>4.63085412979126</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G633" t="n">
-        <v>4.63421249389648</v>
+        <v>4.63421201705933</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G639" t="n">
-        <v>4.47546625137329</v>
+        <v>4.47546672821045</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>4.81199979782104</v>
       </c>
       <c r="G640" t="n">
-        <v>4.60169744491577</v>
+        <v>4.60169792175293</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G645" t="n">
-        <v>4.45634078979492</v>
+        <v>4.45634031295776</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>4.62400007247925</v>
       </c>
       <c r="G647" t="n">
-        <v>4.42191410064697</v>
+        <v>4.42191457748413</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G650" t="n">
-        <v>4.17136478424072</v>
+        <v>4.17136430740356</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G653" t="n">
-        <v>4.20770406723022</v>
+        <v>4.20770359039307</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G659" t="n">
-        <v>3.93037796020508</v>
+        <v>3.9303777217865</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G669" t="n">
-        <v>3.65496468544006</v>
+        <v>3.65496444702148</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G672" t="n">
-        <v>3.81370949745178</v>
+        <v>3.81370973587036</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G673" t="n">
-        <v>3.81370949745178</v>
+        <v>3.81370973587036</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>4.17600011825562</v>
       </c>
       <c r="G674" t="n">
-        <v>3.99349355697632</v>
+        <v>3.99349331855774</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G690" t="n">
-        <v>3.45605492591858</v>
+        <v>3.4560546875</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G703" t="n">
-        <v>3.96862959861755</v>
+        <v>3.96862983703613</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>4.1560001373291</v>
       </c>
       <c r="G704" t="n">
-        <v>3.97436785697937</v>
+        <v>3.97436738014221</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>4.27600002288818</v>
       </c>
       <c r="G706" t="n">
-        <v>4.0891227722168</v>
+        <v>4.08912324905396</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>4.13600015640259</v>
       </c>
       <c r="G707" t="n">
-        <v>3.95524168014526</v>
+        <v>3.95524144172668</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G709" t="n">
-        <v>3.98966813087463</v>
+        <v>3.98966789245605</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G712" t="n">
-        <v>3.67026519775391</v>
+        <v>3.67026543617249</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G717" t="n">
-        <v>3.81370949745178</v>
+        <v>3.81370973587036</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G718" t="n">
-        <v>3.82327270507812</v>
+        <v>3.82327246665955</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G719" t="n">
-        <v>3.91507697105408</v>
+        <v>3.91507720947266</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G722" t="n">
-        <v>3.98584294319153</v>
+        <v>3.98584318161011</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>4.42600011825562</v>
       </c>
       <c r="G724" t="n">
-        <v>4.23256778717041</v>
+        <v>4.23256731033325</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>4.51200008392334</v>
       </c>
       <c r="G725" t="n">
-        <v>4.31480884552002</v>
+        <v>4.31480932235718</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G727" t="n">
-        <v>4.15032625198364</v>
+        <v>4.15032577514648</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>4.25</v>
       </c>
       <c r="G729" t="n">
-        <v>4.06425905227661</v>
+        <v>4.06425952911377</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>4.2039999961853</v>
       </c>
       <c r="G732" t="n">
-        <v>4.0202693939209</v>
+        <v>4.02026987075806</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>4.11399984359741</v>
       </c>
       <c r="G737" t="n">
-        <v>3.93420267105103</v>
+        <v>3.9342029094696</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G740" t="n">
-        <v>3.96862959861755</v>
+        <v>3.96862983703613</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G741" t="n">
-        <v>3.91507697105408</v>
+        <v>3.91507720947266</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>3.90799999237061</v>
       </c>
       <c r="G748" t="n">
-        <v>3.73720574378967</v>
+        <v>3.73720598220825</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G750" t="n">
-        <v>3.70086669921875</v>
+        <v>3.70086646080017</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>3.93799996376038</v>
       </c>
       <c r="G751" t="n">
-        <v>3.76589488983154</v>
+        <v>3.76589465141296</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G755" t="n">
-        <v>3.73911881446838</v>
+        <v>3.7391185760498</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G759" t="n">
-        <v>3.57846093177795</v>
+        <v>3.57846069335938</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G760" t="n">
-        <v>3.62245059013367</v>
+        <v>3.62245035171509</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G762" t="n">
-        <v>3.56315994262695</v>
+        <v>3.56316018104553</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G763" t="n">
-        <v>3.54785919189453</v>
+        <v>3.54785943031311</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>3.64800000190735</v>
       </c>
       <c r="G766" t="n">
-        <v>3.48856902122498</v>
+        <v>3.4885687828064</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>3.64400005340576</v>
       </c>
       <c r="G771" t="n">
-        <v>3.48474359512329</v>
+        <v>3.48474383354187</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>3.63199996948242</v>
       </c>
       <c r="G772" t="n">
-        <v>3.47326827049255</v>
+        <v>3.47326803207397</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>3.95799994468689</v>
       </c>
       <c r="G776" t="n">
-        <v>3.78502082824707</v>
+        <v>3.78502058982849</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G777" t="n">
-        <v>3.76971983909607</v>
+        <v>3.76972007751465</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G779" t="n">
-        <v>3.70086669921875</v>
+        <v>3.70086646080017</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G780" t="n">
-        <v>3.59758687019348</v>
+        <v>3.5975866317749</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G783" t="n">
-        <v>3.44075393676758</v>
+        <v>3.44075417518616</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>3.41599988937378</v>
       </c>
       <c r="G784" t="n">
-        <v>3.26670813560486</v>
+        <v>3.26670789718628</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>3.41599988937378</v>
       </c>
       <c r="G785" t="n">
-        <v>3.26670813560486</v>
+        <v>3.26670789718628</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>3.46799993515015</v>
       </c>
       <c r="G786" t="n">
-        <v>3.31643533706665</v>
+        <v>3.31643557548523</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G787" t="n">
-        <v>3.29157161712646</v>
+        <v>3.29157185554504</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G795" t="n">
-        <v>3.20741772651672</v>
+        <v>3.2074179649353</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>3.47399997711182</v>
       </c>
       <c r="G808" t="n">
-        <v>3.32217335700989</v>
+        <v>3.32217311859131</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G814" t="n">
-        <v>3.22654366493225</v>
+        <v>3.22654390335083</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G820" t="n">
-        <v>3.55168461799622</v>
+        <v>3.55168437957764</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G821" t="n">
-        <v>3.5076949596405</v>
+        <v>3.50769472122192</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G823" t="n">
-        <v>3.53638362884521</v>
+        <v>3.53638386726379</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G826" t="n">
-        <v>3.58228588104248</v>
+        <v>3.58228611946106</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G827" t="n">
-        <v>3.5765483379364</v>
+        <v>3.57654809951782</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>3.84400010108948</v>
       </c>
       <c r="G828" t="n">
-        <v>3.67600321769714</v>
+        <v>3.67600297927856</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>4.22599983215332</v>
       </c>
       <c r="G833" t="n">
-        <v>4.04130792617798</v>
+        <v>4.04130840301514</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>4.68599987030029</v>
       </c>
       <c r="G841" t="n">
-        <v>4.48120450973511</v>
+        <v>4.48120403289795</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G843" t="n">
-        <v>4.54432010650635</v>
+        <v>4.54431962966919</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G846" t="n">
-        <v>4.35688591003418</v>
+        <v>4.35688638687134</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G847" t="n">
-        <v>4.26316928863525</v>
+        <v>4.2631688117981</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G849" t="n">
-        <v>4.17136478424072</v>
+        <v>4.17136430740356</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G851" t="n">
-        <v>3.93037796020508</v>
+        <v>3.9303777217865</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G854" t="n">
-        <v>3.77928280830383</v>
+        <v>3.77928304672241</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>3.51200008392334</v>
       </c>
       <c r="G858" t="n">
-        <v>3.35851263999939</v>
+        <v>3.35851287841797</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>3.56800007820129</v>
       </c>
       <c r="G859" t="n">
-        <v>3.41206526756287</v>
+        <v>3.41206550598145</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G863" t="n">
-        <v>3.47900581359863</v>
+        <v>3.47900605201721</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G868" t="n">
-        <v>3.77928280830383</v>
+        <v>3.77928304672241</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>4.12400007247925</v>
       </c>
       <c r="G872" t="n">
-        <v>3.94376587867737</v>
+        <v>3.94376611709595</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G879" t="n">
-        <v>4.47546625137329</v>
+        <v>4.47546672821045</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>4.38800001144409</v>
       </c>
       <c r="G883" t="n">
-        <v>4.19622850418091</v>
+        <v>4.19622802734375</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G886" t="n">
-        <v>4.20196580886841</v>
+        <v>4.20196628570557</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G892" t="n">
-        <v>4.57109689712524</v>
+        <v>4.57109642028809</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>4.74599981307983</v>
       </c>
       <c r="G894" t="n">
-        <v>4.53858184814453</v>
+        <v>4.53858232498169</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G895" t="n">
-        <v>4.68585205078125</v>
+        <v>4.68585157394409</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -32274,6 +32274,32 @@
         <v>3.91400003433228</v>
       </c>
       <c r="H1227" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1228" t="n">
+        <v>317406</v>
+      </c>
+      <c r="C1228" t="n">
+        <v>4</v>
+      </c>
+      <c r="D1228" t="n">
+        <v>3.89800000190735</v>
+      </c>
+      <c r="E1228" t="n">
+        <v>3.92000007629395</v>
+      </c>
+      <c r="F1228" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1228" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1228" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ARIS.MI.xlsx
+++ b/data/ARIS.MI.xlsx
@@ -421,7 +421,7 @@
         <v>10.25</v>
       </c>
       <c r="G2" t="n">
-        <v>9.21045684814453</v>
+        <v>9.21045780181885</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G4" t="n">
-        <v>9.17451477050781</v>
+        <v>9.1745138168335</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G9" t="n">
-        <v>9.21944236755371</v>
+        <v>9.21944332122803</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G15" t="n">
-        <v>9.21944236755371</v>
+        <v>9.21944332122803</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G16" t="n">
-        <v>8.92291164398193</v>
+        <v>8.92291069030762</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G17" t="n">
-        <v>8.83305263519287</v>
+        <v>8.83305358886719</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G19" t="n">
-        <v>8.71623802185059</v>
+        <v>8.71623706817627</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G22" t="n">
-        <v>8.85102462768555</v>
+        <v>8.85102367401123</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G25" t="n">
-        <v>9.11161327362061</v>
+        <v>9.11161422729492</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G28" t="n">
-        <v>9.65076160430908</v>
+        <v>9.65076065063477</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G29" t="n">
-        <v>9.74062061309814</v>
+        <v>9.74061965942383</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G31" t="n">
-        <v>9.48901748657227</v>
+        <v>9.48901844024658</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G32" t="n">
-        <v>9.17451477050781</v>
+        <v>9.1745138168335</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G36" t="n">
-        <v>10.1988954544067</v>
+        <v>10.1988964080811</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G40" t="n">
-        <v>9.67771816253662</v>
+        <v>9.67771911621094</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>10.25</v>
       </c>
       <c r="G41" t="n">
-        <v>9.21045684814453</v>
+        <v>9.21045780181885</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G43" t="n">
-        <v>9.17451477050781</v>
+        <v>9.1745138168335</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G45" t="n">
-        <v>9.0487117767334</v>
+        <v>9.04871273040771</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G50" t="n">
-        <v>9.11161327362061</v>
+        <v>9.11161422729492</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G51" t="n">
-        <v>9.16552829742432</v>
+        <v>9.16552734375</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G53" t="n">
-        <v>9.24639987945557</v>
+        <v>9.24640083312988</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G54" t="n">
-        <v>9.16552829742432</v>
+        <v>9.16552734375</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G56" t="n">
-        <v>8.72522354125977</v>
+        <v>8.72522258758545</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G61" t="n">
-        <v>8.71623802185059</v>
+        <v>8.71623706817627</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>9.41499996185303</v>
       </c>
       <c r="G62" t="n">
-        <v>8.46014213562012</v>
+        <v>8.4601411819458</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>8.75</v>
       </c>
       <c r="G64" t="n">
-        <v>7.86258506774902</v>
+        <v>7.86258554458618</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>9.20499992370605</v>
       </c>
       <c r="G66" t="n">
-        <v>8.27143955230713</v>
+        <v>8.27144050598145</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G68" t="n">
-        <v>8.03331470489502</v>
+        <v>8.03331565856934</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G69" t="n">
-        <v>7.95244407653809</v>
+        <v>7.95244359970093</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>7.875</v>
       </c>
       <c r="G70" t="n">
-        <v>7.07632637023926</v>
+        <v>7.07632684707642</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G72" t="n">
-        <v>7.42228078842163</v>
+        <v>7.42228126525879</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G73" t="n">
-        <v>7.79069900512695</v>
+        <v>7.79069852828979</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>8.3149995803833</v>
       </c>
       <c r="G74" t="n">
-        <v>7.47170162200928</v>
+        <v>7.47170209884644</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>8.78499984741211</v>
       </c>
       <c r="G75" t="n">
-        <v>7.89403533935547</v>
+        <v>7.89403581619263</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G76" t="n">
-        <v>8.66232204437256</v>
+        <v>8.66232299804688</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>9.51500034332275</v>
       </c>
       <c r="G77" t="n">
-        <v>8.54999923706055</v>
+        <v>8.55000114440918</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G79" t="n">
-        <v>9.08465480804443</v>
+        <v>9.08465576171875</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G86" t="n">
-        <v>8.55898571014404</v>
+        <v>8.55898475646973</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G87" t="n">
-        <v>8.67130756378174</v>
+        <v>8.67130851745605</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G89" t="n">
-        <v>8.50057697296143</v>
+        <v>8.50057792663574</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G90" t="n">
-        <v>8.55898571014404</v>
+        <v>8.55898475646973</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G92" t="n">
-        <v>8.71623802185059</v>
+        <v>8.71623706817627</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G93" t="n">
-        <v>8.50057697296143</v>
+        <v>8.50057792663574</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.25</v>
       </c>
       <c r="G95" t="n">
-        <v>8.31187534332275</v>
+        <v>8.31187438964844</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>9.25</v>
       </c>
       <c r="G97" t="n">
-        <v>8.31187534332275</v>
+        <v>8.31187438964844</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G99" t="n">
-        <v>8.45564937591553</v>
+        <v>8.45564842224121</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G103" t="n">
-        <v>8.71623802185059</v>
+        <v>8.71623706817627</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>9.625</v>
       </c>
       <c r="G104" t="n">
-        <v>8.64884281158447</v>
+        <v>8.64884471893311</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G105" t="n">
-        <v>8.55898571014404</v>
+        <v>8.55898475646973</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G107" t="n">
-        <v>8.67130756378174</v>
+        <v>8.67130851745605</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>9.53499984741211</v>
       </c>
       <c r="G108" t="n">
-        <v>8.56797218322754</v>
+        <v>8.56797122955322</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>9</v>
       </c>
       <c r="G109" t="n">
-        <v>8.08722972869873</v>
+        <v>8.08723068237305</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G110" t="n">
-        <v>7.89852952957153</v>
+        <v>7.89852857589722</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G112" t="n">
-        <v>8.10520362854004</v>
+        <v>8.10520172119141</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G113" t="n">
-        <v>7.99737310409546</v>
+        <v>7.99737215042114</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G115" t="n">
-        <v>7.80866956710815</v>
+        <v>7.80867052078247</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G117" t="n">
-        <v>8.32086181640625</v>
+        <v>8.32086277008057</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>9.94499969482422</v>
       </c>
       <c r="G122" t="n">
-        <v>8.9363899230957</v>
+        <v>8.93638896942139</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>9.78499984741211</v>
       </c>
       <c r="G124" t="n">
-        <v>8.91777896881104</v>
+        <v>8.91777992248535</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>9.82499980926514</v>
       </c>
       <c r="G125" t="n">
-        <v>8.95423221588135</v>
+        <v>8.95423316955566</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G126" t="n">
-        <v>8.9314489364624</v>
+        <v>8.93144989013672</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G127" t="n">
-        <v>9.2504301071167</v>
+        <v>9.25042915344238</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>9.47827339172363</v>
+        <v>9.47827243804932</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G129" t="n">
-        <v>9.51472663879395</v>
+        <v>9.51472759246826</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G132" t="n">
-        <v>9.2413158416748</v>
+        <v>9.24131679534912</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G134" t="n">
-        <v>9.2413158416748</v>
+        <v>9.24131679534912</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>10.25</v>
       </c>
       <c r="G135" t="n">
-        <v>9.34156608581543</v>
+        <v>9.34156703948975</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G140" t="n">
-        <v>7.95628070831299</v>
+        <v>7.95628023147583</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G142" t="n">
-        <v>7.61907291412354</v>
+        <v>7.61907243728638</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G143" t="n">
-        <v>7.73755121231079</v>
+        <v>7.73755168914795</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G144" t="n">
-        <v>7.6464147567749</v>
+        <v>7.64641427993774</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G145" t="n">
-        <v>7.47325372695923</v>
+        <v>7.47325325012207</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G151" t="n">
-        <v>7.0266809463501</v>
+        <v>7.02668142318726</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>7.72499990463257</v>
       </c>
       <c r="G169" t="n">
-        <v>7.04035139083862</v>
+        <v>7.04035186767578</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G174" t="n">
-        <v>7.47325372695923</v>
+        <v>7.47325325012207</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G175" t="n">
-        <v>7.61907291412354</v>
+        <v>7.61907243728638</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>8.20499992370605</v>
       </c>
       <c r="G176" t="n">
-        <v>7.47780990600586</v>
+        <v>7.47781038284302</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G177" t="n">
-        <v>7.46413898468018</v>
+        <v>7.46413946151733</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G179" t="n">
-        <v>7.33199071884155</v>
+        <v>7.33199024200439</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G180" t="n">
-        <v>7.24996662139893</v>
+        <v>7.24996709823608</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>8</v>
       </c>
       <c r="G181" t="n">
-        <v>7.29097843170166</v>
+        <v>7.29097890853882</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>8</v>
       </c>
       <c r="G182" t="n">
-        <v>7.29097843170166</v>
+        <v>7.29097890853882</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>8</v>
       </c>
       <c r="G184" t="n">
-        <v>7.29097843170166</v>
+        <v>7.29097890853882</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>8</v>
       </c>
       <c r="G186" t="n">
-        <v>7.29097843170166</v>
+        <v>7.29097890853882</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G187" t="n">
-        <v>7.30009317398071</v>
+        <v>7.30009269714355</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G189" t="n">
-        <v>7.21351194381714</v>
+        <v>7.2135124206543</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G192" t="n">
-        <v>6.81250858306885</v>
+        <v>6.81250810623169</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G193" t="n">
-        <v>6.81250858306885</v>
+        <v>6.81250810623169</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G198" t="n">
-        <v>6.56188106536865</v>
+        <v>6.56188058853149</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G199" t="n">
-        <v>6.42517518997192</v>
+        <v>6.42517566680908</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G201" t="n">
-        <v>6.63023376464844</v>
+        <v>6.6302342414856</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>7.33500003814697</v>
       </c>
       <c r="G205" t="n">
-        <v>6.68491649627686</v>
+        <v>6.6849160194397</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G206" t="n">
-        <v>6.69858694076538</v>
+        <v>6.69858646392822</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>8.46500015258789</v>
       </c>
       <c r="G207" t="n">
-        <v>7.71476697921753</v>
+        <v>7.71476745605469</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>8.33500003814697</v>
       </c>
       <c r="G209" t="n">
-        <v>7.59628868103027</v>
+        <v>7.59628915786743</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>8.40499973297119</v>
       </c>
       <c r="G210" t="n">
-        <v>7.66008472442627</v>
+        <v>7.66008424758911</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G211" t="n">
-        <v>7.70565319061279</v>
+        <v>7.70565271377563</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G212" t="n">
-        <v>7.75577878952026</v>
+        <v>7.75577831268311</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G213" t="n">
-        <v>7.82868814468384</v>
+        <v>7.82868909835815</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G214" t="n">
-        <v>7.82868814468384</v>
+        <v>7.82868909835815</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>8.48499965667725</v>
       </c>
       <c r="G215" t="n">
-        <v>7.73299407958984</v>
+        <v>7.73299312591553</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G217" t="n">
-        <v>7.9380521774292</v>
+        <v>7.93805313110352</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G218" t="n">
-        <v>8.02007675170898</v>
+        <v>8.0200777053833</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>9.13500022888184</v>
       </c>
       <c r="G219" t="n">
-        <v>8.32538795471191</v>
+        <v>8.32538604736328</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G221" t="n">
-        <v>8.1932373046875</v>
+        <v>8.19323825836182</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>8.84500026702881</v>
       </c>
       <c r="G222" t="n">
-        <v>8.06108856201172</v>
+        <v>8.06108951568604</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>8.86499977111816</v>
       </c>
       <c r="G223" t="n">
-        <v>8.07931518554688</v>
+        <v>8.07931613922119</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G228" t="n">
-        <v>7.71932458877563</v>
+        <v>7.71932411193848</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G230" t="n">
-        <v>7.59173202514648</v>
+        <v>7.59173154830933</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>7.48236703872681</v>
+        <v>7.48236751556396</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G235" t="n">
-        <v>7.81957483291626</v>
+        <v>7.8195743560791</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>8.59500026702881</v>
       </c>
       <c r="G236" t="n">
-        <v>7.83324480056763</v>
+        <v>7.83324575424194</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>8.63500022888184</v>
       </c>
       <c r="G237" t="n">
-        <v>7.86970138549805</v>
+        <v>7.86970090866089</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>8.50500011444092</v>
       </c>
       <c r="G239" t="n">
-        <v>7.75122165679932</v>
+        <v>7.75122213363647</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G240" t="n">
-        <v>7.61907291412354</v>
+        <v>7.61907243728638</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G242" t="n">
-        <v>7.20895528793335</v>
+        <v>7.20895481109619</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>8.29500007629395</v>
       </c>
       <c r="G243" t="n">
-        <v>7.55983304977417</v>
+        <v>7.55983352661133</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>8.3149995803833</v>
       </c>
       <c r="G244" t="n">
-        <v>7.5780611038208</v>
+        <v>7.57806062698364</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>8.49499988555908</v>
       </c>
       <c r="G246" t="n">
-        <v>7.74210834503174</v>
+        <v>7.74210786819458</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G248" t="n">
-        <v>7.73755121231079</v>
+        <v>7.73755168914795</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G249" t="n">
-        <v>7.82868814468384</v>
+        <v>7.82868909835815</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>8.44499969482422</v>
       </c>
       <c r="G250" t="n">
-        <v>7.6965389251709</v>
+        <v>7.69653940200806</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>8.64500045776367</v>
       </c>
       <c r="G254" t="n">
-        <v>7.87881469726562</v>
+        <v>7.87881374359131</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G262" t="n">
-        <v>8.61246967315674</v>
+        <v>8.61246871948242</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>9.23499965667725</v>
       </c>
       <c r="G265" t="n">
-        <v>8.41652297973633</v>
+        <v>8.41652393341064</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G266" t="n">
-        <v>8.44386386871338</v>
+        <v>8.44386577606201</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G267" t="n">
-        <v>8.61246967315674</v>
+        <v>8.61246871948242</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G268" t="n">
-        <v>8.42107963562012</v>
+        <v>8.42108058929443</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G270" t="n">
-        <v>8.61246967315674</v>
+        <v>8.61246871948242</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G271" t="n">
-        <v>8.47576236724854</v>
+        <v>8.47576332092285</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G274" t="n">
-        <v>8.28437519073486</v>
+        <v>8.28437423706055</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>9.25500011444092</v>
       </c>
       <c r="G279" t="n">
-        <v>8.43475151062012</v>
+        <v>8.4347505569458</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>9.40499973297119</v>
       </c>
       <c r="G280" t="n">
-        <v>8.57145690917969</v>
+        <v>8.57145595550537</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>9.625</v>
       </c>
       <c r="G282" t="n">
-        <v>8.77195835113525</v>
+        <v>8.77195930480957</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G295" t="n">
-        <v>8.60335350036621</v>
+        <v>8.60335445404053</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G296" t="n">
-        <v>8.63069534301758</v>
+        <v>8.63069629669189</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G298" t="n">
-        <v>9.04992866516113</v>
+        <v>9.04992771148682</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G300" t="n">
-        <v>8.99524593353271</v>
+        <v>8.9952449798584</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>9.625</v>
       </c>
       <c r="G301" t="n">
-        <v>8.77195835113525</v>
+        <v>8.77195930480957</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G303" t="n">
-        <v>8.67626571655273</v>
+        <v>8.67626476287842</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>9.51500034332275</v>
       </c>
       <c r="G305" t="n">
-        <v>8.67170810699463</v>
+        <v>8.67170906066895</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G310" t="n">
-        <v>8.71271991729736</v>
+        <v>8.71272087097168</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>9.30500030517578</v>
       </c>
       <c r="G311" t="n">
-        <v>8.48032093048096</v>
+        <v>8.48031997680664</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>9.86499977111816</v>
       </c>
       <c r="G313" t="n">
-        <v>8.99068832397461</v>
+        <v>8.99068927764893</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G314" t="n">
-        <v>8.9314489364624</v>
+        <v>8.93144989013672</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G317" t="n">
-        <v>8.44386386871338</v>
+        <v>8.44386577606201</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G318" t="n">
-        <v>8.32994365692139</v>
+        <v>8.32994270324707</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>9.01500034332275</v>
       </c>
       <c r="G320" t="n">
-        <v>8.21602153778076</v>
+        <v>8.21602249145508</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G321" t="n">
-        <v>8.26158905029297</v>
+        <v>8.26159000396729</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>9.23499965667725</v>
       </c>
       <c r="G322" t="n">
-        <v>8.41652297973633</v>
+        <v>8.41652393341064</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>9.125</v>
       </c>
       <c r="G323" t="n">
-        <v>8.31627178192139</v>
+        <v>8.3162727355957</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G324" t="n">
-        <v>8.23880577087402</v>
+        <v>8.23880672454834</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>9.6850004196167</v>
       </c>
       <c r="G325" t="n">
-        <v>8.82664108276367</v>
+        <v>8.82664203643799</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>9.58500003814697</v>
       </c>
       <c r="G331" t="n">
-        <v>8.73550510406494</v>
+        <v>8.73550319671631</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G332" t="n">
-        <v>8.49399089813232</v>
+        <v>8.49398994445801</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G333" t="n">
-        <v>8.60335350036621</v>
+        <v>8.60335445404053</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G334" t="n">
-        <v>8.37551212310791</v>
+        <v>8.37551116943359</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G335" t="n">
-        <v>8.48487758636475</v>
+        <v>8.48487663269043</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G336" t="n">
-        <v>8.60335350036621</v>
+        <v>8.60335445404053</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>9.59500026702881</v>
       </c>
       <c r="G338" t="n">
-        <v>8.7446174621582</v>
+        <v>8.74461841583252</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G341" t="n">
-        <v>8.42107963562012</v>
+        <v>8.42108058929443</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G346" t="n">
-        <v>9.2504301071167</v>
+        <v>9.25042915344238</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G347" t="n">
-        <v>9.47827339172363</v>
+        <v>9.47827243804932</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G348" t="n">
-        <v>9.1319522857666</v>
+        <v>9.13195133209229</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>9.94499969482422</v>
       </c>
       <c r="G350" t="n">
-        <v>9.06359767913818</v>
+        <v>9.0635986328125</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G352" t="n">
-        <v>8.86765384674072</v>
+        <v>8.86765289306641</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G354" t="n">
-        <v>9.02258682250977</v>
+        <v>9.02258586883545</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>9.88500022888184</v>
       </c>
       <c r="G355" t="n">
-        <v>9.00891590118408</v>
+        <v>9.00891494750977</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G356" t="n">
-        <v>9.02258682250977</v>
+        <v>9.02258586883545</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G357" t="n">
-        <v>9.16840553283691</v>
+        <v>9.16840648651123</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G359" t="n">
-        <v>9.6696605682373</v>
+        <v>9.66966152191162</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G360" t="n">
-        <v>9.505615234375</v>
+        <v>9.50561428070068</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G361" t="n">
-        <v>9.47827339172363</v>
+        <v>9.47827243804932</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G363" t="n">
-        <v>9.70611572265625</v>
+        <v>9.70611476898193</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G364" t="n">
-        <v>9.4235897064209</v>
+        <v>9.42359066009521</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G365" t="n">
-        <v>9.33245277404785</v>
+        <v>9.33245182037354</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>9.83500003814697</v>
       </c>
       <c r="G366" t="n">
-        <v>8.96334743499756</v>
+        <v>8.96334648132324</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G367" t="n">
-        <v>9.15017890930176</v>
+        <v>9.15017795562744</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G368" t="n">
-        <v>8.97701740264893</v>
+        <v>8.97701835632324</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G369" t="n">
-        <v>8.66715145111084</v>
+        <v>8.66715240478516</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>9.40499973297119</v>
       </c>
       <c r="G370" t="n">
-        <v>8.57145690917969</v>
+        <v>8.57145595550537</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>9.47500038146973</v>
       </c>
       <c r="G371" t="n">
-        <v>8.63525390625</v>
+        <v>8.63525295257568</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>9.65499973297119</v>
       </c>
       <c r="G373" t="n">
-        <v>8.7992992401123</v>
+        <v>8.79930019378662</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>9.94499969482422</v>
       </c>
       <c r="G376" t="n">
-        <v>9.06359767913818</v>
+        <v>9.0635986328125</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>10.0299997329712</v>
       </c>
       <c r="G377" t="n">
-        <v>9.14106369018555</v>
+        <v>9.14106464385986</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G379" t="n">
-        <v>9.3078784942627</v>
+        <v>9.30787754058838</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>9.41868686676025</v>
+        <v>9.41868591308594</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G384" t="n">
-        <v>9.41868686676025</v>
+        <v>9.41868591308594</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>10.25</v>
       </c>
       <c r="G385" t="n">
-        <v>9.46485614776611</v>
+        <v>9.46485710144043</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G386" t="n">
-        <v>9.43715572357178</v>
+        <v>9.43715476989746</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G389" t="n">
-        <v>9.64030170440674</v>
+        <v>9.64030265808105</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G392" t="n">
-        <v>9.64030170440674</v>
+        <v>9.64030265808105</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G401" t="n">
-        <v>9.04932594299316</v>
+        <v>9.04932689666748</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G403" t="n">
-        <v>8.79539108276367</v>
+        <v>8.79539012908936</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G408" t="n">
-        <v>8.93851757049561</v>
+        <v>8.93851852416992</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G411" t="n">
-        <v>8.82771015167236</v>
+        <v>8.82771110534668</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G414" t="n">
-        <v>8.50451946258545</v>
+        <v>8.50452041625977</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>9.21500015258789</v>
       </c>
       <c r="G415" t="n">
-        <v>8.50913715362549</v>
+        <v>8.50913619995117</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G416" t="n">
-        <v>8.67073249816895</v>
+        <v>8.67073154449463</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G419" t="n">
-        <v>8.57839298248291</v>
+        <v>8.57839202880859</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G421" t="n">
-        <v>8.28290462493896</v>
+        <v>8.28290367126465</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G423" t="n">
-        <v>8.03820323944092</v>
+        <v>8.0382022857666</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>8.54500007629395</v>
       </c>
       <c r="G425" t="n">
-        <v>7.89045858383179</v>
+        <v>7.89045906066895</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G427" t="n">
-        <v>7.82120370864868</v>
+        <v>7.82120323181152</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G428" t="n">
-        <v>7.82120370864868</v>
+        <v>7.82120323181152</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>8.46500015258789</v>
       </c>
       <c r="G429" t="n">
-        <v>7.8165864944458</v>
+        <v>7.81658697128296</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G430" t="n">
-        <v>7.87660789489746</v>
+        <v>7.8766074180603</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G434" t="n">
-        <v>7.25792932510376</v>
+        <v>7.2579288482666</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G436" t="n">
-        <v>7.10095119476318</v>
+        <v>7.10095071792603</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G437" t="n">
-        <v>7.16558933258057</v>
+        <v>7.16558885574341</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7.72499990463257</v>
       </c>
       <c r="G438" t="n">
-        <v>7.13326978683472</v>
+        <v>7.13327026367188</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G440" t="n">
-        <v>6.90703678131104</v>
+        <v>6.90703725814819</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G443" t="n">
-        <v>6.61616516113281</v>
+        <v>6.61616563796997</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>7.02500009536743</v>
       </c>
       <c r="G445" t="n">
-        <v>6.48688936233521</v>
+        <v>6.48688983917236</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G447" t="n">
-        <v>6.33452844619751</v>
+        <v>6.33452892303467</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>7.13500022888184</v>
       </c>
       <c r="G448" t="n">
-        <v>6.588463306427</v>
+        <v>6.58846378326416</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G451" t="n">
-        <v>6.71312236785889</v>
+        <v>6.71312284469604</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G452" t="n">
-        <v>6.55614471435547</v>
+        <v>6.55614423751831</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G453" t="n">
-        <v>6.88856887817383</v>
+        <v>6.88856840133667</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G455" t="n">
-        <v>6.76390933990479</v>
+        <v>6.76390981674194</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G456" t="n">
-        <v>6.76390933990479</v>
+        <v>6.76390981674194</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>7.25</v>
       </c>
       <c r="G457" t="n">
-        <v>6.69465494155884</v>
+        <v>6.69465446472168</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G459" t="n">
-        <v>6.55614471435547</v>
+        <v>6.55614423751831</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G461" t="n">
-        <v>6.37146425247192</v>
+        <v>6.37146472930908</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G462" t="n">
-        <v>6.37146425247192</v>
+        <v>6.37146472930908</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G465" t="n">
-        <v>6.18678379058838</v>
+        <v>6.18678426742554</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G466" t="n">
-        <v>5.808189868927</v>
+        <v>5.80818939208984</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>5.875</v>
       </c>
       <c r="G471" t="n">
-        <v>5.4249792098999</v>
+        <v>5.42497873306274</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>6.16499996185303</v>
       </c>
       <c r="G472" t="n">
-        <v>5.69276523590088</v>
+        <v>5.69276475906372</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G473" t="n">
-        <v>5.5958080291748</v>
+        <v>5.59580755233765</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>5.82499980926514</v>
       </c>
       <c r="G475" t="n">
-        <v>5.37880897521973</v>
+        <v>5.37880849838257</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G479" t="n">
-        <v>5.70661592483521</v>
+        <v>5.70661544799805</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>5.9850001335144</v>
       </c>
       <c r="G480" t="n">
-        <v>5.52655267715454</v>
+        <v>5.5265531539917</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G482" t="n">
-        <v>5.1895112991333</v>
+        <v>5.18951177597046</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G483" t="n">
-        <v>5.1895112991333</v>
+        <v>5.18951177597046</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G485" t="n">
-        <v>5.17566061019897</v>
+        <v>5.17566108703613</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G487" t="n">
-        <v>5.06023597717285</v>
+        <v>5.06023550033569</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>5.45499992370605</v>
       </c>
       <c r="G489" t="n">
-        <v>5.03714990615845</v>
+        <v>5.03715085983276</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G490" t="n">
-        <v>4.80168342590332</v>
+        <v>4.80168294906616</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G491" t="n">
-        <v>4.95404386520386</v>
+        <v>4.95404434204102</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G496" t="n">
-        <v>5.13410758972168</v>
+        <v>5.13410711288452</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>5.77500009536743</v>
       </c>
       <c r="G497" t="n">
-        <v>5.33263826370239</v>
+        <v>5.33263874053955</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>5.61499977111816</v>
       </c>
       <c r="G498" t="n">
-        <v>5.18489408493042</v>
+        <v>5.18489456176758</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>5.69500017166138</v>
       </c>
       <c r="G500" t="n">
-        <v>5.25876712799072</v>
+        <v>5.25876665115356</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G505" t="n">
-        <v>5.39265966415405</v>
+        <v>5.39266014099121</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>5.65500020980835</v>
       </c>
       <c r="G511" t="n">
-        <v>5.22183084487915</v>
+        <v>5.22183036804199</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>5.65500020980835</v>
       </c>
       <c r="G512" t="n">
-        <v>5.22183084487915</v>
+        <v>5.22183036804199</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G515" t="n">
-        <v>5.11563920974731</v>
+        <v>5.11563968658447</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>5.72499990463257</v>
       </c>
       <c r="G517" t="n">
-        <v>5.28646898269653</v>
+        <v>5.28646850585938</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G519" t="n">
-        <v>5.25414943695068</v>
+        <v>5.25414991378784</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>5.65500020980835</v>
       </c>
       <c r="G521" t="n">
-        <v>5.22183084487915</v>
+        <v>5.22183036804199</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>6.30499982833862</v>
       </c>
       <c r="G532" t="n">
-        <v>5.82204055786133</v>
+        <v>5.82204103469849</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>6.40500020980835</v>
       </c>
       <c r="G533" t="n">
-        <v>5.91438102722168</v>
+        <v>5.91438150405884</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>6.33500003814697</v>
       </c>
       <c r="G534" t="n">
-        <v>5.8497428894043</v>
+        <v>5.84974336624146</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>6.38500022888184</v>
       </c>
       <c r="G539" t="n">
-        <v>5.89591360092163</v>
+        <v>5.89591312408447</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G541" t="n">
-        <v>6.05750846862793</v>
+        <v>6.05750799179077</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G549" t="n">
-        <v>5.56810617446899</v>
+        <v>5.56810569763184</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G550" t="n">
-        <v>5.6281270980835</v>
+        <v>5.62812662124634</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G551" t="n">
-        <v>5.70661592483521</v>
+        <v>5.70661544799805</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G552" t="n">
-        <v>5.70661592483521</v>
+        <v>5.70661544799805</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G559" t="n">
-        <v>5.56810617446899</v>
+        <v>5.56810569763184</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G560" t="n">
-        <v>5.36495780944824</v>
+        <v>5.36495733261108</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G561" t="n">
-        <v>5.36957502365112</v>
+        <v>5.36957454681396</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G562" t="n">
-        <v>5.36495780944824</v>
+        <v>5.36495733261108</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G568" t="n">
-        <v>5.32802152633667</v>
+        <v>5.32802200317383</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G571" t="n">
-        <v>5.17566061019897</v>
+        <v>5.17566108703613</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G572" t="n">
-        <v>5.2402982711792</v>
+        <v>5.24029922485352</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G573" t="n">
-        <v>5.32802152633667</v>
+        <v>5.32802200317383</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G575" t="n">
-        <v>5.13410758972168</v>
+        <v>5.13410711288452</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>5.70499992370605</v>
       </c>
       <c r="G576" t="n">
-        <v>5.26800012588501</v>
+        <v>5.26800060272217</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G577" t="n">
-        <v>5.06023597717285</v>
+        <v>5.06023550033569</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>5.45499992370605</v>
       </c>
       <c r="G581" t="n">
-        <v>5.03714990615845</v>
+        <v>5.03715085983276</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G586" t="n">
-        <v>5.56810617446899</v>
+        <v>5.56810569763184</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G588" t="n">
-        <v>5.5958080291748</v>
+        <v>5.59580755233765</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>5.72499990463257</v>
       </c>
       <c r="G590" t="n">
-        <v>5.28646898269653</v>
+        <v>5.28646850585938</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G593" t="n">
-        <v>5.39265966415405</v>
+        <v>5.39266014099121</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G594" t="n">
-        <v>5.05100107192993</v>
+        <v>5.05100154876709</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G599" t="n">
-        <v>4.70010900497437</v>
+        <v>4.70010948181152</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G600" t="n">
-        <v>4.81091737747192</v>
+        <v>4.81091785430908</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G603" t="n">
-        <v>4.89864015579224</v>
+        <v>4.89864063262939</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G605" t="n">
-        <v>4.66317319869995</v>
+        <v>4.66317367553711</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>4.52466297149658</v>
+        <v>4.52466344833374</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G607" t="n">
-        <v>4.52466297149658</v>
+        <v>4.52466344833374</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G613" t="n">
-        <v>4.37691879272461</v>
+        <v>4.37691926956177</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>4.74399995803833</v>
       </c>
       <c r="G614" t="n">
-        <v>4.38061237335205</v>
+        <v>4.38061285018921</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G615" t="n">
-        <v>4.37691879272461</v>
+        <v>4.37691926956177</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>4.71799993515015</v>
       </c>
       <c r="G616" t="n">
-        <v>4.35660362243652</v>
+        <v>4.35660409927368</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>5</v>
       </c>
       <c r="G618" t="n">
-        <v>4.61700296401978</v>
+        <v>4.61700344085693</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G620" t="n">
-        <v>4.50619554519653</v>
+        <v>4.50619506835938</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G621" t="n">
-        <v>4.56898641586304</v>
+        <v>4.56898593902588</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G622" t="n">
-        <v>4.70934343338013</v>
+        <v>4.70934295654297</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G623" t="n">
-        <v>4.7970666885376</v>
+        <v>4.79706621170044</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G624" t="n">
-        <v>4.6262378692627</v>
+        <v>4.62623739242554</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G628" t="n">
-        <v>4.70010900497437</v>
+        <v>4.70010948181152</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G629" t="n">
-        <v>4.60776853561401</v>
+        <v>4.60776901245117</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G633" t="n">
-        <v>4.63421201705933</v>
+        <v>4.63421249389648</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G639" t="n">
-        <v>4.47546672821045</v>
+        <v>4.47546625137329</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>4.81199979782104</v>
       </c>
       <c r="G640" t="n">
-        <v>4.60169792175293</v>
+        <v>4.60169744491577</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G645" t="n">
-        <v>4.45634031295776</v>
+        <v>4.45634078979492</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>4.62400007247925</v>
       </c>
       <c r="G647" t="n">
-        <v>4.42191457748413</v>
+        <v>4.42191410064697</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G650" t="n">
-        <v>4.17136430740356</v>
+        <v>4.17136478424072</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G653" t="n">
-        <v>4.20770359039307</v>
+        <v>4.20770406723022</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G659" t="n">
-        <v>3.9303777217865</v>
+        <v>3.93037796020508</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G669" t="n">
-        <v>3.65496444702148</v>
+        <v>3.65496468544006</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G672" t="n">
-        <v>3.81370973587036</v>
+        <v>3.81370949745178</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G673" t="n">
-        <v>3.81370973587036</v>
+        <v>3.81370949745178</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>4.17600011825562</v>
       </c>
       <c r="G674" t="n">
-        <v>3.99349331855774</v>
+        <v>3.99349355697632</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G690" t="n">
-        <v>3.4560546875</v>
+        <v>3.45605492591858</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G703" t="n">
-        <v>3.96862983703613</v>
+        <v>3.96862959861755</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>4.1560001373291</v>
       </c>
       <c r="G704" t="n">
-        <v>3.97436738014221</v>
+        <v>3.97436785697937</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>4.27600002288818</v>
       </c>
       <c r="G706" t="n">
-        <v>4.08912324905396</v>
+        <v>4.0891227722168</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>4.13600015640259</v>
       </c>
       <c r="G707" t="n">
-        <v>3.95524144172668</v>
+        <v>3.95524168014526</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G709" t="n">
-        <v>3.98966789245605</v>
+        <v>3.98966813087463</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G712" t="n">
-        <v>3.67026543617249</v>
+        <v>3.67026519775391</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G717" t="n">
-        <v>3.81370973587036</v>
+        <v>3.81370949745178</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G718" t="n">
-        <v>3.82327246665955</v>
+        <v>3.82327270507812</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G719" t="n">
-        <v>3.91507720947266</v>
+        <v>3.91507697105408</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G722" t="n">
-        <v>3.98584318161011</v>
+        <v>3.98584294319153</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>4.42600011825562</v>
       </c>
       <c r="G724" t="n">
-        <v>4.23256731033325</v>
+        <v>4.23256778717041</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>4.51200008392334</v>
       </c>
       <c r="G725" t="n">
-        <v>4.31480932235718</v>
+        <v>4.31480884552002</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G727" t="n">
-        <v>4.15032577514648</v>
+        <v>4.15032625198364</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>4.25</v>
       </c>
       <c r="G729" t="n">
-        <v>4.06425952911377</v>
+        <v>4.06425905227661</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>4.2039999961853</v>
       </c>
       <c r="G732" t="n">
-        <v>4.02026987075806</v>
+        <v>4.0202693939209</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>4.11399984359741</v>
       </c>
       <c r="G737" t="n">
-        <v>3.9342029094696</v>
+        <v>3.93420267105103</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G740" t="n">
-        <v>3.96862983703613</v>
+        <v>3.96862959861755</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G741" t="n">
-        <v>3.91507720947266</v>
+        <v>3.91507697105408</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>3.90799999237061</v>
       </c>
       <c r="G748" t="n">
-        <v>3.73720598220825</v>
+        <v>3.73720574378967</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G750" t="n">
-        <v>3.70086646080017</v>
+        <v>3.70086669921875</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>3.93799996376038</v>
       </c>
       <c r="G751" t="n">
-        <v>3.76589465141296</v>
+        <v>3.76589488983154</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G755" t="n">
-        <v>3.7391185760498</v>
+        <v>3.73911881446838</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G759" t="n">
-        <v>3.57846069335938</v>
+        <v>3.57846093177795</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G760" t="n">
-        <v>3.62245035171509</v>
+        <v>3.62245059013367</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G762" t="n">
-        <v>3.56316018104553</v>
+        <v>3.56315994262695</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G763" t="n">
-        <v>3.54785943031311</v>
+        <v>3.54785919189453</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>3.64800000190735</v>
       </c>
       <c r="G766" t="n">
-        <v>3.4885687828064</v>
+        <v>3.48856902122498</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>3.64400005340576</v>
       </c>
       <c r="G771" t="n">
-        <v>3.48474383354187</v>
+        <v>3.48474359512329</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>3.63199996948242</v>
       </c>
       <c r="G772" t="n">
-        <v>3.47326803207397</v>
+        <v>3.47326827049255</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>3.95799994468689</v>
       </c>
       <c r="G776" t="n">
-        <v>3.78502058982849</v>
+        <v>3.78502082824707</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G777" t="n">
-        <v>3.76972007751465</v>
+        <v>3.76971983909607</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G779" t="n">
-        <v>3.70086646080017</v>
+        <v>3.70086669921875</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G780" t="n">
-        <v>3.5975866317749</v>
+        <v>3.59758687019348</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G783" t="n">
-        <v>3.44075417518616</v>
+        <v>3.44075393676758</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>3.41599988937378</v>
       </c>
       <c r="G784" t="n">
-        <v>3.26670789718628</v>
+        <v>3.26670813560486</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>3.41599988937378</v>
       </c>
       <c r="G785" t="n">
-        <v>3.26670789718628</v>
+        <v>3.26670813560486</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>3.46799993515015</v>
       </c>
       <c r="G786" t="n">
-        <v>3.31643557548523</v>
+        <v>3.31643533706665</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G787" t="n">
-        <v>3.29157185554504</v>
+        <v>3.29157161712646</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G795" t="n">
-        <v>3.2074179649353</v>
+        <v>3.20741772651672</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>3.47399997711182</v>
       </c>
       <c r="G808" t="n">
-        <v>3.32217311859131</v>
+        <v>3.32217335700989</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G814" t="n">
-        <v>3.22654390335083</v>
+        <v>3.22654366493225</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G820" t="n">
-        <v>3.55168437957764</v>
+        <v>3.55168461799622</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G821" t="n">
-        <v>3.50769472122192</v>
+        <v>3.5076949596405</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G823" t="n">
-        <v>3.53638386726379</v>
+        <v>3.53638362884521</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G826" t="n">
-        <v>3.58228611946106</v>
+        <v>3.58228588104248</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G827" t="n">
-        <v>3.57654809951782</v>
+        <v>3.5765483379364</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>3.84400010108948</v>
       </c>
       <c r="G828" t="n">
-        <v>3.67600297927856</v>
+        <v>3.67600321769714</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>4.22599983215332</v>
       </c>
       <c r="G833" t="n">
-        <v>4.04130840301514</v>
+        <v>4.04130792617798</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>4.68599987030029</v>
       </c>
       <c r="G841" t="n">
-        <v>4.48120403289795</v>
+        <v>4.48120450973511</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G843" t="n">
-        <v>4.54431962966919</v>
+        <v>4.54432010650635</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G846" t="n">
-        <v>4.35688638687134</v>
+        <v>4.35688591003418</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G847" t="n">
-        <v>4.2631688117981</v>
+        <v>4.26316928863525</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G849" t="n">
-        <v>4.17136430740356</v>
+        <v>4.17136478424072</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G851" t="n">
-        <v>3.9303777217865</v>
+        <v>3.93037796020508</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G854" t="n">
-        <v>3.77928304672241</v>
+        <v>3.77928280830383</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>3.51200008392334</v>
       </c>
       <c r="G858" t="n">
-        <v>3.35851287841797</v>
+        <v>3.35851263999939</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>3.56800007820129</v>
       </c>
       <c r="G859" t="n">
-        <v>3.41206550598145</v>
+        <v>3.41206526756287</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G863" t="n">
-        <v>3.47900605201721</v>
+        <v>3.47900581359863</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G868" t="n">
-        <v>3.77928304672241</v>
+        <v>3.77928280830383</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>4.12400007247925</v>
       </c>
       <c r="G872" t="n">
-        <v>3.94376611709595</v>
+        <v>3.94376587867737</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G879" t="n">
-        <v>4.47546672821045</v>
+        <v>4.47546625137329</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>4.38800001144409</v>
       </c>
       <c r="G883" t="n">
-        <v>4.19622802734375</v>
+        <v>4.19622850418091</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G886" t="n">
-        <v>4.20196628570557</v>
+        <v>4.20196580886841</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G892" t="n">
-        <v>4.57109642028809</v>
+        <v>4.57109689712524</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>4.74599981307983</v>
       </c>
       <c r="G894" t="n">
-        <v>4.53858232498169</v>
+        <v>4.53858184814453</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G895" t="n">
-        <v>4.68585157394409</v>
+        <v>4.68585205078125</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -32352,6 +32352,32 @@
         <v>4.21799993515015</v>
       </c>
       <c r="H1230" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1231" t="n">
+        <v>1006301</v>
+      </c>
+      <c r="C1231" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="D1231" t="n">
+        <v>4.24399995803833</v>
+      </c>
+      <c r="E1231" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="F1231" t="n">
+        <v>4.30800008773804</v>
+      </c>
+      <c r="G1231" t="n">
+        <v>4.30800008773804</v>
+      </c>
+      <c r="H1231" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ARIS.MI.xlsx
+++ b/data/ARIS.MI.xlsx
@@ -28747,8 +28747,31 @@
       <c r="E1234" t="n">
         <v>4.17000007629395</v>
       </c>
-      <c r="F1234"/>
+      <c r="F1234" t="n">
+        <v>4.24399995803833</v>
+      </c>
       <c r="G1234" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1235" t="n">
+        <v>470043</v>
+      </c>
+      <c r="C1235" t="n">
+        <v>4.43599987030029</v>
+      </c>
+      <c r="D1235" t="n">
+        <v>4.26599979400635</v>
+      </c>
+      <c r="E1235" t="n">
+        <v>4.32999992370605</v>
+      </c>
+      <c r="F1235"/>
+      <c r="G1235" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ARIS.MI.xlsx
+++ b/data/ARIS.MI.xlsx
@@ -28770,8 +28770,31 @@
       <c r="E1235" t="n">
         <v>4.32999992370605</v>
       </c>
-      <c r="F1235"/>
+      <c r="F1235" t="n">
+        <v>4.35799980163574</v>
+      </c>
       <c r="G1235" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1236" t="n">
+        <v>550372</v>
+      </c>
+      <c r="C1236" t="n">
+        <v>4.3439998626709</v>
+      </c>
+      <c r="D1236" t="n">
+        <v>4.08599996566772</v>
+      </c>
+      <c r="E1236" t="n">
+        <v>4.26999998092651</v>
+      </c>
+      <c r="F1236"/>
+      <c r="G1236" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ARIS.MI.xlsx
+++ b/data/ARIS.MI.xlsx
@@ -28793,8 +28793,31 @@
       <c r="E1236" t="n">
         <v>4.26999998092651</v>
       </c>
-      <c r="F1236"/>
+      <c r="F1236" t="n">
+        <v>4.10799980163574</v>
+      </c>
       <c r="G1236" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1237" t="n">
+        <v>370813</v>
+      </c>
+      <c r="C1237" t="n">
+        <v>4.15999984741211</v>
+      </c>
+      <c r="D1237" t="n">
+        <v>3.97000002861023</v>
+      </c>
+      <c r="E1237" t="n">
+        <v>4.12400007247925</v>
+      </c>
+      <c r="F1237"/>
+      <c r="G1237" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ARIS.MI.xlsx
+++ b/data/ARIS.MI.xlsx
@@ -28816,8 +28816,31 @@
       <c r="E1237" t="n">
         <v>4.12400007247925</v>
       </c>
-      <c r="F1237"/>
+      <c r="F1237" t="n">
+        <v>4.03200006484985</v>
+      </c>
       <c r="G1237" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1238" t="n">
+        <v>737907</v>
+      </c>
+      <c r="C1238" t="n">
+        <v>4.19999980926514</v>
+      </c>
+      <c r="D1238" t="n">
+        <v>3.84999990463257</v>
+      </c>
+      <c r="E1238" t="n">
+        <v>4.19999980926514</v>
+      </c>
+      <c r="F1238"/>
+      <c r="G1238" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ARIS.MI.xlsx
+++ b/data/ARIS.MI.xlsx
@@ -28846,6 +28846,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1239">
+      <c r="A1239" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1239" t="n">
+        <v>3237357</v>
+      </c>
+      <c r="C1239" t="n">
+        <v>3.92600011825562</v>
+      </c>
+      <c r="D1239" t="n">
+        <v>3.25999999046326</v>
+      </c>
+      <c r="E1239" t="n">
+        <v>3.86400008201599</v>
+      </c>
+      <c r="F1239" t="n">
+        <v>3.34400010108948</v>
+      </c>
+      <c r="G1239" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ARIS.MI.xlsx
+++ b/data/ARIS.MI.xlsx
@@ -447,7 +447,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G3" t="n">
-        <v>9.34524345397949</v>
+        <v>9.34524440765381</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G5" t="n">
-        <v>9.25538539886475</v>
+        <v>9.25538635253906</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G11" t="n">
-        <v>9.23741340637207</v>
+        <v>9.2374153137207</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G17" t="n">
-        <v>8.83305358886719</v>
+        <v>8.83305263519287</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G19" t="n">
-        <v>8.71623802185059</v>
+        <v>8.71623706817627</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G20" t="n">
-        <v>9.12958335876465</v>
+        <v>9.12958431243896</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G21" t="n">
-        <v>9.07566833496094</v>
+        <v>9.07567024230957</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G23" t="n">
-        <v>9.07566833496094</v>
+        <v>9.07567024230957</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G24" t="n">
-        <v>9.12958335876465</v>
+        <v>9.12958431243896</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G25" t="n">
-        <v>9.11161327362061</v>
+        <v>9.11161422729492</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G26" t="n">
-        <v>9.12958335876465</v>
+        <v>9.12958431243896</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G28" t="n">
-        <v>9.65076065063477</v>
+        <v>9.65076160430908</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G29" t="n">
-        <v>9.74061870574951</v>
+        <v>9.74062061309814</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G33" t="n">
-        <v>9.63279056549072</v>
+        <v>9.63279151916504</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G34" t="n">
-        <v>10.0191783905029</v>
+        <v>10.0191793441772</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G44" t="n">
-        <v>9.12059783935547</v>
+        <v>9.12059879302979</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G47" t="n">
-        <v>9.34524345397949</v>
+        <v>9.34524440765381</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>10.4899997711182</v>
       </c>
       <c r="G48" t="n">
-        <v>9.42611503601074</v>
+        <v>9.42611598968506</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G49" t="n">
-        <v>9.34524345397949</v>
+        <v>9.34524440765381</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G50" t="n">
-        <v>9.11161327362061</v>
+        <v>9.11161422729492</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G52" t="n">
-        <v>9.12958335876465</v>
+        <v>9.12958431243896</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G53" t="n">
-        <v>9.24639987945557</v>
+        <v>9.24639892578125</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G56" t="n">
-        <v>8.72522449493408</v>
+        <v>8.72522258758545</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G60" t="n">
-        <v>8.95885372161865</v>
+        <v>8.95885467529297</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G61" t="n">
-        <v>8.71623802185059</v>
+        <v>8.71623706817627</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>8.75</v>
       </c>
       <c r="G64" t="n">
-        <v>7.86258459091187</v>
+        <v>7.86258506774902</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>9.20499992370605</v>
       </c>
       <c r="G66" t="n">
-        <v>8.27144050598145</v>
+        <v>8.27143955230713</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>7.875</v>
       </c>
       <c r="G70" t="n">
-        <v>7.07632684707642</v>
+        <v>7.07632637023926</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>8</v>
       </c>
       <c r="G71" t="n">
-        <v>7.18864965438843</v>
+        <v>7.18864917755127</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G72" t="n">
-        <v>7.42228078842163</v>
+        <v>7.42228174209595</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G73" t="n">
-        <v>7.79069852828979</v>
+        <v>7.79069948196411</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G76" t="n">
-        <v>8.66232299804688</v>
+        <v>8.66232204437256</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G78" t="n">
-        <v>9.23741340637207</v>
+        <v>9.2374153137207</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G82" t="n">
-        <v>9.07566833496094</v>
+        <v>9.07567024230957</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G83" t="n">
-        <v>8.74319458007812</v>
+        <v>8.74319362640381</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>9.48499965667725</v>
       </c>
       <c r="G84" t="n">
-        <v>8.52304267883301</v>
+        <v>8.52304172515869</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G85" t="n">
-        <v>8.6443510055542</v>
+        <v>8.64435005187988</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G87" t="n">
-        <v>8.67130756378174</v>
+        <v>8.67130661010742</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G88" t="n">
-        <v>8.80609607696533</v>
+        <v>8.80609512329102</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G89" t="n">
-        <v>8.50057792663574</v>
+        <v>8.50057697296143</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G92" t="n">
-        <v>8.71623802185059</v>
+        <v>8.71623706817627</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G93" t="n">
-        <v>8.50057792663574</v>
+        <v>8.50057697296143</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G94" t="n">
-        <v>8.18607425689697</v>
+        <v>8.18607330322266</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.25</v>
       </c>
       <c r="G95" t="n">
-        <v>8.31187629699707</v>
+        <v>8.31187534332275</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G96" t="n">
-        <v>8.24897575378418</v>
+        <v>8.24897480010986</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>9.25</v>
       </c>
       <c r="G97" t="n">
-        <v>8.31187629699707</v>
+        <v>8.31187534332275</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G100" t="n">
-        <v>8.80609607696533</v>
+        <v>8.80609512329102</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>9.75</v>
       </c>
       <c r="G101" t="n">
-        <v>8.76116752624512</v>
+        <v>8.7611665725708</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G102" t="n">
-        <v>8.5904369354248</v>
+        <v>8.59043598175049</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G103" t="n">
-        <v>8.71623802185059</v>
+        <v>8.71623706817627</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G107" t="n">
-        <v>8.67130756378174</v>
+        <v>8.67130661010742</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>9</v>
       </c>
       <c r="G109" t="n">
-        <v>8.08723163604736</v>
+        <v>8.08723068237305</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G110" t="n">
-        <v>7.89852809906006</v>
+        <v>7.89852905273438</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>9.25500011444092</v>
       </c>
       <c r="G111" t="n">
-        <v>8.31636905670166</v>
+        <v>8.31636810302734</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G112" t="n">
-        <v>8.10520267486572</v>
+        <v>8.10520172119141</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>8.6850004196167</v>
       </c>
       <c r="G114" t="n">
-        <v>7.80417823791504</v>
+        <v>7.80417728424072</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>9.02499961853027</v>
       </c>
       <c r="G116" t="n">
-        <v>8.10969543457031</v>
+        <v>8.109694480896</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G117" t="n">
-        <v>8.32086181640625</v>
+        <v>8.32086277008057</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G118" t="n">
-        <v>8.54550838470459</v>
+        <v>8.54550743103027</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>8.80609607696533</v>
+        <v>8.80609512329102</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G121" t="n">
-        <v>8.74319458007812</v>
+        <v>8.74319362640381</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>9.94499969482422</v>
       </c>
       <c r="G122" t="n">
-        <v>8.93638896942139</v>
+        <v>8.9363899230957</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G123" t="n">
-        <v>8.96334743499756</v>
+        <v>8.96334838867188</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -32638,6 +32638,32 @@
         <v>3.29999995231628</v>
       </c>
       <c r="H1241" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1242" t="n">
+        <v>903204</v>
+      </c>
+      <c r="C1242" t="n">
+        <v>3.34400010108948</v>
+      </c>
+      <c r="D1242" t="n">
+        <v>3.21199989318848</v>
+      </c>
+      <c r="E1242" t="n">
+        <v>3.31800007820129</v>
+      </c>
+      <c r="F1242" t="n">
+        <v>3.34999990463257</v>
+      </c>
+      <c r="G1242" t="n">
+        <v>3.34999990463257</v>
+      </c>
+      <c r="H1242" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ARIS.MI.xlsx
+++ b/data/ARIS.MI.xlsx
@@ -447,7 +447,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G3" t="n">
-        <v>9.34524440765381</v>
+        <v>9.34524250030518</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G4" t="n">
-        <v>9.17451477050781</v>
+        <v>9.1745138168335</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G6" t="n">
-        <v>9.20147037506104</v>
+        <v>9.20147132873535</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G7" t="n">
-        <v>9.20147037506104</v>
+        <v>9.20147132873535</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G8" t="n">
-        <v>9.20147037506104</v>
+        <v>9.20147132873535</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G9" t="n">
-        <v>9.21944236755371</v>
+        <v>9.21944332122803</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G10" t="n">
-        <v>9.20147037506104</v>
+        <v>9.20147132873535</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G11" t="n">
-        <v>9.2374153137207</v>
+        <v>9.23741340637207</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G12" t="n">
-        <v>9.20147037506104</v>
+        <v>9.20147132873535</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G13" t="n">
-        <v>9.20147037506104</v>
+        <v>9.20147132873535</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G14" t="n">
-        <v>9.20147037506104</v>
+        <v>9.20147132873535</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G15" t="n">
-        <v>9.21944236755371</v>
+        <v>9.21944332122803</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G16" t="n">
-        <v>8.92291069030762</v>
+        <v>8.92291164398193</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G18" t="n">
-        <v>8.6353645324707</v>
+        <v>8.63536548614502</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G20" t="n">
-        <v>9.12958431243896</v>
+        <v>9.12958335876465</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G24" t="n">
-        <v>9.12958431243896</v>
+        <v>9.12958335876465</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G25" t="n">
-        <v>9.11161422729492</v>
+        <v>9.11161327362061</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G26" t="n">
-        <v>9.12958431243896</v>
+        <v>9.12958335876465</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G28" t="n">
-        <v>9.65076160430908</v>
+        <v>9.65076065063477</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G29" t="n">
-        <v>9.74062061309814</v>
+        <v>9.74061965942383</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G30" t="n">
-        <v>10.1180229187012</v>
+        <v>10.1180238723755</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G32" t="n">
-        <v>9.17451477050781</v>
+        <v>9.1745138168335</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G33" t="n">
-        <v>9.63279151916504</v>
+        <v>9.63279056549072</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>10.9899997711182</v>
       </c>
       <c r="G35" t="n">
-        <v>9.87540626525879</v>
+        <v>9.87540721893311</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G37" t="n">
-        <v>10.1180229187012</v>
+        <v>10.1180238723755</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G38" t="n">
-        <v>9.72264766693115</v>
+        <v>9.72264862060547</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G40" t="n">
-        <v>9.67771911621094</v>
+        <v>9.67772006988525</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G42" t="n">
-        <v>9.10262680053711</v>
+        <v>9.10262775421143</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G43" t="n">
-        <v>9.17451477050781</v>
+        <v>9.1745138168335</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G44" t="n">
-        <v>9.12059879302979</v>
+        <v>9.12059783935547</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G46" t="n">
-        <v>9.20147037506104</v>
+        <v>9.20147132873535</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G47" t="n">
-        <v>9.34524440765381</v>
+        <v>9.34524250030518</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G49" t="n">
-        <v>9.34524440765381</v>
+        <v>9.34524250030518</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G50" t="n">
-        <v>9.11161422729492</v>
+        <v>9.11161327362061</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G51" t="n">
-        <v>9.16552734375</v>
+        <v>9.16552829742432</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G52" t="n">
-        <v>9.12958431243896</v>
+        <v>9.12958335876465</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G53" t="n">
-        <v>9.24639892578125</v>
+        <v>9.24639987945557</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G54" t="n">
-        <v>9.16552734375</v>
+        <v>9.16552829742432</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G55" t="n">
-        <v>8.994797706604</v>
+        <v>8.99479866027832</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G57" t="n">
-        <v>9.10262680053711</v>
+        <v>9.10262775421143</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G58" t="n">
-        <v>8.994797706604</v>
+        <v>8.99479866027832</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G59" t="n">
-        <v>9.19248390197754</v>
+        <v>9.19248485565186</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>9.41499996185303</v>
       </c>
       <c r="G62" t="n">
-        <v>8.46014213562012</v>
+        <v>8.4601411819458</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>8.75</v>
       </c>
       <c r="G64" t="n">
-        <v>7.86258506774902</v>
+        <v>7.86258411407471</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G67" t="n">
-        <v>7.70982646942139</v>
+        <v>7.70982599258423</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G68" t="n">
-        <v>8.03331565856934</v>
+        <v>8.03331470489502</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>7.875</v>
       </c>
       <c r="G70" t="n">
-        <v>7.07632637023926</v>
+        <v>7.07632684707642</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G72" t="n">
-        <v>7.42228174209595</v>
+        <v>7.42228078842163</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G73" t="n">
-        <v>7.79069948196411</v>
+        <v>7.79069805145264</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>8.3149995803833</v>
       </c>
       <c r="G74" t="n">
-        <v>7.47170209884644</v>
+        <v>7.47170162200928</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>8.78499984741211</v>
       </c>
       <c r="G75" t="n">
-        <v>7.89403486251831</v>
+        <v>7.89403533935547</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G76" t="n">
-        <v>8.66232204437256</v>
+        <v>8.66232299804688</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>9.51500034332275</v>
       </c>
       <c r="G77" t="n">
-        <v>8.55000019073486</v>
+        <v>8.54999923706055</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G78" t="n">
-        <v>9.2374153137207</v>
+        <v>9.23741340637207</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G80" t="n">
-        <v>9.19248390197754</v>
+        <v>9.19248485565186</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>9.71500015258789</v>
       </c>
       <c r="G81" t="n">
-        <v>8.72971725463867</v>
+        <v>8.72971630096436</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G83" t="n">
-        <v>8.74319362640381</v>
+        <v>8.74319458007812</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>9.48499965667725</v>
       </c>
       <c r="G84" t="n">
-        <v>8.52304172515869</v>
+        <v>8.52304267883301</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G85" t="n">
-        <v>8.64435005187988</v>
+        <v>8.6443510055542</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G87" t="n">
-        <v>8.67130661010742</v>
+        <v>8.67130756378174</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G88" t="n">
-        <v>8.80609512329102</v>
+        <v>8.80609607696533</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G89" t="n">
-        <v>8.50057697296143</v>
+        <v>8.50057792663574</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G91" t="n">
-        <v>8.5185489654541</v>
+        <v>8.51854801177979</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G93" t="n">
-        <v>8.50057697296143</v>
+        <v>8.50057792663574</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G94" t="n">
-        <v>8.18607330322266</v>
+        <v>8.18607425689697</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G98" t="n">
-        <v>8.62637901306152</v>
+        <v>8.62637996673584</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G99" t="n">
-        <v>8.45564842224121</v>
+        <v>8.45564937591553</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G100" t="n">
-        <v>8.80609512329102</v>
+        <v>8.80609607696533</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G102" t="n">
-        <v>8.59043598175049</v>
+        <v>8.5904369354248</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>9.71500015258789</v>
       </c>
       <c r="G106" t="n">
-        <v>8.72971725463867</v>
+        <v>8.72971630096436</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G107" t="n">
-        <v>8.67130661010742</v>
+        <v>8.67130756378174</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>9.53499984741211</v>
       </c>
       <c r="G108" t="n">
-        <v>8.56797218322754</v>
+        <v>8.56797122955322</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>9</v>
       </c>
       <c r="G109" t="n">
-        <v>8.08723068237305</v>
+        <v>8.08723163604736</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G110" t="n">
-        <v>7.89852905273438</v>
+        <v>7.89852857589722</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>9.25500011444092</v>
       </c>
       <c r="G111" t="n">
-        <v>8.31636810302734</v>
+        <v>8.31636905670166</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G112" t="n">
-        <v>8.10520172119141</v>
+        <v>8.10520362854004</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G113" t="n">
-        <v>7.9973726272583</v>
+        <v>7.99737215042114</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G115" t="n">
-        <v>7.80867004394531</v>
+        <v>7.80867052078247</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G117" t="n">
-        <v>8.32086277008057</v>
+        <v>8.32086086273193</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G119" t="n">
-        <v>8.62637901306152</v>
+        <v>8.62637996673584</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>8.80609512329102</v>
+        <v>8.80609607696533</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G121" t="n">
-        <v>8.74319362640381</v>
+        <v>8.74319458007812</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G123" t="n">
-        <v>8.96334838867188</v>
+        <v>8.96334743499756</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>9.82499980926514</v>
       </c>
       <c r="G125" t="n">
-        <v>8.95423316955566</v>
+        <v>8.95423221588135</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G127" t="n">
-        <v>9.25042819976807</v>
+        <v>9.25042915344238</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G129" t="n">
-        <v>9.51472663879395</v>
+        <v>9.51472759246826</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G130" t="n">
-        <v>9.35068035125732</v>
+        <v>9.35068225860596</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G131" t="n">
-        <v>9.20486068725586</v>
+        <v>9.20486164093018</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>10.25</v>
       </c>
       <c r="G135" t="n">
-        <v>9.34156608581543</v>
+        <v>9.34156703948975</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>9.84500026702881</v>
       </c>
       <c r="G137" t="n">
-        <v>8.97246170043945</v>
+        <v>8.97246074676514</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G138" t="n">
-        <v>8.70360660552979</v>
+        <v>8.70360565185547</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G139" t="n">
-        <v>8.52133274078369</v>
+        <v>8.52133178710938</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G142" t="n">
-        <v>7.61907243728638</v>
+        <v>7.61907196044922</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G143" t="n">
-        <v>7.73755168914795</v>
+        <v>7.73755121231079</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G144" t="n">
-        <v>7.64641427993774</v>
+        <v>7.6464147567749</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G146" t="n">
-        <v>7.34566211700439</v>
+        <v>7.34566164016724</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>7.375</v>
       </c>
       <c r="G148" t="n">
-        <v>6.7213716506958</v>
+        <v>6.72137117385864</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G149" t="n">
-        <v>6.87174797058105</v>
+        <v>6.8717474937439</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G151" t="n">
-        <v>7.02668142318726</v>
+        <v>7.0266809463501</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>7.81500005722046</v>
       </c>
       <c r="G152" t="n">
-        <v>7.12237501144409</v>
+        <v>7.12237548828125</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G157" t="n">
-        <v>6.78061056137085</v>
+        <v>6.78061008453369</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G161" t="n">
-        <v>6.64846134185791</v>
+        <v>6.64846181869507</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G165" t="n">
-        <v>6.99478340148926</v>
+        <v>6.9947829246521</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G168" t="n">
-        <v>6.99478340148926</v>
+        <v>6.9947829246521</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G171" t="n">
-        <v>6.99478340148926</v>
+        <v>6.9947829246521</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G175" t="n">
-        <v>7.61907243728638</v>
+        <v>7.61907196044922</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>8.20499992370605</v>
       </c>
       <c r="G176" t="n">
-        <v>7.47780990600586</v>
+        <v>7.4778094291687</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G177" t="n">
-        <v>7.46413946151733</v>
+        <v>7.46413898468018</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G179" t="n">
-        <v>7.33199071884155</v>
+        <v>7.33199024200439</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G180" t="n">
-        <v>7.24996709823608</v>
+        <v>7.24996662139893</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>8</v>
       </c>
       <c r="G181" t="n">
-        <v>7.29097938537598</v>
+        <v>7.29097890853882</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>8</v>
       </c>
       <c r="G182" t="n">
-        <v>7.29097938537598</v>
+        <v>7.29097890853882</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>8</v>
       </c>
       <c r="G184" t="n">
-        <v>7.29097938537598</v>
+        <v>7.29097890853882</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>8</v>
       </c>
       <c r="G186" t="n">
-        <v>7.29097938537598</v>
+        <v>7.29097890853882</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G196" t="n">
-        <v>6.85352039337158</v>
+        <v>6.85351991653442</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G198" t="n">
-        <v>6.56188058853149</v>
+        <v>6.56188106536865</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>7.0149998664856</v>
       </c>
       <c r="G200" t="n">
-        <v>6.39327716827393</v>
+        <v>6.39327764511108</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G201" t="n">
-        <v>6.63023376464844</v>
+        <v>6.6302342414856</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>7.75</v>
       </c>
       <c r="G203" t="n">
-        <v>7.06313610076904</v>
+        <v>7.06313562393188</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>7.33500003814697</v>
       </c>
       <c r="G205" t="n">
-        <v>6.6849160194397</v>
+        <v>6.68491649627686</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>8.46500015258789</v>
       </c>
       <c r="G207" t="n">
-        <v>7.71476745605469</v>
+        <v>7.71476697921753</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G208" t="n">
-        <v>7.55527687072754</v>
+        <v>7.55527591705322</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>8.33500003814697</v>
       </c>
       <c r="G209" t="n">
-        <v>7.59628868103027</v>
+        <v>7.59628915786743</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>8.48499965667725</v>
       </c>
       <c r="G215" t="n">
-        <v>7.732994556427</v>
+        <v>7.73299407958984</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G217" t="n">
-        <v>7.93805360794067</v>
+        <v>7.93805408477783</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G218" t="n">
-        <v>8.02007675170898</v>
+        <v>8.02007579803467</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>9.03499984741211</v>
       </c>
       <c r="G220" t="n">
-        <v>8.23425006866455</v>
+        <v>8.23424911499023</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G221" t="n">
-        <v>8.1932373046875</v>
+        <v>8.19323635101318</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>8.79500007629395</v>
       </c>
       <c r="G224" t="n">
-        <v>8.01552104949951</v>
+        <v>8.0155200958252</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G226" t="n">
-        <v>7.65552759170532</v>
+        <v>7.65552806854248</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>8.60499954223633</v>
       </c>
       <c r="G229" t="n">
-        <v>7.84235906600952</v>
+        <v>7.84235858917236</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>7.48236751556396</v>
+        <v>7.48236656188965</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G232" t="n">
-        <v>7.5416054725647</v>
+        <v>7.54160594940186</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G233" t="n">
-        <v>7.60084581375122</v>
+        <v>7.60084629058838</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G234" t="n">
-        <v>7.85602998733521</v>
+        <v>7.85602951049805</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>8.63500022888184</v>
       </c>
       <c r="G237" t="n">
-        <v>7.86970090866089</v>
+        <v>7.86970043182373</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G238" t="n">
-        <v>7.86514377593994</v>
+        <v>7.86514282226562</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>8.50500011444092</v>
       </c>
       <c r="G239" t="n">
-        <v>7.75122261047363</v>
+        <v>7.75122213363647</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G240" t="n">
-        <v>7.61907243728638</v>
+        <v>7.61907196044922</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G242" t="n">
-        <v>7.20895528793335</v>
+        <v>7.20895576477051</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>8.29500007629395</v>
       </c>
       <c r="G243" t="n">
-        <v>7.55983352661133</v>
+        <v>7.55983304977417</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>8.15499973297119</v>
       </c>
       <c r="G245" t="n">
-        <v>7.43224143981934</v>
+        <v>7.43224096298218</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G248" t="n">
-        <v>7.73755168914795</v>
+        <v>7.73755121231079</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>8.44499969482422</v>
       </c>
       <c r="G250" t="n">
-        <v>7.69653940200806</v>
+        <v>7.6965389251709</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G251" t="n">
-        <v>7.76489353179932</v>
+        <v>7.76489305496216</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>8.64500045776367</v>
       </c>
       <c r="G254" t="n">
-        <v>7.87881565093994</v>
+        <v>7.87881469726562</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G255" t="n">
-        <v>8.06564712524414</v>
+        <v>8.06564617156982</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G257" t="n">
-        <v>8.3800687789917</v>
+        <v>8.38006782531738</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G258" t="n">
-        <v>8.34817123413086</v>
+        <v>8.34817028045654</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>9.50500011444092</v>
       </c>
       <c r="G261" t="n">
-        <v>8.66259479522705</v>
+        <v>8.66259384155273</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>9.5</v>
       </c>
       <c r="G263" t="n">
-        <v>8.65803718566895</v>
+        <v>8.65803623199463</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G266" t="n">
-        <v>8.44386577606201</v>
+        <v>8.4438648223877</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>9.5</v>
       </c>
       <c r="G269" t="n">
-        <v>8.65803718566895</v>
+        <v>8.65803623199463</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G272" t="n">
-        <v>8.46664905548096</v>
+        <v>8.46665000915527</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G275" t="n">
-        <v>8.46664905548096</v>
+        <v>8.46665000915527</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G276" t="n">
-        <v>8.45753574371338</v>
+        <v>8.45753479003906</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G277" t="n">
-        <v>8.52133274078369</v>
+        <v>8.52133178710938</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>9.25500011444092</v>
       </c>
       <c r="G279" t="n">
-        <v>8.43475246429443</v>
+        <v>8.43475151062012</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>9.98499965667725</v>
       </c>
       <c r="G283" t="n">
-        <v>9.10005378723145</v>
+        <v>9.10005283355713</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G286" t="n">
-        <v>9.17751884460449</v>
+        <v>9.17752075195312</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G289" t="n">
-        <v>8.84031295776367</v>
+        <v>8.84031200408936</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G290" t="n">
-        <v>8.70360660552979</v>
+        <v>8.70360565185547</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>9.375</v>
       </c>
       <c r="G293" t="n">
-        <v>8.54411697387695</v>
+        <v>8.54411506652832</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>9.5</v>
       </c>
       <c r="G294" t="n">
-        <v>8.65803718566895</v>
+        <v>8.65803623199463</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G295" t="n">
-        <v>8.60335540771484</v>
+        <v>8.60335445404053</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G296" t="n">
-        <v>8.63069725036621</v>
+        <v>8.63069629669189</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G298" t="n">
-        <v>9.04992771148682</v>
+        <v>9.04992866516113</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>9.875</v>
       </c>
       <c r="G299" t="n">
-        <v>8.9998025894165</v>
+        <v>8.99980163574219</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>9.51500034332275</v>
       </c>
       <c r="G305" t="n">
-        <v>8.67170810699463</v>
+        <v>8.67170715332031</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>9.84500026702881</v>
       </c>
       <c r="G312" t="n">
-        <v>8.97246170043945</v>
+        <v>8.97246074676514</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>9.5649995803833</v>
       </c>
       <c r="G315" t="n">
-        <v>8.71727657318115</v>
+        <v>8.71727561950684</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G317" t="n">
-        <v>8.44386577606201</v>
+        <v>8.4438648223877</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G318" t="n">
-        <v>8.32994365692139</v>
+        <v>8.32994270324707</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G319" t="n">
-        <v>8.10210132598877</v>
+        <v>8.10210037231445</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>9.01500034332275</v>
       </c>
       <c r="G320" t="n">
-        <v>8.21602249145508</v>
+        <v>8.21602153778076</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G321" t="n">
-        <v>8.2615909576416</v>
+        <v>8.26159000396729</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>9.125</v>
       </c>
       <c r="G323" t="n">
-        <v>8.3162727355957</v>
+        <v>8.31627178192139</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G324" t="n">
-        <v>8.23880577087402</v>
+        <v>8.23880672454834</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>9.6850004196167</v>
       </c>
       <c r="G325" t="n">
-        <v>8.82664203643799</v>
+        <v>8.82664108276367</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>9.64500045776367</v>
       </c>
       <c r="G327" t="n">
-        <v>8.79018783569336</v>
+        <v>8.79018688201904</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>9.71500015258789</v>
       </c>
       <c r="G328" t="n">
-        <v>8.85398387908936</v>
+        <v>8.85398292541504</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G329" t="n">
-        <v>8.94056415557861</v>
+        <v>8.9405632019043</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>9.84500026702881</v>
       </c>
       <c r="G330" t="n">
-        <v>8.97246170043945</v>
+        <v>8.97246074676514</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G332" t="n">
-        <v>8.49399089813232</v>
+        <v>8.49398994445801</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G333" t="n">
-        <v>8.60335540771484</v>
+        <v>8.60335445404053</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G334" t="n">
-        <v>8.37551212310791</v>
+        <v>8.37551116943359</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G335" t="n">
-        <v>8.48487758636475</v>
+        <v>8.48487663269043</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G336" t="n">
-        <v>8.60335540771484</v>
+        <v>8.60335445404053</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G337" t="n">
-        <v>8.70360660552979</v>
+        <v>8.70360565185547</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G346" t="n">
-        <v>9.25042819976807</v>
+        <v>9.25042915344238</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G352" t="n">
-        <v>8.86765289306641</v>
+        <v>8.86765384674072</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G357" t="n">
-        <v>9.16840648651123</v>
+        <v>9.16840553283691</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G359" t="n">
-        <v>9.66965961456299</v>
+        <v>9.6696605682373</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G360" t="n">
-        <v>9.50561428070068</v>
+        <v>9.505615234375</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G363" t="n">
-        <v>9.70611476898193</v>
+        <v>9.70611572265625</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>9.83500003814697</v>
       </c>
       <c r="G366" t="n">
-        <v>8.96334838867188</v>
+        <v>8.96334743499756</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G369" t="n">
-        <v>8.66715240478516</v>
+        <v>8.66715145111084</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>9.5</v>
       </c>
       <c r="G372" t="n">
-        <v>8.65803718566895</v>
+        <v>8.65803623199463</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>10.0299997329712</v>
       </c>
       <c r="G377" t="n">
-        <v>9.14106464385986</v>
+        <v>9.14106369018555</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G379" t="n">
-        <v>9.30787754058838</v>
+        <v>9.3078784942627</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G383" t="n">
-        <v>9.61260032653809</v>
+        <v>9.6126012802124</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>10.25</v>
       </c>
       <c r="G385" t="n">
-        <v>9.46485614776611</v>
+        <v>9.46485710144043</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G386" t="n">
-        <v>9.43715572357178</v>
+        <v>9.43715476989746</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G387" t="n">
-        <v>9.5479621887207</v>
+        <v>9.54796314239502</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G388" t="n">
-        <v>9.63106918334961</v>
+        <v>9.63106822967529</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G389" t="n">
-        <v>9.64030170440674</v>
+        <v>9.64030265808105</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G390" t="n">
-        <v>9.78804779052734</v>
+        <v>9.78804683685303</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G392" t="n">
-        <v>9.64030170440674</v>
+        <v>9.64030265808105</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>10.5</v>
       </c>
       <c r="G393" t="n">
-        <v>9.69570636749268</v>
+        <v>9.69570732116699</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G394" t="n">
-        <v>9.84345149993896</v>
+        <v>9.84345054626465</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G397" t="n">
-        <v>9.56643104553223</v>
+        <v>9.56642913818359</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G398" t="n">
-        <v>9.4279203414917</v>
+        <v>9.42792129516602</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G400" t="n">
-        <v>9.18783664703369</v>
+        <v>9.18783569335938</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G401" t="n">
-        <v>9.04932689666748</v>
+        <v>9.04932594299316</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G403" t="n">
-        <v>8.79539012908936</v>
+        <v>8.79539108276367</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G405" t="n">
-        <v>8.58762645721436</v>
+        <v>8.58762550354004</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>9.55500030517578</v>
       </c>
       <c r="G407" t="n">
-        <v>8.82309246063232</v>
+        <v>8.82309341430664</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G410" t="n">
-        <v>8.64303016662598</v>
+        <v>8.64302921295166</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G411" t="n">
-        <v>8.82771110534668</v>
+        <v>8.82771015167236</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G413" t="n">
-        <v>8.42141437530518</v>
+        <v>8.42141342163086</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G414" t="n">
-        <v>8.50451946258545</v>
+        <v>8.50452041625977</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>9.21500015258789</v>
       </c>
       <c r="G415" t="n">
-        <v>8.50913715362549</v>
+        <v>8.5091381072998</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>9.57499980926514</v>
       </c>
       <c r="G418" t="n">
-        <v>8.84156131744385</v>
+        <v>8.84156036376953</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G419" t="n">
-        <v>8.57839298248291</v>
+        <v>8.57839202880859</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G423" t="n">
-        <v>8.03820323944092</v>
+        <v>8.0382022857666</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G426" t="n">
-        <v>7.92277669906616</v>
+        <v>7.92277717590332</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G427" t="n">
-        <v>7.82120370864868</v>
+        <v>7.82120275497437</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G428" t="n">
-        <v>7.82120370864868</v>
+        <v>7.82120275497437</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>8.46500015258789</v>
       </c>
       <c r="G429" t="n">
-        <v>7.8165864944458</v>
+        <v>7.81658744812012</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G431" t="n">
-        <v>7.81196928024292</v>
+        <v>7.81196975708008</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>8.42500019073486</v>
       </c>
       <c r="G432" t="n">
-        <v>7.77965021133423</v>
+        <v>7.77965116500854</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G434" t="n">
-        <v>7.25792932510376</v>
+        <v>7.2579288482666</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G435" t="n">
-        <v>7.06401491165161</v>
+        <v>7.06401538848877</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G436" t="n">
-        <v>7.10095071792603</v>
+        <v>7.10095119476318</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G437" t="n">
-        <v>7.16558933258057</v>
+        <v>7.16558885574341</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7.72499990463257</v>
       </c>
       <c r="G438" t="n">
-        <v>7.13327026367188</v>
+        <v>7.13326930999756</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G441" t="n">
-        <v>6.90242004394531</v>
+        <v>6.90241956710815</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G443" t="n">
-        <v>6.61616563796997</v>
+        <v>6.61616516113281</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G444" t="n">
-        <v>6.61154890060425</v>
+        <v>6.61154842376709</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>7.02500009536743</v>
       </c>
       <c r="G445" t="n">
-        <v>6.48688936233521</v>
+        <v>6.48688983917236</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G447" t="n">
-        <v>6.33452892303467</v>
+        <v>6.33452844619751</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>7.13500022888184</v>
       </c>
       <c r="G448" t="n">
-        <v>6.58846378326416</v>
+        <v>6.588463306427</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G449" t="n">
-        <v>6.90242004394531</v>
+        <v>6.90241956710815</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>7.40500020980835</v>
       </c>
       <c r="G454" t="n">
-        <v>6.83778142929077</v>
+        <v>6.83778190612793</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G455" t="n">
-        <v>6.76390981674194</v>
+        <v>6.76390933990479</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G456" t="n">
-        <v>6.76390981674194</v>
+        <v>6.76390933990479</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>7.09499979019165</v>
       </c>
       <c r="G458" t="n">
-        <v>6.55152702331543</v>
+        <v>6.55152750015259</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G461" t="n">
-        <v>6.37146425247192</v>
+        <v>6.37146472930908</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G462" t="n">
-        <v>6.37146425247192</v>
+        <v>6.37146472930908</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>6.69500017166138</v>
       </c>
       <c r="G464" t="n">
-        <v>6.18216753005981</v>
+        <v>6.18216800689697</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G465" t="n">
-        <v>6.18678426742554</v>
+        <v>6.18678379058838</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G466" t="n">
-        <v>5.808189868927</v>
+        <v>5.80819034576416</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>5.82499980926514</v>
       </c>
       <c r="G475" t="n">
-        <v>5.37880897521973</v>
+        <v>5.37880849838257</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G479" t="n">
-        <v>5.70661592483521</v>
+        <v>5.70661544799805</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>5.9850001335144</v>
       </c>
       <c r="G480" t="n">
-        <v>5.5265531539917</v>
+        <v>5.52655267715454</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G485" t="n">
-        <v>5.17566013336182</v>
+        <v>5.17566108703613</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>5.75</v>
       </c>
       <c r="G486" t="n">
-        <v>5.30955362319946</v>
+        <v>5.30955410003662</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G487" t="n">
-        <v>5.06023550033569</v>
+        <v>5.06023597717285</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G490" t="n">
-        <v>4.80168294906616</v>
+        <v>4.80168342590332</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G494" t="n">
-        <v>4.88478899002075</v>
+        <v>4.88478946685791</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G495" t="n">
-        <v>4.88940620422363</v>
+        <v>4.88940668106079</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>5.69500017166138</v>
       </c>
       <c r="G500" t="n">
-        <v>5.25876665115356</v>
+        <v>5.25876712799072</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G508" t="n">
-        <v>5.41112804412842</v>
+        <v>5.41112756729126</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G509" t="n">
-        <v>5.24491548538208</v>
+        <v>5.24491500854492</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G510" t="n">
-        <v>5.21259689331055</v>
+        <v>5.21259641647339</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G513" t="n">
-        <v>5.21259689331055</v>
+        <v>5.21259641647339</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G515" t="n">
-        <v>5.11563920974731</v>
+        <v>5.11563968658447</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G518" t="n">
-        <v>5.24491548538208</v>
+        <v>5.24491500854492</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>5.5</v>
       </c>
       <c r="G524" t="n">
-        <v>5.0787034034729</v>
+        <v>5.07870388031006</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>6.03499984741211</v>
       </c>
       <c r="G527" t="n">
-        <v>5.57272243499756</v>
+        <v>5.57272291183472</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>6.40500020980835</v>
       </c>
       <c r="G533" t="n">
-        <v>5.91438102722168</v>
+        <v>5.91438150405884</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>6.2649998664856</v>
       </c>
       <c r="G535" t="n">
-        <v>5.78510522842407</v>
+        <v>5.78510475158691</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>6.38500022888184</v>
       </c>
       <c r="G539" t="n">
-        <v>5.89591360092163</v>
+        <v>5.89591312408447</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G540" t="n">
-        <v>6.03904008865356</v>
+        <v>6.03904056549072</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G541" t="n">
-        <v>6.05750799179077</v>
+        <v>6.05750846862793</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>6.57499980926514</v>
       </c>
       <c r="G542" t="n">
-        <v>6.07135915756226</v>
+        <v>6.0713586807251</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G544" t="n">
-        <v>5.86359357833862</v>
+        <v>5.86359405517578</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G551" t="n">
-        <v>5.70661592483521</v>
+        <v>5.70661544799805</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G552" t="n">
-        <v>5.70661592483521</v>
+        <v>5.70661544799805</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>6.29500007629395</v>
       </c>
       <c r="G554" t="n">
-        <v>5.81280755996704</v>
+        <v>5.81280660629272</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>6.0149998664856</v>
       </c>
       <c r="G558" t="n">
-        <v>5.55425500869751</v>
+        <v>5.55425453186035</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G564" t="n">
-        <v>5.41112804412842</v>
+        <v>5.41112756729126</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G571" t="n">
-        <v>5.17566013336182</v>
+        <v>5.17566108703613</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G577" t="n">
-        <v>5.06023550033569</v>
+        <v>5.06023597717285</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G579" t="n">
-        <v>5.07408666610718</v>
+        <v>5.07408618927002</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G582" t="n">
-        <v>5.3003191947937</v>
+        <v>5.30031967163086</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G584" t="n">
-        <v>5.37419176101685</v>
+        <v>5.374192237854</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G585" t="n">
-        <v>5.47576570510864</v>
+        <v>5.47576522827148</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G587" t="n">
-        <v>5.57733917236328</v>
+        <v>5.5773401260376</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>5.53499984741211</v>
       </c>
       <c r="G591" t="n">
-        <v>5.11102199554443</v>
+        <v>5.11102247238159</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G594" t="n">
-        <v>5.05100107192993</v>
+        <v>5.05100154876709</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>4.92172574996948</v>
+        <v>4.92172527313232</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G598" t="n">
-        <v>4.80630016326904</v>
+        <v>4.8063006401062</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G599" t="n">
-        <v>4.70010948181152</v>
+        <v>4.70010900497437</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G600" t="n">
-        <v>4.81091785430908</v>
+        <v>4.81091737747192</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G601" t="n">
-        <v>4.77398109436035</v>
+        <v>4.77398157119751</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>5.22499990463257</v>
       </c>
       <c r="G602" t="n">
-        <v>4.82476854324341</v>
+        <v>4.82476806640625</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G603" t="n">
-        <v>4.89864015579224</v>
+        <v>4.89863967895508</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>4.80630016326904</v>
+        <v>4.8063006401062</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G605" t="n">
-        <v>4.66317367553711</v>
+        <v>4.66317319869995</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>4.52466344833374</v>
+        <v>4.52466297149658</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G607" t="n">
-        <v>4.52466344833374</v>
+        <v>4.52466297149658</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>4.82200002670288</v>
       </c>
       <c r="G608" t="n">
-        <v>4.45263767242432</v>
+        <v>4.45263814926147</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>4.70800018310547</v>
       </c>
       <c r="G609" t="n">
-        <v>4.34737062454224</v>
+        <v>4.34737014770508</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>4.66400003433228</v>
       </c>
       <c r="G610" t="n">
-        <v>4.30674028396606</v>
+        <v>4.30674076080322</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>4.74399995803833</v>
       </c>
       <c r="G614" t="n">
-        <v>4.38061285018921</v>
+        <v>4.38061237335205</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>4.96600008010864</v>
       </c>
       <c r="G617" t="n">
-        <v>4.58560800552368</v>
+        <v>4.58560752868652</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>5</v>
       </c>
       <c r="G618" t="n">
-        <v>4.61700296401978</v>
+        <v>4.61700344085693</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G619" t="n">
-        <v>4.46741247177124</v>
+        <v>4.46741199493408</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G621" t="n">
-        <v>4.56898593902588</v>
+        <v>4.56898641586304</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>5.06500005722046</v>
       </c>
       <c r="G625" t="n">
-        <v>4.67702436447144</v>
+        <v>4.67702388763428</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>4.97800016403198</v>
       </c>
       <c r="G627" t="n">
-        <v>4.59668827056885</v>
+        <v>4.59668874740601</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G628" t="n">
-        <v>4.70010948181152</v>
+        <v>4.70010900497437</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>5.0149998664856</v>
       </c>
       <c r="G630" t="n">
-        <v>4.6308536529541</v>
+        <v>4.63085412979126</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G633" t="n">
-        <v>4.63421249389648</v>
+        <v>4.63421201705933</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G639" t="n">
-        <v>4.47546625137329</v>
+        <v>4.47546672821045</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>4.81199979782104</v>
       </c>
       <c r="G640" t="n">
-        <v>4.60169744491577</v>
+        <v>4.60169792175293</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G645" t="n">
-        <v>4.45634078979492</v>
+        <v>4.45634031295776</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>4.62400007247925</v>
       </c>
       <c r="G647" t="n">
-        <v>4.42191410064697</v>
+        <v>4.42191457748413</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G650" t="n">
-        <v>4.17136478424072</v>
+        <v>4.17136430740356</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G653" t="n">
-        <v>4.20770406723022</v>
+        <v>4.20770359039307</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G659" t="n">
-        <v>3.93037796020508</v>
+        <v>3.9303777217865</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G669" t="n">
-        <v>3.65496468544006</v>
+        <v>3.65496444702148</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G672" t="n">
-        <v>3.81370949745178</v>
+        <v>3.81370973587036</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G673" t="n">
-        <v>3.81370949745178</v>
+        <v>3.81370973587036</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>4.17600011825562</v>
       </c>
       <c r="G674" t="n">
-        <v>3.99349355697632</v>
+        <v>3.99349331855774</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G690" t="n">
-        <v>3.45605492591858</v>
+        <v>3.4560546875</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G703" t="n">
-        <v>3.96862959861755</v>
+        <v>3.96862983703613</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>4.1560001373291</v>
       </c>
       <c r="G704" t="n">
-        <v>3.97436785697937</v>
+        <v>3.97436738014221</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>4.27600002288818</v>
       </c>
       <c r="G706" t="n">
-        <v>4.0891227722168</v>
+        <v>4.08912324905396</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>4.13600015640259</v>
       </c>
       <c r="G707" t="n">
-        <v>3.95524168014526</v>
+        <v>3.95524144172668</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G709" t="n">
-        <v>3.98966813087463</v>
+        <v>3.98966789245605</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G712" t="n">
-        <v>3.67026519775391</v>
+        <v>3.67026543617249</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G717" t="n">
-        <v>3.81370949745178</v>
+        <v>3.81370973587036</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G718" t="n">
-        <v>3.82327270507812</v>
+        <v>3.82327246665955</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G719" t="n">
-        <v>3.91507697105408</v>
+        <v>3.91507720947266</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G722" t="n">
-        <v>3.98584294319153</v>
+        <v>3.98584318161011</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>4.42600011825562</v>
       </c>
       <c r="G724" t="n">
-        <v>4.23256778717041</v>
+        <v>4.23256731033325</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>4.51200008392334</v>
       </c>
       <c r="G725" t="n">
-        <v>4.31480884552002</v>
+        <v>4.31480932235718</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G727" t="n">
-        <v>4.15032625198364</v>
+        <v>4.15032577514648</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>4.25</v>
       </c>
       <c r="G729" t="n">
-        <v>4.06425905227661</v>
+        <v>4.06425952911377</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>4.2039999961853</v>
       </c>
       <c r="G732" t="n">
-        <v>4.0202693939209</v>
+        <v>4.02026987075806</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>4.11399984359741</v>
       </c>
       <c r="G737" t="n">
-        <v>3.93420267105103</v>
+        <v>3.9342029094696</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G740" t="n">
-        <v>3.96862959861755</v>
+        <v>3.96862983703613</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G741" t="n">
-        <v>3.91507697105408</v>
+        <v>3.91507720947266</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>3.90799999237061</v>
       </c>
       <c r="G748" t="n">
-        <v>3.73720574378967</v>
+        <v>3.73720598220825</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G750" t="n">
-        <v>3.70086669921875</v>
+        <v>3.70086646080017</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>3.93799996376038</v>
       </c>
       <c r="G751" t="n">
-        <v>3.76589488983154</v>
+        <v>3.76589465141296</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G755" t="n">
-        <v>3.73911881446838</v>
+        <v>3.7391185760498</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G759" t="n">
-        <v>3.57846093177795</v>
+        <v>3.57846069335938</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G760" t="n">
-        <v>3.62245059013367</v>
+        <v>3.62245035171509</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G762" t="n">
-        <v>3.56315994262695</v>
+        <v>3.56316018104553</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G763" t="n">
-        <v>3.54785919189453</v>
+        <v>3.54785943031311</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>3.64800000190735</v>
       </c>
       <c r="G766" t="n">
-        <v>3.48856902122498</v>
+        <v>3.4885687828064</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>3.64400005340576</v>
       </c>
       <c r="G771" t="n">
-        <v>3.48474359512329</v>
+        <v>3.48474383354187</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>3.63199996948242</v>
       </c>
       <c r="G772" t="n">
-        <v>3.47326827049255</v>
+        <v>3.47326803207397</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>3.95799994468689</v>
       </c>
       <c r="G776" t="n">
-        <v>3.78502082824707</v>
+        <v>3.78502058982849</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G777" t="n">
-        <v>3.76971983909607</v>
+        <v>3.76972007751465</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G779" t="n">
-        <v>3.70086669921875</v>
+        <v>3.70086646080017</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G780" t="n">
-        <v>3.59758687019348</v>
+        <v>3.5975866317749</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G783" t="n">
-        <v>3.44075393676758</v>
+        <v>3.44075417518616</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>3.41599988937378</v>
       </c>
       <c r="G784" t="n">
-        <v>3.26670813560486</v>
+        <v>3.26670789718628</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>3.41599988937378</v>
       </c>
       <c r="G785" t="n">
-        <v>3.26670813560486</v>
+        <v>3.26670789718628</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>3.46799993515015</v>
       </c>
       <c r="G786" t="n">
-        <v>3.31643533706665</v>
+        <v>3.31643557548523</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G787" t="n">
-        <v>3.29157161712646</v>
+        <v>3.29157185554504</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G795" t="n">
-        <v>3.20741772651672</v>
+        <v>3.2074179649353</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>3.47399997711182</v>
       </c>
       <c r="G808" t="n">
-        <v>3.32217335700989</v>
+        <v>3.32217311859131</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G814" t="n">
-        <v>3.22654366493225</v>
+        <v>3.22654390335083</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G820" t="n">
-        <v>3.55168461799622</v>
+        <v>3.55168437957764</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G821" t="n">
-        <v>3.5076949596405</v>
+        <v>3.50769472122192</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G823" t="n">
-        <v>3.53638362884521</v>
+        <v>3.53638386726379</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G826" t="n">
-        <v>3.58228588104248</v>
+        <v>3.58228611946106</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G827" t="n">
-        <v>3.5765483379364</v>
+        <v>3.57654809951782</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>3.84400010108948</v>
       </c>
       <c r="G828" t="n">
-        <v>3.67600321769714</v>
+        <v>3.67600297927856</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>4.22599983215332</v>
       </c>
       <c r="G833" t="n">
-        <v>4.04130792617798</v>
+        <v>4.04130840301514</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>4.68599987030029</v>
       </c>
       <c r="G841" t="n">
-        <v>4.48120450973511</v>
+        <v>4.48120403289795</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G843" t="n">
-        <v>4.54432010650635</v>
+        <v>4.54431962966919</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G846" t="n">
-        <v>4.35688591003418</v>
+        <v>4.35688638687134</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G847" t="n">
-        <v>4.26316928863525</v>
+        <v>4.2631688117981</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G849" t="n">
-        <v>4.17136478424072</v>
+        <v>4.17136430740356</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G851" t="n">
-        <v>3.93037796020508</v>
+        <v>3.9303777217865</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G854" t="n">
-        <v>3.77928280830383</v>
+        <v>3.77928304672241</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>3.51200008392334</v>
       </c>
       <c r="G858" t="n">
-        <v>3.35851263999939</v>
+        <v>3.35851287841797</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>3.56800007820129</v>
       </c>
       <c r="G859" t="n">
-        <v>3.41206526756287</v>
+        <v>3.41206550598145</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G863" t="n">
-        <v>3.47900581359863</v>
+        <v>3.47900605201721</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G868" t="n">
-        <v>3.77928280830383</v>
+        <v>3.77928304672241</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>4.12400007247925</v>
       </c>
       <c r="G872" t="n">
-        <v>3.94376587867737</v>
+        <v>3.94376611709595</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G879" t="n">
-        <v>4.47546625137329</v>
+        <v>4.47546672821045</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>4.38800001144409</v>
       </c>
       <c r="G883" t="n">
-        <v>4.19622850418091</v>
+        <v>4.19622802734375</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G886" t="n">
-        <v>4.20196580886841</v>
+        <v>4.20196628570557</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G892" t="n">
-        <v>4.57109689712524</v>
+        <v>4.57109642028809</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>4.74599981307983</v>
       </c>
       <c r="G894" t="n">
-        <v>4.53858184814453</v>
+        <v>4.53858232498169</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G895" t="n">
-        <v>4.68585205078125</v>
+        <v>4.68585157394409</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -32649,7 +32649,7 @@
         <v>903204</v>
       </c>
       <c r="C1242" t="n">
-        <v>3.34400010108948</v>
+        <v>3.34999990463257</v>
       </c>
       <c r="D1242" t="n">
         <v>3.21199989318848</v>
@@ -32664,6 +32664,32 @@
         <v>3.34999990463257</v>
       </c>
       <c r="H1242" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1243" t="n">
+        <v>763260</v>
+      </c>
+      <c r="C1243" t="n">
+        <v>3.46000003814697</v>
+      </c>
+      <c r="D1243" t="n">
+        <v>3.33599996566772</v>
+      </c>
+      <c r="E1243" t="n">
+        <v>3.35199999809265</v>
+      </c>
+      <c r="F1243" t="n">
+        <v>3.35400009155273</v>
+      </c>
+      <c r="G1243" t="n">
+        <v>3.35400009155273</v>
+      </c>
+      <c r="H1243" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ARIS.MI.xlsx
+++ b/data/ARIS.MI.xlsx
@@ -485,7 +485,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G4" t="n">
-        <v>9.1745138168335</v>
+        <v>9.17451477050781</v>
       </c>
       <c r="H4" t="n">
         <v>732483</v>
@@ -514,7 +514,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G5" t="n">
-        <v>9.25538635253906</v>
+        <v>9.25538730621338</v>
       </c>
       <c r="H5" t="n">
         <v>304924</v>
@@ -543,7 +543,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G6" t="n">
-        <v>9.20147037506104</v>
+        <v>9.20147132873535</v>
       </c>
       <c r="H6" t="n">
         <v>260042</v>
@@ -572,7 +572,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G7" t="n">
-        <v>9.20147037506104</v>
+        <v>9.20147132873535</v>
       </c>
       <c r="H7" t="n">
         <v>279621</v>
@@ -601,7 +601,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G8" t="n">
-        <v>9.20147037506104</v>
+        <v>9.20147132873535</v>
       </c>
       <c r="H8" t="n">
         <v>197900</v>
@@ -659,7 +659,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G10" t="n">
-        <v>9.20147037506104</v>
+        <v>9.20147132873535</v>
       </c>
       <c r="H10" t="n">
         <v>122758</v>
@@ -688,7 +688,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G11" t="n">
-        <v>9.23741436004639</v>
+        <v>9.23741340637207</v>
       </c>
       <c r="H11" t="n">
         <v>199132</v>
@@ -717,7 +717,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G12" t="n">
-        <v>9.20147037506104</v>
+        <v>9.20147132873535</v>
       </c>
       <c r="H12" t="n">
         <v>105196</v>
@@ -746,7 +746,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G13" t="n">
-        <v>9.20147037506104</v>
+        <v>9.20147132873535</v>
       </c>
       <c r="H13" t="n">
         <v>85905</v>
@@ -775,7 +775,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G14" t="n">
-        <v>9.20147037506104</v>
+        <v>9.20147132873535</v>
       </c>
       <c r="H14" t="n">
         <v>198256</v>
@@ -833,7 +833,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G16" t="n">
-        <v>8.92291069030762</v>
+        <v>8.92291164398193</v>
       </c>
       <c r="H16" t="n">
         <v>312158</v>
@@ -862,7 +862,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G17" t="n">
-        <v>8.83305263519287</v>
+        <v>8.83305358886719</v>
       </c>
       <c r="H17" t="n">
         <v>156842</v>
@@ -891,7 +891,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G18" t="n">
-        <v>8.6353645324707</v>
+        <v>8.63536548614502</v>
       </c>
       <c r="H18" t="n">
         <v>319387</v>
@@ -920,7 +920,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G19" t="n">
-        <v>8.71623706817627</v>
+        <v>8.71623802185059</v>
       </c>
       <c r="H19" t="n">
         <v>172790</v>
@@ -949,7 +949,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G20" t="n">
-        <v>9.12958431243896</v>
+        <v>9.12958335876465</v>
       </c>
       <c r="H20" t="n">
         <v>431091</v>
@@ -978,7 +978,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G21" t="n">
-        <v>9.07567119598389</v>
+        <v>9.07567024230957</v>
       </c>
       <c r="H21" t="n">
         <v>404417</v>
@@ -1036,7 +1036,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G23" t="n">
-        <v>9.07567119598389</v>
+        <v>9.07567024230957</v>
       </c>
       <c r="H23" t="n">
         <v>179305</v>
@@ -1065,7 +1065,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G24" t="n">
-        <v>9.12958431243896</v>
+        <v>9.12958335876465</v>
       </c>
       <c r="H24" t="n">
         <v>61464</v>
@@ -1123,7 +1123,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G26" t="n">
-        <v>9.12958431243896</v>
+        <v>9.12958335876465</v>
       </c>
       <c r="H26" t="n">
         <v>53953</v>
@@ -1181,7 +1181,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G28" t="n">
-        <v>9.65076160430908</v>
+        <v>9.65076065063477</v>
       </c>
       <c r="H28" t="n">
         <v>568583</v>
@@ -1210,7 +1210,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G29" t="n">
-        <v>9.74062061309814</v>
+        <v>9.74061965942383</v>
       </c>
       <c r="H29" t="n">
         <v>87322</v>
@@ -1297,7 +1297,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G32" t="n">
-        <v>9.1745138168335</v>
+        <v>9.17451477050781</v>
       </c>
       <c r="H32" t="n">
         <v>405173</v>
@@ -1355,7 +1355,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G34" t="n">
-        <v>10.0191793441772</v>
+        <v>10.0191783905029</v>
       </c>
       <c r="H34" t="n">
         <v>509719</v>
@@ -1384,7 +1384,7 @@
         <v>10.9899997711182</v>
       </c>
       <c r="G35" t="n">
-        <v>9.87540626525879</v>
+        <v>9.87540721893311</v>
       </c>
       <c r="H35" t="n">
         <v>209128</v>
@@ -1413,7 +1413,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G36" t="n">
-        <v>10.1988973617554</v>
+        <v>10.1988954544067</v>
       </c>
       <c r="H36" t="n">
         <v>477707</v>
@@ -1471,7 +1471,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G38" t="n">
-        <v>9.72264671325684</v>
+        <v>9.72264862060547</v>
       </c>
       <c r="H38" t="n">
         <v>233657</v>
@@ -1587,7 +1587,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G42" t="n">
-        <v>9.10262775421143</v>
+        <v>9.10262680053711</v>
       </c>
       <c r="H42" t="n">
         <v>130467</v>
@@ -1616,7 +1616,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G43" t="n">
-        <v>9.1745138168335</v>
+        <v>9.17451477050781</v>
       </c>
       <c r="H43" t="n">
         <v>290667</v>
@@ -1645,7 +1645,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G44" t="n">
-        <v>9.12059783935547</v>
+        <v>9.12059879302979</v>
       </c>
       <c r="H44" t="n">
         <v>167591</v>
@@ -1703,7 +1703,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G46" t="n">
-        <v>9.20147037506104</v>
+        <v>9.20147132873535</v>
       </c>
       <c r="H46" t="n">
         <v>323983</v>
@@ -1761,7 +1761,7 @@
         <v>10.4899997711182</v>
       </c>
       <c r="G48" t="n">
-        <v>9.42611503601074</v>
+        <v>9.42611694335938</v>
       </c>
       <c r="H48" t="n">
         <v>67641</v>
@@ -1877,7 +1877,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G52" t="n">
-        <v>9.12958431243896</v>
+        <v>9.12958335876465</v>
       </c>
       <c r="H52" t="n">
         <v>73644</v>
@@ -1906,7 +1906,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G53" t="n">
-        <v>9.24640083312988</v>
+        <v>9.24639987945557</v>
       </c>
       <c r="H53" t="n">
         <v>328076</v>
@@ -1964,7 +1964,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G55" t="n">
-        <v>8.99479675292969</v>
+        <v>8.994797706604</v>
       </c>
       <c r="H55" t="n">
         <v>276782</v>
@@ -1993,7 +1993,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G56" t="n">
-        <v>8.72522258758545</v>
+        <v>8.72522354125977</v>
       </c>
       <c r="H56" t="n">
         <v>305482</v>
@@ -2022,7 +2022,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G57" t="n">
-        <v>9.10262775421143</v>
+        <v>9.10262680053711</v>
       </c>
       <c r="H57" t="n">
         <v>123193</v>
@@ -2051,7 +2051,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G58" t="n">
-        <v>8.99479675292969</v>
+        <v>8.994797706604</v>
       </c>
       <c r="H58" t="n">
         <v>253397</v>
@@ -2080,7 +2080,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G59" t="n">
-        <v>9.19248390197754</v>
+        <v>9.19248485565186</v>
       </c>
       <c r="H59" t="n">
         <v>486352</v>
@@ -2109,7 +2109,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G60" t="n">
-        <v>8.95885562896729</v>
+        <v>8.95885467529297</v>
       </c>
       <c r="H60" t="n">
         <v>207313</v>
@@ -2138,7 +2138,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G61" t="n">
-        <v>8.71623706817627</v>
+        <v>8.71623802185059</v>
       </c>
       <c r="H61" t="n">
         <v>224870</v>
@@ -2167,7 +2167,7 @@
         <v>9.41499996185303</v>
       </c>
       <c r="G62" t="n">
-        <v>8.4601411819458</v>
+        <v>8.46014213562012</v>
       </c>
       <c r="H62" t="n">
         <v>251208</v>
@@ -2196,7 +2196,7 @@
         <v>9.1850004196167</v>
       </c>
       <c r="G63" t="n">
-        <v>8.25346755981445</v>
+        <v>8.25346851348877</v>
       </c>
       <c r="H63" t="n">
         <v>485171</v>
@@ -2225,7 +2225,7 @@
         <v>8.75</v>
       </c>
       <c r="G64" t="n">
-        <v>7.86258554458618</v>
+        <v>7.86258506774902</v>
       </c>
       <c r="H64" t="n">
         <v>215027</v>
@@ -2254,7 +2254,7 @@
         <v>9.1850004196167</v>
       </c>
       <c r="G65" t="n">
-        <v>8.25346755981445</v>
+        <v>8.25346851348877</v>
       </c>
       <c r="H65" t="n">
         <v>239997</v>
@@ -2312,7 +2312,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G67" t="n">
-        <v>7.70982551574707</v>
+        <v>7.70982599258423</v>
       </c>
       <c r="H67" t="n">
         <v>139521</v>
@@ -2341,7 +2341,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G68" t="n">
-        <v>8.03331470489502</v>
+        <v>8.03331565856934</v>
       </c>
       <c r="H68" t="n">
         <v>139296</v>
@@ -2370,7 +2370,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G69" t="n">
-        <v>7.95244359970093</v>
+        <v>7.95244407653809</v>
       </c>
       <c r="H69" t="n">
         <v>230882</v>
@@ -2399,7 +2399,7 @@
         <v>7.875</v>
       </c>
       <c r="G70" t="n">
-        <v>7.07632637023926</v>
+        <v>7.07632684707642</v>
       </c>
       <c r="H70" t="n">
         <v>381529</v>
@@ -2457,7 +2457,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G72" t="n">
-        <v>7.42228078842163</v>
+        <v>7.42228031158447</v>
       </c>
       <c r="H72" t="n">
         <v>235581</v>
@@ -2631,7 +2631,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G78" t="n">
-        <v>9.23741436004639</v>
+        <v>9.23741340637207</v>
       </c>
       <c r="H78" t="n">
         <v>643900</v>
@@ -2660,7 +2660,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G79" t="n">
-        <v>9.08465480804443</v>
+        <v>9.08465576171875</v>
       </c>
       <c r="H79" t="n">
         <v>663957</v>
@@ -2689,7 +2689,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G80" t="n">
-        <v>9.19248390197754</v>
+        <v>9.19248485565186</v>
       </c>
       <c r="H80" t="n">
         <v>1158996</v>
@@ -2747,7 +2747,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G82" t="n">
-        <v>9.07567119598389</v>
+        <v>9.07567024230957</v>
       </c>
       <c r="H82" t="n">
         <v>174088</v>
@@ -2805,7 +2805,7 @@
         <v>9.48499965667725</v>
       </c>
       <c r="G84" t="n">
-        <v>8.52304172515869</v>
+        <v>8.52304267883301</v>
       </c>
       <c r="H84" t="n">
         <v>211192</v>
@@ -3008,7 +3008,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G91" t="n">
-        <v>8.5185489654541</v>
+        <v>8.51854801177979</v>
       </c>
       <c r="H91" t="n">
         <v>163375</v>
@@ -3037,7 +3037,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G92" t="n">
-        <v>8.71623706817627</v>
+        <v>8.71623802185059</v>
       </c>
       <c r="H92" t="n">
         <v>223170</v>
@@ -3095,7 +3095,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G94" t="n">
-        <v>8.18607330322266</v>
+        <v>8.18607425689697</v>
       </c>
       <c r="H94" t="n">
         <v>173589</v>
@@ -3153,7 +3153,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G96" t="n">
-        <v>8.2489767074585</v>
+        <v>8.24897480010986</v>
       </c>
       <c r="H96" t="n">
         <v>89220</v>
@@ -3240,7 +3240,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G99" t="n">
-        <v>8.45564937591553</v>
+        <v>8.45564842224121</v>
       </c>
       <c r="H99" t="n">
         <v>126252</v>
@@ -3356,7 +3356,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G103" t="n">
-        <v>8.71623706817627</v>
+        <v>8.71623802185059</v>
       </c>
       <c r="H103" t="n">
         <v>216807</v>
@@ -3385,7 +3385,7 @@
         <v>9.625</v>
       </c>
       <c r="G104" t="n">
-        <v>8.64884376525879</v>
+        <v>8.64884281158447</v>
       </c>
       <c r="H104" t="n">
         <v>109168</v>
@@ -3501,7 +3501,7 @@
         <v>9.53499984741211</v>
       </c>
       <c r="G108" t="n">
-        <v>8.56797122955322</v>
+        <v>8.56797027587891</v>
       </c>
       <c r="H108" t="n">
         <v>345401</v>
@@ -3559,7 +3559,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G110" t="n">
-        <v>7.8985276222229</v>
+        <v>7.89852857589722</v>
       </c>
       <c r="H110" t="n">
         <v>136469</v>
@@ -3617,7 +3617,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G112" t="n">
-        <v>8.10520172119141</v>
+        <v>8.10520362854004</v>
       </c>
       <c r="H112" t="n">
         <v>245680</v>
@@ -3646,7 +3646,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G113" t="n">
-        <v>7.99737119674683</v>
+        <v>7.99737215042114</v>
       </c>
       <c r="H113" t="n">
         <v>164165</v>
@@ -3675,7 +3675,7 @@
         <v>8.6850004196167</v>
       </c>
       <c r="G114" t="n">
-        <v>7.8041787147522</v>
+        <v>7.80417728424072</v>
       </c>
       <c r="H114" t="n">
         <v>103341</v>
@@ -3762,7 +3762,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G117" t="n">
-        <v>8.32086277008057</v>
+        <v>8.32086181640625</v>
       </c>
       <c r="H117" t="n">
         <v>146034</v>
@@ -3791,7 +3791,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G118" t="n">
-        <v>8.54550743103027</v>
+        <v>8.54550838470459</v>
       </c>
       <c r="H118" t="n">
         <v>395701</v>
@@ -3936,7 +3936,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G123" t="n">
-        <v>8.96334838867188</v>
+        <v>8.96334648132324</v>
       </c>
       <c r="H123" t="n">
         <v>150460</v>
@@ -3994,7 +3994,7 @@
         <v>9.82499980926514</v>
       </c>
       <c r="G125" t="n">
-        <v>8.95423412322998</v>
+        <v>8.95423221588135</v>
       </c>
       <c r="H125" t="n">
         <v>143405</v>
@@ -4052,7 +4052,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G127" t="n">
-        <v>9.2504301071167</v>
+        <v>9.25042915344238</v>
       </c>
       <c r="H127" t="n">
         <v>154830</v>
@@ -4081,7 +4081,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>9.47827243804932</v>
+        <v>9.478271484375</v>
       </c>
       <c r="H128" t="n">
         <v>307614</v>
@@ -4110,7 +4110,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G129" t="n">
-        <v>9.51472663879395</v>
+        <v>9.51472759246826</v>
       </c>
       <c r="H129" t="n">
         <v>242971</v>
@@ -4139,7 +4139,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G130" t="n">
-        <v>9.35068035125732</v>
+        <v>9.35068225860596</v>
       </c>
       <c r="H130" t="n">
         <v>2902048</v>
@@ -4226,7 +4226,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G133" t="n">
-        <v>9.30511283874512</v>
+        <v>9.3051118850708</v>
       </c>
       <c r="H133" t="n">
         <v>80187</v>
@@ -4284,7 +4284,7 @@
         <v>10.25</v>
       </c>
       <c r="G135" t="n">
-        <v>9.34156608581543</v>
+        <v>9.34156703948975</v>
       </c>
       <c r="H135" t="n">
         <v>52292</v>
@@ -4400,7 +4400,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G139" t="n">
-        <v>8.52133274078369</v>
+        <v>8.52133178710938</v>
       </c>
       <c r="H139" t="n">
         <v>53406</v>
@@ -4429,7 +4429,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G140" t="n">
-        <v>7.95628023147583</v>
+        <v>7.95628118515015</v>
       </c>
       <c r="H140" t="n">
         <v>163728</v>
@@ -4458,7 +4458,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G141" t="n">
-        <v>7.83780241012573</v>
+        <v>7.83780288696289</v>
       </c>
       <c r="H141" t="n">
         <v>132472</v>
@@ -4487,7 +4487,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G142" t="n">
-        <v>7.61907243728638</v>
+        <v>7.61907196044922</v>
       </c>
       <c r="H142" t="n">
         <v>67512</v>
@@ -4545,7 +4545,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G144" t="n">
-        <v>7.64641427993774</v>
+        <v>7.6464147567749</v>
       </c>
       <c r="H144" t="n">
         <v>79110</v>
@@ -4574,7 +4574,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G145" t="n">
-        <v>7.47325325012207</v>
+        <v>7.47325372695923</v>
       </c>
       <c r="H145" t="n">
         <v>33799</v>
@@ -4632,7 +4632,7 @@
         <v>7.50500011444092</v>
       </c>
       <c r="G147" t="n">
-        <v>6.83984994888306</v>
+        <v>6.8398494720459</v>
       </c>
       <c r="H147" t="n">
         <v>173369</v>
@@ -4777,7 +4777,7 @@
         <v>7.81500005722046</v>
       </c>
       <c r="G152" t="n">
-        <v>7.12237501144409</v>
+        <v>7.12237548828125</v>
       </c>
       <c r="H152" t="n">
         <v>173417</v>
@@ -4893,7 +4893,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G156" t="n">
-        <v>6.68035888671875</v>
+        <v>6.68035936355591</v>
       </c>
       <c r="H156" t="n">
         <v>131028</v>
@@ -4922,7 +4922,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G157" t="n">
-        <v>6.78061056137085</v>
+        <v>6.78061008453369</v>
       </c>
       <c r="H157" t="n">
         <v>109900</v>
@@ -4951,7 +4951,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G158" t="n">
-        <v>6.926429271698</v>
+        <v>6.92642974853516</v>
       </c>
       <c r="H158" t="n">
         <v>58691</v>
@@ -5009,7 +5009,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G160" t="n">
-        <v>6.68035888671875</v>
+        <v>6.68035936355591</v>
       </c>
       <c r="H160" t="n">
         <v>64175</v>
@@ -5096,7 +5096,7 @@
         <v>7.31500005722046</v>
       </c>
       <c r="G163" t="n">
-        <v>6.66668844223022</v>
+        <v>6.66668891906738</v>
       </c>
       <c r="H163" t="n">
         <v>63073</v>
@@ -5125,7 +5125,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G164" t="n">
-        <v>6.88086128234863</v>
+        <v>6.88086175918579</v>
       </c>
       <c r="H164" t="n">
         <v>59880</v>
@@ -5270,7 +5270,7 @@
         <v>7.72499990463257</v>
       </c>
       <c r="G169" t="n">
-        <v>7.04035186767578</v>
+        <v>7.04035139083862</v>
       </c>
       <c r="H169" t="n">
         <v>97576</v>
@@ -5415,7 +5415,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G174" t="n">
-        <v>7.47325325012207</v>
+        <v>7.47325372695923</v>
       </c>
       <c r="H174" t="n">
         <v>32018</v>
@@ -5444,7 +5444,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G175" t="n">
-        <v>7.61907243728638</v>
+        <v>7.61907196044922</v>
       </c>
       <c r="H175" t="n">
         <v>67391</v>
@@ -5473,7 +5473,7 @@
         <v>8.20499992370605</v>
       </c>
       <c r="G176" t="n">
-        <v>7.47780990600586</v>
+        <v>7.4778094291687</v>
       </c>
       <c r="H176" t="n">
         <v>152702</v>
@@ -5589,7 +5589,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G180" t="n">
-        <v>7.24996709823608</v>
+        <v>7.24996662139893</v>
       </c>
       <c r="H180" t="n">
         <v>63885</v>
@@ -5821,7 +5821,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G188" t="n">
-        <v>7.10870456695557</v>
+        <v>7.10870504379272</v>
       </c>
       <c r="H188" t="n">
         <v>92732</v>
@@ -5937,7 +5937,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G192" t="n">
-        <v>6.81250810623169</v>
+        <v>6.81250858306885</v>
       </c>
       <c r="H192" t="n">
         <v>43263</v>
@@ -5966,7 +5966,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G193" t="n">
-        <v>6.81250810623169</v>
+        <v>6.81250858306885</v>
       </c>
       <c r="H193" t="n">
         <v>46346</v>
@@ -6082,7 +6082,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G197" t="n">
-        <v>6.926429271698</v>
+        <v>6.92642974853516</v>
       </c>
       <c r="H197" t="n">
         <v>94339</v>
@@ -6111,7 +6111,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G198" t="n">
-        <v>6.56188058853149</v>
+        <v>6.56188106536865</v>
       </c>
       <c r="H198" t="n">
         <v>52394</v>
@@ -6140,7 +6140,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G199" t="n">
-        <v>6.42517518997192</v>
+        <v>6.42517566680908</v>
       </c>
       <c r="H199" t="n">
         <v>115768</v>
@@ -6169,7 +6169,7 @@
         <v>7.0149998664856</v>
       </c>
       <c r="G200" t="n">
-        <v>6.39327716827393</v>
+        <v>6.39327764511108</v>
       </c>
       <c r="H200" t="n">
         <v>115529</v>
@@ -6198,7 +6198,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G201" t="n">
-        <v>6.63023376464844</v>
+        <v>6.6302342414856</v>
       </c>
       <c r="H201" t="n">
         <v>127295</v>
@@ -6343,7 +6343,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G206" t="n">
-        <v>6.69858694076538</v>
+        <v>6.69858646392822</v>
       </c>
       <c r="H206" t="n">
         <v>115365</v>
@@ -6372,7 +6372,7 @@
         <v>8.46500015258789</v>
       </c>
       <c r="G207" t="n">
-        <v>7.71476745605469</v>
+        <v>7.71476697921753</v>
       </c>
       <c r="H207" t="n">
         <v>667919</v>
@@ -6401,7 +6401,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G208" t="n">
-        <v>7.5552773475647</v>
+        <v>7.55527591705322</v>
       </c>
       <c r="H208" t="n">
         <v>323484</v>
@@ -6459,7 +6459,7 @@
         <v>8.40499973297119</v>
       </c>
       <c r="G210" t="n">
-        <v>7.66008424758911</v>
+        <v>7.66008520126343</v>
       </c>
       <c r="H210" t="n">
         <v>162822</v>
@@ -6488,7 +6488,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G211" t="n">
-        <v>7.70565319061279</v>
+        <v>7.70565366744995</v>
       </c>
       <c r="H211" t="n">
         <v>238638</v>
@@ -6517,7 +6517,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G212" t="n">
-        <v>7.75577926635742</v>
+        <v>7.75577974319458</v>
       </c>
       <c r="H212" t="n">
         <v>149734</v>
@@ -6546,7 +6546,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G213" t="n">
-        <v>7.828688621521</v>
+        <v>7.82868909835815</v>
       </c>
       <c r="H213" t="n">
         <v>267292</v>
@@ -6575,7 +6575,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G214" t="n">
-        <v>7.828688621521</v>
+        <v>7.82868909835815</v>
       </c>
       <c r="H214" t="n">
         <v>252704</v>
@@ -6604,7 +6604,7 @@
         <v>8.48499965667725</v>
       </c>
       <c r="G215" t="n">
-        <v>7.73299360275269</v>
+        <v>7.73299407958984</v>
       </c>
       <c r="H215" t="n">
         <v>190999</v>
@@ -6662,7 +6662,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G217" t="n">
-        <v>7.93805265426636</v>
+        <v>7.93805408477783</v>
       </c>
       <c r="H217" t="n">
         <v>247020</v>
@@ -6691,7 +6691,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G218" t="n">
-        <v>8.0200777053833</v>
+        <v>8.02007579803467</v>
       </c>
       <c r="H218" t="n">
         <v>179237</v>
@@ -6720,7 +6720,7 @@
         <v>9.13500022888184</v>
       </c>
       <c r="G219" t="n">
-        <v>8.32538604736328</v>
+        <v>8.3253870010376</v>
       </c>
       <c r="H219" t="n">
         <v>283069</v>
@@ -6749,7 +6749,7 @@
         <v>9.03499984741211</v>
       </c>
       <c r="G220" t="n">
-        <v>8.23425006866455</v>
+        <v>8.23424911499023</v>
       </c>
       <c r="H220" t="n">
         <v>263459</v>
@@ -6778,7 +6778,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G221" t="n">
-        <v>8.1932373046875</v>
+        <v>8.19323635101318</v>
       </c>
       <c r="H221" t="n">
         <v>194602</v>
@@ -6807,7 +6807,7 @@
         <v>8.84500026702881</v>
       </c>
       <c r="G222" t="n">
-        <v>8.06108951568604</v>
+        <v>8.06108856201172</v>
       </c>
       <c r="H222" t="n">
         <v>71498</v>
@@ -6865,7 +6865,7 @@
         <v>8.79500007629395</v>
       </c>
       <c r="G224" t="n">
-        <v>8.01552104949951</v>
+        <v>8.0155200958252</v>
       </c>
       <c r="H224" t="n">
         <v>122024</v>
@@ -6923,7 +6923,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G226" t="n">
-        <v>7.65552759170532</v>
+        <v>7.65552806854248</v>
       </c>
       <c r="H226" t="n">
         <v>242848</v>
@@ -6981,7 +6981,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G228" t="n">
-        <v>7.71932363510132</v>
+        <v>7.71932458877563</v>
       </c>
       <c r="H228" t="n">
         <v>240482</v>
@@ -7010,7 +7010,7 @@
         <v>8.60499954223633</v>
       </c>
       <c r="G229" t="n">
-        <v>7.84235906600952</v>
+        <v>7.84235858917236</v>
       </c>
       <c r="H229" t="n">
         <v>228869</v>
@@ -7068,7 +7068,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>7.48236703872681</v>
+        <v>7.48236656188965</v>
       </c>
       <c r="H231" t="n">
         <v>150112</v>
@@ -7097,7 +7097,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G232" t="n">
-        <v>7.54160642623901</v>
+        <v>7.54160594940186</v>
       </c>
       <c r="H232" t="n">
         <v>183612</v>
@@ -7184,7 +7184,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G235" t="n">
-        <v>7.8195743560791</v>
+        <v>7.81957483291626</v>
       </c>
       <c r="H235" t="n">
         <v>126055</v>
@@ -7213,7 +7213,7 @@
         <v>8.59500026702881</v>
       </c>
       <c r="G236" t="n">
-        <v>7.8332462310791</v>
+        <v>7.83324670791626</v>
       </c>
       <c r="H236" t="n">
         <v>75722</v>
@@ -7271,7 +7271,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G238" t="n">
-        <v>7.86514377593994</v>
+        <v>7.86514282226562</v>
       </c>
       <c r="H238" t="n">
         <v>98511</v>
@@ -7300,7 +7300,7 @@
         <v>8.50500011444092</v>
       </c>
       <c r="G239" t="n">
-        <v>7.75122165679932</v>
+        <v>7.75122213363647</v>
       </c>
       <c r="H239" t="n">
         <v>97800</v>
@@ -7329,7 +7329,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G240" t="n">
-        <v>7.61907243728638</v>
+        <v>7.61907196044922</v>
       </c>
       <c r="H240" t="n">
         <v>242480</v>
@@ -7387,7 +7387,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G242" t="n">
-        <v>7.20895481109619</v>
+        <v>7.20895576477051</v>
       </c>
       <c r="H242" t="n">
         <v>428150</v>
@@ -7416,7 +7416,7 @@
         <v>8.29500007629395</v>
       </c>
       <c r="G243" t="n">
-        <v>7.55983352661133</v>
+        <v>7.55983304977417</v>
       </c>
       <c r="H243" t="n">
         <v>179111</v>
@@ -7445,7 +7445,7 @@
         <v>8.3149995803833</v>
       </c>
       <c r="G244" t="n">
-        <v>7.57806062698364</v>
+        <v>7.5780611038208</v>
       </c>
       <c r="H244" t="n">
         <v>97069</v>
@@ -7503,7 +7503,7 @@
         <v>8.49499988555908</v>
       </c>
       <c r="G246" t="n">
-        <v>7.7421088218689</v>
+        <v>7.74210786819458</v>
       </c>
       <c r="H246" t="n">
         <v>144625</v>
@@ -7532,7 +7532,7 @@
         <v>8.5649995803833</v>
       </c>
       <c r="G247" t="n">
-        <v>7.80590295791626</v>
+        <v>7.80590391159058</v>
       </c>
       <c r="H247" t="n">
         <v>190341</v>
@@ -7590,7 +7590,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G249" t="n">
-        <v>7.828688621521</v>
+        <v>7.82868909835815</v>
       </c>
       <c r="H249" t="n">
         <v>109003</v>
@@ -7619,7 +7619,7 @@
         <v>8.44499969482422</v>
       </c>
       <c r="G250" t="n">
-        <v>7.69653940200806</v>
+        <v>7.6965389251709</v>
       </c>
       <c r="H250" t="n">
         <v>65821</v>
@@ -7677,7 +7677,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G252" t="n">
-        <v>7.87425804138184</v>
+        <v>7.87425756454468</v>
       </c>
       <c r="H252" t="n">
         <v>52613</v>
@@ -7735,7 +7735,7 @@
         <v>8.64500045776367</v>
       </c>
       <c r="G254" t="n">
-        <v>7.87881422042847</v>
+        <v>7.87881469726562</v>
       </c>
       <c r="H254" t="n">
         <v>56212</v>
@@ -7822,7 +7822,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G257" t="n">
-        <v>8.3800687789917</v>
+        <v>8.38006782531738</v>
       </c>
       <c r="H257" t="n">
         <v>166742</v>
@@ -7880,7 +7880,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G259" t="n">
-        <v>8.43930912017822</v>
+        <v>8.43930816650391</v>
       </c>
       <c r="H259" t="n">
         <v>57907</v>
@@ -7938,7 +7938,7 @@
         <v>9.50500011444092</v>
       </c>
       <c r="G261" t="n">
-        <v>8.66259479522705</v>
+        <v>8.66259384155273</v>
       </c>
       <c r="H261" t="n">
         <v>198672</v>
@@ -7996,7 +7996,7 @@
         <v>9.5</v>
       </c>
       <c r="G263" t="n">
-        <v>8.65803813934326</v>
+        <v>8.65803623199463</v>
       </c>
       <c r="H263" t="n">
         <v>120885</v>
@@ -8083,7 +8083,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G266" t="n">
-        <v>8.44386577606201</v>
+        <v>8.4438648223877</v>
       </c>
       <c r="H266" t="n">
         <v>56513</v>
@@ -8141,7 +8141,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G268" t="n">
-        <v>8.42108058929443</v>
+        <v>8.42108154296875</v>
       </c>
       <c r="H268" t="n">
         <v>38362</v>
@@ -8170,7 +8170,7 @@
         <v>9.5</v>
       </c>
       <c r="G269" t="n">
-        <v>8.65803813934326</v>
+        <v>8.65803623199463</v>
       </c>
       <c r="H269" t="n">
         <v>49713</v>
@@ -8286,7 +8286,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G273" t="n">
-        <v>8.40285301208496</v>
+        <v>8.40285396575928</v>
       </c>
       <c r="H273" t="n">
         <v>52732</v>
@@ -8373,7 +8373,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G276" t="n">
-        <v>8.45753383636475</v>
+        <v>8.45753479003906</v>
       </c>
       <c r="H276" t="n">
         <v>55423</v>
@@ -8402,7 +8402,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G277" t="n">
-        <v>8.52133274078369</v>
+        <v>8.52133178710938</v>
       </c>
       <c r="H277" t="n">
         <v>22128</v>
@@ -8431,7 +8431,7 @@
         <v>9.66499996185303</v>
       </c>
       <c r="G278" t="n">
-        <v>8.8084135055542</v>
+        <v>8.80841445922852</v>
       </c>
       <c r="H278" t="n">
         <v>41058</v>
@@ -8489,7 +8489,7 @@
         <v>9.40499973297119</v>
       </c>
       <c r="G280" t="n">
-        <v>8.57145595550537</v>
+        <v>8.57145690917969</v>
       </c>
       <c r="H280" t="n">
         <v>67802</v>
@@ -8750,7 +8750,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G289" t="n">
-        <v>8.84031105041504</v>
+        <v>8.84031200408936</v>
       </c>
       <c r="H289" t="n">
         <v>85842</v>
@@ -8895,7 +8895,7 @@
         <v>9.5</v>
       </c>
       <c r="G294" t="n">
-        <v>8.65803813934326</v>
+        <v>8.65803623199463</v>
       </c>
       <c r="H294" t="n">
         <v>186325</v>
@@ -8982,7 +8982,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G297" t="n">
-        <v>8.82208442687988</v>
+        <v>8.8220853805542</v>
       </c>
       <c r="H297" t="n">
         <v>184820</v>
@@ -9011,7 +9011,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G298" t="n">
-        <v>9.0499267578125</v>
+        <v>9.04992866516113</v>
       </c>
       <c r="H298" t="n">
         <v>175620</v>
@@ -9069,7 +9069,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G300" t="n">
-        <v>8.9952449798584</v>
+        <v>8.99524593353271</v>
       </c>
       <c r="H300" t="n">
         <v>84628</v>
@@ -9185,7 +9185,7 @@
         <v>9.61499977111816</v>
       </c>
       <c r="G304" t="n">
-        <v>8.76284503936768</v>
+        <v>8.76284599304199</v>
       </c>
       <c r="H304" t="n">
         <v>112583</v>
@@ -9214,7 +9214,7 @@
         <v>9.51500034332275</v>
       </c>
       <c r="G305" t="n">
-        <v>8.67170906066895</v>
+        <v>8.67170715332031</v>
       </c>
       <c r="H305" t="n">
         <v>74235</v>
@@ -9272,7 +9272,7 @@
         <v>9.66499996185303</v>
       </c>
       <c r="G307" t="n">
-        <v>8.8084135055542</v>
+        <v>8.80841445922852</v>
       </c>
       <c r="H307" t="n">
         <v>88814</v>
@@ -9301,7 +9301,7 @@
         <v>9.61499977111816</v>
       </c>
       <c r="G308" t="n">
-        <v>8.76284503936768</v>
+        <v>8.76284599304199</v>
       </c>
       <c r="H308" t="n">
         <v>97456</v>
@@ -9388,7 +9388,7 @@
         <v>9.30500030517578</v>
       </c>
       <c r="G311" t="n">
-        <v>8.48031997680664</v>
+        <v>8.48032093048096</v>
       </c>
       <c r="H311" t="n">
         <v>88710</v>
@@ -9504,7 +9504,7 @@
         <v>9.5649995803833</v>
       </c>
       <c r="G315" t="n">
-        <v>8.71727657318115</v>
+        <v>8.71727561950684</v>
       </c>
       <c r="H315" t="n">
         <v>125012</v>
@@ -9562,7 +9562,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G317" t="n">
-        <v>8.44386577606201</v>
+        <v>8.4438648223877</v>
       </c>
       <c r="H317" t="n">
         <v>158286</v>
@@ -9591,7 +9591,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G318" t="n">
-        <v>8.32994365692139</v>
+        <v>8.32994270324707</v>
       </c>
       <c r="H318" t="n">
         <v>82760</v>
@@ -9649,7 +9649,7 @@
         <v>9.01500034332275</v>
       </c>
       <c r="G320" t="n">
-        <v>8.21602249145508</v>
+        <v>8.21602153778076</v>
       </c>
       <c r="H320" t="n">
         <v>69302</v>
@@ -9736,7 +9736,7 @@
         <v>9.125</v>
       </c>
       <c r="G323" t="n">
-        <v>8.3162727355957</v>
+        <v>8.31627178192139</v>
       </c>
       <c r="H323" t="n">
         <v>96023</v>
@@ -9765,7 +9765,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G324" t="n">
-        <v>8.23880577087402</v>
+        <v>8.23880672454834</v>
       </c>
       <c r="H324" t="n">
         <v>125245</v>
@@ -9794,7 +9794,7 @@
         <v>9.6850004196167</v>
       </c>
       <c r="G325" t="n">
-        <v>8.82664203643799</v>
+        <v>8.82664108276367</v>
       </c>
       <c r="H325" t="n">
         <v>499802</v>
@@ -9997,7 +9997,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G332" t="n">
-        <v>8.49399089813232</v>
+        <v>8.49398994445801</v>
       </c>
       <c r="H332" t="n">
         <v>110225</v>
@@ -10055,7 +10055,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G334" t="n">
-        <v>8.37551212310791</v>
+        <v>8.37551116943359</v>
       </c>
       <c r="H334" t="n">
         <v>66953</v>
@@ -10171,7 +10171,7 @@
         <v>9.59500026702881</v>
       </c>
       <c r="G338" t="n">
-        <v>8.74461936950684</v>
+        <v>8.74461841583252</v>
       </c>
       <c r="H338" t="n">
         <v>46333</v>
@@ -10229,7 +10229,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G340" t="n">
-        <v>8.64892292022705</v>
+        <v>8.64892387390137</v>
       </c>
       <c r="H340" t="n">
         <v>60887</v>
@@ -10258,7 +10258,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G341" t="n">
-        <v>8.42108058929443</v>
+        <v>8.42108154296875</v>
       </c>
       <c r="H341" t="n">
         <v>61904</v>
@@ -10287,7 +10287,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G342" t="n">
-        <v>8.43930912017822</v>
+        <v>8.43930816650391</v>
       </c>
       <c r="H342" t="n">
         <v>40942</v>
@@ -10316,7 +10316,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G343" t="n">
-        <v>8.53955841064453</v>
+        <v>8.53955936431885</v>
       </c>
       <c r="H343" t="n">
         <v>356528</v>
@@ -10403,7 +10403,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G346" t="n">
-        <v>9.2504301071167</v>
+        <v>9.25042915344238</v>
       </c>
       <c r="H346" t="n">
         <v>231979</v>
@@ -10432,7 +10432,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G347" t="n">
-        <v>9.47827243804932</v>
+        <v>9.478271484375</v>
       </c>
       <c r="H347" t="n">
         <v>132689</v>
@@ -10519,7 +10519,7 @@
         <v>9.94499969482422</v>
       </c>
       <c r="G350" t="n">
-        <v>9.06359767913818</v>
+        <v>9.0635986328125</v>
       </c>
       <c r="H350" t="n">
         <v>113297</v>
@@ -10577,7 +10577,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G352" t="n">
-        <v>8.86765289306641</v>
+        <v>8.86765384674072</v>
       </c>
       <c r="H352" t="n">
         <v>54316</v>
@@ -10635,7 +10635,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G354" t="n">
-        <v>9.02258586883545</v>
+        <v>9.02258682250977</v>
       </c>
       <c r="H354" t="n">
         <v>58371</v>
@@ -10693,7 +10693,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G356" t="n">
-        <v>9.02258586883545</v>
+        <v>9.02258682250977</v>
       </c>
       <c r="H356" t="n">
         <v>51175</v>
@@ -10722,7 +10722,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G357" t="n">
-        <v>9.16840648651123</v>
+        <v>9.16840553283691</v>
       </c>
       <c r="H357" t="n">
         <v>43978</v>
@@ -10751,7 +10751,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G358" t="n">
-        <v>9.46916007995605</v>
+        <v>9.46915912628174</v>
       </c>
       <c r="H358" t="n">
         <v>119140</v>
@@ -10780,7 +10780,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G359" t="n">
-        <v>9.66966152191162</v>
+        <v>9.6696605682373</v>
       </c>
       <c r="H359" t="n">
         <v>147204</v>
@@ -10809,7 +10809,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G360" t="n">
-        <v>9.50561428070068</v>
+        <v>9.505615234375</v>
       </c>
       <c r="H360" t="n">
         <v>54614</v>
@@ -10838,7 +10838,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G361" t="n">
-        <v>9.47827243804932</v>
+        <v>9.478271484375</v>
       </c>
       <c r="H361" t="n">
         <v>59625</v>
@@ -10896,7 +10896,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G363" t="n">
-        <v>9.70611476898193</v>
+        <v>9.70611572265625</v>
       </c>
       <c r="H363" t="n">
         <v>79881</v>
@@ -10925,7 +10925,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G364" t="n">
-        <v>9.42359066009521</v>
+        <v>9.4235897064209</v>
       </c>
       <c r="H364" t="n">
         <v>225133</v>
@@ -11012,7 +11012,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G367" t="n">
-        <v>9.15017795562744</v>
+        <v>9.15017890930176</v>
       </c>
       <c r="H367" t="n">
         <v>95441</v>
@@ -11041,7 +11041,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G368" t="n">
-        <v>8.97701740264893</v>
+        <v>8.97701835632324</v>
       </c>
       <c r="H368" t="n">
         <v>58875</v>
@@ -11070,7 +11070,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G369" t="n">
-        <v>8.66715240478516</v>
+        <v>8.66715145111084</v>
       </c>
       <c r="H369" t="n">
         <v>180228</v>
@@ -11099,7 +11099,7 @@
         <v>9.40499973297119</v>
       </c>
       <c r="G370" t="n">
-        <v>8.57145595550537</v>
+        <v>8.57145690917969</v>
       </c>
       <c r="H370" t="n">
         <v>122944</v>
@@ -11157,7 +11157,7 @@
         <v>9.5</v>
       </c>
       <c r="G372" t="n">
-        <v>8.65803813934326</v>
+        <v>8.65803623199463</v>
       </c>
       <c r="H372" t="n">
         <v>99284</v>
@@ -11186,7 +11186,7 @@
         <v>9.65499973297119</v>
       </c>
       <c r="G373" t="n">
-        <v>8.79930019378662</v>
+        <v>8.7992992401123</v>
       </c>
       <c r="H373" t="n">
         <v>110462</v>
@@ -11215,7 +11215,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G374" t="n">
-        <v>9.10461044311523</v>
+        <v>9.10460948944092</v>
       </c>
       <c r="H374" t="n">
         <v>180858</v>
@@ -11244,7 +11244,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G375" t="n">
-        <v>9.07726955413818</v>
+        <v>9.07726860046387</v>
       </c>
       <c r="H375" t="n">
         <v>116178</v>
@@ -11273,7 +11273,7 @@
         <v>9.94499969482422</v>
       </c>
       <c r="G376" t="n">
-        <v>9.06359767913818</v>
+        <v>9.0635986328125</v>
       </c>
       <c r="H376" t="n">
         <v>50994</v>
@@ -11476,7 +11476,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G383" t="n">
-        <v>9.61260032653809</v>
+        <v>9.6126012802124</v>
       </c>
       <c r="H383" t="n">
         <v>186379</v>
@@ -11534,7 +11534,7 @@
         <v>10.25</v>
       </c>
       <c r="G385" t="n">
-        <v>9.46485614776611</v>
+        <v>9.46485710144043</v>
       </c>
       <c r="H385" t="n">
         <v>63321</v>
@@ -11621,7 +11621,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G388" t="n">
-        <v>9.63106918334961</v>
+        <v>9.63106822967529</v>
       </c>
       <c r="H388" t="n">
         <v>137120</v>
@@ -11650,7 +11650,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G389" t="n">
-        <v>9.64030170440674</v>
+        <v>9.64030265808105</v>
       </c>
       <c r="H389" t="n">
         <v>168078</v>
@@ -11737,7 +11737,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G392" t="n">
-        <v>9.64030170440674</v>
+        <v>9.64030265808105</v>
       </c>
       <c r="H392" t="n">
         <v>109538</v>
@@ -11766,7 +11766,7 @@
         <v>10.5</v>
       </c>
       <c r="G393" t="n">
-        <v>9.69570636749268</v>
+        <v>9.69570732116699</v>
       </c>
       <c r="H393" t="n">
         <v>63889</v>
@@ -11824,7 +11824,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G395" t="n">
-        <v>9.66800403594971</v>
+        <v>9.66800498962402</v>
       </c>
       <c r="H395" t="n">
         <v>79788</v>
@@ -11882,7 +11882,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G397" t="n">
-        <v>9.56643009185791</v>
+        <v>9.56642913818359</v>
       </c>
       <c r="H397" t="n">
         <v>124190</v>
@@ -11940,7 +11940,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G399" t="n">
-        <v>9.34481334686279</v>
+        <v>9.34481430053711</v>
       </c>
       <c r="H399" t="n">
         <v>45265</v>
@@ -11969,7 +11969,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G400" t="n">
-        <v>9.18783664703369</v>
+        <v>9.18783569335938</v>
       </c>
       <c r="H400" t="n">
         <v>64703</v>
@@ -11998,7 +11998,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G401" t="n">
-        <v>9.04932689666748</v>
+        <v>9.04932594299316</v>
       </c>
       <c r="H401" t="n">
         <v>96905</v>
@@ -12056,7 +12056,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G403" t="n">
-        <v>8.79539012908936</v>
+        <v>8.79539108276367</v>
       </c>
       <c r="H403" t="n">
         <v>80618</v>
@@ -12085,7 +12085,7 @@
         <v>9.36499977111816</v>
       </c>
       <c r="G404" t="n">
-        <v>8.6476469039917</v>
+        <v>8.64764595031738</v>
       </c>
       <c r="H404" t="n">
         <v>93583</v>
@@ -12114,7 +12114,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G405" t="n">
-        <v>8.58762645721436</v>
+        <v>8.58762550354004</v>
       </c>
       <c r="H405" t="n">
         <v>464509</v>
@@ -12143,7 +12143,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G406" t="n">
-        <v>8.80000877380371</v>
+        <v>8.80000782012939</v>
       </c>
       <c r="H406" t="n">
         <v>218689</v>
@@ -12172,7 +12172,7 @@
         <v>9.55500030517578</v>
       </c>
       <c r="G407" t="n">
-        <v>8.82309246063232</v>
+        <v>8.82309341430664</v>
       </c>
       <c r="H407" t="n">
         <v>224972</v>
@@ -12288,7 +12288,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G411" t="n">
-        <v>8.82771110534668</v>
+        <v>8.82771015167236</v>
       </c>
       <c r="H411" t="n">
         <v>189726</v>
@@ -12404,7 +12404,7 @@
         <v>9.21500015258789</v>
       </c>
       <c r="G415" t="n">
-        <v>8.50913619995117</v>
+        <v>8.5091381072998</v>
       </c>
       <c r="H415" t="n">
         <v>86476</v>
@@ -12433,7 +12433,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G416" t="n">
-        <v>8.67073154449463</v>
+        <v>8.67073249816895</v>
       </c>
       <c r="H416" t="n">
         <v>133259</v>
@@ -12491,7 +12491,7 @@
         <v>9.57499980926514</v>
       </c>
       <c r="G418" t="n">
-        <v>8.84156131744385</v>
+        <v>8.84156036376953</v>
       </c>
       <c r="H418" t="n">
         <v>93508</v>
@@ -12520,7 +12520,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G419" t="n">
-        <v>8.57839298248291</v>
+        <v>8.57839202880859</v>
       </c>
       <c r="H419" t="n">
         <v>85948</v>
@@ -12578,7 +12578,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G421" t="n">
-        <v>8.28290462493896</v>
+        <v>8.28290367126465</v>
       </c>
       <c r="H421" t="n">
         <v>194344</v>
@@ -12636,7 +12636,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G423" t="n">
-        <v>8.03820323944092</v>
+        <v>8.0382022857666</v>
       </c>
       <c r="H423" t="n">
         <v>208593</v>
@@ -12723,7 +12723,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G426" t="n">
-        <v>7.92277669906616</v>
+        <v>7.92277717590332</v>
       </c>
       <c r="H426" t="n">
         <v>224688</v>
@@ -12752,7 +12752,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G427" t="n">
-        <v>7.82120323181152</v>
+        <v>7.82120275497437</v>
       </c>
       <c r="H427" t="n">
         <v>315397</v>
@@ -12781,7 +12781,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G428" t="n">
-        <v>7.82120323181152</v>
+        <v>7.82120275497437</v>
       </c>
       <c r="H428" t="n">
         <v>153923</v>
@@ -12810,7 +12810,7 @@
         <v>8.46500015258789</v>
       </c>
       <c r="G429" t="n">
-        <v>7.81658697128296</v>
+        <v>7.81658744812012</v>
       </c>
       <c r="H429" t="n">
         <v>124892</v>
@@ -12839,7 +12839,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G430" t="n">
-        <v>7.87660789489746</v>
+        <v>7.87660694122314</v>
       </c>
       <c r="H430" t="n">
         <v>182047</v>
@@ -12868,7 +12868,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G431" t="n">
-        <v>7.81196928024292</v>
+        <v>7.81196975708008</v>
       </c>
       <c r="H431" t="n">
         <v>211938</v>
@@ -12897,7 +12897,7 @@
         <v>8.42500019073486</v>
       </c>
       <c r="G432" t="n">
-        <v>7.77965021133423</v>
+        <v>7.77965116500854</v>
       </c>
       <c r="H432" t="n">
         <v>499662</v>
@@ -12926,7 +12926,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G433" t="n">
-        <v>7.5441837310791</v>
+        <v>7.54418325424194</v>
       </c>
       <c r="H433" t="n">
         <v>411895</v>
@@ -12955,7 +12955,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G434" t="n">
-        <v>7.25792932510376</v>
+        <v>7.2579288482666</v>
       </c>
       <c r="H434" t="n">
         <v>435932</v>
@@ -12984,7 +12984,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G435" t="n">
-        <v>7.06401491165161</v>
+        <v>7.06401538848877</v>
       </c>
       <c r="H435" t="n">
         <v>300120</v>
@@ -13013,7 +13013,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G436" t="n">
-        <v>7.10095071792603</v>
+        <v>7.10095119476318</v>
       </c>
       <c r="H436" t="n">
         <v>185032</v>
@@ -13071,7 +13071,7 @@
         <v>7.72499990463257</v>
       </c>
       <c r="G438" t="n">
-        <v>7.13327026367188</v>
+        <v>7.13326930999756</v>
       </c>
       <c r="H438" t="n">
         <v>174564</v>
@@ -13332,7 +13332,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G447" t="n">
-        <v>6.33452892303467</v>
+        <v>6.33452844619751</v>
       </c>
       <c r="H447" t="n">
         <v>231466</v>
@@ -13361,7 +13361,7 @@
         <v>7.13500022888184</v>
       </c>
       <c r="G448" t="n">
-        <v>6.58846378326416</v>
+        <v>6.588463306427</v>
       </c>
       <c r="H448" t="n">
         <v>537214</v>
@@ -13419,7 +13419,7 @@
         <v>7.31500005722046</v>
       </c>
       <c r="G450" t="n">
-        <v>6.75467538833618</v>
+        <v>6.75467586517334</v>
       </c>
       <c r="H450" t="n">
         <v>323055</v>
@@ -13477,7 +13477,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G452" t="n">
-        <v>6.55614423751831</v>
+        <v>6.55614471435547</v>
       </c>
       <c r="H452" t="n">
         <v>185501</v>
@@ -13651,7 +13651,7 @@
         <v>7.09499979019165</v>
       </c>
       <c r="G458" t="n">
-        <v>6.55152702331543</v>
+        <v>6.55152750015259</v>
       </c>
       <c r="H458" t="n">
         <v>694126</v>
@@ -13680,7 +13680,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G459" t="n">
-        <v>6.55614423751831</v>
+        <v>6.55614471435547</v>
       </c>
       <c r="H459" t="n">
         <v>342488</v>
@@ -13825,7 +13825,7 @@
         <v>6.69500017166138</v>
       </c>
       <c r="G464" t="n">
-        <v>6.18216753005981</v>
+        <v>6.18216800689697</v>
       </c>
       <c r="H464" t="n">
         <v>494430</v>
@@ -13854,7 +13854,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G465" t="n">
-        <v>6.18678426742554</v>
+        <v>6.18678379058838</v>
       </c>
       <c r="H465" t="n">
         <v>200486</v>
@@ -13883,7 +13883,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G466" t="n">
-        <v>5.80818939208984</v>
+        <v>5.80819034576416</v>
       </c>
       <c r="H466" t="n">
         <v>501243</v>
@@ -14057,7 +14057,7 @@
         <v>6.16499996185303</v>
       </c>
       <c r="G472" t="n">
-        <v>5.69276475906372</v>
+        <v>5.69276523590088</v>
       </c>
       <c r="H472" t="n">
         <v>637767</v>
@@ -14086,7 +14086,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G473" t="n">
-        <v>5.59580755233765</v>
+        <v>5.5958080291748</v>
       </c>
       <c r="H473" t="n">
         <v>246202</v>
@@ -14289,7 +14289,7 @@
         <v>5.9850001335144</v>
       </c>
       <c r="G480" t="n">
-        <v>5.5265531539917</v>
+        <v>5.52655267715454</v>
       </c>
       <c r="H480" t="n">
         <v>491648</v>
@@ -14434,7 +14434,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G485" t="n">
-        <v>5.17566061019897</v>
+        <v>5.17566108703613</v>
       </c>
       <c r="H485" t="n">
         <v>433667</v>
@@ -14666,7 +14666,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G493" t="n">
-        <v>4.83400201797485</v>
+        <v>4.83400249481201</v>
       </c>
       <c r="H493" t="n">
         <v>200923</v>
@@ -14695,7 +14695,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G494" t="n">
-        <v>4.88478899002075</v>
+        <v>4.88478946685791</v>
       </c>
       <c r="H494" t="n">
         <v>111362</v>
@@ -14724,7 +14724,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G495" t="n">
-        <v>4.88940620422363</v>
+        <v>4.88940668106079</v>
       </c>
       <c r="H495" t="n">
         <v>133883</v>
@@ -14753,7 +14753,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G496" t="n">
-        <v>5.13410711288452</v>
+        <v>5.13410758972168</v>
       </c>
       <c r="H496" t="n">
         <v>302728</v>
@@ -14869,7 +14869,7 @@
         <v>5.69500017166138</v>
       </c>
       <c r="G500" t="n">
-        <v>5.25876665115356</v>
+        <v>5.25876712799072</v>
       </c>
       <c r="H500" t="n">
         <v>671518</v>
@@ -14898,7 +14898,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G501" t="n">
-        <v>5.38342523574829</v>
+        <v>5.38342571258545</v>
       </c>
       <c r="H501" t="n">
         <v>200804</v>
@@ -15101,7 +15101,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G508" t="n">
-        <v>5.41112804412842</v>
+        <v>5.41112756729126</v>
       </c>
       <c r="H508" t="n">
         <v>222944</v>
@@ -15159,7 +15159,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G510" t="n">
-        <v>5.21259689331055</v>
+        <v>5.21259641647339</v>
       </c>
       <c r="H510" t="n">
         <v>110937</v>
@@ -15246,7 +15246,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G513" t="n">
-        <v>5.21259689331055</v>
+        <v>5.21259641647339</v>
       </c>
       <c r="H513" t="n">
         <v>215173</v>
@@ -15420,7 +15420,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G519" t="n">
-        <v>5.25414991378784</v>
+        <v>5.25414943695068</v>
       </c>
       <c r="H519" t="n">
         <v>250927</v>
@@ -15536,7 +15536,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G523" t="n">
-        <v>5.16180992126465</v>
+        <v>5.16180944442749</v>
       </c>
       <c r="H523" t="n">
         <v>249552</v>
@@ -15565,7 +15565,7 @@
         <v>5.5</v>
       </c>
       <c r="G524" t="n">
-        <v>5.0787034034729</v>
+        <v>5.07870388031006</v>
       </c>
       <c r="H524" t="n">
         <v>365475</v>
@@ -15797,7 +15797,7 @@
         <v>6.30499982833862</v>
       </c>
       <c r="G532" t="n">
-        <v>5.82204103469849</v>
+        <v>5.82204055786133</v>
       </c>
       <c r="H532" t="n">
         <v>298757</v>
@@ -15884,7 +15884,7 @@
         <v>6.2649998664856</v>
       </c>
       <c r="G535" t="n">
-        <v>5.78510522842407</v>
+        <v>5.78510475158691</v>
       </c>
       <c r="H535" t="n">
         <v>171909</v>
@@ -15913,7 +15913,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G536" t="n">
-        <v>5.71585035324097</v>
+        <v>5.71584987640381</v>
       </c>
       <c r="H536" t="n">
         <v>257462</v>
@@ -16029,7 +16029,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G540" t="n">
-        <v>6.03904008865356</v>
+        <v>6.03904056549072</v>
       </c>
       <c r="H540" t="n">
         <v>416492</v>
@@ -16058,7 +16058,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G541" t="n">
-        <v>6.05750751495361</v>
+        <v>6.05750846862793</v>
       </c>
       <c r="H541" t="n">
         <v>374625</v>
@@ -16087,7 +16087,7 @@
         <v>6.57499980926514</v>
       </c>
       <c r="G542" t="n">
-        <v>6.07135915756226</v>
+        <v>6.0713586807251</v>
       </c>
       <c r="H542" t="n">
         <v>267523</v>
@@ -16435,7 +16435,7 @@
         <v>6.29500007629395</v>
       </c>
       <c r="G554" t="n">
-        <v>5.81280755996704</v>
+        <v>5.81280660629272</v>
       </c>
       <c r="H554" t="n">
         <v>151233</v>
@@ -16464,7 +16464,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G555" t="n">
-        <v>5.71585035324097</v>
+        <v>5.71584987640381</v>
       </c>
       <c r="H555" t="n">
         <v>675111</v>
@@ -16725,7 +16725,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G564" t="n">
-        <v>5.41112804412842</v>
+        <v>5.41112756729126</v>
       </c>
       <c r="H564" t="n">
         <v>104231</v>
@@ -16754,7 +16754,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G565" t="n">
-        <v>5.51270198822021</v>
+        <v>5.51270151138306</v>
       </c>
       <c r="H565" t="n">
         <v>164534</v>
@@ -16783,7 +16783,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G566" t="n">
-        <v>5.38342523574829</v>
+        <v>5.38342571258545</v>
       </c>
       <c r="H566" t="n">
         <v>143325</v>
@@ -16928,7 +16928,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G571" t="n">
-        <v>5.17566061019897</v>
+        <v>5.17566108703613</v>
       </c>
       <c r="H571" t="n">
         <v>188694</v>
@@ -17044,7 +17044,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G575" t="n">
-        <v>5.13410711288452</v>
+        <v>5.13410758972168</v>
       </c>
       <c r="H575" t="n">
         <v>302344</v>
@@ -17160,7 +17160,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G579" t="n">
-        <v>5.07408666610718</v>
+        <v>5.07408618927002</v>
       </c>
       <c r="H579" t="n">
         <v>256005</v>
@@ -17189,7 +17189,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G580" t="n">
-        <v>5.09717082977295</v>
+        <v>5.09717130661011</v>
       </c>
       <c r="H580" t="n">
         <v>391172</v>
@@ -17247,7 +17247,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G582" t="n">
-        <v>5.3003191947937</v>
+        <v>5.30031967163086</v>
       </c>
       <c r="H582" t="n">
         <v>1080928</v>
@@ -17334,7 +17334,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G585" t="n">
-        <v>5.47576570510864</v>
+        <v>5.47576522827148</v>
       </c>
       <c r="H585" t="n">
         <v>310197</v>
@@ -17392,7 +17392,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G587" t="n">
-        <v>5.57733964920044</v>
+        <v>5.5773401260376</v>
       </c>
       <c r="H587" t="n">
         <v>394516</v>
@@ -17421,7 +17421,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G588" t="n">
-        <v>5.59580755233765</v>
+        <v>5.5958080291748</v>
       </c>
       <c r="H588" t="n">
         <v>428003</v>
@@ -17682,7 +17682,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G597" t="n">
-        <v>4.83400201797485</v>
+        <v>4.83400249481201</v>
       </c>
       <c r="H597" t="n">
         <v>384652</v>
@@ -17711,7 +17711,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G598" t="n">
-        <v>4.80630016326904</v>
+        <v>4.8063006401062</v>
       </c>
       <c r="H598" t="n">
         <v>332805</v>
@@ -17740,7 +17740,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G599" t="n">
-        <v>4.70010948181152</v>
+        <v>4.70010900497437</v>
       </c>
       <c r="H599" t="n">
         <v>555539</v>
@@ -17769,7 +17769,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G600" t="n">
-        <v>4.81091785430908</v>
+        <v>4.81091737747192</v>
       </c>
       <c r="H600" t="n">
         <v>367022</v>
@@ -17827,7 +17827,7 @@
         <v>5.22499990463257</v>
       </c>
       <c r="G602" t="n">
-        <v>4.82476854324341</v>
+        <v>4.82476806640625</v>
       </c>
       <c r="H602" t="n">
         <v>549261</v>
@@ -17856,7 +17856,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G603" t="n">
-        <v>4.89864063262939</v>
+        <v>4.89863967895508</v>
       </c>
       <c r="H603" t="n">
         <v>510591</v>
@@ -17885,7 +17885,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>4.80630016326904</v>
+        <v>4.8063006401062</v>
       </c>
       <c r="H604" t="n">
         <v>321087</v>
@@ -17914,7 +17914,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G605" t="n">
-        <v>4.66317367553711</v>
+        <v>4.66317319869995</v>
       </c>
       <c r="H605" t="n">
         <v>1112720</v>
@@ -17943,7 +17943,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>4.52466344833374</v>
+        <v>4.52466297149658</v>
       </c>
       <c r="H606" t="n">
         <v>835466</v>
@@ -17972,7 +17972,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G607" t="n">
-        <v>4.52466344833374</v>
+        <v>4.52466297149658</v>
       </c>
       <c r="H607" t="n">
         <v>662577</v>
@@ -18001,7 +18001,7 @@
         <v>4.82200002670288</v>
       </c>
       <c r="G608" t="n">
-        <v>4.45263767242432</v>
+        <v>4.45263814926147</v>
       </c>
       <c r="H608" t="n">
         <v>597938</v>
@@ -18059,7 +18059,7 @@
         <v>4.66400003433228</v>
       </c>
       <c r="G610" t="n">
-        <v>4.30674028396606</v>
+        <v>4.30674076080322</v>
       </c>
       <c r="H610" t="n">
         <v>394307</v>
@@ -18175,7 +18175,7 @@
         <v>4.74399995803833</v>
       </c>
       <c r="G614" t="n">
-        <v>4.38061285018921</v>
+        <v>4.38061237335205</v>
       </c>
       <c r="H614" t="n">
         <v>609563</v>
@@ -18291,7 +18291,7 @@
         <v>5</v>
       </c>
       <c r="G618" t="n">
-        <v>4.61700296401978</v>
+        <v>4.61700344085693</v>
       </c>
       <c r="H618" t="n">
         <v>694400</v>
@@ -18378,7 +18378,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G621" t="n">
-        <v>4.56898593902588</v>
+        <v>4.56898641586304</v>
       </c>
       <c r="H621" t="n">
         <v>377386</v>
@@ -18494,7 +18494,7 @@
         <v>5.06500005722046</v>
       </c>
       <c r="G625" t="n">
-        <v>4.67702436447144</v>
+        <v>4.67702388763428</v>
       </c>
       <c r="H625" t="n">
         <v>1126607</v>
@@ -18552,7 +18552,7 @@
         <v>4.97800016403198</v>
       </c>
       <c r="G627" t="n">
-        <v>4.59668827056885</v>
+        <v>4.59668874740601</v>
       </c>
       <c r="H627" t="n">
         <v>698215</v>
@@ -18581,7 +18581,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G628" t="n">
-        <v>4.70010948181152</v>
+        <v>4.70010900497437</v>
       </c>
       <c r="H628" t="n">
         <v>666276</v>
@@ -18639,7 +18639,7 @@
         <v>5.0149998664856</v>
       </c>
       <c r="G630" t="n">
-        <v>4.6308536529541</v>
+        <v>4.63085412979126</v>
       </c>
       <c r="H630" t="n">
         <v>580822</v>
@@ -18668,7 +18668,7 @@
         <v>4.94199991226196</v>
       </c>
       <c r="G631" t="n">
-        <v>4.56344604492188</v>
+        <v>4.56344556808472</v>
       </c>
       <c r="H631" t="n">
         <v>610912</v>
@@ -18726,7 +18726,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G633" t="n">
-        <v>4.63421249389648</v>
+        <v>4.63421201705933</v>
       </c>
       <c r="H633" t="n">
         <v>659569</v>
@@ -18900,7 +18900,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G639" t="n">
-        <v>4.47546625137329</v>
+        <v>4.47546672821045</v>
       </c>
       <c r="H639" t="n">
         <v>721270</v>
@@ -18929,7 +18929,7 @@
         <v>4.81199979782104</v>
       </c>
       <c r="G640" t="n">
-        <v>4.60169744491577</v>
+        <v>4.60169792175293</v>
       </c>
       <c r="H640" t="n">
         <v>409298</v>
@@ -19074,7 +19074,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G645" t="n">
-        <v>4.45634078979492</v>
+        <v>4.45634031295776</v>
       </c>
       <c r="H645" t="n">
         <v>337361</v>
@@ -19132,7 +19132,7 @@
         <v>4.62400007247925</v>
       </c>
       <c r="G647" t="n">
-        <v>4.42191410064697</v>
+        <v>4.42191457748413</v>
       </c>
       <c r="H647" t="n">
         <v>590963</v>
@@ -19219,7 +19219,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G650" t="n">
-        <v>4.17136478424072</v>
+        <v>4.17136430740356</v>
       </c>
       <c r="H650" t="n">
         <v>575556</v>
@@ -19306,7 +19306,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G653" t="n">
-        <v>4.20770406723022</v>
+        <v>4.20770359039307</v>
       </c>
       <c r="H653" t="n">
         <v>253568</v>
@@ -19480,7 +19480,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G659" t="n">
-        <v>3.93037796020508</v>
+        <v>3.9303777217865</v>
       </c>
       <c r="H659" t="n">
         <v>499794</v>
@@ -19770,7 +19770,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G669" t="n">
-        <v>3.65496468544006</v>
+        <v>3.65496444702148</v>
       </c>
       <c r="H669" t="n">
         <v>556073</v>
@@ -19857,7 +19857,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G672" t="n">
-        <v>3.81370949745178</v>
+        <v>3.81370973587036</v>
       </c>
       <c r="H672" t="n">
         <v>401105</v>
@@ -19886,7 +19886,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G673" t="n">
-        <v>3.81370949745178</v>
+        <v>3.81370973587036</v>
       </c>
       <c r="H673" t="n">
         <v>294689</v>
@@ -19915,7 +19915,7 @@
         <v>4.17600011825562</v>
       </c>
       <c r="G674" t="n">
-        <v>3.99349355697632</v>
+        <v>3.99349331855774</v>
       </c>
       <c r="H674" t="n">
         <v>714573</v>
@@ -20379,7 +20379,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G690" t="n">
-        <v>3.45605492591858</v>
+        <v>3.4560546875</v>
       </c>
       <c r="H690" t="n">
         <v>383156</v>
@@ -20756,7 +20756,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G703" t="n">
-        <v>3.96862959861755</v>
+        <v>3.96862983703613</v>
       </c>
       <c r="H703" t="n">
         <v>402206</v>
@@ -20785,7 +20785,7 @@
         <v>4.1560001373291</v>
       </c>
       <c r="G704" t="n">
-        <v>3.97436785697937</v>
+        <v>3.97436738014221</v>
       </c>
       <c r="H704" t="n">
         <v>366565</v>
@@ -20843,7 +20843,7 @@
         <v>4.27600002288818</v>
       </c>
       <c r="G706" t="n">
-        <v>4.0891227722168</v>
+        <v>4.08912324905396</v>
       </c>
       <c r="H706" t="n">
         <v>382472</v>
@@ -20872,7 +20872,7 @@
         <v>4.13600015640259</v>
       </c>
       <c r="G707" t="n">
-        <v>3.95524168014526</v>
+        <v>3.95524144172668</v>
       </c>
       <c r="H707" t="n">
         <v>503313</v>
@@ -20930,7 +20930,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G709" t="n">
-        <v>3.98966813087463</v>
+        <v>3.98966789245605</v>
       </c>
       <c r="H709" t="n">
         <v>357159</v>
@@ -21017,7 +21017,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G712" t="n">
-        <v>3.67026519775391</v>
+        <v>3.67026543617249</v>
       </c>
       <c r="H712" t="n">
         <v>437455</v>
@@ -21162,7 +21162,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G717" t="n">
-        <v>3.81370949745178</v>
+        <v>3.81370973587036</v>
       </c>
       <c r="H717" t="n">
         <v>286225</v>
@@ -21191,7 +21191,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G718" t="n">
-        <v>3.82327270507812</v>
+        <v>3.82327246665955</v>
       </c>
       <c r="H718" t="n">
         <v>150642</v>
@@ -21220,7 +21220,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G719" t="n">
-        <v>3.91507697105408</v>
+        <v>3.91507720947266</v>
       </c>
       <c r="H719" t="n">
         <v>372351</v>
@@ -21307,7 +21307,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G722" t="n">
-        <v>3.98584294319153</v>
+        <v>3.98584318161011</v>
       </c>
       <c r="H722" t="n">
         <v>634315</v>
@@ -21365,7 +21365,7 @@
         <v>4.42600011825562</v>
       </c>
       <c r="G724" t="n">
-        <v>4.23256778717041</v>
+        <v>4.23256731033325</v>
       </c>
       <c r="H724" t="n">
         <v>1439555</v>
@@ -21394,7 +21394,7 @@
         <v>4.51200008392334</v>
       </c>
       <c r="G725" t="n">
-        <v>4.31480884552002</v>
+        <v>4.31480932235718</v>
       </c>
       <c r="H725" t="n">
         <v>724657</v>
@@ -21452,7 +21452,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G727" t="n">
-        <v>4.15032625198364</v>
+        <v>4.15032577514648</v>
       </c>
       <c r="H727" t="n">
         <v>336308</v>
@@ -21510,7 +21510,7 @@
         <v>4.25</v>
       </c>
       <c r="G729" t="n">
-        <v>4.06425905227661</v>
+        <v>4.06425952911377</v>
       </c>
       <c r="H729" t="n">
         <v>168991</v>
@@ -21597,7 +21597,7 @@
         <v>4.2039999961853</v>
       </c>
       <c r="G732" t="n">
-        <v>4.0202693939209</v>
+        <v>4.02026987075806</v>
       </c>
       <c r="H732" t="n">
         <v>193502</v>
@@ -21742,7 +21742,7 @@
         <v>4.11399984359741</v>
       </c>
       <c r="G737" t="n">
-        <v>3.93420267105103</v>
+        <v>3.9342029094696</v>
       </c>
       <c r="H737" t="n">
         <v>129269</v>
@@ -21829,7 +21829,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G740" t="n">
-        <v>3.96862959861755</v>
+        <v>3.96862983703613</v>
       </c>
       <c r="H740" t="n">
         <v>236046</v>
@@ -21858,7 +21858,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G741" t="n">
-        <v>3.91507697105408</v>
+        <v>3.91507720947266</v>
       </c>
       <c r="H741" t="n">
         <v>182762</v>
@@ -22061,7 +22061,7 @@
         <v>3.90799999237061</v>
       </c>
       <c r="G748" t="n">
-        <v>3.73720574378967</v>
+        <v>3.73720598220825</v>
       </c>
       <c r="H748" t="n">
         <v>191909</v>
@@ -22119,7 +22119,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G750" t="n">
-        <v>3.70086669921875</v>
+        <v>3.70086646080017</v>
       </c>
       <c r="H750" t="n">
         <v>77185</v>
@@ -22148,7 +22148,7 @@
         <v>3.93799996376038</v>
       </c>
       <c r="G751" t="n">
-        <v>3.76589488983154</v>
+        <v>3.76589465141296</v>
       </c>
       <c r="H751" t="n">
         <v>138045</v>
@@ -22264,7 +22264,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G755" t="n">
-        <v>3.73911881446838</v>
+        <v>3.7391185760498</v>
       </c>
       <c r="H755" t="n">
         <v>208777</v>
@@ -22380,7 +22380,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G759" t="n">
-        <v>3.57846093177795</v>
+        <v>3.57846069335938</v>
       </c>
       <c r="H759" t="n">
         <v>337584</v>
@@ -22409,7 +22409,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G760" t="n">
-        <v>3.62245059013367</v>
+        <v>3.62245035171509</v>
       </c>
       <c r="H760" t="n">
         <v>422072</v>
@@ -22467,7 +22467,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G762" t="n">
-        <v>3.56315994262695</v>
+        <v>3.56316018104553</v>
       </c>
       <c r="H762" t="n">
         <v>704289</v>
@@ -22496,7 +22496,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G763" t="n">
-        <v>3.54785919189453</v>
+        <v>3.54785943031311</v>
       </c>
       <c r="H763" t="n">
         <v>1097480</v>
@@ -22583,7 +22583,7 @@
         <v>3.64800000190735</v>
       </c>
       <c r="G766" t="n">
-        <v>3.48856902122498</v>
+        <v>3.4885687828064</v>
       </c>
       <c r="H766" t="n">
         <v>1669355</v>
@@ -22728,7 +22728,7 @@
         <v>3.64400005340576</v>
       </c>
       <c r="G771" t="n">
-        <v>3.48474359512329</v>
+        <v>3.48474383354187</v>
       </c>
       <c r="H771" t="n">
         <v>105519</v>
@@ -22757,7 +22757,7 @@
         <v>3.63199996948242</v>
       </c>
       <c r="G772" t="n">
-        <v>3.47326827049255</v>
+        <v>3.47326803207397</v>
       </c>
       <c r="H772" t="n">
         <v>121534</v>
@@ -22873,7 +22873,7 @@
         <v>3.95799994468689</v>
       </c>
       <c r="G776" t="n">
-        <v>3.78502082824707</v>
+        <v>3.78502058982849</v>
       </c>
       <c r="H776" t="n">
         <v>243650</v>
@@ -22902,7 +22902,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G777" t="n">
-        <v>3.76971983909607</v>
+        <v>3.76972007751465</v>
       </c>
       <c r="H777" t="n">
         <v>111182</v>
@@ -22960,7 +22960,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G779" t="n">
-        <v>3.70086669921875</v>
+        <v>3.70086646080017</v>
       </c>
       <c r="H779" t="n">
         <v>145693</v>
@@ -22989,7 +22989,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G780" t="n">
-        <v>3.59758687019348</v>
+        <v>3.5975866317749</v>
       </c>
       <c r="H780" t="n">
         <v>157659</v>
@@ -23076,7 +23076,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G783" t="n">
-        <v>3.44075393676758</v>
+        <v>3.44075417518616</v>
       </c>
       <c r="H783" t="n">
         <v>613580</v>
@@ -23105,7 +23105,7 @@
         <v>3.41599988937378</v>
       </c>
       <c r="G784" t="n">
-        <v>3.26670813560486</v>
+        <v>3.26670789718628</v>
       </c>
       <c r="H784" t="n">
         <v>455535</v>
@@ -23134,7 +23134,7 @@
         <v>3.41599988937378</v>
       </c>
       <c r="G785" t="n">
-        <v>3.26670813560486</v>
+        <v>3.26670789718628</v>
       </c>
       <c r="H785" t="n">
         <v>519347</v>
@@ -23163,7 +23163,7 @@
         <v>3.46799993515015</v>
       </c>
       <c r="G786" t="n">
-        <v>3.31643533706665</v>
+        <v>3.31643557548523</v>
       </c>
       <c r="H786" t="n">
         <v>202674</v>
@@ -23192,7 +23192,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G787" t="n">
-        <v>3.29157161712646</v>
+        <v>3.29157185554504</v>
       </c>
       <c r="H787" t="n">
         <v>188696</v>
@@ -23424,7 +23424,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G795" t="n">
-        <v>3.20741772651672</v>
+        <v>3.2074179649353</v>
       </c>
       <c r="H795" t="n">
         <v>383770</v>
@@ -23801,7 +23801,7 @@
         <v>3.47399997711182</v>
       </c>
       <c r="G808" t="n">
-        <v>3.32217335700989</v>
+        <v>3.32217311859131</v>
       </c>
       <c r="H808" t="n">
         <v>80720</v>
@@ -23975,7 +23975,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G814" t="n">
-        <v>3.22654366493225</v>
+        <v>3.22654390335083</v>
       </c>
       <c r="H814" t="n">
         <v>115313</v>
@@ -24149,7 +24149,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G820" t="n">
-        <v>3.55168461799622</v>
+        <v>3.55168437957764</v>
       </c>
       <c r="H820" t="n">
         <v>1031313</v>
@@ -24178,7 +24178,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G821" t="n">
-        <v>3.5076949596405</v>
+        <v>3.50769472122192</v>
       </c>
       <c r="H821" t="n">
         <v>354331</v>
@@ -24236,7 +24236,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G823" t="n">
-        <v>3.53638362884521</v>
+        <v>3.53638386726379</v>
       </c>
       <c r="H823" t="n">
         <v>421877</v>
@@ -24323,7 +24323,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G826" t="n">
-        <v>3.58228588104248</v>
+        <v>3.58228611946106</v>
       </c>
       <c r="H826" t="n">
         <v>258986</v>
@@ -24352,7 +24352,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G827" t="n">
-        <v>3.5765483379364</v>
+        <v>3.57654809951782</v>
       </c>
       <c r="H827" t="n">
         <v>166129</v>
@@ -24381,7 +24381,7 @@
         <v>3.84400010108948</v>
       </c>
       <c r="G828" t="n">
-        <v>3.67600321769714</v>
+        <v>3.67600297927856</v>
       </c>
       <c r="H828" t="n">
         <v>474129</v>
@@ -24526,7 +24526,7 @@
         <v>4.22599983215332</v>
       </c>
       <c r="G833" t="n">
-        <v>4.04130792617798</v>
+        <v>4.04130840301514</v>
       </c>
       <c r="H833" t="n">
         <v>2312238</v>
@@ -24758,7 +24758,7 @@
         <v>4.68599987030029</v>
       </c>
       <c r="G841" t="n">
-        <v>4.48120450973511</v>
+        <v>4.48120403289795</v>
       </c>
       <c r="H841" t="n">
         <v>337090</v>
@@ -24816,7 +24816,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G843" t="n">
-        <v>4.54432010650635</v>
+        <v>4.54431962966919</v>
       </c>
       <c r="H843" t="n">
         <v>212793</v>
@@ -24903,7 +24903,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G846" t="n">
-        <v>4.35688591003418</v>
+        <v>4.35688638687134</v>
       </c>
       <c r="H846" t="n">
         <v>178453</v>
@@ -24932,7 +24932,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G847" t="n">
-        <v>4.26316928863525</v>
+        <v>4.2631688117981</v>
       </c>
       <c r="H847" t="n">
         <v>228223</v>
@@ -24990,7 +24990,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G849" t="n">
-        <v>4.17136478424072</v>
+        <v>4.17136430740356</v>
       </c>
       <c r="H849" t="n">
         <v>216742</v>
@@ -25048,7 +25048,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G851" t="n">
-        <v>3.93037796020508</v>
+        <v>3.9303777217865</v>
       </c>
       <c r="H851" t="n">
         <v>187268</v>
@@ -25135,7 +25135,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G854" t="n">
-        <v>3.77928280830383</v>
+        <v>3.77928304672241</v>
       </c>
       <c r="H854" t="n">
         <v>245578</v>
@@ -25251,7 +25251,7 @@
         <v>3.51200008392334</v>
       </c>
       <c r="G858" t="n">
-        <v>3.35851263999939</v>
+        <v>3.35851287841797</v>
       </c>
       <c r="H858" t="n">
         <v>146055</v>
@@ -25280,7 +25280,7 @@
         <v>3.56800007820129</v>
       </c>
       <c r="G859" t="n">
-        <v>3.41206526756287</v>
+        <v>3.41206550598145</v>
       </c>
       <c r="H859" t="n">
         <v>419236</v>
@@ -25396,7 +25396,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G863" t="n">
-        <v>3.47900581359863</v>
+        <v>3.47900605201721</v>
       </c>
       <c r="H863" t="n">
         <v>215914</v>
@@ -25541,7 +25541,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G868" t="n">
-        <v>3.77928280830383</v>
+        <v>3.77928304672241</v>
       </c>
       <c r="H868" t="n">
         <v>73720</v>
@@ -25657,7 +25657,7 @@
         <v>4.12400007247925</v>
       </c>
       <c r="G872" t="n">
-        <v>3.94376587867737</v>
+        <v>3.94376611709595</v>
       </c>
       <c r="H872" t="n">
         <v>191569</v>
@@ -25860,7 +25860,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G879" t="n">
-        <v>4.47546625137329</v>
+        <v>4.47546672821045</v>
       </c>
       <c r="H879" t="n">
         <v>120035</v>
@@ -25976,7 +25976,7 @@
         <v>4.38800001144409</v>
       </c>
       <c r="G883" t="n">
-        <v>4.19622850418091</v>
+        <v>4.19622802734375</v>
       </c>
       <c r="H883" t="n">
         <v>292289</v>
@@ -26063,7 +26063,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G886" t="n">
-        <v>4.20196580886841</v>
+        <v>4.20196628570557</v>
       </c>
       <c r="H886" t="n">
         <v>132141</v>
@@ -26237,7 +26237,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G892" t="n">
-        <v>4.57109689712524</v>
+        <v>4.57109642028809</v>
       </c>
       <c r="H892" t="n">
         <v>407750</v>
@@ -26295,7 +26295,7 @@
         <v>4.74599981307983</v>
       </c>
       <c r="G894" t="n">
-        <v>4.53858184814453</v>
+        <v>4.53858232498169</v>
       </c>
       <c r="H894" t="n">
         <v>111758</v>
@@ -26324,7 +26324,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G895" t="n">
-        <v>4.68585205078125</v>
+        <v>4.68585157394409</v>
       </c>
       <c r="H895" t="n">
         <v>288639</v>
@@ -36448,9 +36448,38 @@
         <v>3.3659999370575</v>
       </c>
       <c r="H1244" t="n">
-        <v>249124</v>
+        <v>256504</v>
       </c>
       <c r="I1244" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1245" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1245" t="n">
+        <v>3.39199995994568</v>
+      </c>
+      <c r="D1245" t="n">
+        <v>3.39199995994568</v>
+      </c>
+      <c r="E1245" t="n">
+        <v>3.2960000038147</v>
+      </c>
+      <c r="F1245" t="n">
+        <v>3.33599996566772</v>
+      </c>
+      <c r="G1245" t="n">
+        <v>3.33599996566772</v>
+      </c>
+      <c r="H1245" t="n">
+        <v>245017</v>
+      </c>
+      <c r="I1245" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ARIS.MI.xlsx
+++ b/data/ARIS.MI.xlsx
@@ -485,7 +485,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G4" t="n">
-        <v>9.17451477050781</v>
+        <v>9.1745138168335</v>
       </c>
       <c r="H4" t="n">
         <v>732483</v>
@@ -514,7 +514,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G5" t="n">
-        <v>9.25538730621338</v>
+        <v>9.25538635253906</v>
       </c>
       <c r="H5" t="n">
         <v>304924</v>
@@ -543,7 +543,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G6" t="n">
-        <v>9.20147132873535</v>
+        <v>9.20147037506104</v>
       </c>
       <c r="H6" t="n">
         <v>260042</v>
@@ -572,7 +572,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G7" t="n">
-        <v>9.20147132873535</v>
+        <v>9.20147037506104</v>
       </c>
       <c r="H7" t="n">
         <v>279621</v>
@@ -601,7 +601,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G8" t="n">
-        <v>9.20147132873535</v>
+        <v>9.20147037506104</v>
       </c>
       <c r="H8" t="n">
         <v>197900</v>
@@ -659,7 +659,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G10" t="n">
-        <v>9.20147132873535</v>
+        <v>9.20147037506104</v>
       </c>
       <c r="H10" t="n">
         <v>122758</v>
@@ -688,7 +688,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G11" t="n">
-        <v>9.23741340637207</v>
+        <v>9.23741436004639</v>
       </c>
       <c r="H11" t="n">
         <v>199132</v>
@@ -717,7 +717,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G12" t="n">
-        <v>9.20147132873535</v>
+        <v>9.20147037506104</v>
       </c>
       <c r="H12" t="n">
         <v>105196</v>
@@ -746,7 +746,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G13" t="n">
-        <v>9.20147132873535</v>
+        <v>9.20147037506104</v>
       </c>
       <c r="H13" t="n">
         <v>85905</v>
@@ -775,7 +775,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G14" t="n">
-        <v>9.20147132873535</v>
+        <v>9.20147037506104</v>
       </c>
       <c r="H14" t="n">
         <v>198256</v>
@@ -833,7 +833,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G16" t="n">
-        <v>8.92291164398193</v>
+        <v>8.92291069030762</v>
       </c>
       <c r="H16" t="n">
         <v>312158</v>
@@ -891,7 +891,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G18" t="n">
-        <v>8.63536548614502</v>
+        <v>8.6353645324707</v>
       </c>
       <c r="H18" t="n">
         <v>319387</v>
@@ -949,7 +949,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G20" t="n">
-        <v>9.12958335876465</v>
+        <v>9.12958431243896</v>
       </c>
       <c r="H20" t="n">
         <v>431091</v>
@@ -1007,7 +1007,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G22" t="n">
-        <v>8.85102462768555</v>
+        <v>8.85102367401123</v>
       </c>
       <c r="H22" t="n">
         <v>186957</v>
@@ -1065,7 +1065,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G24" t="n">
-        <v>9.12958335876465</v>
+        <v>9.12958431243896</v>
       </c>
       <c r="H24" t="n">
         <v>61464</v>
@@ -1123,7 +1123,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G26" t="n">
-        <v>9.12958335876465</v>
+        <v>9.12958431243896</v>
       </c>
       <c r="H26" t="n">
         <v>53953</v>
@@ -1181,7 +1181,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G28" t="n">
-        <v>9.65076065063477</v>
+        <v>9.65076160430908</v>
       </c>
       <c r="H28" t="n">
         <v>568583</v>
@@ -1210,7 +1210,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G29" t="n">
-        <v>9.74061965942383</v>
+        <v>9.74062061309814</v>
       </c>
       <c r="H29" t="n">
         <v>87322</v>
@@ -1239,7 +1239,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G30" t="n">
-        <v>10.1180248260498</v>
+        <v>10.1180238723755</v>
       </c>
       <c r="H30" t="n">
         <v>401264</v>
@@ -1297,7 +1297,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G32" t="n">
-        <v>9.17451477050781</v>
+        <v>9.1745138168335</v>
       </c>
       <c r="H32" t="n">
         <v>405173</v>
@@ -1326,7 +1326,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G33" t="n">
-        <v>9.63279056549072</v>
+        <v>9.63279151916504</v>
       </c>
       <c r="H33" t="n">
         <v>261751</v>
@@ -1355,7 +1355,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G34" t="n">
-        <v>10.0191783905029</v>
+        <v>10.0191802978516</v>
       </c>
       <c r="H34" t="n">
         <v>509719</v>
@@ -1384,7 +1384,7 @@
         <v>10.9899997711182</v>
       </c>
       <c r="G35" t="n">
-        <v>9.87540721893311</v>
+        <v>9.87540626525879</v>
       </c>
       <c r="H35" t="n">
         <v>209128</v>
@@ -1413,7 +1413,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G36" t="n">
-        <v>10.1988954544067</v>
+        <v>10.1988964080811</v>
       </c>
       <c r="H36" t="n">
         <v>477707</v>
@@ -1442,7 +1442,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G37" t="n">
-        <v>10.1180248260498</v>
+        <v>10.1180238723755</v>
       </c>
       <c r="H37" t="n">
         <v>92776</v>
@@ -1500,7 +1500,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G39" t="n">
-        <v>9.62380313873291</v>
+        <v>9.62380409240723</v>
       </c>
       <c r="H39" t="n">
         <v>115964</v>
@@ -1529,7 +1529,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G40" t="n">
-        <v>9.67771911621094</v>
+        <v>9.67772006988525</v>
       </c>
       <c r="H40" t="n">
         <v>103333</v>
@@ -1587,7 +1587,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G42" t="n">
-        <v>9.10262680053711</v>
+        <v>9.10262775421143</v>
       </c>
       <c r="H42" t="n">
         <v>130467</v>
@@ -1616,7 +1616,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G43" t="n">
-        <v>9.17451477050781</v>
+        <v>9.1745138168335</v>
       </c>
       <c r="H43" t="n">
         <v>290667</v>
@@ -1645,7 +1645,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G44" t="n">
-        <v>9.12059879302979</v>
+        <v>9.1205997467041</v>
       </c>
       <c r="H44" t="n">
         <v>167591</v>
@@ -1674,7 +1674,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G45" t="n">
-        <v>9.0487117767334</v>
+        <v>9.04871273040771</v>
       </c>
       <c r="H45" t="n">
         <v>274213</v>
@@ -1703,7 +1703,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G46" t="n">
-        <v>9.20147132873535</v>
+        <v>9.20147037506104</v>
       </c>
       <c r="H46" t="n">
         <v>323983</v>
@@ -1761,7 +1761,7 @@
         <v>10.4899997711182</v>
       </c>
       <c r="G48" t="n">
-        <v>9.42611694335938</v>
+        <v>9.42611598968506</v>
       </c>
       <c r="H48" t="n">
         <v>67641</v>
@@ -1848,7 +1848,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G51" t="n">
-        <v>9.16552734375</v>
+        <v>9.16552829742432</v>
       </c>
       <c r="H51" t="n">
         <v>170220</v>
@@ -1877,7 +1877,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G52" t="n">
-        <v>9.12958335876465</v>
+        <v>9.12958431243896</v>
       </c>
       <c r="H52" t="n">
         <v>73644</v>
@@ -1906,7 +1906,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G53" t="n">
-        <v>9.24639987945557</v>
+        <v>9.24640083312988</v>
       </c>
       <c r="H53" t="n">
         <v>328076</v>
@@ -1935,7 +1935,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G54" t="n">
-        <v>9.16552734375</v>
+        <v>9.16552829742432</v>
       </c>
       <c r="H54" t="n">
         <v>213651</v>
@@ -2022,7 +2022,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G57" t="n">
-        <v>9.10262680053711</v>
+        <v>9.10262775421143</v>
       </c>
       <c r="H57" t="n">
         <v>123193</v>
@@ -2109,7 +2109,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G60" t="n">
-        <v>8.95885467529297</v>
+        <v>8.95885372161865</v>
       </c>
       <c r="H60" t="n">
         <v>207313</v>
@@ -2196,7 +2196,7 @@
         <v>9.1850004196167</v>
       </c>
       <c r="G63" t="n">
-        <v>8.25346851348877</v>
+        <v>8.25346755981445</v>
       </c>
       <c r="H63" t="n">
         <v>485171</v>
@@ -2225,7 +2225,7 @@
         <v>8.75</v>
       </c>
       <c r="G64" t="n">
-        <v>7.86258506774902</v>
+        <v>7.86258554458618</v>
       </c>
       <c r="H64" t="n">
         <v>215027</v>
@@ -2254,7 +2254,7 @@
         <v>9.1850004196167</v>
       </c>
       <c r="G65" t="n">
-        <v>8.25346851348877</v>
+        <v>8.25346755981445</v>
       </c>
       <c r="H65" t="n">
         <v>239997</v>
@@ -2312,7 +2312,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G67" t="n">
-        <v>7.70982599258423</v>
+        <v>7.70982646942139</v>
       </c>
       <c r="H67" t="n">
         <v>139521</v>
@@ -2341,7 +2341,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G68" t="n">
-        <v>8.03331565856934</v>
+        <v>8.03331470489502</v>
       </c>
       <c r="H68" t="n">
         <v>139296</v>
@@ -2370,7 +2370,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G69" t="n">
-        <v>7.95244407653809</v>
+        <v>7.95244312286377</v>
       </c>
       <c r="H69" t="n">
         <v>230882</v>
@@ -2399,7 +2399,7 @@
         <v>7.875</v>
       </c>
       <c r="G70" t="n">
-        <v>7.07632684707642</v>
+        <v>7.07632732391357</v>
       </c>
       <c r="H70" t="n">
         <v>381529</v>
@@ -2457,7 +2457,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G72" t="n">
-        <v>7.42228031158447</v>
+        <v>7.42228078842163</v>
       </c>
       <c r="H72" t="n">
         <v>235581</v>
@@ -2515,7 +2515,7 @@
         <v>8.3149995803833</v>
       </c>
       <c r="G74" t="n">
-        <v>7.47170162200928</v>
+        <v>7.47170209884644</v>
       </c>
       <c r="H74" t="n">
         <v>89965</v>
@@ -2544,7 +2544,7 @@
         <v>8.78499984741211</v>
       </c>
       <c r="G75" t="n">
-        <v>7.89403533935547</v>
+        <v>7.89403581619263</v>
       </c>
       <c r="H75" t="n">
         <v>220029</v>
@@ -2573,7 +2573,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G76" t="n">
-        <v>8.66232299804688</v>
+        <v>8.66232395172119</v>
       </c>
       <c r="H76" t="n">
         <v>544195</v>
@@ -2631,7 +2631,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G78" t="n">
-        <v>9.23741340637207</v>
+        <v>9.23741436004639</v>
       </c>
       <c r="H78" t="n">
         <v>643900</v>
@@ -2805,7 +2805,7 @@
         <v>9.48499965667725</v>
       </c>
       <c r="G84" t="n">
-        <v>8.52304267883301</v>
+        <v>8.52304172515869</v>
       </c>
       <c r="H84" t="n">
         <v>211192</v>
@@ -2834,7 +2834,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G85" t="n">
-        <v>8.6443510055542</v>
+        <v>8.64435195922852</v>
       </c>
       <c r="H85" t="n">
         <v>93670</v>
@@ -2863,7 +2863,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G86" t="n">
-        <v>8.55898571014404</v>
+        <v>8.55898475646973</v>
       </c>
       <c r="H86" t="n">
         <v>136560</v>
@@ -2921,7 +2921,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G88" t="n">
-        <v>8.80609607696533</v>
+        <v>8.80609512329102</v>
       </c>
       <c r="H88" t="n">
         <v>104006</v>
@@ -2950,7 +2950,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G89" t="n">
-        <v>8.50057792663574</v>
+        <v>8.50057697296143</v>
       </c>
       <c r="H89" t="n">
         <v>95717</v>
@@ -2979,7 +2979,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G90" t="n">
-        <v>8.55898571014404</v>
+        <v>8.55898475646973</v>
       </c>
       <c r="H90" t="n">
         <v>75199</v>
@@ -3066,7 +3066,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G93" t="n">
-        <v>8.50057792663574</v>
+        <v>8.50057697296143</v>
       </c>
       <c r="H93" t="n">
         <v>181323</v>
@@ -3211,7 +3211,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G98" t="n">
-        <v>8.62637901306152</v>
+        <v>8.62637996673584</v>
       </c>
       <c r="H98" t="n">
         <v>131848</v>
@@ -3240,7 +3240,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G99" t="n">
-        <v>8.45564842224121</v>
+        <v>8.45564746856689</v>
       </c>
       <c r="H99" t="n">
         <v>126252</v>
@@ -3269,7 +3269,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G100" t="n">
-        <v>8.80609607696533</v>
+        <v>8.80609512329102</v>
       </c>
       <c r="H100" t="n">
         <v>249000</v>
@@ -3327,7 +3327,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G102" t="n">
-        <v>8.59043598175049</v>
+        <v>8.5904369354248</v>
       </c>
       <c r="H102" t="n">
         <v>81506</v>
@@ -3414,7 +3414,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G105" t="n">
-        <v>8.55898571014404</v>
+        <v>8.55898475646973</v>
       </c>
       <c r="H105" t="n">
         <v>167622</v>
@@ -3501,7 +3501,7 @@
         <v>9.53499984741211</v>
       </c>
       <c r="G108" t="n">
-        <v>8.56797027587891</v>
+        <v>8.56797218322754</v>
       </c>
       <c r="H108" t="n">
         <v>345401</v>
@@ -3559,7 +3559,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G110" t="n">
-        <v>7.89852857589722</v>
+        <v>7.89852905273438</v>
       </c>
       <c r="H110" t="n">
         <v>136469</v>
@@ -3617,7 +3617,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G112" t="n">
-        <v>8.10520362854004</v>
+        <v>8.10520267486572</v>
       </c>
       <c r="H112" t="n">
         <v>245680</v>
@@ -3646,7 +3646,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G113" t="n">
-        <v>7.99737215042114</v>
+        <v>7.99737119674683</v>
       </c>
       <c r="H113" t="n">
         <v>164165</v>
@@ -3733,7 +3733,7 @@
         <v>9.02499961853027</v>
       </c>
       <c r="G116" t="n">
-        <v>8.10969352722168</v>
+        <v>8.109694480896</v>
       </c>
       <c r="H116" t="n">
         <v>88735</v>
@@ -3762,7 +3762,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G117" t="n">
-        <v>8.32086181640625</v>
+        <v>8.32086277008057</v>
       </c>
       <c r="H117" t="n">
         <v>146034</v>
@@ -3791,7 +3791,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G118" t="n">
-        <v>8.54550838470459</v>
+        <v>8.54550647735596</v>
       </c>
       <c r="H118" t="n">
         <v>395701</v>
@@ -3820,7 +3820,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G119" t="n">
-        <v>8.62637901306152</v>
+        <v>8.62637996673584</v>
       </c>
       <c r="H119" t="n">
         <v>249483</v>
@@ -3849,7 +3849,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>8.80609607696533</v>
+        <v>8.80609512329102</v>
       </c>
       <c r="H120" t="n">
         <v>269484</v>
@@ -3936,7 +3936,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G123" t="n">
-        <v>8.96334648132324</v>
+        <v>8.96334838867188</v>
       </c>
       <c r="H123" t="n">
         <v>150460</v>
@@ -3965,7 +3965,7 @@
         <v>9.78499984741211</v>
       </c>
       <c r="G124" t="n">
-        <v>8.91777896881104</v>
+        <v>8.91777801513672</v>
       </c>
       <c r="H124" t="n">
         <v>154912</v>
@@ -3994,7 +3994,7 @@
         <v>9.82499980926514</v>
       </c>
       <c r="G125" t="n">
-        <v>8.95423221588135</v>
+        <v>8.95423316955566</v>
       </c>
       <c r="H125" t="n">
         <v>143405</v>
@@ -4110,7 +4110,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G129" t="n">
-        <v>9.51472759246826</v>
+        <v>9.51472663879395</v>
       </c>
       <c r="H129" t="n">
         <v>242971</v>
@@ -4139,7 +4139,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G130" t="n">
-        <v>9.35068225860596</v>
+        <v>9.35068035125732</v>
       </c>
       <c r="H130" t="n">
         <v>2902048</v>
@@ -4226,7 +4226,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G133" t="n">
-        <v>9.3051118850708</v>
+        <v>9.30511093139648</v>
       </c>
       <c r="H133" t="n">
         <v>80187</v>
@@ -4284,7 +4284,7 @@
         <v>10.25</v>
       </c>
       <c r="G135" t="n">
-        <v>9.34156703948975</v>
+        <v>9.34156608581543</v>
       </c>
       <c r="H135" t="n">
         <v>52292</v>
@@ -4400,7 +4400,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G139" t="n">
-        <v>8.52133178710938</v>
+        <v>8.52133274078369</v>
       </c>
       <c r="H139" t="n">
         <v>53406</v>
@@ -4458,7 +4458,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G141" t="n">
-        <v>7.83780288696289</v>
+        <v>7.83780241012573</v>
       </c>
       <c r="H141" t="n">
         <v>132472</v>
@@ -4487,7 +4487,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G142" t="n">
-        <v>7.61907196044922</v>
+        <v>7.61907243728638</v>
       </c>
       <c r="H142" t="n">
         <v>67512</v>
@@ -4574,7 +4574,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G145" t="n">
-        <v>7.47325372695923</v>
+        <v>7.47325325012207</v>
       </c>
       <c r="H145" t="n">
         <v>33799</v>
@@ -4748,7 +4748,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G151" t="n">
-        <v>7.0266809463501</v>
+        <v>7.02668142318726</v>
       </c>
       <c r="H151" t="n">
         <v>83909</v>
@@ -4777,7 +4777,7 @@
         <v>7.81500005722046</v>
       </c>
       <c r="G152" t="n">
-        <v>7.12237548828125</v>
+        <v>7.12237501144409</v>
       </c>
       <c r="H152" t="n">
         <v>173417</v>
@@ -4864,7 +4864,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G155" t="n">
-        <v>6.74415588378906</v>
+        <v>6.7441554069519</v>
       </c>
       <c r="H155" t="n">
         <v>105692</v>
@@ -5038,7 +5038,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G161" t="n">
-        <v>6.64846181869507</v>
+        <v>6.64846134185791</v>
       </c>
       <c r="H161" t="n">
         <v>62300</v>
@@ -5067,7 +5067,7 @@
         <v>7.05499982833862</v>
       </c>
       <c r="G162" t="n">
-        <v>6.42973184585571</v>
+        <v>6.42973136901855</v>
       </c>
       <c r="H162" t="n">
         <v>80746</v>
@@ -5270,7 +5270,7 @@
         <v>7.72499990463257</v>
       </c>
       <c r="G169" t="n">
-        <v>7.04035139083862</v>
+        <v>7.04035186767578</v>
       </c>
       <c r="H169" t="n">
         <v>97576</v>
@@ -5299,7 +5299,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G170" t="n">
-        <v>6.74415588378906</v>
+        <v>6.7441554069519</v>
       </c>
       <c r="H170" t="n">
         <v>54127</v>
@@ -5386,7 +5386,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G173" t="n">
-        <v>7.38211631774902</v>
+        <v>7.38211679458618</v>
       </c>
       <c r="H173" t="n">
         <v>117230</v>
@@ -5415,7 +5415,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G174" t="n">
-        <v>7.47325372695923</v>
+        <v>7.47325325012207</v>
       </c>
       <c r="H174" t="n">
         <v>32018</v>
@@ -5444,7 +5444,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G175" t="n">
-        <v>7.61907196044922</v>
+        <v>7.61907243728638</v>
       </c>
       <c r="H175" t="n">
         <v>67391</v>
@@ -5473,7 +5473,7 @@
         <v>8.20499992370605</v>
       </c>
       <c r="G176" t="n">
-        <v>7.4778094291687</v>
+        <v>7.47780990600586</v>
       </c>
       <c r="H176" t="n">
         <v>152702</v>
@@ -5502,7 +5502,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G177" t="n">
-        <v>7.46413898468018</v>
+        <v>7.46413946151733</v>
       </c>
       <c r="H177" t="n">
         <v>103642</v>
@@ -5560,7 +5560,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G179" t="n">
-        <v>7.33199024200439</v>
+        <v>7.33199071884155</v>
       </c>
       <c r="H179" t="n">
         <v>88870</v>
@@ -5589,7 +5589,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G180" t="n">
-        <v>7.24996662139893</v>
+        <v>7.24996709823608</v>
       </c>
       <c r="H180" t="n">
         <v>63885</v>
@@ -5618,7 +5618,7 @@
         <v>8</v>
       </c>
       <c r="G181" t="n">
-        <v>7.29097890853882</v>
+        <v>7.29097938537598</v>
       </c>
       <c r="H181" t="n">
         <v>44729</v>
@@ -5647,7 +5647,7 @@
         <v>8</v>
       </c>
       <c r="G182" t="n">
-        <v>7.29097890853882</v>
+        <v>7.29097938537598</v>
       </c>
       <c r="H182" t="n">
         <v>68137</v>
@@ -5676,7 +5676,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G183" t="n">
-        <v>7.37300252914429</v>
+        <v>7.37300205230713</v>
       </c>
       <c r="H183" t="n">
         <v>62938</v>
@@ -5705,7 +5705,7 @@
         <v>8</v>
       </c>
       <c r="G184" t="n">
-        <v>7.29097890853882</v>
+        <v>7.29097938537598</v>
       </c>
       <c r="H184" t="n">
         <v>53674</v>
@@ -5734,7 +5734,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G185" t="n">
-        <v>7.05402231216431</v>
+        <v>7.05402183532715</v>
       </c>
       <c r="H185" t="n">
         <v>89502</v>
@@ -5763,7 +5763,7 @@
         <v>8</v>
       </c>
       <c r="G186" t="n">
-        <v>7.29097890853882</v>
+        <v>7.29097938537598</v>
       </c>
       <c r="H186" t="n">
         <v>98582</v>
@@ -5821,7 +5821,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G188" t="n">
-        <v>7.10870504379272</v>
+        <v>7.10870456695557</v>
       </c>
       <c r="H188" t="n">
         <v>92732</v>
@@ -5879,7 +5879,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G190" t="n">
-        <v>7.1178183555603</v>
+        <v>7.11781787872314</v>
       </c>
       <c r="H190" t="n">
         <v>29579</v>
@@ -6111,7 +6111,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G198" t="n">
-        <v>6.56188106536865</v>
+        <v>6.56188058853149</v>
       </c>
       <c r="H198" t="n">
         <v>52394</v>
@@ -6169,7 +6169,7 @@
         <v>7.0149998664856</v>
       </c>
       <c r="G200" t="n">
-        <v>6.39327764511108</v>
+        <v>6.39327716827393</v>
       </c>
       <c r="H200" t="n">
         <v>115529</v>
@@ -6198,7 +6198,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G201" t="n">
-        <v>6.6302342414856</v>
+        <v>6.63023376464844</v>
       </c>
       <c r="H201" t="n">
         <v>127295</v>
@@ -6227,7 +6227,7 @@
         <v>7.52500009536743</v>
       </c>
       <c r="G202" t="n">
-        <v>6.85807704925537</v>
+        <v>6.85807657241821</v>
       </c>
       <c r="H202" t="n">
         <v>80911</v>
@@ -6256,7 +6256,7 @@
         <v>7.75</v>
       </c>
       <c r="G203" t="n">
-        <v>7.06313562393188</v>
+        <v>7.06313610076904</v>
       </c>
       <c r="H203" t="n">
         <v>74023</v>
@@ -6314,7 +6314,7 @@
         <v>7.33500003814697</v>
       </c>
       <c r="G205" t="n">
-        <v>6.68491649627686</v>
+        <v>6.6849160194397</v>
       </c>
       <c r="H205" t="n">
         <v>69663</v>
@@ -6343,7 +6343,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G206" t="n">
-        <v>6.69858646392822</v>
+        <v>6.69858694076538</v>
       </c>
       <c r="H206" t="n">
         <v>115365</v>
@@ -6401,7 +6401,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G208" t="n">
-        <v>7.55527591705322</v>
+        <v>7.5552773475647</v>
       </c>
       <c r="H208" t="n">
         <v>323484</v>
@@ -6488,7 +6488,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G211" t="n">
-        <v>7.70565366744995</v>
+        <v>7.70565319061279</v>
       </c>
       <c r="H211" t="n">
         <v>238638</v>
@@ -6517,7 +6517,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G212" t="n">
-        <v>7.75577974319458</v>
+        <v>7.75577878952026</v>
       </c>
       <c r="H212" t="n">
         <v>149734</v>
@@ -6546,7 +6546,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G213" t="n">
-        <v>7.82868909835815</v>
+        <v>7.828688621521</v>
       </c>
       <c r="H213" t="n">
         <v>267292</v>
@@ -6575,7 +6575,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G214" t="n">
-        <v>7.82868909835815</v>
+        <v>7.828688621521</v>
       </c>
       <c r="H214" t="n">
         <v>252704</v>
@@ -6662,7 +6662,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G217" t="n">
-        <v>7.93805408477783</v>
+        <v>7.93805265426636</v>
       </c>
       <c r="H217" t="n">
         <v>247020</v>
@@ -6691,7 +6691,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G218" t="n">
-        <v>8.02007579803467</v>
+        <v>8.0200777053833</v>
       </c>
       <c r="H218" t="n">
         <v>179237</v>
@@ -6778,7 +6778,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G221" t="n">
-        <v>8.19323635101318</v>
+        <v>8.19323825836182</v>
       </c>
       <c r="H221" t="n">
         <v>194602</v>
@@ -6836,7 +6836,7 @@
         <v>8.86499977111816</v>
       </c>
       <c r="G223" t="n">
-        <v>8.07931613922119</v>
+        <v>8.07931518554688</v>
       </c>
       <c r="H223" t="n">
         <v>111621</v>
@@ -6923,7 +6923,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G226" t="n">
-        <v>7.65552806854248</v>
+        <v>7.65552711486816</v>
       </c>
       <c r="H226" t="n">
         <v>242848</v>
@@ -7010,7 +7010,7 @@
         <v>8.60499954223633</v>
       </c>
       <c r="G229" t="n">
-        <v>7.84235858917236</v>
+        <v>7.84235906600952</v>
       </c>
       <c r="H229" t="n">
         <v>228869</v>
@@ -7039,7 +7039,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G230" t="n">
-        <v>7.59173202514648</v>
+        <v>7.59173154830933</v>
       </c>
       <c r="H230" t="n">
         <v>175936</v>
@@ -7068,7 +7068,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>7.48236656188965</v>
+        <v>7.48236751556396</v>
       </c>
       <c r="H231" t="n">
         <v>150112</v>
@@ -7126,7 +7126,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G233" t="n">
-        <v>7.60084629058838</v>
+        <v>7.60084581375122</v>
       </c>
       <c r="H233" t="n">
         <v>108751</v>
@@ -7155,7 +7155,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G234" t="n">
-        <v>7.85602951049805</v>
+        <v>7.85602998733521</v>
       </c>
       <c r="H234" t="n">
         <v>185968</v>
@@ -7184,7 +7184,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G235" t="n">
-        <v>7.81957483291626</v>
+        <v>7.8195743560791</v>
       </c>
       <c r="H235" t="n">
         <v>126055</v>
@@ -7213,7 +7213,7 @@
         <v>8.59500026702881</v>
       </c>
       <c r="G236" t="n">
-        <v>7.83324670791626</v>
+        <v>7.83324575424194</v>
       </c>
       <c r="H236" t="n">
         <v>75722</v>
@@ -7242,7 +7242,7 @@
         <v>8.63500022888184</v>
       </c>
       <c r="G237" t="n">
-        <v>7.86970043182373</v>
+        <v>7.86970186233521</v>
       </c>
       <c r="H237" t="n">
         <v>68684</v>
@@ -7271,7 +7271,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G238" t="n">
-        <v>7.86514282226562</v>
+        <v>7.86514377593994</v>
       </c>
       <c r="H238" t="n">
         <v>98511</v>
@@ -7329,7 +7329,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G240" t="n">
-        <v>7.61907196044922</v>
+        <v>7.61907243728638</v>
       </c>
       <c r="H240" t="n">
         <v>242480</v>
@@ -7387,7 +7387,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G242" t="n">
-        <v>7.20895576477051</v>
+        <v>7.20895528793335</v>
       </c>
       <c r="H242" t="n">
         <v>428150</v>
@@ -7474,7 +7474,7 @@
         <v>8.15499973297119</v>
       </c>
       <c r="G245" t="n">
-        <v>7.43224096298218</v>
+        <v>7.43224143981934</v>
       </c>
       <c r="H245" t="n">
         <v>95884</v>
@@ -7532,7 +7532,7 @@
         <v>8.5649995803833</v>
       </c>
       <c r="G247" t="n">
-        <v>7.80590391159058</v>
+        <v>7.80590343475342</v>
       </c>
       <c r="H247" t="n">
         <v>190341</v>
@@ -7590,7 +7590,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G249" t="n">
-        <v>7.82868909835815</v>
+        <v>7.828688621521</v>
       </c>
       <c r="H249" t="n">
         <v>109003</v>
@@ -7619,7 +7619,7 @@
         <v>8.44499969482422</v>
       </c>
       <c r="G250" t="n">
-        <v>7.6965389251709</v>
+        <v>7.69653940200806</v>
       </c>
       <c r="H250" t="n">
         <v>65821</v>
@@ -7764,7 +7764,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G255" t="n">
-        <v>8.06564617156982</v>
+        <v>8.06564521789551</v>
       </c>
       <c r="H255" t="n">
         <v>80541</v>
@@ -7822,7 +7822,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G257" t="n">
-        <v>8.38006782531738</v>
+        <v>8.3800687789917</v>
       </c>
       <c r="H257" t="n">
         <v>166742</v>
@@ -7909,7 +7909,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G260" t="n">
-        <v>8.8767671585083</v>
+        <v>8.87676620483398</v>
       </c>
       <c r="H260" t="n">
         <v>299785</v>
@@ -7938,7 +7938,7 @@
         <v>9.50500011444092</v>
       </c>
       <c r="G261" t="n">
-        <v>8.66259384155273</v>
+        <v>8.66259574890137</v>
       </c>
       <c r="H261" t="n">
         <v>198672</v>
@@ -7996,7 +7996,7 @@
         <v>9.5</v>
       </c>
       <c r="G263" t="n">
-        <v>8.65803623199463</v>
+        <v>8.65803718566895</v>
       </c>
       <c r="H263" t="n">
         <v>120885</v>
@@ -8025,7 +8025,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G264" t="n">
-        <v>8.5669002532959</v>
+        <v>8.56689929962158</v>
       </c>
       <c r="H264" t="n">
         <v>68545</v>
@@ -8141,7 +8141,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G268" t="n">
-        <v>8.42108154296875</v>
+        <v>8.42108058929443</v>
       </c>
       <c r="H268" t="n">
         <v>38362</v>
@@ -8170,7 +8170,7 @@
         <v>9.5</v>
       </c>
       <c r="G269" t="n">
-        <v>8.65803623199463</v>
+        <v>8.65803718566895</v>
       </c>
       <c r="H269" t="n">
         <v>49713</v>
@@ -8257,7 +8257,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G272" t="n">
-        <v>8.46665000915527</v>
+        <v>8.46664905548096</v>
       </c>
       <c r="H272" t="n">
         <v>131322</v>
@@ -8344,7 +8344,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G275" t="n">
-        <v>8.46665000915527</v>
+        <v>8.46664905548096</v>
       </c>
       <c r="H275" t="n">
         <v>56044</v>
@@ -8402,7 +8402,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G277" t="n">
-        <v>8.52133178710938</v>
+        <v>8.52133274078369</v>
       </c>
       <c r="H277" t="n">
         <v>22128</v>
@@ -8431,7 +8431,7 @@
         <v>9.66499996185303</v>
       </c>
       <c r="G278" t="n">
-        <v>8.80841445922852</v>
+        <v>8.8084135055542</v>
       </c>
       <c r="H278" t="n">
         <v>41058</v>
@@ -8547,7 +8547,7 @@
         <v>9.625</v>
       </c>
       <c r="G282" t="n">
-        <v>8.77195930480957</v>
+        <v>8.77195835113525</v>
       </c>
       <c r="H282" t="n">
         <v>30701</v>
@@ -8663,7 +8663,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G286" t="n">
-        <v>9.17752075195312</v>
+        <v>9.17751884460449</v>
       </c>
       <c r="H286" t="n">
         <v>123243</v>
@@ -8837,7 +8837,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G292" t="n">
-        <v>8.5669002532959</v>
+        <v>8.56689929962158</v>
       </c>
       <c r="H292" t="n">
         <v>119313</v>
@@ -8866,7 +8866,7 @@
         <v>9.375</v>
       </c>
       <c r="G293" t="n">
-        <v>8.54411506652832</v>
+        <v>8.54411602020264</v>
       </c>
       <c r="H293" t="n">
         <v>129641</v>
@@ -8895,7 +8895,7 @@
         <v>9.5</v>
       </c>
       <c r="G294" t="n">
-        <v>8.65803623199463</v>
+        <v>8.65803718566895</v>
       </c>
       <c r="H294" t="n">
         <v>186325</v>
@@ -8982,7 +8982,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G297" t="n">
-        <v>8.8220853805542</v>
+        <v>8.82208442687988</v>
       </c>
       <c r="H297" t="n">
         <v>184820</v>
@@ -9069,7 +9069,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G300" t="n">
-        <v>8.99524593353271</v>
+        <v>8.9952449798584</v>
       </c>
       <c r="H300" t="n">
         <v>84628</v>
@@ -9098,7 +9098,7 @@
         <v>9.625</v>
       </c>
       <c r="G301" t="n">
-        <v>8.77195930480957</v>
+        <v>8.77195835113525</v>
       </c>
       <c r="H301" t="n">
         <v>62785</v>
@@ -9185,7 +9185,7 @@
         <v>9.61499977111816</v>
       </c>
       <c r="G304" t="n">
-        <v>8.76284599304199</v>
+        <v>8.76284408569336</v>
       </c>
       <c r="H304" t="n">
         <v>112583</v>
@@ -9214,7 +9214,7 @@
         <v>9.51500034332275</v>
       </c>
       <c r="G305" t="n">
-        <v>8.67170715332031</v>
+        <v>8.67170810699463</v>
       </c>
       <c r="H305" t="n">
         <v>74235</v>
@@ -9272,7 +9272,7 @@
         <v>9.66499996185303</v>
       </c>
       <c r="G307" t="n">
-        <v>8.80841445922852</v>
+        <v>8.8084135055542</v>
       </c>
       <c r="H307" t="n">
         <v>88814</v>
@@ -9301,7 +9301,7 @@
         <v>9.61499977111816</v>
       </c>
       <c r="G308" t="n">
-        <v>8.76284599304199</v>
+        <v>8.76284408569336</v>
       </c>
       <c r="H308" t="n">
         <v>97456</v>
@@ -9388,7 +9388,7 @@
         <v>9.30500030517578</v>
       </c>
       <c r="G311" t="n">
-        <v>8.48032093048096</v>
+        <v>8.48031997680664</v>
       </c>
       <c r="H311" t="n">
         <v>88710</v>
@@ -9446,7 +9446,7 @@
         <v>9.86499977111816</v>
       </c>
       <c r="G313" t="n">
-        <v>8.99068832397461</v>
+        <v>8.99068737030029</v>
       </c>
       <c r="H313" t="n">
         <v>95525</v>
@@ -9504,7 +9504,7 @@
         <v>9.5649995803833</v>
       </c>
       <c r="G315" t="n">
-        <v>8.71727561950684</v>
+        <v>8.71727657318115</v>
       </c>
       <c r="H315" t="n">
         <v>125012</v>
@@ -9591,7 +9591,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G318" t="n">
-        <v>8.32994270324707</v>
+        <v>8.32994365692139</v>
       </c>
       <c r="H318" t="n">
         <v>82760</v>
@@ -9620,7 +9620,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G319" t="n">
-        <v>8.10210037231445</v>
+        <v>8.10210132598877</v>
       </c>
       <c r="H319" t="n">
         <v>152972</v>
@@ -9649,7 +9649,7 @@
         <v>9.01500034332275</v>
       </c>
       <c r="G320" t="n">
-        <v>8.21602153778076</v>
+        <v>8.21602249145508</v>
       </c>
       <c r="H320" t="n">
         <v>69302</v>
@@ -9678,7 +9678,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G321" t="n">
-        <v>8.26159000396729</v>
+        <v>8.26158905029297</v>
       </c>
       <c r="H321" t="n">
         <v>151215</v>
@@ -9736,7 +9736,7 @@
         <v>9.125</v>
       </c>
       <c r="G323" t="n">
-        <v>8.31627178192139</v>
+        <v>8.3162727355957</v>
       </c>
       <c r="H323" t="n">
         <v>96023</v>
@@ -9765,7 +9765,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G324" t="n">
-        <v>8.23880672454834</v>
+        <v>8.23880577087402</v>
       </c>
       <c r="H324" t="n">
         <v>125245</v>
@@ -10055,7 +10055,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G334" t="n">
-        <v>8.37551116943359</v>
+        <v>8.37551212310791</v>
       </c>
       <c r="H334" t="n">
         <v>66953</v>
@@ -10084,7 +10084,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G335" t="n">
-        <v>8.48487663269043</v>
+        <v>8.48487758636475</v>
       </c>
       <c r="H335" t="n">
         <v>124173</v>
@@ -10171,7 +10171,7 @@
         <v>9.59500026702881</v>
       </c>
       <c r="G338" t="n">
-        <v>8.74461841583252</v>
+        <v>8.7446174621582</v>
       </c>
       <c r="H338" t="n">
         <v>46333</v>
@@ -10200,7 +10200,7 @@
         <v>9.36499977111816</v>
       </c>
       <c r="G339" t="n">
-        <v>8.53500175476074</v>
+        <v>8.53500080108643</v>
       </c>
       <c r="H339" t="n">
         <v>78975</v>
@@ -10258,7 +10258,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G341" t="n">
-        <v>8.42108154296875</v>
+        <v>8.42108058929443</v>
       </c>
       <c r="H341" t="n">
         <v>61904</v>
@@ -10374,7 +10374,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G345" t="n">
-        <v>8.8767671585083</v>
+        <v>8.87676620483398</v>
       </c>
       <c r="H345" t="n">
         <v>69041</v>
@@ -10577,7 +10577,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G352" t="n">
-        <v>8.86765384674072</v>
+        <v>8.86765289306641</v>
       </c>
       <c r="H352" t="n">
         <v>54316</v>
@@ -10606,7 +10606,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G353" t="n">
-        <v>8.96790409088135</v>
+        <v>8.96790313720703</v>
       </c>
       <c r="H353" t="n">
         <v>66592</v>
@@ -10635,7 +10635,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G354" t="n">
-        <v>9.02258682250977</v>
+        <v>9.02258586883545</v>
       </c>
       <c r="H354" t="n">
         <v>58371</v>
@@ -10693,7 +10693,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G356" t="n">
-        <v>9.02258682250977</v>
+        <v>9.02258586883545</v>
       </c>
       <c r="H356" t="n">
         <v>51175</v>
@@ -10722,7 +10722,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G357" t="n">
-        <v>9.16840553283691</v>
+        <v>9.16840744018555</v>
       </c>
       <c r="H357" t="n">
         <v>43978</v>
@@ -10809,7 +10809,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G360" t="n">
-        <v>9.505615234375</v>
+        <v>9.50561428070068</v>
       </c>
       <c r="H360" t="n">
         <v>54614</v>
@@ -10896,7 +10896,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G363" t="n">
-        <v>9.70611572265625</v>
+        <v>9.70611476898193</v>
       </c>
       <c r="H363" t="n">
         <v>79881</v>
@@ -10983,7 +10983,7 @@
         <v>9.83500003814697</v>
       </c>
       <c r="G366" t="n">
-        <v>8.96334743499756</v>
+        <v>8.96334838867188</v>
       </c>
       <c r="H366" t="n">
         <v>250182</v>
@@ -11157,7 +11157,7 @@
         <v>9.5</v>
       </c>
       <c r="G372" t="n">
-        <v>8.65803623199463</v>
+        <v>8.65803718566895</v>
       </c>
       <c r="H372" t="n">
         <v>99284</v>
@@ -11215,7 +11215,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G374" t="n">
-        <v>9.10460948944092</v>
+        <v>9.10461044311523</v>
       </c>
       <c r="H374" t="n">
         <v>180858</v>
@@ -11302,7 +11302,7 @@
         <v>10.0299997329712</v>
       </c>
       <c r="G377" t="n">
-        <v>9.14106369018555</v>
+        <v>9.14106464385986</v>
       </c>
       <c r="H377" t="n">
         <v>66283</v>
@@ -11331,7 +11331,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G378" t="n">
-        <v>9.09549617767334</v>
+        <v>9.09549522399902</v>
       </c>
       <c r="H378" t="n">
         <v>71656</v>
@@ -11360,7 +11360,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G379" t="n">
-        <v>9.3078784942627</v>
+        <v>9.30787754058838</v>
       </c>
       <c r="H379" t="n">
         <v>179086</v>
@@ -11476,7 +11476,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G383" t="n">
-        <v>9.6126012802124</v>
+        <v>9.61260032653809</v>
       </c>
       <c r="H383" t="n">
         <v>186379</v>
@@ -11534,7 +11534,7 @@
         <v>10.25</v>
       </c>
       <c r="G385" t="n">
-        <v>9.46485710144043</v>
+        <v>9.46485614776611</v>
       </c>
       <c r="H385" t="n">
         <v>63321</v>
@@ -11563,7 +11563,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G386" t="n">
-        <v>9.43715476989746</v>
+        <v>9.43715572357178</v>
       </c>
       <c r="H386" t="n">
         <v>588687</v>
@@ -11592,7 +11592,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G387" t="n">
-        <v>9.54796314239502</v>
+        <v>9.5479621887207</v>
       </c>
       <c r="H387" t="n">
         <v>97563</v>
@@ -11621,7 +11621,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G388" t="n">
-        <v>9.63106822967529</v>
+        <v>9.63106918334961</v>
       </c>
       <c r="H388" t="n">
         <v>137120</v>
@@ -11650,7 +11650,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G389" t="n">
-        <v>9.64030265808105</v>
+        <v>9.64030170440674</v>
       </c>
       <c r="H389" t="n">
         <v>168078</v>
@@ -11679,7 +11679,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G390" t="n">
-        <v>9.78804683685303</v>
+        <v>9.78804779052734</v>
       </c>
       <c r="H390" t="n">
         <v>146601</v>
@@ -11737,7 +11737,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G392" t="n">
-        <v>9.64030265808105</v>
+        <v>9.64030170440674</v>
       </c>
       <c r="H392" t="n">
         <v>109538</v>
@@ -11766,7 +11766,7 @@
         <v>10.5</v>
       </c>
       <c r="G393" t="n">
-        <v>9.69570732116699</v>
+        <v>9.69570636749268</v>
       </c>
       <c r="H393" t="n">
         <v>63889</v>
@@ -11795,7 +11795,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G394" t="n">
-        <v>9.84345054626465</v>
+        <v>9.84345149993896</v>
       </c>
       <c r="H394" t="n">
         <v>96545</v>
@@ -11882,7 +11882,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G397" t="n">
-        <v>9.56642913818359</v>
+        <v>9.56643104553223</v>
       </c>
       <c r="H397" t="n">
         <v>124190</v>
@@ -11911,7 +11911,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G398" t="n">
-        <v>9.42792129516602</v>
+        <v>9.4279203414917</v>
       </c>
       <c r="H398" t="n">
         <v>119704</v>
@@ -11969,7 +11969,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G400" t="n">
-        <v>9.18783569335938</v>
+        <v>9.18783664703369</v>
       </c>
       <c r="H400" t="n">
         <v>64703</v>
@@ -11998,7 +11998,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G401" t="n">
-        <v>9.04932594299316</v>
+        <v>9.04932689666748</v>
       </c>
       <c r="H401" t="n">
         <v>96905</v>
@@ -12056,7 +12056,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G403" t="n">
-        <v>8.79539108276367</v>
+        <v>8.79539012908936</v>
       </c>
       <c r="H403" t="n">
         <v>80618</v>
@@ -12114,7 +12114,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G405" t="n">
-        <v>8.58762550354004</v>
+        <v>8.58762645721436</v>
       </c>
       <c r="H405" t="n">
         <v>464509</v>
@@ -12172,7 +12172,7 @@
         <v>9.55500030517578</v>
       </c>
       <c r="G407" t="n">
-        <v>8.82309341430664</v>
+        <v>8.82309246063232</v>
       </c>
       <c r="H407" t="n">
         <v>224972</v>
@@ -12259,7 +12259,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G410" t="n">
-        <v>8.64302921295166</v>
+        <v>8.64303016662598</v>
       </c>
       <c r="H410" t="n">
         <v>151206</v>
@@ -12288,7 +12288,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G411" t="n">
-        <v>8.82771015167236</v>
+        <v>8.82771110534668</v>
       </c>
       <c r="H411" t="n">
         <v>189726</v>
@@ -12346,7 +12346,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G413" t="n">
-        <v>8.42141342163086</v>
+        <v>8.42141437530518</v>
       </c>
       <c r="H413" t="n">
         <v>96990</v>
@@ -12375,7 +12375,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G414" t="n">
-        <v>8.50452041625977</v>
+        <v>8.50451946258545</v>
       </c>
       <c r="H414" t="n">
         <v>71607</v>
@@ -12404,7 +12404,7 @@
         <v>9.21500015258789</v>
       </c>
       <c r="G415" t="n">
-        <v>8.5091381072998</v>
+        <v>8.50913715362549</v>
       </c>
       <c r="H415" t="n">
         <v>86476</v>
@@ -12491,7 +12491,7 @@
         <v>9.57499980926514</v>
       </c>
       <c r="G418" t="n">
-        <v>8.84156036376953</v>
+        <v>8.84156131744385</v>
       </c>
       <c r="H418" t="n">
         <v>93508</v>
@@ -12520,7 +12520,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G419" t="n">
-        <v>8.57839202880859</v>
+        <v>8.57839298248291</v>
       </c>
       <c r="H419" t="n">
         <v>85948</v>
@@ -12636,7 +12636,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G423" t="n">
-        <v>8.0382022857666</v>
+        <v>8.03820323944092</v>
       </c>
       <c r="H423" t="n">
         <v>208593</v>
@@ -12723,7 +12723,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G426" t="n">
-        <v>7.92277717590332</v>
+        <v>7.92277669906616</v>
       </c>
       <c r="H426" t="n">
         <v>224688</v>
@@ -12752,7 +12752,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G427" t="n">
-        <v>7.82120275497437</v>
+        <v>7.82120370864868</v>
       </c>
       <c r="H427" t="n">
         <v>315397</v>
@@ -12781,7 +12781,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G428" t="n">
-        <v>7.82120275497437</v>
+        <v>7.82120370864868</v>
       </c>
       <c r="H428" t="n">
         <v>153923</v>
@@ -12810,7 +12810,7 @@
         <v>8.46500015258789</v>
       </c>
       <c r="G429" t="n">
-        <v>7.81658744812012</v>
+        <v>7.8165864944458</v>
       </c>
       <c r="H429" t="n">
         <v>124892</v>
@@ -12868,7 +12868,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G431" t="n">
-        <v>7.81196975708008</v>
+        <v>7.81196928024292</v>
       </c>
       <c r="H431" t="n">
         <v>211938</v>
@@ -12897,7 +12897,7 @@
         <v>8.42500019073486</v>
       </c>
       <c r="G432" t="n">
-        <v>7.77965116500854</v>
+        <v>7.77965021133423</v>
       </c>
       <c r="H432" t="n">
         <v>499662</v>
@@ -12955,7 +12955,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G434" t="n">
-        <v>7.2579288482666</v>
+        <v>7.25792932510376</v>
       </c>
       <c r="H434" t="n">
         <v>435932</v>
@@ -12984,7 +12984,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G435" t="n">
-        <v>7.06401538848877</v>
+        <v>7.06401491165161</v>
       </c>
       <c r="H435" t="n">
         <v>300120</v>
@@ -13013,7 +13013,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G436" t="n">
-        <v>7.10095119476318</v>
+        <v>7.10095071792603</v>
       </c>
       <c r="H436" t="n">
         <v>185032</v>
@@ -13042,7 +13042,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G437" t="n">
-        <v>7.16558885574341</v>
+        <v>7.16558933258057</v>
       </c>
       <c r="H437" t="n">
         <v>348774</v>
@@ -13071,7 +13071,7 @@
         <v>7.72499990463257</v>
       </c>
       <c r="G438" t="n">
-        <v>7.13326930999756</v>
+        <v>7.13327026367188</v>
       </c>
       <c r="H438" t="n">
         <v>174564</v>
@@ -13158,7 +13158,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G441" t="n">
-        <v>6.90241956710815</v>
+        <v>6.90242004394531</v>
       </c>
       <c r="H441" t="n">
         <v>154999</v>
@@ -13216,7 +13216,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G443" t="n">
-        <v>6.61616516113281</v>
+        <v>6.61616563796997</v>
       </c>
       <c r="H443" t="n">
         <v>161736</v>
@@ -13245,7 +13245,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G444" t="n">
-        <v>6.61154842376709</v>
+        <v>6.61154890060425</v>
       </c>
       <c r="H444" t="n">
         <v>161687</v>
@@ -13274,7 +13274,7 @@
         <v>7.02500009536743</v>
       </c>
       <c r="G445" t="n">
-        <v>6.48688983917236</v>
+        <v>6.48688936233521</v>
       </c>
       <c r="H445" t="n">
         <v>144224</v>
@@ -13332,7 +13332,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G447" t="n">
-        <v>6.33452844619751</v>
+        <v>6.33452892303467</v>
       </c>
       <c r="H447" t="n">
         <v>231466</v>
@@ -13361,7 +13361,7 @@
         <v>7.13500022888184</v>
       </c>
       <c r="G448" t="n">
-        <v>6.588463306427</v>
+        <v>6.58846378326416</v>
       </c>
       <c r="H448" t="n">
         <v>537214</v>
@@ -13390,7 +13390,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G449" t="n">
-        <v>6.90241956710815</v>
+        <v>6.90242004394531</v>
       </c>
       <c r="H449" t="n">
         <v>615718</v>
@@ -13535,7 +13535,7 @@
         <v>7.40500020980835</v>
       </c>
       <c r="G454" t="n">
-        <v>6.83778190612793</v>
+        <v>6.83778142929077</v>
       </c>
       <c r="H454" t="n">
         <v>250172</v>
@@ -13564,7 +13564,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G455" t="n">
-        <v>6.76390933990479</v>
+        <v>6.76390981674194</v>
       </c>
       <c r="H455" t="n">
         <v>277616</v>
@@ -13593,7 +13593,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G456" t="n">
-        <v>6.76390933990479</v>
+        <v>6.76390981674194</v>
       </c>
       <c r="H456" t="n">
         <v>287013</v>
@@ -13651,7 +13651,7 @@
         <v>7.09499979019165</v>
       </c>
       <c r="G458" t="n">
-        <v>6.55152750015259</v>
+        <v>6.55152702331543</v>
       </c>
       <c r="H458" t="n">
         <v>694126</v>
@@ -13738,7 +13738,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G461" t="n">
-        <v>6.37146472930908</v>
+        <v>6.37146425247192</v>
       </c>
       <c r="H461" t="n">
         <v>296679</v>
@@ -13767,7 +13767,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G462" t="n">
-        <v>6.37146472930908</v>
+        <v>6.37146425247192</v>
       </c>
       <c r="H462" t="n">
         <v>4069866</v>
@@ -13825,7 +13825,7 @@
         <v>6.69500017166138</v>
       </c>
       <c r="G464" t="n">
-        <v>6.18216800689697</v>
+        <v>6.18216753005981</v>
       </c>
       <c r="H464" t="n">
         <v>494430</v>
@@ -13854,7 +13854,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G465" t="n">
-        <v>6.18678379058838</v>
+        <v>6.18678426742554</v>
       </c>
       <c r="H465" t="n">
         <v>200486</v>
@@ -13883,7 +13883,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G466" t="n">
-        <v>5.80819034576416</v>
+        <v>5.808189868927</v>
       </c>
       <c r="H466" t="n">
         <v>501243</v>
@@ -14144,7 +14144,7 @@
         <v>5.82499980926514</v>
       </c>
       <c r="G475" t="n">
-        <v>5.37880849838257</v>
+        <v>5.37880897521973</v>
       </c>
       <c r="H475" t="n">
         <v>758444</v>
@@ -14260,7 +14260,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G479" t="n">
-        <v>5.70661544799805</v>
+        <v>5.70661592483521</v>
       </c>
       <c r="H479" t="n">
         <v>248086</v>
@@ -14289,7 +14289,7 @@
         <v>5.9850001335144</v>
       </c>
       <c r="G480" t="n">
-        <v>5.52655267715454</v>
+        <v>5.5265531539917</v>
       </c>
       <c r="H480" t="n">
         <v>491648</v>
@@ -14434,7 +14434,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G485" t="n">
-        <v>5.17566108703613</v>
+        <v>5.17566013336182</v>
       </c>
       <c r="H485" t="n">
         <v>433667</v>
@@ -14463,7 +14463,7 @@
         <v>5.75</v>
       </c>
       <c r="G486" t="n">
-        <v>5.30955410003662</v>
+        <v>5.30955362319946</v>
       </c>
       <c r="H486" t="n">
         <v>311135</v>
@@ -14492,7 +14492,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G487" t="n">
-        <v>5.06023597717285</v>
+        <v>5.06023550033569</v>
       </c>
       <c r="H487" t="n">
         <v>544541</v>
@@ -14579,7 +14579,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G490" t="n">
-        <v>4.80168342590332</v>
+        <v>4.80168294906616</v>
       </c>
       <c r="H490" t="n">
         <v>392471</v>
@@ -14695,7 +14695,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G494" t="n">
-        <v>4.88478946685791</v>
+        <v>4.88478899002075</v>
       </c>
       <c r="H494" t="n">
         <v>111362</v>
@@ -14724,7 +14724,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G495" t="n">
-        <v>4.88940668106079</v>
+        <v>4.88940620422363</v>
       </c>
       <c r="H495" t="n">
         <v>133883</v>
@@ -14869,7 +14869,7 @@
         <v>5.69500017166138</v>
       </c>
       <c r="G500" t="n">
-        <v>5.25876712799072</v>
+        <v>5.25876665115356</v>
       </c>
       <c r="H500" t="n">
         <v>671518</v>
@@ -15101,7 +15101,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G508" t="n">
-        <v>5.41112756729126</v>
+        <v>5.41112804412842</v>
       </c>
       <c r="H508" t="n">
         <v>222944</v>
@@ -15130,7 +15130,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G509" t="n">
-        <v>5.24491500854492</v>
+        <v>5.24491548538208</v>
       </c>
       <c r="H509" t="n">
         <v>138219</v>
@@ -15159,7 +15159,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G510" t="n">
-        <v>5.21259641647339</v>
+        <v>5.21259689331055</v>
       </c>
       <c r="H510" t="n">
         <v>110937</v>
@@ -15246,7 +15246,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G513" t="n">
-        <v>5.21259641647339</v>
+        <v>5.21259689331055</v>
       </c>
       <c r="H513" t="n">
         <v>215173</v>
@@ -15304,7 +15304,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G515" t="n">
-        <v>5.11563968658447</v>
+        <v>5.11563920974731</v>
       </c>
       <c r="H515" t="n">
         <v>481344</v>
@@ -15391,7 +15391,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G518" t="n">
-        <v>5.24491500854492</v>
+        <v>5.24491548538208</v>
       </c>
       <c r="H518" t="n">
         <v>260768</v>
@@ -15565,7 +15565,7 @@
         <v>5.5</v>
       </c>
       <c r="G524" t="n">
-        <v>5.07870388031006</v>
+        <v>5.0787034034729</v>
       </c>
       <c r="H524" t="n">
         <v>365475</v>
@@ -15652,7 +15652,7 @@
         <v>6.03499984741211</v>
       </c>
       <c r="G527" t="n">
-        <v>5.57272291183472</v>
+        <v>5.57272243499756</v>
       </c>
       <c r="H527" t="n">
         <v>477831</v>
@@ -15826,7 +15826,7 @@
         <v>6.40500020980835</v>
       </c>
       <c r="G533" t="n">
-        <v>5.91438150405884</v>
+        <v>5.91438102722168</v>
       </c>
       <c r="H533" t="n">
         <v>366529</v>
@@ -15884,7 +15884,7 @@
         <v>6.2649998664856</v>
       </c>
       <c r="G535" t="n">
-        <v>5.78510475158691</v>
+        <v>5.78510522842407</v>
       </c>
       <c r="H535" t="n">
         <v>171909</v>
@@ -16000,7 +16000,7 @@
         <v>6.38500022888184</v>
       </c>
       <c r="G539" t="n">
-        <v>5.89591312408447</v>
+        <v>5.89591360092163</v>
       </c>
       <c r="H539" t="n">
         <v>946632</v>
@@ -16029,7 +16029,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G540" t="n">
-        <v>6.03904056549072</v>
+        <v>6.03904008865356</v>
       </c>
       <c r="H540" t="n">
         <v>416492</v>
@@ -16058,7 +16058,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G541" t="n">
-        <v>6.05750846862793</v>
+        <v>6.05750799179077</v>
       </c>
       <c r="H541" t="n">
         <v>374625</v>
@@ -16087,7 +16087,7 @@
         <v>6.57499980926514</v>
       </c>
       <c r="G542" t="n">
-        <v>6.0713586807251</v>
+        <v>6.07135915756226</v>
       </c>
       <c r="H542" t="n">
         <v>267523</v>
@@ -16145,7 +16145,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G544" t="n">
-        <v>5.86359405517578</v>
+        <v>5.86359357833862</v>
       </c>
       <c r="H544" t="n">
         <v>307396</v>
@@ -16348,7 +16348,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G551" t="n">
-        <v>5.70661544799805</v>
+        <v>5.70661592483521</v>
       </c>
       <c r="H551" t="n">
         <v>159509</v>
@@ -16377,7 +16377,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G552" t="n">
-        <v>5.70661544799805</v>
+        <v>5.70661592483521</v>
       </c>
       <c r="H552" t="n">
         <v>128983</v>
@@ -16435,7 +16435,7 @@
         <v>6.29500007629395</v>
       </c>
       <c r="G554" t="n">
-        <v>5.81280660629272</v>
+        <v>5.81280755996704</v>
       </c>
       <c r="H554" t="n">
         <v>151233</v>
@@ -16551,7 +16551,7 @@
         <v>6.0149998664856</v>
       </c>
       <c r="G558" t="n">
-        <v>5.55425453186035</v>
+        <v>5.55425500869751</v>
       </c>
       <c r="H558" t="n">
         <v>206810</v>
@@ -16725,7 +16725,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G564" t="n">
-        <v>5.41112756729126</v>
+        <v>5.41112804412842</v>
       </c>
       <c r="H564" t="n">
         <v>104231</v>
@@ -16928,7 +16928,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G571" t="n">
-        <v>5.17566108703613</v>
+        <v>5.17566013336182</v>
       </c>
       <c r="H571" t="n">
         <v>188694</v>
@@ -17102,7 +17102,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G577" t="n">
-        <v>5.06023597717285</v>
+        <v>5.06023550033569</v>
       </c>
       <c r="H577" t="n">
         <v>490731</v>
@@ -17160,7 +17160,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G579" t="n">
-        <v>5.07408618927002</v>
+        <v>5.07408666610718</v>
       </c>
       <c r="H579" t="n">
         <v>256005</v>
@@ -17247,7 +17247,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G582" t="n">
-        <v>5.30031967163086</v>
+        <v>5.3003191947937</v>
       </c>
       <c r="H582" t="n">
         <v>1080928</v>
@@ -17305,7 +17305,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G584" t="n">
-        <v>5.374192237854</v>
+        <v>5.37419176101685</v>
       </c>
       <c r="H584" t="n">
         <v>450011</v>
@@ -17334,7 +17334,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G585" t="n">
-        <v>5.47576522827148</v>
+        <v>5.47576570510864</v>
       </c>
       <c r="H585" t="n">
         <v>310197</v>
@@ -17392,7 +17392,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G587" t="n">
-        <v>5.5773401260376</v>
+        <v>5.57733917236328</v>
       </c>
       <c r="H587" t="n">
         <v>394516</v>
@@ -17508,7 +17508,7 @@
         <v>5.53499984741211</v>
       </c>
       <c r="G591" t="n">
-        <v>5.11102247238159</v>
+        <v>5.11102199554443</v>
       </c>
       <c r="H591" t="n">
         <v>899330</v>
@@ -17595,7 +17595,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G594" t="n">
-        <v>5.05100154876709</v>
+        <v>5.05100107192993</v>
       </c>
       <c r="H594" t="n">
         <v>677677</v>
@@ -17624,7 +17624,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>4.92172527313232</v>
+        <v>4.92172574996948</v>
       </c>
       <c r="H595" t="n">
         <v>699777</v>
@@ -17711,7 +17711,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G598" t="n">
-        <v>4.8063006401062</v>
+        <v>4.80630016326904</v>
       </c>
       <c r="H598" t="n">
         <v>332805</v>
@@ -17740,7 +17740,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G599" t="n">
-        <v>4.70010900497437</v>
+        <v>4.70010948181152</v>
       </c>
       <c r="H599" t="n">
         <v>555539</v>
@@ -17769,7 +17769,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G600" t="n">
-        <v>4.81091737747192</v>
+        <v>4.81091785430908</v>
       </c>
       <c r="H600" t="n">
         <v>367022</v>
@@ -17798,7 +17798,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G601" t="n">
-        <v>4.77398157119751</v>
+        <v>4.77398109436035</v>
       </c>
       <c r="H601" t="n">
         <v>305751</v>
@@ -17827,7 +17827,7 @@
         <v>5.22499990463257</v>
       </c>
       <c r="G602" t="n">
-        <v>4.82476806640625</v>
+        <v>4.82476854324341</v>
       </c>
       <c r="H602" t="n">
         <v>549261</v>
@@ -17856,7 +17856,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G603" t="n">
-        <v>4.89863967895508</v>
+        <v>4.89864015579224</v>
       </c>
       <c r="H603" t="n">
         <v>510591</v>
@@ -17885,7 +17885,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>4.8063006401062</v>
+        <v>4.80630016326904</v>
       </c>
       <c r="H604" t="n">
         <v>321087</v>
@@ -17914,7 +17914,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G605" t="n">
-        <v>4.66317319869995</v>
+        <v>4.66317367553711</v>
       </c>
       <c r="H605" t="n">
         <v>1112720</v>
@@ -17943,7 +17943,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>4.52466297149658</v>
+        <v>4.52466344833374</v>
       </c>
       <c r="H606" t="n">
         <v>835466</v>
@@ -17972,7 +17972,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G607" t="n">
-        <v>4.52466297149658</v>
+        <v>4.52466344833374</v>
       </c>
       <c r="H607" t="n">
         <v>662577</v>
@@ -18001,7 +18001,7 @@
         <v>4.82200002670288</v>
       </c>
       <c r="G608" t="n">
-        <v>4.45263814926147</v>
+        <v>4.45263767242432</v>
       </c>
       <c r="H608" t="n">
         <v>597938</v>
@@ -18030,7 +18030,7 @@
         <v>4.70800018310547</v>
       </c>
       <c r="G609" t="n">
-        <v>4.34737014770508</v>
+        <v>4.34737062454224</v>
       </c>
       <c r="H609" t="n">
         <v>838204</v>
@@ -18059,7 +18059,7 @@
         <v>4.66400003433228</v>
       </c>
       <c r="G610" t="n">
-        <v>4.30674076080322</v>
+        <v>4.30674028396606</v>
       </c>
       <c r="H610" t="n">
         <v>394307</v>
@@ -18175,7 +18175,7 @@
         <v>4.74399995803833</v>
       </c>
       <c r="G614" t="n">
-        <v>4.38061237335205</v>
+        <v>4.38061285018921</v>
       </c>
       <c r="H614" t="n">
         <v>609563</v>
@@ -18262,7 +18262,7 @@
         <v>4.96600008010864</v>
       </c>
       <c r="G617" t="n">
-        <v>4.58560752868652</v>
+        <v>4.58560800552368</v>
       </c>
       <c r="H617" t="n">
         <v>558256</v>
@@ -18291,7 +18291,7 @@
         <v>5</v>
       </c>
       <c r="G618" t="n">
-        <v>4.61700344085693</v>
+        <v>4.61700296401978</v>
       </c>
       <c r="H618" t="n">
         <v>694400</v>
@@ -18320,7 +18320,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G619" t="n">
-        <v>4.46741199493408</v>
+        <v>4.46741247177124</v>
       </c>
       <c r="H619" t="n">
         <v>402669</v>
@@ -18378,7 +18378,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G621" t="n">
-        <v>4.56898641586304</v>
+        <v>4.56898593902588</v>
       </c>
       <c r="H621" t="n">
         <v>377386</v>
@@ -18494,7 +18494,7 @@
         <v>5.06500005722046</v>
       </c>
       <c r="G625" t="n">
-        <v>4.67702388763428</v>
+        <v>4.67702436447144</v>
       </c>
       <c r="H625" t="n">
         <v>1126607</v>
@@ -18552,7 +18552,7 @@
         <v>4.97800016403198</v>
       </c>
       <c r="G627" t="n">
-        <v>4.59668874740601</v>
+        <v>4.59668827056885</v>
       </c>
       <c r="H627" t="n">
         <v>698215</v>
@@ -18581,7 +18581,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G628" t="n">
-        <v>4.70010900497437</v>
+        <v>4.70010948181152</v>
       </c>
       <c r="H628" t="n">
         <v>666276</v>
@@ -18639,7 +18639,7 @@
         <v>5.0149998664856</v>
       </c>
       <c r="G630" t="n">
-        <v>4.63085412979126</v>
+        <v>4.6308536529541</v>
       </c>
       <c r="H630" t="n">
         <v>580822</v>
@@ -18726,7 +18726,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G633" t="n">
-        <v>4.63421201705933</v>
+        <v>4.63421249389648</v>
       </c>
       <c r="H633" t="n">
         <v>659569</v>
@@ -18900,7 +18900,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G639" t="n">
-        <v>4.47546672821045</v>
+        <v>4.47546625137329</v>
       </c>
       <c r="H639" t="n">
         <v>721270</v>
@@ -18929,7 +18929,7 @@
         <v>4.81199979782104</v>
       </c>
       <c r="G640" t="n">
-        <v>4.60169792175293</v>
+        <v>4.60169744491577</v>
       </c>
       <c r="H640" t="n">
         <v>409298</v>
@@ -19074,7 +19074,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G645" t="n">
-        <v>4.45634031295776</v>
+        <v>4.45634078979492</v>
       </c>
       <c r="H645" t="n">
         <v>337361</v>
@@ -19132,7 +19132,7 @@
         <v>4.62400007247925</v>
       </c>
       <c r="G647" t="n">
-        <v>4.42191457748413</v>
+        <v>4.42191410064697</v>
       </c>
       <c r="H647" t="n">
         <v>590963</v>
@@ -19219,7 +19219,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G650" t="n">
-        <v>4.17136430740356</v>
+        <v>4.17136478424072</v>
       </c>
       <c r="H650" t="n">
         <v>575556</v>
@@ -19306,7 +19306,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G653" t="n">
-        <v>4.20770359039307</v>
+        <v>4.20770406723022</v>
       </c>
       <c r="H653" t="n">
         <v>253568</v>
@@ -19480,7 +19480,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G659" t="n">
-        <v>3.9303777217865</v>
+        <v>3.93037796020508</v>
       </c>
       <c r="H659" t="n">
         <v>499794</v>
@@ -19770,7 +19770,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G669" t="n">
-        <v>3.65496444702148</v>
+        <v>3.65496468544006</v>
       </c>
       <c r="H669" t="n">
         <v>556073</v>
@@ -19857,7 +19857,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G672" t="n">
-        <v>3.81370973587036</v>
+        <v>3.81370949745178</v>
       </c>
       <c r="H672" t="n">
         <v>401105</v>
@@ -19886,7 +19886,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G673" t="n">
-        <v>3.81370973587036</v>
+        <v>3.81370949745178</v>
       </c>
       <c r="H673" t="n">
         <v>294689</v>
@@ -19915,7 +19915,7 @@
         <v>4.17600011825562</v>
       </c>
       <c r="G674" t="n">
-        <v>3.99349331855774</v>
+        <v>3.99349355697632</v>
       </c>
       <c r="H674" t="n">
         <v>714573</v>
@@ -20379,7 +20379,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G690" t="n">
-        <v>3.4560546875</v>
+        <v>3.45605492591858</v>
       </c>
       <c r="H690" t="n">
         <v>383156</v>
@@ -20756,7 +20756,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G703" t="n">
-        <v>3.96862983703613</v>
+        <v>3.96862959861755</v>
       </c>
       <c r="H703" t="n">
         <v>402206</v>
@@ -20785,7 +20785,7 @@
         <v>4.1560001373291</v>
       </c>
       <c r="G704" t="n">
-        <v>3.97436738014221</v>
+        <v>3.97436785697937</v>
       </c>
       <c r="H704" t="n">
         <v>366565</v>
@@ -20843,7 +20843,7 @@
         <v>4.27600002288818</v>
       </c>
       <c r="G706" t="n">
-        <v>4.08912324905396</v>
+        <v>4.0891227722168</v>
       </c>
       <c r="H706" t="n">
         <v>382472</v>
@@ -20872,7 +20872,7 @@
         <v>4.13600015640259</v>
       </c>
       <c r="G707" t="n">
-        <v>3.95524144172668</v>
+        <v>3.95524168014526</v>
       </c>
       <c r="H707" t="n">
         <v>503313</v>
@@ -20930,7 +20930,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G709" t="n">
-        <v>3.98966789245605</v>
+        <v>3.98966813087463</v>
       </c>
       <c r="H709" t="n">
         <v>357159</v>
@@ -21017,7 +21017,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G712" t="n">
-        <v>3.67026543617249</v>
+        <v>3.67026519775391</v>
       </c>
       <c r="H712" t="n">
         <v>437455</v>
@@ -21162,7 +21162,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G717" t="n">
-        <v>3.81370973587036</v>
+        <v>3.81370949745178</v>
       </c>
       <c r="H717" t="n">
         <v>286225</v>
@@ -21191,7 +21191,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G718" t="n">
-        <v>3.82327246665955</v>
+        <v>3.82327270507812</v>
       </c>
       <c r="H718" t="n">
         <v>150642</v>
@@ -21220,7 +21220,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G719" t="n">
-        <v>3.91507720947266</v>
+        <v>3.91507697105408</v>
       </c>
       <c r="H719" t="n">
         <v>372351</v>
@@ -21307,7 +21307,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G722" t="n">
-        <v>3.98584318161011</v>
+        <v>3.98584294319153</v>
       </c>
       <c r="H722" t="n">
         <v>634315</v>
@@ -21365,7 +21365,7 @@
         <v>4.42600011825562</v>
       </c>
       <c r="G724" t="n">
-        <v>4.23256731033325</v>
+        <v>4.23256778717041</v>
       </c>
       <c r="H724" t="n">
         <v>1439555</v>
@@ -21394,7 +21394,7 @@
         <v>4.51200008392334</v>
       </c>
       <c r="G725" t="n">
-        <v>4.31480932235718</v>
+        <v>4.31480884552002</v>
       </c>
       <c r="H725" t="n">
         <v>724657</v>
@@ -21452,7 +21452,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G727" t="n">
-        <v>4.15032577514648</v>
+        <v>4.15032625198364</v>
       </c>
       <c r="H727" t="n">
         <v>336308</v>
@@ -21510,7 +21510,7 @@
         <v>4.25</v>
       </c>
       <c r="G729" t="n">
-        <v>4.06425952911377</v>
+        <v>4.06425905227661</v>
       </c>
       <c r="H729" t="n">
         <v>168991</v>
@@ -21597,7 +21597,7 @@
         <v>4.2039999961853</v>
       </c>
       <c r="G732" t="n">
-        <v>4.02026987075806</v>
+        <v>4.0202693939209</v>
       </c>
       <c r="H732" t="n">
         <v>193502</v>
@@ -21742,7 +21742,7 @@
         <v>4.11399984359741</v>
       </c>
       <c r="G737" t="n">
-        <v>3.9342029094696</v>
+        <v>3.93420267105103</v>
       </c>
       <c r="H737" t="n">
         <v>129269</v>
@@ -21829,7 +21829,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G740" t="n">
-        <v>3.96862983703613</v>
+        <v>3.96862959861755</v>
       </c>
       <c r="H740" t="n">
         <v>236046</v>
@@ -21858,7 +21858,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G741" t="n">
-        <v>3.91507720947266</v>
+        <v>3.91507697105408</v>
       </c>
       <c r="H741" t="n">
         <v>182762</v>
@@ -22061,7 +22061,7 @@
         <v>3.90799999237061</v>
       </c>
       <c r="G748" t="n">
-        <v>3.73720598220825</v>
+        <v>3.73720574378967</v>
       </c>
       <c r="H748" t="n">
         <v>191909</v>
@@ -22119,7 +22119,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G750" t="n">
-        <v>3.70086646080017</v>
+        <v>3.70086669921875</v>
       </c>
       <c r="H750" t="n">
         <v>77185</v>
@@ -22148,7 +22148,7 @@
         <v>3.93799996376038</v>
       </c>
       <c r="G751" t="n">
-        <v>3.76589465141296</v>
+        <v>3.76589488983154</v>
       </c>
       <c r="H751" t="n">
         <v>138045</v>
@@ -22264,7 +22264,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G755" t="n">
-        <v>3.7391185760498</v>
+        <v>3.73911881446838</v>
       </c>
       <c r="H755" t="n">
         <v>208777</v>
@@ -22380,7 +22380,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G759" t="n">
-        <v>3.57846069335938</v>
+        <v>3.57846093177795</v>
       </c>
       <c r="H759" t="n">
         <v>337584</v>
@@ -22409,7 +22409,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G760" t="n">
-        <v>3.62245035171509</v>
+        <v>3.62245059013367</v>
       </c>
       <c r="H760" t="n">
         <v>422072</v>
@@ -22467,7 +22467,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G762" t="n">
-        <v>3.56316018104553</v>
+        <v>3.56315994262695</v>
       </c>
       <c r="H762" t="n">
         <v>704289</v>
@@ -22496,7 +22496,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G763" t="n">
-        <v>3.54785943031311</v>
+        <v>3.54785919189453</v>
       </c>
       <c r="H763" t="n">
         <v>1097480</v>
@@ -22583,7 +22583,7 @@
         <v>3.64800000190735</v>
       </c>
       <c r="G766" t="n">
-        <v>3.4885687828064</v>
+        <v>3.48856902122498</v>
       </c>
       <c r="H766" t="n">
         <v>1669355</v>
@@ -22728,7 +22728,7 @@
         <v>3.64400005340576</v>
       </c>
       <c r="G771" t="n">
-        <v>3.48474383354187</v>
+        <v>3.48474359512329</v>
       </c>
       <c r="H771" t="n">
         <v>105519</v>
@@ -22757,7 +22757,7 @@
         <v>3.63199996948242</v>
       </c>
       <c r="G772" t="n">
-        <v>3.47326803207397</v>
+        <v>3.47326827049255</v>
       </c>
       <c r="H772" t="n">
         <v>121534</v>
@@ -22873,7 +22873,7 @@
         <v>3.95799994468689</v>
       </c>
       <c r="G776" t="n">
-        <v>3.78502058982849</v>
+        <v>3.78502082824707</v>
       </c>
       <c r="H776" t="n">
         <v>243650</v>
@@ -22902,7 +22902,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G777" t="n">
-        <v>3.76972007751465</v>
+        <v>3.76971983909607</v>
       </c>
       <c r="H777" t="n">
         <v>111182</v>
@@ -22960,7 +22960,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G779" t="n">
-        <v>3.70086646080017</v>
+        <v>3.70086669921875</v>
       </c>
       <c r="H779" t="n">
         <v>145693</v>
@@ -22989,7 +22989,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G780" t="n">
-        <v>3.5975866317749</v>
+        <v>3.59758687019348</v>
       </c>
       <c r="H780" t="n">
         <v>157659</v>
@@ -23076,7 +23076,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G783" t="n">
-        <v>3.44075417518616</v>
+        <v>3.44075393676758</v>
       </c>
       <c r="H783" t="n">
         <v>613580</v>
@@ -23105,7 +23105,7 @@
         <v>3.41599988937378</v>
       </c>
       <c r="G784" t="n">
-        <v>3.26670789718628</v>
+        <v>3.26670813560486</v>
       </c>
       <c r="H784" t="n">
         <v>455535</v>
@@ -23134,7 +23134,7 @@
         <v>3.41599988937378</v>
       </c>
       <c r="G785" t="n">
-        <v>3.26670789718628</v>
+        <v>3.26670813560486</v>
       </c>
       <c r="H785" t="n">
         <v>519347</v>
@@ -23163,7 +23163,7 @@
         <v>3.46799993515015</v>
       </c>
       <c r="G786" t="n">
-        <v>3.31643557548523</v>
+        <v>3.31643533706665</v>
       </c>
       <c r="H786" t="n">
         <v>202674</v>
@@ -23192,7 +23192,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G787" t="n">
-        <v>3.29157185554504</v>
+        <v>3.29157161712646</v>
       </c>
       <c r="H787" t="n">
         <v>188696</v>
@@ -23424,7 +23424,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G795" t="n">
-        <v>3.2074179649353</v>
+        <v>3.20741772651672</v>
       </c>
       <c r="H795" t="n">
         <v>383770</v>
@@ -23801,7 +23801,7 @@
         <v>3.47399997711182</v>
       </c>
       <c r="G808" t="n">
-        <v>3.32217311859131</v>
+        <v>3.32217335700989</v>
       </c>
       <c r="H808" t="n">
         <v>80720</v>
@@ -23975,7 +23975,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G814" t="n">
-        <v>3.22654390335083</v>
+        <v>3.22654366493225</v>
       </c>
       <c r="H814" t="n">
         <v>115313</v>
@@ -24149,7 +24149,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G820" t="n">
-        <v>3.55168437957764</v>
+        <v>3.55168461799622</v>
       </c>
       <c r="H820" t="n">
         <v>1031313</v>
@@ -24178,7 +24178,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G821" t="n">
-        <v>3.50769472122192</v>
+        <v>3.5076949596405</v>
       </c>
       <c r="H821" t="n">
         <v>354331</v>
@@ -24236,7 +24236,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G823" t="n">
-        <v>3.53638386726379</v>
+        <v>3.53638362884521</v>
       </c>
       <c r="H823" t="n">
         <v>421877</v>
@@ -24323,7 +24323,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G826" t="n">
-        <v>3.58228611946106</v>
+        <v>3.58228588104248</v>
       </c>
       <c r="H826" t="n">
         <v>258986</v>
@@ -24352,7 +24352,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G827" t="n">
-        <v>3.57654809951782</v>
+        <v>3.5765483379364</v>
       </c>
       <c r="H827" t="n">
         <v>166129</v>
@@ -24381,7 +24381,7 @@
         <v>3.84400010108948</v>
       </c>
       <c r="G828" t="n">
-        <v>3.67600297927856</v>
+        <v>3.67600321769714</v>
       </c>
       <c r="H828" t="n">
         <v>474129</v>
@@ -24526,7 +24526,7 @@
         <v>4.22599983215332</v>
       </c>
       <c r="G833" t="n">
-        <v>4.04130840301514</v>
+        <v>4.04130792617798</v>
       </c>
       <c r="H833" t="n">
         <v>2312238</v>
@@ -24758,7 +24758,7 @@
         <v>4.68599987030029</v>
       </c>
       <c r="G841" t="n">
-        <v>4.48120403289795</v>
+        <v>4.48120450973511</v>
       </c>
       <c r="H841" t="n">
         <v>337090</v>
@@ -24816,7 +24816,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G843" t="n">
-        <v>4.54431962966919</v>
+        <v>4.54432010650635</v>
       </c>
       <c r="H843" t="n">
         <v>212793</v>
@@ -24903,7 +24903,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G846" t="n">
-        <v>4.35688638687134</v>
+        <v>4.35688591003418</v>
       </c>
       <c r="H846" t="n">
         <v>178453</v>
@@ -24932,7 +24932,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G847" t="n">
-        <v>4.2631688117981</v>
+        <v>4.26316928863525</v>
       </c>
       <c r="H847" t="n">
         <v>228223</v>
@@ -24990,7 +24990,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G849" t="n">
-        <v>4.17136430740356</v>
+        <v>4.17136478424072</v>
       </c>
       <c r="H849" t="n">
         <v>216742</v>
@@ -25048,7 +25048,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G851" t="n">
-        <v>3.9303777217865</v>
+        <v>3.93037796020508</v>
       </c>
       <c r="H851" t="n">
         <v>187268</v>
@@ -25135,7 +25135,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G854" t="n">
-        <v>3.77928304672241</v>
+        <v>3.77928280830383</v>
       </c>
       <c r="H854" t="n">
         <v>245578</v>
@@ -25251,7 +25251,7 @@
         <v>3.51200008392334</v>
       </c>
       <c r="G858" t="n">
-        <v>3.35851287841797</v>
+        <v>3.35851263999939</v>
       </c>
       <c r="H858" t="n">
         <v>146055</v>
@@ -25280,7 +25280,7 @@
         <v>3.56800007820129</v>
       </c>
       <c r="G859" t="n">
-        <v>3.41206550598145</v>
+        <v>3.41206526756287</v>
       </c>
       <c r="H859" t="n">
         <v>419236</v>
@@ -25396,7 +25396,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G863" t="n">
-        <v>3.47900605201721</v>
+        <v>3.47900581359863</v>
       </c>
       <c r="H863" t="n">
         <v>215914</v>
@@ -25541,7 +25541,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G868" t="n">
-        <v>3.77928304672241</v>
+        <v>3.77928280830383</v>
       </c>
       <c r="H868" t="n">
         <v>73720</v>
@@ -25657,7 +25657,7 @@
         <v>4.12400007247925</v>
       </c>
       <c r="G872" t="n">
-        <v>3.94376611709595</v>
+        <v>3.94376587867737</v>
       </c>
       <c r="H872" t="n">
         <v>191569</v>
@@ -25860,7 +25860,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G879" t="n">
-        <v>4.47546672821045</v>
+        <v>4.47546625137329</v>
       </c>
       <c r="H879" t="n">
         <v>120035</v>
@@ -25976,7 +25976,7 @@
         <v>4.38800001144409</v>
       </c>
       <c r="G883" t="n">
-        <v>4.19622802734375</v>
+        <v>4.19622850418091</v>
       </c>
       <c r="H883" t="n">
         <v>292289</v>
@@ -26063,7 +26063,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G886" t="n">
-        <v>4.20196628570557</v>
+        <v>4.20196580886841</v>
       </c>
       <c r="H886" t="n">
         <v>132141</v>
@@ -26237,7 +26237,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G892" t="n">
-        <v>4.57109642028809</v>
+        <v>4.57109689712524</v>
       </c>
       <c r="H892" t="n">
         <v>407750</v>
@@ -26295,7 +26295,7 @@
         <v>4.74599981307983</v>
       </c>
       <c r="G894" t="n">
-        <v>4.53858232498169</v>
+        <v>4.53858184814453</v>
       </c>
       <c r="H894" t="n">
         <v>111758</v>
@@ -26324,7 +26324,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G895" t="n">
-        <v>4.68585157394409</v>
+        <v>4.68585205078125</v>
       </c>
       <c r="H895" t="n">
         <v>288639</v>
@@ -36477,9 +36477,38 @@
         <v>3.33599996566772</v>
       </c>
       <c r="H1245" t="n">
-        <v>245017</v>
+        <v>250911</v>
       </c>
       <c r="I1245" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1246" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1246" t="n">
+        <v>3.40799999237061</v>
+      </c>
+      <c r="D1246" t="n">
+        <v>3.40799999237061</v>
+      </c>
+      <c r="E1246" t="n">
+        <v>3.32599997520447</v>
+      </c>
+      <c r="F1246" t="n">
+        <v>3.34200000762939</v>
+      </c>
+      <c r="G1246" t="n">
+        <v>3.34200000762939</v>
+      </c>
+      <c r="H1246" t="n">
+        <v>164232</v>
+      </c>
+      <c r="I1246" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ARIS.MI.xlsx
+++ b/data/ARIS.MI.xlsx
@@ -485,7 +485,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G4" t="n">
-        <v>9.1745138168335</v>
+        <v>9.17451286315918</v>
       </c>
       <c r="H4" t="n">
         <v>732483</v>
@@ -514,7 +514,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G5" t="n">
-        <v>9.25538635253906</v>
+        <v>9.25538539886475</v>
       </c>
       <c r="H5" t="n">
         <v>304924</v>
@@ -630,7 +630,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G9" t="n">
-        <v>9.21944332122803</v>
+        <v>9.21944236755371</v>
       </c>
       <c r="H9" t="n">
         <v>203801</v>
@@ -804,7 +804,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G15" t="n">
-        <v>9.21944332122803</v>
+        <v>9.21944236755371</v>
       </c>
       <c r="H15" t="n">
         <v>184724</v>
@@ -833,7 +833,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G16" t="n">
-        <v>8.92291069030762</v>
+        <v>8.92291164398193</v>
       </c>
       <c r="H16" t="n">
         <v>312158</v>
@@ -862,7 +862,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G17" t="n">
-        <v>8.83305358886719</v>
+        <v>8.83305263519287</v>
       </c>
       <c r="H17" t="n">
         <v>156842</v>
@@ -920,7 +920,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G19" t="n">
-        <v>8.71623802185059</v>
+        <v>8.71623706817627</v>
       </c>
       <c r="H19" t="n">
         <v>172790</v>
@@ -949,7 +949,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G20" t="n">
-        <v>9.12958431243896</v>
+        <v>9.12958526611328</v>
       </c>
       <c r="H20" t="n">
         <v>431091</v>
@@ -1007,7 +1007,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G22" t="n">
-        <v>8.85102367401123</v>
+        <v>8.85102462768555</v>
       </c>
       <c r="H22" t="n">
         <v>186957</v>
@@ -1065,7 +1065,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G24" t="n">
-        <v>9.12958431243896</v>
+        <v>9.12958526611328</v>
       </c>
       <c r="H24" t="n">
         <v>61464</v>
@@ -1123,7 +1123,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G26" t="n">
-        <v>9.12958431243896</v>
+        <v>9.12958526611328</v>
       </c>
       <c r="H26" t="n">
         <v>53953</v>
@@ -1152,7 +1152,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G27" t="n">
-        <v>9.50698852539062</v>
+        <v>9.50698947906494</v>
       </c>
       <c r="H27" t="n">
         <v>542115</v>
@@ -1181,7 +1181,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G28" t="n">
-        <v>9.65076160430908</v>
+        <v>9.65076065063477</v>
       </c>
       <c r="H28" t="n">
         <v>568583</v>
@@ -1210,7 +1210,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G29" t="n">
-        <v>9.74062061309814</v>
+        <v>9.74061965942383</v>
       </c>
       <c r="H29" t="n">
         <v>87322</v>
@@ -1297,7 +1297,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G32" t="n">
-        <v>9.1745138168335</v>
+        <v>9.17451286315918</v>
       </c>
       <c r="H32" t="n">
         <v>405173</v>
@@ -1326,7 +1326,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G33" t="n">
-        <v>9.63279151916504</v>
+        <v>9.63279056549072</v>
       </c>
       <c r="H33" t="n">
         <v>261751</v>
@@ -1355,7 +1355,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G34" t="n">
-        <v>10.0191802978516</v>
+        <v>10.0191793441772</v>
       </c>
       <c r="H34" t="n">
         <v>509719</v>
@@ -1413,7 +1413,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G36" t="n">
-        <v>10.1988964080811</v>
+        <v>10.1988954544067</v>
       </c>
       <c r="H36" t="n">
         <v>477707</v>
@@ -1471,7 +1471,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G38" t="n">
-        <v>9.72264862060547</v>
+        <v>9.72264766693115</v>
       </c>
       <c r="H38" t="n">
         <v>233657</v>
@@ -1587,7 +1587,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G42" t="n">
-        <v>9.10262775421143</v>
+        <v>9.10262680053711</v>
       </c>
       <c r="H42" t="n">
         <v>130467</v>
@@ -1616,7 +1616,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G43" t="n">
-        <v>9.1745138168335</v>
+        <v>9.17451286315918</v>
       </c>
       <c r="H43" t="n">
         <v>290667</v>
@@ -1645,7 +1645,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G44" t="n">
-        <v>9.1205997467041</v>
+        <v>9.12059879302979</v>
       </c>
       <c r="H44" t="n">
         <v>167591</v>
@@ -1674,7 +1674,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G45" t="n">
-        <v>9.04871273040771</v>
+        <v>9.0487117767334</v>
       </c>
       <c r="H45" t="n">
         <v>274213</v>
@@ -1877,7 +1877,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G52" t="n">
-        <v>9.12958431243896</v>
+        <v>9.12958526611328</v>
       </c>
       <c r="H52" t="n">
         <v>73644</v>
@@ -1906,7 +1906,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G53" t="n">
-        <v>9.24640083312988</v>
+        <v>9.24639987945557</v>
       </c>
       <c r="H53" t="n">
         <v>328076</v>
@@ -1964,7 +1964,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G55" t="n">
-        <v>8.994797706604</v>
+        <v>8.99479866027832</v>
       </c>
       <c r="H55" t="n">
         <v>276782</v>
@@ -2022,7 +2022,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G57" t="n">
-        <v>9.10262775421143</v>
+        <v>9.10262680053711</v>
       </c>
       <c r="H57" t="n">
         <v>123193</v>
@@ -2051,7 +2051,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G58" t="n">
-        <v>8.994797706604</v>
+        <v>8.99479866027832</v>
       </c>
       <c r="H58" t="n">
         <v>253397</v>
@@ -2080,7 +2080,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G59" t="n">
-        <v>9.19248485565186</v>
+        <v>9.19248580932617</v>
       </c>
       <c r="H59" t="n">
         <v>486352</v>
@@ -2109,7 +2109,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G60" t="n">
-        <v>8.95885372161865</v>
+        <v>8.95885467529297</v>
       </c>
       <c r="H60" t="n">
         <v>207313</v>
@@ -2138,7 +2138,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G61" t="n">
-        <v>8.71623802185059</v>
+        <v>8.71623706817627</v>
       </c>
       <c r="H61" t="n">
         <v>224870</v>
@@ -2167,7 +2167,7 @@
         <v>9.41499996185303</v>
       </c>
       <c r="G62" t="n">
-        <v>8.46014213562012</v>
+        <v>8.4601411819458</v>
       </c>
       <c r="H62" t="n">
         <v>251208</v>
@@ -2196,7 +2196,7 @@
         <v>9.1850004196167</v>
       </c>
       <c r="G63" t="n">
-        <v>8.25346755981445</v>
+        <v>8.25346851348877</v>
       </c>
       <c r="H63" t="n">
         <v>485171</v>
@@ -2254,7 +2254,7 @@
         <v>9.1850004196167</v>
       </c>
       <c r="G65" t="n">
-        <v>8.25346755981445</v>
+        <v>8.25346851348877</v>
       </c>
       <c r="H65" t="n">
         <v>239997</v>
@@ -2283,7 +2283,7 @@
         <v>9.20499992370605</v>
       </c>
       <c r="G66" t="n">
-        <v>8.27143955230713</v>
+        <v>8.27144050598145</v>
       </c>
       <c r="H66" t="n">
         <v>126081</v>
@@ -2312,7 +2312,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G67" t="n">
-        <v>7.70982646942139</v>
+        <v>7.70982551574707</v>
       </c>
       <c r="H67" t="n">
         <v>139521</v>
@@ -2341,7 +2341,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G68" t="n">
-        <v>8.03331470489502</v>
+        <v>8.03331565856934</v>
       </c>
       <c r="H68" t="n">
         <v>139296</v>
@@ -2370,7 +2370,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G69" t="n">
-        <v>7.95244312286377</v>
+        <v>7.95244264602661</v>
       </c>
       <c r="H69" t="n">
         <v>230882</v>
@@ -2399,7 +2399,7 @@
         <v>7.875</v>
       </c>
       <c r="G70" t="n">
-        <v>7.07632732391357</v>
+        <v>7.07632684707642</v>
       </c>
       <c r="H70" t="n">
         <v>381529</v>
@@ -2486,7 +2486,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G73" t="n">
-        <v>7.79069900512695</v>
+        <v>7.79069852828979</v>
       </c>
       <c r="H73" t="n">
         <v>361935</v>
@@ -2544,7 +2544,7 @@
         <v>8.78499984741211</v>
       </c>
       <c r="G75" t="n">
-        <v>7.89403581619263</v>
+        <v>7.89403486251831</v>
       </c>
       <c r="H75" t="n">
         <v>220029</v>
@@ -2573,7 +2573,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G76" t="n">
-        <v>8.66232395172119</v>
+        <v>8.66232204437256</v>
       </c>
       <c r="H76" t="n">
         <v>544195</v>
@@ -2660,7 +2660,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G79" t="n">
-        <v>9.08465576171875</v>
+        <v>9.08465480804443</v>
       </c>
       <c r="H79" t="n">
         <v>663957</v>
@@ -2689,7 +2689,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G80" t="n">
-        <v>9.19248485565186</v>
+        <v>9.19248580932617</v>
       </c>
       <c r="H80" t="n">
         <v>1158996</v>
@@ -2805,7 +2805,7 @@
         <v>9.48499965667725</v>
       </c>
       <c r="G84" t="n">
-        <v>8.52304172515869</v>
+        <v>8.52304267883301</v>
       </c>
       <c r="H84" t="n">
         <v>211192</v>
@@ -2834,7 +2834,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G85" t="n">
-        <v>8.64435195922852</v>
+        <v>8.6443510055542</v>
       </c>
       <c r="H85" t="n">
         <v>93670</v>
@@ -2863,7 +2863,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G86" t="n">
-        <v>8.55898475646973</v>
+        <v>8.55898571014404</v>
       </c>
       <c r="H86" t="n">
         <v>136560</v>
@@ -2892,7 +2892,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G87" t="n">
-        <v>8.67130756378174</v>
+        <v>8.67130851745605</v>
       </c>
       <c r="H87" t="n">
         <v>120344</v>
@@ -2950,7 +2950,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G89" t="n">
-        <v>8.50057697296143</v>
+        <v>8.50057792663574</v>
       </c>
       <c r="H89" t="n">
         <v>95717</v>
@@ -2979,7 +2979,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G90" t="n">
-        <v>8.55898475646973</v>
+        <v>8.55898571014404</v>
       </c>
       <c r="H90" t="n">
         <v>75199</v>
@@ -3008,7 +3008,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G91" t="n">
-        <v>8.51854801177979</v>
+        <v>8.5185489654541</v>
       </c>
       <c r="H91" t="n">
         <v>163375</v>
@@ -3037,7 +3037,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G92" t="n">
-        <v>8.71623802185059</v>
+        <v>8.71623706817627</v>
       </c>
       <c r="H92" t="n">
         <v>223170</v>
@@ -3066,7 +3066,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G93" t="n">
-        <v>8.50057697296143</v>
+        <v>8.50057792663574</v>
       </c>
       <c r="H93" t="n">
         <v>181323</v>
@@ -3124,7 +3124,7 @@
         <v>9.25</v>
       </c>
       <c r="G95" t="n">
-        <v>8.31187534332275</v>
+        <v>8.31187629699707</v>
       </c>
       <c r="H95" t="n">
         <v>70088</v>
@@ -3153,7 +3153,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G96" t="n">
-        <v>8.24897480010986</v>
+        <v>8.24897575378418</v>
       </c>
       <c r="H96" t="n">
         <v>89220</v>
@@ -3182,7 +3182,7 @@
         <v>9.25</v>
       </c>
       <c r="G97" t="n">
-        <v>8.31187534332275</v>
+        <v>8.31187629699707</v>
       </c>
       <c r="H97" t="n">
         <v>77345</v>
@@ -3240,7 +3240,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G99" t="n">
-        <v>8.45564746856689</v>
+        <v>8.45564842224121</v>
       </c>
       <c r="H99" t="n">
         <v>126252</v>
@@ -3327,7 +3327,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G102" t="n">
-        <v>8.5904369354248</v>
+        <v>8.59043598175049</v>
       </c>
       <c r="H102" t="n">
         <v>81506</v>
@@ -3356,7 +3356,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G103" t="n">
-        <v>8.71623802185059</v>
+        <v>8.71623706817627</v>
       </c>
       <c r="H103" t="n">
         <v>216807</v>
@@ -3385,7 +3385,7 @@
         <v>9.625</v>
       </c>
       <c r="G104" t="n">
-        <v>8.64884281158447</v>
+        <v>8.64884471893311</v>
       </c>
       <c r="H104" t="n">
         <v>109168</v>
@@ -3414,7 +3414,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G105" t="n">
-        <v>8.55898475646973</v>
+        <v>8.55898571014404</v>
       </c>
       <c r="H105" t="n">
         <v>167622</v>
@@ -3472,7 +3472,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G107" t="n">
-        <v>8.67130756378174</v>
+        <v>8.67130851745605</v>
       </c>
       <c r="H107" t="n">
         <v>107921</v>
@@ -3501,7 +3501,7 @@
         <v>9.53499984741211</v>
       </c>
       <c r="G108" t="n">
-        <v>8.56797218322754</v>
+        <v>8.56797122955322</v>
       </c>
       <c r="H108" t="n">
         <v>345401</v>
@@ -3559,7 +3559,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G110" t="n">
-        <v>7.89852905273438</v>
+        <v>7.89852857589722</v>
       </c>
       <c r="H110" t="n">
         <v>136469</v>
@@ -3646,7 +3646,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G113" t="n">
-        <v>7.99737119674683</v>
+        <v>7.99737215042114</v>
       </c>
       <c r="H113" t="n">
         <v>164165</v>
@@ -3733,7 +3733,7 @@
         <v>9.02499961853027</v>
       </c>
       <c r="G116" t="n">
-        <v>8.109694480896</v>
+        <v>8.10969543457031</v>
       </c>
       <c r="H116" t="n">
         <v>88735</v>
@@ -3762,7 +3762,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G117" t="n">
-        <v>8.32086277008057</v>
+        <v>8.32086086273193</v>
       </c>
       <c r="H117" t="n">
         <v>146034</v>
@@ -3791,7 +3791,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G118" t="n">
-        <v>8.54550647735596</v>
+        <v>8.54550743103027</v>
       </c>
       <c r="H118" t="n">
         <v>395701</v>
@@ -3907,7 +3907,7 @@
         <v>9.94499969482422</v>
       </c>
       <c r="G122" t="n">
-        <v>8.93638896942139</v>
+        <v>8.93638801574707</v>
       </c>
       <c r="H122" t="n">
         <v>223439</v>
@@ -3936,7 +3936,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G123" t="n">
-        <v>8.96334838867188</v>
+        <v>8.96334743499756</v>
       </c>
       <c r="H123" t="n">
         <v>150460</v>
@@ -4023,7 +4023,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G126" t="n">
-        <v>8.93144989013672</v>
+        <v>8.9314489364624</v>
       </c>
       <c r="H126" t="n">
         <v>138520</v>
@@ -4081,7 +4081,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>9.478271484375</v>
+        <v>9.47827243804932</v>
       </c>
       <c r="H128" t="n">
         <v>307614</v>
@@ -4110,7 +4110,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G129" t="n">
-        <v>9.51472663879395</v>
+        <v>9.51472759246826</v>
       </c>
       <c r="H129" t="n">
         <v>242971</v>
@@ -4139,7 +4139,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G130" t="n">
-        <v>9.35068035125732</v>
+        <v>9.35068130493164</v>
       </c>
       <c r="H130" t="n">
         <v>2902048</v>
@@ -4226,7 +4226,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G133" t="n">
-        <v>9.30511093139648</v>
+        <v>9.3051118850708</v>
       </c>
       <c r="H133" t="n">
         <v>80187</v>
@@ -4284,7 +4284,7 @@
         <v>10.25</v>
       </c>
       <c r="G135" t="n">
-        <v>9.34156608581543</v>
+        <v>9.34156703948975</v>
       </c>
       <c r="H135" t="n">
         <v>52292</v>
@@ -4371,7 +4371,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G138" t="n">
-        <v>8.70360565185547</v>
+        <v>8.70360660552979</v>
       </c>
       <c r="H138" t="n">
         <v>108046</v>
@@ -4400,7 +4400,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G139" t="n">
-        <v>8.52133274078369</v>
+        <v>8.52133178710938</v>
       </c>
       <c r="H139" t="n">
         <v>53406</v>
@@ -4429,7 +4429,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G140" t="n">
-        <v>7.95628118515015</v>
+        <v>7.95628023147583</v>
       </c>
       <c r="H140" t="n">
         <v>163728</v>
@@ -4458,7 +4458,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G141" t="n">
-        <v>7.83780241012573</v>
+        <v>7.83780288696289</v>
       </c>
       <c r="H141" t="n">
         <v>132472</v>
@@ -4487,7 +4487,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G142" t="n">
-        <v>7.61907243728638</v>
+        <v>7.61907291412354</v>
       </c>
       <c r="H142" t="n">
         <v>67512</v>
@@ -4516,7 +4516,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G143" t="n">
-        <v>7.73755121231079</v>
+        <v>7.73755168914795</v>
       </c>
       <c r="H143" t="n">
         <v>68881</v>
@@ -4545,7 +4545,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G144" t="n">
-        <v>7.6464147567749</v>
+        <v>7.64641427993774</v>
       </c>
       <c r="H144" t="n">
         <v>79110</v>
@@ -4574,7 +4574,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G145" t="n">
-        <v>7.47325325012207</v>
+        <v>7.47325277328491</v>
       </c>
       <c r="H145" t="n">
         <v>33799</v>
@@ -4632,7 +4632,7 @@
         <v>7.50500011444092</v>
       </c>
       <c r="G147" t="n">
-        <v>6.8398494720459</v>
+        <v>6.83984994888306</v>
       </c>
       <c r="H147" t="n">
         <v>173369</v>
@@ -4748,7 +4748,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G151" t="n">
-        <v>7.02668142318726</v>
+        <v>7.0266809463501</v>
       </c>
       <c r="H151" t="n">
         <v>83909</v>
@@ -4777,7 +4777,7 @@
         <v>7.81500005722046</v>
       </c>
       <c r="G152" t="n">
-        <v>7.12237501144409</v>
+        <v>7.12237548828125</v>
       </c>
       <c r="H152" t="n">
         <v>173417</v>
@@ -4922,7 +4922,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G157" t="n">
-        <v>6.78061008453369</v>
+        <v>6.78061056137085</v>
       </c>
       <c r="H157" t="n">
         <v>109900</v>
@@ -4951,7 +4951,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G158" t="n">
-        <v>6.92642974853516</v>
+        <v>6.92643022537231</v>
       </c>
       <c r="H158" t="n">
         <v>58691</v>
@@ -5038,7 +5038,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G161" t="n">
-        <v>6.64846134185791</v>
+        <v>6.64846181869507</v>
       </c>
       <c r="H161" t="n">
         <v>62300</v>
@@ -5067,7 +5067,7 @@
         <v>7.05499982833862</v>
       </c>
       <c r="G162" t="n">
-        <v>6.42973136901855</v>
+        <v>6.42973184585571</v>
       </c>
       <c r="H162" t="n">
         <v>80746</v>
@@ -5125,7 +5125,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G164" t="n">
-        <v>6.88086175918579</v>
+        <v>6.88086128234863</v>
       </c>
       <c r="H164" t="n">
         <v>59880</v>
@@ -5183,7 +5183,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G166" t="n">
-        <v>6.96288442611694</v>
+        <v>6.9628849029541</v>
       </c>
       <c r="H166" t="n">
         <v>25056</v>
@@ -5212,7 +5212,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G167" t="n">
-        <v>6.96288442611694</v>
+        <v>6.9628849029541</v>
       </c>
       <c r="H167" t="n">
         <v>115212</v>
@@ -5270,7 +5270,7 @@
         <v>7.72499990463257</v>
       </c>
       <c r="G169" t="n">
-        <v>7.04035186767578</v>
+        <v>7.04035139083862</v>
       </c>
       <c r="H169" t="n">
         <v>97576</v>
@@ -5386,7 +5386,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G173" t="n">
-        <v>7.38211679458618</v>
+        <v>7.38211631774902</v>
       </c>
       <c r="H173" t="n">
         <v>117230</v>
@@ -5415,7 +5415,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G174" t="n">
-        <v>7.47325325012207</v>
+        <v>7.47325277328491</v>
       </c>
       <c r="H174" t="n">
         <v>32018</v>
@@ -5444,7 +5444,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G175" t="n">
-        <v>7.61907243728638</v>
+        <v>7.61907291412354</v>
       </c>
       <c r="H175" t="n">
         <v>67391</v>
@@ -5589,7 +5589,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G180" t="n">
-        <v>7.24996709823608</v>
+        <v>7.24996662139893</v>
       </c>
       <c r="H180" t="n">
         <v>63885</v>
@@ -5618,7 +5618,7 @@
         <v>8</v>
       </c>
       <c r="G181" t="n">
-        <v>7.29097938537598</v>
+        <v>7.29097890853882</v>
       </c>
       <c r="H181" t="n">
         <v>44729</v>
@@ -5647,7 +5647,7 @@
         <v>8</v>
       </c>
       <c r="G182" t="n">
-        <v>7.29097938537598</v>
+        <v>7.29097890853882</v>
       </c>
       <c r="H182" t="n">
         <v>68137</v>
@@ -5705,7 +5705,7 @@
         <v>8</v>
       </c>
       <c r="G184" t="n">
-        <v>7.29097938537598</v>
+        <v>7.29097890853882</v>
       </c>
       <c r="H184" t="n">
         <v>53674</v>
@@ -5763,7 +5763,7 @@
         <v>8</v>
       </c>
       <c r="G186" t="n">
-        <v>7.29097938537598</v>
+        <v>7.29097890853882</v>
       </c>
       <c r="H186" t="n">
         <v>98582</v>
@@ -5792,7 +5792,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G187" t="n">
-        <v>7.30009317398071</v>
+        <v>7.30009269714355</v>
       </c>
       <c r="H187" t="n">
         <v>50930</v>
@@ -5821,7 +5821,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G188" t="n">
-        <v>7.10870456695557</v>
+        <v>7.10870409011841</v>
       </c>
       <c r="H188" t="n">
         <v>92732</v>
@@ -5850,7 +5850,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G189" t="n">
-        <v>7.2135124206543</v>
+        <v>7.21351194381714</v>
       </c>
       <c r="H189" t="n">
         <v>58048</v>
@@ -5908,7 +5908,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G191" t="n">
-        <v>6.96288442611694</v>
+        <v>6.9628849029541</v>
       </c>
       <c r="H191" t="n">
         <v>64057</v>
@@ -6024,7 +6024,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G195" t="n">
-        <v>7.00845336914062</v>
+        <v>7.00845384597778</v>
       </c>
       <c r="H195" t="n">
         <v>142516</v>
@@ -6082,7 +6082,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G197" t="n">
-        <v>6.92642974853516</v>
+        <v>6.92643022537231</v>
       </c>
       <c r="H197" t="n">
         <v>94339</v>
@@ -6140,7 +6140,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G199" t="n">
-        <v>6.42517566680908</v>
+        <v>6.42517518997192</v>
       </c>
       <c r="H199" t="n">
         <v>115768</v>
@@ -6169,7 +6169,7 @@
         <v>7.0149998664856</v>
       </c>
       <c r="G200" t="n">
-        <v>6.39327716827393</v>
+        <v>6.39327764511108</v>
       </c>
       <c r="H200" t="n">
         <v>115529</v>
@@ -6198,7 +6198,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G201" t="n">
-        <v>6.63023376464844</v>
+        <v>6.6302342414856</v>
       </c>
       <c r="H201" t="n">
         <v>127295</v>
@@ -6227,7 +6227,7 @@
         <v>7.52500009536743</v>
       </c>
       <c r="G202" t="n">
-        <v>6.85807657241821</v>
+        <v>6.85807704925537</v>
       </c>
       <c r="H202" t="n">
         <v>80911</v>
@@ -6256,7 +6256,7 @@
         <v>7.75</v>
       </c>
       <c r="G203" t="n">
-        <v>7.06313610076904</v>
+        <v>7.06313562393188</v>
       </c>
       <c r="H203" t="n">
         <v>74023</v>
@@ -6314,7 +6314,7 @@
         <v>7.33500003814697</v>
       </c>
       <c r="G205" t="n">
-        <v>6.6849160194397</v>
+        <v>6.68491649627686</v>
       </c>
       <c r="H205" t="n">
         <v>69663</v>
@@ -6372,7 +6372,7 @@
         <v>8.46500015258789</v>
       </c>
       <c r="G207" t="n">
-        <v>7.71476697921753</v>
+        <v>7.71476745605469</v>
       </c>
       <c r="H207" t="n">
         <v>667919</v>
@@ -6459,7 +6459,7 @@
         <v>8.40499973297119</v>
       </c>
       <c r="G210" t="n">
-        <v>7.66008520126343</v>
+        <v>7.66008472442627</v>
       </c>
       <c r="H210" t="n">
         <v>162822</v>
@@ -6488,7 +6488,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G211" t="n">
-        <v>7.70565319061279</v>
+        <v>7.70565271377563</v>
       </c>
       <c r="H211" t="n">
         <v>238638</v>
@@ -6517,7 +6517,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G212" t="n">
-        <v>7.75577878952026</v>
+        <v>7.75577831268311</v>
       </c>
       <c r="H212" t="n">
         <v>149734</v>
@@ -6546,7 +6546,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G213" t="n">
-        <v>7.828688621521</v>
+        <v>7.82868909835815</v>
       </c>
       <c r="H213" t="n">
         <v>267292</v>
@@ -6575,7 +6575,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G214" t="n">
-        <v>7.828688621521</v>
+        <v>7.82868909835815</v>
       </c>
       <c r="H214" t="n">
         <v>252704</v>
@@ -6604,7 +6604,7 @@
         <v>8.48499965667725</v>
       </c>
       <c r="G215" t="n">
-        <v>7.73299407958984</v>
+        <v>7.73299503326416</v>
       </c>
       <c r="H215" t="n">
         <v>190999</v>
@@ -6633,7 +6633,7 @@
         <v>8.65499973297119</v>
       </c>
       <c r="G216" t="n">
-        <v>7.88792753219604</v>
+        <v>7.88792657852173</v>
       </c>
       <c r="H216" t="n">
         <v>352185</v>
@@ -6662,7 +6662,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G217" t="n">
-        <v>7.93805265426636</v>
+        <v>7.93805313110352</v>
       </c>
       <c r="H217" t="n">
         <v>247020</v>
@@ -6691,7 +6691,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G218" t="n">
-        <v>8.0200777053833</v>
+        <v>8.02007579803467</v>
       </c>
       <c r="H218" t="n">
         <v>179237</v>
@@ -6720,7 +6720,7 @@
         <v>9.13500022888184</v>
       </c>
       <c r="G219" t="n">
-        <v>8.3253870010376</v>
+        <v>8.32538604736328</v>
       </c>
       <c r="H219" t="n">
         <v>283069</v>
@@ -6778,7 +6778,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G221" t="n">
-        <v>8.19323825836182</v>
+        <v>8.1932373046875</v>
       </c>
       <c r="H221" t="n">
         <v>194602</v>
@@ -6865,7 +6865,7 @@
         <v>8.79500007629395</v>
       </c>
       <c r="G224" t="n">
-        <v>8.0155200958252</v>
+        <v>8.01551914215088</v>
       </c>
       <c r="H224" t="n">
         <v>122024</v>
@@ -6923,7 +6923,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G226" t="n">
-        <v>7.65552711486816</v>
+        <v>7.65552806854248</v>
       </c>
       <c r="H226" t="n">
         <v>242848</v>
@@ -6981,7 +6981,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G228" t="n">
-        <v>7.71932458877563</v>
+        <v>7.71932411193848</v>
       </c>
       <c r="H228" t="n">
         <v>240482</v>
@@ -7010,7 +7010,7 @@
         <v>8.60499954223633</v>
       </c>
       <c r="G229" t="n">
-        <v>7.84235906600952</v>
+        <v>7.84235954284668</v>
       </c>
       <c r="H229" t="n">
         <v>228869</v>
@@ -7039,7 +7039,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G230" t="n">
-        <v>7.59173154830933</v>
+        <v>7.59173202514648</v>
       </c>
       <c r="H230" t="n">
         <v>175936</v>
@@ -7126,7 +7126,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G233" t="n">
-        <v>7.60084581375122</v>
+        <v>7.60084533691406</v>
       </c>
       <c r="H233" t="n">
         <v>108751</v>
@@ -7155,7 +7155,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G234" t="n">
-        <v>7.85602998733521</v>
+        <v>7.85602951049805</v>
       </c>
       <c r="H234" t="n">
         <v>185968</v>
@@ -7242,7 +7242,7 @@
         <v>8.63500022888184</v>
       </c>
       <c r="G237" t="n">
-        <v>7.86970186233521</v>
+        <v>7.86969995498657</v>
       </c>
       <c r="H237" t="n">
         <v>68684</v>
@@ -7271,7 +7271,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G238" t="n">
-        <v>7.86514377593994</v>
+        <v>7.8651442527771</v>
       </c>
       <c r="H238" t="n">
         <v>98511</v>
@@ -7329,7 +7329,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G240" t="n">
-        <v>7.61907243728638</v>
+        <v>7.61907291412354</v>
       </c>
       <c r="H240" t="n">
         <v>242480</v>
@@ -7358,7 +7358,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G241" t="n">
-        <v>6.99933958053589</v>
+        <v>6.99934005737305</v>
       </c>
       <c r="H241" t="n">
         <v>164686</v>
@@ -7416,7 +7416,7 @@
         <v>8.29500007629395</v>
       </c>
       <c r="G243" t="n">
-        <v>7.55983304977417</v>
+        <v>7.55983400344849</v>
       </c>
       <c r="H243" t="n">
         <v>179111</v>
@@ -7445,7 +7445,7 @@
         <v>8.3149995803833</v>
       </c>
       <c r="G244" t="n">
-        <v>7.5780611038208</v>
+        <v>7.57806062698364</v>
       </c>
       <c r="H244" t="n">
         <v>97069</v>
@@ -7474,7 +7474,7 @@
         <v>8.15499973297119</v>
       </c>
       <c r="G245" t="n">
-        <v>7.43224143981934</v>
+        <v>7.43224191665649</v>
       </c>
       <c r="H245" t="n">
         <v>95884</v>
@@ -7503,7 +7503,7 @@
         <v>8.49499988555908</v>
       </c>
       <c r="G246" t="n">
-        <v>7.74210786819458</v>
+        <v>7.74210739135742</v>
       </c>
       <c r="H246" t="n">
         <v>144625</v>
@@ -7532,7 +7532,7 @@
         <v>8.5649995803833</v>
       </c>
       <c r="G247" t="n">
-        <v>7.80590343475342</v>
+        <v>7.80590391159058</v>
       </c>
       <c r="H247" t="n">
         <v>190341</v>
@@ -7561,7 +7561,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G248" t="n">
-        <v>7.73755121231079</v>
+        <v>7.73755168914795</v>
       </c>
       <c r="H248" t="n">
         <v>79342</v>
@@ -7590,7 +7590,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G249" t="n">
-        <v>7.828688621521</v>
+        <v>7.82868909835815</v>
       </c>
       <c r="H249" t="n">
         <v>109003</v>
@@ -7619,7 +7619,7 @@
         <v>8.44499969482422</v>
       </c>
       <c r="G250" t="n">
-        <v>7.69653940200806</v>
+        <v>7.69653987884521</v>
       </c>
       <c r="H250" t="n">
         <v>65821</v>
@@ -7735,7 +7735,7 @@
         <v>8.64500045776367</v>
       </c>
       <c r="G254" t="n">
-        <v>7.87881469726562</v>
+        <v>7.87881374359131</v>
       </c>
       <c r="H254" t="n">
         <v>56212</v>
@@ -7909,7 +7909,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G260" t="n">
-        <v>8.87676620483398</v>
+        <v>8.8767671585083</v>
       </c>
       <c r="H260" t="n">
         <v>299785</v>
@@ -7938,7 +7938,7 @@
         <v>9.50500011444092</v>
       </c>
       <c r="G261" t="n">
-        <v>8.66259574890137</v>
+        <v>8.66259479522705</v>
       </c>
       <c r="H261" t="n">
         <v>198672</v>
@@ -7967,7 +7967,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G262" t="n">
-        <v>8.61246871948242</v>
+        <v>8.61246776580811</v>
       </c>
       <c r="H262" t="n">
         <v>78088</v>
@@ -8025,7 +8025,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G264" t="n">
-        <v>8.56689929962158</v>
+        <v>8.56690120697021</v>
       </c>
       <c r="H264" t="n">
         <v>68545</v>
@@ -8083,7 +8083,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G266" t="n">
-        <v>8.4438648223877</v>
+        <v>8.44386577606201</v>
       </c>
       <c r="H266" t="n">
         <v>56513</v>
@@ -8112,7 +8112,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G267" t="n">
-        <v>8.61246871948242</v>
+        <v>8.61246776580811</v>
       </c>
       <c r="H267" t="n">
         <v>84891</v>
@@ -8199,7 +8199,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G270" t="n">
-        <v>8.61246871948242</v>
+        <v>8.61246776580811</v>
       </c>
       <c r="H270" t="n">
         <v>91141</v>
@@ -8228,7 +8228,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G271" t="n">
-        <v>8.47576332092285</v>
+        <v>8.47576236724854</v>
       </c>
       <c r="H271" t="n">
         <v>166452</v>
@@ -8286,7 +8286,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G273" t="n">
-        <v>8.40285396575928</v>
+        <v>8.40285301208496</v>
       </c>
       <c r="H273" t="n">
         <v>52732</v>
@@ -8402,7 +8402,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G277" t="n">
-        <v>8.52133274078369</v>
+        <v>8.52133178710938</v>
       </c>
       <c r="H277" t="n">
         <v>22128</v>
@@ -8431,7 +8431,7 @@
         <v>9.66499996185303</v>
       </c>
       <c r="G278" t="n">
-        <v>8.8084135055542</v>
+        <v>8.80841445922852</v>
       </c>
       <c r="H278" t="n">
         <v>41058</v>
@@ -8489,7 +8489,7 @@
         <v>9.40499973297119</v>
       </c>
       <c r="G280" t="n">
-        <v>8.57145690917969</v>
+        <v>8.57145595550537</v>
       </c>
       <c r="H280" t="n">
         <v>67802</v>
@@ -8547,7 +8547,7 @@
         <v>9.625</v>
       </c>
       <c r="G282" t="n">
-        <v>8.77195835113525</v>
+        <v>8.77196025848389</v>
       </c>
       <c r="H282" t="n">
         <v>30701</v>
@@ -8750,7 +8750,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G289" t="n">
-        <v>8.84031200408936</v>
+        <v>8.84031105041504</v>
       </c>
       <c r="H289" t="n">
         <v>85842</v>
@@ -8779,7 +8779,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G290" t="n">
-        <v>8.70360565185547</v>
+        <v>8.70360660552979</v>
       </c>
       <c r="H290" t="n">
         <v>132044</v>
@@ -8837,7 +8837,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G292" t="n">
-        <v>8.56689929962158</v>
+        <v>8.56690120697021</v>
       </c>
       <c r="H292" t="n">
         <v>119313</v>
@@ -8924,7 +8924,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G295" t="n">
-        <v>8.60335445404053</v>
+        <v>8.60335540771484</v>
       </c>
       <c r="H295" t="n">
         <v>150159</v>
@@ -8953,7 +8953,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G296" t="n">
-        <v>8.63069629669189</v>
+        <v>8.63069725036621</v>
       </c>
       <c r="H296" t="n">
         <v>142335</v>
@@ -9011,7 +9011,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G298" t="n">
-        <v>9.04992866516113</v>
+        <v>9.04992771148682</v>
       </c>
       <c r="H298" t="n">
         <v>175620</v>
@@ -9040,7 +9040,7 @@
         <v>9.875</v>
       </c>
       <c r="G299" t="n">
-        <v>8.99980163574219</v>
+        <v>8.9998025894165</v>
       </c>
       <c r="H299" t="n">
         <v>71056</v>
@@ -9098,7 +9098,7 @@
         <v>9.625</v>
       </c>
       <c r="G301" t="n">
-        <v>8.77195835113525</v>
+        <v>8.77196025848389</v>
       </c>
       <c r="H301" t="n">
         <v>62785</v>
@@ -9127,7 +9127,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G302" t="n">
-        <v>8.59424209594727</v>
+        <v>8.59424114227295</v>
       </c>
       <c r="H302" t="n">
         <v>79466</v>
@@ -9185,7 +9185,7 @@
         <v>9.61499977111816</v>
       </c>
       <c r="G304" t="n">
-        <v>8.76284408569336</v>
+        <v>8.76284503936768</v>
       </c>
       <c r="H304" t="n">
         <v>112583</v>
@@ -9214,7 +9214,7 @@
         <v>9.51500034332275</v>
       </c>
       <c r="G305" t="n">
-        <v>8.67170810699463</v>
+        <v>8.67170906066895</v>
       </c>
       <c r="H305" t="n">
         <v>74235</v>
@@ -9243,7 +9243,7 @@
         <v>9.57499980926514</v>
       </c>
       <c r="G306" t="n">
-        <v>8.72639083862305</v>
+        <v>8.72638988494873</v>
       </c>
       <c r="H306" t="n">
         <v>170795</v>
@@ -9272,7 +9272,7 @@
         <v>9.66499996185303</v>
       </c>
       <c r="G307" t="n">
-        <v>8.8084135055542</v>
+        <v>8.80841445922852</v>
       </c>
       <c r="H307" t="n">
         <v>88814</v>
@@ -9301,7 +9301,7 @@
         <v>9.61499977111816</v>
       </c>
       <c r="G308" t="n">
-        <v>8.76284408569336</v>
+        <v>8.76284503936768</v>
       </c>
       <c r="H308" t="n">
         <v>97456</v>
@@ -9330,7 +9330,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G309" t="n">
-        <v>8.59424209594727</v>
+        <v>8.59424114227295</v>
       </c>
       <c r="H309" t="n">
         <v>55428</v>
@@ -9359,7 +9359,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G310" t="n">
-        <v>8.71272087097168</v>
+        <v>8.71271991729736</v>
       </c>
       <c r="H310" t="n">
         <v>71168</v>
@@ -9475,7 +9475,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G314" t="n">
-        <v>8.93144989013672</v>
+        <v>8.9314489364624</v>
       </c>
       <c r="H314" t="n">
         <v>79734</v>
@@ -9504,7 +9504,7 @@
         <v>9.5649995803833</v>
       </c>
       <c r="G315" t="n">
-        <v>8.71727657318115</v>
+        <v>8.71727561950684</v>
       </c>
       <c r="H315" t="n">
         <v>125012</v>
@@ -9562,7 +9562,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G317" t="n">
-        <v>8.4438648223877</v>
+        <v>8.44386577606201</v>
       </c>
       <c r="H317" t="n">
         <v>158286</v>
@@ -9591,7 +9591,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G318" t="n">
-        <v>8.32994365692139</v>
+        <v>8.32994270324707</v>
       </c>
       <c r="H318" t="n">
         <v>82760</v>
@@ -9620,7 +9620,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G319" t="n">
-        <v>8.10210132598877</v>
+        <v>8.10210037231445</v>
       </c>
       <c r="H319" t="n">
         <v>152972</v>
@@ -9678,7 +9678,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G321" t="n">
-        <v>8.26158905029297</v>
+        <v>8.26159000396729</v>
       </c>
       <c r="H321" t="n">
         <v>151215</v>
@@ -9736,7 +9736,7 @@
         <v>9.125</v>
       </c>
       <c r="G323" t="n">
-        <v>8.3162727355957</v>
+        <v>8.31627368927002</v>
       </c>
       <c r="H323" t="n">
         <v>96023</v>
@@ -9765,7 +9765,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G324" t="n">
-        <v>8.23880577087402</v>
+        <v>8.23880672454834</v>
       </c>
       <c r="H324" t="n">
         <v>125245</v>
@@ -9794,7 +9794,7 @@
         <v>9.6850004196167</v>
       </c>
       <c r="G325" t="n">
-        <v>8.82664108276367</v>
+        <v>8.82664203643799</v>
       </c>
       <c r="H325" t="n">
         <v>499802</v>
@@ -9823,7 +9823,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G326" t="n">
-        <v>8.59424209594727</v>
+        <v>8.59424114227295</v>
       </c>
       <c r="H326" t="n">
         <v>346862</v>
@@ -9881,7 +9881,7 @@
         <v>9.71500015258789</v>
       </c>
       <c r="G328" t="n">
-        <v>8.85398292541504</v>
+        <v>8.85398197174072</v>
       </c>
       <c r="H328" t="n">
         <v>220819</v>
@@ -10026,7 +10026,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G333" t="n">
-        <v>8.60335445404053</v>
+        <v>8.60335540771484</v>
       </c>
       <c r="H333" t="n">
         <v>90522</v>
@@ -10113,7 +10113,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G336" t="n">
-        <v>8.60335445404053</v>
+        <v>8.60335540771484</v>
       </c>
       <c r="H336" t="n">
         <v>169827</v>
@@ -10142,7 +10142,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G337" t="n">
-        <v>8.70360565185547</v>
+        <v>8.70360660552979</v>
       </c>
       <c r="H337" t="n">
         <v>99184</v>
@@ -10200,7 +10200,7 @@
         <v>9.36499977111816</v>
       </c>
       <c r="G339" t="n">
-        <v>8.53500080108643</v>
+        <v>8.53500175476074</v>
       </c>
       <c r="H339" t="n">
         <v>78975</v>
@@ -10229,7 +10229,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G340" t="n">
-        <v>8.64892387390137</v>
+        <v>8.64892292022705</v>
       </c>
       <c r="H340" t="n">
         <v>60887</v>
@@ -10316,7 +10316,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G343" t="n">
-        <v>8.53955936431885</v>
+        <v>8.53955841064453</v>
       </c>
       <c r="H343" t="n">
         <v>356528</v>
@@ -10345,7 +10345,7 @@
         <v>9.57499980926514</v>
       </c>
       <c r="G344" t="n">
-        <v>8.72639083862305</v>
+        <v>8.72638988494873</v>
       </c>
       <c r="H344" t="n">
         <v>48723</v>
@@ -10374,7 +10374,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G345" t="n">
-        <v>8.87676620483398</v>
+        <v>8.8767671585083</v>
       </c>
       <c r="H345" t="n">
         <v>69041</v>
@@ -10432,7 +10432,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G347" t="n">
-        <v>9.478271484375</v>
+        <v>9.47827243804932</v>
       </c>
       <c r="H347" t="n">
         <v>132689</v>
@@ -10490,7 +10490,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G349" t="n">
-        <v>9.18663311004639</v>
+        <v>9.1866340637207</v>
       </c>
       <c r="H349" t="n">
         <v>120697</v>
@@ -10519,7 +10519,7 @@
         <v>9.94499969482422</v>
       </c>
       <c r="G350" t="n">
-        <v>9.0635986328125</v>
+        <v>9.06359767913818</v>
       </c>
       <c r="H350" t="n">
         <v>113297</v>
@@ -10606,7 +10606,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G353" t="n">
-        <v>8.96790313720703</v>
+        <v>8.96790409088135</v>
       </c>
       <c r="H353" t="n">
         <v>66592</v>
@@ -10635,7 +10635,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G354" t="n">
-        <v>9.02258586883545</v>
+        <v>9.02258682250977</v>
       </c>
       <c r="H354" t="n">
         <v>58371</v>
@@ -10693,7 +10693,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G356" t="n">
-        <v>9.02258586883545</v>
+        <v>9.02258682250977</v>
       </c>
       <c r="H356" t="n">
         <v>51175</v>
@@ -10722,7 +10722,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G357" t="n">
-        <v>9.16840744018555</v>
+        <v>9.16840553283691</v>
       </c>
       <c r="H357" t="n">
         <v>43978</v>
@@ -10751,7 +10751,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G358" t="n">
-        <v>9.46915912628174</v>
+        <v>9.46916007995605</v>
       </c>
       <c r="H358" t="n">
         <v>119140</v>
@@ -10809,7 +10809,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G360" t="n">
-        <v>9.50561428070068</v>
+        <v>9.50561332702637</v>
       </c>
       <c r="H360" t="n">
         <v>54614</v>
@@ -10838,7 +10838,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G361" t="n">
-        <v>9.478271484375</v>
+        <v>9.47827243804932</v>
       </c>
       <c r="H361" t="n">
         <v>59625</v>
@@ -10954,7 +10954,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G365" t="n">
-        <v>9.33245277404785</v>
+        <v>9.33245182037354</v>
       </c>
       <c r="H365" t="n">
         <v>135405</v>
@@ -10983,7 +10983,7 @@
         <v>9.83500003814697</v>
       </c>
       <c r="G366" t="n">
-        <v>8.96334838867188</v>
+        <v>8.96334743499756</v>
       </c>
       <c r="H366" t="n">
         <v>250182</v>
@@ -11099,7 +11099,7 @@
         <v>9.40499973297119</v>
       </c>
       <c r="G370" t="n">
-        <v>8.57145690917969</v>
+        <v>8.57145595550537</v>
       </c>
       <c r="H370" t="n">
         <v>122944</v>
@@ -11215,7 +11215,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G374" t="n">
-        <v>9.10461044311523</v>
+        <v>9.10460948944092</v>
       </c>
       <c r="H374" t="n">
         <v>180858</v>
@@ -11244,7 +11244,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G375" t="n">
-        <v>9.07726860046387</v>
+        <v>9.07726955413818</v>
       </c>
       <c r="H375" t="n">
         <v>116178</v>
@@ -11273,7 +11273,7 @@
         <v>9.94499969482422</v>
       </c>
       <c r="G376" t="n">
-        <v>9.0635986328125</v>
+        <v>9.06359767913818</v>
       </c>
       <c r="H376" t="n">
         <v>50994</v>
@@ -11331,7 +11331,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G378" t="n">
-        <v>9.09549522399902</v>
+        <v>9.09549617767334</v>
       </c>
       <c r="H378" t="n">
         <v>71656</v>
@@ -11476,7 +11476,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G383" t="n">
-        <v>9.61260032653809</v>
+        <v>9.6126012802124</v>
       </c>
       <c r="H383" t="n">
         <v>186379</v>
@@ -11534,7 +11534,7 @@
         <v>10.25</v>
       </c>
       <c r="G385" t="n">
-        <v>9.46485614776611</v>
+        <v>9.46485710144043</v>
       </c>
       <c r="H385" t="n">
         <v>63321</v>
@@ -11563,7 +11563,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G386" t="n">
-        <v>9.43715572357178</v>
+        <v>9.43715381622314</v>
       </c>
       <c r="H386" t="n">
         <v>588687</v>
@@ -11650,7 +11650,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G389" t="n">
-        <v>9.64030170440674</v>
+        <v>9.64030265808105</v>
       </c>
       <c r="H389" t="n">
         <v>168078</v>
@@ -11737,7 +11737,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G392" t="n">
-        <v>9.64030170440674</v>
+        <v>9.64030265808105</v>
       </c>
       <c r="H392" t="n">
         <v>109538</v>
@@ -11766,7 +11766,7 @@
         <v>10.5</v>
       </c>
       <c r="G393" t="n">
-        <v>9.69570636749268</v>
+        <v>9.69570732116699</v>
       </c>
       <c r="H393" t="n">
         <v>63889</v>
@@ -11795,7 +11795,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G394" t="n">
-        <v>9.84345149993896</v>
+        <v>9.84345054626465</v>
       </c>
       <c r="H394" t="n">
         <v>96545</v>
@@ -11882,7 +11882,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G397" t="n">
-        <v>9.56643104553223</v>
+        <v>9.56643009185791</v>
       </c>
       <c r="H397" t="n">
         <v>124190</v>
@@ -11998,7 +11998,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G401" t="n">
-        <v>9.04932689666748</v>
+        <v>9.04932594299316</v>
       </c>
       <c r="H401" t="n">
         <v>96905</v>
@@ -12027,7 +12027,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G402" t="n">
-        <v>8.89234828948975</v>
+        <v>8.89234924316406</v>
       </c>
       <c r="H402" t="n">
         <v>66073</v>
@@ -12056,7 +12056,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G403" t="n">
-        <v>8.79539012908936</v>
+        <v>8.79539108276367</v>
       </c>
       <c r="H403" t="n">
         <v>80618</v>
@@ -12114,7 +12114,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G405" t="n">
-        <v>8.58762645721436</v>
+        <v>8.58762550354004</v>
       </c>
       <c r="H405" t="n">
         <v>464509</v>
@@ -12172,7 +12172,7 @@
         <v>9.55500030517578</v>
       </c>
       <c r="G407" t="n">
-        <v>8.82309246063232</v>
+        <v>8.82309341430664</v>
       </c>
       <c r="H407" t="n">
         <v>224972</v>
@@ -12288,7 +12288,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G411" t="n">
-        <v>8.82771110534668</v>
+        <v>8.82771015167236</v>
       </c>
       <c r="H411" t="n">
         <v>189726</v>
@@ -12346,7 +12346,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G413" t="n">
-        <v>8.42141437530518</v>
+        <v>8.42141342163086</v>
       </c>
       <c r="H413" t="n">
         <v>96990</v>
@@ -12375,7 +12375,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G414" t="n">
-        <v>8.50451946258545</v>
+        <v>8.50452041625977</v>
       </c>
       <c r="H414" t="n">
         <v>71607</v>
@@ -12462,7 +12462,7 @@
         <v>9.48499965667725</v>
       </c>
       <c r="G417" t="n">
-        <v>8.75845432281494</v>
+        <v>8.75845527648926</v>
       </c>
       <c r="H417" t="n">
         <v>166541</v>
@@ -12520,7 +12520,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G419" t="n">
-        <v>8.57839298248291</v>
+        <v>8.57839202880859</v>
       </c>
       <c r="H419" t="n">
         <v>85948</v>
@@ -12636,7 +12636,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G423" t="n">
-        <v>8.03820323944092</v>
+        <v>8.0382022857666</v>
       </c>
       <c r="H423" t="n">
         <v>208593</v>
@@ -12694,7 +12694,7 @@
         <v>8.54500007629395</v>
       </c>
       <c r="G425" t="n">
-        <v>7.89045858383179</v>
+        <v>7.89045906066895</v>
       </c>
       <c r="H425" t="n">
         <v>157771</v>
@@ -12723,7 +12723,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G426" t="n">
-        <v>7.92277669906616</v>
+        <v>7.92277717590332</v>
       </c>
       <c r="H426" t="n">
         <v>224688</v>
@@ -12752,7 +12752,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G427" t="n">
-        <v>7.82120370864868</v>
+        <v>7.82120323181152</v>
       </c>
       <c r="H427" t="n">
         <v>315397</v>
@@ -12781,7 +12781,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G428" t="n">
-        <v>7.82120370864868</v>
+        <v>7.82120323181152</v>
       </c>
       <c r="H428" t="n">
         <v>153923</v>
@@ -12810,7 +12810,7 @@
         <v>8.46500015258789</v>
       </c>
       <c r="G429" t="n">
-        <v>7.8165864944458</v>
+        <v>7.81658697128296</v>
       </c>
       <c r="H429" t="n">
         <v>124892</v>
@@ -12839,7 +12839,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G430" t="n">
-        <v>7.87660694122314</v>
+        <v>7.87660646438599</v>
       </c>
       <c r="H430" t="n">
         <v>182047</v>
@@ -12868,7 +12868,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G431" t="n">
-        <v>7.81196928024292</v>
+        <v>7.81196975708008</v>
       </c>
       <c r="H431" t="n">
         <v>211938</v>
@@ -12897,7 +12897,7 @@
         <v>8.42500019073486</v>
       </c>
       <c r="G432" t="n">
-        <v>7.77965021133423</v>
+        <v>7.77965116500854</v>
       </c>
       <c r="H432" t="n">
         <v>499662</v>
@@ -12955,7 +12955,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G434" t="n">
-        <v>7.25792932510376</v>
+        <v>7.2579288482666</v>
       </c>
       <c r="H434" t="n">
         <v>435932</v>
@@ -12984,7 +12984,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G435" t="n">
-        <v>7.06401491165161</v>
+        <v>7.06401538848877</v>
       </c>
       <c r="H435" t="n">
         <v>300120</v>
@@ -13042,7 +13042,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G437" t="n">
-        <v>7.16558933258057</v>
+        <v>7.16558885574341</v>
       </c>
       <c r="H437" t="n">
         <v>348774</v>
@@ -13071,7 +13071,7 @@
         <v>7.72499990463257</v>
       </c>
       <c r="G438" t="n">
-        <v>7.13327026367188</v>
+        <v>7.13326978683472</v>
       </c>
       <c r="H438" t="n">
         <v>174564</v>
@@ -13274,7 +13274,7 @@
         <v>7.02500009536743</v>
       </c>
       <c r="G445" t="n">
-        <v>6.48688936233521</v>
+        <v>6.48688983917236</v>
       </c>
       <c r="H445" t="n">
         <v>144224</v>
@@ -13361,7 +13361,7 @@
         <v>7.13500022888184</v>
       </c>
       <c r="G448" t="n">
-        <v>6.58846378326416</v>
+        <v>6.588463306427</v>
       </c>
       <c r="H448" t="n">
         <v>537214</v>
@@ -13506,7 +13506,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G453" t="n">
-        <v>6.88856887817383</v>
+        <v>6.88856840133667</v>
       </c>
       <c r="H453" t="n">
         <v>417380</v>
@@ -13535,7 +13535,7 @@
         <v>7.40500020980835</v>
       </c>
       <c r="G454" t="n">
-        <v>6.83778142929077</v>
+        <v>6.83778190612793</v>
       </c>
       <c r="H454" t="n">
         <v>250172</v>
@@ -13651,7 +13651,7 @@
         <v>7.09499979019165</v>
       </c>
       <c r="G458" t="n">
-        <v>6.55152702331543</v>
+        <v>6.55152750015259</v>
       </c>
       <c r="H458" t="n">
         <v>694126</v>
@@ -13796,7 +13796,7 @@
         <v>6.70499992370605</v>
       </c>
       <c r="G463" t="n">
-        <v>6.19140100479126</v>
+        <v>6.19140148162842</v>
       </c>
       <c r="H463" t="n">
         <v>303572</v>
@@ -13825,7 +13825,7 @@
         <v>6.69500017166138</v>
       </c>
       <c r="G464" t="n">
-        <v>6.18216753005981</v>
+        <v>6.18216800689697</v>
       </c>
       <c r="H464" t="n">
         <v>494430</v>
@@ -13941,7 +13941,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G468" t="n">
-        <v>5.52193593978882</v>
+        <v>5.52193546295166</v>
       </c>
       <c r="H468" t="n">
         <v>612281</v>
@@ -14086,7 +14086,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G473" t="n">
-        <v>5.5958080291748</v>
+        <v>5.59580755233765</v>
       </c>
       <c r="H473" t="n">
         <v>246202</v>
@@ -14115,7 +14115,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G474" t="n">
-        <v>5.44806385040283</v>
+        <v>5.44806337356567</v>
       </c>
       <c r="H474" t="n">
         <v>326663</v>
@@ -14144,7 +14144,7 @@
         <v>5.82499980926514</v>
       </c>
       <c r="G475" t="n">
-        <v>5.37880897521973</v>
+        <v>5.37880849838257</v>
       </c>
       <c r="H475" t="n">
         <v>758444</v>
@@ -14202,7 +14202,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G477" t="n">
-        <v>5.55887174606323</v>
+        <v>5.55887222290039</v>
       </c>
       <c r="H477" t="n">
         <v>286452</v>
@@ -14260,7 +14260,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G479" t="n">
-        <v>5.70661592483521</v>
+        <v>5.70661544799805</v>
       </c>
       <c r="H479" t="n">
         <v>248086</v>
@@ -14405,7 +14405,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G484" t="n">
-        <v>5.17104339599609</v>
+        <v>5.17104387283325</v>
       </c>
       <c r="H484" t="n">
         <v>335662</v>
@@ -14434,7 +14434,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G485" t="n">
-        <v>5.17566013336182</v>
+        <v>5.17566108703613</v>
       </c>
       <c r="H485" t="n">
         <v>433667</v>
@@ -14695,7 +14695,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G494" t="n">
-        <v>4.88478899002075</v>
+        <v>4.88478946685791</v>
       </c>
       <c r="H494" t="n">
         <v>111362</v>
@@ -14869,7 +14869,7 @@
         <v>5.69500017166138</v>
       </c>
       <c r="G500" t="n">
-        <v>5.25876665115356</v>
+        <v>5.25876712799072</v>
       </c>
       <c r="H500" t="n">
         <v>671518</v>
@@ -14985,7 +14985,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>5.44806385040283</v>
+        <v>5.44806337356567</v>
       </c>
       <c r="H504" t="n">
         <v>262185</v>
@@ -15014,7 +15014,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G505" t="n">
-        <v>5.39265966415405</v>
+        <v>5.39266014099121</v>
       </c>
       <c r="H505" t="n">
         <v>225134</v>
@@ -15159,7 +15159,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G510" t="n">
-        <v>5.21259689331055</v>
+        <v>5.21259641647339</v>
       </c>
       <c r="H510" t="n">
         <v>110937</v>
@@ -15246,7 +15246,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G513" t="n">
-        <v>5.21259689331055</v>
+        <v>5.21259641647339</v>
       </c>
       <c r="H513" t="n">
         <v>215173</v>
@@ -15275,7 +15275,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G514" t="n">
-        <v>5.17104339599609</v>
+        <v>5.17104387283325</v>
       </c>
       <c r="H514" t="n">
         <v>307201</v>
@@ -15304,7 +15304,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G515" t="n">
-        <v>5.11563920974731</v>
+        <v>5.11563968658447</v>
       </c>
       <c r="H515" t="n">
         <v>481344</v>
@@ -15623,7 +15623,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G526" t="n">
-        <v>5.44806385040283</v>
+        <v>5.44806337356567</v>
       </c>
       <c r="H526" t="n">
         <v>1071210</v>
@@ -15681,7 +15681,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G528" t="n">
-        <v>5.52193593978882</v>
+        <v>5.52193546295166</v>
       </c>
       <c r="H528" t="n">
         <v>271052</v>
@@ -15739,7 +15739,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G530" t="n">
-        <v>5.72508382797241</v>
+        <v>5.72508335113525</v>
       </c>
       <c r="H530" t="n">
         <v>604320</v>
@@ -15797,7 +15797,7 @@
         <v>6.30499982833862</v>
       </c>
       <c r="G532" t="n">
-        <v>5.82204055786133</v>
+        <v>5.82204103469849</v>
       </c>
       <c r="H532" t="n">
         <v>298757</v>
@@ -15826,7 +15826,7 @@
         <v>6.40500020980835</v>
       </c>
       <c r="G533" t="n">
-        <v>5.91438102722168</v>
+        <v>5.91438150405884</v>
       </c>
       <c r="H533" t="n">
         <v>366529</v>
@@ -15884,7 +15884,7 @@
         <v>6.2649998664856</v>
       </c>
       <c r="G535" t="n">
-        <v>5.78510522842407</v>
+        <v>5.78510475158691</v>
       </c>
       <c r="H535" t="n">
         <v>171909</v>
@@ -15942,7 +15942,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G537" t="n">
-        <v>5.52193593978882</v>
+        <v>5.52193546295166</v>
       </c>
       <c r="H537" t="n">
         <v>426609</v>
@@ -16000,7 +16000,7 @@
         <v>6.38500022888184</v>
       </c>
       <c r="G539" t="n">
-        <v>5.89591360092163</v>
+        <v>5.89591312408447</v>
       </c>
       <c r="H539" t="n">
         <v>946632</v>
@@ -16029,7 +16029,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G540" t="n">
-        <v>6.03904008865356</v>
+        <v>6.03904056549072</v>
       </c>
       <c r="H540" t="n">
         <v>416492</v>
@@ -16058,7 +16058,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G541" t="n">
-        <v>6.05750799179077</v>
+        <v>6.05750846862793</v>
       </c>
       <c r="H541" t="n">
         <v>374625</v>
@@ -16087,7 +16087,7 @@
         <v>6.57499980926514</v>
       </c>
       <c r="G542" t="n">
-        <v>6.07135915756226</v>
+        <v>6.0713586807251</v>
       </c>
       <c r="H542" t="n">
         <v>267523</v>
@@ -16145,7 +16145,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G544" t="n">
-        <v>5.86359357833862</v>
+        <v>5.86359405517578</v>
       </c>
       <c r="H544" t="n">
         <v>307396</v>
@@ -16348,7 +16348,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G551" t="n">
-        <v>5.70661592483521</v>
+        <v>5.70661544799805</v>
       </c>
       <c r="H551" t="n">
         <v>159509</v>
@@ -16377,7 +16377,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G552" t="n">
-        <v>5.70661592483521</v>
+        <v>5.70661544799805</v>
       </c>
       <c r="H552" t="n">
         <v>128983</v>
@@ -16435,7 +16435,7 @@
         <v>6.29500007629395</v>
       </c>
       <c r="G554" t="n">
-        <v>5.81280755996704</v>
+        <v>5.81280660629272</v>
       </c>
       <c r="H554" t="n">
         <v>151233</v>
@@ -16493,7 +16493,7 @@
         <v>6.06500005722046</v>
       </c>
       <c r="G556" t="n">
-        <v>5.60042476654053</v>
+        <v>5.60042524337769</v>
       </c>
       <c r="H556" t="n">
         <v>275234</v>
@@ -16551,7 +16551,7 @@
         <v>6.0149998664856</v>
       </c>
       <c r="G558" t="n">
-        <v>5.55425500869751</v>
+        <v>5.55425453186035</v>
       </c>
       <c r="H558" t="n">
         <v>206810</v>
@@ -16754,7 +16754,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G565" t="n">
-        <v>5.51270151138306</v>
+        <v>5.5127010345459</v>
       </c>
       <c r="H565" t="n">
         <v>164534</v>
@@ -16841,7 +16841,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G568" t="n">
-        <v>5.32802152633667</v>
+        <v>5.32802200317383</v>
       </c>
       <c r="H568" t="n">
         <v>253739</v>
@@ -16899,7 +16899,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G570" t="n">
-        <v>5.22644758224487</v>
+        <v>5.22644710540771</v>
       </c>
       <c r="H570" t="n">
         <v>465075</v>
@@ -16928,7 +16928,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G571" t="n">
-        <v>5.17566013336182</v>
+        <v>5.17566108703613</v>
       </c>
       <c r="H571" t="n">
         <v>188694</v>
@@ -16957,7 +16957,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G572" t="n">
-        <v>5.24029874801636</v>
+        <v>5.24029922485352</v>
       </c>
       <c r="H572" t="n">
         <v>371542</v>
@@ -16986,7 +16986,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G573" t="n">
-        <v>5.32802152633667</v>
+        <v>5.32802200317383</v>
       </c>
       <c r="H573" t="n">
         <v>246507</v>
@@ -17015,7 +17015,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G574" t="n">
-        <v>5.22644758224487</v>
+        <v>5.22644710540771</v>
       </c>
       <c r="H574" t="n">
         <v>441053</v>
@@ -17160,7 +17160,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G579" t="n">
-        <v>5.07408666610718</v>
+        <v>5.07408618927002</v>
       </c>
       <c r="H579" t="n">
         <v>256005</v>
@@ -17189,7 +17189,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G580" t="n">
-        <v>5.09717130661011</v>
+        <v>5.09717178344727</v>
       </c>
       <c r="H580" t="n">
         <v>391172</v>
@@ -17247,7 +17247,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G582" t="n">
-        <v>5.3003191947937</v>
+        <v>5.30031967163086</v>
       </c>
       <c r="H582" t="n">
         <v>1080928</v>
@@ -17392,7 +17392,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G587" t="n">
-        <v>5.57733917236328</v>
+        <v>5.57733964920044</v>
       </c>
       <c r="H587" t="n">
         <v>394516</v>
@@ -17421,7 +17421,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G588" t="n">
-        <v>5.5958080291748</v>
+        <v>5.59580755233765</v>
       </c>
       <c r="H588" t="n">
         <v>428003</v>
@@ -17450,7 +17450,7 @@
         <v>6.06500005722046</v>
       </c>
       <c r="G589" t="n">
-        <v>5.60042476654053</v>
+        <v>5.60042524337769</v>
       </c>
       <c r="H589" t="n">
         <v>462275</v>
@@ -17508,7 +17508,7 @@
         <v>5.53499984741211</v>
       </c>
       <c r="G591" t="n">
-        <v>5.11102199554443</v>
+        <v>5.11102247238159</v>
       </c>
       <c r="H591" t="n">
         <v>899330</v>
@@ -17566,7 +17566,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G593" t="n">
-        <v>5.39265966415405</v>
+        <v>5.39266014099121</v>
       </c>
       <c r="H593" t="n">
         <v>558485</v>
@@ -17595,7 +17595,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G594" t="n">
-        <v>5.05100107192993</v>
+        <v>5.05100154876709</v>
       </c>
       <c r="H594" t="n">
         <v>677677</v>
@@ -17624,7 +17624,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>4.92172574996948</v>
+        <v>4.92172527313232</v>
       </c>
       <c r="H595" t="n">
         <v>699777</v>
@@ -17711,7 +17711,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G598" t="n">
-        <v>4.80630016326904</v>
+        <v>4.8063006401062</v>
       </c>
       <c r="H598" t="n">
         <v>332805</v>
@@ -17827,7 +17827,7 @@
         <v>5.22499990463257</v>
       </c>
       <c r="G602" t="n">
-        <v>4.82476854324341</v>
+        <v>4.82476806640625</v>
       </c>
       <c r="H602" t="n">
         <v>549261</v>
@@ -17885,7 +17885,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>4.80630016326904</v>
+        <v>4.8063006401062</v>
       </c>
       <c r="H604" t="n">
         <v>321087</v>
@@ -17943,7 +17943,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>4.52466344833374</v>
+        <v>4.52466297149658</v>
       </c>
       <c r="H606" t="n">
         <v>835466</v>
@@ -17972,7 +17972,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G607" t="n">
-        <v>4.52466344833374</v>
+        <v>4.52466297149658</v>
       </c>
       <c r="H607" t="n">
         <v>662577</v>
@@ -18001,7 +18001,7 @@
         <v>4.82200002670288</v>
       </c>
       <c r="G608" t="n">
-        <v>4.45263767242432</v>
+        <v>4.45263814926147</v>
       </c>
       <c r="H608" t="n">
         <v>597938</v>
@@ -18030,7 +18030,7 @@
         <v>4.70800018310547</v>
       </c>
       <c r="G609" t="n">
-        <v>4.34737062454224</v>
+        <v>4.34737014770508</v>
       </c>
       <c r="H609" t="n">
         <v>838204</v>
@@ -18059,7 +18059,7 @@
         <v>4.66400003433228</v>
       </c>
       <c r="G610" t="n">
-        <v>4.30674028396606</v>
+        <v>4.30674076080322</v>
       </c>
       <c r="H610" t="n">
         <v>394307</v>
@@ -18146,7 +18146,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G613" t="n">
-        <v>4.37691879272461</v>
+        <v>4.37691926956177</v>
       </c>
       <c r="H613" t="n">
         <v>380449</v>
@@ -18204,7 +18204,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G615" t="n">
-        <v>4.37691879272461</v>
+        <v>4.37691926956177</v>
       </c>
       <c r="H615" t="n">
         <v>510752</v>
@@ -18262,7 +18262,7 @@
         <v>4.96600008010864</v>
       </c>
       <c r="G617" t="n">
-        <v>4.58560800552368</v>
+        <v>4.58560752868652</v>
       </c>
       <c r="H617" t="n">
         <v>558256</v>
@@ -18291,7 +18291,7 @@
         <v>5</v>
       </c>
       <c r="G618" t="n">
-        <v>4.61700296401978</v>
+        <v>4.61700344085693</v>
       </c>
       <c r="H618" t="n">
         <v>694400</v>
@@ -18378,7 +18378,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G621" t="n">
-        <v>4.56898593902588</v>
+        <v>4.56898641586304</v>
       </c>
       <c r="H621" t="n">
         <v>377386</v>
@@ -18436,7 +18436,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G623" t="n">
-        <v>4.7970666885376</v>
+        <v>4.79706621170044</v>
       </c>
       <c r="H623" t="n">
         <v>817405</v>
@@ -18552,7 +18552,7 @@
         <v>4.97800016403198</v>
       </c>
       <c r="G627" t="n">
-        <v>4.59668827056885</v>
+        <v>4.59668874740601</v>
       </c>
       <c r="H627" t="n">
         <v>698215</v>
@@ -18726,7 +18726,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G633" t="n">
-        <v>4.63421249389648</v>
+        <v>4.63421201705933</v>
       </c>
       <c r="H633" t="n">
         <v>659569</v>
@@ -18900,7 +18900,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G639" t="n">
-        <v>4.47546625137329</v>
+        <v>4.47546672821045</v>
       </c>
       <c r="H639" t="n">
         <v>721270</v>
@@ -18929,7 +18929,7 @@
         <v>4.81199979782104</v>
       </c>
       <c r="G640" t="n">
-        <v>4.60169744491577</v>
+        <v>4.60169792175293</v>
       </c>
       <c r="H640" t="n">
         <v>409298</v>
@@ -19074,7 +19074,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G645" t="n">
-        <v>4.45634078979492</v>
+        <v>4.45634031295776</v>
       </c>
       <c r="H645" t="n">
         <v>337361</v>
@@ -19132,7 +19132,7 @@
         <v>4.62400007247925</v>
       </c>
       <c r="G647" t="n">
-        <v>4.42191410064697</v>
+        <v>4.42191457748413</v>
       </c>
       <c r="H647" t="n">
         <v>590963</v>
@@ -19219,7 +19219,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G650" t="n">
-        <v>4.17136478424072</v>
+        <v>4.17136430740356</v>
       </c>
       <c r="H650" t="n">
         <v>575556</v>
@@ -19306,7 +19306,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G653" t="n">
-        <v>4.20770406723022</v>
+        <v>4.20770359039307</v>
       </c>
       <c r="H653" t="n">
         <v>253568</v>
@@ -19480,7 +19480,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G659" t="n">
-        <v>3.93037796020508</v>
+        <v>3.9303777217865</v>
       </c>
       <c r="H659" t="n">
         <v>499794</v>
@@ -19770,7 +19770,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G669" t="n">
-        <v>3.65496468544006</v>
+        <v>3.65496444702148</v>
       </c>
       <c r="H669" t="n">
         <v>556073</v>
@@ -19857,7 +19857,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G672" t="n">
-        <v>3.81370949745178</v>
+        <v>3.81370973587036</v>
       </c>
       <c r="H672" t="n">
         <v>401105</v>
@@ -19886,7 +19886,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G673" t="n">
-        <v>3.81370949745178</v>
+        <v>3.81370973587036</v>
       </c>
       <c r="H673" t="n">
         <v>294689</v>
@@ -19915,7 +19915,7 @@
         <v>4.17600011825562</v>
       </c>
       <c r="G674" t="n">
-        <v>3.99349355697632</v>
+        <v>3.99349331855774</v>
       </c>
       <c r="H674" t="n">
         <v>714573</v>
@@ -20379,7 +20379,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G690" t="n">
-        <v>3.45605492591858</v>
+        <v>3.4560546875</v>
       </c>
       <c r="H690" t="n">
         <v>383156</v>
@@ -20756,7 +20756,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G703" t="n">
-        <v>3.96862959861755</v>
+        <v>3.96862983703613</v>
       </c>
       <c r="H703" t="n">
         <v>402206</v>
@@ -20785,7 +20785,7 @@
         <v>4.1560001373291</v>
       </c>
       <c r="G704" t="n">
-        <v>3.97436785697937</v>
+        <v>3.97436738014221</v>
       </c>
       <c r="H704" t="n">
         <v>366565</v>
@@ -20843,7 +20843,7 @@
         <v>4.27600002288818</v>
       </c>
       <c r="G706" t="n">
-        <v>4.0891227722168</v>
+        <v>4.08912324905396</v>
       </c>
       <c r="H706" t="n">
         <v>382472</v>
@@ -20872,7 +20872,7 @@
         <v>4.13600015640259</v>
       </c>
       <c r="G707" t="n">
-        <v>3.95524168014526</v>
+        <v>3.95524144172668</v>
       </c>
       <c r="H707" t="n">
         <v>503313</v>
@@ -20930,7 +20930,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G709" t="n">
-        <v>3.98966813087463</v>
+        <v>3.98966789245605</v>
       </c>
       <c r="H709" t="n">
         <v>357159</v>
@@ -21017,7 +21017,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G712" t="n">
-        <v>3.67026519775391</v>
+        <v>3.67026543617249</v>
       </c>
       <c r="H712" t="n">
         <v>437455</v>
@@ -21162,7 +21162,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G717" t="n">
-        <v>3.81370949745178</v>
+        <v>3.81370973587036</v>
       </c>
       <c r="H717" t="n">
         <v>286225</v>
@@ -21191,7 +21191,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G718" t="n">
-        <v>3.82327270507812</v>
+        <v>3.82327246665955</v>
       </c>
       <c r="H718" t="n">
         <v>150642</v>
@@ -21220,7 +21220,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G719" t="n">
-        <v>3.91507697105408</v>
+        <v>3.91507720947266</v>
       </c>
       <c r="H719" t="n">
         <v>372351</v>
@@ -21307,7 +21307,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G722" t="n">
-        <v>3.98584294319153</v>
+        <v>3.98584318161011</v>
       </c>
       <c r="H722" t="n">
         <v>634315</v>
@@ -21365,7 +21365,7 @@
         <v>4.42600011825562</v>
       </c>
       <c r="G724" t="n">
-        <v>4.23256778717041</v>
+        <v>4.23256731033325</v>
       </c>
       <c r="H724" t="n">
         <v>1439555</v>
@@ -21394,7 +21394,7 @@
         <v>4.51200008392334</v>
       </c>
       <c r="G725" t="n">
-        <v>4.31480884552002</v>
+        <v>4.31480932235718</v>
       </c>
       <c r="H725" t="n">
         <v>724657</v>
@@ -21452,7 +21452,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G727" t="n">
-        <v>4.15032625198364</v>
+        <v>4.15032577514648</v>
       </c>
       <c r="H727" t="n">
         <v>336308</v>
@@ -21510,7 +21510,7 @@
         <v>4.25</v>
       </c>
       <c r="G729" t="n">
-        <v>4.06425905227661</v>
+        <v>4.06425952911377</v>
       </c>
       <c r="H729" t="n">
         <v>168991</v>
@@ -21597,7 +21597,7 @@
         <v>4.2039999961853</v>
       </c>
       <c r="G732" t="n">
-        <v>4.0202693939209</v>
+        <v>4.02026987075806</v>
       </c>
       <c r="H732" t="n">
         <v>193502</v>
@@ -21742,7 +21742,7 @@
         <v>4.11399984359741</v>
       </c>
       <c r="G737" t="n">
-        <v>3.93420267105103</v>
+        <v>3.9342029094696</v>
       </c>
       <c r="H737" t="n">
         <v>129269</v>
@@ -21829,7 +21829,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G740" t="n">
-        <v>3.96862959861755</v>
+        <v>3.96862983703613</v>
       </c>
       <c r="H740" t="n">
         <v>236046</v>
@@ -21858,7 +21858,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G741" t="n">
-        <v>3.91507697105408</v>
+        <v>3.91507720947266</v>
       </c>
       <c r="H741" t="n">
         <v>182762</v>
@@ -22061,7 +22061,7 @@
         <v>3.90799999237061</v>
       </c>
       <c r="G748" t="n">
-        <v>3.73720574378967</v>
+        <v>3.73720598220825</v>
       </c>
       <c r="H748" t="n">
         <v>191909</v>
@@ -22119,7 +22119,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G750" t="n">
-        <v>3.70086669921875</v>
+        <v>3.70086646080017</v>
       </c>
       <c r="H750" t="n">
         <v>77185</v>
@@ -22148,7 +22148,7 @@
         <v>3.93799996376038</v>
       </c>
       <c r="G751" t="n">
-        <v>3.76589488983154</v>
+        <v>3.76589465141296</v>
       </c>
       <c r="H751" t="n">
         <v>138045</v>
@@ -22264,7 +22264,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G755" t="n">
-        <v>3.73911881446838</v>
+        <v>3.7391185760498</v>
       </c>
       <c r="H755" t="n">
         <v>208777</v>
@@ -22380,7 +22380,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G759" t="n">
-        <v>3.57846093177795</v>
+        <v>3.57846069335938</v>
       </c>
       <c r="H759" t="n">
         <v>337584</v>
@@ -22409,7 +22409,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G760" t="n">
-        <v>3.62245059013367</v>
+        <v>3.62245035171509</v>
       </c>
       <c r="H760" t="n">
         <v>422072</v>
@@ -22467,7 +22467,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G762" t="n">
-        <v>3.56315994262695</v>
+        <v>3.56316018104553</v>
       </c>
       <c r="H762" t="n">
         <v>704289</v>
@@ -22496,7 +22496,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G763" t="n">
-        <v>3.54785919189453</v>
+        <v>3.54785943031311</v>
       </c>
       <c r="H763" t="n">
         <v>1097480</v>
@@ -22583,7 +22583,7 @@
         <v>3.64800000190735</v>
       </c>
       <c r="G766" t="n">
-        <v>3.48856902122498</v>
+        <v>3.4885687828064</v>
       </c>
       <c r="H766" t="n">
         <v>1669355</v>
@@ -22728,7 +22728,7 @@
         <v>3.64400005340576</v>
       </c>
       <c r="G771" t="n">
-        <v>3.48474359512329</v>
+        <v>3.48474383354187</v>
       </c>
       <c r="H771" t="n">
         <v>105519</v>
@@ -22757,7 +22757,7 @@
         <v>3.63199996948242</v>
       </c>
       <c r="G772" t="n">
-        <v>3.47326827049255</v>
+        <v>3.47326803207397</v>
       </c>
       <c r="H772" t="n">
         <v>121534</v>
@@ -22873,7 +22873,7 @@
         <v>3.95799994468689</v>
       </c>
       <c r="G776" t="n">
-        <v>3.78502082824707</v>
+        <v>3.78502058982849</v>
       </c>
       <c r="H776" t="n">
         <v>243650</v>
@@ -22902,7 +22902,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G777" t="n">
-        <v>3.76971983909607</v>
+        <v>3.76972007751465</v>
       </c>
       <c r="H777" t="n">
         <v>111182</v>
@@ -22960,7 +22960,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G779" t="n">
-        <v>3.70086669921875</v>
+        <v>3.70086646080017</v>
       </c>
       <c r="H779" t="n">
         <v>145693</v>
@@ -22989,7 +22989,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G780" t="n">
-        <v>3.59758687019348</v>
+        <v>3.5975866317749</v>
       </c>
       <c r="H780" t="n">
         <v>157659</v>
@@ -23076,7 +23076,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G783" t="n">
-        <v>3.44075393676758</v>
+        <v>3.44075417518616</v>
       </c>
       <c r="H783" t="n">
         <v>613580</v>
@@ -23105,7 +23105,7 @@
         <v>3.41599988937378</v>
       </c>
       <c r="G784" t="n">
-        <v>3.26670813560486</v>
+        <v>3.26670789718628</v>
       </c>
       <c r="H784" t="n">
         <v>455535</v>
@@ -23134,7 +23134,7 @@
         <v>3.41599988937378</v>
       </c>
       <c r="G785" t="n">
-        <v>3.26670813560486</v>
+        <v>3.26670789718628</v>
       </c>
       <c r="H785" t="n">
         <v>519347</v>
@@ -23163,7 +23163,7 @@
         <v>3.46799993515015</v>
       </c>
       <c r="G786" t="n">
-        <v>3.31643533706665</v>
+        <v>3.31643557548523</v>
       </c>
       <c r="H786" t="n">
         <v>202674</v>
@@ -23192,7 +23192,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G787" t="n">
-        <v>3.29157161712646</v>
+        <v>3.29157185554504</v>
       </c>
       <c r="H787" t="n">
         <v>188696</v>
@@ -23424,7 +23424,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G795" t="n">
-        <v>3.20741772651672</v>
+        <v>3.2074179649353</v>
       </c>
       <c r="H795" t="n">
         <v>383770</v>
@@ -23801,7 +23801,7 @@
         <v>3.47399997711182</v>
       </c>
       <c r="G808" t="n">
-        <v>3.32217335700989</v>
+        <v>3.32217311859131</v>
       </c>
       <c r="H808" t="n">
         <v>80720</v>
@@ -23975,7 +23975,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G814" t="n">
-        <v>3.22654366493225</v>
+        <v>3.22654390335083</v>
       </c>
       <c r="H814" t="n">
         <v>115313</v>
@@ -24149,7 +24149,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G820" t="n">
-        <v>3.55168461799622</v>
+        <v>3.55168437957764</v>
       </c>
       <c r="H820" t="n">
         <v>1031313</v>
@@ -24178,7 +24178,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G821" t="n">
-        <v>3.5076949596405</v>
+        <v>3.50769472122192</v>
       </c>
       <c r="H821" t="n">
         <v>354331</v>
@@ -24236,7 +24236,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G823" t="n">
-        <v>3.53638362884521</v>
+        <v>3.53638386726379</v>
       </c>
       <c r="H823" t="n">
         <v>421877</v>
@@ -24323,7 +24323,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G826" t="n">
-        <v>3.58228588104248</v>
+        <v>3.58228611946106</v>
       </c>
       <c r="H826" t="n">
         <v>258986</v>
@@ -24352,7 +24352,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G827" t="n">
-        <v>3.5765483379364</v>
+        <v>3.57654809951782</v>
       </c>
       <c r="H827" t="n">
         <v>166129</v>
@@ -24381,7 +24381,7 @@
         <v>3.84400010108948</v>
       </c>
       <c r="G828" t="n">
-        <v>3.67600321769714</v>
+        <v>3.67600297927856</v>
       </c>
       <c r="H828" t="n">
         <v>474129</v>
@@ -24526,7 +24526,7 @@
         <v>4.22599983215332</v>
       </c>
       <c r="G833" t="n">
-        <v>4.04130792617798</v>
+        <v>4.04130840301514</v>
       </c>
       <c r="H833" t="n">
         <v>2312238</v>
@@ -24758,7 +24758,7 @@
         <v>4.68599987030029</v>
       </c>
       <c r="G841" t="n">
-        <v>4.48120450973511</v>
+        <v>4.48120403289795</v>
       </c>
       <c r="H841" t="n">
         <v>337090</v>
@@ -24816,7 +24816,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G843" t="n">
-        <v>4.54432010650635</v>
+        <v>4.54431962966919</v>
       </c>
       <c r="H843" t="n">
         <v>212793</v>
@@ -24903,7 +24903,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G846" t="n">
-        <v>4.35688591003418</v>
+        <v>4.35688638687134</v>
       </c>
       <c r="H846" t="n">
         <v>178453</v>
@@ -24932,7 +24932,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G847" t="n">
-        <v>4.26316928863525</v>
+        <v>4.2631688117981</v>
       </c>
       <c r="H847" t="n">
         <v>228223</v>
@@ -24990,7 +24990,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G849" t="n">
-        <v>4.17136478424072</v>
+        <v>4.17136430740356</v>
       </c>
       <c r="H849" t="n">
         <v>216742</v>
@@ -25048,7 +25048,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G851" t="n">
-        <v>3.93037796020508</v>
+        <v>3.9303777217865</v>
       </c>
       <c r="H851" t="n">
         <v>187268</v>
@@ -25135,7 +25135,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G854" t="n">
-        <v>3.77928280830383</v>
+        <v>3.77928304672241</v>
       </c>
       <c r="H854" t="n">
         <v>245578</v>
@@ -25251,7 +25251,7 @@
         <v>3.51200008392334</v>
       </c>
       <c r="G858" t="n">
-        <v>3.35851263999939</v>
+        <v>3.35851287841797</v>
       </c>
       <c r="H858" t="n">
         <v>146055</v>
@@ -25280,7 +25280,7 @@
         <v>3.56800007820129</v>
       </c>
       <c r="G859" t="n">
-        <v>3.41206526756287</v>
+        <v>3.41206550598145</v>
       </c>
       <c r="H859" t="n">
         <v>419236</v>
@@ -25396,7 +25396,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G863" t="n">
-        <v>3.47900581359863</v>
+        <v>3.47900605201721</v>
       </c>
       <c r="H863" t="n">
         <v>215914</v>
@@ -25541,7 +25541,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G868" t="n">
-        <v>3.77928280830383</v>
+        <v>3.77928304672241</v>
       </c>
       <c r="H868" t="n">
         <v>73720</v>
@@ -25657,7 +25657,7 @@
         <v>4.12400007247925</v>
       </c>
       <c r="G872" t="n">
-        <v>3.94376587867737</v>
+        <v>3.94376611709595</v>
       </c>
       <c r="H872" t="n">
         <v>191569</v>
@@ -25860,7 +25860,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G879" t="n">
-        <v>4.47546625137329</v>
+        <v>4.47546672821045</v>
       </c>
       <c r="H879" t="n">
         <v>120035</v>
@@ -25976,7 +25976,7 @@
         <v>4.38800001144409</v>
       </c>
       <c r="G883" t="n">
-        <v>4.19622850418091</v>
+        <v>4.19622802734375</v>
       </c>
       <c r="H883" t="n">
         <v>292289</v>
@@ -26063,7 +26063,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G886" t="n">
-        <v>4.20196580886841</v>
+        <v>4.20196628570557</v>
       </c>
       <c r="H886" t="n">
         <v>132141</v>
@@ -26237,7 +26237,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G892" t="n">
-        <v>4.57109689712524</v>
+        <v>4.57109642028809</v>
       </c>
       <c r="H892" t="n">
         <v>407750</v>
@@ -26295,7 +26295,7 @@
         <v>4.74599981307983</v>
       </c>
       <c r="G894" t="n">
-        <v>4.53858184814453</v>
+        <v>4.53858232498169</v>
       </c>
       <c r="H894" t="n">
         <v>111758</v>
@@ -26324,7 +26324,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G895" t="n">
-        <v>4.68585205078125</v>
+        <v>4.68585157394409</v>
       </c>
       <c r="H895" t="n">
         <v>288639</v>
@@ -36506,9 +36506,38 @@
         <v>3.34200000762939</v>
       </c>
       <c r="H1246" t="n">
-        <v>164232</v>
+        <v>165849</v>
       </c>
       <c r="I1246" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1247" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1247" t="n">
+        <v>3.3840000629425</v>
+      </c>
+      <c r="D1247" t="n">
+        <v>3.3840000629425</v>
+      </c>
+      <c r="E1247" t="n">
+        <v>3.25999999046326</v>
+      </c>
+      <c r="F1247" t="n">
+        <v>3.28399991989136</v>
+      </c>
+      <c r="G1247" t="n">
+        <v>3.28399991989136</v>
+      </c>
+      <c r="H1247" t="n">
+        <v>463697</v>
+      </c>
+      <c r="I1247" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ARIS.MI.xlsx
+++ b/data/ARIS.MI.xlsx
@@ -456,7 +456,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G3" t="n">
-        <v>9.34524345397949</v>
+        <v>9.34524440765381</v>
       </c>
       <c r="H3" t="n">
         <v>1460667</v>
@@ -485,7 +485,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G4" t="n">
-        <v>9.17451286315918</v>
+        <v>9.1745138168335</v>
       </c>
       <c r="H4" t="n">
         <v>732483</v>
@@ -514,7 +514,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G5" t="n">
-        <v>9.25538539886475</v>
+        <v>9.25538635253906</v>
       </c>
       <c r="H5" t="n">
         <v>304924</v>
@@ -630,7 +630,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G9" t="n">
-        <v>9.21944236755371</v>
+        <v>9.21944332122803</v>
       </c>
       <c r="H9" t="n">
         <v>203801</v>
@@ -804,7 +804,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G15" t="n">
-        <v>9.21944236755371</v>
+        <v>9.21944332122803</v>
       </c>
       <c r="H15" t="n">
         <v>184724</v>
@@ -833,7 +833,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G16" t="n">
-        <v>8.92291164398193</v>
+        <v>8.92291069030762</v>
       </c>
       <c r="H16" t="n">
         <v>312158</v>
@@ -862,7 +862,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G17" t="n">
-        <v>8.83305263519287</v>
+        <v>8.83305358886719</v>
       </c>
       <c r="H17" t="n">
         <v>156842</v>
@@ -920,7 +920,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G19" t="n">
-        <v>8.71623706817627</v>
+        <v>8.71623802185059</v>
       </c>
       <c r="H19" t="n">
         <v>172790</v>
@@ -949,7 +949,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G20" t="n">
-        <v>9.12958526611328</v>
+        <v>9.12958335876465</v>
       </c>
       <c r="H20" t="n">
         <v>431091</v>
@@ -978,7 +978,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G21" t="n">
-        <v>9.07567024230957</v>
+        <v>9.07566928863525</v>
       </c>
       <c r="H21" t="n">
         <v>404417</v>
@@ -1036,7 +1036,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G23" t="n">
-        <v>9.07567024230957</v>
+        <v>9.07566928863525</v>
       </c>
       <c r="H23" t="n">
         <v>179305</v>
@@ -1065,7 +1065,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G24" t="n">
-        <v>9.12958526611328</v>
+        <v>9.12958335876465</v>
       </c>
       <c r="H24" t="n">
         <v>61464</v>
@@ -1123,7 +1123,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G26" t="n">
-        <v>9.12958526611328</v>
+        <v>9.12958335876465</v>
       </c>
       <c r="H26" t="n">
         <v>53953</v>
@@ -1152,7 +1152,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G27" t="n">
-        <v>9.50698947906494</v>
+        <v>9.50698852539062</v>
       </c>
       <c r="H27" t="n">
         <v>542115</v>
@@ -1297,7 +1297,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G32" t="n">
-        <v>9.17451286315918</v>
+        <v>9.1745138168335</v>
       </c>
       <c r="H32" t="n">
         <v>405173</v>
@@ -1326,7 +1326,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G33" t="n">
-        <v>9.63279056549072</v>
+        <v>9.63279151916504</v>
       </c>
       <c r="H33" t="n">
         <v>261751</v>
@@ -1355,7 +1355,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G34" t="n">
-        <v>10.0191793441772</v>
+        <v>10.0191802978516</v>
       </c>
       <c r="H34" t="n">
         <v>509719</v>
@@ -1384,7 +1384,7 @@
         <v>10.9899997711182</v>
       </c>
       <c r="G35" t="n">
-        <v>9.87540626525879</v>
+        <v>9.87540721893311</v>
       </c>
       <c r="H35" t="n">
         <v>209128</v>
@@ -1413,7 +1413,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G36" t="n">
-        <v>10.1988954544067</v>
+        <v>10.1988973617554</v>
       </c>
       <c r="H36" t="n">
         <v>477707</v>
@@ -1529,7 +1529,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G40" t="n">
-        <v>9.67772006988525</v>
+        <v>9.67771911621094</v>
       </c>
       <c r="H40" t="n">
         <v>103333</v>
@@ -1587,7 +1587,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G42" t="n">
-        <v>9.10262680053711</v>
+        <v>9.10262775421143</v>
       </c>
       <c r="H42" t="n">
         <v>130467</v>
@@ -1616,7 +1616,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G43" t="n">
-        <v>9.17451286315918</v>
+        <v>9.1745138168335</v>
       </c>
       <c r="H43" t="n">
         <v>290667</v>
@@ -1674,7 +1674,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G45" t="n">
-        <v>9.0487117767334</v>
+        <v>9.04871273040771</v>
       </c>
       <c r="H45" t="n">
         <v>274213</v>
@@ -1732,7 +1732,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G47" t="n">
-        <v>9.34524345397949</v>
+        <v>9.34524440765381</v>
       </c>
       <c r="H47" t="n">
         <v>331892</v>
@@ -1790,7 +1790,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G49" t="n">
-        <v>9.34524345397949</v>
+        <v>9.34524440765381</v>
       </c>
       <c r="H49" t="n">
         <v>164923</v>
@@ -1848,7 +1848,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G51" t="n">
-        <v>9.16552829742432</v>
+        <v>9.16552734375</v>
       </c>
       <c r="H51" t="n">
         <v>170220</v>
@@ -1877,7 +1877,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G52" t="n">
-        <v>9.12958526611328</v>
+        <v>9.12958335876465</v>
       </c>
       <c r="H52" t="n">
         <v>73644</v>
@@ -1935,7 +1935,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G54" t="n">
-        <v>9.16552829742432</v>
+        <v>9.16552734375</v>
       </c>
       <c r="H54" t="n">
         <v>213651</v>
@@ -1964,7 +1964,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G55" t="n">
-        <v>8.99479866027832</v>
+        <v>8.994797706604</v>
       </c>
       <c r="H55" t="n">
         <v>276782</v>
@@ -2022,7 +2022,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G57" t="n">
-        <v>9.10262680053711</v>
+        <v>9.10262775421143</v>
       </c>
       <c r="H57" t="n">
         <v>123193</v>
@@ -2051,7 +2051,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G58" t="n">
-        <v>8.99479866027832</v>
+        <v>8.994797706604</v>
       </c>
       <c r="H58" t="n">
         <v>253397</v>
@@ -2080,7 +2080,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G59" t="n">
-        <v>9.19248580932617</v>
+        <v>9.19248485565186</v>
       </c>
       <c r="H59" t="n">
         <v>486352</v>
@@ -2138,7 +2138,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G61" t="n">
-        <v>8.71623706817627</v>
+        <v>8.71623802185059</v>
       </c>
       <c r="H61" t="n">
         <v>224870</v>
@@ -2167,7 +2167,7 @@
         <v>9.41499996185303</v>
       </c>
       <c r="G62" t="n">
-        <v>8.4601411819458</v>
+        <v>8.46014213562012</v>
       </c>
       <c r="H62" t="n">
         <v>251208</v>
@@ -2283,7 +2283,7 @@
         <v>9.20499992370605</v>
       </c>
       <c r="G66" t="n">
-        <v>8.27144050598145</v>
+        <v>8.27143955230713</v>
       </c>
       <c r="H66" t="n">
         <v>126081</v>
@@ -2312,7 +2312,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G67" t="n">
-        <v>7.70982551574707</v>
+        <v>7.70982646942139</v>
       </c>
       <c r="H67" t="n">
         <v>139521</v>
@@ -2370,7 +2370,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G69" t="n">
-        <v>7.95244264602661</v>
+        <v>7.95244312286377</v>
       </c>
       <c r="H69" t="n">
         <v>230882</v>
@@ -2428,7 +2428,7 @@
         <v>8</v>
       </c>
       <c r="G71" t="n">
-        <v>7.18864917755127</v>
+        <v>7.18864965438843</v>
       </c>
       <c r="H71" t="n">
         <v>192401</v>
@@ -2457,7 +2457,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G72" t="n">
-        <v>7.42228078842163</v>
+        <v>7.42228126525879</v>
       </c>
       <c r="H72" t="n">
         <v>235581</v>
@@ -2486,7 +2486,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G73" t="n">
-        <v>7.79069852828979</v>
+        <v>7.79069900512695</v>
       </c>
       <c r="H73" t="n">
         <v>361935</v>
@@ -2544,7 +2544,7 @@
         <v>8.78499984741211</v>
       </c>
       <c r="G75" t="n">
-        <v>7.89403486251831</v>
+        <v>7.89403581619263</v>
       </c>
       <c r="H75" t="n">
         <v>220029</v>
@@ -2573,7 +2573,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G76" t="n">
-        <v>8.66232204437256</v>
+        <v>8.66232299804688</v>
       </c>
       <c r="H76" t="n">
         <v>544195</v>
@@ -2689,7 +2689,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G80" t="n">
-        <v>9.19248580932617</v>
+        <v>9.19248485565186</v>
       </c>
       <c r="H80" t="n">
         <v>1158996</v>
@@ -2718,7 +2718,7 @@
         <v>9.71500015258789</v>
       </c>
       <c r="G81" t="n">
-        <v>8.72971630096436</v>
+        <v>8.72971725463867</v>
       </c>
       <c r="H81" t="n">
         <v>221597</v>
@@ -2747,7 +2747,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G82" t="n">
-        <v>9.07567024230957</v>
+        <v>9.07566928863525</v>
       </c>
       <c r="H82" t="n">
         <v>174088</v>
@@ -2805,7 +2805,7 @@
         <v>9.48499965667725</v>
       </c>
       <c r="G84" t="n">
-        <v>8.52304267883301</v>
+        <v>8.52304172515869</v>
       </c>
       <c r="H84" t="n">
         <v>211192</v>
@@ -2863,7 +2863,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G86" t="n">
-        <v>8.55898571014404</v>
+        <v>8.55898475646973</v>
       </c>
       <c r="H86" t="n">
         <v>136560</v>
@@ -2892,7 +2892,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G87" t="n">
-        <v>8.67130851745605</v>
+        <v>8.67130756378174</v>
       </c>
       <c r="H87" t="n">
         <v>120344</v>
@@ -2921,7 +2921,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G88" t="n">
-        <v>8.80609512329102</v>
+        <v>8.80609607696533</v>
       </c>
       <c r="H88" t="n">
         <v>104006</v>
@@ -2950,7 +2950,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G89" t="n">
-        <v>8.50057792663574</v>
+        <v>8.50057697296143</v>
       </c>
       <c r="H89" t="n">
         <v>95717</v>
@@ -2979,7 +2979,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G90" t="n">
-        <v>8.55898571014404</v>
+        <v>8.55898475646973</v>
       </c>
       <c r="H90" t="n">
         <v>75199</v>
@@ -3037,7 +3037,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G92" t="n">
-        <v>8.71623706817627</v>
+        <v>8.71623802185059</v>
       </c>
       <c r="H92" t="n">
         <v>223170</v>
@@ -3066,7 +3066,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G93" t="n">
-        <v>8.50057792663574</v>
+        <v>8.50057697296143</v>
       </c>
       <c r="H93" t="n">
         <v>181323</v>
@@ -3095,7 +3095,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G94" t="n">
-        <v>8.18607425689697</v>
+        <v>8.18607521057129</v>
       </c>
       <c r="H94" t="n">
         <v>173589</v>
@@ -3124,7 +3124,7 @@
         <v>9.25</v>
       </c>
       <c r="G95" t="n">
-        <v>8.31187629699707</v>
+        <v>8.31187534332275</v>
       </c>
       <c r="H95" t="n">
         <v>70088</v>
@@ -3182,7 +3182,7 @@
         <v>9.25</v>
       </c>
       <c r="G97" t="n">
-        <v>8.31187629699707</v>
+        <v>8.31187534332275</v>
       </c>
       <c r="H97" t="n">
         <v>77345</v>
@@ -3211,7 +3211,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G98" t="n">
-        <v>8.62637996673584</v>
+        <v>8.62637901306152</v>
       </c>
       <c r="H98" t="n">
         <v>131848</v>
@@ -3240,7 +3240,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G99" t="n">
-        <v>8.45564842224121</v>
+        <v>8.45564746856689</v>
       </c>
       <c r="H99" t="n">
         <v>126252</v>
@@ -3269,7 +3269,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G100" t="n">
-        <v>8.80609512329102</v>
+        <v>8.80609607696533</v>
       </c>
       <c r="H100" t="n">
         <v>249000</v>
@@ -3327,7 +3327,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G102" t="n">
-        <v>8.59043598175049</v>
+        <v>8.5904369354248</v>
       </c>
       <c r="H102" t="n">
         <v>81506</v>
@@ -3356,7 +3356,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G103" t="n">
-        <v>8.71623706817627</v>
+        <v>8.71623802185059</v>
       </c>
       <c r="H103" t="n">
         <v>216807</v>
@@ -3385,7 +3385,7 @@
         <v>9.625</v>
       </c>
       <c r="G104" t="n">
-        <v>8.64884471893311</v>
+        <v>8.64884281158447</v>
       </c>
       <c r="H104" t="n">
         <v>109168</v>
@@ -3414,7 +3414,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G105" t="n">
-        <v>8.55898571014404</v>
+        <v>8.55898475646973</v>
       </c>
       <c r="H105" t="n">
         <v>167622</v>
@@ -3443,7 +3443,7 @@
         <v>9.71500015258789</v>
       </c>
       <c r="G106" t="n">
-        <v>8.72971630096436</v>
+        <v>8.72971725463867</v>
       </c>
       <c r="H106" t="n">
         <v>81637</v>
@@ -3472,7 +3472,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G107" t="n">
-        <v>8.67130851745605</v>
+        <v>8.67130756378174</v>
       </c>
       <c r="H107" t="n">
         <v>107921</v>
@@ -3530,7 +3530,7 @@
         <v>9</v>
       </c>
       <c r="G109" t="n">
-        <v>8.08723068237305</v>
+        <v>8.08722972869873</v>
       </c>
       <c r="H109" t="n">
         <v>151306</v>
@@ -3559,7 +3559,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G110" t="n">
-        <v>7.89852857589722</v>
+        <v>7.89852809906006</v>
       </c>
       <c r="H110" t="n">
         <v>136469</v>
@@ -3617,7 +3617,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G112" t="n">
-        <v>8.10520267486572</v>
+        <v>8.10520172119141</v>
       </c>
       <c r="H112" t="n">
         <v>245680</v>
@@ -3646,7 +3646,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G113" t="n">
-        <v>7.99737215042114</v>
+        <v>7.99737119674683</v>
       </c>
       <c r="H113" t="n">
         <v>164165</v>
@@ -3733,7 +3733,7 @@
         <v>9.02499961853027</v>
       </c>
       <c r="G116" t="n">
-        <v>8.10969543457031</v>
+        <v>8.109694480896</v>
       </c>
       <c r="H116" t="n">
         <v>88735</v>
@@ -3762,7 +3762,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G117" t="n">
-        <v>8.32086086273193</v>
+        <v>8.32086277008057</v>
       </c>
       <c r="H117" t="n">
         <v>146034</v>
@@ -3820,7 +3820,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G119" t="n">
-        <v>8.62637996673584</v>
+        <v>8.62637901306152</v>
       </c>
       <c r="H119" t="n">
         <v>249483</v>
@@ -3849,7 +3849,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>8.80609512329102</v>
+        <v>8.80609607696533</v>
       </c>
       <c r="H120" t="n">
         <v>269484</v>
@@ -3907,7 +3907,7 @@
         <v>9.94499969482422</v>
       </c>
       <c r="G122" t="n">
-        <v>8.93638801574707</v>
+        <v>8.93638896942139</v>
       </c>
       <c r="H122" t="n">
         <v>223439</v>
@@ -3936,7 +3936,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G123" t="n">
-        <v>8.96334743499756</v>
+        <v>8.96334838867188</v>
       </c>
       <c r="H123" t="n">
         <v>150460</v>
@@ -3965,7 +3965,7 @@
         <v>9.78499984741211</v>
       </c>
       <c r="G124" t="n">
-        <v>8.91777801513672</v>
+        <v>8.91777896881104</v>
       </c>
       <c r="H124" t="n">
         <v>154912</v>
@@ -4023,7 +4023,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G126" t="n">
-        <v>8.9314489364624</v>
+        <v>8.93144989013672</v>
       </c>
       <c r="H126" t="n">
         <v>138520</v>
@@ -4110,7 +4110,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G129" t="n">
-        <v>9.51472759246826</v>
+        <v>9.51472663879395</v>
       </c>
       <c r="H129" t="n">
         <v>242971</v>
@@ -4139,7 +4139,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G130" t="n">
-        <v>9.35068130493164</v>
+        <v>9.35068035125732</v>
       </c>
       <c r="H130" t="n">
         <v>2902048</v>
@@ -4284,7 +4284,7 @@
         <v>10.25</v>
       </c>
       <c r="G135" t="n">
-        <v>9.34156703948975</v>
+        <v>9.34156608581543</v>
       </c>
       <c r="H135" t="n">
         <v>52292</v>
@@ -4371,7 +4371,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G138" t="n">
-        <v>8.70360660552979</v>
+        <v>8.70360565185547</v>
       </c>
       <c r="H138" t="n">
         <v>108046</v>
@@ -4400,7 +4400,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G139" t="n">
-        <v>8.52133178710938</v>
+        <v>8.52133274078369</v>
       </c>
       <c r="H139" t="n">
         <v>53406</v>
@@ -4458,7 +4458,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G141" t="n">
-        <v>7.83780288696289</v>
+        <v>7.83780241012573</v>
       </c>
       <c r="H141" t="n">
         <v>132472</v>
@@ -4487,7 +4487,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G142" t="n">
-        <v>7.61907291412354</v>
+        <v>7.61907196044922</v>
       </c>
       <c r="H142" t="n">
         <v>67512</v>
@@ -4516,7 +4516,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G143" t="n">
-        <v>7.73755168914795</v>
+        <v>7.73755121231079</v>
       </c>
       <c r="H143" t="n">
         <v>68881</v>
@@ -4574,7 +4574,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G145" t="n">
-        <v>7.47325277328491</v>
+        <v>7.47325325012207</v>
       </c>
       <c r="H145" t="n">
         <v>33799</v>
@@ -4632,7 +4632,7 @@
         <v>7.50500011444092</v>
       </c>
       <c r="G147" t="n">
-        <v>6.83984994888306</v>
+        <v>6.8398494720459</v>
       </c>
       <c r="H147" t="n">
         <v>173369</v>
@@ -4748,7 +4748,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G151" t="n">
-        <v>7.0266809463501</v>
+        <v>7.02668142318726</v>
       </c>
       <c r="H151" t="n">
         <v>83909</v>
@@ -4777,7 +4777,7 @@
         <v>7.81500005722046</v>
       </c>
       <c r="G152" t="n">
-        <v>7.12237548828125</v>
+        <v>7.12237453460693</v>
       </c>
       <c r="H152" t="n">
         <v>173417</v>
@@ -4864,7 +4864,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G155" t="n">
-        <v>6.7441554069519</v>
+        <v>6.74415588378906</v>
       </c>
       <c r="H155" t="n">
         <v>105692</v>
@@ -4893,7 +4893,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G156" t="n">
-        <v>6.68035936355591</v>
+        <v>6.68035888671875</v>
       </c>
       <c r="H156" t="n">
         <v>131028</v>
@@ -4922,7 +4922,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G157" t="n">
-        <v>6.78061056137085</v>
+        <v>6.78061008453369</v>
       </c>
       <c r="H157" t="n">
         <v>109900</v>
@@ -4951,7 +4951,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G158" t="n">
-        <v>6.92643022537231</v>
+        <v>6.926429271698</v>
       </c>
       <c r="H158" t="n">
         <v>58691</v>
@@ -5009,7 +5009,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G160" t="n">
-        <v>6.68035936355591</v>
+        <v>6.68035888671875</v>
       </c>
       <c r="H160" t="n">
         <v>64175</v>
@@ -5038,7 +5038,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G161" t="n">
-        <v>6.64846181869507</v>
+        <v>6.64846134185791</v>
       </c>
       <c r="H161" t="n">
         <v>62300</v>
@@ -5067,7 +5067,7 @@
         <v>7.05499982833862</v>
       </c>
       <c r="G162" t="n">
-        <v>6.42973184585571</v>
+        <v>6.42973136901855</v>
       </c>
       <c r="H162" t="n">
         <v>80746</v>
@@ -5096,7 +5096,7 @@
         <v>7.31500005722046</v>
       </c>
       <c r="G163" t="n">
-        <v>6.66668891906738</v>
+        <v>6.66668844223022</v>
       </c>
       <c r="H163" t="n">
         <v>63073</v>
@@ -5125,7 +5125,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G164" t="n">
-        <v>6.88086128234863</v>
+        <v>6.88086175918579</v>
       </c>
       <c r="H164" t="n">
         <v>59880</v>
@@ -5154,7 +5154,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G165" t="n">
-        <v>6.9947829246521</v>
+        <v>6.99478340148926</v>
       </c>
       <c r="H165" t="n">
         <v>39622</v>
@@ -5183,7 +5183,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G166" t="n">
-        <v>6.9628849029541</v>
+        <v>6.96288442611694</v>
       </c>
       <c r="H166" t="n">
         <v>25056</v>
@@ -5212,7 +5212,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G167" t="n">
-        <v>6.9628849029541</v>
+        <v>6.96288442611694</v>
       </c>
       <c r="H167" t="n">
         <v>115212</v>
@@ -5241,7 +5241,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G168" t="n">
-        <v>6.9947829246521</v>
+        <v>6.99478340148926</v>
       </c>
       <c r="H168" t="n">
         <v>116551</v>
@@ -5270,7 +5270,7 @@
         <v>7.72499990463257</v>
       </c>
       <c r="G169" t="n">
-        <v>7.04035139083862</v>
+        <v>7.04035186767578</v>
       </c>
       <c r="H169" t="n">
         <v>97576</v>
@@ -5299,7 +5299,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G170" t="n">
-        <v>6.7441554069519</v>
+        <v>6.74415588378906</v>
       </c>
       <c r="H170" t="n">
         <v>54127</v>
@@ -5328,7 +5328,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G171" t="n">
-        <v>6.9947829246521</v>
+        <v>6.99478340148926</v>
       </c>
       <c r="H171" t="n">
         <v>62027</v>
@@ -5357,7 +5357,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G172" t="n">
-        <v>7.26819467544556</v>
+        <v>7.2681941986084</v>
       </c>
       <c r="H172" t="n">
         <v>107198</v>
@@ -5415,7 +5415,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G174" t="n">
-        <v>7.47325277328491</v>
+        <v>7.47325325012207</v>
       </c>
       <c r="H174" t="n">
         <v>32018</v>
@@ -5444,7 +5444,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G175" t="n">
-        <v>7.61907291412354</v>
+        <v>7.61907196044922</v>
       </c>
       <c r="H175" t="n">
         <v>67391</v>
@@ -5560,7 +5560,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G179" t="n">
-        <v>7.33199071884155</v>
+        <v>7.33199024200439</v>
       </c>
       <c r="H179" t="n">
         <v>88870</v>
@@ -5589,7 +5589,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G180" t="n">
-        <v>7.24996662139893</v>
+        <v>7.24996709823608</v>
       </c>
       <c r="H180" t="n">
         <v>63885</v>
@@ -5618,7 +5618,7 @@
         <v>8</v>
       </c>
       <c r="G181" t="n">
-        <v>7.29097890853882</v>
+        <v>7.29097938537598</v>
       </c>
       <c r="H181" t="n">
         <v>44729</v>
@@ -5647,7 +5647,7 @@
         <v>8</v>
       </c>
       <c r="G182" t="n">
-        <v>7.29097890853882</v>
+        <v>7.29097938537598</v>
       </c>
       <c r="H182" t="n">
         <v>68137</v>
@@ -5676,7 +5676,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G183" t="n">
-        <v>7.37300205230713</v>
+        <v>7.37300252914429</v>
       </c>
       <c r="H183" t="n">
         <v>62938</v>
@@ -5705,7 +5705,7 @@
         <v>8</v>
       </c>
       <c r="G184" t="n">
-        <v>7.29097890853882</v>
+        <v>7.29097938537598</v>
       </c>
       <c r="H184" t="n">
         <v>53674</v>
@@ -5734,7 +5734,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G185" t="n">
-        <v>7.05402183532715</v>
+        <v>7.05402231216431</v>
       </c>
       <c r="H185" t="n">
         <v>89502</v>
@@ -5763,7 +5763,7 @@
         <v>8</v>
       </c>
       <c r="G186" t="n">
-        <v>7.29097890853882</v>
+        <v>7.29097938537598</v>
       </c>
       <c r="H186" t="n">
         <v>98582</v>
@@ -5792,7 +5792,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G187" t="n">
-        <v>7.30009269714355</v>
+        <v>7.30009317398071</v>
       </c>
       <c r="H187" t="n">
         <v>50930</v>
@@ -5821,7 +5821,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G188" t="n">
-        <v>7.10870409011841</v>
+        <v>7.10870456695557</v>
       </c>
       <c r="H188" t="n">
         <v>92732</v>
@@ -5850,7 +5850,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G189" t="n">
-        <v>7.21351194381714</v>
+        <v>7.2135124206543</v>
       </c>
       <c r="H189" t="n">
         <v>58048</v>
@@ -5908,7 +5908,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G191" t="n">
-        <v>6.9628849029541</v>
+        <v>6.96288442611694</v>
       </c>
       <c r="H191" t="n">
         <v>64057</v>
@@ -5937,7 +5937,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G192" t="n">
-        <v>6.81250858306885</v>
+        <v>6.81250810623169</v>
       </c>
       <c r="H192" t="n">
         <v>43263</v>
@@ -5966,7 +5966,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G193" t="n">
-        <v>6.81250858306885</v>
+        <v>6.81250810623169</v>
       </c>
       <c r="H193" t="n">
         <v>46346</v>
@@ -6024,7 +6024,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G195" t="n">
-        <v>7.00845384597778</v>
+        <v>7.00845336914062</v>
       </c>
       <c r="H195" t="n">
         <v>142516</v>
@@ -6082,7 +6082,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G197" t="n">
-        <v>6.92643022537231</v>
+        <v>6.926429271698</v>
       </c>
       <c r="H197" t="n">
         <v>94339</v>
@@ -6140,7 +6140,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G199" t="n">
-        <v>6.42517518997192</v>
+        <v>6.42517566680908</v>
       </c>
       <c r="H199" t="n">
         <v>115768</v>
@@ -6169,7 +6169,7 @@
         <v>7.0149998664856</v>
       </c>
       <c r="G200" t="n">
-        <v>6.39327764511108</v>
+        <v>6.39327716827393</v>
       </c>
       <c r="H200" t="n">
         <v>115529</v>
@@ -6198,7 +6198,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G201" t="n">
-        <v>6.6302342414856</v>
+        <v>6.63023376464844</v>
       </c>
       <c r="H201" t="n">
         <v>127295</v>
@@ -6256,7 +6256,7 @@
         <v>7.75</v>
       </c>
       <c r="G203" t="n">
-        <v>7.06313562393188</v>
+        <v>7.06313610076904</v>
       </c>
       <c r="H203" t="n">
         <v>74023</v>
@@ -6314,7 +6314,7 @@
         <v>7.33500003814697</v>
       </c>
       <c r="G205" t="n">
-        <v>6.68491649627686</v>
+        <v>6.6849160194397</v>
       </c>
       <c r="H205" t="n">
         <v>69663</v>
@@ -6459,7 +6459,7 @@
         <v>8.40499973297119</v>
       </c>
       <c r="G210" t="n">
-        <v>7.66008472442627</v>
+        <v>7.66008424758911</v>
       </c>
       <c r="H210" t="n">
         <v>162822</v>
@@ -6488,7 +6488,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G211" t="n">
-        <v>7.70565271377563</v>
+        <v>7.70565319061279</v>
       </c>
       <c r="H211" t="n">
         <v>238638</v>
@@ -6517,7 +6517,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G212" t="n">
-        <v>7.75577831268311</v>
+        <v>7.75577926635742</v>
       </c>
       <c r="H212" t="n">
         <v>149734</v>
@@ -6546,7 +6546,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G213" t="n">
-        <v>7.82868909835815</v>
+        <v>7.828688621521</v>
       </c>
       <c r="H213" t="n">
         <v>267292</v>
@@ -6575,7 +6575,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G214" t="n">
-        <v>7.82868909835815</v>
+        <v>7.828688621521</v>
       </c>
       <c r="H214" t="n">
         <v>252704</v>
@@ -6604,7 +6604,7 @@
         <v>8.48499965667725</v>
       </c>
       <c r="G215" t="n">
-        <v>7.73299503326416</v>
+        <v>7.73299360275269</v>
       </c>
       <c r="H215" t="n">
         <v>190999</v>
@@ -6633,7 +6633,7 @@
         <v>8.65499973297119</v>
       </c>
       <c r="G216" t="n">
-        <v>7.88792657852173</v>
+        <v>7.88792753219604</v>
       </c>
       <c r="H216" t="n">
         <v>352185</v>
@@ -6662,7 +6662,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G217" t="n">
-        <v>7.93805313110352</v>
+        <v>7.93805265426636</v>
       </c>
       <c r="H217" t="n">
         <v>247020</v>
@@ -6691,7 +6691,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G218" t="n">
-        <v>8.02007579803467</v>
+        <v>8.0200777053833</v>
       </c>
       <c r="H218" t="n">
         <v>179237</v>
@@ -6778,7 +6778,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G221" t="n">
-        <v>8.1932373046875</v>
+        <v>8.19323825836182</v>
       </c>
       <c r="H221" t="n">
         <v>194602</v>
@@ -6836,7 +6836,7 @@
         <v>8.86499977111816</v>
       </c>
       <c r="G223" t="n">
-        <v>8.07931518554688</v>
+        <v>8.07931613922119</v>
       </c>
       <c r="H223" t="n">
         <v>111621</v>
@@ -6865,7 +6865,7 @@
         <v>8.79500007629395</v>
       </c>
       <c r="G224" t="n">
-        <v>8.01551914215088</v>
+        <v>8.01552104949951</v>
       </c>
       <c r="H224" t="n">
         <v>122024</v>
@@ -6923,7 +6923,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G226" t="n">
-        <v>7.65552806854248</v>
+        <v>7.65552759170532</v>
       </c>
       <c r="H226" t="n">
         <v>242848</v>
@@ -7010,7 +7010,7 @@
         <v>8.60499954223633</v>
       </c>
       <c r="G229" t="n">
-        <v>7.84235954284668</v>
+        <v>7.84235906600952</v>
       </c>
       <c r="H229" t="n">
         <v>228869</v>
@@ -7039,7 +7039,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G230" t="n">
-        <v>7.59173202514648</v>
+        <v>7.59173154830933</v>
       </c>
       <c r="H230" t="n">
         <v>175936</v>
@@ -7097,7 +7097,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G232" t="n">
-        <v>7.54160594940186</v>
+        <v>7.54160642623901</v>
       </c>
       <c r="H232" t="n">
         <v>183612</v>
@@ -7126,7 +7126,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G233" t="n">
-        <v>7.60084533691406</v>
+        <v>7.60084629058838</v>
       </c>
       <c r="H233" t="n">
         <v>108751</v>
@@ -7155,7 +7155,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G234" t="n">
-        <v>7.85602951049805</v>
+        <v>7.85602903366089</v>
       </c>
       <c r="H234" t="n">
         <v>185968</v>
@@ -7213,7 +7213,7 @@
         <v>8.59500026702881</v>
       </c>
       <c r="G236" t="n">
-        <v>7.83324575424194</v>
+        <v>7.83324670791626</v>
       </c>
       <c r="H236" t="n">
         <v>75722</v>
@@ -7242,7 +7242,7 @@
         <v>8.63500022888184</v>
       </c>
       <c r="G237" t="n">
-        <v>7.86969995498657</v>
+        <v>7.86970090866089</v>
       </c>
       <c r="H237" t="n">
         <v>68684</v>
@@ -7271,7 +7271,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G238" t="n">
-        <v>7.8651442527771</v>
+        <v>7.86514377593994</v>
       </c>
       <c r="H238" t="n">
         <v>98511</v>
@@ -7300,7 +7300,7 @@
         <v>8.50500011444092</v>
       </c>
       <c r="G239" t="n">
-        <v>7.75122213363647</v>
+        <v>7.75122165679932</v>
       </c>
       <c r="H239" t="n">
         <v>97800</v>
@@ -7329,7 +7329,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G240" t="n">
-        <v>7.61907291412354</v>
+        <v>7.61907196044922</v>
       </c>
       <c r="H240" t="n">
         <v>242480</v>
@@ -7358,7 +7358,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G241" t="n">
-        <v>6.99934005737305</v>
+        <v>6.99933958053589</v>
       </c>
       <c r="H241" t="n">
         <v>164686</v>
@@ -7387,7 +7387,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G242" t="n">
-        <v>7.20895528793335</v>
+        <v>7.20895481109619</v>
       </c>
       <c r="H242" t="n">
         <v>428150</v>
@@ -7416,7 +7416,7 @@
         <v>8.29500007629395</v>
       </c>
       <c r="G243" t="n">
-        <v>7.55983400344849</v>
+        <v>7.55983304977417</v>
       </c>
       <c r="H243" t="n">
         <v>179111</v>
@@ -7474,7 +7474,7 @@
         <v>8.15499973297119</v>
       </c>
       <c r="G245" t="n">
-        <v>7.43224191665649</v>
+        <v>7.43224096298218</v>
       </c>
       <c r="H245" t="n">
         <v>95884</v>
@@ -7503,7 +7503,7 @@
         <v>8.49499988555908</v>
       </c>
       <c r="G246" t="n">
-        <v>7.74210739135742</v>
+        <v>7.74210834503174</v>
       </c>
       <c r="H246" t="n">
         <v>144625</v>
@@ -7532,7 +7532,7 @@
         <v>8.5649995803833</v>
       </c>
       <c r="G247" t="n">
-        <v>7.80590391159058</v>
+        <v>7.80590343475342</v>
       </c>
       <c r="H247" t="n">
         <v>190341</v>
@@ -7561,7 +7561,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G248" t="n">
-        <v>7.73755168914795</v>
+        <v>7.73755121231079</v>
       </c>
       <c r="H248" t="n">
         <v>79342</v>
@@ -7590,7 +7590,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G249" t="n">
-        <v>7.82868909835815</v>
+        <v>7.828688621521</v>
       </c>
       <c r="H249" t="n">
         <v>109003</v>
@@ -7619,7 +7619,7 @@
         <v>8.44499969482422</v>
       </c>
       <c r="G250" t="n">
-        <v>7.69653987884521</v>
+        <v>7.69653940200806</v>
       </c>
       <c r="H250" t="n">
         <v>65821</v>
@@ -7677,7 +7677,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G252" t="n">
-        <v>7.87425756454468</v>
+        <v>7.87425851821899</v>
       </c>
       <c r="H252" t="n">
         <v>52613</v>
@@ -7764,7 +7764,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G255" t="n">
-        <v>8.06564521789551</v>
+        <v>8.06564617156982</v>
       </c>
       <c r="H255" t="n">
         <v>80541</v>
@@ -7909,7 +7909,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G260" t="n">
-        <v>8.8767671585083</v>
+        <v>8.87676620483398</v>
       </c>
       <c r="H260" t="n">
         <v>299785</v>
@@ -7967,7 +7967,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G262" t="n">
-        <v>8.61246776580811</v>
+        <v>8.61246871948242</v>
       </c>
       <c r="H262" t="n">
         <v>78088</v>
@@ -8025,7 +8025,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G264" t="n">
-        <v>8.56690120697021</v>
+        <v>8.5669002532959</v>
       </c>
       <c r="H264" t="n">
         <v>68545</v>
@@ -8083,7 +8083,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G266" t="n">
-        <v>8.44386577606201</v>
+        <v>8.4438648223877</v>
       </c>
       <c r="H266" t="n">
         <v>56513</v>
@@ -8112,7 +8112,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G267" t="n">
-        <v>8.61246776580811</v>
+        <v>8.61246871948242</v>
       </c>
       <c r="H267" t="n">
         <v>84891</v>
@@ -8199,7 +8199,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G270" t="n">
-        <v>8.61246776580811</v>
+        <v>8.61246871948242</v>
       </c>
       <c r="H270" t="n">
         <v>91141</v>
@@ -8228,7 +8228,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G271" t="n">
-        <v>8.47576236724854</v>
+        <v>8.47576332092285</v>
       </c>
       <c r="H271" t="n">
         <v>166452</v>
@@ -8286,7 +8286,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G273" t="n">
-        <v>8.40285301208496</v>
+        <v>8.40285396575928</v>
       </c>
       <c r="H273" t="n">
         <v>52732</v>
@@ -8402,7 +8402,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G277" t="n">
-        <v>8.52133178710938</v>
+        <v>8.52133274078369</v>
       </c>
       <c r="H277" t="n">
         <v>22128</v>
@@ -8431,7 +8431,7 @@
         <v>9.66499996185303</v>
       </c>
       <c r="G278" t="n">
-        <v>8.80841445922852</v>
+        <v>8.8084135055542</v>
       </c>
       <c r="H278" t="n">
         <v>41058</v>
@@ -8547,7 +8547,7 @@
         <v>9.625</v>
       </c>
       <c r="G282" t="n">
-        <v>8.77196025848389</v>
+        <v>8.77195930480957</v>
       </c>
       <c r="H282" t="n">
         <v>30701</v>
@@ -8663,7 +8663,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G286" t="n">
-        <v>9.17751884460449</v>
+        <v>9.17751979827881</v>
       </c>
       <c r="H286" t="n">
         <v>123243</v>
@@ -8750,7 +8750,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G289" t="n">
-        <v>8.84031105041504</v>
+        <v>8.84031200408936</v>
       </c>
       <c r="H289" t="n">
         <v>85842</v>
@@ -8779,7 +8779,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G290" t="n">
-        <v>8.70360660552979</v>
+        <v>8.70360565185547</v>
       </c>
       <c r="H290" t="n">
         <v>132044</v>
@@ -8837,7 +8837,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G292" t="n">
-        <v>8.56690120697021</v>
+        <v>8.5669002532959</v>
       </c>
       <c r="H292" t="n">
         <v>119313</v>
@@ -8924,7 +8924,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G295" t="n">
-        <v>8.60335540771484</v>
+        <v>8.60335445404053</v>
       </c>
       <c r="H295" t="n">
         <v>150159</v>
@@ -8953,7 +8953,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G296" t="n">
-        <v>8.63069725036621</v>
+        <v>8.63069629669189</v>
       </c>
       <c r="H296" t="n">
         <v>142335</v>
@@ -9040,7 +9040,7 @@
         <v>9.875</v>
       </c>
       <c r="G299" t="n">
-        <v>8.9998025894165</v>
+        <v>8.99980163574219</v>
       </c>
       <c r="H299" t="n">
         <v>71056</v>
@@ -9098,7 +9098,7 @@
         <v>9.625</v>
       </c>
       <c r="G301" t="n">
-        <v>8.77196025848389</v>
+        <v>8.77195930480957</v>
       </c>
       <c r="H301" t="n">
         <v>62785</v>
@@ -9127,7 +9127,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G302" t="n">
-        <v>8.59424114227295</v>
+        <v>8.59424209594727</v>
       </c>
       <c r="H302" t="n">
         <v>79466</v>
@@ -9185,7 +9185,7 @@
         <v>9.61499977111816</v>
       </c>
       <c r="G304" t="n">
-        <v>8.76284503936768</v>
+        <v>8.76284408569336</v>
       </c>
       <c r="H304" t="n">
         <v>112583</v>
@@ -9214,7 +9214,7 @@
         <v>9.51500034332275</v>
       </c>
       <c r="G305" t="n">
-        <v>8.67170906066895</v>
+        <v>8.67170810699463</v>
       </c>
       <c r="H305" t="n">
         <v>74235</v>
@@ -9243,7 +9243,7 @@
         <v>9.57499980926514</v>
       </c>
       <c r="G306" t="n">
-        <v>8.72638988494873</v>
+        <v>8.72639083862305</v>
       </c>
       <c r="H306" t="n">
         <v>170795</v>
@@ -9272,7 +9272,7 @@
         <v>9.66499996185303</v>
       </c>
       <c r="G307" t="n">
-        <v>8.80841445922852</v>
+        <v>8.8084135055542</v>
       </c>
       <c r="H307" t="n">
         <v>88814</v>
@@ -9301,7 +9301,7 @@
         <v>9.61499977111816</v>
       </c>
       <c r="G308" t="n">
-        <v>8.76284503936768</v>
+        <v>8.76284408569336</v>
       </c>
       <c r="H308" t="n">
         <v>97456</v>
@@ -9330,7 +9330,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G309" t="n">
-        <v>8.59424114227295</v>
+        <v>8.59424209594727</v>
       </c>
       <c r="H309" t="n">
         <v>55428</v>
@@ -9359,7 +9359,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G310" t="n">
-        <v>8.71271991729736</v>
+        <v>8.71272087097168</v>
       </c>
       <c r="H310" t="n">
         <v>71168</v>
@@ -9446,7 +9446,7 @@
         <v>9.86499977111816</v>
       </c>
       <c r="G313" t="n">
-        <v>8.99068737030029</v>
+        <v>8.99068832397461</v>
       </c>
       <c r="H313" t="n">
         <v>95525</v>
@@ -9475,7 +9475,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G314" t="n">
-        <v>8.9314489364624</v>
+        <v>8.93144989013672</v>
       </c>
       <c r="H314" t="n">
         <v>79734</v>
@@ -9504,7 +9504,7 @@
         <v>9.5649995803833</v>
       </c>
       <c r="G315" t="n">
-        <v>8.71727561950684</v>
+        <v>8.71727657318115</v>
       </c>
       <c r="H315" t="n">
         <v>125012</v>
@@ -9562,7 +9562,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G317" t="n">
-        <v>8.44386577606201</v>
+        <v>8.4438648223877</v>
       </c>
       <c r="H317" t="n">
         <v>158286</v>
@@ -9591,7 +9591,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G318" t="n">
-        <v>8.32994270324707</v>
+        <v>8.32994365692139</v>
       </c>
       <c r="H318" t="n">
         <v>82760</v>
@@ -9620,7 +9620,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G319" t="n">
-        <v>8.10210037231445</v>
+        <v>8.10210132598877</v>
       </c>
       <c r="H319" t="n">
         <v>152972</v>
@@ -9765,7 +9765,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G324" t="n">
-        <v>8.23880672454834</v>
+        <v>8.23880481719971</v>
       </c>
       <c r="H324" t="n">
         <v>125245</v>
@@ -9823,7 +9823,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G326" t="n">
-        <v>8.59424114227295</v>
+        <v>8.59424209594727</v>
       </c>
       <c r="H326" t="n">
         <v>346862</v>
@@ -9852,7 +9852,7 @@
         <v>9.64500045776367</v>
       </c>
       <c r="G327" t="n">
-        <v>8.79018688201904</v>
+        <v>8.79018592834473</v>
       </c>
       <c r="H327" t="n">
         <v>201564</v>
@@ -9881,7 +9881,7 @@
         <v>9.71500015258789</v>
       </c>
       <c r="G328" t="n">
-        <v>8.85398197174072</v>
+        <v>8.85398292541504</v>
       </c>
       <c r="H328" t="n">
         <v>220819</v>
@@ -10026,7 +10026,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G333" t="n">
-        <v>8.60335540771484</v>
+        <v>8.60335445404053</v>
       </c>
       <c r="H333" t="n">
         <v>90522</v>
@@ -10113,7 +10113,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G336" t="n">
-        <v>8.60335540771484</v>
+        <v>8.60335445404053</v>
       </c>
       <c r="H336" t="n">
         <v>169827</v>
@@ -10142,7 +10142,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G337" t="n">
-        <v>8.70360660552979</v>
+        <v>8.70360565185547</v>
       </c>
       <c r="H337" t="n">
         <v>99184</v>
@@ -10171,7 +10171,7 @@
         <v>9.59500026702881</v>
       </c>
       <c r="G338" t="n">
-        <v>8.7446174621582</v>
+        <v>8.74461841583252</v>
       </c>
       <c r="H338" t="n">
         <v>46333</v>
@@ -10316,7 +10316,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G343" t="n">
-        <v>8.53955841064453</v>
+        <v>8.53955936431885</v>
       </c>
       <c r="H343" t="n">
         <v>356528</v>
@@ -10345,7 +10345,7 @@
         <v>9.57499980926514</v>
       </c>
       <c r="G344" t="n">
-        <v>8.72638988494873</v>
+        <v>8.72639083862305</v>
       </c>
       <c r="H344" t="n">
         <v>48723</v>
@@ -10374,7 +10374,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G345" t="n">
-        <v>8.8767671585083</v>
+        <v>8.87676620483398</v>
       </c>
       <c r="H345" t="n">
         <v>69041</v>
@@ -10635,7 +10635,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G354" t="n">
-        <v>9.02258682250977</v>
+        <v>9.02258586883545</v>
       </c>
       <c r="H354" t="n">
         <v>58371</v>
@@ -10664,7 +10664,7 @@
         <v>9.88500022888184</v>
       </c>
       <c r="G355" t="n">
-        <v>9.00891590118408</v>
+        <v>9.00891494750977</v>
       </c>
       <c r="H355" t="n">
         <v>123367</v>
@@ -10693,7 +10693,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G356" t="n">
-        <v>9.02258682250977</v>
+        <v>9.02258586883545</v>
       </c>
       <c r="H356" t="n">
         <v>51175</v>
@@ -10722,7 +10722,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G357" t="n">
-        <v>9.16840553283691</v>
+        <v>9.16840744018555</v>
       </c>
       <c r="H357" t="n">
         <v>43978</v>
@@ -10751,7 +10751,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G358" t="n">
-        <v>9.46916007995605</v>
+        <v>9.46915912628174</v>
       </c>
       <c r="H358" t="n">
         <v>119140</v>
@@ -10780,7 +10780,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G359" t="n">
-        <v>9.6696605682373</v>
+        <v>9.66966152191162</v>
       </c>
       <c r="H359" t="n">
         <v>147204</v>
@@ -10809,7 +10809,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G360" t="n">
-        <v>9.50561332702637</v>
+        <v>9.50561428070068</v>
       </c>
       <c r="H360" t="n">
         <v>54614</v>
@@ -10925,7 +10925,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G364" t="n">
-        <v>9.4235897064209</v>
+        <v>9.42359066009521</v>
       </c>
       <c r="H364" t="n">
         <v>225133</v>
@@ -10954,7 +10954,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G365" t="n">
-        <v>9.33245182037354</v>
+        <v>9.33245277404785</v>
       </c>
       <c r="H365" t="n">
         <v>135405</v>
@@ -11012,7 +11012,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G367" t="n">
-        <v>9.15017890930176</v>
+        <v>9.15017795562744</v>
       </c>
       <c r="H367" t="n">
         <v>95441</v>
@@ -11070,7 +11070,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G369" t="n">
-        <v>8.66715145111084</v>
+        <v>8.66715240478516</v>
       </c>
       <c r="H369" t="n">
         <v>180228</v>
@@ -11215,7 +11215,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G374" t="n">
-        <v>9.10460948944092</v>
+        <v>9.10461044311523</v>
       </c>
       <c r="H374" t="n">
         <v>180858</v>
@@ -11331,7 +11331,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G378" t="n">
-        <v>9.09549617767334</v>
+        <v>9.09549522399902</v>
       </c>
       <c r="H378" t="n">
         <v>71656</v>
@@ -11360,7 +11360,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G379" t="n">
-        <v>9.30787754058838</v>
+        <v>9.3078784942627</v>
       </c>
       <c r="H379" t="n">
         <v>179086</v>
@@ -11476,7 +11476,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G383" t="n">
-        <v>9.6126012802124</v>
+        <v>9.61260032653809</v>
       </c>
       <c r="H383" t="n">
         <v>186379</v>
@@ -11534,7 +11534,7 @@
         <v>10.25</v>
       </c>
       <c r="G385" t="n">
-        <v>9.46485710144043</v>
+        <v>9.46485614776611</v>
       </c>
       <c r="H385" t="n">
         <v>63321</v>
@@ -11563,7 +11563,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G386" t="n">
-        <v>9.43715381622314</v>
+        <v>9.43715476989746</v>
       </c>
       <c r="H386" t="n">
         <v>588687</v>
@@ -11592,7 +11592,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G387" t="n">
-        <v>9.5479621887207</v>
+        <v>9.54796314239502</v>
       </c>
       <c r="H387" t="n">
         <v>97563</v>
@@ -11650,7 +11650,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G389" t="n">
-        <v>9.64030265808105</v>
+        <v>9.64030170440674</v>
       </c>
       <c r="H389" t="n">
         <v>168078</v>
@@ -11679,7 +11679,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G390" t="n">
-        <v>9.78804779052734</v>
+        <v>9.78804683685303</v>
       </c>
       <c r="H390" t="n">
         <v>146601</v>
@@ -11737,7 +11737,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G392" t="n">
-        <v>9.64030265808105</v>
+        <v>9.64030170440674</v>
       </c>
       <c r="H392" t="n">
         <v>109538</v>
@@ -11766,7 +11766,7 @@
         <v>10.5</v>
       </c>
       <c r="G393" t="n">
-        <v>9.69570732116699</v>
+        <v>9.69570636749268</v>
       </c>
       <c r="H393" t="n">
         <v>63889</v>
@@ -11824,7 +11824,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G395" t="n">
-        <v>9.66800498962402</v>
+        <v>9.66800403594971</v>
       </c>
       <c r="H395" t="n">
         <v>79788</v>
@@ -11911,7 +11911,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G398" t="n">
-        <v>9.4279203414917</v>
+        <v>9.42792129516602</v>
       </c>
       <c r="H398" t="n">
         <v>119704</v>
@@ -11940,7 +11940,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G399" t="n">
-        <v>9.34481430053711</v>
+        <v>9.34481334686279</v>
       </c>
       <c r="H399" t="n">
         <v>45265</v>
@@ -11998,7 +11998,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G401" t="n">
-        <v>9.04932594299316</v>
+        <v>9.04932689666748</v>
       </c>
       <c r="H401" t="n">
         <v>96905</v>
@@ -12027,7 +12027,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G402" t="n">
-        <v>8.89234924316406</v>
+        <v>8.89234828948975</v>
       </c>
       <c r="H402" t="n">
         <v>66073</v>
@@ -12056,7 +12056,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G403" t="n">
-        <v>8.79539108276367</v>
+        <v>8.79539012908936</v>
       </c>
       <c r="H403" t="n">
         <v>80618</v>
@@ -12085,7 +12085,7 @@
         <v>9.36499977111816</v>
       </c>
       <c r="G404" t="n">
-        <v>8.64764595031738</v>
+        <v>8.6476469039917</v>
       </c>
       <c r="H404" t="n">
         <v>93583</v>
@@ -12114,7 +12114,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G405" t="n">
-        <v>8.58762550354004</v>
+        <v>8.58762645721436</v>
       </c>
       <c r="H405" t="n">
         <v>464509</v>
@@ -12143,7 +12143,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G406" t="n">
-        <v>8.80000782012939</v>
+        <v>8.80000877380371</v>
       </c>
       <c r="H406" t="n">
         <v>218689</v>
@@ -12172,7 +12172,7 @@
         <v>9.55500030517578</v>
       </c>
       <c r="G407" t="n">
-        <v>8.82309341430664</v>
+        <v>8.82309246063232</v>
       </c>
       <c r="H407" t="n">
         <v>224972</v>
@@ -12259,7 +12259,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G410" t="n">
-        <v>8.64303016662598</v>
+        <v>8.64302921295166</v>
       </c>
       <c r="H410" t="n">
         <v>151206</v>
@@ -12288,7 +12288,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G411" t="n">
-        <v>8.82771015167236</v>
+        <v>8.82771110534668</v>
       </c>
       <c r="H411" t="n">
         <v>189726</v>
@@ -12404,7 +12404,7 @@
         <v>9.21500015258789</v>
       </c>
       <c r="G415" t="n">
-        <v>8.50913715362549</v>
+        <v>8.50913619995117</v>
       </c>
       <c r="H415" t="n">
         <v>86476</v>
@@ -12433,7 +12433,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G416" t="n">
-        <v>8.67073249816895</v>
+        <v>8.67073154449463</v>
       </c>
       <c r="H416" t="n">
         <v>133259</v>
@@ -12462,7 +12462,7 @@
         <v>9.48499965667725</v>
       </c>
       <c r="G417" t="n">
-        <v>8.75845527648926</v>
+        <v>8.75845432281494</v>
       </c>
       <c r="H417" t="n">
         <v>166541</v>
@@ -12520,7 +12520,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G419" t="n">
-        <v>8.57839202880859</v>
+        <v>8.57839298248291</v>
       </c>
       <c r="H419" t="n">
         <v>85948</v>
@@ -12578,7 +12578,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G421" t="n">
-        <v>8.28290367126465</v>
+        <v>8.28290462493896</v>
       </c>
       <c r="H421" t="n">
         <v>194344</v>
@@ -12636,7 +12636,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G423" t="n">
-        <v>8.0382022857666</v>
+        <v>8.03820323944092</v>
       </c>
       <c r="H423" t="n">
         <v>208593</v>
@@ -12694,7 +12694,7 @@
         <v>8.54500007629395</v>
       </c>
       <c r="G425" t="n">
-        <v>7.89045906066895</v>
+        <v>7.89045858383179</v>
       </c>
       <c r="H425" t="n">
         <v>157771</v>
@@ -12723,7 +12723,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G426" t="n">
-        <v>7.92277717590332</v>
+        <v>7.92277669906616</v>
       </c>
       <c r="H426" t="n">
         <v>224688</v>
@@ -12839,7 +12839,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G430" t="n">
-        <v>7.87660646438599</v>
+        <v>7.87660789489746</v>
       </c>
       <c r="H430" t="n">
         <v>182047</v>
@@ -12868,7 +12868,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G431" t="n">
-        <v>7.81196975708008</v>
+        <v>7.81196928024292</v>
       </c>
       <c r="H431" t="n">
         <v>211938</v>
@@ -12897,7 +12897,7 @@
         <v>8.42500019073486</v>
       </c>
       <c r="G432" t="n">
-        <v>7.77965116500854</v>
+        <v>7.77965021133423</v>
       </c>
       <c r="H432" t="n">
         <v>499662</v>
@@ -12926,7 +12926,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G433" t="n">
-        <v>7.54418325424194</v>
+        <v>7.5441837310791</v>
       </c>
       <c r="H433" t="n">
         <v>411895</v>
@@ -12955,7 +12955,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G434" t="n">
-        <v>7.2579288482666</v>
+        <v>7.25792932510376</v>
       </c>
       <c r="H434" t="n">
         <v>435932</v>
@@ -12984,7 +12984,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G435" t="n">
-        <v>7.06401538848877</v>
+        <v>7.06401491165161</v>
       </c>
       <c r="H435" t="n">
         <v>300120</v>
@@ -13071,7 +13071,7 @@
         <v>7.72499990463257</v>
       </c>
       <c r="G438" t="n">
-        <v>7.13326978683472</v>
+        <v>7.13327026367188</v>
       </c>
       <c r="H438" t="n">
         <v>174564</v>
@@ -13158,7 +13158,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G441" t="n">
-        <v>6.90242004394531</v>
+        <v>6.90241956710815</v>
       </c>
       <c r="H441" t="n">
         <v>154999</v>
@@ -13216,7 +13216,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G443" t="n">
-        <v>6.61616563796997</v>
+        <v>6.61616516113281</v>
       </c>
       <c r="H443" t="n">
         <v>161736</v>
@@ -13245,7 +13245,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G444" t="n">
-        <v>6.61154890060425</v>
+        <v>6.61154842376709</v>
       </c>
       <c r="H444" t="n">
         <v>161687</v>
@@ -13361,7 +13361,7 @@
         <v>7.13500022888184</v>
       </c>
       <c r="G448" t="n">
-        <v>6.588463306427</v>
+        <v>6.58846378326416</v>
       </c>
       <c r="H448" t="n">
         <v>537214</v>
@@ -13390,7 +13390,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G449" t="n">
-        <v>6.90242004394531</v>
+        <v>6.90241956710815</v>
       </c>
       <c r="H449" t="n">
         <v>615718</v>
@@ -13419,7 +13419,7 @@
         <v>7.31500005722046</v>
       </c>
       <c r="G450" t="n">
-        <v>6.75467586517334</v>
+        <v>6.75467538833618</v>
       </c>
       <c r="H450" t="n">
         <v>323055</v>
@@ -13477,7 +13477,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G452" t="n">
-        <v>6.55614471435547</v>
+        <v>6.55614423751831</v>
       </c>
       <c r="H452" t="n">
         <v>185501</v>
@@ -13506,7 +13506,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G453" t="n">
-        <v>6.88856840133667</v>
+        <v>6.88856887817383</v>
       </c>
       <c r="H453" t="n">
         <v>417380</v>
@@ -13564,7 +13564,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G455" t="n">
-        <v>6.76390981674194</v>
+        <v>6.76390933990479</v>
       </c>
       <c r="H455" t="n">
         <v>277616</v>
@@ -13593,7 +13593,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G456" t="n">
-        <v>6.76390981674194</v>
+        <v>6.76390933990479</v>
       </c>
       <c r="H456" t="n">
         <v>287013</v>
@@ -13651,7 +13651,7 @@
         <v>7.09499979019165</v>
       </c>
       <c r="G458" t="n">
-        <v>6.55152750015259</v>
+        <v>6.55152702331543</v>
       </c>
       <c r="H458" t="n">
         <v>694126</v>
@@ -13680,7 +13680,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G459" t="n">
-        <v>6.55614471435547</v>
+        <v>6.55614423751831</v>
       </c>
       <c r="H459" t="n">
         <v>342488</v>
@@ -13738,7 +13738,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G461" t="n">
-        <v>6.37146425247192</v>
+        <v>6.37146472930908</v>
       </c>
       <c r="H461" t="n">
         <v>296679</v>
@@ -13767,7 +13767,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G462" t="n">
-        <v>6.37146425247192</v>
+        <v>6.37146472930908</v>
       </c>
       <c r="H462" t="n">
         <v>4069866</v>
@@ -13796,7 +13796,7 @@
         <v>6.70499992370605</v>
       </c>
       <c r="G463" t="n">
-        <v>6.19140148162842</v>
+        <v>6.19140100479126</v>
       </c>
       <c r="H463" t="n">
         <v>303572</v>
@@ -13825,7 +13825,7 @@
         <v>6.69500017166138</v>
       </c>
       <c r="G464" t="n">
-        <v>6.18216800689697</v>
+        <v>6.18216753005981</v>
       </c>
       <c r="H464" t="n">
         <v>494430</v>
@@ -13883,7 +13883,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G466" t="n">
-        <v>5.808189868927</v>
+        <v>5.80818939208984</v>
       </c>
       <c r="H466" t="n">
         <v>501243</v>
@@ -13941,7 +13941,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G468" t="n">
-        <v>5.52193546295166</v>
+        <v>5.52193593978882</v>
       </c>
       <c r="H468" t="n">
         <v>612281</v>
@@ -14057,7 +14057,7 @@
         <v>6.16499996185303</v>
       </c>
       <c r="G472" t="n">
-        <v>5.69276523590088</v>
+        <v>5.69276475906372</v>
       </c>
       <c r="H472" t="n">
         <v>637767</v>
@@ -14115,7 +14115,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G474" t="n">
-        <v>5.44806337356567</v>
+        <v>5.44806385040283</v>
       </c>
       <c r="H474" t="n">
         <v>326663</v>
@@ -14202,7 +14202,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G477" t="n">
-        <v>5.55887222290039</v>
+        <v>5.55887174606323</v>
       </c>
       <c r="H477" t="n">
         <v>286452</v>
@@ -14405,7 +14405,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G484" t="n">
-        <v>5.17104387283325</v>
+        <v>5.17104339599609</v>
       </c>
       <c r="H484" t="n">
         <v>335662</v>
@@ -14434,7 +14434,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G485" t="n">
-        <v>5.17566108703613</v>
+        <v>5.17566061019897</v>
       </c>
       <c r="H485" t="n">
         <v>433667</v>
@@ -14463,7 +14463,7 @@
         <v>5.75</v>
       </c>
       <c r="G486" t="n">
-        <v>5.30955362319946</v>
+        <v>5.30955410003662</v>
       </c>
       <c r="H486" t="n">
         <v>311135</v>
@@ -14492,7 +14492,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G487" t="n">
-        <v>5.06023550033569</v>
+        <v>5.06023597717285</v>
       </c>
       <c r="H487" t="n">
         <v>544541</v>
@@ -14579,7 +14579,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G490" t="n">
-        <v>4.80168294906616</v>
+        <v>4.80168342590332</v>
       </c>
       <c r="H490" t="n">
         <v>392471</v>
@@ -14666,7 +14666,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G493" t="n">
-        <v>4.83400249481201</v>
+        <v>4.83400201797485</v>
       </c>
       <c r="H493" t="n">
         <v>200923</v>
@@ -14695,7 +14695,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G494" t="n">
-        <v>4.88478946685791</v>
+        <v>4.88478899002075</v>
       </c>
       <c r="H494" t="n">
         <v>111362</v>
@@ -14753,7 +14753,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G496" t="n">
-        <v>5.13410758972168</v>
+        <v>5.13410711288452</v>
       </c>
       <c r="H496" t="n">
         <v>302728</v>
@@ -14869,7 +14869,7 @@
         <v>5.69500017166138</v>
       </c>
       <c r="G500" t="n">
-        <v>5.25876712799072</v>
+        <v>5.25876665115356</v>
       </c>
       <c r="H500" t="n">
         <v>671518</v>
@@ -14898,7 +14898,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G501" t="n">
-        <v>5.38342571258545</v>
+        <v>5.38342523574829</v>
       </c>
       <c r="H501" t="n">
         <v>200804</v>
@@ -14985,7 +14985,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>5.44806337356567</v>
+        <v>5.44806385040283</v>
       </c>
       <c r="H504" t="n">
         <v>262185</v>
@@ -15014,7 +15014,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G505" t="n">
-        <v>5.39266014099121</v>
+        <v>5.39265966415405</v>
       </c>
       <c r="H505" t="n">
         <v>225134</v>
@@ -15130,7 +15130,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G509" t="n">
-        <v>5.24491548538208</v>
+        <v>5.24491500854492</v>
       </c>
       <c r="H509" t="n">
         <v>138219</v>
@@ -15159,7 +15159,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G510" t="n">
-        <v>5.21259641647339</v>
+        <v>5.21259689331055</v>
       </c>
       <c r="H510" t="n">
         <v>110937</v>
@@ -15246,7 +15246,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G513" t="n">
-        <v>5.21259641647339</v>
+        <v>5.21259689331055</v>
       </c>
       <c r="H513" t="n">
         <v>215173</v>
@@ -15275,7 +15275,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G514" t="n">
-        <v>5.17104387283325</v>
+        <v>5.17104339599609</v>
       </c>
       <c r="H514" t="n">
         <v>307201</v>
@@ -15391,7 +15391,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G518" t="n">
-        <v>5.24491548538208</v>
+        <v>5.24491500854492</v>
       </c>
       <c r="H518" t="n">
         <v>260768</v>
@@ -15420,7 +15420,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G519" t="n">
-        <v>5.25414943695068</v>
+        <v>5.25414991378784</v>
       </c>
       <c r="H519" t="n">
         <v>250927</v>
@@ -15536,7 +15536,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G523" t="n">
-        <v>5.16180944442749</v>
+        <v>5.16180992126465</v>
       </c>
       <c r="H523" t="n">
         <v>249552</v>
@@ -15623,7 +15623,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G526" t="n">
-        <v>5.44806337356567</v>
+        <v>5.44806385040283</v>
       </c>
       <c r="H526" t="n">
         <v>1071210</v>
@@ -15652,7 +15652,7 @@
         <v>6.03499984741211</v>
       </c>
       <c r="G527" t="n">
-        <v>5.57272243499756</v>
+        <v>5.57272291183472</v>
       </c>
       <c r="H527" t="n">
         <v>477831</v>
@@ -15681,7 +15681,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G528" t="n">
-        <v>5.52193546295166</v>
+        <v>5.52193593978882</v>
       </c>
       <c r="H528" t="n">
         <v>271052</v>
@@ -15739,7 +15739,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G530" t="n">
-        <v>5.72508335113525</v>
+        <v>5.72508382797241</v>
       </c>
       <c r="H530" t="n">
         <v>604320</v>
@@ -15884,7 +15884,7 @@
         <v>6.2649998664856</v>
       </c>
       <c r="G535" t="n">
-        <v>5.78510475158691</v>
+        <v>5.78510522842407</v>
       </c>
       <c r="H535" t="n">
         <v>171909</v>
@@ -15913,7 +15913,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G536" t="n">
-        <v>5.71584987640381</v>
+        <v>5.71585035324097</v>
       </c>
       <c r="H536" t="n">
         <v>257462</v>
@@ -15942,7 +15942,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G537" t="n">
-        <v>5.52193546295166</v>
+        <v>5.52193593978882</v>
       </c>
       <c r="H537" t="n">
         <v>426609</v>
@@ -16029,7 +16029,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G540" t="n">
-        <v>6.03904056549072</v>
+        <v>6.03904008865356</v>
       </c>
       <c r="H540" t="n">
         <v>416492</v>
@@ -16058,7 +16058,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G541" t="n">
-        <v>6.05750846862793</v>
+        <v>6.05750751495361</v>
       </c>
       <c r="H541" t="n">
         <v>374625</v>
@@ -16087,7 +16087,7 @@
         <v>6.57499980926514</v>
       </c>
       <c r="G542" t="n">
-        <v>6.0713586807251</v>
+        <v>6.07135915756226</v>
       </c>
       <c r="H542" t="n">
         <v>267523</v>
@@ -16435,7 +16435,7 @@
         <v>6.29500007629395</v>
       </c>
       <c r="G554" t="n">
-        <v>5.81280660629272</v>
+        <v>5.81280755996704</v>
       </c>
       <c r="H554" t="n">
         <v>151233</v>
@@ -16464,7 +16464,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G555" t="n">
-        <v>5.71584987640381</v>
+        <v>5.71585035324097</v>
       </c>
       <c r="H555" t="n">
         <v>675111</v>
@@ -16493,7 +16493,7 @@
         <v>6.06500005722046</v>
       </c>
       <c r="G556" t="n">
-        <v>5.60042524337769</v>
+        <v>5.60042476654053</v>
       </c>
       <c r="H556" t="n">
         <v>275234</v>
@@ -16754,7 +16754,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G565" t="n">
-        <v>5.5127010345459</v>
+        <v>5.51270198822021</v>
       </c>
       <c r="H565" t="n">
         <v>164534</v>
@@ -16783,7 +16783,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G566" t="n">
-        <v>5.38342571258545</v>
+        <v>5.38342523574829</v>
       </c>
       <c r="H566" t="n">
         <v>143325</v>
@@ -16841,7 +16841,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G568" t="n">
-        <v>5.32802200317383</v>
+        <v>5.32802152633667</v>
       </c>
       <c r="H568" t="n">
         <v>253739</v>
@@ -16899,7 +16899,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G570" t="n">
-        <v>5.22644710540771</v>
+        <v>5.22644758224487</v>
       </c>
       <c r="H570" t="n">
         <v>465075</v>
@@ -16928,7 +16928,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G571" t="n">
-        <v>5.17566108703613</v>
+        <v>5.17566061019897</v>
       </c>
       <c r="H571" t="n">
         <v>188694</v>
@@ -16957,7 +16957,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G572" t="n">
-        <v>5.24029922485352</v>
+        <v>5.24029874801636</v>
       </c>
       <c r="H572" t="n">
         <v>371542</v>
@@ -16986,7 +16986,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G573" t="n">
-        <v>5.32802200317383</v>
+        <v>5.32802152633667</v>
       </c>
       <c r="H573" t="n">
         <v>246507</v>
@@ -17015,7 +17015,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G574" t="n">
-        <v>5.22644710540771</v>
+        <v>5.22644758224487</v>
       </c>
       <c r="H574" t="n">
         <v>441053</v>
@@ -17044,7 +17044,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G575" t="n">
-        <v>5.13410758972168</v>
+        <v>5.13410711288452</v>
       </c>
       <c r="H575" t="n">
         <v>302344</v>
@@ -17102,7 +17102,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G577" t="n">
-        <v>5.06023550033569</v>
+        <v>5.06023597717285</v>
       </c>
       <c r="H577" t="n">
         <v>490731</v>
@@ -17160,7 +17160,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G579" t="n">
-        <v>5.07408618927002</v>
+        <v>5.07408666610718</v>
       </c>
       <c r="H579" t="n">
         <v>256005</v>
@@ -17189,7 +17189,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G580" t="n">
-        <v>5.09717178344727</v>
+        <v>5.09717082977295</v>
       </c>
       <c r="H580" t="n">
         <v>391172</v>
@@ -17247,7 +17247,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G582" t="n">
-        <v>5.30031967163086</v>
+        <v>5.3003191947937</v>
       </c>
       <c r="H582" t="n">
         <v>1080928</v>
@@ -17305,7 +17305,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G584" t="n">
-        <v>5.37419176101685</v>
+        <v>5.374192237854</v>
       </c>
       <c r="H584" t="n">
         <v>450011</v>
@@ -17450,7 +17450,7 @@
         <v>6.06500005722046</v>
       </c>
       <c r="G589" t="n">
-        <v>5.60042524337769</v>
+        <v>5.60042476654053</v>
       </c>
       <c r="H589" t="n">
         <v>462275</v>
@@ -17566,7 +17566,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G593" t="n">
-        <v>5.39266014099121</v>
+        <v>5.39265966415405</v>
       </c>
       <c r="H593" t="n">
         <v>558485</v>
@@ -17682,7 +17682,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G597" t="n">
-        <v>4.83400249481201</v>
+        <v>4.83400201797485</v>
       </c>
       <c r="H597" t="n">
         <v>384652</v>
@@ -17711,7 +17711,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G598" t="n">
-        <v>4.8063006401062</v>
+        <v>4.80630016326904</v>
       </c>
       <c r="H598" t="n">
         <v>332805</v>
@@ -17798,7 +17798,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G601" t="n">
-        <v>4.77398109436035</v>
+        <v>4.77398157119751</v>
       </c>
       <c r="H601" t="n">
         <v>305751</v>
@@ -17827,7 +17827,7 @@
         <v>5.22499990463257</v>
       </c>
       <c r="G602" t="n">
-        <v>4.82476806640625</v>
+        <v>4.82476854324341</v>
       </c>
       <c r="H602" t="n">
         <v>549261</v>
@@ -17856,7 +17856,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G603" t="n">
-        <v>4.89864015579224</v>
+        <v>4.89864063262939</v>
       </c>
       <c r="H603" t="n">
         <v>510591</v>
@@ -17885,7 +17885,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>4.8063006401062</v>
+        <v>4.80630016326904</v>
       </c>
       <c r="H604" t="n">
         <v>321087</v>
@@ -17943,7 +17943,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>4.52466297149658</v>
+        <v>4.52466344833374</v>
       </c>
       <c r="H606" t="n">
         <v>835466</v>
@@ -17972,7 +17972,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G607" t="n">
-        <v>4.52466297149658</v>
+        <v>4.52466344833374</v>
       </c>
       <c r="H607" t="n">
         <v>662577</v>
@@ -18001,7 +18001,7 @@
         <v>4.82200002670288</v>
       </c>
       <c r="G608" t="n">
-        <v>4.45263814926147</v>
+        <v>4.45263767242432</v>
       </c>
       <c r="H608" t="n">
         <v>597938</v>
@@ -18059,7 +18059,7 @@
         <v>4.66400003433228</v>
       </c>
       <c r="G610" t="n">
-        <v>4.30674076080322</v>
+        <v>4.30674028396606</v>
       </c>
       <c r="H610" t="n">
         <v>394307</v>
@@ -18146,7 +18146,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G613" t="n">
-        <v>4.37691926956177</v>
+        <v>4.37691879272461</v>
       </c>
       <c r="H613" t="n">
         <v>380449</v>
@@ -18204,7 +18204,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G615" t="n">
-        <v>4.37691926956177</v>
+        <v>4.37691879272461</v>
       </c>
       <c r="H615" t="n">
         <v>510752</v>
@@ -18291,7 +18291,7 @@
         <v>5</v>
       </c>
       <c r="G618" t="n">
-        <v>4.61700344085693</v>
+        <v>4.61700296401978</v>
       </c>
       <c r="H618" t="n">
         <v>694400</v>
@@ -18320,7 +18320,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G619" t="n">
-        <v>4.46741247177124</v>
+        <v>4.46741199493408</v>
       </c>
       <c r="H619" t="n">
         <v>402669</v>
@@ -18378,7 +18378,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G621" t="n">
-        <v>4.56898641586304</v>
+        <v>4.56898593902588</v>
       </c>
       <c r="H621" t="n">
         <v>377386</v>
@@ -18436,7 +18436,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G623" t="n">
-        <v>4.79706621170044</v>
+        <v>4.7970666885376</v>
       </c>
       <c r="H623" t="n">
         <v>817405</v>
@@ -18552,7 +18552,7 @@
         <v>4.97800016403198</v>
       </c>
       <c r="G627" t="n">
-        <v>4.59668874740601</v>
+        <v>4.59668827056885</v>
       </c>
       <c r="H627" t="n">
         <v>698215</v>
@@ -18668,7 +18668,7 @@
         <v>4.94199991226196</v>
       </c>
       <c r="G631" t="n">
-        <v>4.56344556808472</v>
+        <v>4.56344604492188</v>
       </c>
       <c r="H631" t="n">
         <v>610912</v>
@@ -18726,7 +18726,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G633" t="n">
-        <v>4.63421201705933</v>
+        <v>4.63421249389648</v>
       </c>
       <c r="H633" t="n">
         <v>659569</v>
@@ -18900,7 +18900,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G639" t="n">
-        <v>4.47546672821045</v>
+        <v>4.47546625137329</v>
       </c>
       <c r="H639" t="n">
         <v>721270</v>
@@ -18929,7 +18929,7 @@
         <v>4.81199979782104</v>
       </c>
       <c r="G640" t="n">
-        <v>4.60169792175293</v>
+        <v>4.60169744491577</v>
       </c>
       <c r="H640" t="n">
         <v>409298</v>
@@ -19074,7 +19074,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G645" t="n">
-        <v>4.45634031295776</v>
+        <v>4.45634078979492</v>
       </c>
       <c r="H645" t="n">
         <v>337361</v>
@@ -19132,7 +19132,7 @@
         <v>4.62400007247925</v>
       </c>
       <c r="G647" t="n">
-        <v>4.42191457748413</v>
+        <v>4.42191410064697</v>
       </c>
       <c r="H647" t="n">
         <v>590963</v>
@@ -19219,7 +19219,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G650" t="n">
-        <v>4.17136430740356</v>
+        <v>4.17136478424072</v>
       </c>
       <c r="H650" t="n">
         <v>575556</v>
@@ -19306,7 +19306,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G653" t="n">
-        <v>4.20770359039307</v>
+        <v>4.20770406723022</v>
       </c>
       <c r="H653" t="n">
         <v>253568</v>
@@ -19480,7 +19480,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G659" t="n">
-        <v>3.9303777217865</v>
+        <v>3.93037796020508</v>
       </c>
       <c r="H659" t="n">
         <v>499794</v>
@@ -19770,7 +19770,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G669" t="n">
-        <v>3.65496444702148</v>
+        <v>3.65496468544006</v>
       </c>
       <c r="H669" t="n">
         <v>556073</v>
@@ -19857,7 +19857,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G672" t="n">
-        <v>3.81370973587036</v>
+        <v>3.81370949745178</v>
       </c>
       <c r="H672" t="n">
         <v>401105</v>
@@ -19886,7 +19886,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G673" t="n">
-        <v>3.81370973587036</v>
+        <v>3.81370949745178</v>
       </c>
       <c r="H673" t="n">
         <v>294689</v>
@@ -19915,7 +19915,7 @@
         <v>4.17600011825562</v>
       </c>
       <c r="G674" t="n">
-        <v>3.99349331855774</v>
+        <v>3.99349355697632</v>
       </c>
       <c r="H674" t="n">
         <v>714573</v>
@@ -20379,7 +20379,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G690" t="n">
-        <v>3.4560546875</v>
+        <v>3.45605492591858</v>
       </c>
       <c r="H690" t="n">
         <v>383156</v>
@@ -20756,7 +20756,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G703" t="n">
-        <v>3.96862983703613</v>
+        <v>3.96862959861755</v>
       </c>
       <c r="H703" t="n">
         <v>402206</v>
@@ -20785,7 +20785,7 @@
         <v>4.1560001373291</v>
       </c>
       <c r="G704" t="n">
-        <v>3.97436738014221</v>
+        <v>3.97436785697937</v>
       </c>
       <c r="H704" t="n">
         <v>366565</v>
@@ -20843,7 +20843,7 @@
         <v>4.27600002288818</v>
       </c>
       <c r="G706" t="n">
-        <v>4.08912324905396</v>
+        <v>4.0891227722168</v>
       </c>
       <c r="H706" t="n">
         <v>382472</v>
@@ -20872,7 +20872,7 @@
         <v>4.13600015640259</v>
       </c>
       <c r="G707" t="n">
-        <v>3.95524144172668</v>
+        <v>3.95524168014526</v>
       </c>
       <c r="H707" t="n">
         <v>503313</v>
@@ -20930,7 +20930,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G709" t="n">
-        <v>3.98966789245605</v>
+        <v>3.98966813087463</v>
       </c>
       <c r="H709" t="n">
         <v>357159</v>
@@ -21017,7 +21017,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G712" t="n">
-        <v>3.67026543617249</v>
+        <v>3.67026519775391</v>
       </c>
       <c r="H712" t="n">
         <v>437455</v>
@@ -21162,7 +21162,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G717" t="n">
-        <v>3.81370973587036</v>
+        <v>3.81370949745178</v>
       </c>
       <c r="H717" t="n">
         <v>286225</v>
@@ -21191,7 +21191,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G718" t="n">
-        <v>3.82327246665955</v>
+        <v>3.82327270507812</v>
       </c>
       <c r="H718" t="n">
         <v>150642</v>
@@ -21220,7 +21220,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G719" t="n">
-        <v>3.91507720947266</v>
+        <v>3.91507697105408</v>
       </c>
       <c r="H719" t="n">
         <v>372351</v>
@@ -21307,7 +21307,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G722" t="n">
-        <v>3.98584318161011</v>
+        <v>3.98584294319153</v>
       </c>
       <c r="H722" t="n">
         <v>634315</v>
@@ -21365,7 +21365,7 @@
         <v>4.42600011825562</v>
       </c>
       <c r="G724" t="n">
-        <v>4.23256731033325</v>
+        <v>4.23256778717041</v>
       </c>
       <c r="H724" t="n">
         <v>1439555</v>
@@ -21394,7 +21394,7 @@
         <v>4.51200008392334</v>
       </c>
       <c r="G725" t="n">
-        <v>4.31480932235718</v>
+        <v>4.31480884552002</v>
       </c>
       <c r="H725" t="n">
         <v>724657</v>
@@ -21452,7 +21452,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G727" t="n">
-        <v>4.15032577514648</v>
+        <v>4.15032625198364</v>
       </c>
       <c r="H727" t="n">
         <v>336308</v>
@@ -21510,7 +21510,7 @@
         <v>4.25</v>
       </c>
       <c r="G729" t="n">
-        <v>4.06425952911377</v>
+        <v>4.06425905227661</v>
       </c>
       <c r="H729" t="n">
         <v>168991</v>
@@ -21597,7 +21597,7 @@
         <v>4.2039999961853</v>
       </c>
       <c r="G732" t="n">
-        <v>4.02026987075806</v>
+        <v>4.0202693939209</v>
       </c>
       <c r="H732" t="n">
         <v>193502</v>
@@ -21742,7 +21742,7 @@
         <v>4.11399984359741</v>
       </c>
       <c r="G737" t="n">
-        <v>3.9342029094696</v>
+        <v>3.93420267105103</v>
       </c>
       <c r="H737" t="n">
         <v>129269</v>
@@ -21829,7 +21829,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G740" t="n">
-        <v>3.96862983703613</v>
+        <v>3.96862959861755</v>
       </c>
       <c r="H740" t="n">
         <v>236046</v>
@@ -21858,7 +21858,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G741" t="n">
-        <v>3.91507720947266</v>
+        <v>3.91507697105408</v>
       </c>
       <c r="H741" t="n">
         <v>182762</v>
@@ -22061,7 +22061,7 @@
         <v>3.90799999237061</v>
       </c>
       <c r="G748" t="n">
-        <v>3.73720598220825</v>
+        <v>3.73720574378967</v>
       </c>
       <c r="H748" t="n">
         <v>191909</v>
@@ -22119,7 +22119,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G750" t="n">
-        <v>3.70086646080017</v>
+        <v>3.70086669921875</v>
       </c>
       <c r="H750" t="n">
         <v>77185</v>
@@ -22148,7 +22148,7 @@
         <v>3.93799996376038</v>
       </c>
       <c r="G751" t="n">
-        <v>3.76589465141296</v>
+        <v>3.76589488983154</v>
       </c>
       <c r="H751" t="n">
         <v>138045</v>
@@ -22264,7 +22264,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G755" t="n">
-        <v>3.7391185760498</v>
+        <v>3.73911881446838</v>
       </c>
       <c r="H755" t="n">
         <v>208777</v>
@@ -22380,7 +22380,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G759" t="n">
-        <v>3.57846069335938</v>
+        <v>3.57846093177795</v>
       </c>
       <c r="H759" t="n">
         <v>337584</v>
@@ -22409,7 +22409,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G760" t="n">
-        <v>3.62245035171509</v>
+        <v>3.62245059013367</v>
       </c>
       <c r="H760" t="n">
         <v>422072</v>
@@ -22467,7 +22467,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G762" t="n">
-        <v>3.56316018104553</v>
+        <v>3.56315994262695</v>
       </c>
       <c r="H762" t="n">
         <v>704289</v>
@@ -22496,7 +22496,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G763" t="n">
-        <v>3.54785943031311</v>
+        <v>3.54785919189453</v>
       </c>
       <c r="H763" t="n">
         <v>1097480</v>
@@ -22583,7 +22583,7 @@
         <v>3.64800000190735</v>
       </c>
       <c r="G766" t="n">
-        <v>3.4885687828064</v>
+        <v>3.48856902122498</v>
       </c>
       <c r="H766" t="n">
         <v>1669355</v>
@@ -22728,7 +22728,7 @@
         <v>3.64400005340576</v>
       </c>
       <c r="G771" t="n">
-        <v>3.48474383354187</v>
+        <v>3.48474359512329</v>
       </c>
       <c r="H771" t="n">
         <v>105519</v>
@@ -22757,7 +22757,7 @@
         <v>3.63199996948242</v>
       </c>
       <c r="G772" t="n">
-        <v>3.47326803207397</v>
+        <v>3.47326827049255</v>
       </c>
       <c r="H772" t="n">
         <v>121534</v>
@@ -22873,7 +22873,7 @@
         <v>3.95799994468689</v>
       </c>
       <c r="G776" t="n">
-        <v>3.78502058982849</v>
+        <v>3.78502082824707</v>
       </c>
       <c r="H776" t="n">
         <v>243650</v>
@@ -22902,7 +22902,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G777" t="n">
-        <v>3.76972007751465</v>
+        <v>3.76971983909607</v>
       </c>
       <c r="H777" t="n">
         <v>111182</v>
@@ -22960,7 +22960,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G779" t="n">
-        <v>3.70086646080017</v>
+        <v>3.70086669921875</v>
       </c>
       <c r="H779" t="n">
         <v>145693</v>
@@ -22989,7 +22989,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G780" t="n">
-        <v>3.5975866317749</v>
+        <v>3.59758687019348</v>
       </c>
       <c r="H780" t="n">
         <v>157659</v>
@@ -23076,7 +23076,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G783" t="n">
-        <v>3.44075417518616</v>
+        <v>3.44075393676758</v>
       </c>
       <c r="H783" t="n">
         <v>613580</v>
@@ -23105,7 +23105,7 @@
         <v>3.41599988937378</v>
       </c>
       <c r="G784" t="n">
-        <v>3.26670789718628</v>
+        <v>3.26670813560486</v>
       </c>
       <c r="H784" t="n">
         <v>455535</v>
@@ -23134,7 +23134,7 @@
         <v>3.41599988937378</v>
       </c>
       <c r="G785" t="n">
-        <v>3.26670789718628</v>
+        <v>3.26670813560486</v>
       </c>
       <c r="H785" t="n">
         <v>519347</v>
@@ -23163,7 +23163,7 @@
         <v>3.46799993515015</v>
       </c>
       <c r="G786" t="n">
-        <v>3.31643557548523</v>
+        <v>3.31643533706665</v>
       </c>
       <c r="H786" t="n">
         <v>202674</v>
@@ -23192,7 +23192,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G787" t="n">
-        <v>3.29157185554504</v>
+        <v>3.29157161712646</v>
       </c>
       <c r="H787" t="n">
         <v>188696</v>
@@ -23424,7 +23424,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G795" t="n">
-        <v>3.2074179649353</v>
+        <v>3.20741772651672</v>
       </c>
       <c r="H795" t="n">
         <v>383770</v>
@@ -23801,7 +23801,7 @@
         <v>3.47399997711182</v>
       </c>
       <c r="G808" t="n">
-        <v>3.32217311859131</v>
+        <v>3.32217335700989</v>
       </c>
       <c r="H808" t="n">
         <v>80720</v>
@@ -23975,7 +23975,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G814" t="n">
-        <v>3.22654390335083</v>
+        <v>3.22654366493225</v>
       </c>
       <c r="H814" t="n">
         <v>115313</v>
@@ -24149,7 +24149,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G820" t="n">
-        <v>3.55168437957764</v>
+        <v>3.55168461799622</v>
       </c>
       <c r="H820" t="n">
         <v>1031313</v>
@@ -24178,7 +24178,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G821" t="n">
-        <v>3.50769472122192</v>
+        <v>3.5076949596405</v>
       </c>
       <c r="H821" t="n">
         <v>354331</v>
@@ -24236,7 +24236,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G823" t="n">
-        <v>3.53638386726379</v>
+        <v>3.53638362884521</v>
       </c>
       <c r="H823" t="n">
         <v>421877</v>
@@ -24323,7 +24323,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G826" t="n">
-        <v>3.58228611946106</v>
+        <v>3.58228588104248</v>
       </c>
       <c r="H826" t="n">
         <v>258986</v>
@@ -24352,7 +24352,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G827" t="n">
-        <v>3.57654809951782</v>
+        <v>3.5765483379364</v>
       </c>
       <c r="H827" t="n">
         <v>166129</v>
@@ -24381,7 +24381,7 @@
         <v>3.84400010108948</v>
       </c>
       <c r="G828" t="n">
-        <v>3.67600297927856</v>
+        <v>3.67600321769714</v>
       </c>
       <c r="H828" t="n">
         <v>474129</v>
@@ -24526,7 +24526,7 @@
         <v>4.22599983215332</v>
       </c>
       <c r="G833" t="n">
-        <v>4.04130840301514</v>
+        <v>4.04130792617798</v>
       </c>
       <c r="H833" t="n">
         <v>2312238</v>
@@ -24758,7 +24758,7 @@
         <v>4.68599987030029</v>
       </c>
       <c r="G841" t="n">
-        <v>4.48120403289795</v>
+        <v>4.48120450973511</v>
       </c>
       <c r="H841" t="n">
         <v>337090</v>
@@ -24816,7 +24816,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G843" t="n">
-        <v>4.54431962966919</v>
+        <v>4.54432010650635</v>
       </c>
       <c r="H843" t="n">
         <v>212793</v>
@@ -24903,7 +24903,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G846" t="n">
-        <v>4.35688638687134</v>
+        <v>4.35688591003418</v>
       </c>
       <c r="H846" t="n">
         <v>178453</v>
@@ -24932,7 +24932,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G847" t="n">
-        <v>4.2631688117981</v>
+        <v>4.26316928863525</v>
       </c>
       <c r="H847" t="n">
         <v>228223</v>
@@ -24990,7 +24990,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G849" t="n">
-        <v>4.17136430740356</v>
+        <v>4.17136478424072</v>
       </c>
       <c r="H849" t="n">
         <v>216742</v>
@@ -25048,7 +25048,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G851" t="n">
-        <v>3.9303777217865</v>
+        <v>3.93037796020508</v>
       </c>
       <c r="H851" t="n">
         <v>187268</v>
@@ -25135,7 +25135,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G854" t="n">
-        <v>3.77928304672241</v>
+        <v>3.77928280830383</v>
       </c>
       <c r="H854" t="n">
         <v>245578</v>
@@ -25251,7 +25251,7 @@
         <v>3.51200008392334</v>
       </c>
       <c r="G858" t="n">
-        <v>3.35851287841797</v>
+        <v>3.35851263999939</v>
       </c>
       <c r="H858" t="n">
         <v>146055</v>
@@ -25280,7 +25280,7 @@
         <v>3.56800007820129</v>
       </c>
       <c r="G859" t="n">
-        <v>3.41206550598145</v>
+        <v>3.41206526756287</v>
       </c>
       <c r="H859" t="n">
         <v>419236</v>
@@ -25396,7 +25396,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G863" t="n">
-        <v>3.47900605201721</v>
+        <v>3.47900581359863</v>
       </c>
       <c r="H863" t="n">
         <v>215914</v>
@@ -25541,7 +25541,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G868" t="n">
-        <v>3.77928304672241</v>
+        <v>3.77928280830383</v>
       </c>
       <c r="H868" t="n">
         <v>73720</v>
@@ -25657,7 +25657,7 @@
         <v>4.12400007247925</v>
       </c>
       <c r="G872" t="n">
-        <v>3.94376611709595</v>
+        <v>3.94376587867737</v>
       </c>
       <c r="H872" t="n">
         <v>191569</v>
@@ -25860,7 +25860,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G879" t="n">
-        <v>4.47546672821045</v>
+        <v>4.47546625137329</v>
       </c>
       <c r="H879" t="n">
         <v>120035</v>
@@ -25976,7 +25976,7 @@
         <v>4.38800001144409</v>
       </c>
       <c r="G883" t="n">
-        <v>4.19622802734375</v>
+        <v>4.19622850418091</v>
       </c>
       <c r="H883" t="n">
         <v>292289</v>
@@ -26063,7 +26063,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G886" t="n">
-        <v>4.20196628570557</v>
+        <v>4.20196580886841</v>
       </c>
       <c r="H886" t="n">
         <v>132141</v>
@@ -26237,7 +26237,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G892" t="n">
-        <v>4.57109642028809</v>
+        <v>4.57109689712524</v>
       </c>
       <c r="H892" t="n">
         <v>407750</v>
@@ -26295,7 +26295,7 @@
         <v>4.74599981307983</v>
       </c>
       <c r="G894" t="n">
-        <v>4.53858232498169</v>
+        <v>4.53858184814453</v>
       </c>
       <c r="H894" t="n">
         <v>111758</v>
@@ -26324,7 +26324,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G895" t="n">
-        <v>4.68585157394409</v>
+        <v>4.68585205078125</v>
       </c>
       <c r="H895" t="n">
         <v>288639</v>
@@ -36538,6 +36538,35 @@
         <v>463697</v>
       </c>
       <c r="I1247" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1248" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1248" t="n">
+        <v>3.28399991989136</v>
+      </c>
+      <c r="D1248" t="n">
+        <v>3.3199999332428</v>
+      </c>
+      <c r="E1248" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="F1248" t="n">
+        <v>3.25999999046326</v>
+      </c>
+      <c r="G1248" t="n">
+        <v>3.25999999046326</v>
+      </c>
+      <c r="H1248" t="n">
+        <v>241872</v>
+      </c>
+      <c r="I1248" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ARIS.MI.xlsx
+++ b/data/ARIS.MI.xlsx
@@ -427,7 +427,7 @@
         <v>10.25</v>
       </c>
       <c r="G2" t="n">
-        <v>9.21045684814453</v>
+        <v>9.21045589447021</v>
       </c>
       <c r="H2" t="n">
         <v>8269720</v>
@@ -456,7 +456,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G3" t="n">
-        <v>9.34524440765381</v>
+        <v>9.34524345397949</v>
       </c>
       <c r="H3" t="n">
         <v>1460667</v>
@@ -543,7 +543,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G6" t="n">
-        <v>9.20147037506104</v>
+        <v>9.20146942138672</v>
       </c>
       <c r="H6" t="n">
         <v>260042</v>
@@ -572,7 +572,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G7" t="n">
-        <v>9.20147037506104</v>
+        <v>9.20146942138672</v>
       </c>
       <c r="H7" t="n">
         <v>279621</v>
@@ -601,7 +601,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G8" t="n">
-        <v>9.20147037506104</v>
+        <v>9.20146942138672</v>
       </c>
       <c r="H8" t="n">
         <v>197900</v>
@@ -630,7 +630,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G9" t="n">
-        <v>9.21944332122803</v>
+        <v>9.21944236755371</v>
       </c>
       <c r="H9" t="n">
         <v>203801</v>
@@ -659,7 +659,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G10" t="n">
-        <v>9.20147037506104</v>
+        <v>9.20146942138672</v>
       </c>
       <c r="H10" t="n">
         <v>122758</v>
@@ -717,7 +717,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G12" t="n">
-        <v>9.20147037506104</v>
+        <v>9.20146942138672</v>
       </c>
       <c r="H12" t="n">
         <v>105196</v>
@@ -746,7 +746,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G13" t="n">
-        <v>9.20147037506104</v>
+        <v>9.20146942138672</v>
       </c>
       <c r="H13" t="n">
         <v>85905</v>
@@ -775,7 +775,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G14" t="n">
-        <v>9.20147037506104</v>
+        <v>9.20146942138672</v>
       </c>
       <c r="H14" t="n">
         <v>198256</v>
@@ -804,7 +804,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G15" t="n">
-        <v>9.21944332122803</v>
+        <v>9.21944236755371</v>
       </c>
       <c r="H15" t="n">
         <v>184724</v>
@@ -891,7 +891,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G18" t="n">
-        <v>8.6353645324707</v>
+        <v>8.63536357879639</v>
       </c>
       <c r="H18" t="n">
         <v>319387</v>
@@ -920,7 +920,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G19" t="n">
-        <v>8.71623802185059</v>
+        <v>8.71623706817627</v>
       </c>
       <c r="H19" t="n">
         <v>172790</v>
@@ -949,7 +949,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G20" t="n">
-        <v>9.12958335876465</v>
+        <v>9.12958431243896</v>
       </c>
       <c r="H20" t="n">
         <v>431091</v>
@@ -1007,7 +1007,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G22" t="n">
-        <v>8.85102462768555</v>
+        <v>8.85102367401123</v>
       </c>
       <c r="H22" t="n">
         <v>186957</v>
@@ -1065,7 +1065,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G24" t="n">
-        <v>9.12958335876465</v>
+        <v>9.12958431243896</v>
       </c>
       <c r="H24" t="n">
         <v>61464</v>
@@ -1094,7 +1094,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G25" t="n">
-        <v>9.11161327362061</v>
+        <v>9.11161422729492</v>
       </c>
       <c r="H25" t="n">
         <v>29624</v>
@@ -1123,7 +1123,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G26" t="n">
-        <v>9.12958335876465</v>
+        <v>9.12958431243896</v>
       </c>
       <c r="H26" t="n">
         <v>53953</v>
@@ -1210,7 +1210,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G29" t="n">
-        <v>9.74061965942383</v>
+        <v>9.74062061309814</v>
       </c>
       <c r="H29" t="n">
         <v>87322</v>
@@ -1239,7 +1239,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G30" t="n">
-        <v>10.1180238723755</v>
+        <v>10.1180248260498</v>
       </c>
       <c r="H30" t="n">
         <v>401264</v>
@@ -1268,7 +1268,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G31" t="n">
-        <v>9.48901748657227</v>
+        <v>9.48901653289795</v>
       </c>
       <c r="H31" t="n">
         <v>328664</v>
@@ -1326,7 +1326,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G33" t="n">
-        <v>9.63279151916504</v>
+        <v>9.63279056549072</v>
       </c>
       <c r="H33" t="n">
         <v>261751</v>
@@ -1413,7 +1413,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G36" t="n">
-        <v>10.1988973617554</v>
+        <v>10.1988954544067</v>
       </c>
       <c r="H36" t="n">
         <v>477707</v>
@@ -1442,7 +1442,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G37" t="n">
-        <v>10.1180238723755</v>
+        <v>10.1180248260498</v>
       </c>
       <c r="H37" t="n">
         <v>92776</v>
@@ -1500,7 +1500,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G39" t="n">
-        <v>9.62380409240723</v>
+        <v>9.62380504608154</v>
       </c>
       <c r="H39" t="n">
         <v>115964</v>
@@ -1529,7 +1529,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G40" t="n">
-        <v>9.67771911621094</v>
+        <v>9.67772006988525</v>
       </c>
       <c r="H40" t="n">
         <v>103333</v>
@@ -1558,7 +1558,7 @@
         <v>10.25</v>
       </c>
       <c r="G41" t="n">
-        <v>9.21045684814453</v>
+        <v>9.21045589447021</v>
       </c>
       <c r="H41" t="n">
         <v>213846</v>
@@ -1645,7 +1645,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G44" t="n">
-        <v>9.12059879302979</v>
+        <v>9.1205997467041</v>
       </c>
       <c r="H44" t="n">
         <v>167591</v>
@@ -1703,7 +1703,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G46" t="n">
-        <v>9.20147037506104</v>
+        <v>9.20146942138672</v>
       </c>
       <c r="H46" t="n">
         <v>323983</v>
@@ -1732,7 +1732,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G47" t="n">
-        <v>9.34524440765381</v>
+        <v>9.34524345397949</v>
       </c>
       <c r="H47" t="n">
         <v>331892</v>
@@ -1790,7 +1790,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G49" t="n">
-        <v>9.34524440765381</v>
+        <v>9.34524345397949</v>
       </c>
       <c r="H49" t="n">
         <v>164923</v>
@@ -1819,7 +1819,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G50" t="n">
-        <v>9.11161327362061</v>
+        <v>9.11161422729492</v>
       </c>
       <c r="H50" t="n">
         <v>253720</v>
@@ -1848,7 +1848,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G51" t="n">
-        <v>9.16552734375</v>
+        <v>9.16552829742432</v>
       </c>
       <c r="H51" t="n">
         <v>170220</v>
@@ -1877,7 +1877,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G52" t="n">
-        <v>9.12958335876465</v>
+        <v>9.12958431243896</v>
       </c>
       <c r="H52" t="n">
         <v>73644</v>
@@ -1935,7 +1935,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G54" t="n">
-        <v>9.16552734375</v>
+        <v>9.16552829742432</v>
       </c>
       <c r="H54" t="n">
         <v>213651</v>
@@ -1964,7 +1964,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G55" t="n">
-        <v>8.994797706604</v>
+        <v>8.99479675292969</v>
       </c>
       <c r="H55" t="n">
         <v>276782</v>
@@ -1993,7 +1993,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G56" t="n">
-        <v>8.72522354125977</v>
+        <v>8.72522258758545</v>
       </c>
       <c r="H56" t="n">
         <v>305482</v>
@@ -2051,7 +2051,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G58" t="n">
-        <v>8.994797706604</v>
+        <v>8.99479675292969</v>
       </c>
       <c r="H58" t="n">
         <v>253397</v>
@@ -2138,7 +2138,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G61" t="n">
-        <v>8.71623802185059</v>
+        <v>8.71623706817627</v>
       </c>
       <c r="H61" t="n">
         <v>224870</v>
@@ -2225,7 +2225,7 @@
         <v>8.75</v>
       </c>
       <c r="G64" t="n">
-        <v>7.86258554458618</v>
+        <v>7.86258506774902</v>
       </c>
       <c r="H64" t="n">
         <v>215027</v>
@@ -2283,7 +2283,7 @@
         <v>9.20499992370605</v>
       </c>
       <c r="G66" t="n">
-        <v>8.27143955230713</v>
+        <v>8.27143859863281</v>
       </c>
       <c r="H66" t="n">
         <v>126081</v>
@@ -2370,7 +2370,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G69" t="n">
-        <v>7.95244312286377</v>
+        <v>7.95244407653809</v>
       </c>
       <c r="H69" t="n">
         <v>230882</v>
@@ -2428,7 +2428,7 @@
         <v>8</v>
       </c>
       <c r="G71" t="n">
-        <v>7.18864965438843</v>
+        <v>7.18864917755127</v>
       </c>
       <c r="H71" t="n">
         <v>192401</v>
@@ -2515,7 +2515,7 @@
         <v>8.3149995803833</v>
       </c>
       <c r="G74" t="n">
-        <v>7.47170209884644</v>
+        <v>7.47170162200928</v>
       </c>
       <c r="H74" t="n">
         <v>89965</v>
@@ -2602,7 +2602,7 @@
         <v>9.51500034332275</v>
       </c>
       <c r="G77" t="n">
-        <v>8.55000019073486</v>
+        <v>8.55000114440918</v>
       </c>
       <c r="H77" t="n">
         <v>369586</v>
@@ -2718,7 +2718,7 @@
         <v>9.71500015258789</v>
       </c>
       <c r="G81" t="n">
-        <v>8.72971725463867</v>
+        <v>8.72971630096436</v>
       </c>
       <c r="H81" t="n">
         <v>221597</v>
@@ -2834,7 +2834,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G85" t="n">
-        <v>8.6443510055542</v>
+        <v>8.64435005187988</v>
       </c>
       <c r="H85" t="n">
         <v>93670</v>
@@ -2892,7 +2892,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G87" t="n">
-        <v>8.67130756378174</v>
+        <v>8.67130851745605</v>
       </c>
       <c r="H87" t="n">
         <v>120344</v>
@@ -2921,7 +2921,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G88" t="n">
-        <v>8.80609607696533</v>
+        <v>8.80609512329102</v>
       </c>
       <c r="H88" t="n">
         <v>104006</v>
@@ -2950,7 +2950,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G89" t="n">
-        <v>8.50057697296143</v>
+        <v>8.50057792663574</v>
       </c>
       <c r="H89" t="n">
         <v>95717</v>
@@ -3037,7 +3037,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G92" t="n">
-        <v>8.71623802185059</v>
+        <v>8.71623706817627</v>
       </c>
       <c r="H92" t="n">
         <v>223170</v>
@@ -3066,7 +3066,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G93" t="n">
-        <v>8.50057697296143</v>
+        <v>8.50057792663574</v>
       </c>
       <c r="H93" t="n">
         <v>181323</v>
@@ -3095,7 +3095,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G94" t="n">
-        <v>8.18607521057129</v>
+        <v>8.18607425689697</v>
       </c>
       <c r="H94" t="n">
         <v>173589</v>
@@ -3153,7 +3153,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G96" t="n">
-        <v>8.24897575378418</v>
+        <v>8.24897480010986</v>
       </c>
       <c r="H96" t="n">
         <v>89220</v>
@@ -3240,7 +3240,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G99" t="n">
-        <v>8.45564746856689</v>
+        <v>8.45564842224121</v>
       </c>
       <c r="H99" t="n">
         <v>126252</v>
@@ -3269,7 +3269,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G100" t="n">
-        <v>8.80609607696533</v>
+        <v>8.80609512329102</v>
       </c>
       <c r="H100" t="n">
         <v>249000</v>
@@ -3298,7 +3298,7 @@
         <v>9.75</v>
       </c>
       <c r="G101" t="n">
-        <v>8.7611665725708</v>
+        <v>8.76116752624512</v>
       </c>
       <c r="H101" t="n">
         <v>134667</v>
@@ -3327,7 +3327,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G102" t="n">
-        <v>8.5904369354248</v>
+        <v>8.59043598175049</v>
       </c>
       <c r="H102" t="n">
         <v>81506</v>
@@ -3356,7 +3356,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G103" t="n">
-        <v>8.71623802185059</v>
+        <v>8.71623706817627</v>
       </c>
       <c r="H103" t="n">
         <v>216807</v>
@@ -3443,7 +3443,7 @@
         <v>9.71500015258789</v>
       </c>
       <c r="G106" t="n">
-        <v>8.72971725463867</v>
+        <v>8.72971630096436</v>
       </c>
       <c r="H106" t="n">
         <v>81637</v>
@@ -3472,7 +3472,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G107" t="n">
-        <v>8.67130756378174</v>
+        <v>8.67130851745605</v>
       </c>
       <c r="H107" t="n">
         <v>107921</v>
@@ -3559,7 +3559,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G110" t="n">
-        <v>7.89852809906006</v>
+        <v>7.89852952957153</v>
       </c>
       <c r="H110" t="n">
         <v>136469</v>
@@ -3617,7 +3617,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G112" t="n">
-        <v>8.10520172119141</v>
+        <v>8.10520362854004</v>
       </c>
       <c r="H112" t="n">
         <v>245680</v>
@@ -3646,7 +3646,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G113" t="n">
-        <v>7.99737119674683</v>
+        <v>7.99737215042114</v>
       </c>
       <c r="H113" t="n">
         <v>164165</v>
@@ -3704,7 +3704,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G115" t="n">
-        <v>7.80867052078247</v>
+        <v>7.80867004394531</v>
       </c>
       <c r="H115" t="n">
         <v>87012</v>
@@ -3733,7 +3733,7 @@
         <v>9.02499961853027</v>
       </c>
       <c r="G116" t="n">
-        <v>8.109694480896</v>
+        <v>8.10969543457031</v>
       </c>
       <c r="H116" t="n">
         <v>88735</v>
@@ -3849,7 +3849,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>8.80609607696533</v>
+        <v>8.80609512329102</v>
       </c>
       <c r="H120" t="n">
         <v>269484</v>
@@ -4023,7 +4023,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G126" t="n">
-        <v>8.93144989013672</v>
+        <v>8.9314489364624</v>
       </c>
       <c r="H126" t="n">
         <v>138520</v>
@@ -4052,7 +4052,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G127" t="n">
-        <v>9.25042915344238</v>
+        <v>9.2504301071167</v>
       </c>
       <c r="H127" t="n">
         <v>154830</v>
@@ -4168,7 +4168,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G131" t="n">
-        <v>9.20486164093018</v>
+        <v>9.20486068725586</v>
       </c>
       <c r="H131" t="n">
         <v>105012</v>
@@ -4197,7 +4197,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G132" t="n">
-        <v>9.2413158416748</v>
+        <v>9.24131679534912</v>
       </c>
       <c r="H132" t="n">
         <v>39938</v>
@@ -4255,7 +4255,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G134" t="n">
-        <v>9.2413158416748</v>
+        <v>9.24131679534912</v>
       </c>
       <c r="H134" t="n">
         <v>32325</v>
@@ -4313,7 +4313,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G136" t="n">
-        <v>9.29599761962891</v>
+        <v>9.29599857330322</v>
       </c>
       <c r="H136" t="n">
         <v>59750</v>
@@ -4342,7 +4342,7 @@
         <v>9.84500026702881</v>
       </c>
       <c r="G137" t="n">
-        <v>8.97246074676514</v>
+        <v>8.97246170043945</v>
       </c>
       <c r="H137" t="n">
         <v>84612</v>
@@ -4429,7 +4429,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G140" t="n">
-        <v>7.95628023147583</v>
+        <v>7.95628118515015</v>
       </c>
       <c r="H140" t="n">
         <v>163728</v>
@@ -4487,7 +4487,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G142" t="n">
-        <v>7.61907196044922</v>
+        <v>7.61907291412354</v>
       </c>
       <c r="H142" t="n">
         <v>67512</v>
@@ -4516,7 +4516,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G143" t="n">
-        <v>7.73755121231079</v>
+        <v>7.73755168914795</v>
       </c>
       <c r="H143" t="n">
         <v>68881</v>
@@ -4545,7 +4545,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G144" t="n">
-        <v>7.64641427993774</v>
+        <v>7.6464147567749</v>
       </c>
       <c r="H144" t="n">
         <v>79110</v>
@@ -4603,7 +4603,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G146" t="n">
-        <v>7.34566164016724</v>
+        <v>7.34566211700439</v>
       </c>
       <c r="H146" t="n">
         <v>105071</v>
@@ -4632,7 +4632,7 @@
         <v>7.50500011444092</v>
       </c>
       <c r="G147" t="n">
-        <v>6.8398494720459</v>
+        <v>6.83984994888306</v>
       </c>
       <c r="H147" t="n">
         <v>173369</v>
@@ -4661,7 +4661,7 @@
         <v>7.375</v>
       </c>
       <c r="G148" t="n">
-        <v>6.72137117385864</v>
+        <v>6.7213716506958</v>
       </c>
       <c r="H148" t="n">
         <v>158803</v>
@@ -4748,7 +4748,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G151" t="n">
-        <v>7.02668142318726</v>
+        <v>7.0266809463501</v>
       </c>
       <c r="H151" t="n">
         <v>83909</v>
@@ -4777,7 +4777,7 @@
         <v>7.81500005722046</v>
       </c>
       <c r="G152" t="n">
-        <v>7.12237453460693</v>
+        <v>7.12237548828125</v>
       </c>
       <c r="H152" t="n">
         <v>173417</v>
@@ -4864,7 +4864,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G155" t="n">
-        <v>6.74415588378906</v>
+        <v>6.7441554069519</v>
       </c>
       <c r="H155" t="n">
         <v>105692</v>
@@ -4893,7 +4893,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G156" t="n">
-        <v>6.68035888671875</v>
+        <v>6.68035936355591</v>
       </c>
       <c r="H156" t="n">
         <v>131028</v>
@@ -4922,7 +4922,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G157" t="n">
-        <v>6.78061008453369</v>
+        <v>6.78061056137085</v>
       </c>
       <c r="H157" t="n">
         <v>109900</v>
@@ -4951,7 +4951,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G158" t="n">
-        <v>6.926429271698</v>
+        <v>6.92642974853516</v>
       </c>
       <c r="H158" t="n">
         <v>58691</v>
@@ -5009,7 +5009,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G160" t="n">
-        <v>6.68035888671875</v>
+        <v>6.68035936355591</v>
       </c>
       <c r="H160" t="n">
         <v>64175</v>
@@ -5067,7 +5067,7 @@
         <v>7.05499982833862</v>
       </c>
       <c r="G162" t="n">
-        <v>6.42973136901855</v>
+        <v>6.42973184585571</v>
       </c>
       <c r="H162" t="n">
         <v>80746</v>
@@ -5096,7 +5096,7 @@
         <v>7.31500005722046</v>
       </c>
       <c r="G163" t="n">
-        <v>6.66668844223022</v>
+        <v>6.66668891906738</v>
       </c>
       <c r="H163" t="n">
         <v>63073</v>
@@ -5125,7 +5125,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G164" t="n">
-        <v>6.88086175918579</v>
+        <v>6.88086128234863</v>
       </c>
       <c r="H164" t="n">
         <v>59880</v>
@@ -5154,7 +5154,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G165" t="n">
-        <v>6.99478340148926</v>
+        <v>6.9947829246521</v>
       </c>
       <c r="H165" t="n">
         <v>39622</v>
@@ -5241,7 +5241,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G168" t="n">
-        <v>6.99478340148926</v>
+        <v>6.9947829246521</v>
       </c>
       <c r="H168" t="n">
         <v>116551</v>
@@ -5270,7 +5270,7 @@
         <v>7.72499990463257</v>
       </c>
       <c r="G169" t="n">
-        <v>7.04035186767578</v>
+        <v>7.04035139083862</v>
       </c>
       <c r="H169" t="n">
         <v>97576</v>
@@ -5299,7 +5299,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G170" t="n">
-        <v>6.74415588378906</v>
+        <v>6.7441554069519</v>
       </c>
       <c r="H170" t="n">
         <v>54127</v>
@@ -5328,7 +5328,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G171" t="n">
-        <v>6.99478340148926</v>
+        <v>6.9947829246521</v>
       </c>
       <c r="H171" t="n">
         <v>62027</v>
@@ -5357,7 +5357,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G172" t="n">
-        <v>7.2681941986084</v>
+        <v>7.26819467544556</v>
       </c>
       <c r="H172" t="n">
         <v>107198</v>
@@ -5444,7 +5444,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G175" t="n">
-        <v>7.61907196044922</v>
+        <v>7.61907291412354</v>
       </c>
       <c r="H175" t="n">
         <v>67391</v>
@@ -5502,7 +5502,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G177" t="n">
-        <v>7.46413946151733</v>
+        <v>7.46413898468018</v>
       </c>
       <c r="H177" t="n">
         <v>103642</v>
@@ -5560,7 +5560,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G179" t="n">
-        <v>7.33199024200439</v>
+        <v>7.33199071884155</v>
       </c>
       <c r="H179" t="n">
         <v>88870</v>
@@ -5589,7 +5589,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G180" t="n">
-        <v>7.24996709823608</v>
+        <v>7.24996662139893</v>
       </c>
       <c r="H180" t="n">
         <v>63885</v>
@@ -5618,7 +5618,7 @@
         <v>8</v>
       </c>
       <c r="G181" t="n">
-        <v>7.29097938537598</v>
+        <v>7.29097890853882</v>
       </c>
       <c r="H181" t="n">
         <v>44729</v>
@@ -5647,7 +5647,7 @@
         <v>8</v>
       </c>
       <c r="G182" t="n">
-        <v>7.29097938537598</v>
+        <v>7.29097890853882</v>
       </c>
       <c r="H182" t="n">
         <v>68137</v>
@@ -5705,7 +5705,7 @@
         <v>8</v>
       </c>
       <c r="G184" t="n">
-        <v>7.29097938537598</v>
+        <v>7.29097890853882</v>
       </c>
       <c r="H184" t="n">
         <v>53674</v>
@@ -5734,7 +5734,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G185" t="n">
-        <v>7.05402231216431</v>
+        <v>7.05402183532715</v>
       </c>
       <c r="H185" t="n">
         <v>89502</v>
@@ -5763,7 +5763,7 @@
         <v>8</v>
       </c>
       <c r="G186" t="n">
-        <v>7.29097938537598</v>
+        <v>7.29097890853882</v>
       </c>
       <c r="H186" t="n">
         <v>98582</v>
@@ -5850,7 +5850,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G189" t="n">
-        <v>7.2135124206543</v>
+        <v>7.21351194381714</v>
       </c>
       <c r="H189" t="n">
         <v>58048</v>
@@ -5879,7 +5879,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G190" t="n">
-        <v>7.11781787872314</v>
+        <v>7.1178183555603</v>
       </c>
       <c r="H190" t="n">
         <v>29579</v>
@@ -6024,7 +6024,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G195" t="n">
-        <v>7.00845336914062</v>
+        <v>7.00845384597778</v>
       </c>
       <c r="H195" t="n">
         <v>142516</v>
@@ -6082,7 +6082,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G197" t="n">
-        <v>6.926429271698</v>
+        <v>6.92642974853516</v>
       </c>
       <c r="H197" t="n">
         <v>94339</v>
@@ -6140,7 +6140,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G199" t="n">
-        <v>6.42517566680908</v>
+        <v>6.42517518997192</v>
       </c>
       <c r="H199" t="n">
         <v>115768</v>
@@ -6256,7 +6256,7 @@
         <v>7.75</v>
       </c>
       <c r="G203" t="n">
-        <v>7.06313610076904</v>
+        <v>7.06313562393188</v>
       </c>
       <c r="H203" t="n">
         <v>74023</v>
@@ -6285,7 +6285,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G204" t="n">
-        <v>6.83073568344116</v>
+        <v>6.83073616027832</v>
       </c>
       <c r="H204" t="n">
         <v>55532</v>
@@ -6314,7 +6314,7 @@
         <v>7.33500003814697</v>
       </c>
       <c r="G205" t="n">
-        <v>6.6849160194397</v>
+        <v>6.68491649627686</v>
       </c>
       <c r="H205" t="n">
         <v>69663</v>
@@ -6343,7 +6343,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G206" t="n">
-        <v>6.69858694076538</v>
+        <v>6.69858646392822</v>
       </c>
       <c r="H206" t="n">
         <v>115365</v>
@@ -6372,7 +6372,7 @@
         <v>8.46500015258789</v>
       </c>
       <c r="G207" t="n">
-        <v>7.71476745605469</v>
+        <v>7.71476697921753</v>
       </c>
       <c r="H207" t="n">
         <v>667919</v>
@@ -6459,7 +6459,7 @@
         <v>8.40499973297119</v>
       </c>
       <c r="G210" t="n">
-        <v>7.66008424758911</v>
+        <v>7.66008520126343</v>
       </c>
       <c r="H210" t="n">
         <v>162822</v>
@@ -6517,7 +6517,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G212" t="n">
-        <v>7.75577926635742</v>
+        <v>7.75577831268311</v>
       </c>
       <c r="H212" t="n">
         <v>149734</v>
@@ -6604,7 +6604,7 @@
         <v>8.48499965667725</v>
       </c>
       <c r="G215" t="n">
-        <v>7.73299360275269</v>
+        <v>7.73299407958984</v>
       </c>
       <c r="H215" t="n">
         <v>190999</v>
@@ -6691,7 +6691,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G218" t="n">
-        <v>8.0200777053833</v>
+        <v>8.02007675170898</v>
       </c>
       <c r="H218" t="n">
         <v>179237</v>
@@ -6720,7 +6720,7 @@
         <v>9.13500022888184</v>
       </c>
       <c r="G219" t="n">
-        <v>8.32538604736328</v>
+        <v>8.3253870010376</v>
       </c>
       <c r="H219" t="n">
         <v>283069</v>
@@ -6749,7 +6749,7 @@
         <v>9.03499984741211</v>
       </c>
       <c r="G220" t="n">
-        <v>8.23424911499023</v>
+        <v>8.23425006866455</v>
       </c>
       <c r="H220" t="n">
         <v>263459</v>
@@ -6778,7 +6778,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G221" t="n">
-        <v>8.19323825836182</v>
+        <v>8.1932373046875</v>
       </c>
       <c r="H221" t="n">
         <v>194602</v>
@@ -6807,7 +6807,7 @@
         <v>8.84500026702881</v>
       </c>
       <c r="G222" t="n">
-        <v>8.06108856201172</v>
+        <v>8.06108951568604</v>
       </c>
       <c r="H222" t="n">
         <v>71498</v>
@@ -6836,7 +6836,7 @@
         <v>8.86499977111816</v>
       </c>
       <c r="G223" t="n">
-        <v>8.07931613922119</v>
+        <v>8.07931518554688</v>
       </c>
       <c r="H223" t="n">
         <v>111621</v>
@@ -6865,7 +6865,7 @@
         <v>8.79500007629395</v>
       </c>
       <c r="G224" t="n">
-        <v>8.01552104949951</v>
+        <v>8.0155200958252</v>
       </c>
       <c r="H224" t="n">
         <v>122024</v>
@@ -7039,7 +7039,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G230" t="n">
-        <v>7.59173154830933</v>
+        <v>7.59173202514648</v>
       </c>
       <c r="H230" t="n">
         <v>175936</v>
@@ -7126,7 +7126,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G233" t="n">
-        <v>7.60084629058838</v>
+        <v>7.60084581375122</v>
       </c>
       <c r="H233" t="n">
         <v>108751</v>
@@ -7155,7 +7155,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G234" t="n">
-        <v>7.85602903366089</v>
+        <v>7.85602998733521</v>
       </c>
       <c r="H234" t="n">
         <v>185968</v>
@@ -7184,7 +7184,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G235" t="n">
-        <v>7.8195743560791</v>
+        <v>7.81957483291626</v>
       </c>
       <c r="H235" t="n">
         <v>126055</v>
@@ -7213,7 +7213,7 @@
         <v>8.59500026702881</v>
       </c>
       <c r="G236" t="n">
-        <v>7.83324670791626</v>
+        <v>7.83324480056763</v>
       </c>
       <c r="H236" t="n">
         <v>75722</v>
@@ -7271,7 +7271,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G238" t="n">
-        <v>7.86514377593994</v>
+        <v>7.86514329910278</v>
       </c>
       <c r="H238" t="n">
         <v>98511</v>
@@ -7329,7 +7329,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G240" t="n">
-        <v>7.61907196044922</v>
+        <v>7.61907291412354</v>
       </c>
       <c r="H240" t="n">
         <v>242480</v>
@@ -7416,7 +7416,7 @@
         <v>8.29500007629395</v>
       </c>
       <c r="G243" t="n">
-        <v>7.55983304977417</v>
+        <v>7.55983352661133</v>
       </c>
       <c r="H243" t="n">
         <v>179111</v>
@@ -7474,7 +7474,7 @@
         <v>8.15499973297119</v>
       </c>
       <c r="G245" t="n">
-        <v>7.43224096298218</v>
+        <v>7.43224143981934</v>
       </c>
       <c r="H245" t="n">
         <v>95884</v>
@@ -7532,7 +7532,7 @@
         <v>8.5649995803833</v>
       </c>
       <c r="G247" t="n">
-        <v>7.80590343475342</v>
+        <v>7.80590295791626</v>
       </c>
       <c r="H247" t="n">
         <v>190341</v>
@@ -7561,7 +7561,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G248" t="n">
-        <v>7.73755121231079</v>
+        <v>7.73755168914795</v>
       </c>
       <c r="H248" t="n">
         <v>79342</v>
@@ -7619,7 +7619,7 @@
         <v>8.44499969482422</v>
       </c>
       <c r="G250" t="n">
-        <v>7.69653940200806</v>
+        <v>7.6965389251709</v>
       </c>
       <c r="H250" t="n">
         <v>65821</v>
@@ -7648,7 +7648,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G251" t="n">
-        <v>7.76489305496216</v>
+        <v>7.76489353179932</v>
       </c>
       <c r="H251" t="n">
         <v>81589</v>
@@ -7677,7 +7677,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G252" t="n">
-        <v>7.87425851821899</v>
+        <v>7.87425756454468</v>
       </c>
       <c r="H252" t="n">
         <v>52613</v>
@@ -7735,7 +7735,7 @@
         <v>8.64500045776367</v>
       </c>
       <c r="G254" t="n">
-        <v>7.87881374359131</v>
+        <v>7.87881517410278</v>
       </c>
       <c r="H254" t="n">
         <v>56212</v>
@@ -7851,7 +7851,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G258" t="n">
-        <v>8.34817028045654</v>
+        <v>8.34817123413086</v>
       </c>
       <c r="H258" t="n">
         <v>65591</v>
@@ -7880,7 +7880,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G259" t="n">
-        <v>8.43930816650391</v>
+        <v>8.43930912017822</v>
       </c>
       <c r="H259" t="n">
         <v>57907</v>
@@ -8054,7 +8054,7 @@
         <v>9.23499965667725</v>
       </c>
       <c r="G265" t="n">
-        <v>8.41652393341064</v>
+        <v>8.41652297973633</v>
       </c>
       <c r="H265" t="n">
         <v>63237</v>
@@ -8141,7 +8141,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G268" t="n">
-        <v>8.42108058929443</v>
+        <v>8.42107963562012</v>
       </c>
       <c r="H268" t="n">
         <v>38362</v>
@@ -8228,7 +8228,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G271" t="n">
-        <v>8.47576332092285</v>
+        <v>8.47576236724854</v>
       </c>
       <c r="H271" t="n">
         <v>166452</v>
@@ -8257,7 +8257,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G272" t="n">
-        <v>8.46664905548096</v>
+        <v>8.46665000915527</v>
       </c>
       <c r="H272" t="n">
         <v>131322</v>
@@ -8344,7 +8344,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G275" t="n">
-        <v>8.46664905548096</v>
+        <v>8.46665000915527</v>
       </c>
       <c r="H275" t="n">
         <v>56044</v>
@@ -8431,7 +8431,7 @@
         <v>9.66499996185303</v>
       </c>
       <c r="G278" t="n">
-        <v>8.8084135055542</v>
+        <v>8.80841445922852</v>
       </c>
       <c r="H278" t="n">
         <v>41058</v>
@@ -8489,7 +8489,7 @@
         <v>9.40499973297119</v>
       </c>
       <c r="G280" t="n">
-        <v>8.57145595550537</v>
+        <v>8.571457862854</v>
       </c>
       <c r="H280" t="n">
         <v>67802</v>
@@ -8518,7 +8518,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G281" t="n">
-        <v>8.76740264892578</v>
+        <v>8.76740169525146</v>
       </c>
       <c r="H281" t="n">
         <v>53938</v>
@@ -8547,7 +8547,7 @@
         <v>9.625</v>
       </c>
       <c r="G282" t="n">
-        <v>8.77195930480957</v>
+        <v>8.77195835113525</v>
       </c>
       <c r="H282" t="n">
         <v>30701</v>
@@ -8634,7 +8634,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G285" t="n">
-        <v>9.29599761962891</v>
+        <v>9.29599857330322</v>
       </c>
       <c r="H285" t="n">
         <v>110062</v>
@@ -8808,7 +8808,7 @@
         <v>9.4350004196167</v>
       </c>
       <c r="G291" t="n">
-        <v>8.59879875183105</v>
+        <v>8.59879970550537</v>
       </c>
       <c r="H291" t="n">
         <v>100006</v>
@@ -8924,7 +8924,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G295" t="n">
-        <v>8.60335445404053</v>
+        <v>8.60335350036621</v>
       </c>
       <c r="H295" t="n">
         <v>150159</v>
@@ -8982,7 +8982,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G297" t="n">
-        <v>8.82208442687988</v>
+        <v>8.82208347320557</v>
       </c>
       <c r="H297" t="n">
         <v>184820</v>
@@ -9040,7 +9040,7 @@
         <v>9.875</v>
       </c>
       <c r="G299" t="n">
-        <v>8.99980163574219</v>
+        <v>8.9998025894165</v>
       </c>
       <c r="H299" t="n">
         <v>71056</v>
@@ -9098,7 +9098,7 @@
         <v>9.625</v>
       </c>
       <c r="G301" t="n">
-        <v>8.77195930480957</v>
+        <v>8.77195835113525</v>
       </c>
       <c r="H301" t="n">
         <v>62785</v>
@@ -9156,7 +9156,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G303" t="n">
-        <v>8.67626476287842</v>
+        <v>8.67626571655273</v>
       </c>
       <c r="H303" t="n">
         <v>101596</v>
@@ -9214,7 +9214,7 @@
         <v>9.51500034332275</v>
       </c>
       <c r="G305" t="n">
-        <v>8.67170810699463</v>
+        <v>8.67170906066895</v>
       </c>
       <c r="H305" t="n">
         <v>74235</v>
@@ -9272,7 +9272,7 @@
         <v>9.66499996185303</v>
       </c>
       <c r="G307" t="n">
-        <v>8.8084135055542</v>
+        <v>8.80841445922852</v>
       </c>
       <c r="H307" t="n">
         <v>88814</v>
@@ -9359,7 +9359,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G310" t="n">
-        <v>8.71272087097168</v>
+        <v>8.71271991729736</v>
       </c>
       <c r="H310" t="n">
         <v>71168</v>
@@ -9417,7 +9417,7 @@
         <v>9.84500026702881</v>
       </c>
       <c r="G312" t="n">
-        <v>8.97246074676514</v>
+        <v>8.97246170043945</v>
       </c>
       <c r="H312" t="n">
         <v>201439</v>
@@ -9446,7 +9446,7 @@
         <v>9.86499977111816</v>
       </c>
       <c r="G313" t="n">
-        <v>8.99068832397461</v>
+        <v>8.99068737030029</v>
       </c>
       <c r="H313" t="n">
         <v>95525</v>
@@ -9475,7 +9475,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G314" t="n">
-        <v>8.93144989013672</v>
+        <v>8.9314489364624</v>
       </c>
       <c r="H314" t="n">
         <v>79734</v>
@@ -9504,7 +9504,7 @@
         <v>9.5649995803833</v>
       </c>
       <c r="G315" t="n">
-        <v>8.71727657318115</v>
+        <v>8.71727561950684</v>
       </c>
       <c r="H315" t="n">
         <v>125012</v>
@@ -9620,7 +9620,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G319" t="n">
-        <v>8.10210132598877</v>
+        <v>8.10210037231445</v>
       </c>
       <c r="H319" t="n">
         <v>152972</v>
@@ -9678,7 +9678,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G321" t="n">
-        <v>8.26159000396729</v>
+        <v>8.26158905029297</v>
       </c>
       <c r="H321" t="n">
         <v>151215</v>
@@ -9707,7 +9707,7 @@
         <v>9.23499965667725</v>
       </c>
       <c r="G322" t="n">
-        <v>8.41652393341064</v>
+        <v>8.41652297973633</v>
       </c>
       <c r="H322" t="n">
         <v>57007</v>
@@ -9736,7 +9736,7 @@
         <v>9.125</v>
       </c>
       <c r="G323" t="n">
-        <v>8.31627368927002</v>
+        <v>8.31627178192139</v>
       </c>
       <c r="H323" t="n">
         <v>96023</v>
@@ -9765,7 +9765,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G324" t="n">
-        <v>8.23880481719971</v>
+        <v>8.23880577087402</v>
       </c>
       <c r="H324" t="n">
         <v>125245</v>
@@ -9794,7 +9794,7 @@
         <v>9.6850004196167</v>
       </c>
       <c r="G325" t="n">
-        <v>8.82664203643799</v>
+        <v>8.82664108276367</v>
       </c>
       <c r="H325" t="n">
         <v>499802</v>
@@ -9852,7 +9852,7 @@
         <v>9.64500045776367</v>
       </c>
       <c r="G327" t="n">
-        <v>8.79018592834473</v>
+        <v>8.79018688201904</v>
       </c>
       <c r="H327" t="n">
         <v>201564</v>
@@ -9939,7 +9939,7 @@
         <v>9.84500026702881</v>
       </c>
       <c r="G330" t="n">
-        <v>8.97246074676514</v>
+        <v>8.97246170043945</v>
       </c>
       <c r="H330" t="n">
         <v>120285</v>
@@ -9968,7 +9968,7 @@
         <v>9.58500003814697</v>
       </c>
       <c r="G331" t="n">
-        <v>8.73550415039062</v>
+        <v>8.73550510406494</v>
       </c>
       <c r="H331" t="n">
         <v>128694</v>
@@ -9997,7 +9997,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G332" t="n">
-        <v>8.49398994445801</v>
+        <v>8.49399089813232</v>
       </c>
       <c r="H332" t="n">
         <v>110225</v>
@@ -10026,7 +10026,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G333" t="n">
-        <v>8.60335445404053</v>
+        <v>8.60335350036621</v>
       </c>
       <c r="H333" t="n">
         <v>90522</v>
@@ -10084,7 +10084,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G335" t="n">
-        <v>8.48487758636475</v>
+        <v>8.48487663269043</v>
       </c>
       <c r="H335" t="n">
         <v>124173</v>
@@ -10113,7 +10113,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G336" t="n">
-        <v>8.60335445404053</v>
+        <v>8.60335350036621</v>
       </c>
       <c r="H336" t="n">
         <v>169827</v>
@@ -10200,7 +10200,7 @@
         <v>9.36499977111816</v>
       </c>
       <c r="G339" t="n">
-        <v>8.53500175476074</v>
+        <v>8.53500080108643</v>
       </c>
       <c r="H339" t="n">
         <v>78975</v>
@@ -10229,7 +10229,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G340" t="n">
-        <v>8.64892292022705</v>
+        <v>8.64892387390137</v>
       </c>
       <c r="H340" t="n">
         <v>60887</v>
@@ -10258,7 +10258,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G341" t="n">
-        <v>8.42108058929443</v>
+        <v>8.42107963562012</v>
       </c>
       <c r="H341" t="n">
         <v>61904</v>
@@ -10287,7 +10287,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G342" t="n">
-        <v>8.43930816650391</v>
+        <v>8.43930912017822</v>
       </c>
       <c r="H342" t="n">
         <v>40942</v>
@@ -10316,7 +10316,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G343" t="n">
-        <v>8.53955936431885</v>
+        <v>8.53955841064453</v>
       </c>
       <c r="H343" t="n">
         <v>356528</v>
@@ -10403,7 +10403,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G346" t="n">
-        <v>9.25042915344238</v>
+        <v>9.2504301071167</v>
       </c>
       <c r="H346" t="n">
         <v>231979</v>
@@ -10461,7 +10461,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G348" t="n">
-        <v>9.13195133209229</v>
+        <v>9.1319522857666</v>
       </c>
       <c r="H348" t="n">
         <v>160856</v>
@@ -10490,7 +10490,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G349" t="n">
-        <v>9.1866340637207</v>
+        <v>9.18663311004639</v>
       </c>
       <c r="H349" t="n">
         <v>120697</v>
@@ -10635,7 +10635,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G354" t="n">
-        <v>9.02258586883545</v>
+        <v>9.02258682250977</v>
       </c>
       <c r="H354" t="n">
         <v>58371</v>
@@ -10664,7 +10664,7 @@
         <v>9.88500022888184</v>
       </c>
       <c r="G355" t="n">
-        <v>9.00891494750977</v>
+        <v>9.00891590118408</v>
       </c>
       <c r="H355" t="n">
         <v>123367</v>
@@ -10693,7 +10693,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G356" t="n">
-        <v>9.02258586883545</v>
+        <v>9.02258682250977</v>
       </c>
       <c r="H356" t="n">
         <v>51175</v>
@@ -10722,7 +10722,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G357" t="n">
-        <v>9.16840744018555</v>
+        <v>9.16840648651123</v>
       </c>
       <c r="H357" t="n">
         <v>43978</v>
@@ -10751,7 +10751,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G358" t="n">
-        <v>9.46915912628174</v>
+        <v>9.46916007995605</v>
       </c>
       <c r="H358" t="n">
         <v>119140</v>
@@ -10780,7 +10780,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G359" t="n">
-        <v>9.66966152191162</v>
+        <v>9.6696605682373</v>
       </c>
       <c r="H359" t="n">
         <v>147204</v>
@@ -10896,7 +10896,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G363" t="n">
-        <v>9.70611476898193</v>
+        <v>9.70611572265625</v>
       </c>
       <c r="H363" t="n">
         <v>79881</v>
@@ -10954,7 +10954,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G365" t="n">
-        <v>9.33245277404785</v>
+        <v>9.33245182037354</v>
       </c>
       <c r="H365" t="n">
         <v>135405</v>
@@ -10983,7 +10983,7 @@
         <v>9.83500003814697</v>
       </c>
       <c r="G366" t="n">
-        <v>8.96334743499756</v>
+        <v>8.96334838867188</v>
       </c>
       <c r="H366" t="n">
         <v>250182</v>
@@ -11041,7 +11041,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G368" t="n">
-        <v>8.97701835632324</v>
+        <v>8.97701740264893</v>
       </c>
       <c r="H368" t="n">
         <v>58875</v>
@@ -11070,7 +11070,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G369" t="n">
-        <v>8.66715240478516</v>
+        <v>8.66715145111084</v>
       </c>
       <c r="H369" t="n">
         <v>180228</v>
@@ -11099,7 +11099,7 @@
         <v>9.40499973297119</v>
       </c>
       <c r="G370" t="n">
-        <v>8.57145595550537</v>
+        <v>8.571457862854</v>
       </c>
       <c r="H370" t="n">
         <v>122944</v>
@@ -11186,7 +11186,7 @@
         <v>9.65499973297119</v>
       </c>
       <c r="G373" t="n">
-        <v>8.7992992401123</v>
+        <v>8.79930019378662</v>
       </c>
       <c r="H373" t="n">
         <v>110462</v>
@@ -11389,7 +11389,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>9.41868591308594</v>
+        <v>9.41868686676025</v>
       </c>
       <c r="H380" t="n">
         <v>108271</v>
@@ -11505,7 +11505,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G384" t="n">
-        <v>9.41868591308594</v>
+        <v>9.41868686676025</v>
       </c>
       <c r="H384" t="n">
         <v>58349</v>
@@ -11563,7 +11563,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G386" t="n">
-        <v>9.43715476989746</v>
+        <v>9.43715572357178</v>
       </c>
       <c r="H386" t="n">
         <v>588687</v>
@@ -11824,7 +11824,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G395" t="n">
-        <v>9.66800403594971</v>
+        <v>9.66800498962402</v>
       </c>
       <c r="H395" t="n">
         <v>79788</v>
@@ -11911,7 +11911,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G398" t="n">
-        <v>9.42792129516602</v>
+        <v>9.4279203414917</v>
       </c>
       <c r="H398" t="n">
         <v>119704</v>
@@ -11940,7 +11940,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G399" t="n">
-        <v>9.34481334686279</v>
+        <v>9.34481430053711</v>
       </c>
       <c r="H399" t="n">
         <v>45265</v>
@@ -11998,7 +11998,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G401" t="n">
-        <v>9.04932689666748</v>
+        <v>9.04932594299316</v>
       </c>
       <c r="H401" t="n">
         <v>96905</v>
@@ -12056,7 +12056,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G403" t="n">
-        <v>8.79539012908936</v>
+        <v>8.79539108276367</v>
       </c>
       <c r="H403" t="n">
         <v>80618</v>
@@ -12085,7 +12085,7 @@
         <v>9.36499977111816</v>
       </c>
       <c r="G404" t="n">
-        <v>8.6476469039917</v>
+        <v>8.64764595031738</v>
       </c>
       <c r="H404" t="n">
         <v>93583</v>
@@ -12114,7 +12114,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G405" t="n">
-        <v>8.58762645721436</v>
+        <v>8.58762550354004</v>
       </c>
       <c r="H405" t="n">
         <v>464509</v>
@@ -12143,7 +12143,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G406" t="n">
-        <v>8.80000877380371</v>
+        <v>8.80000782012939</v>
       </c>
       <c r="H406" t="n">
         <v>218689</v>
@@ -12172,7 +12172,7 @@
         <v>9.55500030517578</v>
       </c>
       <c r="G407" t="n">
-        <v>8.82309246063232</v>
+        <v>8.82309341430664</v>
       </c>
       <c r="H407" t="n">
         <v>224972</v>
@@ -12201,7 +12201,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G408" t="n">
-        <v>8.93851852416992</v>
+        <v>8.93851757049561</v>
       </c>
       <c r="H408" t="n">
         <v>244272</v>
@@ -12230,7 +12230,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G409" t="n">
-        <v>8.7169017791748</v>
+        <v>8.71690082550049</v>
       </c>
       <c r="H409" t="n">
         <v>213955</v>
@@ -12288,7 +12288,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G411" t="n">
-        <v>8.82771110534668</v>
+        <v>8.82771015167236</v>
       </c>
       <c r="H411" t="n">
         <v>189726</v>
@@ -12375,7 +12375,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G414" t="n">
-        <v>8.50452041625977</v>
+        <v>8.50451946258545</v>
       </c>
       <c r="H414" t="n">
         <v>71607</v>
@@ -12404,7 +12404,7 @@
         <v>9.21500015258789</v>
       </c>
       <c r="G415" t="n">
-        <v>8.50913619995117</v>
+        <v>8.50913715362549</v>
       </c>
       <c r="H415" t="n">
         <v>86476</v>
@@ -12433,7 +12433,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G416" t="n">
-        <v>8.67073154449463</v>
+        <v>8.67073249816895</v>
       </c>
       <c r="H416" t="n">
         <v>133259</v>
@@ -12665,7 +12665,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G424" t="n">
-        <v>8.05205345153809</v>
+        <v>8.0520544052124</v>
       </c>
       <c r="H424" t="n">
         <v>141617</v>
@@ -12723,7 +12723,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G426" t="n">
-        <v>7.92277669906616</v>
+        <v>7.92277717590332</v>
       </c>
       <c r="H426" t="n">
         <v>224688</v>
@@ -12752,7 +12752,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G427" t="n">
-        <v>7.82120323181152</v>
+        <v>7.82120370864868</v>
       </c>
       <c r="H427" t="n">
         <v>315397</v>
@@ -12781,7 +12781,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G428" t="n">
-        <v>7.82120323181152</v>
+        <v>7.82120370864868</v>
       </c>
       <c r="H428" t="n">
         <v>153923</v>
@@ -12810,7 +12810,7 @@
         <v>8.46500015258789</v>
       </c>
       <c r="G429" t="n">
-        <v>7.81658697128296</v>
+        <v>7.8165864944458</v>
       </c>
       <c r="H429" t="n">
         <v>124892</v>
@@ -12868,7 +12868,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G431" t="n">
-        <v>7.81196928024292</v>
+        <v>7.81196975708008</v>
       </c>
       <c r="H431" t="n">
         <v>211938</v>
@@ -12926,7 +12926,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G433" t="n">
-        <v>7.5441837310791</v>
+        <v>7.54418325424194</v>
       </c>
       <c r="H433" t="n">
         <v>411895</v>
@@ -13013,7 +13013,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G436" t="n">
-        <v>7.10095071792603</v>
+        <v>7.10095119476318</v>
       </c>
       <c r="H436" t="n">
         <v>185032</v>
@@ -13042,7 +13042,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G437" t="n">
-        <v>7.16558885574341</v>
+        <v>7.16558933258057</v>
       </c>
       <c r="H437" t="n">
         <v>348774</v>
@@ -13071,7 +13071,7 @@
         <v>7.72499990463257</v>
       </c>
       <c r="G438" t="n">
-        <v>7.13327026367188</v>
+        <v>7.13326978683472</v>
       </c>
       <c r="H438" t="n">
         <v>174564</v>
@@ -13100,7 +13100,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G439" t="n">
-        <v>7.12403583526611</v>
+        <v>7.12403631210327</v>
       </c>
       <c r="H439" t="n">
         <v>206525</v>
@@ -13245,7 +13245,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G444" t="n">
-        <v>6.61154842376709</v>
+        <v>6.61154890060425</v>
       </c>
       <c r="H444" t="n">
         <v>161687</v>
@@ -13274,7 +13274,7 @@
         <v>7.02500009536743</v>
       </c>
       <c r="G445" t="n">
-        <v>6.48688983917236</v>
+        <v>6.48688936233521</v>
       </c>
       <c r="H445" t="n">
         <v>144224</v>
@@ -13332,7 +13332,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G447" t="n">
-        <v>6.33452892303467</v>
+        <v>6.33452844619751</v>
       </c>
       <c r="H447" t="n">
         <v>231466</v>
@@ -13361,7 +13361,7 @@
         <v>7.13500022888184</v>
       </c>
       <c r="G448" t="n">
-        <v>6.58846378326416</v>
+        <v>6.588463306427</v>
       </c>
       <c r="H448" t="n">
         <v>537214</v>
@@ -13419,7 +13419,7 @@
         <v>7.31500005722046</v>
       </c>
       <c r="G450" t="n">
-        <v>6.75467538833618</v>
+        <v>6.75467586517334</v>
       </c>
       <c r="H450" t="n">
         <v>323055</v>
@@ -13477,7 +13477,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G452" t="n">
-        <v>6.55614423751831</v>
+        <v>6.55614471435547</v>
       </c>
       <c r="H452" t="n">
         <v>185501</v>
@@ -13622,7 +13622,7 @@
         <v>7.25</v>
       </c>
       <c r="G457" t="n">
-        <v>6.69465446472168</v>
+        <v>6.69465494155884</v>
       </c>
       <c r="H457" t="n">
         <v>280368</v>
@@ -13651,7 +13651,7 @@
         <v>7.09499979019165</v>
       </c>
       <c r="G458" t="n">
-        <v>6.55152702331543</v>
+        <v>6.55152750015259</v>
       </c>
       <c r="H458" t="n">
         <v>694126</v>
@@ -13680,7 +13680,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G459" t="n">
-        <v>6.55614423751831</v>
+        <v>6.55614471435547</v>
       </c>
       <c r="H459" t="n">
         <v>342488</v>
@@ -13738,7 +13738,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G461" t="n">
-        <v>6.37146472930908</v>
+        <v>6.37146425247192</v>
       </c>
       <c r="H461" t="n">
         <v>296679</v>
@@ -13767,7 +13767,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G462" t="n">
-        <v>6.37146472930908</v>
+        <v>6.37146425247192</v>
       </c>
       <c r="H462" t="n">
         <v>4069866</v>
@@ -13854,7 +13854,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G465" t="n">
-        <v>6.18678426742554</v>
+        <v>6.18678379058838</v>
       </c>
       <c r="H465" t="n">
         <v>200486</v>
@@ -13883,7 +13883,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G466" t="n">
-        <v>5.80818939208984</v>
+        <v>5.808189868927</v>
       </c>
       <c r="H466" t="n">
         <v>501243</v>
@@ -13970,7 +13970,7 @@
         <v>5.84499979019165</v>
       </c>
       <c r="G469" t="n">
-        <v>5.39727640151978</v>
+        <v>5.39727687835693</v>
       </c>
       <c r="H469" t="n">
         <v>467466</v>
@@ -14028,7 +14028,7 @@
         <v>5.875</v>
       </c>
       <c r="G471" t="n">
-        <v>5.42497873306274</v>
+        <v>5.4249792098999</v>
       </c>
       <c r="H471" t="n">
         <v>292652</v>
@@ -14057,7 +14057,7 @@
         <v>6.16499996185303</v>
       </c>
       <c r="G472" t="n">
-        <v>5.69276475906372</v>
+        <v>5.69276523590088</v>
       </c>
       <c r="H472" t="n">
         <v>637767</v>
@@ -14086,7 +14086,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G473" t="n">
-        <v>5.59580755233765</v>
+        <v>5.5958080291748</v>
       </c>
       <c r="H473" t="n">
         <v>246202</v>
@@ -14144,7 +14144,7 @@
         <v>5.82499980926514</v>
       </c>
       <c r="G475" t="n">
-        <v>5.37880849838257</v>
+        <v>5.37880897521973</v>
       </c>
       <c r="H475" t="n">
         <v>758444</v>
@@ -14260,7 +14260,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G479" t="n">
-        <v>5.70661544799805</v>
+        <v>5.70661592483521</v>
       </c>
       <c r="H479" t="n">
         <v>248086</v>
@@ -14289,7 +14289,7 @@
         <v>5.9850001335144</v>
       </c>
       <c r="G480" t="n">
-        <v>5.5265531539917</v>
+        <v>5.52655267715454</v>
       </c>
       <c r="H480" t="n">
         <v>491648</v>
@@ -14318,7 +14318,7 @@
         <v>5.86499977111816</v>
       </c>
       <c r="G481" t="n">
-        <v>5.41574478149414</v>
+        <v>5.41574430465698</v>
       </c>
       <c r="H481" t="n">
         <v>276524</v>
@@ -14463,7 +14463,7 @@
         <v>5.75</v>
       </c>
       <c r="G486" t="n">
-        <v>5.30955410003662</v>
+        <v>5.30955362319946</v>
       </c>
       <c r="H486" t="n">
         <v>311135</v>
@@ -14550,7 +14550,7 @@
         <v>5.45499992370605</v>
       </c>
       <c r="G489" t="n">
-        <v>5.03715038299561</v>
+        <v>5.03714990615845</v>
       </c>
       <c r="H489" t="n">
         <v>208132</v>
@@ -14608,7 +14608,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G491" t="n">
-        <v>4.95404434204102</v>
+        <v>4.95404386520386</v>
       </c>
       <c r="H491" t="n">
         <v>378086</v>
@@ -14666,7 +14666,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G493" t="n">
-        <v>4.83400201797485</v>
+        <v>4.83400249481201</v>
       </c>
       <c r="H493" t="n">
         <v>200923</v>
@@ -14695,7 +14695,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G494" t="n">
-        <v>4.88478899002075</v>
+        <v>4.88478946685791</v>
       </c>
       <c r="H494" t="n">
         <v>111362</v>
@@ -14724,7 +14724,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G495" t="n">
-        <v>4.88940620422363</v>
+        <v>4.88940668106079</v>
       </c>
       <c r="H495" t="n">
         <v>133883</v>
@@ -14753,7 +14753,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G496" t="n">
-        <v>5.13410711288452</v>
+        <v>5.13410758972168</v>
       </c>
       <c r="H496" t="n">
         <v>302728</v>
@@ -14782,7 +14782,7 @@
         <v>5.77500009536743</v>
       </c>
       <c r="G497" t="n">
-        <v>5.33263874053955</v>
+        <v>5.33263826370239</v>
       </c>
       <c r="H497" t="n">
         <v>328997</v>
@@ -14811,7 +14811,7 @@
         <v>5.61499977111816</v>
       </c>
       <c r="G498" t="n">
-        <v>5.18489456176758</v>
+        <v>5.18489408493042</v>
       </c>
       <c r="H498" t="n">
         <v>207381</v>
@@ -14869,7 +14869,7 @@
         <v>5.69500017166138</v>
       </c>
       <c r="G500" t="n">
-        <v>5.25876665115356</v>
+        <v>5.25876712799072</v>
       </c>
       <c r="H500" t="n">
         <v>671518</v>
@@ -14898,7 +14898,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G501" t="n">
-        <v>5.38342523574829</v>
+        <v>5.38342571258545</v>
       </c>
       <c r="H501" t="n">
         <v>200804</v>
@@ -15130,7 +15130,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G509" t="n">
-        <v>5.24491500854492</v>
+        <v>5.24491548538208</v>
       </c>
       <c r="H509" t="n">
         <v>138219</v>
@@ -15159,7 +15159,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G510" t="n">
-        <v>5.21259689331055</v>
+        <v>5.21259641647339</v>
       </c>
       <c r="H510" t="n">
         <v>110937</v>
@@ -15246,7 +15246,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G513" t="n">
-        <v>5.21259689331055</v>
+        <v>5.21259641647339</v>
       </c>
       <c r="H513" t="n">
         <v>215173</v>
@@ -15304,7 +15304,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G515" t="n">
-        <v>5.11563968658447</v>
+        <v>5.11563920974731</v>
       </c>
       <c r="H515" t="n">
         <v>481344</v>
@@ -15362,7 +15362,7 @@
         <v>5.72499990463257</v>
       </c>
       <c r="G517" t="n">
-        <v>5.28646850585938</v>
+        <v>5.28646898269653</v>
       </c>
       <c r="H517" t="n">
         <v>250687</v>
@@ -15391,7 +15391,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G518" t="n">
-        <v>5.24491500854492</v>
+        <v>5.24491548538208</v>
       </c>
       <c r="H518" t="n">
         <v>260768</v>
@@ -15420,7 +15420,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G519" t="n">
-        <v>5.25414991378784</v>
+        <v>5.25414943695068</v>
       </c>
       <c r="H519" t="n">
         <v>250927</v>
@@ -15536,7 +15536,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G523" t="n">
-        <v>5.16180992126465</v>
+        <v>5.16180944442749</v>
       </c>
       <c r="H523" t="n">
         <v>249552</v>
@@ -15797,7 +15797,7 @@
         <v>6.30499982833862</v>
       </c>
       <c r="G532" t="n">
-        <v>5.82204103469849</v>
+        <v>5.82204055786133</v>
       </c>
       <c r="H532" t="n">
         <v>298757</v>
@@ -15826,7 +15826,7 @@
         <v>6.40500020980835</v>
       </c>
       <c r="G533" t="n">
-        <v>5.91438150405884</v>
+        <v>5.91438102722168</v>
       </c>
       <c r="H533" t="n">
         <v>366529</v>
@@ -15884,7 +15884,7 @@
         <v>6.2649998664856</v>
       </c>
       <c r="G535" t="n">
-        <v>5.78510522842407</v>
+        <v>5.78510475158691</v>
       </c>
       <c r="H535" t="n">
         <v>171909</v>
@@ -15913,7 +15913,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G536" t="n">
-        <v>5.71585035324097</v>
+        <v>5.71584987640381</v>
       </c>
       <c r="H536" t="n">
         <v>257462</v>
@@ -16000,7 +16000,7 @@
         <v>6.38500022888184</v>
       </c>
       <c r="G539" t="n">
-        <v>5.89591312408447</v>
+        <v>5.89591360092163</v>
       </c>
       <c r="H539" t="n">
         <v>946632</v>
@@ -16058,7 +16058,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G541" t="n">
-        <v>6.05750751495361</v>
+        <v>6.05750846862793</v>
       </c>
       <c r="H541" t="n">
         <v>374625</v>
@@ -16319,7 +16319,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G550" t="n">
-        <v>5.62812662124634</v>
+        <v>5.6281270980835</v>
       </c>
       <c r="H550" t="n">
         <v>208450</v>
@@ -16348,7 +16348,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G551" t="n">
-        <v>5.70661544799805</v>
+        <v>5.70661592483521</v>
       </c>
       <c r="H551" t="n">
         <v>159509</v>
@@ -16377,7 +16377,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G552" t="n">
-        <v>5.70661544799805</v>
+        <v>5.70661592483521</v>
       </c>
       <c r="H552" t="n">
         <v>128983</v>
@@ -16406,7 +16406,7 @@
         <v>6.22499990463257</v>
       </c>
       <c r="G553" t="n">
-        <v>5.7481689453125</v>
+        <v>5.74816942214966</v>
       </c>
       <c r="H553" t="n">
         <v>87583</v>
@@ -16435,7 +16435,7 @@
         <v>6.29500007629395</v>
       </c>
       <c r="G554" t="n">
-        <v>5.81280755996704</v>
+        <v>5.81280708312988</v>
       </c>
       <c r="H554" t="n">
         <v>151233</v>
@@ -16464,7 +16464,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G555" t="n">
-        <v>5.71585035324097</v>
+        <v>5.71584987640381</v>
       </c>
       <c r="H555" t="n">
         <v>675111</v>
@@ -16493,7 +16493,7 @@
         <v>6.06500005722046</v>
       </c>
       <c r="G556" t="n">
-        <v>5.60042476654053</v>
+        <v>5.60042524337769</v>
       </c>
       <c r="H556" t="n">
         <v>275234</v>
@@ -16638,7 +16638,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G561" t="n">
-        <v>5.36957454681396</v>
+        <v>5.36957502365112</v>
       </c>
       <c r="H561" t="n">
         <v>298629</v>
@@ -16754,7 +16754,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G565" t="n">
-        <v>5.51270198822021</v>
+        <v>5.51270151138306</v>
       </c>
       <c r="H565" t="n">
         <v>164534</v>
@@ -16783,7 +16783,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G566" t="n">
-        <v>5.38342523574829</v>
+        <v>5.38342571258545</v>
       </c>
       <c r="H566" t="n">
         <v>143325</v>
@@ -16957,7 +16957,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G572" t="n">
-        <v>5.24029874801636</v>
+        <v>5.2402982711792</v>
       </c>
       <c r="H572" t="n">
         <v>371542</v>
@@ -17044,7 +17044,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G575" t="n">
-        <v>5.13410711288452</v>
+        <v>5.13410758972168</v>
       </c>
       <c r="H575" t="n">
         <v>302344</v>
@@ -17073,7 +17073,7 @@
         <v>5.70499992370605</v>
       </c>
       <c r="G576" t="n">
-        <v>5.26800060272217</v>
+        <v>5.26800012588501</v>
       </c>
       <c r="H576" t="n">
         <v>379568</v>
@@ -17189,7 +17189,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G580" t="n">
-        <v>5.09717082977295</v>
+        <v>5.09717130661011</v>
       </c>
       <c r="H580" t="n">
         <v>391172</v>
@@ -17218,7 +17218,7 @@
         <v>5.45499992370605</v>
       </c>
       <c r="G581" t="n">
-        <v>5.03715038299561</v>
+        <v>5.03714990615845</v>
       </c>
       <c r="H581" t="n">
         <v>1475414</v>
@@ -17305,7 +17305,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G584" t="n">
-        <v>5.374192237854</v>
+        <v>5.37419176101685</v>
       </c>
       <c r="H584" t="n">
         <v>450011</v>
@@ -17421,7 +17421,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G588" t="n">
-        <v>5.59580755233765</v>
+        <v>5.5958080291748</v>
       </c>
       <c r="H588" t="n">
         <v>428003</v>
@@ -17450,7 +17450,7 @@
         <v>6.06500005722046</v>
       </c>
       <c r="G589" t="n">
-        <v>5.60042476654053</v>
+        <v>5.60042524337769</v>
       </c>
       <c r="H589" t="n">
         <v>462275</v>
@@ -17479,7 +17479,7 @@
         <v>5.72499990463257</v>
       </c>
       <c r="G590" t="n">
-        <v>5.28646850585938</v>
+        <v>5.28646898269653</v>
       </c>
       <c r="H590" t="n">
         <v>562114</v>
@@ -17595,7 +17595,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G594" t="n">
-        <v>5.05100154876709</v>
+        <v>5.05100107192993</v>
       </c>
       <c r="H594" t="n">
         <v>677677</v>
@@ -17682,7 +17682,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G597" t="n">
-        <v>4.83400201797485</v>
+        <v>4.83400249481201</v>
       </c>
       <c r="H597" t="n">
         <v>384652</v>
@@ -17740,7 +17740,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G599" t="n">
-        <v>4.70010948181152</v>
+        <v>4.70010900497437</v>
       </c>
       <c r="H599" t="n">
         <v>555539</v>
@@ -17769,7 +17769,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G600" t="n">
-        <v>4.81091785430908</v>
+        <v>4.81091737747192</v>
       </c>
       <c r="H600" t="n">
         <v>367022</v>
@@ -17856,7 +17856,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G603" t="n">
-        <v>4.89864063262939</v>
+        <v>4.89864015579224</v>
       </c>
       <c r="H603" t="n">
         <v>510591</v>
@@ -17914,7 +17914,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G605" t="n">
-        <v>4.66317367553711</v>
+        <v>4.66317319869995</v>
       </c>
       <c r="H605" t="n">
         <v>1112720</v>
@@ -17943,7 +17943,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>4.52466344833374</v>
+        <v>4.52466297149658</v>
       </c>
       <c r="H606" t="n">
         <v>835466</v>
@@ -17972,7 +17972,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G607" t="n">
-        <v>4.52466344833374</v>
+        <v>4.52466297149658</v>
       </c>
       <c r="H607" t="n">
         <v>662577</v>
@@ -18001,7 +18001,7 @@
         <v>4.82200002670288</v>
       </c>
       <c r="G608" t="n">
-        <v>4.45263767242432</v>
+        <v>4.45263814926147</v>
       </c>
       <c r="H608" t="n">
         <v>597938</v>
@@ -18059,7 +18059,7 @@
         <v>4.66400003433228</v>
       </c>
       <c r="G610" t="n">
-        <v>4.30674028396606</v>
+        <v>4.30674076080322</v>
       </c>
       <c r="H610" t="n">
         <v>394307</v>
@@ -18117,7 +18117,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G612" t="n">
-        <v>4.3584508895874</v>
+        <v>4.35845041275024</v>
       </c>
       <c r="H612" t="n">
         <v>462964</v>
@@ -18175,7 +18175,7 @@
         <v>4.74399995803833</v>
       </c>
       <c r="G614" t="n">
-        <v>4.38061285018921</v>
+        <v>4.38061237335205</v>
       </c>
       <c r="H614" t="n">
         <v>609563</v>
@@ -18233,7 +18233,7 @@
         <v>4.71799993515015</v>
       </c>
       <c r="G616" t="n">
-        <v>4.35660409927368</v>
+        <v>4.35660362243652</v>
       </c>
       <c r="H616" t="n">
         <v>435069</v>
@@ -18349,7 +18349,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G620" t="n">
-        <v>4.50619506835938</v>
+        <v>4.50619554519653</v>
       </c>
       <c r="H620" t="n">
         <v>279339</v>
@@ -18378,7 +18378,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G621" t="n">
-        <v>4.56898593902588</v>
+        <v>4.56898641586304</v>
       </c>
       <c r="H621" t="n">
         <v>377386</v>
@@ -18407,7 +18407,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G622" t="n">
-        <v>4.70934295654297</v>
+        <v>4.70934343338013</v>
       </c>
       <c r="H622" t="n">
         <v>579073</v>
@@ -18465,7 +18465,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G624" t="n">
-        <v>4.62623739242554</v>
+        <v>4.6262378692627</v>
       </c>
       <c r="H624" t="n">
         <v>1420570</v>
@@ -18552,7 +18552,7 @@
         <v>4.97800016403198</v>
       </c>
       <c r="G627" t="n">
-        <v>4.59668827056885</v>
+        <v>4.59668874740601</v>
       </c>
       <c r="H627" t="n">
         <v>698215</v>
@@ -18581,7 +18581,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G628" t="n">
-        <v>4.70010948181152</v>
+        <v>4.70010900497437</v>
       </c>
       <c r="H628" t="n">
         <v>666276</v>
@@ -18610,7 +18610,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G629" t="n">
-        <v>4.60776901245117</v>
+        <v>4.60776853561401</v>
       </c>
       <c r="H629" t="n">
         <v>695656</v>
@@ -18639,7 +18639,7 @@
         <v>5.0149998664856</v>
       </c>
       <c r="G630" t="n">
-        <v>4.6308536529541</v>
+        <v>4.63085412979126</v>
       </c>
       <c r="H630" t="n">
         <v>580822</v>
@@ -18726,7 +18726,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G633" t="n">
-        <v>4.63421249389648</v>
+        <v>4.63421201705933</v>
       </c>
       <c r="H633" t="n">
         <v>659569</v>
@@ -18900,7 +18900,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G639" t="n">
-        <v>4.47546625137329</v>
+        <v>4.47546672821045</v>
       </c>
       <c r="H639" t="n">
         <v>721270</v>
@@ -18929,7 +18929,7 @@
         <v>4.81199979782104</v>
       </c>
       <c r="G640" t="n">
-        <v>4.60169744491577</v>
+        <v>4.60169792175293</v>
       </c>
       <c r="H640" t="n">
         <v>409298</v>
@@ -19074,7 +19074,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G645" t="n">
-        <v>4.45634078979492</v>
+        <v>4.45634031295776</v>
       </c>
       <c r="H645" t="n">
         <v>337361</v>
@@ -19132,7 +19132,7 @@
         <v>4.62400007247925</v>
       </c>
       <c r="G647" t="n">
-        <v>4.42191410064697</v>
+        <v>4.42191457748413</v>
       </c>
       <c r="H647" t="n">
         <v>590963</v>
@@ -19219,7 +19219,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G650" t="n">
-        <v>4.17136478424072</v>
+        <v>4.17136430740356</v>
       </c>
       <c r="H650" t="n">
         <v>575556</v>
@@ -19306,7 +19306,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G653" t="n">
-        <v>4.20770406723022</v>
+        <v>4.20770359039307</v>
       </c>
       <c r="H653" t="n">
         <v>253568</v>
@@ -19480,7 +19480,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G659" t="n">
-        <v>3.93037796020508</v>
+        <v>3.9303777217865</v>
       </c>
       <c r="H659" t="n">
         <v>499794</v>
@@ -19770,7 +19770,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G669" t="n">
-        <v>3.65496468544006</v>
+        <v>3.65496444702148</v>
       </c>
       <c r="H669" t="n">
         <v>556073</v>
@@ -19857,7 +19857,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G672" t="n">
-        <v>3.81370949745178</v>
+        <v>3.81370973587036</v>
       </c>
       <c r="H672" t="n">
         <v>401105</v>
@@ -19886,7 +19886,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G673" t="n">
-        <v>3.81370949745178</v>
+        <v>3.81370973587036</v>
       </c>
       <c r="H673" t="n">
         <v>294689</v>
@@ -19915,7 +19915,7 @@
         <v>4.17600011825562</v>
       </c>
       <c r="G674" t="n">
-        <v>3.99349355697632</v>
+        <v>3.99349331855774</v>
       </c>
       <c r="H674" t="n">
         <v>714573</v>
@@ -20379,7 +20379,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G690" t="n">
-        <v>3.45605492591858</v>
+        <v>3.4560546875</v>
       </c>
       <c r="H690" t="n">
         <v>383156</v>
@@ -20756,7 +20756,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G703" t="n">
-        <v>3.96862959861755</v>
+        <v>3.96862983703613</v>
       </c>
       <c r="H703" t="n">
         <v>402206</v>
@@ -20785,7 +20785,7 @@
         <v>4.1560001373291</v>
       </c>
       <c r="G704" t="n">
-        <v>3.97436785697937</v>
+        <v>3.97436738014221</v>
       </c>
       <c r="H704" t="n">
         <v>366565</v>
@@ -20843,7 +20843,7 @@
         <v>4.27600002288818</v>
       </c>
       <c r="G706" t="n">
-        <v>4.0891227722168</v>
+        <v>4.08912324905396</v>
       </c>
       <c r="H706" t="n">
         <v>382472</v>
@@ -20872,7 +20872,7 @@
         <v>4.13600015640259</v>
       </c>
       <c r="G707" t="n">
-        <v>3.95524168014526</v>
+        <v>3.95524144172668</v>
       </c>
       <c r="H707" t="n">
         <v>503313</v>
@@ -20930,7 +20930,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G709" t="n">
-        <v>3.98966813087463</v>
+        <v>3.98966789245605</v>
       </c>
       <c r="H709" t="n">
         <v>357159</v>
@@ -21017,7 +21017,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G712" t="n">
-        <v>3.67026519775391</v>
+        <v>3.67026543617249</v>
       </c>
       <c r="H712" t="n">
         <v>437455</v>
@@ -21162,7 +21162,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G717" t="n">
-        <v>3.81370949745178</v>
+        <v>3.81370973587036</v>
       </c>
       <c r="H717" t="n">
         <v>286225</v>
@@ -21191,7 +21191,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G718" t="n">
-        <v>3.82327270507812</v>
+        <v>3.82327246665955</v>
       </c>
       <c r="H718" t="n">
         <v>150642</v>
@@ -21220,7 +21220,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G719" t="n">
-        <v>3.91507697105408</v>
+        <v>3.91507720947266</v>
       </c>
       <c r="H719" t="n">
         <v>372351</v>
@@ -21307,7 +21307,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G722" t="n">
-        <v>3.98584294319153</v>
+        <v>3.98584318161011</v>
       </c>
       <c r="H722" t="n">
         <v>634315</v>
@@ -21365,7 +21365,7 @@
         <v>4.42600011825562</v>
       </c>
       <c r="G724" t="n">
-        <v>4.23256778717041</v>
+        <v>4.23256731033325</v>
       </c>
       <c r="H724" t="n">
         <v>1439555</v>
@@ -21394,7 +21394,7 @@
         <v>4.51200008392334</v>
       </c>
       <c r="G725" t="n">
-        <v>4.31480884552002</v>
+        <v>4.31480932235718</v>
       </c>
       <c r="H725" t="n">
         <v>724657</v>
@@ -21452,7 +21452,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G727" t="n">
-        <v>4.15032625198364</v>
+        <v>4.15032577514648</v>
       </c>
       <c r="H727" t="n">
         <v>336308</v>
@@ -21510,7 +21510,7 @@
         <v>4.25</v>
       </c>
       <c r="G729" t="n">
-        <v>4.06425905227661</v>
+        <v>4.06425952911377</v>
       </c>
       <c r="H729" t="n">
         <v>168991</v>
@@ -21597,7 +21597,7 @@
         <v>4.2039999961853</v>
       </c>
       <c r="G732" t="n">
-        <v>4.0202693939209</v>
+        <v>4.02026987075806</v>
       </c>
       <c r="H732" t="n">
         <v>193502</v>
@@ -21742,7 +21742,7 @@
         <v>4.11399984359741</v>
       </c>
       <c r="G737" t="n">
-        <v>3.93420267105103</v>
+        <v>3.9342029094696</v>
       </c>
       <c r="H737" t="n">
         <v>129269</v>
@@ -21829,7 +21829,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G740" t="n">
-        <v>3.96862959861755</v>
+        <v>3.96862983703613</v>
       </c>
       <c r="H740" t="n">
         <v>236046</v>
@@ -21858,7 +21858,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G741" t="n">
-        <v>3.91507697105408</v>
+        <v>3.91507720947266</v>
       </c>
       <c r="H741" t="n">
         <v>182762</v>
@@ -22061,7 +22061,7 @@
         <v>3.90799999237061</v>
       </c>
       <c r="G748" t="n">
-        <v>3.73720574378967</v>
+        <v>3.73720598220825</v>
       </c>
       <c r="H748" t="n">
         <v>191909</v>
@@ -22119,7 +22119,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G750" t="n">
-        <v>3.70086669921875</v>
+        <v>3.70086646080017</v>
       </c>
       <c r="H750" t="n">
         <v>77185</v>
@@ -22148,7 +22148,7 @@
         <v>3.93799996376038</v>
       </c>
       <c r="G751" t="n">
-        <v>3.76589488983154</v>
+        <v>3.76589465141296</v>
       </c>
       <c r="H751" t="n">
         <v>138045</v>
@@ -22264,7 +22264,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G755" t="n">
-        <v>3.73911881446838</v>
+        <v>3.7391185760498</v>
       </c>
       <c r="H755" t="n">
         <v>208777</v>
@@ -22380,7 +22380,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G759" t="n">
-        <v>3.57846093177795</v>
+        <v>3.57846069335938</v>
       </c>
       <c r="H759" t="n">
         <v>337584</v>
@@ -22409,7 +22409,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G760" t="n">
-        <v>3.62245059013367</v>
+        <v>3.62245035171509</v>
       </c>
       <c r="H760" t="n">
         <v>422072</v>
@@ -22467,7 +22467,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G762" t="n">
-        <v>3.56315994262695</v>
+        <v>3.56316018104553</v>
       </c>
       <c r="H762" t="n">
         <v>704289</v>
@@ -22496,7 +22496,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G763" t="n">
-        <v>3.54785919189453</v>
+        <v>3.54785943031311</v>
       </c>
       <c r="H763" t="n">
         <v>1097480</v>
@@ -22583,7 +22583,7 @@
         <v>3.64800000190735</v>
       </c>
       <c r="G766" t="n">
-        <v>3.48856902122498</v>
+        <v>3.4885687828064</v>
       </c>
       <c r="H766" t="n">
         <v>1669355</v>
@@ -22728,7 +22728,7 @@
         <v>3.64400005340576</v>
       </c>
       <c r="G771" t="n">
-        <v>3.48474359512329</v>
+        <v>3.48474383354187</v>
       </c>
       <c r="H771" t="n">
         <v>105519</v>
@@ -22757,7 +22757,7 @@
         <v>3.63199996948242</v>
       </c>
       <c r="G772" t="n">
-        <v>3.47326827049255</v>
+        <v>3.47326803207397</v>
       </c>
       <c r="H772" t="n">
         <v>121534</v>
@@ -22873,7 +22873,7 @@
         <v>3.95799994468689</v>
       </c>
       <c r="G776" t="n">
-        <v>3.78502082824707</v>
+        <v>3.78502058982849</v>
       </c>
       <c r="H776" t="n">
         <v>243650</v>
@@ -22902,7 +22902,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G777" t="n">
-        <v>3.76971983909607</v>
+        <v>3.76972007751465</v>
       </c>
       <c r="H777" t="n">
         <v>111182</v>
@@ -22960,7 +22960,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G779" t="n">
-        <v>3.70086669921875</v>
+        <v>3.70086646080017</v>
       </c>
       <c r="H779" t="n">
         <v>145693</v>
@@ -22989,7 +22989,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G780" t="n">
-        <v>3.59758687019348</v>
+        <v>3.5975866317749</v>
       </c>
       <c r="H780" t="n">
         <v>157659</v>
@@ -23076,7 +23076,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G783" t="n">
-        <v>3.44075393676758</v>
+        <v>3.44075417518616</v>
       </c>
       <c r="H783" t="n">
         <v>613580</v>
@@ -23105,7 +23105,7 @@
         <v>3.41599988937378</v>
       </c>
       <c r="G784" t="n">
-        <v>3.26670813560486</v>
+        <v>3.26670789718628</v>
       </c>
       <c r="H784" t="n">
         <v>455535</v>
@@ -23134,7 +23134,7 @@
         <v>3.41599988937378</v>
       </c>
       <c r="G785" t="n">
-        <v>3.26670813560486</v>
+        <v>3.26670789718628</v>
       </c>
       <c r="H785" t="n">
         <v>519347</v>
@@ -23163,7 +23163,7 @@
         <v>3.46799993515015</v>
       </c>
       <c r="G786" t="n">
-        <v>3.31643533706665</v>
+        <v>3.31643557548523</v>
       </c>
       <c r="H786" t="n">
         <v>202674</v>
@@ -23192,7 +23192,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G787" t="n">
-        <v>3.29157161712646</v>
+        <v>3.29157185554504</v>
       </c>
       <c r="H787" t="n">
         <v>188696</v>
@@ -23424,7 +23424,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G795" t="n">
-        <v>3.20741772651672</v>
+        <v>3.2074179649353</v>
       </c>
       <c r="H795" t="n">
         <v>383770</v>
@@ -23801,7 +23801,7 @@
         <v>3.47399997711182</v>
       </c>
       <c r="G808" t="n">
-        <v>3.32217335700989</v>
+        <v>3.32217311859131</v>
       </c>
       <c r="H808" t="n">
         <v>80720</v>
@@ -23975,7 +23975,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G814" t="n">
-        <v>3.22654366493225</v>
+        <v>3.22654390335083</v>
       </c>
       <c r="H814" t="n">
         <v>115313</v>
@@ -24149,7 +24149,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G820" t="n">
-        <v>3.55168461799622</v>
+        <v>3.55168437957764</v>
       </c>
       <c r="H820" t="n">
         <v>1031313</v>
@@ -24178,7 +24178,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G821" t="n">
-        <v>3.5076949596405</v>
+        <v>3.50769472122192</v>
       </c>
       <c r="H821" t="n">
         <v>354331</v>
@@ -24236,7 +24236,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G823" t="n">
-        <v>3.53638362884521</v>
+        <v>3.53638386726379</v>
       </c>
       <c r="H823" t="n">
         <v>421877</v>
@@ -24323,7 +24323,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G826" t="n">
-        <v>3.58228588104248</v>
+        <v>3.58228611946106</v>
       </c>
       <c r="H826" t="n">
         <v>258986</v>
@@ -24352,7 +24352,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G827" t="n">
-        <v>3.5765483379364</v>
+        <v>3.57654809951782</v>
       </c>
       <c r="H827" t="n">
         <v>166129</v>
@@ -24381,7 +24381,7 @@
         <v>3.84400010108948</v>
       </c>
       <c r="G828" t="n">
-        <v>3.67600321769714</v>
+        <v>3.67600297927856</v>
       </c>
       <c r="H828" t="n">
         <v>474129</v>
@@ -24526,7 +24526,7 @@
         <v>4.22599983215332</v>
       </c>
       <c r="G833" t="n">
-        <v>4.04130792617798</v>
+        <v>4.04130840301514</v>
       </c>
       <c r="H833" t="n">
         <v>2312238</v>
@@ -24758,7 +24758,7 @@
         <v>4.68599987030029</v>
       </c>
       <c r="G841" t="n">
-        <v>4.48120450973511</v>
+        <v>4.48120403289795</v>
       </c>
       <c r="H841" t="n">
         <v>337090</v>
@@ -24816,7 +24816,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G843" t="n">
-        <v>4.54432010650635</v>
+        <v>4.54431962966919</v>
       </c>
       <c r="H843" t="n">
         <v>212793</v>
@@ -24903,7 +24903,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G846" t="n">
-        <v>4.35688591003418</v>
+        <v>4.35688638687134</v>
       </c>
       <c r="H846" t="n">
         <v>178453</v>
@@ -24932,7 +24932,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G847" t="n">
-        <v>4.26316928863525</v>
+        <v>4.2631688117981</v>
       </c>
       <c r="H847" t="n">
         <v>228223</v>
@@ -24990,7 +24990,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G849" t="n">
-        <v>4.17136478424072</v>
+        <v>4.17136430740356</v>
       </c>
       <c r="H849" t="n">
         <v>216742</v>
@@ -25048,7 +25048,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G851" t="n">
-        <v>3.93037796020508</v>
+        <v>3.9303777217865</v>
       </c>
       <c r="H851" t="n">
         <v>187268</v>
@@ -25135,7 +25135,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G854" t="n">
-        <v>3.77928280830383</v>
+        <v>3.77928304672241</v>
       </c>
       <c r="H854" t="n">
         <v>245578</v>
@@ -25251,7 +25251,7 @@
         <v>3.51200008392334</v>
       </c>
       <c r="G858" t="n">
-        <v>3.35851263999939</v>
+        <v>3.35851287841797</v>
       </c>
       <c r="H858" t="n">
         <v>146055</v>
@@ -25280,7 +25280,7 @@
         <v>3.56800007820129</v>
       </c>
       <c r="G859" t="n">
-        <v>3.41206526756287</v>
+        <v>3.41206550598145</v>
       </c>
       <c r="H859" t="n">
         <v>419236</v>
@@ -25396,7 +25396,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G863" t="n">
-        <v>3.47900581359863</v>
+        <v>3.47900605201721</v>
       </c>
       <c r="H863" t="n">
         <v>215914</v>
@@ -25541,7 +25541,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G868" t="n">
-        <v>3.77928280830383</v>
+        <v>3.77928304672241</v>
       </c>
       <c r="H868" t="n">
         <v>73720</v>
@@ -25657,7 +25657,7 @@
         <v>4.12400007247925</v>
       </c>
       <c r="G872" t="n">
-        <v>3.94376587867737</v>
+        <v>3.94376611709595</v>
       </c>
       <c r="H872" t="n">
         <v>191569</v>
@@ -25860,7 +25860,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G879" t="n">
-        <v>4.47546625137329</v>
+        <v>4.47546672821045</v>
       </c>
       <c r="H879" t="n">
         <v>120035</v>
@@ -25976,7 +25976,7 @@
         <v>4.38800001144409</v>
       </c>
       <c r="G883" t="n">
-        <v>4.19622850418091</v>
+        <v>4.19622802734375</v>
       </c>
       <c r="H883" t="n">
         <v>292289</v>
@@ -26063,7 +26063,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G886" t="n">
-        <v>4.20196580886841</v>
+        <v>4.20196628570557</v>
       </c>
       <c r="H886" t="n">
         <v>132141</v>
@@ -26237,7 +26237,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G892" t="n">
-        <v>4.57109689712524</v>
+        <v>4.57109642028809</v>
       </c>
       <c r="H892" t="n">
         <v>407750</v>
@@ -26295,7 +26295,7 @@
         <v>4.74599981307983</v>
       </c>
       <c r="G894" t="n">
-        <v>4.53858184814453</v>
+        <v>4.53858232498169</v>
       </c>
       <c r="H894" t="n">
         <v>111758</v>
@@ -26324,7 +26324,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G895" t="n">
-        <v>4.68585205078125</v>
+        <v>4.68585157394409</v>
       </c>
       <c r="H895" t="n">
         <v>288639</v>
@@ -36564,9 +36564,38 @@
         <v>3.25999999046326</v>
       </c>
       <c r="H1248" t="n">
-        <v>241872</v>
+        <v>248381</v>
       </c>
       <c r="I1248" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1249" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1249" t="n">
+        <v>3.35999989509583</v>
+      </c>
+      <c r="D1249" t="n">
+        <v>3.40199995040894</v>
+      </c>
+      <c r="E1249" t="n">
+        <v>3.26999998092651</v>
+      </c>
+      <c r="F1249" t="n">
+        <v>3.38599991798401</v>
+      </c>
+      <c r="G1249" t="n">
+        <v>3.38599991798401</v>
+      </c>
+      <c r="H1249" t="n">
+        <v>418741</v>
+      </c>
+      <c r="I1249" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ARIS.MI.xlsx
+++ b/data/ARIS.MI.xlsx
@@ -427,7 +427,7 @@
         <v>10.25</v>
       </c>
       <c r="G2" t="n">
-        <v>9.21045589447021</v>
+        <v>9.21045684814453</v>
       </c>
       <c r="H2" t="n">
         <v>8269720</v>
@@ -456,7 +456,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G3" t="n">
-        <v>9.34524345397949</v>
+        <v>9.34524440765381</v>
       </c>
       <c r="H3" t="n">
         <v>1460667</v>
@@ -543,7 +543,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G6" t="n">
-        <v>9.20146942138672</v>
+        <v>9.20147037506104</v>
       </c>
       <c r="H6" t="n">
         <v>260042</v>
@@ -572,7 +572,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G7" t="n">
-        <v>9.20146942138672</v>
+        <v>9.20147037506104</v>
       </c>
       <c r="H7" t="n">
         <v>279621</v>
@@ -601,7 +601,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G8" t="n">
-        <v>9.20146942138672</v>
+        <v>9.20147037506104</v>
       </c>
       <c r="H8" t="n">
         <v>197900</v>
@@ -630,7 +630,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G9" t="n">
-        <v>9.21944236755371</v>
+        <v>9.21944332122803</v>
       </c>
       <c r="H9" t="n">
         <v>203801</v>
@@ -659,7 +659,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G10" t="n">
-        <v>9.20146942138672</v>
+        <v>9.20147037506104</v>
       </c>
       <c r="H10" t="n">
         <v>122758</v>
@@ -717,7 +717,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G12" t="n">
-        <v>9.20146942138672</v>
+        <v>9.20147037506104</v>
       </c>
       <c r="H12" t="n">
         <v>105196</v>
@@ -746,7 +746,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G13" t="n">
-        <v>9.20146942138672</v>
+        <v>9.20147037506104</v>
       </c>
       <c r="H13" t="n">
         <v>85905</v>
@@ -775,7 +775,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G14" t="n">
-        <v>9.20146942138672</v>
+        <v>9.20147037506104</v>
       </c>
       <c r="H14" t="n">
         <v>198256</v>
@@ -804,7 +804,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G15" t="n">
-        <v>9.21944236755371</v>
+        <v>9.21944332122803</v>
       </c>
       <c r="H15" t="n">
         <v>184724</v>
@@ -891,7 +891,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G18" t="n">
-        <v>8.63536357879639</v>
+        <v>8.6353645324707</v>
       </c>
       <c r="H18" t="n">
         <v>319387</v>
@@ -920,7 +920,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G19" t="n">
-        <v>8.71623706817627</v>
+        <v>8.71623802185059</v>
       </c>
       <c r="H19" t="n">
         <v>172790</v>
@@ -949,7 +949,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G20" t="n">
-        <v>9.12958431243896</v>
+        <v>9.12958335876465</v>
       </c>
       <c r="H20" t="n">
         <v>431091</v>
@@ -1007,7 +1007,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G22" t="n">
-        <v>8.85102367401123</v>
+        <v>8.85102462768555</v>
       </c>
       <c r="H22" t="n">
         <v>186957</v>
@@ -1065,7 +1065,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G24" t="n">
-        <v>9.12958431243896</v>
+        <v>9.12958335876465</v>
       </c>
       <c r="H24" t="n">
         <v>61464</v>
@@ -1094,7 +1094,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G25" t="n">
-        <v>9.11161422729492</v>
+        <v>9.11161327362061</v>
       </c>
       <c r="H25" t="n">
         <v>29624</v>
@@ -1123,7 +1123,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G26" t="n">
-        <v>9.12958431243896</v>
+        <v>9.12958335876465</v>
       </c>
       <c r="H26" t="n">
         <v>53953</v>
@@ -1210,7 +1210,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G29" t="n">
-        <v>9.74062061309814</v>
+        <v>9.74061965942383</v>
       </c>
       <c r="H29" t="n">
         <v>87322</v>
@@ -1239,7 +1239,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G30" t="n">
-        <v>10.1180248260498</v>
+        <v>10.1180238723755</v>
       </c>
       <c r="H30" t="n">
         <v>401264</v>
@@ -1268,7 +1268,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G31" t="n">
-        <v>9.48901653289795</v>
+        <v>9.48901748657227</v>
       </c>
       <c r="H31" t="n">
         <v>328664</v>
@@ -1326,7 +1326,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G33" t="n">
-        <v>9.63279056549072</v>
+        <v>9.63279151916504</v>
       </c>
       <c r="H33" t="n">
         <v>261751</v>
@@ -1413,7 +1413,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G36" t="n">
-        <v>10.1988954544067</v>
+        <v>10.1988973617554</v>
       </c>
       <c r="H36" t="n">
         <v>477707</v>
@@ -1442,7 +1442,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G37" t="n">
-        <v>10.1180248260498</v>
+        <v>10.1180238723755</v>
       </c>
       <c r="H37" t="n">
         <v>92776</v>
@@ -1500,7 +1500,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G39" t="n">
-        <v>9.62380504608154</v>
+        <v>9.62380409240723</v>
       </c>
       <c r="H39" t="n">
         <v>115964</v>
@@ -1529,7 +1529,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G40" t="n">
-        <v>9.67772006988525</v>
+        <v>9.67771911621094</v>
       </c>
       <c r="H40" t="n">
         <v>103333</v>
@@ -1558,7 +1558,7 @@
         <v>10.25</v>
       </c>
       <c r="G41" t="n">
-        <v>9.21045589447021</v>
+        <v>9.21045684814453</v>
       </c>
       <c r="H41" t="n">
         <v>213846</v>
@@ -1645,7 +1645,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G44" t="n">
-        <v>9.1205997467041</v>
+        <v>9.12059879302979</v>
       </c>
       <c r="H44" t="n">
         <v>167591</v>
@@ -1703,7 +1703,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G46" t="n">
-        <v>9.20146942138672</v>
+        <v>9.20147037506104</v>
       </c>
       <c r="H46" t="n">
         <v>323983</v>
@@ -1732,7 +1732,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G47" t="n">
-        <v>9.34524345397949</v>
+        <v>9.34524440765381</v>
       </c>
       <c r="H47" t="n">
         <v>331892</v>
@@ -1790,7 +1790,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G49" t="n">
-        <v>9.34524345397949</v>
+        <v>9.34524440765381</v>
       </c>
       <c r="H49" t="n">
         <v>164923</v>
@@ -1819,7 +1819,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G50" t="n">
-        <v>9.11161422729492</v>
+        <v>9.11161327362061</v>
       </c>
       <c r="H50" t="n">
         <v>253720</v>
@@ -1848,7 +1848,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G51" t="n">
-        <v>9.16552829742432</v>
+        <v>9.16552734375</v>
       </c>
       <c r="H51" t="n">
         <v>170220</v>
@@ -1877,7 +1877,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G52" t="n">
-        <v>9.12958431243896</v>
+        <v>9.12958335876465</v>
       </c>
       <c r="H52" t="n">
         <v>73644</v>
@@ -1935,7 +1935,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G54" t="n">
-        <v>9.16552829742432</v>
+        <v>9.16552734375</v>
       </c>
       <c r="H54" t="n">
         <v>213651</v>
@@ -1964,7 +1964,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G55" t="n">
-        <v>8.99479675292969</v>
+        <v>8.994797706604</v>
       </c>
       <c r="H55" t="n">
         <v>276782</v>
@@ -1993,7 +1993,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G56" t="n">
-        <v>8.72522258758545</v>
+        <v>8.72522354125977</v>
       </c>
       <c r="H56" t="n">
         <v>305482</v>
@@ -2051,7 +2051,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G58" t="n">
-        <v>8.99479675292969</v>
+        <v>8.994797706604</v>
       </c>
       <c r="H58" t="n">
         <v>253397</v>
@@ -2138,7 +2138,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G61" t="n">
-        <v>8.71623706817627</v>
+        <v>8.71623802185059</v>
       </c>
       <c r="H61" t="n">
         <v>224870</v>
@@ -2225,7 +2225,7 @@
         <v>8.75</v>
       </c>
       <c r="G64" t="n">
-        <v>7.86258506774902</v>
+        <v>7.86258554458618</v>
       </c>
       <c r="H64" t="n">
         <v>215027</v>
@@ -2283,7 +2283,7 @@
         <v>9.20499992370605</v>
       </c>
       <c r="G66" t="n">
-        <v>8.27143859863281</v>
+        <v>8.27143955230713</v>
       </c>
       <c r="H66" t="n">
         <v>126081</v>
@@ -2370,7 +2370,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G69" t="n">
-        <v>7.95244407653809</v>
+        <v>7.95244312286377</v>
       </c>
       <c r="H69" t="n">
         <v>230882</v>
@@ -2428,7 +2428,7 @@
         <v>8</v>
       </c>
       <c r="G71" t="n">
-        <v>7.18864917755127</v>
+        <v>7.18864965438843</v>
       </c>
       <c r="H71" t="n">
         <v>192401</v>
@@ -2515,7 +2515,7 @@
         <v>8.3149995803833</v>
       </c>
       <c r="G74" t="n">
-        <v>7.47170162200928</v>
+        <v>7.47170209884644</v>
       </c>
       <c r="H74" t="n">
         <v>89965</v>
@@ -2602,7 +2602,7 @@
         <v>9.51500034332275</v>
       </c>
       <c r="G77" t="n">
-        <v>8.55000114440918</v>
+        <v>8.55000019073486</v>
       </c>
       <c r="H77" t="n">
         <v>369586</v>
@@ -2718,7 +2718,7 @@
         <v>9.71500015258789</v>
       </c>
       <c r="G81" t="n">
-        <v>8.72971630096436</v>
+        <v>8.72971725463867</v>
       </c>
       <c r="H81" t="n">
         <v>221597</v>
@@ -2834,7 +2834,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G85" t="n">
-        <v>8.64435005187988</v>
+        <v>8.6443510055542</v>
       </c>
       <c r="H85" t="n">
         <v>93670</v>
@@ -2892,7 +2892,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G87" t="n">
-        <v>8.67130851745605</v>
+        <v>8.67130756378174</v>
       </c>
       <c r="H87" t="n">
         <v>120344</v>
@@ -2921,7 +2921,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G88" t="n">
-        <v>8.80609512329102</v>
+        <v>8.80609607696533</v>
       </c>
       <c r="H88" t="n">
         <v>104006</v>
@@ -2950,7 +2950,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G89" t="n">
-        <v>8.50057792663574</v>
+        <v>8.50057697296143</v>
       </c>
       <c r="H89" t="n">
         <v>95717</v>
@@ -3037,7 +3037,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G92" t="n">
-        <v>8.71623706817627</v>
+        <v>8.71623802185059</v>
       </c>
       <c r="H92" t="n">
         <v>223170</v>
@@ -3066,7 +3066,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G93" t="n">
-        <v>8.50057792663574</v>
+        <v>8.50057697296143</v>
       </c>
       <c r="H93" t="n">
         <v>181323</v>
@@ -3095,7 +3095,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G94" t="n">
-        <v>8.18607425689697</v>
+        <v>8.18607521057129</v>
       </c>
       <c r="H94" t="n">
         <v>173589</v>
@@ -3153,7 +3153,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G96" t="n">
-        <v>8.24897480010986</v>
+        <v>8.24897575378418</v>
       </c>
       <c r="H96" t="n">
         <v>89220</v>
@@ -3240,7 +3240,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G99" t="n">
-        <v>8.45564842224121</v>
+        <v>8.45564746856689</v>
       </c>
       <c r="H99" t="n">
         <v>126252</v>
@@ -3269,7 +3269,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G100" t="n">
-        <v>8.80609512329102</v>
+        <v>8.80609607696533</v>
       </c>
       <c r="H100" t="n">
         <v>249000</v>
@@ -3298,7 +3298,7 @@
         <v>9.75</v>
       </c>
       <c r="G101" t="n">
-        <v>8.76116752624512</v>
+        <v>8.7611665725708</v>
       </c>
       <c r="H101" t="n">
         <v>134667</v>
@@ -3327,7 +3327,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G102" t="n">
-        <v>8.59043598175049</v>
+        <v>8.5904369354248</v>
       </c>
       <c r="H102" t="n">
         <v>81506</v>
@@ -3356,7 +3356,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G103" t="n">
-        <v>8.71623706817627</v>
+        <v>8.71623802185059</v>
       </c>
       <c r="H103" t="n">
         <v>216807</v>
@@ -3443,7 +3443,7 @@
         <v>9.71500015258789</v>
       </c>
       <c r="G106" t="n">
-        <v>8.72971630096436</v>
+        <v>8.72971725463867</v>
       </c>
       <c r="H106" t="n">
         <v>81637</v>
@@ -3472,7 +3472,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G107" t="n">
-        <v>8.67130851745605</v>
+        <v>8.67130756378174</v>
       </c>
       <c r="H107" t="n">
         <v>107921</v>
@@ -3559,7 +3559,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G110" t="n">
-        <v>7.89852952957153</v>
+        <v>7.89852809906006</v>
       </c>
       <c r="H110" t="n">
         <v>136469</v>
@@ -3617,7 +3617,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G112" t="n">
-        <v>8.10520362854004</v>
+        <v>8.10520172119141</v>
       </c>
       <c r="H112" t="n">
         <v>245680</v>
@@ -3646,7 +3646,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G113" t="n">
-        <v>7.99737215042114</v>
+        <v>7.99737119674683</v>
       </c>
       <c r="H113" t="n">
         <v>164165</v>
@@ -3704,7 +3704,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G115" t="n">
-        <v>7.80867004394531</v>
+        <v>7.80867052078247</v>
       </c>
       <c r="H115" t="n">
         <v>87012</v>
@@ -3733,7 +3733,7 @@
         <v>9.02499961853027</v>
       </c>
       <c r="G116" t="n">
-        <v>8.10969543457031</v>
+        <v>8.109694480896</v>
       </c>
       <c r="H116" t="n">
         <v>88735</v>
@@ -3849,7 +3849,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>8.80609512329102</v>
+        <v>8.80609607696533</v>
       </c>
       <c r="H120" t="n">
         <v>269484</v>
@@ -4023,7 +4023,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G126" t="n">
-        <v>8.9314489364624</v>
+        <v>8.93144989013672</v>
       </c>
       <c r="H126" t="n">
         <v>138520</v>
@@ -4052,7 +4052,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G127" t="n">
-        <v>9.2504301071167</v>
+        <v>9.25042915344238</v>
       </c>
       <c r="H127" t="n">
         <v>154830</v>
@@ -4168,7 +4168,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G131" t="n">
-        <v>9.20486068725586</v>
+        <v>9.20486164093018</v>
       </c>
       <c r="H131" t="n">
         <v>105012</v>
@@ -4197,7 +4197,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G132" t="n">
-        <v>9.24131679534912</v>
+        <v>9.2413158416748</v>
       </c>
       <c r="H132" t="n">
         <v>39938</v>
@@ -4255,7 +4255,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G134" t="n">
-        <v>9.24131679534912</v>
+        <v>9.2413158416748</v>
       </c>
       <c r="H134" t="n">
         <v>32325</v>
@@ -4313,7 +4313,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G136" t="n">
-        <v>9.29599857330322</v>
+        <v>9.29599761962891</v>
       </c>
       <c r="H136" t="n">
         <v>59750</v>
@@ -4342,7 +4342,7 @@
         <v>9.84500026702881</v>
       </c>
       <c r="G137" t="n">
-        <v>8.97246170043945</v>
+        <v>8.97246074676514</v>
       </c>
       <c r="H137" t="n">
         <v>84612</v>
@@ -4429,7 +4429,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G140" t="n">
-        <v>7.95628118515015</v>
+        <v>7.95628023147583</v>
       </c>
       <c r="H140" t="n">
         <v>163728</v>
@@ -4487,7 +4487,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G142" t="n">
-        <v>7.61907291412354</v>
+        <v>7.61907196044922</v>
       </c>
       <c r="H142" t="n">
         <v>67512</v>
@@ -4516,7 +4516,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G143" t="n">
-        <v>7.73755168914795</v>
+        <v>7.73755121231079</v>
       </c>
       <c r="H143" t="n">
         <v>68881</v>
@@ -4545,7 +4545,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G144" t="n">
-        <v>7.6464147567749</v>
+        <v>7.64641427993774</v>
       </c>
       <c r="H144" t="n">
         <v>79110</v>
@@ -4603,7 +4603,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G146" t="n">
-        <v>7.34566211700439</v>
+        <v>7.34566164016724</v>
       </c>
       <c r="H146" t="n">
         <v>105071</v>
@@ -4632,7 +4632,7 @@
         <v>7.50500011444092</v>
       </c>
       <c r="G147" t="n">
-        <v>6.83984994888306</v>
+        <v>6.8398494720459</v>
       </c>
       <c r="H147" t="n">
         <v>173369</v>
@@ -4661,7 +4661,7 @@
         <v>7.375</v>
       </c>
       <c r="G148" t="n">
-        <v>6.7213716506958</v>
+        <v>6.72137117385864</v>
       </c>
       <c r="H148" t="n">
         <v>158803</v>
@@ -4748,7 +4748,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G151" t="n">
-        <v>7.0266809463501</v>
+        <v>7.02668142318726</v>
       </c>
       <c r="H151" t="n">
         <v>83909</v>
@@ -4777,7 +4777,7 @@
         <v>7.81500005722046</v>
       </c>
       <c r="G152" t="n">
-        <v>7.12237548828125</v>
+        <v>7.12237453460693</v>
       </c>
       <c r="H152" t="n">
         <v>173417</v>
@@ -4864,7 +4864,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G155" t="n">
-        <v>6.7441554069519</v>
+        <v>6.74415588378906</v>
       </c>
       <c r="H155" t="n">
         <v>105692</v>
@@ -4893,7 +4893,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G156" t="n">
-        <v>6.68035936355591</v>
+        <v>6.68035888671875</v>
       </c>
       <c r="H156" t="n">
         <v>131028</v>
@@ -4922,7 +4922,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G157" t="n">
-        <v>6.78061056137085</v>
+        <v>6.78061008453369</v>
       </c>
       <c r="H157" t="n">
         <v>109900</v>
@@ -4951,7 +4951,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G158" t="n">
-        <v>6.92642974853516</v>
+        <v>6.926429271698</v>
       </c>
       <c r="H158" t="n">
         <v>58691</v>
@@ -5009,7 +5009,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G160" t="n">
-        <v>6.68035936355591</v>
+        <v>6.68035888671875</v>
       </c>
       <c r="H160" t="n">
         <v>64175</v>
@@ -5067,7 +5067,7 @@
         <v>7.05499982833862</v>
       </c>
       <c r="G162" t="n">
-        <v>6.42973184585571</v>
+        <v>6.42973136901855</v>
       </c>
       <c r="H162" t="n">
         <v>80746</v>
@@ -5096,7 +5096,7 @@
         <v>7.31500005722046</v>
       </c>
       <c r="G163" t="n">
-        <v>6.66668891906738</v>
+        <v>6.66668844223022</v>
       </c>
       <c r="H163" t="n">
         <v>63073</v>
@@ -5125,7 +5125,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G164" t="n">
-        <v>6.88086128234863</v>
+        <v>6.88086175918579</v>
       </c>
       <c r="H164" t="n">
         <v>59880</v>
@@ -5154,7 +5154,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G165" t="n">
-        <v>6.9947829246521</v>
+        <v>6.99478340148926</v>
       </c>
       <c r="H165" t="n">
         <v>39622</v>
@@ -5241,7 +5241,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G168" t="n">
-        <v>6.9947829246521</v>
+        <v>6.99478340148926</v>
       </c>
       <c r="H168" t="n">
         <v>116551</v>
@@ -5270,7 +5270,7 @@
         <v>7.72499990463257</v>
       </c>
       <c r="G169" t="n">
-        <v>7.04035139083862</v>
+        <v>7.04035186767578</v>
       </c>
       <c r="H169" t="n">
         <v>97576</v>
@@ -5299,7 +5299,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G170" t="n">
-        <v>6.7441554069519</v>
+        <v>6.74415588378906</v>
       </c>
       <c r="H170" t="n">
         <v>54127</v>
@@ -5328,7 +5328,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G171" t="n">
-        <v>6.9947829246521</v>
+        <v>6.99478340148926</v>
       </c>
       <c r="H171" t="n">
         <v>62027</v>
@@ -5357,7 +5357,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G172" t="n">
-        <v>7.26819467544556</v>
+        <v>7.2681941986084</v>
       </c>
       <c r="H172" t="n">
         <v>107198</v>
@@ -5444,7 +5444,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G175" t="n">
-        <v>7.61907291412354</v>
+        <v>7.61907196044922</v>
       </c>
       <c r="H175" t="n">
         <v>67391</v>
@@ -5502,7 +5502,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G177" t="n">
-        <v>7.46413898468018</v>
+        <v>7.46413946151733</v>
       </c>
       <c r="H177" t="n">
         <v>103642</v>
@@ -5560,7 +5560,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G179" t="n">
-        <v>7.33199071884155</v>
+        <v>7.33199024200439</v>
       </c>
       <c r="H179" t="n">
         <v>88870</v>
@@ -5589,7 +5589,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G180" t="n">
-        <v>7.24996662139893</v>
+        <v>7.24996709823608</v>
       </c>
       <c r="H180" t="n">
         <v>63885</v>
@@ -5618,7 +5618,7 @@
         <v>8</v>
       </c>
       <c r="G181" t="n">
-        <v>7.29097890853882</v>
+        <v>7.29097938537598</v>
       </c>
       <c r="H181" t="n">
         <v>44729</v>
@@ -5647,7 +5647,7 @@
         <v>8</v>
       </c>
       <c r="G182" t="n">
-        <v>7.29097890853882</v>
+        <v>7.29097938537598</v>
       </c>
       <c r="H182" t="n">
         <v>68137</v>
@@ -5705,7 +5705,7 @@
         <v>8</v>
       </c>
       <c r="G184" t="n">
-        <v>7.29097890853882</v>
+        <v>7.29097938537598</v>
       </c>
       <c r="H184" t="n">
         <v>53674</v>
@@ -5734,7 +5734,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G185" t="n">
-        <v>7.05402183532715</v>
+        <v>7.05402231216431</v>
       </c>
       <c r="H185" t="n">
         <v>89502</v>
@@ -5763,7 +5763,7 @@
         <v>8</v>
       </c>
       <c r="G186" t="n">
-        <v>7.29097890853882</v>
+        <v>7.29097938537598</v>
       </c>
       <c r="H186" t="n">
         <v>98582</v>
@@ -5850,7 +5850,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G189" t="n">
-        <v>7.21351194381714</v>
+        <v>7.2135124206543</v>
       </c>
       <c r="H189" t="n">
         <v>58048</v>
@@ -5879,7 +5879,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G190" t="n">
-        <v>7.1178183555603</v>
+        <v>7.11781787872314</v>
       </c>
       <c r="H190" t="n">
         <v>29579</v>
@@ -6024,7 +6024,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G195" t="n">
-        <v>7.00845384597778</v>
+        <v>7.00845336914062</v>
       </c>
       <c r="H195" t="n">
         <v>142516</v>
@@ -6082,7 +6082,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G197" t="n">
-        <v>6.92642974853516</v>
+        <v>6.926429271698</v>
       </c>
       <c r="H197" t="n">
         <v>94339</v>
@@ -6140,7 +6140,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G199" t="n">
-        <v>6.42517518997192</v>
+        <v>6.42517566680908</v>
       </c>
       <c r="H199" t="n">
         <v>115768</v>
@@ -6256,7 +6256,7 @@
         <v>7.75</v>
       </c>
       <c r="G203" t="n">
-        <v>7.06313562393188</v>
+        <v>7.06313610076904</v>
       </c>
       <c r="H203" t="n">
         <v>74023</v>
@@ -6285,7 +6285,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G204" t="n">
-        <v>6.83073616027832</v>
+        <v>6.83073568344116</v>
       </c>
       <c r="H204" t="n">
         <v>55532</v>
@@ -6314,7 +6314,7 @@
         <v>7.33500003814697</v>
       </c>
       <c r="G205" t="n">
-        <v>6.68491649627686</v>
+        <v>6.6849160194397</v>
       </c>
       <c r="H205" t="n">
         <v>69663</v>
@@ -6343,7 +6343,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G206" t="n">
-        <v>6.69858646392822</v>
+        <v>6.69858694076538</v>
       </c>
       <c r="H206" t="n">
         <v>115365</v>
@@ -6372,7 +6372,7 @@
         <v>8.46500015258789</v>
       </c>
       <c r="G207" t="n">
-        <v>7.71476697921753</v>
+        <v>7.71476745605469</v>
       </c>
       <c r="H207" t="n">
         <v>667919</v>
@@ -6459,7 +6459,7 @@
         <v>8.40499973297119</v>
       </c>
       <c r="G210" t="n">
-        <v>7.66008520126343</v>
+        <v>7.66008424758911</v>
       </c>
       <c r="H210" t="n">
         <v>162822</v>
@@ -6517,7 +6517,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G212" t="n">
-        <v>7.75577831268311</v>
+        <v>7.75577926635742</v>
       </c>
       <c r="H212" t="n">
         <v>149734</v>
@@ -6604,7 +6604,7 @@
         <v>8.48499965667725</v>
       </c>
       <c r="G215" t="n">
-        <v>7.73299407958984</v>
+        <v>7.73299360275269</v>
       </c>
       <c r="H215" t="n">
         <v>190999</v>
@@ -6691,7 +6691,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G218" t="n">
-        <v>8.02007675170898</v>
+        <v>8.0200777053833</v>
       </c>
       <c r="H218" t="n">
         <v>179237</v>
@@ -6720,7 +6720,7 @@
         <v>9.13500022888184</v>
       </c>
       <c r="G219" t="n">
-        <v>8.3253870010376</v>
+        <v>8.32538604736328</v>
       </c>
       <c r="H219" t="n">
         <v>283069</v>
@@ -6749,7 +6749,7 @@
         <v>9.03499984741211</v>
       </c>
       <c r="G220" t="n">
-        <v>8.23425006866455</v>
+        <v>8.23424911499023</v>
       </c>
       <c r="H220" t="n">
         <v>263459</v>
@@ -6778,7 +6778,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G221" t="n">
-        <v>8.1932373046875</v>
+        <v>8.19323825836182</v>
       </c>
       <c r="H221" t="n">
         <v>194602</v>
@@ -6807,7 +6807,7 @@
         <v>8.84500026702881</v>
       </c>
       <c r="G222" t="n">
-        <v>8.06108951568604</v>
+        <v>8.06108856201172</v>
       </c>
       <c r="H222" t="n">
         <v>71498</v>
@@ -6836,7 +6836,7 @@
         <v>8.86499977111816</v>
       </c>
       <c r="G223" t="n">
-        <v>8.07931518554688</v>
+        <v>8.07931613922119</v>
       </c>
       <c r="H223" t="n">
         <v>111621</v>
@@ -6865,7 +6865,7 @@
         <v>8.79500007629395</v>
       </c>
       <c r="G224" t="n">
-        <v>8.0155200958252</v>
+        <v>8.01552104949951</v>
       </c>
       <c r="H224" t="n">
         <v>122024</v>
@@ -7039,7 +7039,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G230" t="n">
-        <v>7.59173202514648</v>
+        <v>7.59173154830933</v>
       </c>
       <c r="H230" t="n">
         <v>175936</v>
@@ -7126,7 +7126,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G233" t="n">
-        <v>7.60084581375122</v>
+        <v>7.60084629058838</v>
       </c>
       <c r="H233" t="n">
         <v>108751</v>
@@ -7155,7 +7155,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G234" t="n">
-        <v>7.85602998733521</v>
+        <v>7.85602903366089</v>
       </c>
       <c r="H234" t="n">
         <v>185968</v>
@@ -7184,7 +7184,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G235" t="n">
-        <v>7.81957483291626</v>
+        <v>7.8195743560791</v>
       </c>
       <c r="H235" t="n">
         <v>126055</v>
@@ -7213,7 +7213,7 @@
         <v>8.59500026702881</v>
       </c>
       <c r="G236" t="n">
-        <v>7.83324480056763</v>
+        <v>7.83324670791626</v>
       </c>
       <c r="H236" t="n">
         <v>75722</v>
@@ -7271,7 +7271,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G238" t="n">
-        <v>7.86514329910278</v>
+        <v>7.86514377593994</v>
       </c>
       <c r="H238" t="n">
         <v>98511</v>
@@ -7329,7 +7329,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G240" t="n">
-        <v>7.61907291412354</v>
+        <v>7.61907196044922</v>
       </c>
       <c r="H240" t="n">
         <v>242480</v>
@@ -7416,7 +7416,7 @@
         <v>8.29500007629395</v>
       </c>
       <c r="G243" t="n">
-        <v>7.55983352661133</v>
+        <v>7.55983304977417</v>
       </c>
       <c r="H243" t="n">
         <v>179111</v>
@@ -7474,7 +7474,7 @@
         <v>8.15499973297119</v>
       </c>
       <c r="G245" t="n">
-        <v>7.43224143981934</v>
+        <v>7.43224096298218</v>
       </c>
       <c r="H245" t="n">
         <v>95884</v>
@@ -7532,7 +7532,7 @@
         <v>8.5649995803833</v>
       </c>
       <c r="G247" t="n">
-        <v>7.80590295791626</v>
+        <v>7.80590343475342</v>
       </c>
       <c r="H247" t="n">
         <v>190341</v>
@@ -7561,7 +7561,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G248" t="n">
-        <v>7.73755168914795</v>
+        <v>7.73755121231079</v>
       </c>
       <c r="H248" t="n">
         <v>79342</v>
@@ -7619,7 +7619,7 @@
         <v>8.44499969482422</v>
       </c>
       <c r="G250" t="n">
-        <v>7.6965389251709</v>
+        <v>7.69653940200806</v>
       </c>
       <c r="H250" t="n">
         <v>65821</v>
@@ -7648,7 +7648,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G251" t="n">
-        <v>7.76489353179932</v>
+        <v>7.76489305496216</v>
       </c>
       <c r="H251" t="n">
         <v>81589</v>
@@ -7677,7 +7677,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G252" t="n">
-        <v>7.87425756454468</v>
+        <v>7.87425851821899</v>
       </c>
       <c r="H252" t="n">
         <v>52613</v>
@@ -7735,7 +7735,7 @@
         <v>8.64500045776367</v>
       </c>
       <c r="G254" t="n">
-        <v>7.87881517410278</v>
+        <v>7.87881374359131</v>
       </c>
       <c r="H254" t="n">
         <v>56212</v>
@@ -7851,7 +7851,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G258" t="n">
-        <v>8.34817123413086</v>
+        <v>8.34817028045654</v>
       </c>
       <c r="H258" t="n">
         <v>65591</v>
@@ -7880,7 +7880,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G259" t="n">
-        <v>8.43930912017822</v>
+        <v>8.43930816650391</v>
       </c>
       <c r="H259" t="n">
         <v>57907</v>
@@ -8054,7 +8054,7 @@
         <v>9.23499965667725</v>
       </c>
       <c r="G265" t="n">
-        <v>8.41652297973633</v>
+        <v>8.41652393341064</v>
       </c>
       <c r="H265" t="n">
         <v>63237</v>
@@ -8141,7 +8141,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G268" t="n">
-        <v>8.42107963562012</v>
+        <v>8.42108058929443</v>
       </c>
       <c r="H268" t="n">
         <v>38362</v>
@@ -8228,7 +8228,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G271" t="n">
-        <v>8.47576236724854</v>
+        <v>8.47576332092285</v>
       </c>
       <c r="H271" t="n">
         <v>166452</v>
@@ -8257,7 +8257,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G272" t="n">
-        <v>8.46665000915527</v>
+        <v>8.46664905548096</v>
       </c>
       <c r="H272" t="n">
         <v>131322</v>
@@ -8344,7 +8344,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G275" t="n">
-        <v>8.46665000915527</v>
+        <v>8.46664905548096</v>
       </c>
       <c r="H275" t="n">
         <v>56044</v>
@@ -8431,7 +8431,7 @@
         <v>9.66499996185303</v>
       </c>
       <c r="G278" t="n">
-        <v>8.80841445922852</v>
+        <v>8.8084135055542</v>
       </c>
       <c r="H278" t="n">
         <v>41058</v>
@@ -8489,7 +8489,7 @@
         <v>9.40499973297119</v>
       </c>
       <c r="G280" t="n">
-        <v>8.571457862854</v>
+        <v>8.57145595550537</v>
       </c>
       <c r="H280" t="n">
         <v>67802</v>
@@ -8518,7 +8518,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G281" t="n">
-        <v>8.76740169525146</v>
+        <v>8.76740264892578</v>
       </c>
       <c r="H281" t="n">
         <v>53938</v>
@@ -8547,7 +8547,7 @@
         <v>9.625</v>
       </c>
       <c r="G282" t="n">
-        <v>8.77195835113525</v>
+        <v>8.77195930480957</v>
       </c>
       <c r="H282" t="n">
         <v>30701</v>
@@ -8634,7 +8634,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G285" t="n">
-        <v>9.29599857330322</v>
+        <v>9.29599761962891</v>
       </c>
       <c r="H285" t="n">
         <v>110062</v>
@@ -8808,7 +8808,7 @@
         <v>9.4350004196167</v>
       </c>
       <c r="G291" t="n">
-        <v>8.59879970550537</v>
+        <v>8.59879875183105</v>
       </c>
       <c r="H291" t="n">
         <v>100006</v>
@@ -8924,7 +8924,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G295" t="n">
-        <v>8.60335350036621</v>
+        <v>8.60335445404053</v>
       </c>
       <c r="H295" t="n">
         <v>150159</v>
@@ -8982,7 +8982,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G297" t="n">
-        <v>8.82208347320557</v>
+        <v>8.82208442687988</v>
       </c>
       <c r="H297" t="n">
         <v>184820</v>
@@ -9040,7 +9040,7 @@
         <v>9.875</v>
       </c>
       <c r="G299" t="n">
-        <v>8.9998025894165</v>
+        <v>8.99980163574219</v>
       </c>
       <c r="H299" t="n">
         <v>71056</v>
@@ -9098,7 +9098,7 @@
         <v>9.625</v>
       </c>
       <c r="G301" t="n">
-        <v>8.77195835113525</v>
+        <v>8.77195930480957</v>
       </c>
       <c r="H301" t="n">
         <v>62785</v>
@@ -9156,7 +9156,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G303" t="n">
-        <v>8.67626571655273</v>
+        <v>8.67626476287842</v>
       </c>
       <c r="H303" t="n">
         <v>101596</v>
@@ -9214,7 +9214,7 @@
         <v>9.51500034332275</v>
       </c>
       <c r="G305" t="n">
-        <v>8.67170906066895</v>
+        <v>8.67170810699463</v>
       </c>
       <c r="H305" t="n">
         <v>74235</v>
@@ -9272,7 +9272,7 @@
         <v>9.66499996185303</v>
       </c>
       <c r="G307" t="n">
-        <v>8.80841445922852</v>
+        <v>8.8084135055542</v>
       </c>
       <c r="H307" t="n">
         <v>88814</v>
@@ -9359,7 +9359,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G310" t="n">
-        <v>8.71271991729736</v>
+        <v>8.71272087097168</v>
       </c>
       <c r="H310" t="n">
         <v>71168</v>
@@ -9417,7 +9417,7 @@
         <v>9.84500026702881</v>
       </c>
       <c r="G312" t="n">
-        <v>8.97246170043945</v>
+        <v>8.97246074676514</v>
       </c>
       <c r="H312" t="n">
         <v>201439</v>
@@ -9446,7 +9446,7 @@
         <v>9.86499977111816</v>
       </c>
       <c r="G313" t="n">
-        <v>8.99068737030029</v>
+        <v>8.99068832397461</v>
       </c>
       <c r="H313" t="n">
         <v>95525</v>
@@ -9475,7 +9475,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G314" t="n">
-        <v>8.9314489364624</v>
+        <v>8.93144989013672</v>
       </c>
       <c r="H314" t="n">
         <v>79734</v>
@@ -9504,7 +9504,7 @@
         <v>9.5649995803833</v>
       </c>
       <c r="G315" t="n">
-        <v>8.71727561950684</v>
+        <v>8.71727657318115</v>
       </c>
       <c r="H315" t="n">
         <v>125012</v>
@@ -9620,7 +9620,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G319" t="n">
-        <v>8.10210037231445</v>
+        <v>8.10210132598877</v>
       </c>
       <c r="H319" t="n">
         <v>152972</v>
@@ -9678,7 +9678,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G321" t="n">
-        <v>8.26158905029297</v>
+        <v>8.26159000396729</v>
       </c>
       <c r="H321" t="n">
         <v>151215</v>
@@ -9707,7 +9707,7 @@
         <v>9.23499965667725</v>
       </c>
       <c r="G322" t="n">
-        <v>8.41652297973633</v>
+        <v>8.41652393341064</v>
       </c>
       <c r="H322" t="n">
         <v>57007</v>
@@ -9736,7 +9736,7 @@
         <v>9.125</v>
       </c>
       <c r="G323" t="n">
-        <v>8.31627178192139</v>
+        <v>8.31627368927002</v>
       </c>
       <c r="H323" t="n">
         <v>96023</v>
@@ -9765,7 +9765,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G324" t="n">
-        <v>8.23880577087402</v>
+        <v>8.23880481719971</v>
       </c>
       <c r="H324" t="n">
         <v>125245</v>
@@ -9794,7 +9794,7 @@
         <v>9.6850004196167</v>
       </c>
       <c r="G325" t="n">
-        <v>8.82664108276367</v>
+        <v>8.82664203643799</v>
       </c>
       <c r="H325" t="n">
         <v>499802</v>
@@ -9852,7 +9852,7 @@
         <v>9.64500045776367</v>
       </c>
       <c r="G327" t="n">
-        <v>8.79018688201904</v>
+        <v>8.79018592834473</v>
       </c>
       <c r="H327" t="n">
         <v>201564</v>
@@ -9939,7 +9939,7 @@
         <v>9.84500026702881</v>
       </c>
       <c r="G330" t="n">
-        <v>8.97246170043945</v>
+        <v>8.97246074676514</v>
       </c>
       <c r="H330" t="n">
         <v>120285</v>
@@ -9968,7 +9968,7 @@
         <v>9.58500003814697</v>
       </c>
       <c r="G331" t="n">
-        <v>8.73550510406494</v>
+        <v>8.73550415039062</v>
       </c>
       <c r="H331" t="n">
         <v>128694</v>
@@ -9997,7 +9997,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G332" t="n">
-        <v>8.49399089813232</v>
+        <v>8.49398994445801</v>
       </c>
       <c r="H332" t="n">
         <v>110225</v>
@@ -10026,7 +10026,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G333" t="n">
-        <v>8.60335350036621</v>
+        <v>8.60335445404053</v>
       </c>
       <c r="H333" t="n">
         <v>90522</v>
@@ -10084,7 +10084,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G335" t="n">
-        <v>8.48487663269043</v>
+        <v>8.48487758636475</v>
       </c>
       <c r="H335" t="n">
         <v>124173</v>
@@ -10113,7 +10113,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G336" t="n">
-        <v>8.60335350036621</v>
+        <v>8.60335445404053</v>
       </c>
       <c r="H336" t="n">
         <v>169827</v>
@@ -10200,7 +10200,7 @@
         <v>9.36499977111816</v>
       </c>
       <c r="G339" t="n">
-        <v>8.53500080108643</v>
+        <v>8.53500175476074</v>
       </c>
       <c r="H339" t="n">
         <v>78975</v>
@@ -10229,7 +10229,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G340" t="n">
-        <v>8.64892387390137</v>
+        <v>8.64892292022705</v>
       </c>
       <c r="H340" t="n">
         <v>60887</v>
@@ -10258,7 +10258,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G341" t="n">
-        <v>8.42107963562012</v>
+        <v>8.42108058929443</v>
       </c>
       <c r="H341" t="n">
         <v>61904</v>
@@ -10287,7 +10287,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G342" t="n">
-        <v>8.43930912017822</v>
+        <v>8.43930816650391</v>
       </c>
       <c r="H342" t="n">
         <v>40942</v>
@@ -10316,7 +10316,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G343" t="n">
-        <v>8.53955841064453</v>
+        <v>8.53955936431885</v>
       </c>
       <c r="H343" t="n">
         <v>356528</v>
@@ -10403,7 +10403,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G346" t="n">
-        <v>9.2504301071167</v>
+        <v>9.25042915344238</v>
       </c>
       <c r="H346" t="n">
         <v>231979</v>
@@ -10461,7 +10461,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G348" t="n">
-        <v>9.1319522857666</v>
+        <v>9.13195133209229</v>
       </c>
       <c r="H348" t="n">
         <v>160856</v>
@@ -10490,7 +10490,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G349" t="n">
-        <v>9.18663311004639</v>
+        <v>9.1866340637207</v>
       </c>
       <c r="H349" t="n">
         <v>120697</v>
@@ -10635,7 +10635,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G354" t="n">
-        <v>9.02258682250977</v>
+        <v>9.02258586883545</v>
       </c>
       <c r="H354" t="n">
         <v>58371</v>
@@ -10664,7 +10664,7 @@
         <v>9.88500022888184</v>
       </c>
       <c r="G355" t="n">
-        <v>9.00891590118408</v>
+        <v>9.00891494750977</v>
       </c>
       <c r="H355" t="n">
         <v>123367</v>
@@ -10693,7 +10693,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G356" t="n">
-        <v>9.02258682250977</v>
+        <v>9.02258586883545</v>
       </c>
       <c r="H356" t="n">
         <v>51175</v>
@@ -10722,7 +10722,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G357" t="n">
-        <v>9.16840648651123</v>
+        <v>9.16840744018555</v>
       </c>
       <c r="H357" t="n">
         <v>43978</v>
@@ -10751,7 +10751,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G358" t="n">
-        <v>9.46916007995605</v>
+        <v>9.46915912628174</v>
       </c>
       <c r="H358" t="n">
         <v>119140</v>
@@ -10780,7 +10780,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G359" t="n">
-        <v>9.6696605682373</v>
+        <v>9.66966152191162</v>
       </c>
       <c r="H359" t="n">
         <v>147204</v>
@@ -10896,7 +10896,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G363" t="n">
-        <v>9.70611572265625</v>
+        <v>9.70611476898193</v>
       </c>
       <c r="H363" t="n">
         <v>79881</v>
@@ -10954,7 +10954,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G365" t="n">
-        <v>9.33245182037354</v>
+        <v>9.33245277404785</v>
       </c>
       <c r="H365" t="n">
         <v>135405</v>
@@ -10983,7 +10983,7 @@
         <v>9.83500003814697</v>
       </c>
       <c r="G366" t="n">
-        <v>8.96334838867188</v>
+        <v>8.96334743499756</v>
       </c>
       <c r="H366" t="n">
         <v>250182</v>
@@ -11041,7 +11041,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G368" t="n">
-        <v>8.97701740264893</v>
+        <v>8.97701835632324</v>
       </c>
       <c r="H368" t="n">
         <v>58875</v>
@@ -11070,7 +11070,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G369" t="n">
-        <v>8.66715145111084</v>
+        <v>8.66715240478516</v>
       </c>
       <c r="H369" t="n">
         <v>180228</v>
@@ -11099,7 +11099,7 @@
         <v>9.40499973297119</v>
       </c>
       <c r="G370" t="n">
-        <v>8.571457862854</v>
+        <v>8.57145595550537</v>
       </c>
       <c r="H370" t="n">
         <v>122944</v>
@@ -11186,7 +11186,7 @@
         <v>9.65499973297119</v>
       </c>
       <c r="G373" t="n">
-        <v>8.79930019378662</v>
+        <v>8.7992992401123</v>
       </c>
       <c r="H373" t="n">
         <v>110462</v>
@@ -11389,7 +11389,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>9.41868686676025</v>
+        <v>9.41868591308594</v>
       </c>
       <c r="H380" t="n">
         <v>108271</v>
@@ -11505,7 +11505,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G384" t="n">
-        <v>9.41868686676025</v>
+        <v>9.41868591308594</v>
       </c>
       <c r="H384" t="n">
         <v>58349</v>
@@ -11563,7 +11563,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G386" t="n">
-        <v>9.43715572357178</v>
+        <v>9.43715476989746</v>
       </c>
       <c r="H386" t="n">
         <v>588687</v>
@@ -11824,7 +11824,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G395" t="n">
-        <v>9.66800498962402</v>
+        <v>9.66800403594971</v>
       </c>
       <c r="H395" t="n">
         <v>79788</v>
@@ -11911,7 +11911,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G398" t="n">
-        <v>9.4279203414917</v>
+        <v>9.42792129516602</v>
       </c>
       <c r="H398" t="n">
         <v>119704</v>
@@ -11940,7 +11940,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G399" t="n">
-        <v>9.34481430053711</v>
+        <v>9.34481334686279</v>
       </c>
       <c r="H399" t="n">
         <v>45265</v>
@@ -11998,7 +11998,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G401" t="n">
-        <v>9.04932594299316</v>
+        <v>9.04932689666748</v>
       </c>
       <c r="H401" t="n">
         <v>96905</v>
@@ -12056,7 +12056,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G403" t="n">
-        <v>8.79539108276367</v>
+        <v>8.79539012908936</v>
       </c>
       <c r="H403" t="n">
         <v>80618</v>
@@ -12085,7 +12085,7 @@
         <v>9.36499977111816</v>
       </c>
       <c r="G404" t="n">
-        <v>8.64764595031738</v>
+        <v>8.6476469039917</v>
       </c>
       <c r="H404" t="n">
         <v>93583</v>
@@ -12114,7 +12114,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G405" t="n">
-        <v>8.58762550354004</v>
+        <v>8.58762645721436</v>
       </c>
       <c r="H405" t="n">
         <v>464509</v>
@@ -12143,7 +12143,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G406" t="n">
-        <v>8.80000782012939</v>
+        <v>8.80000877380371</v>
       </c>
       <c r="H406" t="n">
         <v>218689</v>
@@ -12172,7 +12172,7 @@
         <v>9.55500030517578</v>
       </c>
       <c r="G407" t="n">
-        <v>8.82309341430664</v>
+        <v>8.82309246063232</v>
       </c>
       <c r="H407" t="n">
         <v>224972</v>
@@ -12201,7 +12201,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G408" t="n">
-        <v>8.93851757049561</v>
+        <v>8.93851852416992</v>
       </c>
       <c r="H408" t="n">
         <v>244272</v>
@@ -12230,7 +12230,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G409" t="n">
-        <v>8.71690082550049</v>
+        <v>8.7169017791748</v>
       </c>
       <c r="H409" t="n">
         <v>213955</v>
@@ -12288,7 +12288,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G411" t="n">
-        <v>8.82771015167236</v>
+        <v>8.82771110534668</v>
       </c>
       <c r="H411" t="n">
         <v>189726</v>
@@ -12375,7 +12375,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G414" t="n">
-        <v>8.50451946258545</v>
+        <v>8.50452041625977</v>
       </c>
       <c r="H414" t="n">
         <v>71607</v>
@@ -12404,7 +12404,7 @@
         <v>9.21500015258789</v>
       </c>
       <c r="G415" t="n">
-        <v>8.50913715362549</v>
+        <v>8.50913619995117</v>
       </c>
       <c r="H415" t="n">
         <v>86476</v>
@@ -12433,7 +12433,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G416" t="n">
-        <v>8.67073249816895</v>
+        <v>8.67073154449463</v>
       </c>
       <c r="H416" t="n">
         <v>133259</v>
@@ -12665,7 +12665,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G424" t="n">
-        <v>8.0520544052124</v>
+        <v>8.05205345153809</v>
       </c>
       <c r="H424" t="n">
         <v>141617</v>
@@ -12723,7 +12723,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G426" t="n">
-        <v>7.92277717590332</v>
+        <v>7.92277669906616</v>
       </c>
       <c r="H426" t="n">
         <v>224688</v>
@@ -12752,7 +12752,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G427" t="n">
-        <v>7.82120370864868</v>
+        <v>7.82120323181152</v>
       </c>
       <c r="H427" t="n">
         <v>315397</v>
@@ -12781,7 +12781,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G428" t="n">
-        <v>7.82120370864868</v>
+        <v>7.82120323181152</v>
       </c>
       <c r="H428" t="n">
         <v>153923</v>
@@ -12810,7 +12810,7 @@
         <v>8.46500015258789</v>
       </c>
       <c r="G429" t="n">
-        <v>7.8165864944458</v>
+        <v>7.81658697128296</v>
       </c>
       <c r="H429" t="n">
         <v>124892</v>
@@ -12868,7 +12868,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G431" t="n">
-        <v>7.81196975708008</v>
+        <v>7.81196928024292</v>
       </c>
       <c r="H431" t="n">
         <v>211938</v>
@@ -12926,7 +12926,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G433" t="n">
-        <v>7.54418325424194</v>
+        <v>7.5441837310791</v>
       </c>
       <c r="H433" t="n">
         <v>411895</v>
@@ -13013,7 +13013,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G436" t="n">
-        <v>7.10095119476318</v>
+        <v>7.10095071792603</v>
       </c>
       <c r="H436" t="n">
         <v>185032</v>
@@ -13042,7 +13042,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G437" t="n">
-        <v>7.16558933258057</v>
+        <v>7.16558885574341</v>
       </c>
       <c r="H437" t="n">
         <v>348774</v>
@@ -13071,7 +13071,7 @@
         <v>7.72499990463257</v>
       </c>
       <c r="G438" t="n">
-        <v>7.13326978683472</v>
+        <v>7.13327026367188</v>
       </c>
       <c r="H438" t="n">
         <v>174564</v>
@@ -13100,7 +13100,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G439" t="n">
-        <v>7.12403631210327</v>
+        <v>7.12403583526611</v>
       </c>
       <c r="H439" t="n">
         <v>206525</v>
@@ -13245,7 +13245,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G444" t="n">
-        <v>6.61154890060425</v>
+        <v>6.61154842376709</v>
       </c>
       <c r="H444" t="n">
         <v>161687</v>
@@ -13274,7 +13274,7 @@
         <v>7.02500009536743</v>
       </c>
       <c r="G445" t="n">
-        <v>6.48688936233521</v>
+        <v>6.48688983917236</v>
       </c>
       <c r="H445" t="n">
         <v>144224</v>
@@ -13332,7 +13332,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G447" t="n">
-        <v>6.33452844619751</v>
+        <v>6.33452892303467</v>
       </c>
       <c r="H447" t="n">
         <v>231466</v>
@@ -13361,7 +13361,7 @@
         <v>7.13500022888184</v>
       </c>
       <c r="G448" t="n">
-        <v>6.588463306427</v>
+        <v>6.58846378326416</v>
       </c>
       <c r="H448" t="n">
         <v>537214</v>
@@ -13419,7 +13419,7 @@
         <v>7.31500005722046</v>
       </c>
       <c r="G450" t="n">
-        <v>6.75467586517334</v>
+        <v>6.75467538833618</v>
       </c>
       <c r="H450" t="n">
         <v>323055</v>
@@ -13477,7 +13477,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G452" t="n">
-        <v>6.55614471435547</v>
+        <v>6.55614423751831</v>
       </c>
       <c r="H452" t="n">
         <v>185501</v>
@@ -13622,7 +13622,7 @@
         <v>7.25</v>
       </c>
       <c r="G457" t="n">
-        <v>6.69465494155884</v>
+        <v>6.69465446472168</v>
       </c>
       <c r="H457" t="n">
         <v>280368</v>
@@ -13651,7 +13651,7 @@
         <v>7.09499979019165</v>
       </c>
       <c r="G458" t="n">
-        <v>6.55152750015259</v>
+        <v>6.55152702331543</v>
       </c>
       <c r="H458" t="n">
         <v>694126</v>
@@ -13680,7 +13680,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G459" t="n">
-        <v>6.55614471435547</v>
+        <v>6.55614423751831</v>
       </c>
       <c r="H459" t="n">
         <v>342488</v>
@@ -13738,7 +13738,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G461" t="n">
-        <v>6.37146425247192</v>
+        <v>6.37146472930908</v>
       </c>
       <c r="H461" t="n">
         <v>296679</v>
@@ -13767,7 +13767,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G462" t="n">
-        <v>6.37146425247192</v>
+        <v>6.37146472930908</v>
       </c>
       <c r="H462" t="n">
         <v>4069866</v>
@@ -13854,7 +13854,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G465" t="n">
-        <v>6.18678379058838</v>
+        <v>6.18678426742554</v>
       </c>
       <c r="H465" t="n">
         <v>200486</v>
@@ -13883,7 +13883,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G466" t="n">
-        <v>5.808189868927</v>
+        <v>5.80818939208984</v>
       </c>
       <c r="H466" t="n">
         <v>501243</v>
@@ -13970,7 +13970,7 @@
         <v>5.84499979019165</v>
       </c>
       <c r="G469" t="n">
-        <v>5.39727687835693</v>
+        <v>5.39727640151978</v>
       </c>
       <c r="H469" t="n">
         <v>467466</v>
@@ -14028,7 +14028,7 @@
         <v>5.875</v>
       </c>
       <c r="G471" t="n">
-        <v>5.4249792098999</v>
+        <v>5.42497873306274</v>
       </c>
       <c r="H471" t="n">
         <v>292652</v>
@@ -14057,7 +14057,7 @@
         <v>6.16499996185303</v>
       </c>
       <c r="G472" t="n">
-        <v>5.69276523590088</v>
+        <v>5.69276475906372</v>
       </c>
       <c r="H472" t="n">
         <v>637767</v>
@@ -14086,7 +14086,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G473" t="n">
-        <v>5.5958080291748</v>
+        <v>5.59580755233765</v>
       </c>
       <c r="H473" t="n">
         <v>246202</v>
@@ -14144,7 +14144,7 @@
         <v>5.82499980926514</v>
       </c>
       <c r="G475" t="n">
-        <v>5.37880897521973</v>
+        <v>5.37880849838257</v>
       </c>
       <c r="H475" t="n">
         <v>758444</v>
@@ -14260,7 +14260,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G479" t="n">
-        <v>5.70661592483521</v>
+        <v>5.70661544799805</v>
       </c>
       <c r="H479" t="n">
         <v>248086</v>
@@ -14289,7 +14289,7 @@
         <v>5.9850001335144</v>
       </c>
       <c r="G480" t="n">
-        <v>5.52655267715454</v>
+        <v>5.5265531539917</v>
       </c>
       <c r="H480" t="n">
         <v>491648</v>
@@ -14318,7 +14318,7 @@
         <v>5.86499977111816</v>
       </c>
       <c r="G481" t="n">
-        <v>5.41574430465698</v>
+        <v>5.41574478149414</v>
       </c>
       <c r="H481" t="n">
         <v>276524</v>
@@ -14463,7 +14463,7 @@
         <v>5.75</v>
       </c>
       <c r="G486" t="n">
-        <v>5.30955362319946</v>
+        <v>5.30955410003662</v>
       </c>
       <c r="H486" t="n">
         <v>311135</v>
@@ -14550,7 +14550,7 @@
         <v>5.45499992370605</v>
       </c>
       <c r="G489" t="n">
-        <v>5.03714990615845</v>
+        <v>5.03715038299561</v>
       </c>
       <c r="H489" t="n">
         <v>208132</v>
@@ -14608,7 +14608,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G491" t="n">
-        <v>4.95404386520386</v>
+        <v>4.95404434204102</v>
       </c>
       <c r="H491" t="n">
         <v>378086</v>
@@ -14666,7 +14666,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G493" t="n">
-        <v>4.83400249481201</v>
+        <v>4.83400201797485</v>
       </c>
       <c r="H493" t="n">
         <v>200923</v>
@@ -14695,7 +14695,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G494" t="n">
-        <v>4.88478946685791</v>
+        <v>4.88478899002075</v>
       </c>
       <c r="H494" t="n">
         <v>111362</v>
@@ -14724,7 +14724,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G495" t="n">
-        <v>4.88940668106079</v>
+        <v>4.88940620422363</v>
       </c>
       <c r="H495" t="n">
         <v>133883</v>
@@ -14753,7 +14753,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G496" t="n">
-        <v>5.13410758972168</v>
+        <v>5.13410711288452</v>
       </c>
       <c r="H496" t="n">
         <v>302728</v>
@@ -14782,7 +14782,7 @@
         <v>5.77500009536743</v>
       </c>
       <c r="G497" t="n">
-        <v>5.33263826370239</v>
+        <v>5.33263874053955</v>
       </c>
       <c r="H497" t="n">
         <v>328997</v>
@@ -14811,7 +14811,7 @@
         <v>5.61499977111816</v>
       </c>
       <c r="G498" t="n">
-        <v>5.18489408493042</v>
+        <v>5.18489456176758</v>
       </c>
       <c r="H498" t="n">
         <v>207381</v>
@@ -14869,7 +14869,7 @@
         <v>5.69500017166138</v>
       </c>
       <c r="G500" t="n">
-        <v>5.25876712799072</v>
+        <v>5.25876665115356</v>
       </c>
       <c r="H500" t="n">
         <v>671518</v>
@@ -14898,7 +14898,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G501" t="n">
-        <v>5.38342571258545</v>
+        <v>5.38342523574829</v>
       </c>
       <c r="H501" t="n">
         <v>200804</v>
@@ -15130,7 +15130,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G509" t="n">
-        <v>5.24491548538208</v>
+        <v>5.24491500854492</v>
       </c>
       <c r="H509" t="n">
         <v>138219</v>
@@ -15159,7 +15159,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G510" t="n">
-        <v>5.21259641647339</v>
+        <v>5.21259689331055</v>
       </c>
       <c r="H510" t="n">
         <v>110937</v>
@@ -15246,7 +15246,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G513" t="n">
-        <v>5.21259641647339</v>
+        <v>5.21259689331055</v>
       </c>
       <c r="H513" t="n">
         <v>215173</v>
@@ -15304,7 +15304,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G515" t="n">
-        <v>5.11563920974731</v>
+        <v>5.11563968658447</v>
       </c>
       <c r="H515" t="n">
         <v>481344</v>
@@ -15362,7 +15362,7 @@
         <v>5.72499990463257</v>
       </c>
       <c r="G517" t="n">
-        <v>5.28646898269653</v>
+        <v>5.28646850585938</v>
       </c>
       <c r="H517" t="n">
         <v>250687</v>
@@ -15391,7 +15391,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G518" t="n">
-        <v>5.24491548538208</v>
+        <v>5.24491500854492</v>
       </c>
       <c r="H518" t="n">
         <v>260768</v>
@@ -15420,7 +15420,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G519" t="n">
-        <v>5.25414943695068</v>
+        <v>5.25414991378784</v>
       </c>
       <c r="H519" t="n">
         <v>250927</v>
@@ -15536,7 +15536,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G523" t="n">
-        <v>5.16180944442749</v>
+        <v>5.16180992126465</v>
       </c>
       <c r="H523" t="n">
         <v>249552</v>
@@ -15797,7 +15797,7 @@
         <v>6.30499982833862</v>
       </c>
       <c r="G532" t="n">
-        <v>5.82204055786133</v>
+        <v>5.82204103469849</v>
       </c>
       <c r="H532" t="n">
         <v>298757</v>
@@ -15826,7 +15826,7 @@
         <v>6.40500020980835</v>
       </c>
       <c r="G533" t="n">
-        <v>5.91438102722168</v>
+        <v>5.91438150405884</v>
       </c>
       <c r="H533" t="n">
         <v>366529</v>
@@ -15884,7 +15884,7 @@
         <v>6.2649998664856</v>
       </c>
       <c r="G535" t="n">
-        <v>5.78510475158691</v>
+        <v>5.78510522842407</v>
       </c>
       <c r="H535" t="n">
         <v>171909</v>
@@ -15913,7 +15913,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G536" t="n">
-        <v>5.71584987640381</v>
+        <v>5.71585035324097</v>
       </c>
       <c r="H536" t="n">
         <v>257462</v>
@@ -16000,7 +16000,7 @@
         <v>6.38500022888184</v>
       </c>
       <c r="G539" t="n">
-        <v>5.89591360092163</v>
+        <v>5.89591312408447</v>
       </c>
       <c r="H539" t="n">
         <v>946632</v>
@@ -16058,7 +16058,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G541" t="n">
-        <v>6.05750846862793</v>
+        <v>6.05750751495361</v>
       </c>
       <c r="H541" t="n">
         <v>374625</v>
@@ -16319,7 +16319,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G550" t="n">
-        <v>5.6281270980835</v>
+        <v>5.62812662124634</v>
       </c>
       <c r="H550" t="n">
         <v>208450</v>
@@ -16348,7 +16348,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G551" t="n">
-        <v>5.70661592483521</v>
+        <v>5.70661544799805</v>
       </c>
       <c r="H551" t="n">
         <v>159509</v>
@@ -16377,7 +16377,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G552" t="n">
-        <v>5.70661592483521</v>
+        <v>5.70661544799805</v>
       </c>
       <c r="H552" t="n">
         <v>128983</v>
@@ -16406,7 +16406,7 @@
         <v>6.22499990463257</v>
       </c>
       <c r="G553" t="n">
-        <v>5.74816942214966</v>
+        <v>5.7481689453125</v>
       </c>
       <c r="H553" t="n">
         <v>87583</v>
@@ -16435,7 +16435,7 @@
         <v>6.29500007629395</v>
       </c>
       <c r="G554" t="n">
-        <v>5.81280708312988</v>
+        <v>5.81280755996704</v>
       </c>
       <c r="H554" t="n">
         <v>151233</v>
@@ -16464,7 +16464,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G555" t="n">
-        <v>5.71584987640381</v>
+        <v>5.71585035324097</v>
       </c>
       <c r="H555" t="n">
         <v>675111</v>
@@ -16493,7 +16493,7 @@
         <v>6.06500005722046</v>
       </c>
       <c r="G556" t="n">
-        <v>5.60042524337769</v>
+        <v>5.60042476654053</v>
       </c>
       <c r="H556" t="n">
         <v>275234</v>
@@ -16638,7 +16638,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G561" t="n">
-        <v>5.36957502365112</v>
+        <v>5.36957454681396</v>
       </c>
       <c r="H561" t="n">
         <v>298629</v>
@@ -16754,7 +16754,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G565" t="n">
-        <v>5.51270151138306</v>
+        <v>5.51270198822021</v>
       </c>
       <c r="H565" t="n">
         <v>164534</v>
@@ -16783,7 +16783,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G566" t="n">
-        <v>5.38342571258545</v>
+        <v>5.38342523574829</v>
       </c>
       <c r="H566" t="n">
         <v>143325</v>
@@ -16957,7 +16957,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G572" t="n">
-        <v>5.2402982711792</v>
+        <v>5.24029874801636</v>
       </c>
       <c r="H572" t="n">
         <v>371542</v>
@@ -17044,7 +17044,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G575" t="n">
-        <v>5.13410758972168</v>
+        <v>5.13410711288452</v>
       </c>
       <c r="H575" t="n">
         <v>302344</v>
@@ -17073,7 +17073,7 @@
         <v>5.70499992370605</v>
       </c>
       <c r="G576" t="n">
-        <v>5.26800012588501</v>
+        <v>5.26800060272217</v>
       </c>
       <c r="H576" t="n">
         <v>379568</v>
@@ -17189,7 +17189,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G580" t="n">
-        <v>5.09717130661011</v>
+        <v>5.09717082977295</v>
       </c>
       <c r="H580" t="n">
         <v>391172</v>
@@ -17218,7 +17218,7 @@
         <v>5.45499992370605</v>
       </c>
       <c r="G581" t="n">
-        <v>5.03714990615845</v>
+        <v>5.03715038299561</v>
       </c>
       <c r="H581" t="n">
         <v>1475414</v>
@@ -17305,7 +17305,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G584" t="n">
-        <v>5.37419176101685</v>
+        <v>5.374192237854</v>
       </c>
       <c r="H584" t="n">
         <v>450011</v>
@@ -17421,7 +17421,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G588" t="n">
-        <v>5.5958080291748</v>
+        <v>5.59580755233765</v>
       </c>
       <c r="H588" t="n">
         <v>428003</v>
@@ -17450,7 +17450,7 @@
         <v>6.06500005722046</v>
       </c>
       <c r="G589" t="n">
-        <v>5.60042524337769</v>
+        <v>5.60042476654053</v>
       </c>
       <c r="H589" t="n">
         <v>462275</v>
@@ -17479,7 +17479,7 @@
         <v>5.72499990463257</v>
       </c>
       <c r="G590" t="n">
-        <v>5.28646898269653</v>
+        <v>5.28646850585938</v>
       </c>
       <c r="H590" t="n">
         <v>562114</v>
@@ -17595,7 +17595,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G594" t="n">
-        <v>5.05100107192993</v>
+        <v>5.05100154876709</v>
       </c>
       <c r="H594" t="n">
         <v>677677</v>
@@ -17682,7 +17682,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G597" t="n">
-        <v>4.83400249481201</v>
+        <v>4.83400201797485</v>
       </c>
       <c r="H597" t="n">
         <v>384652</v>
@@ -17740,7 +17740,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G599" t="n">
-        <v>4.70010900497437</v>
+        <v>4.70010948181152</v>
       </c>
       <c r="H599" t="n">
         <v>555539</v>
@@ -17769,7 +17769,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G600" t="n">
-        <v>4.81091737747192</v>
+        <v>4.81091785430908</v>
       </c>
       <c r="H600" t="n">
         <v>367022</v>
@@ -17856,7 +17856,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G603" t="n">
-        <v>4.89864015579224</v>
+        <v>4.89864063262939</v>
       </c>
       <c r="H603" t="n">
         <v>510591</v>
@@ -17914,7 +17914,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G605" t="n">
-        <v>4.66317319869995</v>
+        <v>4.66317367553711</v>
       </c>
       <c r="H605" t="n">
         <v>1112720</v>
@@ -17943,7 +17943,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>4.52466297149658</v>
+        <v>4.52466344833374</v>
       </c>
       <c r="H606" t="n">
         <v>835466</v>
@@ -17972,7 +17972,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G607" t="n">
-        <v>4.52466297149658</v>
+        <v>4.52466344833374</v>
       </c>
       <c r="H607" t="n">
         <v>662577</v>
@@ -18001,7 +18001,7 @@
         <v>4.82200002670288</v>
       </c>
       <c r="G608" t="n">
-        <v>4.45263814926147</v>
+        <v>4.45263767242432</v>
       </c>
       <c r="H608" t="n">
         <v>597938</v>
@@ -18059,7 +18059,7 @@
         <v>4.66400003433228</v>
       </c>
       <c r="G610" t="n">
-        <v>4.30674076080322</v>
+        <v>4.30674028396606</v>
       </c>
       <c r="H610" t="n">
         <v>394307</v>
@@ -18117,7 +18117,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G612" t="n">
-        <v>4.35845041275024</v>
+        <v>4.3584508895874</v>
       </c>
       <c r="H612" t="n">
         <v>462964</v>
@@ -18175,7 +18175,7 @@
         <v>4.74399995803833</v>
       </c>
       <c r="G614" t="n">
-        <v>4.38061237335205</v>
+        <v>4.38061285018921</v>
       </c>
       <c r="H614" t="n">
         <v>609563</v>
@@ -18233,7 +18233,7 @@
         <v>4.71799993515015</v>
       </c>
       <c r="G616" t="n">
-        <v>4.35660362243652</v>
+        <v>4.35660409927368</v>
       </c>
       <c r="H616" t="n">
         <v>435069</v>
@@ -18349,7 +18349,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G620" t="n">
-        <v>4.50619554519653</v>
+        <v>4.50619506835938</v>
       </c>
       <c r="H620" t="n">
         <v>279339</v>
@@ -18378,7 +18378,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G621" t="n">
-        <v>4.56898641586304</v>
+        <v>4.56898593902588</v>
       </c>
       <c r="H621" t="n">
         <v>377386</v>
@@ -18407,7 +18407,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G622" t="n">
-        <v>4.70934343338013</v>
+        <v>4.70934295654297</v>
       </c>
       <c r="H622" t="n">
         <v>579073</v>
@@ -18465,7 +18465,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G624" t="n">
-        <v>4.6262378692627</v>
+        <v>4.62623739242554</v>
       </c>
       <c r="H624" t="n">
         <v>1420570</v>
@@ -18552,7 +18552,7 @@
         <v>4.97800016403198</v>
       </c>
       <c r="G627" t="n">
-        <v>4.59668874740601</v>
+        <v>4.59668827056885</v>
       </c>
       <c r="H627" t="n">
         <v>698215</v>
@@ -18581,7 +18581,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G628" t="n">
-        <v>4.70010900497437</v>
+        <v>4.70010948181152</v>
       </c>
       <c r="H628" t="n">
         <v>666276</v>
@@ -18610,7 +18610,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G629" t="n">
-        <v>4.60776853561401</v>
+        <v>4.60776901245117</v>
       </c>
       <c r="H629" t="n">
         <v>695656</v>
@@ -18639,7 +18639,7 @@
         <v>5.0149998664856</v>
       </c>
       <c r="G630" t="n">
-        <v>4.63085412979126</v>
+        <v>4.6308536529541</v>
       </c>
       <c r="H630" t="n">
         <v>580822</v>
@@ -18726,7 +18726,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G633" t="n">
-        <v>4.63421201705933</v>
+        <v>4.63421249389648</v>
       </c>
       <c r="H633" t="n">
         <v>659569</v>
@@ -18900,7 +18900,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G639" t="n">
-        <v>4.47546672821045</v>
+        <v>4.47546625137329</v>
       </c>
       <c r="H639" t="n">
         <v>721270</v>
@@ -18929,7 +18929,7 @@
         <v>4.81199979782104</v>
       </c>
       <c r="G640" t="n">
-        <v>4.60169792175293</v>
+        <v>4.60169744491577</v>
       </c>
       <c r="H640" t="n">
         <v>409298</v>
@@ -19074,7 +19074,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G645" t="n">
-        <v>4.45634031295776</v>
+        <v>4.45634078979492</v>
       </c>
       <c r="H645" t="n">
         <v>337361</v>
@@ -19132,7 +19132,7 @@
         <v>4.62400007247925</v>
       </c>
       <c r="G647" t="n">
-        <v>4.42191457748413</v>
+        <v>4.42191410064697</v>
       </c>
       <c r="H647" t="n">
         <v>590963</v>
@@ -19219,7 +19219,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G650" t="n">
-        <v>4.17136430740356</v>
+        <v>4.17136478424072</v>
       </c>
       <c r="H650" t="n">
         <v>575556</v>
@@ -19306,7 +19306,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G653" t="n">
-        <v>4.20770359039307</v>
+        <v>4.20770406723022</v>
       </c>
       <c r="H653" t="n">
         <v>253568</v>
@@ -19480,7 +19480,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G659" t="n">
-        <v>3.9303777217865</v>
+        <v>3.93037796020508</v>
       </c>
       <c r="H659" t="n">
         <v>499794</v>
@@ -19770,7 +19770,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G669" t="n">
-        <v>3.65496444702148</v>
+        <v>3.65496468544006</v>
       </c>
       <c r="H669" t="n">
         <v>556073</v>
@@ -19857,7 +19857,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G672" t="n">
-        <v>3.81370973587036</v>
+        <v>3.81370949745178</v>
       </c>
       <c r="H672" t="n">
         <v>401105</v>
@@ -19886,7 +19886,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G673" t="n">
-        <v>3.81370973587036</v>
+        <v>3.81370949745178</v>
       </c>
       <c r="H673" t="n">
         <v>294689</v>
@@ -19915,7 +19915,7 @@
         <v>4.17600011825562</v>
       </c>
       <c r="G674" t="n">
-        <v>3.99349331855774</v>
+        <v>3.99349355697632</v>
       </c>
       <c r="H674" t="n">
         <v>714573</v>
@@ -20379,7 +20379,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G690" t="n">
-        <v>3.4560546875</v>
+        <v>3.45605492591858</v>
       </c>
       <c r="H690" t="n">
         <v>383156</v>
@@ -20756,7 +20756,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G703" t="n">
-        <v>3.96862983703613</v>
+        <v>3.96862959861755</v>
       </c>
       <c r="H703" t="n">
         <v>402206</v>
@@ -20785,7 +20785,7 @@
         <v>4.1560001373291</v>
       </c>
       <c r="G704" t="n">
-        <v>3.97436738014221</v>
+        <v>3.97436785697937</v>
       </c>
       <c r="H704" t="n">
         <v>366565</v>
@@ -20843,7 +20843,7 @@
         <v>4.27600002288818</v>
       </c>
       <c r="G706" t="n">
-        <v>4.08912324905396</v>
+        <v>4.0891227722168</v>
       </c>
       <c r="H706" t="n">
         <v>382472</v>
@@ -20872,7 +20872,7 @@
         <v>4.13600015640259</v>
       </c>
       <c r="G707" t="n">
-        <v>3.95524144172668</v>
+        <v>3.95524168014526</v>
       </c>
       <c r="H707" t="n">
         <v>503313</v>
@@ -20930,7 +20930,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G709" t="n">
-        <v>3.98966789245605</v>
+        <v>3.98966813087463</v>
       </c>
       <c r="H709" t="n">
         <v>357159</v>
@@ -21017,7 +21017,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G712" t="n">
-        <v>3.67026543617249</v>
+        <v>3.67026519775391</v>
       </c>
       <c r="H712" t="n">
         <v>437455</v>
@@ -21162,7 +21162,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G717" t="n">
-        <v>3.81370973587036</v>
+        <v>3.81370949745178</v>
       </c>
       <c r="H717" t="n">
         <v>286225</v>
@@ -21191,7 +21191,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G718" t="n">
-        <v>3.82327246665955</v>
+        <v>3.82327270507812</v>
       </c>
       <c r="H718" t="n">
         <v>150642</v>
@@ -21220,7 +21220,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G719" t="n">
-        <v>3.91507720947266</v>
+        <v>3.91507697105408</v>
       </c>
       <c r="H719" t="n">
         <v>372351</v>
@@ -21307,7 +21307,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G722" t="n">
-        <v>3.98584318161011</v>
+        <v>3.98584294319153</v>
       </c>
       <c r="H722" t="n">
         <v>634315</v>
@@ -21365,7 +21365,7 @@
         <v>4.42600011825562</v>
       </c>
       <c r="G724" t="n">
-        <v>4.23256731033325</v>
+        <v>4.23256778717041</v>
       </c>
       <c r="H724" t="n">
         <v>1439555</v>
@@ -21394,7 +21394,7 @@
         <v>4.51200008392334</v>
       </c>
       <c r="G725" t="n">
-        <v>4.31480932235718</v>
+        <v>4.31480884552002</v>
       </c>
       <c r="H725" t="n">
         <v>724657</v>
@@ -21452,7 +21452,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G727" t="n">
-        <v>4.15032577514648</v>
+        <v>4.15032625198364</v>
       </c>
       <c r="H727" t="n">
         <v>336308</v>
@@ -21510,7 +21510,7 @@
         <v>4.25</v>
       </c>
       <c r="G729" t="n">
-        <v>4.06425952911377</v>
+        <v>4.06425905227661</v>
       </c>
       <c r="H729" t="n">
         <v>168991</v>
@@ -21597,7 +21597,7 @@
         <v>4.2039999961853</v>
       </c>
       <c r="G732" t="n">
-        <v>4.02026987075806</v>
+        <v>4.0202693939209</v>
       </c>
       <c r="H732" t="n">
         <v>193502</v>
@@ -21742,7 +21742,7 @@
         <v>4.11399984359741</v>
       </c>
       <c r="G737" t="n">
-        <v>3.9342029094696</v>
+        <v>3.93420267105103</v>
       </c>
       <c r="H737" t="n">
         <v>129269</v>
@@ -21829,7 +21829,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G740" t="n">
-        <v>3.96862983703613</v>
+        <v>3.96862959861755</v>
       </c>
       <c r="H740" t="n">
         <v>236046</v>
@@ -21858,7 +21858,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G741" t="n">
-        <v>3.91507720947266</v>
+        <v>3.91507697105408</v>
       </c>
       <c r="H741" t="n">
         <v>182762</v>
@@ -22061,7 +22061,7 @@
         <v>3.90799999237061</v>
       </c>
       <c r="G748" t="n">
-        <v>3.73720598220825</v>
+        <v>3.73720574378967</v>
       </c>
       <c r="H748" t="n">
         <v>191909</v>
@@ -22119,7 +22119,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G750" t="n">
-        <v>3.70086646080017</v>
+        <v>3.70086669921875</v>
       </c>
       <c r="H750" t="n">
         <v>77185</v>
@@ -22148,7 +22148,7 @@
         <v>3.93799996376038</v>
       </c>
       <c r="G751" t="n">
-        <v>3.76589465141296</v>
+        <v>3.76589488983154</v>
       </c>
       <c r="H751" t="n">
         <v>138045</v>
@@ -22264,7 +22264,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G755" t="n">
-        <v>3.7391185760498</v>
+        <v>3.73911881446838</v>
       </c>
       <c r="H755" t="n">
         <v>208777</v>
@@ -22380,7 +22380,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G759" t="n">
-        <v>3.57846069335938</v>
+        <v>3.57846093177795</v>
       </c>
       <c r="H759" t="n">
         <v>337584</v>
@@ -22409,7 +22409,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G760" t="n">
-        <v>3.62245035171509</v>
+        <v>3.62245059013367</v>
       </c>
       <c r="H760" t="n">
         <v>422072</v>
@@ -22467,7 +22467,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G762" t="n">
-        <v>3.56316018104553</v>
+        <v>3.56315994262695</v>
       </c>
       <c r="H762" t="n">
         <v>704289</v>
@@ -22496,7 +22496,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G763" t="n">
-        <v>3.54785943031311</v>
+        <v>3.54785919189453</v>
       </c>
       <c r="H763" t="n">
         <v>1097480</v>
@@ -22583,7 +22583,7 @@
         <v>3.64800000190735</v>
       </c>
       <c r="G766" t="n">
-        <v>3.4885687828064</v>
+        <v>3.48856902122498</v>
       </c>
       <c r="H766" t="n">
         <v>1669355</v>
@@ -22728,7 +22728,7 @@
         <v>3.64400005340576</v>
       </c>
       <c r="G771" t="n">
-        <v>3.48474383354187</v>
+        <v>3.48474359512329</v>
       </c>
       <c r="H771" t="n">
         <v>105519</v>
@@ -22757,7 +22757,7 @@
         <v>3.63199996948242</v>
       </c>
       <c r="G772" t="n">
-        <v>3.47326803207397</v>
+        <v>3.47326827049255</v>
       </c>
       <c r="H772" t="n">
         <v>121534</v>
@@ -22873,7 +22873,7 @@
         <v>3.95799994468689</v>
       </c>
       <c r="G776" t="n">
-        <v>3.78502058982849</v>
+        <v>3.78502082824707</v>
       </c>
       <c r="H776" t="n">
         <v>243650</v>
@@ -22902,7 +22902,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G777" t="n">
-        <v>3.76972007751465</v>
+        <v>3.76971983909607</v>
       </c>
       <c r="H777" t="n">
         <v>111182</v>
@@ -22960,7 +22960,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G779" t="n">
-        <v>3.70086646080017</v>
+        <v>3.70086669921875</v>
       </c>
       <c r="H779" t="n">
         <v>145693</v>
@@ -22989,7 +22989,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G780" t="n">
-        <v>3.5975866317749</v>
+        <v>3.59758687019348</v>
       </c>
       <c r="H780" t="n">
         <v>157659</v>
@@ -23076,7 +23076,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G783" t="n">
-        <v>3.44075417518616</v>
+        <v>3.44075393676758</v>
       </c>
       <c r="H783" t="n">
         <v>613580</v>
@@ -23105,7 +23105,7 @@
         <v>3.41599988937378</v>
       </c>
       <c r="G784" t="n">
-        <v>3.26670789718628</v>
+        <v>3.26670813560486</v>
       </c>
       <c r="H784" t="n">
         <v>455535</v>
@@ -23134,7 +23134,7 @@
         <v>3.41599988937378</v>
       </c>
       <c r="G785" t="n">
-        <v>3.26670789718628</v>
+        <v>3.26670813560486</v>
       </c>
       <c r="H785" t="n">
         <v>519347</v>
@@ -23163,7 +23163,7 @@
         <v>3.46799993515015</v>
       </c>
       <c r="G786" t="n">
-        <v>3.31643557548523</v>
+        <v>3.31643533706665</v>
       </c>
       <c r="H786" t="n">
         <v>202674</v>
@@ -23192,7 +23192,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G787" t="n">
-        <v>3.29157185554504</v>
+        <v>3.29157161712646</v>
       </c>
       <c r="H787" t="n">
         <v>188696</v>
@@ -23424,7 +23424,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G795" t="n">
-        <v>3.2074179649353</v>
+        <v>3.20741772651672</v>
       </c>
       <c r="H795" t="n">
         <v>383770</v>
@@ -23801,7 +23801,7 @@
         <v>3.47399997711182</v>
       </c>
       <c r="G808" t="n">
-        <v>3.32217311859131</v>
+        <v>3.32217335700989</v>
       </c>
       <c r="H808" t="n">
         <v>80720</v>
@@ -23975,7 +23975,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G814" t="n">
-        <v>3.22654390335083</v>
+        <v>3.22654366493225</v>
       </c>
       <c r="H814" t="n">
         <v>115313</v>
@@ -24149,7 +24149,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G820" t="n">
-        <v>3.55168437957764</v>
+        <v>3.55168461799622</v>
       </c>
       <c r="H820" t="n">
         <v>1031313</v>
@@ -24178,7 +24178,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G821" t="n">
-        <v>3.50769472122192</v>
+        <v>3.5076949596405</v>
       </c>
       <c r="H821" t="n">
         <v>354331</v>
@@ -24236,7 +24236,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G823" t="n">
-        <v>3.53638386726379</v>
+        <v>3.53638362884521</v>
       </c>
       <c r="H823" t="n">
         <v>421877</v>
@@ -24323,7 +24323,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G826" t="n">
-        <v>3.58228611946106</v>
+        <v>3.58228588104248</v>
       </c>
       <c r="H826" t="n">
         <v>258986</v>
@@ -24352,7 +24352,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G827" t="n">
-        <v>3.57654809951782</v>
+        <v>3.5765483379364</v>
       </c>
       <c r="H827" t="n">
         <v>166129</v>
@@ -24381,7 +24381,7 @@
         <v>3.84400010108948</v>
       </c>
       <c r="G828" t="n">
-        <v>3.67600297927856</v>
+        <v>3.67600321769714</v>
       </c>
       <c r="H828" t="n">
         <v>474129</v>
@@ -24526,7 +24526,7 @@
         <v>4.22599983215332</v>
       </c>
       <c r="G833" t="n">
-        <v>4.04130840301514</v>
+        <v>4.04130792617798</v>
       </c>
       <c r="H833" t="n">
         <v>2312238</v>
@@ -24758,7 +24758,7 @@
         <v>4.68599987030029</v>
       </c>
       <c r="G841" t="n">
-        <v>4.48120403289795</v>
+        <v>4.48120450973511</v>
       </c>
       <c r="H841" t="n">
         <v>337090</v>
@@ -24816,7 +24816,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G843" t="n">
-        <v>4.54431962966919</v>
+        <v>4.54432010650635</v>
       </c>
       <c r="H843" t="n">
         <v>212793</v>
@@ -24903,7 +24903,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G846" t="n">
-        <v>4.35688638687134</v>
+        <v>4.35688591003418</v>
       </c>
       <c r="H846" t="n">
         <v>178453</v>
@@ -24932,7 +24932,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G847" t="n">
-        <v>4.2631688117981</v>
+        <v>4.26316928863525</v>
       </c>
       <c r="H847" t="n">
         <v>228223</v>
@@ -24990,7 +24990,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G849" t="n">
-        <v>4.17136430740356</v>
+        <v>4.17136478424072</v>
       </c>
       <c r="H849" t="n">
         <v>216742</v>
@@ -25048,7 +25048,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G851" t="n">
-        <v>3.9303777217865</v>
+        <v>3.93037796020508</v>
       </c>
       <c r="H851" t="n">
         <v>187268</v>
@@ -25135,7 +25135,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G854" t="n">
-        <v>3.77928304672241</v>
+        <v>3.77928280830383</v>
       </c>
       <c r="H854" t="n">
         <v>245578</v>
@@ -25251,7 +25251,7 @@
         <v>3.51200008392334</v>
       </c>
       <c r="G858" t="n">
-        <v>3.35851287841797</v>
+        <v>3.35851263999939</v>
       </c>
       <c r="H858" t="n">
         <v>146055</v>
@@ -25280,7 +25280,7 @@
         <v>3.56800007820129</v>
       </c>
       <c r="G859" t="n">
-        <v>3.41206550598145</v>
+        <v>3.41206526756287</v>
       </c>
       <c r="H859" t="n">
         <v>419236</v>
@@ -25396,7 +25396,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G863" t="n">
-        <v>3.47900605201721</v>
+        <v>3.47900581359863</v>
       </c>
       <c r="H863" t="n">
         <v>215914</v>
@@ -25541,7 +25541,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G868" t="n">
-        <v>3.77928304672241</v>
+        <v>3.77928280830383</v>
       </c>
       <c r="H868" t="n">
         <v>73720</v>
@@ -25657,7 +25657,7 @@
         <v>4.12400007247925</v>
       </c>
       <c r="G872" t="n">
-        <v>3.94376611709595</v>
+        <v>3.94376587867737</v>
       </c>
       <c r="H872" t="n">
         <v>191569</v>
@@ -25860,7 +25860,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G879" t="n">
-        <v>4.47546672821045</v>
+        <v>4.47546625137329</v>
       </c>
       <c r="H879" t="n">
         <v>120035</v>
@@ -25976,7 +25976,7 @@
         <v>4.38800001144409</v>
       </c>
       <c r="G883" t="n">
-        <v>4.19622802734375</v>
+        <v>4.19622850418091</v>
       </c>
       <c r="H883" t="n">
         <v>292289</v>
@@ -26063,7 +26063,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G886" t="n">
-        <v>4.20196628570557</v>
+        <v>4.20196580886841</v>
       </c>
       <c r="H886" t="n">
         <v>132141</v>
@@ -26237,7 +26237,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G892" t="n">
-        <v>4.57109642028809</v>
+        <v>4.57109689712524</v>
       </c>
       <c r="H892" t="n">
         <v>407750</v>
@@ -26295,7 +26295,7 @@
         <v>4.74599981307983</v>
       </c>
       <c r="G894" t="n">
-        <v>4.53858232498169</v>
+        <v>4.53858184814453</v>
       </c>
       <c r="H894" t="n">
         <v>111758</v>
@@ -26324,7 +26324,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G895" t="n">
-        <v>4.68585157394409</v>
+        <v>4.68585205078125</v>
       </c>
       <c r="H895" t="n">
         <v>288639</v>
@@ -36596,6 +36596,35 @@
         <v>418741</v>
       </c>
       <c r="I1249" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1250" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1250" t="n">
+        <v>3.39199995994568</v>
+      </c>
+      <c r="D1250" t="n">
+        <v>3.44799995422363</v>
+      </c>
+      <c r="E1250" t="n">
+        <v>3.35400009155273</v>
+      </c>
+      <c r="F1250" t="n">
+        <v>3.42199993133545</v>
+      </c>
+      <c r="G1250" t="n">
+        <v>3.42199993133545</v>
+      </c>
+      <c r="H1250" t="n">
+        <v>325739</v>
+      </c>
+      <c r="I1250" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ARIS.MI.xlsx
+++ b/data/ARIS.MI.xlsx
@@ -456,7 +456,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G3" t="n">
-        <v>9.34524440765381</v>
+        <v>9.34524345397949</v>
       </c>
       <c r="H3" t="n">
         <v>1460667</v>
@@ -485,7 +485,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G4" t="n">
-        <v>9.1745138168335</v>
+        <v>9.17451477050781</v>
       </c>
       <c r="H4" t="n">
         <v>732483</v>
@@ -543,7 +543,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G6" t="n">
-        <v>9.20147037506104</v>
+        <v>9.20146942138672</v>
       </c>
       <c r="H6" t="n">
         <v>260042</v>
@@ -572,7 +572,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G7" t="n">
-        <v>9.20147037506104</v>
+        <v>9.20146942138672</v>
       </c>
       <c r="H7" t="n">
         <v>279621</v>
@@ -601,7 +601,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G8" t="n">
-        <v>9.20147037506104</v>
+        <v>9.20146942138672</v>
       </c>
       <c r="H8" t="n">
         <v>197900</v>
@@ -630,7 +630,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G9" t="n">
-        <v>9.21944332122803</v>
+        <v>9.21944236755371</v>
       </c>
       <c r="H9" t="n">
         <v>203801</v>
@@ -659,7 +659,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G10" t="n">
-        <v>9.20147037506104</v>
+        <v>9.20146942138672</v>
       </c>
       <c r="H10" t="n">
         <v>122758</v>
@@ -717,7 +717,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G12" t="n">
-        <v>9.20147037506104</v>
+        <v>9.20146942138672</v>
       </c>
       <c r="H12" t="n">
         <v>105196</v>
@@ -746,7 +746,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G13" t="n">
-        <v>9.20147037506104</v>
+        <v>9.20146942138672</v>
       </c>
       <c r="H13" t="n">
         <v>85905</v>
@@ -775,7 +775,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G14" t="n">
-        <v>9.20147037506104</v>
+        <v>9.20146942138672</v>
       </c>
       <c r="H14" t="n">
         <v>198256</v>
@@ -804,7 +804,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G15" t="n">
-        <v>9.21944332122803</v>
+        <v>9.21944236755371</v>
       </c>
       <c r="H15" t="n">
         <v>184724</v>
@@ -833,7 +833,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G16" t="n">
-        <v>8.92291069030762</v>
+        <v>8.9229097366333</v>
       </c>
       <c r="H16" t="n">
         <v>312158</v>
@@ -891,7 +891,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G18" t="n">
-        <v>8.6353645324707</v>
+        <v>8.63536357879639</v>
       </c>
       <c r="H18" t="n">
         <v>319387</v>
@@ -920,7 +920,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G19" t="n">
-        <v>8.71623802185059</v>
+        <v>8.71623611450195</v>
       </c>
       <c r="H19" t="n">
         <v>172790</v>
@@ -949,7 +949,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G20" t="n">
-        <v>9.12958335876465</v>
+        <v>9.12958431243896</v>
       </c>
       <c r="H20" t="n">
         <v>431091</v>
@@ -1065,7 +1065,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G24" t="n">
-        <v>9.12958335876465</v>
+        <v>9.12958431243896</v>
       </c>
       <c r="H24" t="n">
         <v>61464</v>
@@ -1094,7 +1094,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G25" t="n">
-        <v>9.11161327362061</v>
+        <v>9.11161422729492</v>
       </c>
       <c r="H25" t="n">
         <v>29624</v>
@@ -1123,7 +1123,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G26" t="n">
-        <v>9.12958335876465</v>
+        <v>9.12958431243896</v>
       </c>
       <c r="H26" t="n">
         <v>53953</v>
@@ -1210,7 +1210,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G29" t="n">
-        <v>9.74061965942383</v>
+        <v>9.74062061309814</v>
       </c>
       <c r="H29" t="n">
         <v>87322</v>
@@ -1239,7 +1239,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G30" t="n">
-        <v>10.1180238723755</v>
+        <v>10.1180248260498</v>
       </c>
       <c r="H30" t="n">
         <v>401264</v>
@@ -1268,7 +1268,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G31" t="n">
-        <v>9.48901748657227</v>
+        <v>9.48901653289795</v>
       </c>
       <c r="H31" t="n">
         <v>328664</v>
@@ -1297,7 +1297,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G32" t="n">
-        <v>9.1745138168335</v>
+        <v>9.17451477050781</v>
       </c>
       <c r="H32" t="n">
         <v>405173</v>
@@ -1326,7 +1326,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G33" t="n">
-        <v>9.63279151916504</v>
+        <v>9.63278961181641</v>
       </c>
       <c r="H33" t="n">
         <v>261751</v>
@@ -1355,7 +1355,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G34" t="n">
-        <v>10.0191802978516</v>
+        <v>10.0191793441772</v>
       </c>
       <c r="H34" t="n">
         <v>509719</v>
@@ -1384,7 +1384,7 @@
         <v>10.9899997711182</v>
       </c>
       <c r="G35" t="n">
-        <v>9.87540721893311</v>
+        <v>9.87540626525879</v>
       </c>
       <c r="H35" t="n">
         <v>209128</v>
@@ -1413,7 +1413,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G36" t="n">
-        <v>10.1988973617554</v>
+        <v>10.1988964080811</v>
       </c>
       <c r="H36" t="n">
         <v>477707</v>
@@ -1442,7 +1442,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G37" t="n">
-        <v>10.1180238723755</v>
+        <v>10.1180248260498</v>
       </c>
       <c r="H37" t="n">
         <v>92776</v>
@@ -1500,7 +1500,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G39" t="n">
-        <v>9.62380409240723</v>
+        <v>9.62380599975586</v>
       </c>
       <c r="H39" t="n">
         <v>115964</v>
@@ -1529,7 +1529,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G40" t="n">
-        <v>9.67771911621094</v>
+        <v>9.67772006988525</v>
       </c>
       <c r="H40" t="n">
         <v>103333</v>
@@ -1587,7 +1587,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G42" t="n">
-        <v>9.10262775421143</v>
+        <v>9.10262680053711</v>
       </c>
       <c r="H42" t="n">
         <v>130467</v>
@@ -1616,7 +1616,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G43" t="n">
-        <v>9.1745138168335</v>
+        <v>9.17451477050781</v>
       </c>
       <c r="H43" t="n">
         <v>290667</v>
@@ -1645,7 +1645,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G44" t="n">
-        <v>9.12059879302979</v>
+        <v>9.1205997467041</v>
       </c>
       <c r="H44" t="n">
         <v>167591</v>
@@ -1703,7 +1703,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G46" t="n">
-        <v>9.20147037506104</v>
+        <v>9.20146942138672</v>
       </c>
       <c r="H46" t="n">
         <v>323983</v>
@@ -1732,7 +1732,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G47" t="n">
-        <v>9.34524440765381</v>
+        <v>9.34524345397949</v>
       </c>
       <c r="H47" t="n">
         <v>331892</v>
@@ -1761,7 +1761,7 @@
         <v>10.4899997711182</v>
       </c>
       <c r="G48" t="n">
-        <v>9.42611598968506</v>
+        <v>9.42611503601074</v>
       </c>
       <c r="H48" t="n">
         <v>67641</v>
@@ -1790,7 +1790,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G49" t="n">
-        <v>9.34524440765381</v>
+        <v>9.34524345397949</v>
       </c>
       <c r="H49" t="n">
         <v>164923</v>
@@ -1819,7 +1819,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G50" t="n">
-        <v>9.11161327362061</v>
+        <v>9.11161422729492</v>
       </c>
       <c r="H50" t="n">
         <v>253720</v>
@@ -1877,7 +1877,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G52" t="n">
-        <v>9.12958335876465</v>
+        <v>9.12958431243896</v>
       </c>
       <c r="H52" t="n">
         <v>73644</v>
@@ -1964,7 +1964,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G55" t="n">
-        <v>8.994797706604</v>
+        <v>8.99479675292969</v>
       </c>
       <c r="H55" t="n">
         <v>276782</v>
@@ -2022,7 +2022,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G57" t="n">
-        <v>9.10262775421143</v>
+        <v>9.10262680053711</v>
       </c>
       <c r="H57" t="n">
         <v>123193</v>
@@ -2051,7 +2051,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G58" t="n">
-        <v>8.994797706604</v>
+        <v>8.99479675292969</v>
       </c>
       <c r="H58" t="n">
         <v>253397</v>
@@ -2080,7 +2080,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G59" t="n">
-        <v>9.19248485565186</v>
+        <v>9.19248580932617</v>
       </c>
       <c r="H59" t="n">
         <v>486352</v>
@@ -2138,7 +2138,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G61" t="n">
-        <v>8.71623802185059</v>
+        <v>8.71623611450195</v>
       </c>
       <c r="H61" t="n">
         <v>224870</v>
@@ -2225,7 +2225,7 @@
         <v>8.75</v>
       </c>
       <c r="G64" t="n">
-        <v>7.86258554458618</v>
+        <v>7.86258506774902</v>
       </c>
       <c r="H64" t="n">
         <v>215027</v>
@@ -2283,7 +2283,7 @@
         <v>9.20499992370605</v>
       </c>
       <c r="G66" t="n">
-        <v>8.27143955230713</v>
+        <v>8.27143859863281</v>
       </c>
       <c r="H66" t="n">
         <v>126081</v>
@@ -2370,7 +2370,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G69" t="n">
-        <v>7.95244312286377</v>
+        <v>7.95244407653809</v>
       </c>
       <c r="H69" t="n">
         <v>230882</v>
@@ -2399,7 +2399,7 @@
         <v>7.875</v>
       </c>
       <c r="G70" t="n">
-        <v>7.07632684707642</v>
+        <v>7.07632637023926</v>
       </c>
       <c r="H70" t="n">
         <v>381529</v>
@@ -2428,7 +2428,7 @@
         <v>8</v>
       </c>
       <c r="G71" t="n">
-        <v>7.18864965438843</v>
+        <v>7.18864917755127</v>
       </c>
       <c r="H71" t="n">
         <v>192401</v>
@@ -2457,7 +2457,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G72" t="n">
-        <v>7.42228126525879</v>
+        <v>7.42228031158447</v>
       </c>
       <c r="H72" t="n">
         <v>235581</v>
@@ -2515,7 +2515,7 @@
         <v>8.3149995803833</v>
       </c>
       <c r="G74" t="n">
-        <v>7.47170209884644</v>
+        <v>7.47170162200928</v>
       </c>
       <c r="H74" t="n">
         <v>89965</v>
@@ -2602,7 +2602,7 @@
         <v>9.51500034332275</v>
       </c>
       <c r="G77" t="n">
-        <v>8.55000019073486</v>
+        <v>8.55000114440918</v>
       </c>
       <c r="H77" t="n">
         <v>369586</v>
@@ -2660,7 +2660,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G79" t="n">
-        <v>9.08465480804443</v>
+        <v>9.08465385437012</v>
       </c>
       <c r="H79" t="n">
         <v>663957</v>
@@ -2689,7 +2689,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G80" t="n">
-        <v>9.19248485565186</v>
+        <v>9.19248580932617</v>
       </c>
       <c r="H80" t="n">
         <v>1158996</v>
@@ -2718,7 +2718,7 @@
         <v>9.71500015258789</v>
       </c>
       <c r="G81" t="n">
-        <v>8.72971725463867</v>
+        <v>8.72971630096436</v>
       </c>
       <c r="H81" t="n">
         <v>221597</v>
@@ -2834,7 +2834,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G85" t="n">
-        <v>8.6443510055542</v>
+        <v>8.64435005187988</v>
       </c>
       <c r="H85" t="n">
         <v>93670</v>
@@ -2892,7 +2892,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G87" t="n">
-        <v>8.67130756378174</v>
+        <v>8.67130851745605</v>
       </c>
       <c r="H87" t="n">
         <v>120344</v>
@@ -2921,7 +2921,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G88" t="n">
-        <v>8.80609607696533</v>
+        <v>8.80609512329102</v>
       </c>
       <c r="H88" t="n">
         <v>104006</v>
@@ -2950,7 +2950,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G89" t="n">
-        <v>8.50057697296143</v>
+        <v>8.50057792663574</v>
       </c>
       <c r="H89" t="n">
         <v>95717</v>
@@ -3037,7 +3037,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G92" t="n">
-        <v>8.71623802185059</v>
+        <v>8.71623611450195</v>
       </c>
       <c r="H92" t="n">
         <v>223170</v>
@@ -3066,7 +3066,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G93" t="n">
-        <v>8.50057697296143</v>
+        <v>8.50057792663574</v>
       </c>
       <c r="H93" t="n">
         <v>181323</v>
@@ -3095,7 +3095,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G94" t="n">
-        <v>8.18607521057129</v>
+        <v>8.18607425689697</v>
       </c>
       <c r="H94" t="n">
         <v>173589</v>
@@ -3124,7 +3124,7 @@
         <v>9.25</v>
       </c>
       <c r="G95" t="n">
-        <v>8.31187534332275</v>
+        <v>8.31187629699707</v>
       </c>
       <c r="H95" t="n">
         <v>70088</v>
@@ -3182,7 +3182,7 @@
         <v>9.25</v>
       </c>
       <c r="G97" t="n">
-        <v>8.31187534332275</v>
+        <v>8.31187629699707</v>
       </c>
       <c r="H97" t="n">
         <v>77345</v>
@@ -3240,7 +3240,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G99" t="n">
-        <v>8.45564746856689</v>
+        <v>8.45564937591553</v>
       </c>
       <c r="H99" t="n">
         <v>126252</v>
@@ -3269,7 +3269,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G100" t="n">
-        <v>8.80609607696533</v>
+        <v>8.80609512329102</v>
       </c>
       <c r="H100" t="n">
         <v>249000</v>
@@ -3298,7 +3298,7 @@
         <v>9.75</v>
       </c>
       <c r="G101" t="n">
-        <v>8.7611665725708</v>
+        <v>8.76116752624512</v>
       </c>
       <c r="H101" t="n">
         <v>134667</v>
@@ -3327,7 +3327,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G102" t="n">
-        <v>8.5904369354248</v>
+        <v>8.59043598175049</v>
       </c>
       <c r="H102" t="n">
         <v>81506</v>
@@ -3356,7 +3356,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G103" t="n">
-        <v>8.71623802185059</v>
+        <v>8.71623611450195</v>
       </c>
       <c r="H103" t="n">
         <v>216807</v>
@@ -3385,7 +3385,7 @@
         <v>9.625</v>
       </c>
       <c r="G104" t="n">
-        <v>8.64884281158447</v>
+        <v>8.64884376525879</v>
       </c>
       <c r="H104" t="n">
         <v>109168</v>
@@ -3443,7 +3443,7 @@
         <v>9.71500015258789</v>
       </c>
       <c r="G106" t="n">
-        <v>8.72971725463867</v>
+        <v>8.72971630096436</v>
       </c>
       <c r="H106" t="n">
         <v>81637</v>
@@ -3472,7 +3472,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G107" t="n">
-        <v>8.67130756378174</v>
+        <v>8.67130851745605</v>
       </c>
       <c r="H107" t="n">
         <v>107921</v>
@@ -3530,7 +3530,7 @@
         <v>9</v>
       </c>
       <c r="G109" t="n">
-        <v>8.08722972869873</v>
+        <v>8.08723068237305</v>
       </c>
       <c r="H109" t="n">
         <v>151306</v>
@@ -3559,7 +3559,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G110" t="n">
-        <v>7.89852809906006</v>
+        <v>7.89852857589722</v>
       </c>
       <c r="H110" t="n">
         <v>136469</v>
@@ -3617,7 +3617,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G112" t="n">
-        <v>8.10520172119141</v>
+        <v>8.10520267486572</v>
       </c>
       <c r="H112" t="n">
         <v>245680</v>
@@ -3646,7 +3646,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G113" t="n">
-        <v>7.99737119674683</v>
+        <v>7.99737215042114</v>
       </c>
       <c r="H113" t="n">
         <v>164165</v>
@@ -3704,7 +3704,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G115" t="n">
-        <v>7.80867052078247</v>
+        <v>7.80867004394531</v>
       </c>
       <c r="H115" t="n">
         <v>87012</v>
@@ -3733,7 +3733,7 @@
         <v>9.02499961853027</v>
       </c>
       <c r="G116" t="n">
-        <v>8.109694480896</v>
+        <v>8.10969543457031</v>
       </c>
       <c r="H116" t="n">
         <v>88735</v>
@@ -3762,7 +3762,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G117" t="n">
-        <v>8.32086277008057</v>
+        <v>8.32086181640625</v>
       </c>
       <c r="H117" t="n">
         <v>146034</v>
@@ -3849,7 +3849,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>8.80609607696533</v>
+        <v>8.80609512329102</v>
       </c>
       <c r="H120" t="n">
         <v>269484</v>
@@ -4023,7 +4023,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G126" t="n">
-        <v>8.93144989013672</v>
+        <v>8.9314489364624</v>
       </c>
       <c r="H126" t="n">
         <v>138520</v>
@@ -4052,7 +4052,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G127" t="n">
-        <v>9.25042915344238</v>
+        <v>9.2504301071167</v>
       </c>
       <c r="H127" t="n">
         <v>154830</v>
@@ -4110,7 +4110,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G129" t="n">
-        <v>9.51472663879395</v>
+        <v>9.51472759246826</v>
       </c>
       <c r="H129" t="n">
         <v>242971</v>
@@ -4168,7 +4168,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G131" t="n">
-        <v>9.20486164093018</v>
+        <v>9.20486068725586</v>
       </c>
       <c r="H131" t="n">
         <v>105012</v>
@@ -4197,7 +4197,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G132" t="n">
-        <v>9.2413158416748</v>
+        <v>9.24131679534912</v>
       </c>
       <c r="H132" t="n">
         <v>39938</v>
@@ -4226,7 +4226,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G133" t="n">
-        <v>9.3051118850708</v>
+        <v>9.30511283874512</v>
       </c>
       <c r="H133" t="n">
         <v>80187</v>
@@ -4255,7 +4255,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G134" t="n">
-        <v>9.2413158416748</v>
+        <v>9.24131679534912</v>
       </c>
       <c r="H134" t="n">
         <v>32325</v>
@@ -4284,7 +4284,7 @@
         <v>10.25</v>
       </c>
       <c r="G135" t="n">
-        <v>9.34156608581543</v>
+        <v>9.34156703948975</v>
       </c>
       <c r="H135" t="n">
         <v>52292</v>
@@ -4429,7 +4429,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G140" t="n">
-        <v>7.95628023147583</v>
+        <v>7.95628118515015</v>
       </c>
       <c r="H140" t="n">
         <v>163728</v>
@@ -4487,7 +4487,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G142" t="n">
-        <v>7.61907196044922</v>
+        <v>7.61907291412354</v>
       </c>
       <c r="H142" t="n">
         <v>67512</v>
@@ -4516,7 +4516,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G143" t="n">
-        <v>7.73755121231079</v>
+        <v>7.73755073547363</v>
       </c>
       <c r="H143" t="n">
         <v>68881</v>
@@ -4574,7 +4574,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G145" t="n">
-        <v>7.47325325012207</v>
+        <v>7.47325277328491</v>
       </c>
       <c r="H145" t="n">
         <v>33799</v>
@@ -4603,7 +4603,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G146" t="n">
-        <v>7.34566164016724</v>
+        <v>7.34566211700439</v>
       </c>
       <c r="H146" t="n">
         <v>105071</v>
@@ -4632,7 +4632,7 @@
         <v>7.50500011444092</v>
       </c>
       <c r="G147" t="n">
-        <v>6.8398494720459</v>
+        <v>6.83984994888306</v>
       </c>
       <c r="H147" t="n">
         <v>173369</v>
@@ -4748,7 +4748,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G151" t="n">
-        <v>7.02668142318726</v>
+        <v>7.0266809463501</v>
       </c>
       <c r="H151" t="n">
         <v>83909</v>
@@ -4777,7 +4777,7 @@
         <v>7.81500005722046</v>
       </c>
       <c r="G152" t="n">
-        <v>7.12237453460693</v>
+        <v>7.12237548828125</v>
       </c>
       <c r="H152" t="n">
         <v>173417</v>
@@ -4922,7 +4922,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G157" t="n">
-        <v>6.78061008453369</v>
+        <v>6.78061056137085</v>
       </c>
       <c r="H157" t="n">
         <v>109900</v>
@@ -4951,7 +4951,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G158" t="n">
-        <v>6.926429271698</v>
+        <v>6.92642974853516</v>
       </c>
       <c r="H158" t="n">
         <v>58691</v>
@@ -5067,7 +5067,7 @@
         <v>7.05499982833862</v>
       </c>
       <c r="G162" t="n">
-        <v>6.42973136901855</v>
+        <v>6.42973184585571</v>
       </c>
       <c r="H162" t="n">
         <v>80746</v>
@@ -5096,7 +5096,7 @@
         <v>7.31500005722046</v>
       </c>
       <c r="G163" t="n">
-        <v>6.66668844223022</v>
+        <v>6.66668891906738</v>
       </c>
       <c r="H163" t="n">
         <v>63073</v>
@@ -5125,7 +5125,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G164" t="n">
-        <v>6.88086175918579</v>
+        <v>6.88086128234863</v>
       </c>
       <c r="H164" t="n">
         <v>59880</v>
@@ -5154,7 +5154,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G165" t="n">
-        <v>6.99478340148926</v>
+        <v>6.9947829246521</v>
       </c>
       <c r="H165" t="n">
         <v>39622</v>
@@ -5183,7 +5183,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G166" t="n">
-        <v>6.96288442611694</v>
+        <v>6.9628849029541</v>
       </c>
       <c r="H166" t="n">
         <v>25056</v>
@@ -5212,7 +5212,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G167" t="n">
-        <v>6.96288442611694</v>
+        <v>6.9628849029541</v>
       </c>
       <c r="H167" t="n">
         <v>115212</v>
@@ -5241,7 +5241,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G168" t="n">
-        <v>6.99478340148926</v>
+        <v>6.9947829246521</v>
       </c>
       <c r="H168" t="n">
         <v>116551</v>
@@ -5270,7 +5270,7 @@
         <v>7.72499990463257</v>
       </c>
       <c r="G169" t="n">
-        <v>7.04035186767578</v>
+        <v>7.04035091400146</v>
       </c>
       <c r="H169" t="n">
         <v>97576</v>
@@ -5328,7 +5328,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G171" t="n">
-        <v>6.99478340148926</v>
+        <v>6.9947829246521</v>
       </c>
       <c r="H171" t="n">
         <v>62027</v>
@@ -5415,7 +5415,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G174" t="n">
-        <v>7.47325325012207</v>
+        <v>7.47325277328491</v>
       </c>
       <c r="H174" t="n">
         <v>32018</v>
@@ -5444,7 +5444,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G175" t="n">
-        <v>7.61907196044922</v>
+        <v>7.61907291412354</v>
       </c>
       <c r="H175" t="n">
         <v>67391</v>
@@ -5502,7 +5502,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G177" t="n">
-        <v>7.46413946151733</v>
+        <v>7.46413898468018</v>
       </c>
       <c r="H177" t="n">
         <v>103642</v>
@@ -5560,7 +5560,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G179" t="n">
-        <v>7.33199024200439</v>
+        <v>7.33199071884155</v>
       </c>
       <c r="H179" t="n">
         <v>88870</v>
@@ -5589,7 +5589,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G180" t="n">
-        <v>7.24996709823608</v>
+        <v>7.24996662139893</v>
       </c>
       <c r="H180" t="n">
         <v>63885</v>
@@ -5618,7 +5618,7 @@
         <v>8</v>
       </c>
       <c r="G181" t="n">
-        <v>7.29097938537598</v>
+        <v>7.29097890853882</v>
       </c>
       <c r="H181" t="n">
         <v>44729</v>
@@ -5647,7 +5647,7 @@
         <v>8</v>
       </c>
       <c r="G182" t="n">
-        <v>7.29097938537598</v>
+        <v>7.29097890853882</v>
       </c>
       <c r="H182" t="n">
         <v>68137</v>
@@ -5705,7 +5705,7 @@
         <v>8</v>
       </c>
       <c r="G184" t="n">
-        <v>7.29097938537598</v>
+        <v>7.29097890853882</v>
       </c>
       <c r="H184" t="n">
         <v>53674</v>
@@ -5734,7 +5734,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G185" t="n">
-        <v>7.05402231216431</v>
+        <v>7.05402183532715</v>
       </c>
       <c r="H185" t="n">
         <v>89502</v>
@@ -5763,7 +5763,7 @@
         <v>8</v>
       </c>
       <c r="G186" t="n">
-        <v>7.29097938537598</v>
+        <v>7.29097890853882</v>
       </c>
       <c r="H186" t="n">
         <v>98582</v>
@@ -5792,7 +5792,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G187" t="n">
-        <v>7.30009317398071</v>
+        <v>7.30009269714355</v>
       </c>
       <c r="H187" t="n">
         <v>50930</v>
@@ -5850,7 +5850,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G189" t="n">
-        <v>7.2135124206543</v>
+        <v>7.21351194381714</v>
       </c>
       <c r="H189" t="n">
         <v>58048</v>
@@ -5879,7 +5879,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G190" t="n">
-        <v>7.11781787872314</v>
+        <v>7.1178183555603</v>
       </c>
       <c r="H190" t="n">
         <v>29579</v>
@@ -5908,7 +5908,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G191" t="n">
-        <v>6.96288442611694</v>
+        <v>6.9628849029541</v>
       </c>
       <c r="H191" t="n">
         <v>64057</v>
@@ -6024,7 +6024,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G195" t="n">
-        <v>7.00845336914062</v>
+        <v>7.00845384597778</v>
       </c>
       <c r="H195" t="n">
         <v>142516</v>
@@ -6082,7 +6082,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G197" t="n">
-        <v>6.926429271698</v>
+        <v>6.92642974853516</v>
       </c>
       <c r="H197" t="n">
         <v>94339</v>
@@ -6140,7 +6140,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G199" t="n">
-        <v>6.42517566680908</v>
+        <v>6.42517518997192</v>
       </c>
       <c r="H199" t="n">
         <v>115768</v>
@@ -6198,7 +6198,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G201" t="n">
-        <v>6.63023376464844</v>
+        <v>6.6302342414856</v>
       </c>
       <c r="H201" t="n">
         <v>127295</v>
@@ -6227,7 +6227,7 @@
         <v>7.52500009536743</v>
       </c>
       <c r="G202" t="n">
-        <v>6.85807704925537</v>
+        <v>6.85807752609253</v>
       </c>
       <c r="H202" t="n">
         <v>80911</v>
@@ -6256,7 +6256,7 @@
         <v>7.75</v>
       </c>
       <c r="G203" t="n">
-        <v>7.06313610076904</v>
+        <v>7.06313562393188</v>
       </c>
       <c r="H203" t="n">
         <v>74023</v>
@@ -6285,7 +6285,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G204" t="n">
-        <v>6.83073568344116</v>
+        <v>6.83073616027832</v>
       </c>
       <c r="H204" t="n">
         <v>55532</v>
@@ -6314,7 +6314,7 @@
         <v>7.33500003814697</v>
       </c>
       <c r="G205" t="n">
-        <v>6.6849160194397</v>
+        <v>6.68491649627686</v>
       </c>
       <c r="H205" t="n">
         <v>69663</v>
@@ -6343,7 +6343,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G206" t="n">
-        <v>6.69858694076538</v>
+        <v>6.69858646392822</v>
       </c>
       <c r="H206" t="n">
         <v>115365</v>
@@ -6372,7 +6372,7 @@
         <v>8.46500015258789</v>
       </c>
       <c r="G207" t="n">
-        <v>7.71476745605469</v>
+        <v>7.71476793289185</v>
       </c>
       <c r="H207" t="n">
         <v>667919</v>
@@ -6401,7 +6401,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G208" t="n">
-        <v>7.5552773475647</v>
+        <v>7.55527687072754</v>
       </c>
       <c r="H208" t="n">
         <v>323484</v>
@@ -6459,7 +6459,7 @@
         <v>8.40499973297119</v>
       </c>
       <c r="G210" t="n">
-        <v>7.66008424758911</v>
+        <v>7.66008520126343</v>
       </c>
       <c r="H210" t="n">
         <v>162822</v>
@@ -6517,7 +6517,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G212" t="n">
-        <v>7.75577926635742</v>
+        <v>7.75577831268311</v>
       </c>
       <c r="H212" t="n">
         <v>149734</v>
@@ -6546,7 +6546,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G213" t="n">
-        <v>7.828688621521</v>
+        <v>7.82868957519531</v>
       </c>
       <c r="H213" t="n">
         <v>267292</v>
@@ -6575,7 +6575,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G214" t="n">
-        <v>7.828688621521</v>
+        <v>7.82868957519531</v>
       </c>
       <c r="H214" t="n">
         <v>252704</v>
@@ -6604,7 +6604,7 @@
         <v>8.48499965667725</v>
       </c>
       <c r="G215" t="n">
-        <v>7.73299360275269</v>
+        <v>7.73299407958984</v>
       </c>
       <c r="H215" t="n">
         <v>190999</v>
@@ -6662,7 +6662,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G217" t="n">
-        <v>7.93805265426636</v>
+        <v>7.93805360794067</v>
       </c>
       <c r="H217" t="n">
         <v>247020</v>
@@ -6691,7 +6691,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G218" t="n">
-        <v>8.0200777053833</v>
+        <v>8.02007675170898</v>
       </c>
       <c r="H218" t="n">
         <v>179237</v>
@@ -6749,7 +6749,7 @@
         <v>9.03499984741211</v>
       </c>
       <c r="G220" t="n">
-        <v>8.23424911499023</v>
+        <v>8.23425006866455</v>
       </c>
       <c r="H220" t="n">
         <v>263459</v>
@@ -6778,7 +6778,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G221" t="n">
-        <v>8.19323825836182</v>
+        <v>8.19323635101318</v>
       </c>
       <c r="H221" t="n">
         <v>194602</v>
@@ -6836,7 +6836,7 @@
         <v>8.86499977111816</v>
       </c>
       <c r="G223" t="n">
-        <v>8.07931613922119</v>
+        <v>8.07931518554688</v>
       </c>
       <c r="H223" t="n">
         <v>111621</v>
@@ -6865,7 +6865,7 @@
         <v>8.79500007629395</v>
       </c>
       <c r="G224" t="n">
-        <v>8.01552104949951</v>
+        <v>8.0155200958252</v>
       </c>
       <c r="H224" t="n">
         <v>122024</v>
@@ -6923,7 +6923,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G226" t="n">
-        <v>7.65552759170532</v>
+        <v>7.65552806854248</v>
       </c>
       <c r="H226" t="n">
         <v>242848</v>
@@ -6981,7 +6981,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G228" t="n">
-        <v>7.71932411193848</v>
+        <v>7.71932315826416</v>
       </c>
       <c r="H228" t="n">
         <v>240482</v>
@@ -7155,7 +7155,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G234" t="n">
-        <v>7.85602903366089</v>
+        <v>7.85602998733521</v>
       </c>
       <c r="H234" t="n">
         <v>185968</v>
@@ -7184,7 +7184,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G235" t="n">
-        <v>7.8195743560791</v>
+        <v>7.81957483291626</v>
       </c>
       <c r="H235" t="n">
         <v>126055</v>
@@ -7213,7 +7213,7 @@
         <v>8.59500026702881</v>
       </c>
       <c r="G236" t="n">
-        <v>7.83324670791626</v>
+        <v>7.83324480056763</v>
       </c>
       <c r="H236" t="n">
         <v>75722</v>
@@ -7242,7 +7242,7 @@
         <v>8.63500022888184</v>
       </c>
       <c r="G237" t="n">
-        <v>7.86970090866089</v>
+        <v>7.86969995498657</v>
       </c>
       <c r="H237" t="n">
         <v>68684</v>
@@ -7271,7 +7271,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G238" t="n">
-        <v>7.86514377593994</v>
+        <v>7.86514329910278</v>
       </c>
       <c r="H238" t="n">
         <v>98511</v>
@@ -7329,7 +7329,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G240" t="n">
-        <v>7.61907196044922</v>
+        <v>7.61907291412354</v>
       </c>
       <c r="H240" t="n">
         <v>242480</v>
@@ -7416,7 +7416,7 @@
         <v>8.29500007629395</v>
       </c>
       <c r="G243" t="n">
-        <v>7.55983304977417</v>
+        <v>7.55983400344849</v>
       </c>
       <c r="H243" t="n">
         <v>179111</v>
@@ -7474,7 +7474,7 @@
         <v>8.15499973297119</v>
       </c>
       <c r="G245" t="n">
-        <v>7.43224096298218</v>
+        <v>7.43224191665649</v>
       </c>
       <c r="H245" t="n">
         <v>95884</v>
@@ -7532,7 +7532,7 @@
         <v>8.5649995803833</v>
       </c>
       <c r="G247" t="n">
-        <v>7.80590343475342</v>
+        <v>7.80590391159058</v>
       </c>
       <c r="H247" t="n">
         <v>190341</v>
@@ -7561,7 +7561,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G248" t="n">
-        <v>7.73755121231079</v>
+        <v>7.73755073547363</v>
       </c>
       <c r="H248" t="n">
         <v>79342</v>
@@ -7590,7 +7590,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G249" t="n">
-        <v>7.828688621521</v>
+        <v>7.82868957519531</v>
       </c>
       <c r="H249" t="n">
         <v>109003</v>
@@ -7619,7 +7619,7 @@
         <v>8.44499969482422</v>
       </c>
       <c r="G250" t="n">
-        <v>7.69653940200806</v>
+        <v>7.69653987884521</v>
       </c>
       <c r="H250" t="n">
         <v>65821</v>
@@ -7648,7 +7648,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G251" t="n">
-        <v>7.76489305496216</v>
+        <v>7.76489353179932</v>
       </c>
       <c r="H251" t="n">
         <v>81589</v>
@@ -7677,7 +7677,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G252" t="n">
-        <v>7.87425851821899</v>
+        <v>7.87425756454468</v>
       </c>
       <c r="H252" t="n">
         <v>52613</v>
@@ -7735,7 +7735,7 @@
         <v>8.64500045776367</v>
       </c>
       <c r="G254" t="n">
-        <v>7.87881374359131</v>
+        <v>7.87881517410278</v>
       </c>
       <c r="H254" t="n">
         <v>56212</v>
@@ -7851,7 +7851,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G258" t="n">
-        <v>8.34817028045654</v>
+        <v>8.34817123413086</v>
       </c>
       <c r="H258" t="n">
         <v>65591</v>
@@ -7967,7 +7967,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G262" t="n">
-        <v>8.61246871948242</v>
+        <v>8.61246776580811</v>
       </c>
       <c r="H262" t="n">
         <v>78088</v>
@@ -7996,7 +7996,7 @@
         <v>9.5</v>
       </c>
       <c r="G263" t="n">
-        <v>8.65803718566895</v>
+        <v>8.65803813934326</v>
       </c>
       <c r="H263" t="n">
         <v>120885</v>
@@ -8054,7 +8054,7 @@
         <v>9.23499965667725</v>
       </c>
       <c r="G265" t="n">
-        <v>8.41652393341064</v>
+        <v>8.41652297973633</v>
       </c>
       <c r="H265" t="n">
         <v>63237</v>
@@ -8083,7 +8083,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G266" t="n">
-        <v>8.4438648223877</v>
+        <v>8.44386577606201</v>
       </c>
       <c r="H266" t="n">
         <v>56513</v>
@@ -8112,7 +8112,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G267" t="n">
-        <v>8.61246871948242</v>
+        <v>8.61246776580811</v>
       </c>
       <c r="H267" t="n">
         <v>84891</v>
@@ -8141,7 +8141,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G268" t="n">
-        <v>8.42108058929443</v>
+        <v>8.42107963562012</v>
       </c>
       <c r="H268" t="n">
         <v>38362</v>
@@ -8170,7 +8170,7 @@
         <v>9.5</v>
       </c>
       <c r="G269" t="n">
-        <v>8.65803718566895</v>
+        <v>8.65803813934326</v>
       </c>
       <c r="H269" t="n">
         <v>49713</v>
@@ -8199,7 +8199,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G270" t="n">
-        <v>8.61246871948242</v>
+        <v>8.61246776580811</v>
       </c>
       <c r="H270" t="n">
         <v>91141</v>
@@ -8228,7 +8228,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G271" t="n">
-        <v>8.47576332092285</v>
+        <v>8.47576236724854</v>
       </c>
       <c r="H271" t="n">
         <v>166452</v>
@@ -8286,7 +8286,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G273" t="n">
-        <v>8.40285396575928</v>
+        <v>8.40285301208496</v>
       </c>
       <c r="H273" t="n">
         <v>52732</v>
@@ -8315,7 +8315,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G274" t="n">
-        <v>8.28437519073486</v>
+        <v>8.28437614440918</v>
       </c>
       <c r="H274" t="n">
         <v>67078</v>
@@ -8431,7 +8431,7 @@
         <v>9.66499996185303</v>
       </c>
       <c r="G278" t="n">
-        <v>8.8084135055542</v>
+        <v>8.80841445922852</v>
       </c>
       <c r="H278" t="n">
         <v>41058</v>
@@ -8489,7 +8489,7 @@
         <v>9.40499973297119</v>
       </c>
       <c r="G280" t="n">
-        <v>8.57145595550537</v>
+        <v>8.57145690917969</v>
       </c>
       <c r="H280" t="n">
         <v>67802</v>
@@ -8518,7 +8518,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G281" t="n">
-        <v>8.76740264892578</v>
+        <v>8.76740169525146</v>
       </c>
       <c r="H281" t="n">
         <v>53938</v>
@@ -8576,7 +8576,7 @@
         <v>9.98499965667725</v>
       </c>
       <c r="G283" t="n">
-        <v>9.10005283355713</v>
+        <v>9.10005187988281</v>
       </c>
       <c r="H283" t="n">
         <v>197501</v>
@@ -8750,7 +8750,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G289" t="n">
-        <v>8.84031200408936</v>
+        <v>8.84031105041504</v>
       </c>
       <c r="H289" t="n">
         <v>85842</v>
@@ -8895,7 +8895,7 @@
         <v>9.5</v>
       </c>
       <c r="G294" t="n">
-        <v>8.65803718566895</v>
+        <v>8.65803813934326</v>
       </c>
       <c r="H294" t="n">
         <v>186325</v>
@@ -9011,7 +9011,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G298" t="n">
-        <v>9.04992771148682</v>
+        <v>9.0499267578125</v>
       </c>
       <c r="H298" t="n">
         <v>175620</v>
@@ -9040,7 +9040,7 @@
         <v>9.875</v>
       </c>
       <c r="G299" t="n">
-        <v>8.99980163574219</v>
+        <v>8.9998025894165</v>
       </c>
       <c r="H299" t="n">
         <v>71056</v>
@@ -9214,7 +9214,7 @@
         <v>9.51500034332275</v>
       </c>
       <c r="G305" t="n">
-        <v>8.67170810699463</v>
+        <v>8.67170906066895</v>
       </c>
       <c r="H305" t="n">
         <v>74235</v>
@@ -9243,7 +9243,7 @@
         <v>9.57499980926514</v>
       </c>
       <c r="G306" t="n">
-        <v>8.72639083862305</v>
+        <v>8.72638988494873</v>
       </c>
       <c r="H306" t="n">
         <v>170795</v>
@@ -9272,7 +9272,7 @@
         <v>9.66499996185303</v>
       </c>
       <c r="G307" t="n">
-        <v>8.8084135055542</v>
+        <v>8.80841445922852</v>
       </c>
       <c r="H307" t="n">
         <v>88814</v>
@@ -9359,7 +9359,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G310" t="n">
-        <v>8.71272087097168</v>
+        <v>8.71271991729736</v>
       </c>
       <c r="H310" t="n">
         <v>71168</v>
@@ -9446,7 +9446,7 @@
         <v>9.86499977111816</v>
       </c>
       <c r="G313" t="n">
-        <v>8.99068832397461</v>
+        <v>8.99068737030029</v>
       </c>
       <c r="H313" t="n">
         <v>95525</v>
@@ -9475,7 +9475,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G314" t="n">
-        <v>8.93144989013672</v>
+        <v>8.9314489364624</v>
       </c>
       <c r="H314" t="n">
         <v>79734</v>
@@ -9562,7 +9562,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G317" t="n">
-        <v>8.4438648223877</v>
+        <v>8.44386577606201</v>
       </c>
       <c r="H317" t="n">
         <v>158286</v>
@@ -9620,7 +9620,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G319" t="n">
-        <v>8.10210132598877</v>
+        <v>8.10210037231445</v>
       </c>
       <c r="H319" t="n">
         <v>152972</v>
@@ -9707,7 +9707,7 @@
         <v>9.23499965667725</v>
       </c>
       <c r="G322" t="n">
-        <v>8.41652393341064</v>
+        <v>8.41652297973633</v>
       </c>
       <c r="H322" t="n">
         <v>57007</v>
@@ -9736,7 +9736,7 @@
         <v>9.125</v>
       </c>
       <c r="G323" t="n">
-        <v>8.31627368927002</v>
+        <v>8.3162727355957</v>
       </c>
       <c r="H323" t="n">
         <v>96023</v>
@@ -9765,7 +9765,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G324" t="n">
-        <v>8.23880481719971</v>
+        <v>8.23880577087402</v>
       </c>
       <c r="H324" t="n">
         <v>125245</v>
@@ -9794,7 +9794,7 @@
         <v>9.6850004196167</v>
       </c>
       <c r="G325" t="n">
-        <v>8.82664203643799</v>
+        <v>8.82664108276367</v>
       </c>
       <c r="H325" t="n">
         <v>499802</v>
@@ -9852,7 +9852,7 @@
         <v>9.64500045776367</v>
       </c>
       <c r="G327" t="n">
-        <v>8.79018592834473</v>
+        <v>8.79018688201904</v>
       </c>
       <c r="H327" t="n">
         <v>201564</v>
@@ -9968,7 +9968,7 @@
         <v>9.58500003814697</v>
       </c>
       <c r="G331" t="n">
-        <v>8.73550415039062</v>
+        <v>8.73550510406494</v>
       </c>
       <c r="H331" t="n">
         <v>128694</v>
@@ -10084,7 +10084,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G335" t="n">
-        <v>8.48487758636475</v>
+        <v>8.48487663269043</v>
       </c>
       <c r="H335" t="n">
         <v>124173</v>
@@ -10200,7 +10200,7 @@
         <v>9.36499977111816</v>
       </c>
       <c r="G339" t="n">
-        <v>8.53500175476074</v>
+        <v>8.53500080108643</v>
       </c>
       <c r="H339" t="n">
         <v>78975</v>
@@ -10258,7 +10258,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G341" t="n">
-        <v>8.42108058929443</v>
+        <v>8.42107963562012</v>
       </c>
       <c r="H341" t="n">
         <v>61904</v>
@@ -10316,7 +10316,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G343" t="n">
-        <v>8.53955936431885</v>
+        <v>8.53955841064453</v>
       </c>
       <c r="H343" t="n">
         <v>356528</v>
@@ -10345,7 +10345,7 @@
         <v>9.57499980926514</v>
       </c>
       <c r="G344" t="n">
-        <v>8.72639083862305</v>
+        <v>8.72638988494873</v>
       </c>
       <c r="H344" t="n">
         <v>48723</v>
@@ -10403,7 +10403,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G346" t="n">
-        <v>9.25042915344238</v>
+        <v>9.2504301071167</v>
       </c>
       <c r="H346" t="n">
         <v>231979</v>
@@ -10490,7 +10490,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G349" t="n">
-        <v>9.1866340637207</v>
+        <v>9.18663311004639</v>
       </c>
       <c r="H349" t="n">
         <v>120697</v>
@@ -10635,7 +10635,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G354" t="n">
-        <v>9.02258586883545</v>
+        <v>9.02258682250977</v>
       </c>
       <c r="H354" t="n">
         <v>58371</v>
@@ -10664,7 +10664,7 @@
         <v>9.88500022888184</v>
       </c>
       <c r="G355" t="n">
-        <v>9.00891494750977</v>
+        <v>9.00891590118408</v>
       </c>
       <c r="H355" t="n">
         <v>123367</v>
@@ -10693,7 +10693,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G356" t="n">
-        <v>9.02258586883545</v>
+        <v>9.02258682250977</v>
       </c>
       <c r="H356" t="n">
         <v>51175</v>
@@ -10722,7 +10722,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G357" t="n">
-        <v>9.16840744018555</v>
+        <v>9.16840648651123</v>
       </c>
       <c r="H357" t="n">
         <v>43978</v>
@@ -10751,7 +10751,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G358" t="n">
-        <v>9.46915912628174</v>
+        <v>9.46916007995605</v>
       </c>
       <c r="H358" t="n">
         <v>119140</v>
@@ -10780,7 +10780,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G359" t="n">
-        <v>9.66966152191162</v>
+        <v>9.66965961456299</v>
       </c>
       <c r="H359" t="n">
         <v>147204</v>
@@ -10809,7 +10809,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G360" t="n">
-        <v>9.50561428070068</v>
+        <v>9.50561332702637</v>
       </c>
       <c r="H360" t="n">
         <v>54614</v>
@@ -10954,7 +10954,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G365" t="n">
-        <v>9.33245277404785</v>
+        <v>9.33245182037354</v>
       </c>
       <c r="H365" t="n">
         <v>135405</v>
@@ -10983,7 +10983,7 @@
         <v>9.83500003814697</v>
       </c>
       <c r="G366" t="n">
-        <v>8.96334743499756</v>
+        <v>8.96334838867188</v>
       </c>
       <c r="H366" t="n">
         <v>250182</v>
@@ -11070,7 +11070,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G369" t="n">
-        <v>8.66715240478516</v>
+        <v>8.66715145111084</v>
       </c>
       <c r="H369" t="n">
         <v>180228</v>
@@ -11099,7 +11099,7 @@
         <v>9.40499973297119</v>
       </c>
       <c r="G370" t="n">
-        <v>8.57145595550537</v>
+        <v>8.57145690917969</v>
       </c>
       <c r="H370" t="n">
         <v>122944</v>
@@ -11157,7 +11157,7 @@
         <v>9.5</v>
       </c>
       <c r="G372" t="n">
-        <v>8.65803718566895</v>
+        <v>8.65803813934326</v>
       </c>
       <c r="H372" t="n">
         <v>99284</v>
@@ -11186,7 +11186,7 @@
         <v>9.65499973297119</v>
       </c>
       <c r="G373" t="n">
-        <v>8.7992992401123</v>
+        <v>8.79930019378662</v>
       </c>
       <c r="H373" t="n">
         <v>110462</v>
@@ -11215,7 +11215,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G374" t="n">
-        <v>9.10461044311523</v>
+        <v>9.10460948944092</v>
       </c>
       <c r="H374" t="n">
         <v>180858</v>
@@ -11331,7 +11331,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G378" t="n">
-        <v>9.09549522399902</v>
+        <v>9.09549617767334</v>
       </c>
       <c r="H378" t="n">
         <v>71656</v>
@@ -11476,7 +11476,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G383" t="n">
-        <v>9.61260032653809</v>
+        <v>9.6126012802124</v>
       </c>
       <c r="H383" t="n">
         <v>186379</v>
@@ -11534,7 +11534,7 @@
         <v>10.25</v>
       </c>
       <c r="G385" t="n">
-        <v>9.46485614776611</v>
+        <v>9.46485710144043</v>
       </c>
       <c r="H385" t="n">
         <v>63321</v>
@@ -11621,7 +11621,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G388" t="n">
-        <v>9.63106918334961</v>
+        <v>9.63106822967529</v>
       </c>
       <c r="H388" t="n">
         <v>137120</v>
@@ -11650,7 +11650,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G389" t="n">
-        <v>9.64030170440674</v>
+        <v>9.64030265808105</v>
       </c>
       <c r="H389" t="n">
         <v>168078</v>
@@ -11737,7 +11737,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G392" t="n">
-        <v>9.64030170440674</v>
+        <v>9.64030265808105</v>
       </c>
       <c r="H392" t="n">
         <v>109538</v>
@@ -11766,7 +11766,7 @@
         <v>10.5</v>
       </c>
       <c r="G393" t="n">
-        <v>9.69570636749268</v>
+        <v>9.69570732116699</v>
       </c>
       <c r="H393" t="n">
         <v>63889</v>
@@ -11824,7 +11824,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G395" t="n">
-        <v>9.66800403594971</v>
+        <v>9.66800498962402</v>
       </c>
       <c r="H395" t="n">
         <v>79788</v>
@@ -11882,7 +11882,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G397" t="n">
-        <v>9.56643009185791</v>
+        <v>9.56642913818359</v>
       </c>
       <c r="H397" t="n">
         <v>124190</v>
@@ -11940,7 +11940,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G399" t="n">
-        <v>9.34481334686279</v>
+        <v>9.34481430053711</v>
       </c>
       <c r="H399" t="n">
         <v>45265</v>
@@ -11969,7 +11969,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G400" t="n">
-        <v>9.18783664703369</v>
+        <v>9.18783569335938</v>
       </c>
       <c r="H400" t="n">
         <v>64703</v>
@@ -11998,7 +11998,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G401" t="n">
-        <v>9.04932689666748</v>
+        <v>9.04932594299316</v>
       </c>
       <c r="H401" t="n">
         <v>96905</v>
@@ -12056,7 +12056,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G403" t="n">
-        <v>8.79539012908936</v>
+        <v>8.79539108276367</v>
       </c>
       <c r="H403" t="n">
         <v>80618</v>
@@ -12085,7 +12085,7 @@
         <v>9.36499977111816</v>
       </c>
       <c r="G404" t="n">
-        <v>8.6476469039917</v>
+        <v>8.64764595031738</v>
       </c>
       <c r="H404" t="n">
         <v>93583</v>
@@ -12114,7 +12114,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G405" t="n">
-        <v>8.58762645721436</v>
+        <v>8.58762550354004</v>
       </c>
       <c r="H405" t="n">
         <v>464509</v>
@@ -12143,7 +12143,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G406" t="n">
-        <v>8.80000877380371</v>
+        <v>8.80000782012939</v>
       </c>
       <c r="H406" t="n">
         <v>218689</v>
@@ -12172,7 +12172,7 @@
         <v>9.55500030517578</v>
       </c>
       <c r="G407" t="n">
-        <v>8.82309246063232</v>
+        <v>8.82309341430664</v>
       </c>
       <c r="H407" t="n">
         <v>224972</v>
@@ -12288,7 +12288,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G411" t="n">
-        <v>8.82771110534668</v>
+        <v>8.82771015167236</v>
       </c>
       <c r="H411" t="n">
         <v>189726</v>
@@ -12404,7 +12404,7 @@
         <v>9.21500015258789</v>
       </c>
       <c r="G415" t="n">
-        <v>8.50913619995117</v>
+        <v>8.5091381072998</v>
       </c>
       <c r="H415" t="n">
         <v>86476</v>
@@ -12433,7 +12433,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G416" t="n">
-        <v>8.67073154449463</v>
+        <v>8.67073249816895</v>
       </c>
       <c r="H416" t="n">
         <v>133259</v>
@@ -12491,7 +12491,7 @@
         <v>9.57499980926514</v>
       </c>
       <c r="G418" t="n">
-        <v>8.84156131744385</v>
+        <v>8.84156036376953</v>
       </c>
       <c r="H418" t="n">
         <v>93508</v>
@@ -12520,7 +12520,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G419" t="n">
-        <v>8.57839298248291</v>
+        <v>8.57839202880859</v>
       </c>
       <c r="H419" t="n">
         <v>85948</v>
@@ -12578,7 +12578,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G421" t="n">
-        <v>8.28290462493896</v>
+        <v>8.28290367126465</v>
       </c>
       <c r="H421" t="n">
         <v>194344</v>
@@ -12636,7 +12636,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G423" t="n">
-        <v>8.03820323944092</v>
+        <v>8.0382022857666</v>
       </c>
       <c r="H423" t="n">
         <v>208593</v>
@@ -12723,7 +12723,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G426" t="n">
-        <v>7.92277669906616</v>
+        <v>7.92277717590332</v>
       </c>
       <c r="H426" t="n">
         <v>224688</v>
@@ -12752,7 +12752,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G427" t="n">
-        <v>7.82120323181152</v>
+        <v>7.82120275497437</v>
       </c>
       <c r="H427" t="n">
         <v>315397</v>
@@ -12781,7 +12781,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G428" t="n">
-        <v>7.82120323181152</v>
+        <v>7.82120275497437</v>
       </c>
       <c r="H428" t="n">
         <v>153923</v>
@@ -12810,7 +12810,7 @@
         <v>8.46500015258789</v>
       </c>
       <c r="G429" t="n">
-        <v>7.81658697128296</v>
+        <v>7.81658744812012</v>
       </c>
       <c r="H429" t="n">
         <v>124892</v>
@@ -12839,7 +12839,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G430" t="n">
-        <v>7.87660789489746</v>
+        <v>7.87660694122314</v>
       </c>
       <c r="H430" t="n">
         <v>182047</v>
@@ -12868,7 +12868,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G431" t="n">
-        <v>7.81196928024292</v>
+        <v>7.81196975708008</v>
       </c>
       <c r="H431" t="n">
         <v>211938</v>
@@ -12897,7 +12897,7 @@
         <v>8.42500019073486</v>
       </c>
       <c r="G432" t="n">
-        <v>7.77965021133423</v>
+        <v>7.77965116500854</v>
       </c>
       <c r="H432" t="n">
         <v>499662</v>
@@ -12926,7 +12926,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G433" t="n">
-        <v>7.5441837310791</v>
+        <v>7.54418325424194</v>
       </c>
       <c r="H433" t="n">
         <v>411895</v>
@@ -12955,7 +12955,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G434" t="n">
-        <v>7.25792932510376</v>
+        <v>7.2579288482666</v>
       </c>
       <c r="H434" t="n">
         <v>435932</v>
@@ -12984,7 +12984,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G435" t="n">
-        <v>7.06401491165161</v>
+        <v>7.06401538848877</v>
       </c>
       <c r="H435" t="n">
         <v>300120</v>
@@ -13013,7 +13013,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G436" t="n">
-        <v>7.10095071792603</v>
+        <v>7.10095119476318</v>
       </c>
       <c r="H436" t="n">
         <v>185032</v>
@@ -13071,7 +13071,7 @@
         <v>7.72499990463257</v>
       </c>
       <c r="G438" t="n">
-        <v>7.13327026367188</v>
+        <v>7.13326930999756</v>
       </c>
       <c r="H438" t="n">
         <v>174564</v>
@@ -13332,7 +13332,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G447" t="n">
-        <v>6.33452892303467</v>
+        <v>6.33452844619751</v>
       </c>
       <c r="H447" t="n">
         <v>231466</v>
@@ -13361,7 +13361,7 @@
         <v>7.13500022888184</v>
       </c>
       <c r="G448" t="n">
-        <v>6.58846378326416</v>
+        <v>6.588463306427</v>
       </c>
       <c r="H448" t="n">
         <v>537214</v>
@@ -13419,7 +13419,7 @@
         <v>7.31500005722046</v>
       </c>
       <c r="G450" t="n">
-        <v>6.75467538833618</v>
+        <v>6.75467586517334</v>
       </c>
       <c r="H450" t="n">
         <v>323055</v>
@@ -13477,7 +13477,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G452" t="n">
-        <v>6.55614423751831</v>
+        <v>6.55614471435547</v>
       </c>
       <c r="H452" t="n">
         <v>185501</v>
@@ -13651,7 +13651,7 @@
         <v>7.09499979019165</v>
       </c>
       <c r="G458" t="n">
-        <v>6.55152702331543</v>
+        <v>6.55152750015259</v>
       </c>
       <c r="H458" t="n">
         <v>694126</v>
@@ -13680,7 +13680,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G459" t="n">
-        <v>6.55614423751831</v>
+        <v>6.55614471435547</v>
       </c>
       <c r="H459" t="n">
         <v>342488</v>
@@ -13825,7 +13825,7 @@
         <v>6.69500017166138</v>
       </c>
       <c r="G464" t="n">
-        <v>6.18216753005981</v>
+        <v>6.18216800689697</v>
       </c>
       <c r="H464" t="n">
         <v>494430</v>
@@ -13854,7 +13854,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G465" t="n">
-        <v>6.18678426742554</v>
+        <v>6.18678379058838</v>
       </c>
       <c r="H465" t="n">
         <v>200486</v>
@@ -13883,7 +13883,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G466" t="n">
-        <v>5.80818939208984</v>
+        <v>5.80819034576416</v>
       </c>
       <c r="H466" t="n">
         <v>501243</v>
@@ -14057,7 +14057,7 @@
         <v>6.16499996185303</v>
       </c>
       <c r="G472" t="n">
-        <v>5.69276475906372</v>
+        <v>5.69276523590088</v>
       </c>
       <c r="H472" t="n">
         <v>637767</v>
@@ -14086,7 +14086,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G473" t="n">
-        <v>5.59580755233765</v>
+        <v>5.5958080291748</v>
       </c>
       <c r="H473" t="n">
         <v>246202</v>
@@ -14289,7 +14289,7 @@
         <v>5.9850001335144</v>
       </c>
       <c r="G480" t="n">
-        <v>5.5265531539917</v>
+        <v>5.52655267715454</v>
       </c>
       <c r="H480" t="n">
         <v>491648</v>
@@ -14434,7 +14434,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G485" t="n">
-        <v>5.17566061019897</v>
+        <v>5.17566108703613</v>
       </c>
       <c r="H485" t="n">
         <v>433667</v>
@@ -14666,7 +14666,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G493" t="n">
-        <v>4.83400201797485</v>
+        <v>4.83400249481201</v>
       </c>
       <c r="H493" t="n">
         <v>200923</v>
@@ -14695,7 +14695,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G494" t="n">
-        <v>4.88478899002075</v>
+        <v>4.88478946685791</v>
       </c>
       <c r="H494" t="n">
         <v>111362</v>
@@ -14724,7 +14724,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G495" t="n">
-        <v>4.88940620422363</v>
+        <v>4.88940668106079</v>
       </c>
       <c r="H495" t="n">
         <v>133883</v>
@@ -14753,7 +14753,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G496" t="n">
-        <v>5.13410711288452</v>
+        <v>5.13410758972168</v>
       </c>
       <c r="H496" t="n">
         <v>302728</v>
@@ -14869,7 +14869,7 @@
         <v>5.69500017166138</v>
       </c>
       <c r="G500" t="n">
-        <v>5.25876665115356</v>
+        <v>5.25876712799072</v>
       </c>
       <c r="H500" t="n">
         <v>671518</v>
@@ -14898,7 +14898,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G501" t="n">
-        <v>5.38342523574829</v>
+        <v>5.38342571258545</v>
       </c>
       <c r="H501" t="n">
         <v>200804</v>
@@ -15101,7 +15101,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G508" t="n">
-        <v>5.41112804412842</v>
+        <v>5.41112756729126</v>
       </c>
       <c r="H508" t="n">
         <v>222944</v>
@@ -15159,7 +15159,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G510" t="n">
-        <v>5.21259689331055</v>
+        <v>5.21259641647339</v>
       </c>
       <c r="H510" t="n">
         <v>110937</v>
@@ -15246,7 +15246,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G513" t="n">
-        <v>5.21259689331055</v>
+        <v>5.21259641647339</v>
       </c>
       <c r="H513" t="n">
         <v>215173</v>
@@ -15420,7 +15420,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G519" t="n">
-        <v>5.25414991378784</v>
+        <v>5.25414943695068</v>
       </c>
       <c r="H519" t="n">
         <v>250927</v>
@@ -15536,7 +15536,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G523" t="n">
-        <v>5.16180992126465</v>
+        <v>5.16180944442749</v>
       </c>
       <c r="H523" t="n">
         <v>249552</v>
@@ -15565,7 +15565,7 @@
         <v>5.5</v>
       </c>
       <c r="G524" t="n">
-        <v>5.0787034034729</v>
+        <v>5.07870388031006</v>
       </c>
       <c r="H524" t="n">
         <v>365475</v>
@@ -15797,7 +15797,7 @@
         <v>6.30499982833862</v>
       </c>
       <c r="G532" t="n">
-        <v>5.82204103469849</v>
+        <v>5.82204055786133</v>
       </c>
       <c r="H532" t="n">
         <v>298757</v>
@@ -15884,7 +15884,7 @@
         <v>6.2649998664856</v>
       </c>
       <c r="G535" t="n">
-        <v>5.78510522842407</v>
+        <v>5.78510475158691</v>
       </c>
       <c r="H535" t="n">
         <v>171909</v>
@@ -15913,7 +15913,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G536" t="n">
-        <v>5.71585035324097</v>
+        <v>5.71584987640381</v>
       </c>
       <c r="H536" t="n">
         <v>257462</v>
@@ -16029,7 +16029,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G540" t="n">
-        <v>6.03904008865356</v>
+        <v>6.03904056549072</v>
       </c>
       <c r="H540" t="n">
         <v>416492</v>
@@ -16058,7 +16058,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G541" t="n">
-        <v>6.05750751495361</v>
+        <v>6.05750846862793</v>
       </c>
       <c r="H541" t="n">
         <v>374625</v>
@@ -16087,7 +16087,7 @@
         <v>6.57499980926514</v>
       </c>
       <c r="G542" t="n">
-        <v>6.07135915756226</v>
+        <v>6.0713586807251</v>
       </c>
       <c r="H542" t="n">
         <v>267523</v>
@@ -16435,7 +16435,7 @@
         <v>6.29500007629395</v>
       </c>
       <c r="G554" t="n">
-        <v>5.81280755996704</v>
+        <v>5.81280660629272</v>
       </c>
       <c r="H554" t="n">
         <v>151233</v>
@@ -16464,7 +16464,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G555" t="n">
-        <v>5.71585035324097</v>
+        <v>5.71584987640381</v>
       </c>
       <c r="H555" t="n">
         <v>675111</v>
@@ -16725,7 +16725,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G564" t="n">
-        <v>5.41112804412842</v>
+        <v>5.41112756729126</v>
       </c>
       <c r="H564" t="n">
         <v>104231</v>
@@ -16754,7 +16754,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G565" t="n">
-        <v>5.51270198822021</v>
+        <v>5.51270151138306</v>
       </c>
       <c r="H565" t="n">
         <v>164534</v>
@@ -16783,7 +16783,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G566" t="n">
-        <v>5.38342523574829</v>
+        <v>5.38342571258545</v>
       </c>
       <c r="H566" t="n">
         <v>143325</v>
@@ -16928,7 +16928,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G571" t="n">
-        <v>5.17566061019897</v>
+        <v>5.17566108703613</v>
       </c>
       <c r="H571" t="n">
         <v>188694</v>
@@ -17044,7 +17044,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G575" t="n">
-        <v>5.13410711288452</v>
+        <v>5.13410758972168</v>
       </c>
       <c r="H575" t="n">
         <v>302344</v>
@@ -17160,7 +17160,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G579" t="n">
-        <v>5.07408666610718</v>
+        <v>5.07408618927002</v>
       </c>
       <c r="H579" t="n">
         <v>256005</v>
@@ -17189,7 +17189,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G580" t="n">
-        <v>5.09717082977295</v>
+        <v>5.09717130661011</v>
       </c>
       <c r="H580" t="n">
         <v>391172</v>
@@ -17247,7 +17247,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G582" t="n">
-        <v>5.3003191947937</v>
+        <v>5.30031967163086</v>
       </c>
       <c r="H582" t="n">
         <v>1080928</v>
@@ -17334,7 +17334,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G585" t="n">
-        <v>5.47576570510864</v>
+        <v>5.47576522827148</v>
       </c>
       <c r="H585" t="n">
         <v>310197</v>
@@ -17392,7 +17392,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G587" t="n">
-        <v>5.57733964920044</v>
+        <v>5.5773401260376</v>
       </c>
       <c r="H587" t="n">
         <v>394516</v>
@@ -17421,7 +17421,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G588" t="n">
-        <v>5.59580755233765</v>
+        <v>5.5958080291748</v>
       </c>
       <c r="H588" t="n">
         <v>428003</v>
@@ -17682,7 +17682,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G597" t="n">
-        <v>4.83400201797485</v>
+        <v>4.83400249481201</v>
       </c>
       <c r="H597" t="n">
         <v>384652</v>
@@ -17711,7 +17711,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G598" t="n">
-        <v>4.80630016326904</v>
+        <v>4.8063006401062</v>
       </c>
       <c r="H598" t="n">
         <v>332805</v>
@@ -17740,7 +17740,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G599" t="n">
-        <v>4.70010948181152</v>
+        <v>4.70010900497437</v>
       </c>
       <c r="H599" t="n">
         <v>555539</v>
@@ -17769,7 +17769,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G600" t="n">
-        <v>4.81091785430908</v>
+        <v>4.81091737747192</v>
       </c>
       <c r="H600" t="n">
         <v>367022</v>
@@ -17827,7 +17827,7 @@
         <v>5.22499990463257</v>
       </c>
       <c r="G602" t="n">
-        <v>4.82476854324341</v>
+        <v>4.82476806640625</v>
       </c>
       <c r="H602" t="n">
         <v>549261</v>
@@ -17856,7 +17856,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G603" t="n">
-        <v>4.89864063262939</v>
+        <v>4.89863967895508</v>
       </c>
       <c r="H603" t="n">
         <v>510591</v>
@@ -17885,7 +17885,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>4.80630016326904</v>
+        <v>4.8063006401062</v>
       </c>
       <c r="H604" t="n">
         <v>321087</v>
@@ -17914,7 +17914,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G605" t="n">
-        <v>4.66317367553711</v>
+        <v>4.66317319869995</v>
       </c>
       <c r="H605" t="n">
         <v>1112720</v>
@@ -17943,7 +17943,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>4.52466344833374</v>
+        <v>4.52466297149658</v>
       </c>
       <c r="H606" t="n">
         <v>835466</v>
@@ -17972,7 +17972,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G607" t="n">
-        <v>4.52466344833374</v>
+        <v>4.52466297149658</v>
       </c>
       <c r="H607" t="n">
         <v>662577</v>
@@ -18001,7 +18001,7 @@
         <v>4.82200002670288</v>
       </c>
       <c r="G608" t="n">
-        <v>4.45263767242432</v>
+        <v>4.45263814926147</v>
       </c>
       <c r="H608" t="n">
         <v>597938</v>
@@ -18059,7 +18059,7 @@
         <v>4.66400003433228</v>
       </c>
       <c r="G610" t="n">
-        <v>4.30674028396606</v>
+        <v>4.30674076080322</v>
       </c>
       <c r="H610" t="n">
         <v>394307</v>
@@ -18175,7 +18175,7 @@
         <v>4.74399995803833</v>
       </c>
       <c r="G614" t="n">
-        <v>4.38061285018921</v>
+        <v>4.38061237335205</v>
       </c>
       <c r="H614" t="n">
         <v>609563</v>
@@ -18291,7 +18291,7 @@
         <v>5</v>
       </c>
       <c r="G618" t="n">
-        <v>4.61700296401978</v>
+        <v>4.61700344085693</v>
       </c>
       <c r="H618" t="n">
         <v>694400</v>
@@ -18378,7 +18378,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G621" t="n">
-        <v>4.56898593902588</v>
+        <v>4.56898641586304</v>
       </c>
       <c r="H621" t="n">
         <v>377386</v>
@@ -18494,7 +18494,7 @@
         <v>5.06500005722046</v>
       </c>
       <c r="G625" t="n">
-        <v>4.67702436447144</v>
+        <v>4.67702388763428</v>
       </c>
       <c r="H625" t="n">
         <v>1126607</v>
@@ -18552,7 +18552,7 @@
         <v>4.97800016403198</v>
       </c>
       <c r="G627" t="n">
-        <v>4.59668827056885</v>
+        <v>4.59668874740601</v>
       </c>
       <c r="H627" t="n">
         <v>698215</v>
@@ -18581,7 +18581,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G628" t="n">
-        <v>4.70010948181152</v>
+        <v>4.70010900497437</v>
       </c>
       <c r="H628" t="n">
         <v>666276</v>
@@ -18639,7 +18639,7 @@
         <v>5.0149998664856</v>
       </c>
       <c r="G630" t="n">
-        <v>4.6308536529541</v>
+        <v>4.63085412979126</v>
       </c>
       <c r="H630" t="n">
         <v>580822</v>
@@ -18668,7 +18668,7 @@
         <v>4.94199991226196</v>
       </c>
       <c r="G631" t="n">
-        <v>4.56344604492188</v>
+        <v>4.56344556808472</v>
       </c>
       <c r="H631" t="n">
         <v>610912</v>
@@ -18726,7 +18726,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G633" t="n">
-        <v>4.63421249389648</v>
+        <v>4.63421201705933</v>
       </c>
       <c r="H633" t="n">
         <v>659569</v>
@@ -18900,7 +18900,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G639" t="n">
-        <v>4.47546625137329</v>
+        <v>4.47546672821045</v>
       </c>
       <c r="H639" t="n">
         <v>721270</v>
@@ -18929,7 +18929,7 @@
         <v>4.81199979782104</v>
       </c>
       <c r="G640" t="n">
-        <v>4.60169744491577</v>
+        <v>4.60169792175293</v>
       </c>
       <c r="H640" t="n">
         <v>409298</v>
@@ -19074,7 +19074,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G645" t="n">
-        <v>4.45634078979492</v>
+        <v>4.45634031295776</v>
       </c>
       <c r="H645" t="n">
         <v>337361</v>
@@ -19132,7 +19132,7 @@
         <v>4.62400007247925</v>
       </c>
       <c r="G647" t="n">
-        <v>4.42191410064697</v>
+        <v>4.42191457748413</v>
       </c>
       <c r="H647" t="n">
         <v>590963</v>
@@ -19219,7 +19219,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G650" t="n">
-        <v>4.17136478424072</v>
+        <v>4.17136430740356</v>
       </c>
       <c r="H650" t="n">
         <v>575556</v>
@@ -19306,7 +19306,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G653" t="n">
-        <v>4.20770406723022</v>
+        <v>4.20770359039307</v>
       </c>
       <c r="H653" t="n">
         <v>253568</v>
@@ -19480,7 +19480,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G659" t="n">
-        <v>3.93037796020508</v>
+        <v>3.9303777217865</v>
       </c>
       <c r="H659" t="n">
         <v>499794</v>
@@ -19770,7 +19770,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G669" t="n">
-        <v>3.65496468544006</v>
+        <v>3.65496444702148</v>
       </c>
       <c r="H669" t="n">
         <v>556073</v>
@@ -19857,7 +19857,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G672" t="n">
-        <v>3.81370949745178</v>
+        <v>3.81370973587036</v>
       </c>
       <c r="H672" t="n">
         <v>401105</v>
@@ -19886,7 +19886,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G673" t="n">
-        <v>3.81370949745178</v>
+        <v>3.81370973587036</v>
       </c>
       <c r="H673" t="n">
         <v>294689</v>
@@ -19915,7 +19915,7 @@
         <v>4.17600011825562</v>
       </c>
       <c r="G674" t="n">
-        <v>3.99349355697632</v>
+        <v>3.99349331855774</v>
       </c>
       <c r="H674" t="n">
         <v>714573</v>
@@ -20379,7 +20379,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G690" t="n">
-        <v>3.45605492591858</v>
+        <v>3.4560546875</v>
       </c>
       <c r="H690" t="n">
         <v>383156</v>
@@ -20756,7 +20756,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G703" t="n">
-        <v>3.96862959861755</v>
+        <v>3.96862983703613</v>
       </c>
       <c r="H703" t="n">
         <v>402206</v>
@@ -20785,7 +20785,7 @@
         <v>4.1560001373291</v>
       </c>
       <c r="G704" t="n">
-        <v>3.97436785697937</v>
+        <v>3.97436738014221</v>
       </c>
       <c r="H704" t="n">
         <v>366565</v>
@@ -20843,7 +20843,7 @@
         <v>4.27600002288818</v>
       </c>
       <c r="G706" t="n">
-        <v>4.0891227722168</v>
+        <v>4.08912324905396</v>
       </c>
       <c r="H706" t="n">
         <v>382472</v>
@@ -20872,7 +20872,7 @@
         <v>4.13600015640259</v>
       </c>
       <c r="G707" t="n">
-        <v>3.95524168014526</v>
+        <v>3.95524144172668</v>
       </c>
       <c r="H707" t="n">
         <v>503313</v>
@@ -20930,7 +20930,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G709" t="n">
-        <v>3.98966813087463</v>
+        <v>3.98966789245605</v>
       </c>
       <c r="H709" t="n">
         <v>357159</v>
@@ -21017,7 +21017,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G712" t="n">
-        <v>3.67026519775391</v>
+        <v>3.67026543617249</v>
       </c>
       <c r="H712" t="n">
         <v>437455</v>
@@ -21162,7 +21162,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G717" t="n">
-        <v>3.81370949745178</v>
+        <v>3.81370973587036</v>
       </c>
       <c r="H717" t="n">
         <v>286225</v>
@@ -21191,7 +21191,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G718" t="n">
-        <v>3.82327270507812</v>
+        <v>3.82327246665955</v>
       </c>
       <c r="H718" t="n">
         <v>150642</v>
@@ -21220,7 +21220,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G719" t="n">
-        <v>3.91507697105408</v>
+        <v>3.91507720947266</v>
       </c>
       <c r="H719" t="n">
         <v>372351</v>
@@ -21307,7 +21307,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G722" t="n">
-        <v>3.98584294319153</v>
+        <v>3.98584318161011</v>
       </c>
       <c r="H722" t="n">
         <v>634315</v>
@@ -21365,7 +21365,7 @@
         <v>4.42600011825562</v>
       </c>
       <c r="G724" t="n">
-        <v>4.23256778717041</v>
+        <v>4.23256731033325</v>
       </c>
       <c r="H724" t="n">
         <v>1439555</v>
@@ -21394,7 +21394,7 @@
         <v>4.51200008392334</v>
       </c>
       <c r="G725" t="n">
-        <v>4.31480884552002</v>
+        <v>4.31480932235718</v>
       </c>
       <c r="H725" t="n">
         <v>724657</v>
@@ -21452,7 +21452,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G727" t="n">
-        <v>4.15032625198364</v>
+        <v>4.15032577514648</v>
       </c>
       <c r="H727" t="n">
         <v>336308</v>
@@ -21510,7 +21510,7 @@
         <v>4.25</v>
       </c>
       <c r="G729" t="n">
-        <v>4.06425905227661</v>
+        <v>4.06425952911377</v>
       </c>
       <c r="H729" t="n">
         <v>168991</v>
@@ -21597,7 +21597,7 @@
         <v>4.2039999961853</v>
       </c>
       <c r="G732" t="n">
-        <v>4.0202693939209</v>
+        <v>4.02026987075806</v>
       </c>
       <c r="H732" t="n">
         <v>193502</v>
@@ -21742,7 +21742,7 @@
         <v>4.11399984359741</v>
       </c>
       <c r="G737" t="n">
-        <v>3.93420267105103</v>
+        <v>3.9342029094696</v>
       </c>
       <c r="H737" t="n">
         <v>129269</v>
@@ -21829,7 +21829,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G740" t="n">
-        <v>3.96862959861755</v>
+        <v>3.96862983703613</v>
       </c>
       <c r="H740" t="n">
         <v>236046</v>
@@ -21858,7 +21858,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G741" t="n">
-        <v>3.91507697105408</v>
+        <v>3.91507720947266</v>
       </c>
       <c r="H741" t="n">
         <v>182762</v>
@@ -22061,7 +22061,7 @@
         <v>3.90799999237061</v>
       </c>
       <c r="G748" t="n">
-        <v>3.73720574378967</v>
+        <v>3.73720598220825</v>
       </c>
       <c r="H748" t="n">
         <v>191909</v>
@@ -22119,7 +22119,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G750" t="n">
-        <v>3.70086669921875</v>
+        <v>3.70086646080017</v>
       </c>
       <c r="H750" t="n">
         <v>77185</v>
@@ -22148,7 +22148,7 @@
         <v>3.93799996376038</v>
       </c>
       <c r="G751" t="n">
-        <v>3.76589488983154</v>
+        <v>3.76589465141296</v>
       </c>
       <c r="H751" t="n">
         <v>138045</v>
@@ -22264,7 +22264,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G755" t="n">
-        <v>3.73911881446838</v>
+        <v>3.7391185760498</v>
       </c>
       <c r="H755" t="n">
         <v>208777</v>
@@ -22380,7 +22380,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G759" t="n">
-        <v>3.57846093177795</v>
+        <v>3.57846069335938</v>
       </c>
       <c r="H759" t="n">
         <v>337584</v>
@@ -22409,7 +22409,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G760" t="n">
-        <v>3.62245059013367</v>
+        <v>3.62245035171509</v>
       </c>
       <c r="H760" t="n">
         <v>422072</v>
@@ -22467,7 +22467,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G762" t="n">
-        <v>3.56315994262695</v>
+        <v>3.56316018104553</v>
       </c>
       <c r="H762" t="n">
         <v>704289</v>
@@ -22496,7 +22496,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G763" t="n">
-        <v>3.54785919189453</v>
+        <v>3.54785943031311</v>
       </c>
       <c r="H763" t="n">
         <v>1097480</v>
@@ -22583,7 +22583,7 @@
         <v>3.64800000190735</v>
       </c>
       <c r="G766" t="n">
-        <v>3.48856902122498</v>
+        <v>3.4885687828064</v>
       </c>
       <c r="H766" t="n">
         <v>1669355</v>
@@ -22728,7 +22728,7 @@
         <v>3.64400005340576</v>
       </c>
       <c r="G771" t="n">
-        <v>3.48474359512329</v>
+        <v>3.48474383354187</v>
       </c>
       <c r="H771" t="n">
         <v>105519</v>
@@ -22757,7 +22757,7 @@
         <v>3.63199996948242</v>
       </c>
       <c r="G772" t="n">
-        <v>3.47326827049255</v>
+        <v>3.47326803207397</v>
       </c>
       <c r="H772" t="n">
         <v>121534</v>
@@ -22873,7 +22873,7 @@
         <v>3.95799994468689</v>
       </c>
       <c r="G776" t="n">
-        <v>3.78502082824707</v>
+        <v>3.78502058982849</v>
       </c>
       <c r="H776" t="n">
         <v>243650</v>
@@ -22902,7 +22902,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G777" t="n">
-        <v>3.76971983909607</v>
+        <v>3.76972007751465</v>
       </c>
       <c r="H777" t="n">
         <v>111182</v>
@@ -22960,7 +22960,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G779" t="n">
-        <v>3.70086669921875</v>
+        <v>3.70086646080017</v>
       </c>
       <c r="H779" t="n">
         <v>145693</v>
@@ -22989,7 +22989,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G780" t="n">
-        <v>3.59758687019348</v>
+        <v>3.5975866317749</v>
       </c>
       <c r="H780" t="n">
         <v>157659</v>
@@ -23076,7 +23076,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G783" t="n">
-        <v>3.44075393676758</v>
+        <v>3.44075417518616</v>
       </c>
       <c r="H783" t="n">
         <v>613580</v>
@@ -23105,7 +23105,7 @@
         <v>3.41599988937378</v>
       </c>
       <c r="G784" t="n">
-        <v>3.26670813560486</v>
+        <v>3.26670789718628</v>
       </c>
       <c r="H784" t="n">
         <v>455535</v>
@@ -23134,7 +23134,7 @@
         <v>3.41599988937378</v>
       </c>
       <c r="G785" t="n">
-        <v>3.26670813560486</v>
+        <v>3.26670789718628</v>
       </c>
       <c r="H785" t="n">
         <v>519347</v>
@@ -23163,7 +23163,7 @@
         <v>3.46799993515015</v>
       </c>
       <c r="G786" t="n">
-        <v>3.31643533706665</v>
+        <v>3.31643557548523</v>
       </c>
       <c r="H786" t="n">
         <v>202674</v>
@@ -23192,7 +23192,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G787" t="n">
-        <v>3.29157161712646</v>
+        <v>3.29157185554504</v>
       </c>
       <c r="H787" t="n">
         <v>188696</v>
@@ -23424,7 +23424,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G795" t="n">
-        <v>3.20741772651672</v>
+        <v>3.2074179649353</v>
       </c>
       <c r="H795" t="n">
         <v>383770</v>
@@ -23801,7 +23801,7 @@
         <v>3.47399997711182</v>
       </c>
       <c r="G808" t="n">
-        <v>3.32217335700989</v>
+        <v>3.32217311859131</v>
       </c>
       <c r="H808" t="n">
         <v>80720</v>
@@ -23975,7 +23975,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G814" t="n">
-        <v>3.22654366493225</v>
+        <v>3.22654390335083</v>
       </c>
       <c r="H814" t="n">
         <v>115313</v>
@@ -24149,7 +24149,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G820" t="n">
-        <v>3.55168461799622</v>
+        <v>3.55168437957764</v>
       </c>
       <c r="H820" t="n">
         <v>1031313</v>
@@ -24178,7 +24178,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G821" t="n">
-        <v>3.5076949596405</v>
+        <v>3.50769472122192</v>
       </c>
       <c r="H821" t="n">
         <v>354331</v>
@@ -24236,7 +24236,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G823" t="n">
-        <v>3.53638362884521</v>
+        <v>3.53638386726379</v>
       </c>
       <c r="H823" t="n">
         <v>421877</v>
@@ -24323,7 +24323,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G826" t="n">
-        <v>3.58228588104248</v>
+        <v>3.58228611946106</v>
       </c>
       <c r="H826" t="n">
         <v>258986</v>
@@ -24352,7 +24352,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G827" t="n">
-        <v>3.5765483379364</v>
+        <v>3.57654809951782</v>
       </c>
       <c r="H827" t="n">
         <v>166129</v>
@@ -24381,7 +24381,7 @@
         <v>3.84400010108948</v>
       </c>
       <c r="G828" t="n">
-        <v>3.67600321769714</v>
+        <v>3.67600297927856</v>
       </c>
       <c r="H828" t="n">
         <v>474129</v>
@@ -24526,7 +24526,7 @@
         <v>4.22599983215332</v>
       </c>
       <c r="G833" t="n">
-        <v>4.04130792617798</v>
+        <v>4.04130840301514</v>
       </c>
       <c r="H833" t="n">
         <v>2312238</v>
@@ -24758,7 +24758,7 @@
         <v>4.68599987030029</v>
       </c>
       <c r="G841" t="n">
-        <v>4.48120450973511</v>
+        <v>4.48120403289795</v>
       </c>
       <c r="H841" t="n">
         <v>337090</v>
@@ -24816,7 +24816,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G843" t="n">
-        <v>4.54432010650635</v>
+        <v>4.54431962966919</v>
       </c>
       <c r="H843" t="n">
         <v>212793</v>
@@ -24903,7 +24903,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G846" t="n">
-        <v>4.35688591003418</v>
+        <v>4.35688638687134</v>
       </c>
       <c r="H846" t="n">
         <v>178453</v>
@@ -24932,7 +24932,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G847" t="n">
-        <v>4.26316928863525</v>
+        <v>4.2631688117981</v>
       </c>
       <c r="H847" t="n">
         <v>228223</v>
@@ -24990,7 +24990,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G849" t="n">
-        <v>4.17136478424072</v>
+        <v>4.17136430740356</v>
       </c>
       <c r="H849" t="n">
         <v>216742</v>
@@ -25048,7 +25048,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G851" t="n">
-        <v>3.93037796020508</v>
+        <v>3.9303777217865</v>
       </c>
       <c r="H851" t="n">
         <v>187268</v>
@@ -25135,7 +25135,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G854" t="n">
-        <v>3.77928280830383</v>
+        <v>3.77928304672241</v>
       </c>
       <c r="H854" t="n">
         <v>245578</v>
@@ -25251,7 +25251,7 @@
         <v>3.51200008392334</v>
       </c>
       <c r="G858" t="n">
-        <v>3.35851263999939</v>
+        <v>3.35851287841797</v>
       </c>
       <c r="H858" t="n">
         <v>146055</v>
@@ -25280,7 +25280,7 @@
         <v>3.56800007820129</v>
       </c>
       <c r="G859" t="n">
-        <v>3.41206526756287</v>
+        <v>3.41206550598145</v>
       </c>
       <c r="H859" t="n">
         <v>419236</v>
@@ -25396,7 +25396,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G863" t="n">
-        <v>3.47900581359863</v>
+        <v>3.47900605201721</v>
       </c>
       <c r="H863" t="n">
         <v>215914</v>
@@ -25541,7 +25541,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G868" t="n">
-        <v>3.77928280830383</v>
+        <v>3.77928304672241</v>
       </c>
       <c r="H868" t="n">
         <v>73720</v>
@@ -25657,7 +25657,7 @@
         <v>4.12400007247925</v>
       </c>
       <c r="G872" t="n">
-        <v>3.94376587867737</v>
+        <v>3.94376611709595</v>
       </c>
       <c r="H872" t="n">
         <v>191569</v>
@@ -25860,7 +25860,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G879" t="n">
-        <v>4.47546625137329</v>
+        <v>4.47546672821045</v>
       </c>
       <c r="H879" t="n">
         <v>120035</v>
@@ -25976,7 +25976,7 @@
         <v>4.38800001144409</v>
       </c>
       <c r="G883" t="n">
-        <v>4.19622850418091</v>
+        <v>4.19622802734375</v>
       </c>
       <c r="H883" t="n">
         <v>292289</v>
@@ -26063,7 +26063,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G886" t="n">
-        <v>4.20196580886841</v>
+        <v>4.20196628570557</v>
       </c>
       <c r="H886" t="n">
         <v>132141</v>
@@ -26237,7 +26237,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G892" t="n">
-        <v>4.57109689712524</v>
+        <v>4.57109642028809</v>
       </c>
       <c r="H892" t="n">
         <v>407750</v>
@@ -26295,7 +26295,7 @@
         <v>4.74599981307983</v>
       </c>
       <c r="G894" t="n">
-        <v>4.53858184814453</v>
+        <v>4.53858232498169</v>
       </c>
       <c r="H894" t="n">
         <v>111758</v>
@@ -26324,7 +26324,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G895" t="n">
-        <v>4.68585205078125</v>
+        <v>4.68585157394409</v>
       </c>
       <c r="H895" t="n">
         <v>288639</v>
@@ -36625,6 +36625,35 @@
         <v>325739</v>
       </c>
       <c r="I1250" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1251" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1251" t="n">
+        <v>3.44400000572205</v>
+      </c>
+      <c r="D1251" t="n">
+        <v>3.52999997138977</v>
+      </c>
+      <c r="E1251" t="n">
+        <v>3.41400003433228</v>
+      </c>
+      <c r="F1251" t="n">
+        <v>3.48000001907349</v>
+      </c>
+      <c r="G1251" t="n">
+        <v>3.48000001907349</v>
+      </c>
+      <c r="H1251" t="n">
+        <v>369362</v>
+      </c>
+      <c r="I1251" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ARIS.MI.xlsx
+++ b/data/ARIS.MI.xlsx
@@ -456,7 +456,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G3" t="n">
-        <v>9.34524345397949</v>
+        <v>9.34524440765381</v>
       </c>
       <c r="H3" t="n">
         <v>1460667</v>
@@ -543,7 +543,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G6" t="n">
-        <v>9.20146942138672</v>
+        <v>9.20147037506104</v>
       </c>
       <c r="H6" t="n">
         <v>260042</v>
@@ -572,7 +572,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G7" t="n">
-        <v>9.20146942138672</v>
+        <v>9.20147037506104</v>
       </c>
       <c r="H7" t="n">
         <v>279621</v>
@@ -601,7 +601,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G8" t="n">
-        <v>9.20146942138672</v>
+        <v>9.20147037506104</v>
       </c>
       <c r="H8" t="n">
         <v>197900</v>
@@ -659,7 +659,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G10" t="n">
-        <v>9.20146942138672</v>
+        <v>9.20147037506104</v>
       </c>
       <c r="H10" t="n">
         <v>122758</v>
@@ -688,7 +688,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G11" t="n">
-        <v>9.23741436004639</v>
+        <v>9.23741340637207</v>
       </c>
       <c r="H11" t="n">
         <v>199132</v>
@@ -717,7 +717,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G12" t="n">
-        <v>9.20146942138672</v>
+        <v>9.20147037506104</v>
       </c>
       <c r="H12" t="n">
         <v>105196</v>
@@ -746,7 +746,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G13" t="n">
-        <v>9.20146942138672</v>
+        <v>9.20147037506104</v>
       </c>
       <c r="H13" t="n">
         <v>85905</v>
@@ -775,7 +775,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G14" t="n">
-        <v>9.20146942138672</v>
+        <v>9.20147037506104</v>
       </c>
       <c r="H14" t="n">
         <v>198256</v>
@@ -833,7 +833,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G16" t="n">
-        <v>8.9229097366333</v>
+        <v>8.92291069030762</v>
       </c>
       <c r="H16" t="n">
         <v>312158</v>
@@ -862,7 +862,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G17" t="n">
-        <v>8.83305358886719</v>
+        <v>8.83305263519287</v>
       </c>
       <c r="H17" t="n">
         <v>156842</v>
@@ -891,7 +891,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G18" t="n">
-        <v>8.63536357879639</v>
+        <v>8.6353645324707</v>
       </c>
       <c r="H18" t="n">
         <v>319387</v>
@@ -920,7 +920,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G19" t="n">
-        <v>8.71623611450195</v>
+        <v>8.71623706817627</v>
       </c>
       <c r="H19" t="n">
         <v>172790</v>
@@ -949,7 +949,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G20" t="n">
-        <v>9.12958431243896</v>
+        <v>9.12958526611328</v>
       </c>
       <c r="H20" t="n">
         <v>431091</v>
@@ -978,7 +978,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G21" t="n">
-        <v>9.07566928863525</v>
+        <v>9.07567119598389</v>
       </c>
       <c r="H21" t="n">
         <v>404417</v>
@@ -1036,7 +1036,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G23" t="n">
-        <v>9.07566928863525</v>
+        <v>9.07567119598389</v>
       </c>
       <c r="H23" t="n">
         <v>179305</v>
@@ -1065,7 +1065,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G24" t="n">
-        <v>9.12958431243896</v>
+        <v>9.12958526611328</v>
       </c>
       <c r="H24" t="n">
         <v>61464</v>
@@ -1094,7 +1094,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G25" t="n">
-        <v>9.11161422729492</v>
+        <v>9.11161327362061</v>
       </c>
       <c r="H25" t="n">
         <v>29624</v>
@@ -1123,7 +1123,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G26" t="n">
-        <v>9.12958431243896</v>
+        <v>9.12958526611328</v>
       </c>
       <c r="H26" t="n">
         <v>53953</v>
@@ -1181,7 +1181,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G28" t="n">
-        <v>9.65076065063477</v>
+        <v>9.65076160430908</v>
       </c>
       <c r="H28" t="n">
         <v>568583</v>
@@ -1239,7 +1239,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G30" t="n">
-        <v>10.1180248260498</v>
+        <v>10.1180238723755</v>
       </c>
       <c r="H30" t="n">
         <v>401264</v>
@@ -1268,7 +1268,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G31" t="n">
-        <v>9.48901653289795</v>
+        <v>9.48901748657227</v>
       </c>
       <c r="H31" t="n">
         <v>328664</v>
@@ -1442,7 +1442,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G37" t="n">
-        <v>10.1180248260498</v>
+        <v>10.1180238723755</v>
       </c>
       <c r="H37" t="n">
         <v>92776</v>
@@ -1500,7 +1500,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G39" t="n">
-        <v>9.62380599975586</v>
+        <v>9.62380504608154</v>
       </c>
       <c r="H39" t="n">
         <v>115964</v>
@@ -1529,7 +1529,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G40" t="n">
-        <v>9.67772006988525</v>
+        <v>9.67771911621094</v>
       </c>
       <c r="H40" t="n">
         <v>103333</v>
@@ -1645,7 +1645,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G44" t="n">
-        <v>9.1205997467041</v>
+        <v>9.12059879302979</v>
       </c>
       <c r="H44" t="n">
         <v>167591</v>
@@ -1674,7 +1674,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G45" t="n">
-        <v>9.04871273040771</v>
+        <v>9.0487117767334</v>
       </c>
       <c r="H45" t="n">
         <v>274213</v>
@@ -1703,7 +1703,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G46" t="n">
-        <v>9.20146942138672</v>
+        <v>9.20147037506104</v>
       </c>
       <c r="H46" t="n">
         <v>323983</v>
@@ -1732,7 +1732,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G47" t="n">
-        <v>9.34524345397949</v>
+        <v>9.34524440765381</v>
       </c>
       <c r="H47" t="n">
         <v>331892</v>
@@ -1761,7 +1761,7 @@
         <v>10.4899997711182</v>
       </c>
       <c r="G48" t="n">
-        <v>9.42611503601074</v>
+        <v>9.42611598968506</v>
       </c>
       <c r="H48" t="n">
         <v>67641</v>
@@ -1790,7 +1790,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G49" t="n">
-        <v>9.34524345397949</v>
+        <v>9.34524440765381</v>
       </c>
       <c r="H49" t="n">
         <v>164923</v>
@@ -1819,7 +1819,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G50" t="n">
-        <v>9.11161422729492</v>
+        <v>9.11161327362061</v>
       </c>
       <c r="H50" t="n">
         <v>253720</v>
@@ -1877,7 +1877,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G52" t="n">
-        <v>9.12958431243896</v>
+        <v>9.12958526611328</v>
       </c>
       <c r="H52" t="n">
         <v>73644</v>
@@ -1964,7 +1964,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G55" t="n">
-        <v>8.99479675292969</v>
+        <v>8.994797706604</v>
       </c>
       <c r="H55" t="n">
         <v>276782</v>
@@ -2051,7 +2051,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G58" t="n">
-        <v>8.99479675292969</v>
+        <v>8.994797706604</v>
       </c>
       <c r="H58" t="n">
         <v>253397</v>
@@ -2109,7 +2109,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G60" t="n">
-        <v>8.95885467529297</v>
+        <v>8.95885372161865</v>
       </c>
       <c r="H60" t="n">
         <v>207313</v>
@@ -2138,7 +2138,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G61" t="n">
-        <v>8.71623611450195</v>
+        <v>8.71623706817627</v>
       </c>
       <c r="H61" t="n">
         <v>224870</v>
@@ -2167,7 +2167,7 @@
         <v>9.41499996185303</v>
       </c>
       <c r="G62" t="n">
-        <v>8.46014213562012</v>
+        <v>8.4601411819458</v>
       </c>
       <c r="H62" t="n">
         <v>251208</v>
@@ -2283,7 +2283,7 @@
         <v>9.20499992370605</v>
       </c>
       <c r="G66" t="n">
-        <v>8.27143859863281</v>
+        <v>8.27143955230713</v>
       </c>
       <c r="H66" t="n">
         <v>126081</v>
@@ -2312,7 +2312,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G67" t="n">
-        <v>7.70982646942139</v>
+        <v>7.70982599258423</v>
       </c>
       <c r="H67" t="n">
         <v>139521</v>
@@ -2341,7 +2341,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G68" t="n">
-        <v>8.03331565856934</v>
+        <v>8.03331470489502</v>
       </c>
       <c r="H68" t="n">
         <v>139296</v>
@@ -2399,7 +2399,7 @@
         <v>7.875</v>
       </c>
       <c r="G70" t="n">
-        <v>7.07632637023926</v>
+        <v>7.0763258934021</v>
       </c>
       <c r="H70" t="n">
         <v>381529</v>
@@ -2457,7 +2457,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G72" t="n">
-        <v>7.42228031158447</v>
+        <v>7.42227983474731</v>
       </c>
       <c r="H72" t="n">
         <v>235581</v>
@@ -2515,7 +2515,7 @@
         <v>8.3149995803833</v>
       </c>
       <c r="G74" t="n">
-        <v>7.47170162200928</v>
+        <v>7.47170209884644</v>
       </c>
       <c r="H74" t="n">
         <v>89965</v>
@@ -2544,7 +2544,7 @@
         <v>8.78499984741211</v>
       </c>
       <c r="G75" t="n">
-        <v>7.89403581619263</v>
+        <v>7.89403629302979</v>
       </c>
       <c r="H75" t="n">
         <v>220029</v>
@@ -2602,7 +2602,7 @@
         <v>9.51500034332275</v>
       </c>
       <c r="G77" t="n">
-        <v>8.55000114440918</v>
+        <v>8.54999923706055</v>
       </c>
       <c r="H77" t="n">
         <v>369586</v>
@@ -2631,7 +2631,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G78" t="n">
-        <v>9.23741436004639</v>
+        <v>9.23741340637207</v>
       </c>
       <c r="H78" t="n">
         <v>643900</v>
@@ -2660,7 +2660,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G79" t="n">
-        <v>9.08465385437012</v>
+        <v>9.08465480804443</v>
       </c>
       <c r="H79" t="n">
         <v>663957</v>
@@ -2747,7 +2747,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G82" t="n">
-        <v>9.07566928863525</v>
+        <v>9.07567119598389</v>
       </c>
       <c r="H82" t="n">
         <v>174088</v>
@@ -2834,7 +2834,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G85" t="n">
-        <v>8.64435005187988</v>
+        <v>8.6443510055542</v>
       </c>
       <c r="H85" t="n">
         <v>93670</v>
@@ -2863,7 +2863,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G86" t="n">
-        <v>8.55898475646973</v>
+        <v>8.55898571014404</v>
       </c>
       <c r="H86" t="n">
         <v>136560</v>
@@ -2979,7 +2979,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G90" t="n">
-        <v>8.55898475646973</v>
+        <v>8.55898571014404</v>
       </c>
       <c r="H90" t="n">
         <v>75199</v>
@@ -3037,7 +3037,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G92" t="n">
-        <v>8.71623611450195</v>
+        <v>8.71623706817627</v>
       </c>
       <c r="H92" t="n">
         <v>223170</v>
@@ -3211,7 +3211,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G98" t="n">
-        <v>8.62637901306152</v>
+        <v>8.62637996673584</v>
       </c>
       <c r="H98" t="n">
         <v>131848</v>
@@ -3356,7 +3356,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G103" t="n">
-        <v>8.71623611450195</v>
+        <v>8.71623706817627</v>
       </c>
       <c r="H103" t="n">
         <v>216807</v>
@@ -3414,7 +3414,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G105" t="n">
-        <v>8.55898475646973</v>
+        <v>8.55898571014404</v>
       </c>
       <c r="H105" t="n">
         <v>167622</v>
@@ -3704,7 +3704,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G115" t="n">
-        <v>7.80867004394531</v>
+        <v>7.80867052078247</v>
       </c>
       <c r="H115" t="n">
         <v>87012</v>
@@ -3733,7 +3733,7 @@
         <v>9.02499961853027</v>
       </c>
       <c r="G116" t="n">
-        <v>8.10969543457031</v>
+        <v>8.109694480896</v>
       </c>
       <c r="H116" t="n">
         <v>88735</v>
@@ -3762,7 +3762,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G117" t="n">
-        <v>8.32086181640625</v>
+        <v>8.32086086273193</v>
       </c>
       <c r="H117" t="n">
         <v>146034</v>
@@ -3791,7 +3791,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G118" t="n">
-        <v>8.54550743103027</v>
+        <v>8.54550647735596</v>
       </c>
       <c r="H118" t="n">
         <v>395701</v>
@@ -3820,7 +3820,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G119" t="n">
-        <v>8.62637901306152</v>
+        <v>8.62637996673584</v>
       </c>
       <c r="H119" t="n">
         <v>249483</v>
@@ -3907,7 +3907,7 @@
         <v>9.94499969482422</v>
       </c>
       <c r="G122" t="n">
-        <v>8.93638896942139</v>
+        <v>8.9363899230957</v>
       </c>
       <c r="H122" t="n">
         <v>223439</v>
@@ -3936,7 +3936,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G123" t="n">
-        <v>8.96334838867188</v>
+        <v>8.96334743499756</v>
       </c>
       <c r="H123" t="n">
         <v>150460</v>
@@ -3994,7 +3994,7 @@
         <v>9.82499980926514</v>
       </c>
       <c r="G125" t="n">
-        <v>8.95423316955566</v>
+        <v>8.95423221588135</v>
       </c>
       <c r="H125" t="n">
         <v>143405</v>
@@ -4081,7 +4081,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>9.47827243804932</v>
+        <v>9.47827339172363</v>
       </c>
       <c r="H128" t="n">
         <v>307614</v>
@@ -4139,7 +4139,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G130" t="n">
-        <v>9.35068035125732</v>
+        <v>9.35068130493164</v>
       </c>
       <c r="H130" t="n">
         <v>2902048</v>
@@ -4168,7 +4168,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G131" t="n">
-        <v>9.20486068725586</v>
+        <v>9.20486164093018</v>
       </c>
       <c r="H131" t="n">
         <v>105012</v>
@@ -4197,7 +4197,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G132" t="n">
-        <v>9.24131679534912</v>
+        <v>9.2413158416748</v>
       </c>
       <c r="H132" t="n">
         <v>39938</v>
@@ -4255,7 +4255,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G134" t="n">
-        <v>9.24131679534912</v>
+        <v>9.2413158416748</v>
       </c>
       <c r="H134" t="n">
         <v>32325</v>
@@ -4313,7 +4313,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G136" t="n">
-        <v>9.29599761962891</v>
+        <v>9.29599666595459</v>
       </c>
       <c r="H136" t="n">
         <v>59750</v>
@@ -4400,7 +4400,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G139" t="n">
-        <v>8.52133274078369</v>
+        <v>8.52133178710938</v>
       </c>
       <c r="H139" t="n">
         <v>53406</v>
@@ -4429,7 +4429,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G140" t="n">
-        <v>7.95628118515015</v>
+        <v>7.95628070831299</v>
       </c>
       <c r="H140" t="n">
         <v>163728</v>
@@ -4458,7 +4458,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G141" t="n">
-        <v>7.83780241012573</v>
+        <v>7.83780288696289</v>
       </c>
       <c r="H141" t="n">
         <v>132472</v>
@@ -4516,7 +4516,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G143" t="n">
-        <v>7.73755073547363</v>
+        <v>7.73755025863647</v>
       </c>
       <c r="H143" t="n">
         <v>68881</v>
@@ -4574,7 +4574,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G145" t="n">
-        <v>7.47325277328491</v>
+        <v>7.47325325012207</v>
       </c>
       <c r="H145" t="n">
         <v>33799</v>
@@ -4603,7 +4603,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G146" t="n">
-        <v>7.34566211700439</v>
+        <v>7.34566164016724</v>
       </c>
       <c r="H146" t="n">
         <v>105071</v>
@@ -4661,7 +4661,7 @@
         <v>7.375</v>
       </c>
       <c r="G148" t="n">
-        <v>6.72137117385864</v>
+        <v>6.72137069702148</v>
       </c>
       <c r="H148" t="n">
         <v>158803</v>
@@ -4777,7 +4777,7 @@
         <v>7.81500005722046</v>
       </c>
       <c r="G152" t="n">
-        <v>7.12237548828125</v>
+        <v>7.12237501144409</v>
       </c>
       <c r="H152" t="n">
         <v>173417</v>
@@ -4835,7 +4835,7 @@
         <v>7.625</v>
       </c>
       <c r="G154" t="n">
-        <v>6.94921445846558</v>
+        <v>6.94921398162842</v>
       </c>
       <c r="H154" t="n">
         <v>154512</v>
@@ -4951,7 +4951,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G158" t="n">
-        <v>6.92642974853516</v>
+        <v>6.92643022537231</v>
       </c>
       <c r="H158" t="n">
         <v>58691</v>
@@ -5125,7 +5125,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G164" t="n">
-        <v>6.88086128234863</v>
+        <v>6.88086175918579</v>
       </c>
       <c r="H164" t="n">
         <v>59880</v>
@@ -5270,7 +5270,7 @@
         <v>7.72499990463257</v>
       </c>
       <c r="G169" t="n">
-        <v>7.04035091400146</v>
+        <v>7.04035139083862</v>
       </c>
       <c r="H169" t="n">
         <v>97576</v>
@@ -5415,7 +5415,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G174" t="n">
-        <v>7.47325277328491</v>
+        <v>7.47325325012207</v>
       </c>
       <c r="H174" t="n">
         <v>32018</v>
@@ -5502,7 +5502,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G177" t="n">
-        <v>7.46413898468018</v>
+        <v>7.46413946151733</v>
       </c>
       <c r="H177" t="n">
         <v>103642</v>
@@ -5618,7 +5618,7 @@
         <v>8</v>
       </c>
       <c r="G181" t="n">
-        <v>7.29097890853882</v>
+        <v>7.29097843170166</v>
       </c>
       <c r="H181" t="n">
         <v>44729</v>
@@ -5647,7 +5647,7 @@
         <v>8</v>
       </c>
       <c r="G182" t="n">
-        <v>7.29097890853882</v>
+        <v>7.29097843170166</v>
       </c>
       <c r="H182" t="n">
         <v>68137</v>
@@ -5705,7 +5705,7 @@
         <v>8</v>
       </c>
       <c r="G184" t="n">
-        <v>7.29097890853882</v>
+        <v>7.29097843170166</v>
       </c>
       <c r="H184" t="n">
         <v>53674</v>
@@ -5763,7 +5763,7 @@
         <v>8</v>
       </c>
       <c r="G186" t="n">
-        <v>7.29097890853882</v>
+        <v>7.29097843170166</v>
       </c>
       <c r="H186" t="n">
         <v>98582</v>
@@ -5937,7 +5937,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G192" t="n">
-        <v>6.81250810623169</v>
+        <v>6.81250858306885</v>
       </c>
       <c r="H192" t="n">
         <v>43263</v>
@@ -5966,7 +5966,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G193" t="n">
-        <v>6.81250810623169</v>
+        <v>6.81250858306885</v>
       </c>
       <c r="H193" t="n">
         <v>46346</v>
@@ -5995,7 +5995,7 @@
         <v>7.625</v>
       </c>
       <c r="G194" t="n">
-        <v>6.94921445846558</v>
+        <v>6.94921398162842</v>
       </c>
       <c r="H194" t="n">
         <v>47909</v>
@@ -6024,7 +6024,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G195" t="n">
-        <v>7.00845384597778</v>
+        <v>7.00845336914062</v>
       </c>
       <c r="H195" t="n">
         <v>142516</v>
@@ -6082,7 +6082,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G197" t="n">
-        <v>6.92642974853516</v>
+        <v>6.92643022537231</v>
       </c>
       <c r="H197" t="n">
         <v>94339</v>
@@ -6111,7 +6111,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G198" t="n">
-        <v>6.56188058853149</v>
+        <v>6.56188106536865</v>
       </c>
       <c r="H198" t="n">
         <v>52394</v>
@@ -6343,7 +6343,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G206" t="n">
-        <v>6.69858646392822</v>
+        <v>6.69858694076538</v>
       </c>
       <c r="H206" t="n">
         <v>115365</v>
@@ -6430,7 +6430,7 @@
         <v>8.33500003814697</v>
       </c>
       <c r="G209" t="n">
-        <v>7.59628915786743</v>
+        <v>7.59628868103027</v>
       </c>
       <c r="H209" t="n">
         <v>154677</v>
@@ -6459,7 +6459,7 @@
         <v>8.40499973297119</v>
       </c>
       <c r="G210" t="n">
-        <v>7.66008520126343</v>
+        <v>7.66008472442627</v>
       </c>
       <c r="H210" t="n">
         <v>162822</v>
@@ -6517,7 +6517,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G212" t="n">
-        <v>7.75577831268311</v>
+        <v>7.75577878952026</v>
       </c>
       <c r="H212" t="n">
         <v>149734</v>
@@ -6546,7 +6546,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G213" t="n">
-        <v>7.82868957519531</v>
+        <v>7.82868909835815</v>
       </c>
       <c r="H213" t="n">
         <v>267292</v>
@@ -6575,7 +6575,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G214" t="n">
-        <v>7.82868957519531</v>
+        <v>7.82868909835815</v>
       </c>
       <c r="H214" t="n">
         <v>252704</v>
@@ -6662,7 +6662,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G217" t="n">
-        <v>7.93805360794067</v>
+        <v>7.93805313110352</v>
       </c>
       <c r="H217" t="n">
         <v>247020</v>
@@ -6720,7 +6720,7 @@
         <v>9.13500022888184</v>
       </c>
       <c r="G219" t="n">
-        <v>8.32538604736328</v>
+        <v>8.3253870010376</v>
       </c>
       <c r="H219" t="n">
         <v>283069</v>
@@ -6749,7 +6749,7 @@
         <v>9.03499984741211</v>
       </c>
       <c r="G220" t="n">
-        <v>8.23425006866455</v>
+        <v>8.23424911499023</v>
       </c>
       <c r="H220" t="n">
         <v>263459</v>
@@ -6807,7 +6807,7 @@
         <v>8.84500026702881</v>
       </c>
       <c r="G222" t="n">
-        <v>8.06108856201172</v>
+        <v>8.0610876083374</v>
       </c>
       <c r="H222" t="n">
         <v>71498</v>
@@ -6981,7 +6981,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G228" t="n">
-        <v>7.71932315826416</v>
+        <v>7.71932363510132</v>
       </c>
       <c r="H228" t="n">
         <v>240482</v>
@@ -7010,7 +7010,7 @@
         <v>8.60499954223633</v>
       </c>
       <c r="G229" t="n">
-        <v>7.84235906600952</v>
+        <v>7.84235954284668</v>
       </c>
       <c r="H229" t="n">
         <v>228869</v>
@@ -7068,7 +7068,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>7.48236751556396</v>
+        <v>7.48236703872681</v>
       </c>
       <c r="H231" t="n">
         <v>150112</v>
@@ -7155,7 +7155,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G234" t="n">
-        <v>7.85602998733521</v>
+        <v>7.85602951049805</v>
       </c>
       <c r="H234" t="n">
         <v>185968</v>
@@ -7242,7 +7242,7 @@
         <v>8.63500022888184</v>
       </c>
       <c r="G237" t="n">
-        <v>7.86969995498657</v>
+        <v>7.86970043182373</v>
       </c>
       <c r="H237" t="n">
         <v>68684</v>
@@ -7271,7 +7271,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G238" t="n">
-        <v>7.86514329910278</v>
+        <v>7.86514377593994</v>
       </c>
       <c r="H238" t="n">
         <v>98511</v>
@@ -7387,7 +7387,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G242" t="n">
-        <v>7.20895481109619</v>
+        <v>7.20895528793335</v>
       </c>
       <c r="H242" t="n">
         <v>428150</v>
@@ -7416,7 +7416,7 @@
         <v>8.29500007629395</v>
       </c>
       <c r="G243" t="n">
-        <v>7.55983400344849</v>
+        <v>7.55983352661133</v>
       </c>
       <c r="H243" t="n">
         <v>179111</v>
@@ -7445,7 +7445,7 @@
         <v>8.3149995803833</v>
       </c>
       <c r="G244" t="n">
-        <v>7.57806062698364</v>
+        <v>7.5780611038208</v>
       </c>
       <c r="H244" t="n">
         <v>97069</v>
@@ -7561,7 +7561,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G248" t="n">
-        <v>7.73755073547363</v>
+        <v>7.73755025863647</v>
       </c>
       <c r="H248" t="n">
         <v>79342</v>
@@ -7590,7 +7590,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G249" t="n">
-        <v>7.82868957519531</v>
+        <v>7.82868909835815</v>
       </c>
       <c r="H249" t="n">
         <v>109003</v>
@@ -7648,7 +7648,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G251" t="n">
-        <v>7.76489353179932</v>
+        <v>7.76489305496216</v>
       </c>
       <c r="H251" t="n">
         <v>81589</v>
@@ -7735,7 +7735,7 @@
         <v>8.64500045776367</v>
       </c>
       <c r="G254" t="n">
-        <v>7.87881517410278</v>
+        <v>7.87881469726562</v>
       </c>
       <c r="H254" t="n">
         <v>56212</v>
@@ -7764,7 +7764,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G255" t="n">
-        <v>8.06564617156982</v>
+        <v>8.06564521789551</v>
       </c>
       <c r="H255" t="n">
         <v>80541</v>
@@ -7851,7 +7851,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G258" t="n">
-        <v>8.34817123413086</v>
+        <v>8.34817028045654</v>
       </c>
       <c r="H258" t="n">
         <v>65591</v>
@@ -7967,7 +7967,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G262" t="n">
-        <v>8.61246776580811</v>
+        <v>8.61246871948242</v>
       </c>
       <c r="H262" t="n">
         <v>78088</v>
@@ -8083,7 +8083,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G266" t="n">
-        <v>8.44386577606201</v>
+        <v>8.4438648223877</v>
       </c>
       <c r="H266" t="n">
         <v>56513</v>
@@ -8112,7 +8112,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G267" t="n">
-        <v>8.61246776580811</v>
+        <v>8.61246871948242</v>
       </c>
       <c r="H267" t="n">
         <v>84891</v>
@@ -8199,7 +8199,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G270" t="n">
-        <v>8.61246776580811</v>
+        <v>8.61246871948242</v>
       </c>
       <c r="H270" t="n">
         <v>91141</v>
@@ -8402,7 +8402,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G277" t="n">
-        <v>8.52133274078369</v>
+        <v>8.52133178710938</v>
       </c>
       <c r="H277" t="n">
         <v>22128</v>
@@ -8431,7 +8431,7 @@
         <v>9.66499996185303</v>
       </c>
       <c r="G278" t="n">
-        <v>8.80841445922852</v>
+        <v>8.8084135055542</v>
       </c>
       <c r="H278" t="n">
         <v>41058</v>
@@ -8489,7 +8489,7 @@
         <v>9.40499973297119</v>
       </c>
       <c r="G280" t="n">
-        <v>8.57145690917969</v>
+        <v>8.57145595550537</v>
       </c>
       <c r="H280" t="n">
         <v>67802</v>
@@ -8518,7 +8518,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G281" t="n">
-        <v>8.76740169525146</v>
+        <v>8.76740264892578</v>
       </c>
       <c r="H281" t="n">
         <v>53938</v>
@@ -8634,7 +8634,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G285" t="n">
-        <v>9.29599761962891</v>
+        <v>9.29599666595459</v>
       </c>
       <c r="H285" t="n">
         <v>110062</v>
@@ -8750,7 +8750,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G289" t="n">
-        <v>8.84031105041504</v>
+        <v>8.84031200408936</v>
       </c>
       <c r="H289" t="n">
         <v>85842</v>
@@ -8953,7 +8953,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G296" t="n">
-        <v>8.63069629669189</v>
+        <v>8.63069534301758</v>
       </c>
       <c r="H296" t="n">
         <v>142335</v>
@@ -8982,7 +8982,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G297" t="n">
-        <v>8.82208442687988</v>
+        <v>8.8220853805542</v>
       </c>
       <c r="H297" t="n">
         <v>184820</v>
@@ -9011,7 +9011,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G298" t="n">
-        <v>9.0499267578125</v>
+        <v>9.04992771148682</v>
       </c>
       <c r="H298" t="n">
         <v>175620</v>
@@ -9069,7 +9069,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G300" t="n">
-        <v>8.9952449798584</v>
+        <v>8.99524593353271</v>
       </c>
       <c r="H300" t="n">
         <v>84628</v>
@@ -9185,7 +9185,7 @@
         <v>9.61499977111816</v>
       </c>
       <c r="G304" t="n">
-        <v>8.76284408569336</v>
+        <v>8.76284503936768</v>
       </c>
       <c r="H304" t="n">
         <v>112583</v>
@@ -9214,7 +9214,7 @@
         <v>9.51500034332275</v>
       </c>
       <c r="G305" t="n">
-        <v>8.67170906066895</v>
+        <v>8.67170810699463</v>
       </c>
       <c r="H305" t="n">
         <v>74235</v>
@@ -9272,7 +9272,7 @@
         <v>9.66499996185303</v>
       </c>
       <c r="G307" t="n">
-        <v>8.80841445922852</v>
+        <v>8.8084135055542</v>
       </c>
       <c r="H307" t="n">
         <v>88814</v>
@@ -9301,7 +9301,7 @@
         <v>9.61499977111816</v>
       </c>
       <c r="G308" t="n">
-        <v>8.76284408569336</v>
+        <v>8.76284503936768</v>
       </c>
       <c r="H308" t="n">
         <v>97456</v>
@@ -9388,7 +9388,7 @@
         <v>9.30500030517578</v>
       </c>
       <c r="G311" t="n">
-        <v>8.48031997680664</v>
+        <v>8.48032093048096</v>
       </c>
       <c r="H311" t="n">
         <v>88710</v>
@@ -9446,7 +9446,7 @@
         <v>9.86499977111816</v>
       </c>
       <c r="G313" t="n">
-        <v>8.99068737030029</v>
+        <v>8.99068832397461</v>
       </c>
       <c r="H313" t="n">
         <v>95525</v>
@@ -9533,7 +9533,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G316" t="n">
-        <v>8.63980960845947</v>
+        <v>8.63981056213379</v>
       </c>
       <c r="H316" t="n">
         <v>142054</v>
@@ -9562,7 +9562,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G317" t="n">
-        <v>8.44386577606201</v>
+        <v>8.4438648223877</v>
       </c>
       <c r="H317" t="n">
         <v>158286</v>
@@ -9649,7 +9649,7 @@
         <v>9.01500034332275</v>
       </c>
       <c r="G320" t="n">
-        <v>8.21602249145508</v>
+        <v>8.21602153778076</v>
       </c>
       <c r="H320" t="n">
         <v>69302</v>
@@ -10084,7 +10084,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G335" t="n">
-        <v>8.48487663269043</v>
+        <v>8.48487758636475</v>
       </c>
       <c r="H335" t="n">
         <v>124173</v>
@@ -10171,7 +10171,7 @@
         <v>9.59500026702881</v>
       </c>
       <c r="G338" t="n">
-        <v>8.74461841583252</v>
+        <v>8.7446174621582</v>
       </c>
       <c r="H338" t="n">
         <v>46333</v>
@@ -10200,7 +10200,7 @@
         <v>9.36499977111816</v>
       </c>
       <c r="G339" t="n">
-        <v>8.53500080108643</v>
+        <v>8.53500175476074</v>
       </c>
       <c r="H339" t="n">
         <v>78975</v>
@@ -10316,7 +10316,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G343" t="n">
-        <v>8.53955841064453</v>
+        <v>8.53955936431885</v>
       </c>
       <c r="H343" t="n">
         <v>356528</v>
@@ -10432,7 +10432,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G347" t="n">
-        <v>9.47827243804932</v>
+        <v>9.47827339172363</v>
       </c>
       <c r="H347" t="n">
         <v>132689</v>
@@ -10577,7 +10577,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G352" t="n">
-        <v>8.86765289306641</v>
+        <v>8.86765384674072</v>
       </c>
       <c r="H352" t="n">
         <v>54316</v>
@@ -10722,7 +10722,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G357" t="n">
-        <v>9.16840648651123</v>
+        <v>9.16840553283691</v>
       </c>
       <c r="H357" t="n">
         <v>43978</v>
@@ -10751,7 +10751,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G358" t="n">
-        <v>9.46916007995605</v>
+        <v>9.46915912628174</v>
       </c>
       <c r="H358" t="n">
         <v>119140</v>
@@ -10809,7 +10809,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G360" t="n">
-        <v>9.50561332702637</v>
+        <v>9.50561428070068</v>
       </c>
       <c r="H360" t="n">
         <v>54614</v>
@@ -10838,7 +10838,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G361" t="n">
-        <v>9.47827243804932</v>
+        <v>9.47827339172363</v>
       </c>
       <c r="H361" t="n">
         <v>59625</v>
@@ -10925,7 +10925,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G364" t="n">
-        <v>9.42359066009521</v>
+        <v>9.4235897064209</v>
       </c>
       <c r="H364" t="n">
         <v>225133</v>
@@ -10954,7 +10954,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G365" t="n">
-        <v>9.33245182037354</v>
+        <v>9.33245277404785</v>
       </c>
       <c r="H365" t="n">
         <v>135405</v>
@@ -10983,7 +10983,7 @@
         <v>9.83500003814697</v>
       </c>
       <c r="G366" t="n">
-        <v>8.96334838867188</v>
+        <v>8.96334743499756</v>
       </c>
       <c r="H366" t="n">
         <v>250182</v>
@@ -11012,7 +11012,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G367" t="n">
-        <v>9.15017795562744</v>
+        <v>9.15017890930176</v>
       </c>
       <c r="H367" t="n">
         <v>95441</v>
@@ -11099,7 +11099,7 @@
         <v>9.40499973297119</v>
       </c>
       <c r="G370" t="n">
-        <v>8.57145690917969</v>
+        <v>8.57145595550537</v>
       </c>
       <c r="H370" t="n">
         <v>122944</v>
@@ -11186,7 +11186,7 @@
         <v>9.65499973297119</v>
       </c>
       <c r="G373" t="n">
-        <v>8.79930019378662</v>
+        <v>8.7992992401123</v>
       </c>
       <c r="H373" t="n">
         <v>110462</v>
@@ -11302,7 +11302,7 @@
         <v>10.0299997329712</v>
       </c>
       <c r="G377" t="n">
-        <v>9.14106464385986</v>
+        <v>9.14106369018555</v>
       </c>
       <c r="H377" t="n">
         <v>66283</v>
@@ -11331,7 +11331,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G378" t="n">
-        <v>9.09549617767334</v>
+        <v>9.09549713134766</v>
       </c>
       <c r="H378" t="n">
         <v>71656</v>
@@ -36651,9 +36651,38 @@
         <v>3.48000001907349</v>
       </c>
       <c r="H1251" t="n">
-        <v>369362</v>
+        <v>373827</v>
       </c>
       <c r="I1251" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1252" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1252" t="n">
+        <v>3.46000003814697</v>
+      </c>
+      <c r="D1252" t="n">
+        <v>3.54399991035461</v>
+      </c>
+      <c r="E1252" t="n">
+        <v>3.43600010871887</v>
+      </c>
+      <c r="F1252" t="n">
+        <v>3.51200008392334</v>
+      </c>
+      <c r="G1252" t="n">
+        <v>3.51200008392334</v>
+      </c>
+      <c r="H1252" t="n">
+        <v>565087</v>
+      </c>
+      <c r="I1252" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ARIS.MI.xlsx
+++ b/data/ARIS.MI.xlsx
@@ -456,7 +456,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G3" t="n">
-        <v>9.34524440765381</v>
+        <v>9.34524345397949</v>
       </c>
       <c r="H3" t="n">
         <v>1460667</v>
@@ -485,7 +485,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G4" t="n">
-        <v>9.17451477050781</v>
+        <v>9.1745138168335</v>
       </c>
       <c r="H4" t="n">
         <v>732483</v>
@@ -688,7 +688,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G11" t="n">
-        <v>9.23741340637207</v>
+        <v>9.23741436004639</v>
       </c>
       <c r="H11" t="n">
         <v>199132</v>
@@ -862,7 +862,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G17" t="n">
-        <v>8.83305263519287</v>
+        <v>8.83305358886719</v>
       </c>
       <c r="H17" t="n">
         <v>156842</v>
@@ -920,7 +920,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G19" t="n">
-        <v>8.71623706817627</v>
+        <v>8.71623802185059</v>
       </c>
       <c r="H19" t="n">
         <v>172790</v>
@@ -949,7 +949,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G20" t="n">
-        <v>9.12958526611328</v>
+        <v>9.12958431243896</v>
       </c>
       <c r="H20" t="n">
         <v>431091</v>
@@ -978,7 +978,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G21" t="n">
-        <v>9.07567119598389</v>
+        <v>9.07567024230957</v>
       </c>
       <c r="H21" t="n">
         <v>404417</v>
@@ -1007,7 +1007,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G22" t="n">
-        <v>8.85102462768555</v>
+        <v>8.85102367401123</v>
       </c>
       <c r="H22" t="n">
         <v>186957</v>
@@ -1036,7 +1036,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G23" t="n">
-        <v>9.07567119598389</v>
+        <v>9.07567024230957</v>
       </c>
       <c r="H23" t="n">
         <v>179305</v>
@@ -1065,7 +1065,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G24" t="n">
-        <v>9.12958526611328</v>
+        <v>9.12958431243896</v>
       </c>
       <c r="H24" t="n">
         <v>61464</v>
@@ -1123,7 +1123,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G26" t="n">
-        <v>9.12958526611328</v>
+        <v>9.12958431243896</v>
       </c>
       <c r="H26" t="n">
         <v>53953</v>
@@ -1210,7 +1210,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G29" t="n">
-        <v>9.74062061309814</v>
+        <v>9.74061965942383</v>
       </c>
       <c r="H29" t="n">
         <v>87322</v>
@@ -1297,7 +1297,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G32" t="n">
-        <v>9.17451477050781</v>
+        <v>9.1745138168335</v>
       </c>
       <c r="H32" t="n">
         <v>405173</v>
@@ -1326,7 +1326,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G33" t="n">
-        <v>9.63278961181641</v>
+        <v>9.63279151916504</v>
       </c>
       <c r="H33" t="n">
         <v>261751</v>
@@ -1413,7 +1413,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G36" t="n">
-        <v>10.1988964080811</v>
+        <v>10.1988954544067</v>
       </c>
       <c r="H36" t="n">
         <v>477707</v>
@@ -1500,7 +1500,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G39" t="n">
-        <v>9.62380504608154</v>
+        <v>9.62380409240723</v>
       </c>
       <c r="H39" t="n">
         <v>115964</v>
@@ -1616,7 +1616,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G43" t="n">
-        <v>9.17451477050781</v>
+        <v>9.1745138168335</v>
       </c>
       <c r="H43" t="n">
         <v>290667</v>
@@ -1732,7 +1732,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G47" t="n">
-        <v>9.34524440765381</v>
+        <v>9.34524345397949</v>
       </c>
       <c r="H47" t="n">
         <v>331892</v>
@@ -1761,7 +1761,7 @@
         <v>10.4899997711182</v>
       </c>
       <c r="G48" t="n">
-        <v>9.42611598968506</v>
+        <v>9.42611694335938</v>
       </c>
       <c r="H48" t="n">
         <v>67641</v>
@@ -1790,7 +1790,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G49" t="n">
-        <v>9.34524440765381</v>
+        <v>9.34524345397949</v>
       </c>
       <c r="H49" t="n">
         <v>164923</v>
@@ -1848,7 +1848,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G51" t="n">
-        <v>9.16552734375</v>
+        <v>9.16552829742432</v>
       </c>
       <c r="H51" t="n">
         <v>170220</v>
@@ -1877,7 +1877,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G52" t="n">
-        <v>9.12958526611328</v>
+        <v>9.12958431243896</v>
       </c>
       <c r="H52" t="n">
         <v>73644</v>
@@ -1935,7 +1935,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G54" t="n">
-        <v>9.16552734375</v>
+        <v>9.16552829742432</v>
       </c>
       <c r="H54" t="n">
         <v>213651</v>
@@ -2080,7 +2080,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G59" t="n">
-        <v>9.19248580932617</v>
+        <v>9.19248485565186</v>
       </c>
       <c r="H59" t="n">
         <v>486352</v>
@@ -2109,7 +2109,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G60" t="n">
-        <v>8.95885372161865</v>
+        <v>8.95885467529297</v>
       </c>
       <c r="H60" t="n">
         <v>207313</v>
@@ -2138,7 +2138,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G61" t="n">
-        <v>8.71623706817627</v>
+        <v>8.71623802185059</v>
       </c>
       <c r="H61" t="n">
         <v>224870</v>
@@ -2167,7 +2167,7 @@
         <v>9.41499996185303</v>
       </c>
       <c r="G62" t="n">
-        <v>8.4601411819458</v>
+        <v>8.46014213562012</v>
       </c>
       <c r="H62" t="n">
         <v>251208</v>
@@ -2283,7 +2283,7 @@
         <v>9.20499992370605</v>
       </c>
       <c r="G66" t="n">
-        <v>8.27143955230713</v>
+        <v>8.27144050598145</v>
       </c>
       <c r="H66" t="n">
         <v>126081</v>
@@ -2312,7 +2312,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G67" t="n">
-        <v>7.70982599258423</v>
+        <v>7.70982646942139</v>
       </c>
       <c r="H67" t="n">
         <v>139521</v>
@@ -2341,7 +2341,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G68" t="n">
-        <v>8.03331470489502</v>
+        <v>8.03331565856934</v>
       </c>
       <c r="H68" t="n">
         <v>139296</v>
@@ -2370,7 +2370,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G69" t="n">
-        <v>7.95244407653809</v>
+        <v>7.95244312286377</v>
       </c>
       <c r="H69" t="n">
         <v>230882</v>
@@ -2399,7 +2399,7 @@
         <v>7.875</v>
       </c>
       <c r="G70" t="n">
-        <v>7.0763258934021</v>
+        <v>7.07632684707642</v>
       </c>
       <c r="H70" t="n">
         <v>381529</v>
@@ -2457,7 +2457,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G72" t="n">
-        <v>7.42227983474731</v>
+        <v>7.42228078842163</v>
       </c>
       <c r="H72" t="n">
         <v>235581</v>
@@ -2486,7 +2486,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G73" t="n">
-        <v>7.79069900512695</v>
+        <v>7.79069948196411</v>
       </c>
       <c r="H73" t="n">
         <v>361935</v>
@@ -2544,7 +2544,7 @@
         <v>8.78499984741211</v>
       </c>
       <c r="G75" t="n">
-        <v>7.89403629302979</v>
+        <v>7.89403581619263</v>
       </c>
       <c r="H75" t="n">
         <v>220029</v>
@@ -2602,7 +2602,7 @@
         <v>9.51500034332275</v>
       </c>
       <c r="G77" t="n">
-        <v>8.54999923706055</v>
+        <v>8.55000019073486</v>
       </c>
       <c r="H77" t="n">
         <v>369586</v>
@@ -2631,7 +2631,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G78" t="n">
-        <v>9.23741340637207</v>
+        <v>9.23741436004639</v>
       </c>
       <c r="H78" t="n">
         <v>643900</v>
@@ -2689,7 +2689,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G80" t="n">
-        <v>9.19248580932617</v>
+        <v>9.19248485565186</v>
       </c>
       <c r="H80" t="n">
         <v>1158996</v>
@@ -2718,7 +2718,7 @@
         <v>9.71500015258789</v>
       </c>
       <c r="G81" t="n">
-        <v>8.72971630096436</v>
+        <v>8.72971725463867</v>
       </c>
       <c r="H81" t="n">
         <v>221597</v>
@@ -2747,7 +2747,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G82" t="n">
-        <v>9.07567119598389</v>
+        <v>9.07567024230957</v>
       </c>
       <c r="H82" t="n">
         <v>174088</v>
@@ -2776,7 +2776,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G83" t="n">
-        <v>8.74319458007812</v>
+        <v>8.74319362640381</v>
       </c>
       <c r="H83" t="n">
         <v>214161</v>
@@ -2863,7 +2863,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G86" t="n">
-        <v>8.55898571014404</v>
+        <v>8.55898475646973</v>
       </c>
       <c r="H86" t="n">
         <v>136560</v>
@@ -2892,7 +2892,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G87" t="n">
-        <v>8.67130851745605</v>
+        <v>8.67130756378174</v>
       </c>
       <c r="H87" t="n">
         <v>120344</v>
@@ -2979,7 +2979,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G90" t="n">
-        <v>8.55898571014404</v>
+        <v>8.55898475646973</v>
       </c>
       <c r="H90" t="n">
         <v>75199</v>
@@ -3008,7 +3008,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G91" t="n">
-        <v>8.5185489654541</v>
+        <v>8.51854801177979</v>
       </c>
       <c r="H91" t="n">
         <v>163375</v>
@@ -3037,7 +3037,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G92" t="n">
-        <v>8.71623706817627</v>
+        <v>8.71623802185059</v>
       </c>
       <c r="H92" t="n">
         <v>223170</v>
@@ -3095,7 +3095,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G94" t="n">
-        <v>8.18607425689697</v>
+        <v>8.18607330322266</v>
       </c>
       <c r="H94" t="n">
         <v>173589</v>
@@ -3124,7 +3124,7 @@
         <v>9.25</v>
       </c>
       <c r="G95" t="n">
-        <v>8.31187629699707</v>
+        <v>8.31187534332275</v>
       </c>
       <c r="H95" t="n">
         <v>70088</v>
@@ -3153,7 +3153,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G96" t="n">
-        <v>8.24897575378418</v>
+        <v>8.24897480010986</v>
       </c>
       <c r="H96" t="n">
         <v>89220</v>
@@ -3182,7 +3182,7 @@
         <v>9.25</v>
       </c>
       <c r="G97" t="n">
-        <v>8.31187629699707</v>
+        <v>8.31187534332275</v>
       </c>
       <c r="H97" t="n">
         <v>77345</v>
@@ -3211,7 +3211,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G98" t="n">
-        <v>8.62637996673584</v>
+        <v>8.62637901306152</v>
       </c>
       <c r="H98" t="n">
         <v>131848</v>
@@ -3240,7 +3240,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G99" t="n">
-        <v>8.45564937591553</v>
+        <v>8.45564842224121</v>
       </c>
       <c r="H99" t="n">
         <v>126252</v>
@@ -3298,7 +3298,7 @@
         <v>9.75</v>
       </c>
       <c r="G101" t="n">
-        <v>8.76116752624512</v>
+        <v>8.7611665725708</v>
       </c>
       <c r="H101" t="n">
         <v>134667</v>
@@ -3356,7 +3356,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G103" t="n">
-        <v>8.71623706817627</v>
+        <v>8.71623802185059</v>
       </c>
       <c r="H103" t="n">
         <v>216807</v>
@@ -3414,7 +3414,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G105" t="n">
-        <v>8.55898571014404</v>
+        <v>8.55898475646973</v>
       </c>
       <c r="H105" t="n">
         <v>167622</v>
@@ -3443,7 +3443,7 @@
         <v>9.71500015258789</v>
       </c>
       <c r="G106" t="n">
-        <v>8.72971630096436</v>
+        <v>8.72971725463867</v>
       </c>
       <c r="H106" t="n">
         <v>81637</v>
@@ -3472,7 +3472,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G107" t="n">
-        <v>8.67130851745605</v>
+        <v>8.67130756378174</v>
       </c>
       <c r="H107" t="n">
         <v>107921</v>
@@ -3501,7 +3501,7 @@
         <v>9.53499984741211</v>
       </c>
       <c r="G108" t="n">
-        <v>8.56797122955322</v>
+        <v>8.56797218322754</v>
       </c>
       <c r="H108" t="n">
         <v>345401</v>
@@ -3530,7 +3530,7 @@
         <v>9</v>
       </c>
       <c r="G109" t="n">
-        <v>8.08723068237305</v>
+        <v>8.08722972869873</v>
       </c>
       <c r="H109" t="n">
         <v>151306</v>
@@ -3559,7 +3559,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G110" t="n">
-        <v>7.89852857589722</v>
+        <v>7.89852905273438</v>
       </c>
       <c r="H110" t="n">
         <v>136469</v>
@@ -3588,7 +3588,7 @@
         <v>9.25500011444092</v>
       </c>
       <c r="G111" t="n">
-        <v>8.31636905670166</v>
+        <v>8.31636810302734</v>
       </c>
       <c r="H111" t="n">
         <v>491155</v>
@@ -3617,7 +3617,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G112" t="n">
-        <v>8.10520267486572</v>
+        <v>8.10520172119141</v>
       </c>
       <c r="H112" t="n">
         <v>245680</v>
@@ -3646,7 +3646,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G113" t="n">
-        <v>7.99737215042114</v>
+        <v>7.99737167358398</v>
       </c>
       <c r="H113" t="n">
         <v>164165</v>
@@ -3675,7 +3675,7 @@
         <v>8.6850004196167</v>
       </c>
       <c r="G114" t="n">
-        <v>7.80417728424072</v>
+        <v>7.80417823791504</v>
       </c>
       <c r="H114" t="n">
         <v>103341</v>
@@ -3704,7 +3704,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G115" t="n">
-        <v>7.80867052078247</v>
+        <v>7.80867099761963</v>
       </c>
       <c r="H115" t="n">
         <v>87012</v>
@@ -3762,7 +3762,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G117" t="n">
-        <v>8.32086086273193</v>
+        <v>8.32086277008057</v>
       </c>
       <c r="H117" t="n">
         <v>146034</v>
@@ -3820,7 +3820,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G119" t="n">
-        <v>8.62637996673584</v>
+        <v>8.62637901306152</v>
       </c>
       <c r="H119" t="n">
         <v>249483</v>
@@ -3878,7 +3878,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G121" t="n">
-        <v>8.74319458007812</v>
+        <v>8.74319362640381</v>
       </c>
       <c r="H121" t="n">
         <v>164576</v>
@@ -3907,7 +3907,7 @@
         <v>9.94499969482422</v>
       </c>
       <c r="G122" t="n">
-        <v>8.9363899230957</v>
+        <v>8.93638896942139</v>
       </c>
       <c r="H122" t="n">
         <v>223439</v>
@@ -3936,7 +3936,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G123" t="n">
-        <v>8.96334743499756</v>
+        <v>8.96334838867188</v>
       </c>
       <c r="H123" t="n">
         <v>150460</v>
@@ -3965,7 +3965,7 @@
         <v>9.78499984741211</v>
       </c>
       <c r="G124" t="n">
-        <v>8.91777896881104</v>
+        <v>8.91777801513672</v>
       </c>
       <c r="H124" t="n">
         <v>154912</v>
@@ -4052,7 +4052,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G127" t="n">
-        <v>9.2504301071167</v>
+        <v>9.25042915344238</v>
       </c>
       <c r="H127" t="n">
         <v>154830</v>
@@ -4081,7 +4081,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>9.47827339172363</v>
+        <v>9.47827243804932</v>
       </c>
       <c r="H128" t="n">
         <v>307614</v>
@@ -4110,7 +4110,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G129" t="n">
-        <v>9.51472759246826</v>
+        <v>9.51472663879395</v>
       </c>
       <c r="H129" t="n">
         <v>242971</v>
@@ -4139,7 +4139,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G130" t="n">
-        <v>9.35068130493164</v>
+        <v>9.35068035125732</v>
       </c>
       <c r="H130" t="n">
         <v>2902048</v>
@@ -4168,7 +4168,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G131" t="n">
-        <v>9.20486164093018</v>
+        <v>9.20486068725586</v>
       </c>
       <c r="H131" t="n">
         <v>105012</v>
@@ -4226,7 +4226,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G133" t="n">
-        <v>9.30511283874512</v>
+        <v>9.3051118850708</v>
       </c>
       <c r="H133" t="n">
         <v>80187</v>
@@ -4284,7 +4284,7 @@
         <v>10.25</v>
       </c>
       <c r="G135" t="n">
-        <v>9.34156703948975</v>
+        <v>9.34156608581543</v>
       </c>
       <c r="H135" t="n">
         <v>52292</v>
@@ -4313,7 +4313,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G136" t="n">
-        <v>9.29599666595459</v>
+        <v>9.29599857330322</v>
       </c>
       <c r="H136" t="n">
         <v>59750</v>
@@ -4342,7 +4342,7 @@
         <v>9.84500026702881</v>
       </c>
       <c r="G137" t="n">
-        <v>8.97246074676514</v>
+        <v>8.97246170043945</v>
       </c>
       <c r="H137" t="n">
         <v>84612</v>
@@ -4429,7 +4429,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G140" t="n">
-        <v>7.95628070831299</v>
+        <v>7.95628023147583</v>
       </c>
       <c r="H140" t="n">
         <v>163728</v>
@@ -4516,7 +4516,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G143" t="n">
-        <v>7.73755025863647</v>
+        <v>7.73755168914795</v>
       </c>
       <c r="H143" t="n">
         <v>68881</v>
@@ -4603,7 +4603,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G146" t="n">
-        <v>7.34566164016724</v>
+        <v>7.34566211700439</v>
       </c>
       <c r="H146" t="n">
         <v>105071</v>
@@ -4632,7 +4632,7 @@
         <v>7.50500011444092</v>
       </c>
       <c r="G147" t="n">
-        <v>6.83984994888306</v>
+        <v>6.8398494720459</v>
       </c>
       <c r="H147" t="n">
         <v>173369</v>
@@ -4661,7 +4661,7 @@
         <v>7.375</v>
       </c>
       <c r="G148" t="n">
-        <v>6.72137069702148</v>
+        <v>6.7213716506958</v>
       </c>
       <c r="H148" t="n">
         <v>158803</v>
@@ -4748,7 +4748,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G151" t="n">
-        <v>7.0266809463501</v>
+        <v>7.02668142318726</v>
       </c>
       <c r="H151" t="n">
         <v>83909</v>
@@ -4864,7 +4864,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G155" t="n">
-        <v>6.74415588378906</v>
+        <v>6.7441554069519</v>
       </c>
       <c r="H155" t="n">
         <v>105692</v>
@@ -4893,7 +4893,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G156" t="n">
-        <v>6.68035888671875</v>
+        <v>6.68035936355591</v>
       </c>
       <c r="H156" t="n">
         <v>131028</v>
@@ -4922,7 +4922,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G157" t="n">
-        <v>6.78061056137085</v>
+        <v>6.78061008453369</v>
       </c>
       <c r="H157" t="n">
         <v>109900</v>
@@ -4951,7 +4951,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G158" t="n">
-        <v>6.92643022537231</v>
+        <v>6.92642974853516</v>
       </c>
       <c r="H158" t="n">
         <v>58691</v>
@@ -5009,7 +5009,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G160" t="n">
-        <v>6.68035888671875</v>
+        <v>6.68035936355591</v>
       </c>
       <c r="H160" t="n">
         <v>64175</v>
@@ -5096,7 +5096,7 @@
         <v>7.31500005722046</v>
       </c>
       <c r="G163" t="n">
-        <v>6.66668891906738</v>
+        <v>6.66668844223022</v>
       </c>
       <c r="H163" t="n">
         <v>63073</v>
@@ -5183,7 +5183,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G166" t="n">
-        <v>6.9628849029541</v>
+        <v>6.96288442611694</v>
       </c>
       <c r="H166" t="n">
         <v>25056</v>
@@ -5212,7 +5212,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G167" t="n">
-        <v>6.9628849029541</v>
+        <v>6.96288442611694</v>
       </c>
       <c r="H167" t="n">
         <v>115212</v>
@@ -5270,7 +5270,7 @@
         <v>7.72499990463257</v>
       </c>
       <c r="G169" t="n">
-        <v>7.04035139083862</v>
+        <v>7.04035186767578</v>
       </c>
       <c r="H169" t="n">
         <v>97576</v>
@@ -5299,7 +5299,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G170" t="n">
-        <v>6.74415588378906</v>
+        <v>6.7441554069519</v>
       </c>
       <c r="H170" t="n">
         <v>54127</v>
@@ -5357,7 +5357,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G172" t="n">
-        <v>7.2681941986084</v>
+        <v>7.26819467544556</v>
       </c>
       <c r="H172" t="n">
         <v>107198</v>
@@ -5589,7 +5589,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G180" t="n">
-        <v>7.24996662139893</v>
+        <v>7.24996709823608</v>
       </c>
       <c r="H180" t="n">
         <v>63885</v>
@@ -5618,7 +5618,7 @@
         <v>8</v>
       </c>
       <c r="G181" t="n">
-        <v>7.29097843170166</v>
+        <v>7.29097938537598</v>
       </c>
       <c r="H181" t="n">
         <v>44729</v>
@@ -5647,7 +5647,7 @@
         <v>8</v>
       </c>
       <c r="G182" t="n">
-        <v>7.29097843170166</v>
+        <v>7.29097938537598</v>
       </c>
       <c r="H182" t="n">
         <v>68137</v>
@@ -5705,7 +5705,7 @@
         <v>8</v>
       </c>
       <c r="G184" t="n">
-        <v>7.29097843170166</v>
+        <v>7.29097938537598</v>
       </c>
       <c r="H184" t="n">
         <v>53674</v>
@@ -5763,7 +5763,7 @@
         <v>8</v>
       </c>
       <c r="G186" t="n">
-        <v>7.29097843170166</v>
+        <v>7.29097938537598</v>
       </c>
       <c r="H186" t="n">
         <v>98582</v>
@@ -5792,7 +5792,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G187" t="n">
-        <v>7.30009269714355</v>
+        <v>7.30009317398071</v>
       </c>
       <c r="H187" t="n">
         <v>50930</v>
@@ -5850,7 +5850,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G189" t="n">
-        <v>7.21351194381714</v>
+        <v>7.2135124206543</v>
       </c>
       <c r="H189" t="n">
         <v>58048</v>
@@ -5908,7 +5908,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G191" t="n">
-        <v>6.9628849029541</v>
+        <v>6.96288442611694</v>
       </c>
       <c r="H191" t="n">
         <v>64057</v>
@@ -6053,7 +6053,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G196" t="n">
-        <v>6.85351991653442</v>
+        <v>6.85352039337158</v>
       </c>
       <c r="H196" t="n">
         <v>51472</v>
@@ -6082,7 +6082,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G197" t="n">
-        <v>6.92643022537231</v>
+        <v>6.92642974853516</v>
       </c>
       <c r="H197" t="n">
         <v>94339</v>
@@ -6111,7 +6111,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G198" t="n">
-        <v>6.56188106536865</v>
+        <v>6.56188058853149</v>
       </c>
       <c r="H198" t="n">
         <v>52394</v>
@@ -6140,7 +6140,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G199" t="n">
-        <v>6.42517518997192</v>
+        <v>6.42517566680908</v>
       </c>
       <c r="H199" t="n">
         <v>115768</v>
@@ -6198,7 +6198,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G201" t="n">
-        <v>6.6302342414856</v>
+        <v>6.63023376464844</v>
       </c>
       <c r="H201" t="n">
         <v>127295</v>
@@ -6227,7 +6227,7 @@
         <v>7.52500009536743</v>
       </c>
       <c r="G202" t="n">
-        <v>6.85807752609253</v>
+        <v>6.85807657241821</v>
       </c>
       <c r="H202" t="n">
         <v>80911</v>
@@ -6256,7 +6256,7 @@
         <v>7.75</v>
       </c>
       <c r="G203" t="n">
-        <v>7.06313562393188</v>
+        <v>7.06313610076904</v>
       </c>
       <c r="H203" t="n">
         <v>74023</v>
@@ -6285,7 +6285,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G204" t="n">
-        <v>6.83073616027832</v>
+        <v>6.83073568344116</v>
       </c>
       <c r="H204" t="n">
         <v>55532</v>
@@ -6314,7 +6314,7 @@
         <v>7.33500003814697</v>
       </c>
       <c r="G205" t="n">
-        <v>6.68491649627686</v>
+        <v>6.6849160194397</v>
       </c>
       <c r="H205" t="n">
         <v>69663</v>
@@ -6343,7 +6343,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G206" t="n">
-        <v>6.69858694076538</v>
+        <v>6.69858646392822</v>
       </c>
       <c r="H206" t="n">
         <v>115365</v>
@@ -6372,7 +6372,7 @@
         <v>8.46500015258789</v>
       </c>
       <c r="G207" t="n">
-        <v>7.71476793289185</v>
+        <v>7.71476650238037</v>
       </c>
       <c r="H207" t="n">
         <v>667919</v>
@@ -6401,7 +6401,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G208" t="n">
-        <v>7.55527687072754</v>
+        <v>7.5552773475647</v>
       </c>
       <c r="H208" t="n">
         <v>323484</v>
@@ -6430,7 +6430,7 @@
         <v>8.33500003814697</v>
       </c>
       <c r="G209" t="n">
-        <v>7.59628868103027</v>
+        <v>7.59628915786743</v>
       </c>
       <c r="H209" t="n">
         <v>154677</v>
@@ -6459,7 +6459,7 @@
         <v>8.40499973297119</v>
       </c>
       <c r="G210" t="n">
-        <v>7.66008472442627</v>
+        <v>7.66008520126343</v>
       </c>
       <c r="H210" t="n">
         <v>162822</v>
@@ -6488,7 +6488,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G211" t="n">
-        <v>7.70565319061279</v>
+        <v>7.70565271377563</v>
       </c>
       <c r="H211" t="n">
         <v>238638</v>
@@ -6604,7 +6604,7 @@
         <v>8.48499965667725</v>
       </c>
       <c r="G215" t="n">
-        <v>7.73299407958984</v>
+        <v>7.732994556427</v>
       </c>
       <c r="H215" t="n">
         <v>190999</v>
@@ -6662,7 +6662,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G217" t="n">
-        <v>7.93805313110352</v>
+        <v>7.93805265426636</v>
       </c>
       <c r="H217" t="n">
         <v>247020</v>
@@ -6749,7 +6749,7 @@
         <v>9.03499984741211</v>
       </c>
       <c r="G220" t="n">
-        <v>8.23424911499023</v>
+        <v>8.23425006866455</v>
       </c>
       <c r="H220" t="n">
         <v>263459</v>
@@ -6778,7 +6778,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G221" t="n">
-        <v>8.19323635101318</v>
+        <v>8.1932373046875</v>
       </c>
       <c r="H221" t="n">
         <v>194602</v>
@@ -6807,7 +6807,7 @@
         <v>8.84500026702881</v>
       </c>
       <c r="G222" t="n">
-        <v>8.0610876083374</v>
+        <v>8.06108856201172</v>
       </c>
       <c r="H222" t="n">
         <v>71498</v>
@@ -6923,7 +6923,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G226" t="n">
-        <v>7.65552806854248</v>
+        <v>7.65552759170532</v>
       </c>
       <c r="H226" t="n">
         <v>242848</v>
@@ -7010,7 +7010,7 @@
         <v>8.60499954223633</v>
       </c>
       <c r="G229" t="n">
-        <v>7.84235954284668</v>
+        <v>7.84235906600952</v>
       </c>
       <c r="H229" t="n">
         <v>228869</v>
@@ -7039,7 +7039,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G230" t="n">
-        <v>7.59173154830933</v>
+        <v>7.59173202514648</v>
       </c>
       <c r="H230" t="n">
         <v>175936</v>
@@ -7068,7 +7068,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>7.48236703872681</v>
+        <v>7.48236751556396</v>
       </c>
       <c r="H231" t="n">
         <v>150112</v>
@@ -7097,7 +7097,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G232" t="n">
-        <v>7.54160642623901</v>
+        <v>7.54160594940186</v>
       </c>
       <c r="H232" t="n">
         <v>183612</v>
@@ -7126,7 +7126,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G233" t="n">
-        <v>7.60084629058838</v>
+        <v>7.60084533691406</v>
       </c>
       <c r="H233" t="n">
         <v>108751</v>
@@ -7155,7 +7155,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G234" t="n">
-        <v>7.85602951049805</v>
+        <v>7.85602998733521</v>
       </c>
       <c r="H234" t="n">
         <v>185968</v>
@@ -7213,7 +7213,7 @@
         <v>8.59500026702881</v>
       </c>
       <c r="G236" t="n">
-        <v>7.83324480056763</v>
+        <v>7.83324575424194</v>
       </c>
       <c r="H236" t="n">
         <v>75722</v>
@@ -7242,7 +7242,7 @@
         <v>8.63500022888184</v>
       </c>
       <c r="G237" t="n">
-        <v>7.86970043182373</v>
+        <v>7.86970090866089</v>
       </c>
       <c r="H237" t="n">
         <v>68684</v>
@@ -7300,7 +7300,7 @@
         <v>8.50500011444092</v>
       </c>
       <c r="G239" t="n">
-        <v>7.75122165679932</v>
+        <v>7.75122261047363</v>
       </c>
       <c r="H239" t="n">
         <v>97800</v>
@@ -7416,7 +7416,7 @@
         <v>8.29500007629395</v>
       </c>
       <c r="G243" t="n">
-        <v>7.55983352661133</v>
+        <v>7.55983304977417</v>
       </c>
       <c r="H243" t="n">
         <v>179111</v>
@@ -7474,7 +7474,7 @@
         <v>8.15499973297119</v>
       </c>
       <c r="G245" t="n">
-        <v>7.43224191665649</v>
+        <v>7.43224143981934</v>
       </c>
       <c r="H245" t="n">
         <v>95884</v>
@@ -7503,7 +7503,7 @@
         <v>8.49499988555908</v>
       </c>
       <c r="G246" t="n">
-        <v>7.74210834503174</v>
+        <v>7.74210786819458</v>
       </c>
       <c r="H246" t="n">
         <v>144625</v>
@@ -7561,7 +7561,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G248" t="n">
-        <v>7.73755025863647</v>
+        <v>7.73755168914795</v>
       </c>
       <c r="H248" t="n">
         <v>79342</v>
@@ -7619,7 +7619,7 @@
         <v>8.44499969482422</v>
       </c>
       <c r="G250" t="n">
-        <v>7.69653987884521</v>
+        <v>7.69653940200806</v>
       </c>
       <c r="H250" t="n">
         <v>65821</v>
@@ -7648,7 +7648,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G251" t="n">
-        <v>7.76489305496216</v>
+        <v>7.76489353179932</v>
       </c>
       <c r="H251" t="n">
         <v>81589</v>
@@ -7677,7 +7677,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G252" t="n">
-        <v>7.87425756454468</v>
+        <v>7.87425661087036</v>
       </c>
       <c r="H252" t="n">
         <v>52613</v>
@@ -7764,7 +7764,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G255" t="n">
-        <v>8.06564521789551</v>
+        <v>8.06564617156982</v>
       </c>
       <c r="H255" t="n">
         <v>80541</v>
@@ -7793,7 +7793,7 @@
         <v>9.08500003814697</v>
       </c>
       <c r="G256" t="n">
-        <v>8.27981853485107</v>
+        <v>8.27981758117676</v>
       </c>
       <c r="H256" t="n">
         <v>275857</v>
@@ -7822,7 +7822,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G257" t="n">
-        <v>8.3800687789917</v>
+        <v>8.38006782531738</v>
       </c>
       <c r="H257" t="n">
         <v>166742</v>
@@ -7851,7 +7851,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G258" t="n">
-        <v>8.34817028045654</v>
+        <v>8.34817123413086</v>
       </c>
       <c r="H258" t="n">
         <v>65591</v>
@@ -7909,7 +7909,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G260" t="n">
-        <v>8.87676620483398</v>
+        <v>8.8767671585083</v>
       </c>
       <c r="H260" t="n">
         <v>299785</v>
@@ -7996,7 +7996,7 @@
         <v>9.5</v>
       </c>
       <c r="G263" t="n">
-        <v>8.65803813934326</v>
+        <v>8.65803718566895</v>
       </c>
       <c r="H263" t="n">
         <v>120885</v>
@@ -8054,7 +8054,7 @@
         <v>9.23499965667725</v>
       </c>
       <c r="G265" t="n">
-        <v>8.41652297973633</v>
+        <v>8.41652393341064</v>
       </c>
       <c r="H265" t="n">
         <v>63237</v>
@@ -8141,7 +8141,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G268" t="n">
-        <v>8.42107963562012</v>
+        <v>8.42108058929443</v>
       </c>
       <c r="H268" t="n">
         <v>38362</v>
@@ -8170,7 +8170,7 @@
         <v>9.5</v>
       </c>
       <c r="G269" t="n">
-        <v>8.65803813934326</v>
+        <v>8.65803718566895</v>
       </c>
       <c r="H269" t="n">
         <v>49713</v>
@@ -8228,7 +8228,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G271" t="n">
-        <v>8.47576236724854</v>
+        <v>8.47576332092285</v>
       </c>
       <c r="H271" t="n">
         <v>166452</v>
@@ -8286,7 +8286,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G273" t="n">
-        <v>8.40285301208496</v>
+        <v>8.40285396575928</v>
       </c>
       <c r="H273" t="n">
         <v>52732</v>
@@ -8315,7 +8315,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G274" t="n">
-        <v>8.28437614440918</v>
+        <v>8.28437519073486</v>
       </c>
       <c r="H274" t="n">
         <v>67078</v>
@@ -8489,7 +8489,7 @@
         <v>9.40499973297119</v>
       </c>
       <c r="G280" t="n">
-        <v>8.57145595550537</v>
+        <v>8.57145690917969</v>
       </c>
       <c r="H280" t="n">
         <v>67802</v>
@@ -8547,7 +8547,7 @@
         <v>9.625</v>
       </c>
       <c r="G282" t="n">
-        <v>8.77195930480957</v>
+        <v>8.77195835113525</v>
       </c>
       <c r="H282" t="n">
         <v>30701</v>
@@ -8576,7 +8576,7 @@
         <v>9.98499965667725</v>
       </c>
       <c r="G283" t="n">
-        <v>9.10005187988281</v>
+        <v>9.10005283355713</v>
       </c>
       <c r="H283" t="n">
         <v>197501</v>
@@ -8634,7 +8634,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G285" t="n">
-        <v>9.29599666595459</v>
+        <v>9.29599857330322</v>
       </c>
       <c r="H285" t="n">
         <v>110062</v>
@@ -8663,7 +8663,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G286" t="n">
-        <v>9.17751979827881</v>
+        <v>9.17751884460449</v>
       </c>
       <c r="H286" t="n">
         <v>123243</v>
@@ -8895,7 +8895,7 @@
         <v>9.5</v>
       </c>
       <c r="G294" t="n">
-        <v>8.65803813934326</v>
+        <v>8.65803718566895</v>
       </c>
       <c r="H294" t="n">
         <v>186325</v>
@@ -8953,7 +8953,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G296" t="n">
-        <v>8.63069534301758</v>
+        <v>8.63069725036621</v>
       </c>
       <c r="H296" t="n">
         <v>142335</v>
@@ -8982,7 +8982,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G297" t="n">
-        <v>8.8220853805542</v>
+        <v>8.82208442687988</v>
       </c>
       <c r="H297" t="n">
         <v>184820</v>
@@ -9011,7 +9011,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G298" t="n">
-        <v>9.04992771148682</v>
+        <v>9.04992866516113</v>
       </c>
       <c r="H298" t="n">
         <v>175620</v>
@@ -9069,7 +9069,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G300" t="n">
-        <v>8.99524593353271</v>
+        <v>8.9952449798584</v>
       </c>
       <c r="H300" t="n">
         <v>84628</v>
@@ -9098,7 +9098,7 @@
         <v>9.625</v>
       </c>
       <c r="G301" t="n">
-        <v>8.77195930480957</v>
+        <v>8.77195835113525</v>
       </c>
       <c r="H301" t="n">
         <v>62785</v>
@@ -9243,7 +9243,7 @@
         <v>9.57499980926514</v>
       </c>
       <c r="G306" t="n">
-        <v>8.72638988494873</v>
+        <v>8.72639083862305</v>
       </c>
       <c r="H306" t="n">
         <v>170795</v>
@@ -9359,7 +9359,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G310" t="n">
-        <v>8.71271991729736</v>
+        <v>8.71272087097168</v>
       </c>
       <c r="H310" t="n">
         <v>71168</v>
@@ -9417,7 +9417,7 @@
         <v>9.84500026702881</v>
       </c>
       <c r="G312" t="n">
-        <v>8.97246074676514</v>
+        <v>8.97246170043945</v>
       </c>
       <c r="H312" t="n">
         <v>201439</v>
@@ -9446,7 +9446,7 @@
         <v>9.86499977111816</v>
       </c>
       <c r="G313" t="n">
-        <v>8.99068832397461</v>
+        <v>8.99068737030029</v>
       </c>
       <c r="H313" t="n">
         <v>95525</v>
@@ -9533,7 +9533,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G316" t="n">
-        <v>8.63981056213379</v>
+        <v>8.63980960845947</v>
       </c>
       <c r="H316" t="n">
         <v>142054</v>
@@ -9620,7 +9620,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G319" t="n">
-        <v>8.10210037231445</v>
+        <v>8.10210132598877</v>
       </c>
       <c r="H319" t="n">
         <v>152972</v>
@@ -9707,7 +9707,7 @@
         <v>9.23499965667725</v>
       </c>
       <c r="G322" t="n">
-        <v>8.41652297973633</v>
+        <v>8.41652393341064</v>
       </c>
       <c r="H322" t="n">
         <v>57007</v>
@@ -9794,7 +9794,7 @@
         <v>9.6850004196167</v>
       </c>
       <c r="G325" t="n">
-        <v>8.82664108276367</v>
+        <v>8.82664203643799</v>
       </c>
       <c r="H325" t="n">
         <v>499802</v>
@@ -9939,7 +9939,7 @@
         <v>9.84500026702881</v>
       </c>
       <c r="G330" t="n">
-        <v>8.97246074676514</v>
+        <v>8.97246170043945</v>
       </c>
       <c r="H330" t="n">
         <v>120285</v>
@@ -9968,7 +9968,7 @@
         <v>9.58500003814697</v>
       </c>
       <c r="G331" t="n">
-        <v>8.73550510406494</v>
+        <v>8.73550415039062</v>
       </c>
       <c r="H331" t="n">
         <v>128694</v>
@@ -9997,7 +9997,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G332" t="n">
-        <v>8.49398994445801</v>
+        <v>8.49399089813232</v>
       </c>
       <c r="H332" t="n">
         <v>110225</v>
@@ -10055,7 +10055,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G334" t="n">
-        <v>8.37551212310791</v>
+        <v>8.37551116943359</v>
       </c>
       <c r="H334" t="n">
         <v>66953</v>
@@ -10200,7 +10200,7 @@
         <v>9.36499977111816</v>
       </c>
       <c r="G339" t="n">
-        <v>8.53500175476074</v>
+        <v>8.53500080108643</v>
       </c>
       <c r="H339" t="n">
         <v>78975</v>
@@ -10229,7 +10229,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G340" t="n">
-        <v>8.64892292022705</v>
+        <v>8.64892387390137</v>
       </c>
       <c r="H340" t="n">
         <v>60887</v>
@@ -10258,7 +10258,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G341" t="n">
-        <v>8.42107963562012</v>
+        <v>8.42108058929443</v>
       </c>
       <c r="H341" t="n">
         <v>61904</v>
@@ -10316,7 +10316,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G343" t="n">
-        <v>8.53955936431885</v>
+        <v>8.53955841064453</v>
       </c>
       <c r="H343" t="n">
         <v>356528</v>
@@ -10345,7 +10345,7 @@
         <v>9.57499980926514</v>
       </c>
       <c r="G344" t="n">
-        <v>8.72638988494873</v>
+        <v>8.72639083862305</v>
       </c>
       <c r="H344" t="n">
         <v>48723</v>
@@ -10374,7 +10374,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G345" t="n">
-        <v>8.87676620483398</v>
+        <v>8.8767671585083</v>
       </c>
       <c r="H345" t="n">
         <v>69041</v>
@@ -10403,7 +10403,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G346" t="n">
-        <v>9.2504301071167</v>
+        <v>9.25042915344238</v>
       </c>
       <c r="H346" t="n">
         <v>231979</v>
@@ -10432,7 +10432,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G347" t="n">
-        <v>9.47827339172363</v>
+        <v>9.47827243804932</v>
       </c>
       <c r="H347" t="n">
         <v>132689</v>
@@ -10461,7 +10461,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G348" t="n">
-        <v>9.13195133209229</v>
+        <v>9.1319522857666</v>
       </c>
       <c r="H348" t="n">
         <v>160856</v>
@@ -10519,7 +10519,7 @@
         <v>9.94499969482422</v>
       </c>
       <c r="G350" t="n">
-        <v>9.06359767913818</v>
+        <v>9.0635986328125</v>
       </c>
       <c r="H350" t="n">
         <v>113297</v>
@@ -10548,7 +10548,7 @@
         <v>9.8149995803833</v>
       </c>
       <c r="G351" t="n">
-        <v>8.94511985778809</v>
+        <v>8.94511890411377</v>
       </c>
       <c r="H351" t="n">
         <v>115103</v>
@@ -10577,7 +10577,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G352" t="n">
-        <v>8.86765384674072</v>
+        <v>8.86765193939209</v>
       </c>
       <c r="H352" t="n">
         <v>54316</v>
@@ -10635,7 +10635,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G354" t="n">
-        <v>9.02258682250977</v>
+        <v>9.02258586883545</v>
       </c>
       <c r="H354" t="n">
         <v>58371</v>
@@ -10693,7 +10693,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G356" t="n">
-        <v>9.02258682250977</v>
+        <v>9.02258586883545</v>
       </c>
       <c r="H356" t="n">
         <v>51175</v>
@@ -10722,7 +10722,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G357" t="n">
-        <v>9.16840553283691</v>
+        <v>9.16840648651123</v>
       </c>
       <c r="H357" t="n">
         <v>43978</v>
@@ -10751,7 +10751,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G358" t="n">
-        <v>9.46915912628174</v>
+        <v>9.46916007995605</v>
       </c>
       <c r="H358" t="n">
         <v>119140</v>
@@ -10838,7 +10838,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G361" t="n">
-        <v>9.47827339172363</v>
+        <v>9.47827243804932</v>
       </c>
       <c r="H361" t="n">
         <v>59625</v>
@@ -10896,7 +10896,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G363" t="n">
-        <v>9.70611476898193</v>
+        <v>9.70611572265625</v>
       </c>
       <c r="H363" t="n">
         <v>79881</v>
@@ -10983,7 +10983,7 @@
         <v>9.83500003814697</v>
       </c>
       <c r="G366" t="n">
-        <v>8.96334743499756</v>
+        <v>8.96334838867188</v>
       </c>
       <c r="H366" t="n">
         <v>250182</v>
@@ -11099,7 +11099,7 @@
         <v>9.40499973297119</v>
       </c>
       <c r="G370" t="n">
-        <v>8.57145595550537</v>
+        <v>8.57145690917969</v>
       </c>
       <c r="H370" t="n">
         <v>122944</v>
@@ -11157,7 +11157,7 @@
         <v>9.5</v>
       </c>
       <c r="G372" t="n">
-        <v>8.65803813934326</v>
+        <v>8.65803718566895</v>
       </c>
       <c r="H372" t="n">
         <v>99284</v>
@@ -11244,7 +11244,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G375" t="n">
-        <v>9.07726955413818</v>
+        <v>9.07726860046387</v>
       </c>
       <c r="H375" t="n">
         <v>116178</v>
@@ -11273,7 +11273,7 @@
         <v>9.94499969482422</v>
       </c>
       <c r="G376" t="n">
-        <v>9.06359767913818</v>
+        <v>9.0635986328125</v>
       </c>
       <c r="H376" t="n">
         <v>50994</v>
@@ -11302,7 +11302,7 @@
         <v>10.0299997329712</v>
       </c>
       <c r="G377" t="n">
-        <v>9.14106369018555</v>
+        <v>9.14106464385986</v>
       </c>
       <c r="H377" t="n">
         <v>66283</v>
@@ -11331,7 +11331,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G378" t="n">
-        <v>9.09549713134766</v>
+        <v>9.09549522399902</v>
       </c>
       <c r="H378" t="n">
         <v>71656</v>
@@ -11360,7 +11360,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G379" t="n">
-        <v>9.3078784942627</v>
+        <v>9.30787754058838</v>
       </c>
       <c r="H379" t="n">
         <v>179086</v>
@@ -11476,7 +11476,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G383" t="n">
-        <v>9.6126012802124</v>
+        <v>9.61260032653809</v>
       </c>
       <c r="H383" t="n">
         <v>186379</v>
@@ -11534,7 +11534,7 @@
         <v>10.25</v>
       </c>
       <c r="G385" t="n">
-        <v>9.46485710144043</v>
+        <v>9.46485614776611</v>
       </c>
       <c r="H385" t="n">
         <v>63321</v>
@@ -11563,7 +11563,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G386" t="n">
-        <v>9.43715476989746</v>
+        <v>9.43715572357178</v>
       </c>
       <c r="H386" t="n">
         <v>588687</v>
@@ -11592,7 +11592,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G387" t="n">
-        <v>9.54796314239502</v>
+        <v>9.5479621887207</v>
       </c>
       <c r="H387" t="n">
         <v>97563</v>
@@ -11621,7 +11621,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G388" t="n">
-        <v>9.63106822967529</v>
+        <v>9.63106918334961</v>
       </c>
       <c r="H388" t="n">
         <v>137120</v>
@@ -11650,7 +11650,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G389" t="n">
-        <v>9.64030265808105</v>
+        <v>9.64030170440674</v>
       </c>
       <c r="H389" t="n">
         <v>168078</v>
@@ -11679,7 +11679,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G390" t="n">
-        <v>9.78804683685303</v>
+        <v>9.78804779052734</v>
       </c>
       <c r="H390" t="n">
         <v>146601</v>
@@ -11737,7 +11737,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G392" t="n">
-        <v>9.64030265808105</v>
+        <v>9.64030170440674</v>
       </c>
       <c r="H392" t="n">
         <v>109538</v>
@@ -11766,7 +11766,7 @@
         <v>10.5</v>
       </c>
       <c r="G393" t="n">
-        <v>9.69570732116699</v>
+        <v>9.69570636749268</v>
       </c>
       <c r="H393" t="n">
         <v>63889</v>
@@ -11795,7 +11795,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G394" t="n">
-        <v>9.84345054626465</v>
+        <v>9.84345149993896</v>
       </c>
       <c r="H394" t="n">
         <v>96545</v>
@@ -11882,7 +11882,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G397" t="n">
-        <v>9.56642913818359</v>
+        <v>9.56643104553223</v>
       </c>
       <c r="H397" t="n">
         <v>124190</v>
@@ -11911,7 +11911,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G398" t="n">
-        <v>9.42792129516602</v>
+        <v>9.4279203414917</v>
       </c>
       <c r="H398" t="n">
         <v>119704</v>
@@ -11969,7 +11969,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G400" t="n">
-        <v>9.18783569335938</v>
+        <v>9.18783664703369</v>
       </c>
       <c r="H400" t="n">
         <v>64703</v>
@@ -11998,7 +11998,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G401" t="n">
-        <v>9.04932594299316</v>
+        <v>9.04932689666748</v>
       </c>
       <c r="H401" t="n">
         <v>96905</v>
@@ -12056,7 +12056,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G403" t="n">
-        <v>8.79539108276367</v>
+        <v>8.79539012908936</v>
       </c>
       <c r="H403" t="n">
         <v>80618</v>
@@ -12114,7 +12114,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G405" t="n">
-        <v>8.58762550354004</v>
+        <v>8.58762645721436</v>
       </c>
       <c r="H405" t="n">
         <v>464509</v>
@@ -12172,7 +12172,7 @@
         <v>9.55500030517578</v>
       </c>
       <c r="G407" t="n">
-        <v>8.82309341430664</v>
+        <v>8.82309246063232</v>
       </c>
       <c r="H407" t="n">
         <v>224972</v>
@@ -12259,7 +12259,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G410" t="n">
-        <v>8.64302921295166</v>
+        <v>8.64303016662598</v>
       </c>
       <c r="H410" t="n">
         <v>151206</v>
@@ -12288,7 +12288,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G411" t="n">
-        <v>8.82771015167236</v>
+        <v>8.82771110534668</v>
       </c>
       <c r="H411" t="n">
         <v>189726</v>
@@ -12346,7 +12346,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G413" t="n">
-        <v>8.42141342163086</v>
+        <v>8.42141437530518</v>
       </c>
       <c r="H413" t="n">
         <v>96990</v>
@@ -12375,7 +12375,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G414" t="n">
-        <v>8.50452041625977</v>
+        <v>8.50451946258545</v>
       </c>
       <c r="H414" t="n">
         <v>71607</v>
@@ -12404,7 +12404,7 @@
         <v>9.21500015258789</v>
       </c>
       <c r="G415" t="n">
-        <v>8.5091381072998</v>
+        <v>8.50913715362549</v>
       </c>
       <c r="H415" t="n">
         <v>86476</v>
@@ -12491,7 +12491,7 @@
         <v>9.57499980926514</v>
       </c>
       <c r="G418" t="n">
-        <v>8.84156036376953</v>
+        <v>8.84156131744385</v>
       </c>
       <c r="H418" t="n">
         <v>93508</v>
@@ -12520,7 +12520,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G419" t="n">
-        <v>8.57839202880859</v>
+        <v>8.57839298248291</v>
       </c>
       <c r="H419" t="n">
         <v>85948</v>
@@ -12636,7 +12636,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G423" t="n">
-        <v>8.0382022857666</v>
+        <v>8.03820323944092</v>
       </c>
       <c r="H423" t="n">
         <v>208593</v>
@@ -12723,7 +12723,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G426" t="n">
-        <v>7.92277717590332</v>
+        <v>7.92277669906616</v>
       </c>
       <c r="H426" t="n">
         <v>224688</v>
@@ -12752,7 +12752,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G427" t="n">
-        <v>7.82120275497437</v>
+        <v>7.82120370864868</v>
       </c>
       <c r="H427" t="n">
         <v>315397</v>
@@ -12781,7 +12781,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G428" t="n">
-        <v>7.82120275497437</v>
+        <v>7.82120370864868</v>
       </c>
       <c r="H428" t="n">
         <v>153923</v>
@@ -12810,7 +12810,7 @@
         <v>8.46500015258789</v>
       </c>
       <c r="G429" t="n">
-        <v>7.81658744812012</v>
+        <v>7.8165864944458</v>
       </c>
       <c r="H429" t="n">
         <v>124892</v>
@@ -12868,7 +12868,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G431" t="n">
-        <v>7.81196975708008</v>
+        <v>7.81196928024292</v>
       </c>
       <c r="H431" t="n">
         <v>211938</v>
@@ -12897,7 +12897,7 @@
         <v>8.42500019073486</v>
       </c>
       <c r="G432" t="n">
-        <v>7.77965116500854</v>
+        <v>7.77965021133423</v>
       </c>
       <c r="H432" t="n">
         <v>499662</v>
@@ -12955,7 +12955,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G434" t="n">
-        <v>7.2579288482666</v>
+        <v>7.25792932510376</v>
       </c>
       <c r="H434" t="n">
         <v>435932</v>
@@ -12984,7 +12984,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G435" t="n">
-        <v>7.06401538848877</v>
+        <v>7.06401491165161</v>
       </c>
       <c r="H435" t="n">
         <v>300120</v>
@@ -13013,7 +13013,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G436" t="n">
-        <v>7.10095119476318</v>
+        <v>7.10095071792603</v>
       </c>
       <c r="H436" t="n">
         <v>185032</v>
@@ -13042,7 +13042,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G437" t="n">
-        <v>7.16558885574341</v>
+        <v>7.16558933258057</v>
       </c>
       <c r="H437" t="n">
         <v>348774</v>
@@ -13071,7 +13071,7 @@
         <v>7.72499990463257</v>
       </c>
       <c r="G438" t="n">
-        <v>7.13326930999756</v>
+        <v>7.13327026367188</v>
       </c>
       <c r="H438" t="n">
         <v>174564</v>
@@ -13158,7 +13158,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G441" t="n">
-        <v>6.90241956710815</v>
+        <v>6.90242004394531</v>
       </c>
       <c r="H441" t="n">
         <v>154999</v>
@@ -13216,7 +13216,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G443" t="n">
-        <v>6.61616516113281</v>
+        <v>6.61616563796997</v>
       </c>
       <c r="H443" t="n">
         <v>161736</v>
@@ -13245,7 +13245,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G444" t="n">
-        <v>6.61154842376709</v>
+        <v>6.61154890060425</v>
       </c>
       <c r="H444" t="n">
         <v>161687</v>
@@ -13274,7 +13274,7 @@
         <v>7.02500009536743</v>
       </c>
       <c r="G445" t="n">
-        <v>6.48688983917236</v>
+        <v>6.48688936233521</v>
       </c>
       <c r="H445" t="n">
         <v>144224</v>
@@ -13332,7 +13332,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G447" t="n">
-        <v>6.33452844619751</v>
+        <v>6.33452892303467</v>
       </c>
       <c r="H447" t="n">
         <v>231466</v>
@@ -13361,7 +13361,7 @@
         <v>7.13500022888184</v>
       </c>
       <c r="G448" t="n">
-        <v>6.588463306427</v>
+        <v>6.58846378326416</v>
       </c>
       <c r="H448" t="n">
         <v>537214</v>
@@ -13390,7 +13390,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G449" t="n">
-        <v>6.90241956710815</v>
+        <v>6.90242004394531</v>
       </c>
       <c r="H449" t="n">
         <v>615718</v>
@@ -13535,7 +13535,7 @@
         <v>7.40500020980835</v>
       </c>
       <c r="G454" t="n">
-        <v>6.83778190612793</v>
+        <v>6.83778142929077</v>
       </c>
       <c r="H454" t="n">
         <v>250172</v>
@@ -13564,7 +13564,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G455" t="n">
-        <v>6.76390933990479</v>
+        <v>6.76390981674194</v>
       </c>
       <c r="H455" t="n">
         <v>277616</v>
@@ -13593,7 +13593,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G456" t="n">
-        <v>6.76390933990479</v>
+        <v>6.76390981674194</v>
       </c>
       <c r="H456" t="n">
         <v>287013</v>
@@ -13651,7 +13651,7 @@
         <v>7.09499979019165</v>
       </c>
       <c r="G458" t="n">
-        <v>6.55152750015259</v>
+        <v>6.55152702331543</v>
       </c>
       <c r="H458" t="n">
         <v>694126</v>
@@ -13738,7 +13738,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G461" t="n">
-        <v>6.37146472930908</v>
+        <v>6.37146425247192</v>
       </c>
       <c r="H461" t="n">
         <v>296679</v>
@@ -13767,7 +13767,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G462" t="n">
-        <v>6.37146472930908</v>
+        <v>6.37146425247192</v>
       </c>
       <c r="H462" t="n">
         <v>4069866</v>
@@ -13825,7 +13825,7 @@
         <v>6.69500017166138</v>
       </c>
       <c r="G464" t="n">
-        <v>6.18216800689697</v>
+        <v>6.18216753005981</v>
       </c>
       <c r="H464" t="n">
         <v>494430</v>
@@ -13854,7 +13854,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G465" t="n">
-        <v>6.18678379058838</v>
+        <v>6.18678426742554</v>
       </c>
       <c r="H465" t="n">
         <v>200486</v>
@@ -13883,7 +13883,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G466" t="n">
-        <v>5.80819034576416</v>
+        <v>5.808189868927</v>
       </c>
       <c r="H466" t="n">
         <v>501243</v>
@@ -14144,7 +14144,7 @@
         <v>5.82499980926514</v>
       </c>
       <c r="G475" t="n">
-        <v>5.37880849838257</v>
+        <v>5.37880897521973</v>
       </c>
       <c r="H475" t="n">
         <v>758444</v>
@@ -14260,7 +14260,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G479" t="n">
-        <v>5.70661544799805</v>
+        <v>5.70661592483521</v>
       </c>
       <c r="H479" t="n">
         <v>248086</v>
@@ -14289,7 +14289,7 @@
         <v>5.9850001335144</v>
       </c>
       <c r="G480" t="n">
-        <v>5.52655267715454</v>
+        <v>5.5265531539917</v>
       </c>
       <c r="H480" t="n">
         <v>491648</v>
@@ -14434,7 +14434,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G485" t="n">
-        <v>5.17566108703613</v>
+        <v>5.17566013336182</v>
       </c>
       <c r="H485" t="n">
         <v>433667</v>
@@ -14463,7 +14463,7 @@
         <v>5.75</v>
       </c>
       <c r="G486" t="n">
-        <v>5.30955410003662</v>
+        <v>5.30955362319946</v>
       </c>
       <c r="H486" t="n">
         <v>311135</v>
@@ -14492,7 +14492,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G487" t="n">
-        <v>5.06023597717285</v>
+        <v>5.06023550033569</v>
       </c>
       <c r="H487" t="n">
         <v>544541</v>
@@ -14579,7 +14579,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G490" t="n">
-        <v>4.80168342590332</v>
+        <v>4.80168294906616</v>
       </c>
       <c r="H490" t="n">
         <v>392471</v>
@@ -14695,7 +14695,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G494" t="n">
-        <v>4.88478946685791</v>
+        <v>4.88478899002075</v>
       </c>
       <c r="H494" t="n">
         <v>111362</v>
@@ -14724,7 +14724,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G495" t="n">
-        <v>4.88940668106079</v>
+        <v>4.88940620422363</v>
       </c>
       <c r="H495" t="n">
         <v>133883</v>
@@ -14869,7 +14869,7 @@
         <v>5.69500017166138</v>
       </c>
       <c r="G500" t="n">
-        <v>5.25876712799072</v>
+        <v>5.25876665115356</v>
       </c>
       <c r="H500" t="n">
         <v>671518</v>
@@ -15101,7 +15101,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G508" t="n">
-        <v>5.41112756729126</v>
+        <v>5.41112804412842</v>
       </c>
       <c r="H508" t="n">
         <v>222944</v>
@@ -15130,7 +15130,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G509" t="n">
-        <v>5.24491500854492</v>
+        <v>5.24491548538208</v>
       </c>
       <c r="H509" t="n">
         <v>138219</v>
@@ -15159,7 +15159,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G510" t="n">
-        <v>5.21259641647339</v>
+        <v>5.21259689331055</v>
       </c>
       <c r="H510" t="n">
         <v>110937</v>
@@ -15246,7 +15246,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G513" t="n">
-        <v>5.21259641647339</v>
+        <v>5.21259689331055</v>
       </c>
       <c r="H513" t="n">
         <v>215173</v>
@@ -15304,7 +15304,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G515" t="n">
-        <v>5.11563968658447</v>
+        <v>5.11563920974731</v>
       </c>
       <c r="H515" t="n">
         <v>481344</v>
@@ -15391,7 +15391,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G518" t="n">
-        <v>5.24491500854492</v>
+        <v>5.24491548538208</v>
       </c>
       <c r="H518" t="n">
         <v>260768</v>
@@ -15565,7 +15565,7 @@
         <v>5.5</v>
       </c>
       <c r="G524" t="n">
-        <v>5.07870388031006</v>
+        <v>5.0787034034729</v>
       </c>
       <c r="H524" t="n">
         <v>365475</v>
@@ -15652,7 +15652,7 @@
         <v>6.03499984741211</v>
       </c>
       <c r="G527" t="n">
-        <v>5.57272291183472</v>
+        <v>5.57272243499756</v>
       </c>
       <c r="H527" t="n">
         <v>477831</v>
@@ -15826,7 +15826,7 @@
         <v>6.40500020980835</v>
       </c>
       <c r="G533" t="n">
-        <v>5.91438150405884</v>
+        <v>5.91438102722168</v>
       </c>
       <c r="H533" t="n">
         <v>366529</v>
@@ -15884,7 +15884,7 @@
         <v>6.2649998664856</v>
       </c>
       <c r="G535" t="n">
-        <v>5.78510475158691</v>
+        <v>5.78510522842407</v>
       </c>
       <c r="H535" t="n">
         <v>171909</v>
@@ -16000,7 +16000,7 @@
         <v>6.38500022888184</v>
       </c>
       <c r="G539" t="n">
-        <v>5.89591312408447</v>
+        <v>5.89591360092163</v>
       </c>
       <c r="H539" t="n">
         <v>946632</v>
@@ -16029,7 +16029,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G540" t="n">
-        <v>6.03904056549072</v>
+        <v>6.03904008865356</v>
       </c>
       <c r="H540" t="n">
         <v>416492</v>
@@ -16058,7 +16058,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G541" t="n">
-        <v>6.05750846862793</v>
+        <v>6.05750799179077</v>
       </c>
       <c r="H541" t="n">
         <v>374625</v>
@@ -16087,7 +16087,7 @@
         <v>6.57499980926514</v>
       </c>
       <c r="G542" t="n">
-        <v>6.0713586807251</v>
+        <v>6.07135915756226</v>
       </c>
       <c r="H542" t="n">
         <v>267523</v>
@@ -16145,7 +16145,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G544" t="n">
-        <v>5.86359405517578</v>
+        <v>5.86359357833862</v>
       </c>
       <c r="H544" t="n">
         <v>307396</v>
@@ -16348,7 +16348,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G551" t="n">
-        <v>5.70661544799805</v>
+        <v>5.70661592483521</v>
       </c>
       <c r="H551" t="n">
         <v>159509</v>
@@ -16377,7 +16377,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G552" t="n">
-        <v>5.70661544799805</v>
+        <v>5.70661592483521</v>
       </c>
       <c r="H552" t="n">
         <v>128983</v>
@@ -16435,7 +16435,7 @@
         <v>6.29500007629395</v>
       </c>
       <c r="G554" t="n">
-        <v>5.81280660629272</v>
+        <v>5.81280755996704</v>
       </c>
       <c r="H554" t="n">
         <v>151233</v>
@@ -16551,7 +16551,7 @@
         <v>6.0149998664856</v>
       </c>
       <c r="G558" t="n">
-        <v>5.55425453186035</v>
+        <v>5.55425500869751</v>
       </c>
       <c r="H558" t="n">
         <v>206810</v>
@@ -16725,7 +16725,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G564" t="n">
-        <v>5.41112756729126</v>
+        <v>5.41112804412842</v>
       </c>
       <c r="H564" t="n">
         <v>104231</v>
@@ -16928,7 +16928,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G571" t="n">
-        <v>5.17566108703613</v>
+        <v>5.17566013336182</v>
       </c>
       <c r="H571" t="n">
         <v>188694</v>
@@ -17102,7 +17102,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G577" t="n">
-        <v>5.06023597717285</v>
+        <v>5.06023550033569</v>
       </c>
       <c r="H577" t="n">
         <v>490731</v>
@@ -17160,7 +17160,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G579" t="n">
-        <v>5.07408618927002</v>
+        <v>5.07408666610718</v>
       </c>
       <c r="H579" t="n">
         <v>256005</v>
@@ -17247,7 +17247,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G582" t="n">
-        <v>5.30031967163086</v>
+        <v>5.3003191947937</v>
       </c>
       <c r="H582" t="n">
         <v>1080928</v>
@@ -17305,7 +17305,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G584" t="n">
-        <v>5.374192237854</v>
+        <v>5.37419176101685</v>
       </c>
       <c r="H584" t="n">
         <v>450011</v>
@@ -17334,7 +17334,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G585" t="n">
-        <v>5.47576522827148</v>
+        <v>5.47576570510864</v>
       </c>
       <c r="H585" t="n">
         <v>310197</v>
@@ -17392,7 +17392,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G587" t="n">
-        <v>5.5773401260376</v>
+        <v>5.57733917236328</v>
       </c>
       <c r="H587" t="n">
         <v>394516</v>
@@ -17508,7 +17508,7 @@
         <v>5.53499984741211</v>
       </c>
       <c r="G591" t="n">
-        <v>5.11102247238159</v>
+        <v>5.11102199554443</v>
       </c>
       <c r="H591" t="n">
         <v>899330</v>
@@ -17595,7 +17595,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G594" t="n">
-        <v>5.05100154876709</v>
+        <v>5.05100107192993</v>
       </c>
       <c r="H594" t="n">
         <v>677677</v>
@@ -17624,7 +17624,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>4.92172527313232</v>
+        <v>4.92172574996948</v>
       </c>
       <c r="H595" t="n">
         <v>699777</v>
@@ -17711,7 +17711,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G598" t="n">
-        <v>4.8063006401062</v>
+        <v>4.80630016326904</v>
       </c>
       <c r="H598" t="n">
         <v>332805</v>
@@ -17740,7 +17740,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G599" t="n">
-        <v>4.70010900497437</v>
+        <v>4.70010948181152</v>
       </c>
       <c r="H599" t="n">
         <v>555539</v>
@@ -17769,7 +17769,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G600" t="n">
-        <v>4.81091737747192</v>
+        <v>4.81091785430908</v>
       </c>
       <c r="H600" t="n">
         <v>367022</v>
@@ -17798,7 +17798,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G601" t="n">
-        <v>4.77398157119751</v>
+        <v>4.77398109436035</v>
       </c>
       <c r="H601" t="n">
         <v>305751</v>
@@ -17827,7 +17827,7 @@
         <v>5.22499990463257</v>
       </c>
       <c r="G602" t="n">
-        <v>4.82476806640625</v>
+        <v>4.82476854324341</v>
       </c>
       <c r="H602" t="n">
         <v>549261</v>
@@ -17856,7 +17856,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G603" t="n">
-        <v>4.89863967895508</v>
+        <v>4.89864015579224</v>
       </c>
       <c r="H603" t="n">
         <v>510591</v>
@@ -17885,7 +17885,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>4.8063006401062</v>
+        <v>4.80630016326904</v>
       </c>
       <c r="H604" t="n">
         <v>321087</v>
@@ -17914,7 +17914,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G605" t="n">
-        <v>4.66317319869995</v>
+        <v>4.66317367553711</v>
       </c>
       <c r="H605" t="n">
         <v>1112720</v>
@@ -17943,7 +17943,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>4.52466297149658</v>
+        <v>4.52466344833374</v>
       </c>
       <c r="H606" t="n">
         <v>835466</v>
@@ -17972,7 +17972,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G607" t="n">
-        <v>4.52466297149658</v>
+        <v>4.52466344833374</v>
       </c>
       <c r="H607" t="n">
         <v>662577</v>
@@ -18001,7 +18001,7 @@
         <v>4.82200002670288</v>
       </c>
       <c r="G608" t="n">
-        <v>4.45263814926147</v>
+        <v>4.45263767242432</v>
       </c>
       <c r="H608" t="n">
         <v>597938</v>
@@ -18030,7 +18030,7 @@
         <v>4.70800018310547</v>
       </c>
       <c r="G609" t="n">
-        <v>4.34737014770508</v>
+        <v>4.34737062454224</v>
       </c>
       <c r="H609" t="n">
         <v>838204</v>
@@ -18059,7 +18059,7 @@
         <v>4.66400003433228</v>
       </c>
       <c r="G610" t="n">
-        <v>4.30674076080322</v>
+        <v>4.30674028396606</v>
       </c>
       <c r="H610" t="n">
         <v>394307</v>
@@ -18175,7 +18175,7 @@
         <v>4.74399995803833</v>
       </c>
       <c r="G614" t="n">
-        <v>4.38061237335205</v>
+        <v>4.38061285018921</v>
       </c>
       <c r="H614" t="n">
         <v>609563</v>
@@ -18262,7 +18262,7 @@
         <v>4.96600008010864</v>
       </c>
       <c r="G617" t="n">
-        <v>4.58560752868652</v>
+        <v>4.58560800552368</v>
       </c>
       <c r="H617" t="n">
         <v>558256</v>
@@ -18291,7 +18291,7 @@
         <v>5</v>
       </c>
       <c r="G618" t="n">
-        <v>4.61700344085693</v>
+        <v>4.61700296401978</v>
       </c>
       <c r="H618" t="n">
         <v>694400</v>
@@ -18320,7 +18320,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G619" t="n">
-        <v>4.46741199493408</v>
+        <v>4.46741247177124</v>
       </c>
       <c r="H619" t="n">
         <v>402669</v>
@@ -18378,7 +18378,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G621" t="n">
-        <v>4.56898641586304</v>
+        <v>4.56898593902588</v>
       </c>
       <c r="H621" t="n">
         <v>377386</v>
@@ -18494,7 +18494,7 @@
         <v>5.06500005722046</v>
       </c>
       <c r="G625" t="n">
-        <v>4.67702388763428</v>
+        <v>4.67702436447144</v>
       </c>
       <c r="H625" t="n">
         <v>1126607</v>
@@ -18552,7 +18552,7 @@
         <v>4.97800016403198</v>
       </c>
       <c r="G627" t="n">
-        <v>4.59668874740601</v>
+        <v>4.59668827056885</v>
       </c>
       <c r="H627" t="n">
         <v>698215</v>
@@ -18581,7 +18581,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G628" t="n">
-        <v>4.70010900497437</v>
+        <v>4.70010948181152</v>
       </c>
       <c r="H628" t="n">
         <v>666276</v>
@@ -18639,7 +18639,7 @@
         <v>5.0149998664856</v>
       </c>
       <c r="G630" t="n">
-        <v>4.63085412979126</v>
+        <v>4.6308536529541</v>
       </c>
       <c r="H630" t="n">
         <v>580822</v>
@@ -18726,7 +18726,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G633" t="n">
-        <v>4.63421201705933</v>
+        <v>4.63421249389648</v>
       </c>
       <c r="H633" t="n">
         <v>659569</v>
@@ -18900,7 +18900,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G639" t="n">
-        <v>4.47546672821045</v>
+        <v>4.47546625137329</v>
       </c>
       <c r="H639" t="n">
         <v>721270</v>
@@ -18929,7 +18929,7 @@
         <v>4.81199979782104</v>
       </c>
       <c r="G640" t="n">
-        <v>4.60169792175293</v>
+        <v>4.60169744491577</v>
       </c>
       <c r="H640" t="n">
         <v>409298</v>
@@ -19074,7 +19074,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G645" t="n">
-        <v>4.45634031295776</v>
+        <v>4.45634078979492</v>
       </c>
       <c r="H645" t="n">
         <v>337361</v>
@@ -19132,7 +19132,7 @@
         <v>4.62400007247925</v>
       </c>
       <c r="G647" t="n">
-        <v>4.42191457748413</v>
+        <v>4.42191410064697</v>
       </c>
       <c r="H647" t="n">
         <v>590963</v>
@@ -19219,7 +19219,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G650" t="n">
-        <v>4.17136430740356</v>
+        <v>4.17136478424072</v>
       </c>
       <c r="H650" t="n">
         <v>575556</v>
@@ -19306,7 +19306,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G653" t="n">
-        <v>4.20770359039307</v>
+        <v>4.20770406723022</v>
       </c>
       <c r="H653" t="n">
         <v>253568</v>
@@ -19480,7 +19480,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G659" t="n">
-        <v>3.9303777217865</v>
+        <v>3.93037796020508</v>
       </c>
       <c r="H659" t="n">
         <v>499794</v>
@@ -19770,7 +19770,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G669" t="n">
-        <v>3.65496444702148</v>
+        <v>3.65496468544006</v>
       </c>
       <c r="H669" t="n">
         <v>556073</v>
@@ -19857,7 +19857,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G672" t="n">
-        <v>3.81370973587036</v>
+        <v>3.81370949745178</v>
       </c>
       <c r="H672" t="n">
         <v>401105</v>
@@ -19886,7 +19886,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G673" t="n">
-        <v>3.81370973587036</v>
+        <v>3.81370949745178</v>
       </c>
       <c r="H673" t="n">
         <v>294689</v>
@@ -19915,7 +19915,7 @@
         <v>4.17600011825562</v>
       </c>
       <c r="G674" t="n">
-        <v>3.99349331855774</v>
+        <v>3.99349355697632</v>
       </c>
       <c r="H674" t="n">
         <v>714573</v>
@@ -20379,7 +20379,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G690" t="n">
-        <v>3.4560546875</v>
+        <v>3.45605492591858</v>
       </c>
       <c r="H690" t="n">
         <v>383156</v>
@@ -20756,7 +20756,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G703" t="n">
-        <v>3.96862983703613</v>
+        <v>3.96862959861755</v>
       </c>
       <c r="H703" t="n">
         <v>402206</v>
@@ -20785,7 +20785,7 @@
         <v>4.1560001373291</v>
       </c>
       <c r="G704" t="n">
-        <v>3.97436738014221</v>
+        <v>3.97436785697937</v>
       </c>
       <c r="H704" t="n">
         <v>366565</v>
@@ -20843,7 +20843,7 @@
         <v>4.27600002288818</v>
       </c>
       <c r="G706" t="n">
-        <v>4.08912324905396</v>
+        <v>4.0891227722168</v>
       </c>
       <c r="H706" t="n">
         <v>382472</v>
@@ -20872,7 +20872,7 @@
         <v>4.13600015640259</v>
       </c>
       <c r="G707" t="n">
-        <v>3.95524144172668</v>
+        <v>3.95524168014526</v>
       </c>
       <c r="H707" t="n">
         <v>503313</v>
@@ -20930,7 +20930,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G709" t="n">
-        <v>3.98966789245605</v>
+        <v>3.98966813087463</v>
       </c>
       <c r="H709" t="n">
         <v>357159</v>
@@ -21017,7 +21017,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G712" t="n">
-        <v>3.67026543617249</v>
+        <v>3.67026519775391</v>
       </c>
       <c r="H712" t="n">
         <v>437455</v>
@@ -21162,7 +21162,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G717" t="n">
-        <v>3.81370973587036</v>
+        <v>3.81370949745178</v>
       </c>
       <c r="H717" t="n">
         <v>286225</v>
@@ -21191,7 +21191,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G718" t="n">
-        <v>3.82327246665955</v>
+        <v>3.82327270507812</v>
       </c>
       <c r="H718" t="n">
         <v>150642</v>
@@ -21220,7 +21220,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G719" t="n">
-        <v>3.91507720947266</v>
+        <v>3.91507697105408</v>
       </c>
       <c r="H719" t="n">
         <v>372351</v>
@@ -21307,7 +21307,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G722" t="n">
-        <v>3.98584318161011</v>
+        <v>3.98584294319153</v>
       </c>
       <c r="H722" t="n">
         <v>634315</v>
@@ -21365,7 +21365,7 @@
         <v>4.42600011825562</v>
       </c>
       <c r="G724" t="n">
-        <v>4.23256731033325</v>
+        <v>4.23256778717041</v>
       </c>
       <c r="H724" t="n">
         <v>1439555</v>
@@ -21394,7 +21394,7 @@
         <v>4.51200008392334</v>
       </c>
       <c r="G725" t="n">
-        <v>4.31480932235718</v>
+        <v>4.31480884552002</v>
       </c>
       <c r="H725" t="n">
         <v>724657</v>
@@ -21452,7 +21452,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G727" t="n">
-        <v>4.15032577514648</v>
+        <v>4.15032625198364</v>
       </c>
       <c r="H727" t="n">
         <v>336308</v>
@@ -21510,7 +21510,7 @@
         <v>4.25</v>
       </c>
       <c r="G729" t="n">
-        <v>4.06425952911377</v>
+        <v>4.06425905227661</v>
       </c>
       <c r="H729" t="n">
         <v>168991</v>
@@ -21597,7 +21597,7 @@
         <v>4.2039999961853</v>
       </c>
       <c r="G732" t="n">
-        <v>4.02026987075806</v>
+        <v>4.0202693939209</v>
       </c>
       <c r="H732" t="n">
         <v>193502</v>
@@ -21742,7 +21742,7 @@
         <v>4.11399984359741</v>
       </c>
       <c r="G737" t="n">
-        <v>3.9342029094696</v>
+        <v>3.93420267105103</v>
       </c>
       <c r="H737" t="n">
         <v>129269</v>
@@ -21829,7 +21829,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G740" t="n">
-        <v>3.96862983703613</v>
+        <v>3.96862959861755</v>
       </c>
       <c r="H740" t="n">
         <v>236046</v>
@@ -21858,7 +21858,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G741" t="n">
-        <v>3.91507720947266</v>
+        <v>3.91507697105408</v>
       </c>
       <c r="H741" t="n">
         <v>182762</v>
@@ -22061,7 +22061,7 @@
         <v>3.90799999237061</v>
       </c>
       <c r="G748" t="n">
-        <v>3.73720598220825</v>
+        <v>3.73720574378967</v>
       </c>
       <c r="H748" t="n">
         <v>191909</v>
@@ -22119,7 +22119,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G750" t="n">
-        <v>3.70086646080017</v>
+        <v>3.70086669921875</v>
       </c>
       <c r="H750" t="n">
         <v>77185</v>
@@ -22148,7 +22148,7 @@
         <v>3.93799996376038</v>
       </c>
       <c r="G751" t="n">
-        <v>3.76589465141296</v>
+        <v>3.76589488983154</v>
       </c>
       <c r="H751" t="n">
         <v>138045</v>
@@ -22264,7 +22264,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G755" t="n">
-        <v>3.7391185760498</v>
+        <v>3.73911881446838</v>
       </c>
       <c r="H755" t="n">
         <v>208777</v>
@@ -22380,7 +22380,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G759" t="n">
-        <v>3.57846069335938</v>
+        <v>3.57846093177795</v>
       </c>
       <c r="H759" t="n">
         <v>337584</v>
@@ -22409,7 +22409,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G760" t="n">
-        <v>3.62245035171509</v>
+        <v>3.62245059013367</v>
       </c>
       <c r="H760" t="n">
         <v>422072</v>
@@ -22467,7 +22467,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G762" t="n">
-        <v>3.56316018104553</v>
+        <v>3.56315994262695</v>
       </c>
       <c r="H762" t="n">
         <v>704289</v>
@@ -22496,7 +22496,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G763" t="n">
-        <v>3.54785943031311</v>
+        <v>3.54785919189453</v>
       </c>
       <c r="H763" t="n">
         <v>1097480</v>
@@ -22583,7 +22583,7 @@
         <v>3.64800000190735</v>
       </c>
       <c r="G766" t="n">
-        <v>3.4885687828064</v>
+        <v>3.48856902122498</v>
       </c>
       <c r="H766" t="n">
         <v>1669355</v>
@@ -22728,7 +22728,7 @@
         <v>3.64400005340576</v>
       </c>
       <c r="G771" t="n">
-        <v>3.48474383354187</v>
+        <v>3.48474359512329</v>
       </c>
       <c r="H771" t="n">
         <v>105519</v>
@@ -22757,7 +22757,7 @@
         <v>3.63199996948242</v>
       </c>
       <c r="G772" t="n">
-        <v>3.47326803207397</v>
+        <v>3.47326827049255</v>
       </c>
       <c r="H772" t="n">
         <v>121534</v>
@@ -22873,7 +22873,7 @@
         <v>3.95799994468689</v>
       </c>
       <c r="G776" t="n">
-        <v>3.78502058982849</v>
+        <v>3.78502082824707</v>
       </c>
       <c r="H776" t="n">
         <v>243650</v>
@@ -22902,7 +22902,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G777" t="n">
-        <v>3.76972007751465</v>
+        <v>3.76971983909607</v>
       </c>
       <c r="H777" t="n">
         <v>111182</v>
@@ -22960,7 +22960,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G779" t="n">
-        <v>3.70086646080017</v>
+        <v>3.70086669921875</v>
       </c>
       <c r="H779" t="n">
         <v>145693</v>
@@ -22989,7 +22989,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G780" t="n">
-        <v>3.5975866317749</v>
+        <v>3.59758687019348</v>
       </c>
       <c r="H780" t="n">
         <v>157659</v>
@@ -23076,7 +23076,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G783" t="n">
-        <v>3.44075417518616</v>
+        <v>3.44075393676758</v>
       </c>
       <c r="H783" t="n">
         <v>613580</v>
@@ -23105,7 +23105,7 @@
         <v>3.41599988937378</v>
       </c>
       <c r="G784" t="n">
-        <v>3.26670789718628</v>
+        <v>3.26670813560486</v>
       </c>
       <c r="H784" t="n">
         <v>455535</v>
@@ -23134,7 +23134,7 @@
         <v>3.41599988937378</v>
       </c>
       <c r="G785" t="n">
-        <v>3.26670789718628</v>
+        <v>3.26670813560486</v>
       </c>
       <c r="H785" t="n">
         <v>519347</v>
@@ -23163,7 +23163,7 @@
         <v>3.46799993515015</v>
       </c>
       <c r="G786" t="n">
-        <v>3.31643557548523</v>
+        <v>3.31643533706665</v>
       </c>
       <c r="H786" t="n">
         <v>202674</v>
@@ -23192,7 +23192,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G787" t="n">
-        <v>3.29157185554504</v>
+        <v>3.29157161712646</v>
       </c>
       <c r="H787" t="n">
         <v>188696</v>
@@ -23424,7 +23424,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G795" t="n">
-        <v>3.2074179649353</v>
+        <v>3.20741772651672</v>
       </c>
       <c r="H795" t="n">
         <v>383770</v>
@@ -23801,7 +23801,7 @@
         <v>3.47399997711182</v>
       </c>
       <c r="G808" t="n">
-        <v>3.32217311859131</v>
+        <v>3.32217335700989</v>
       </c>
       <c r="H808" t="n">
         <v>80720</v>
@@ -23975,7 +23975,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G814" t="n">
-        <v>3.22654390335083</v>
+        <v>3.22654366493225</v>
       </c>
       <c r="H814" t="n">
         <v>115313</v>
@@ -24149,7 +24149,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G820" t="n">
-        <v>3.55168437957764</v>
+        <v>3.55168461799622</v>
       </c>
       <c r="H820" t="n">
         <v>1031313</v>
@@ -24178,7 +24178,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G821" t="n">
-        <v>3.50769472122192</v>
+        <v>3.5076949596405</v>
       </c>
       <c r="H821" t="n">
         <v>354331</v>
@@ -24236,7 +24236,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G823" t="n">
-        <v>3.53638386726379</v>
+        <v>3.53638362884521</v>
       </c>
       <c r="H823" t="n">
         <v>421877</v>
@@ -24323,7 +24323,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G826" t="n">
-        <v>3.58228611946106</v>
+        <v>3.58228588104248</v>
       </c>
       <c r="H826" t="n">
         <v>258986</v>
@@ -24352,7 +24352,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G827" t="n">
-        <v>3.57654809951782</v>
+        <v>3.5765483379364</v>
       </c>
       <c r="H827" t="n">
         <v>166129</v>
@@ -24381,7 +24381,7 @@
         <v>3.84400010108948</v>
       </c>
       <c r="G828" t="n">
-        <v>3.67600297927856</v>
+        <v>3.67600321769714</v>
       </c>
       <c r="H828" t="n">
         <v>474129</v>
@@ -24526,7 +24526,7 @@
         <v>4.22599983215332</v>
       </c>
       <c r="G833" t="n">
-        <v>4.04130840301514</v>
+        <v>4.04130792617798</v>
       </c>
       <c r="H833" t="n">
         <v>2312238</v>
@@ -24758,7 +24758,7 @@
         <v>4.68599987030029</v>
       </c>
       <c r="G841" t="n">
-        <v>4.48120403289795</v>
+        <v>4.48120450973511</v>
       </c>
       <c r="H841" t="n">
         <v>337090</v>
@@ -24816,7 +24816,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G843" t="n">
-        <v>4.54431962966919</v>
+        <v>4.54432010650635</v>
       </c>
       <c r="H843" t="n">
         <v>212793</v>
@@ -24903,7 +24903,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G846" t="n">
-        <v>4.35688638687134</v>
+        <v>4.35688591003418</v>
       </c>
       <c r="H846" t="n">
         <v>178453</v>
@@ -24932,7 +24932,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G847" t="n">
-        <v>4.2631688117981</v>
+        <v>4.26316928863525</v>
       </c>
       <c r="H847" t="n">
         <v>228223</v>
@@ -24990,7 +24990,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G849" t="n">
-        <v>4.17136430740356</v>
+        <v>4.17136478424072</v>
       </c>
       <c r="H849" t="n">
         <v>216742</v>
@@ -25048,7 +25048,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G851" t="n">
-        <v>3.9303777217865</v>
+        <v>3.93037796020508</v>
       </c>
       <c r="H851" t="n">
         <v>187268</v>
@@ -25135,7 +25135,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G854" t="n">
-        <v>3.77928304672241</v>
+        <v>3.77928280830383</v>
       </c>
       <c r="H854" t="n">
         <v>245578</v>
@@ -25251,7 +25251,7 @@
         <v>3.51200008392334</v>
       </c>
       <c r="G858" t="n">
-        <v>3.35851287841797</v>
+        <v>3.35851263999939</v>
       </c>
       <c r="H858" t="n">
         <v>146055</v>
@@ -25280,7 +25280,7 @@
         <v>3.56800007820129</v>
       </c>
       <c r="G859" t="n">
-        <v>3.41206550598145</v>
+        <v>3.41206526756287</v>
       </c>
       <c r="H859" t="n">
         <v>419236</v>
@@ -25396,7 +25396,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G863" t="n">
-        <v>3.47900605201721</v>
+        <v>3.47900581359863</v>
       </c>
       <c r="H863" t="n">
         <v>215914</v>
@@ -25541,7 +25541,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G868" t="n">
-        <v>3.77928304672241</v>
+        <v>3.77928280830383</v>
       </c>
       <c r="H868" t="n">
         <v>73720</v>
@@ -25657,7 +25657,7 @@
         <v>4.12400007247925</v>
       </c>
       <c r="G872" t="n">
-        <v>3.94376611709595</v>
+        <v>3.94376587867737</v>
       </c>
       <c r="H872" t="n">
         <v>191569</v>
@@ -25860,7 +25860,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G879" t="n">
-        <v>4.47546672821045</v>
+        <v>4.47546625137329</v>
       </c>
       <c r="H879" t="n">
         <v>120035</v>
@@ -25976,7 +25976,7 @@
         <v>4.38800001144409</v>
       </c>
       <c r="G883" t="n">
-        <v>4.19622802734375</v>
+        <v>4.19622850418091</v>
       </c>
       <c r="H883" t="n">
         <v>292289</v>
@@ -26063,7 +26063,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G886" t="n">
-        <v>4.20196628570557</v>
+        <v>4.20196580886841</v>
       </c>
       <c r="H886" t="n">
         <v>132141</v>
@@ -26237,7 +26237,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G892" t="n">
-        <v>4.57109642028809</v>
+        <v>4.57109689712524</v>
       </c>
       <c r="H892" t="n">
         <v>407750</v>
@@ -26295,7 +26295,7 @@
         <v>4.74599981307983</v>
       </c>
       <c r="G894" t="n">
-        <v>4.53858232498169</v>
+        <v>4.53858184814453</v>
       </c>
       <c r="H894" t="n">
         <v>111758</v>
@@ -26324,7 +26324,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G895" t="n">
-        <v>4.68585157394409</v>
+        <v>4.68585205078125</v>
       </c>
       <c r="H895" t="n">
         <v>288639</v>
@@ -36683,6 +36683,35 @@
         <v>565087</v>
       </c>
       <c r="I1252" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1253" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1253" t="n">
+        <v>3.53999996185303</v>
+      </c>
+      <c r="D1253" t="n">
+        <v>3.56399989128113</v>
+      </c>
+      <c r="E1253" t="n">
+        <v>3.4539999961853</v>
+      </c>
+      <c r="F1253" t="n">
+        <v>3.46600008010864</v>
+      </c>
+      <c r="G1253" t="n">
+        <v>3.46600008010864</v>
+      </c>
+      <c r="H1253" t="n">
+        <v>241443</v>
+      </c>
+      <c r="I1253" t="s">
         <v>9</v>
       </c>
     </row>
